--- a/Conlangs/Kagalarian.xlsx
+++ b/Conlangs/Kagalarian.xlsx
@@ -7611,7 +7611,7 @@
     <t>rules</t>
   </si>
   <si>
-    <t>adjectives always agree to gender, except for neuter 3rd person pronouns which use masculine</t>
+    <t>adjectives always agree to gender, except for neuter 3rd person pronouns and abbrevations which use masculine</t>
   </si>
   <si>
     <t>-a and -ta endings</t>
@@ -24363,6 +24363,7 @@
   <mergeCells count="39">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C8:C9"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -24394,7 +24395,6 @@
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C8:C9"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="A15:D15"/>

--- a/Conlangs/Kagalarian.xlsx
+++ b/Conlangs/Kagalarian.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3995" uniqueCount="2651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3997" uniqueCount="2652">
   <si>
     <t>Word</t>
   </si>
@@ -7159,6 +7159,10 @@
   </si>
   <si>
     <t>consonant ending masuline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lemeynelov
+</t>
   </si>
   <si>
     <t>known word endings</t>
@@ -23054,11 +23058,11 @@
         <v>2314</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>2196</v>
+        <v>2315</v>
       </c>
       <c r="D1" s="21"/>
       <c r="E1" s="20" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
@@ -23070,67 +23074,67 @@
       </c>
       <c r="D2" s="21"/>
       <c r="E2" s="20" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="20" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="B3" s="21" t="s">
         <v>253</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="D3" s="21"/>
       <c r="E3" s="20" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="F3" s="20" t="s">
+        <v>2323</v>
+      </c>
+      <c r="G3" s="20" t="s">
         <v>2322</v>
       </c>
-      <c r="G3" s="20" t="s">
-        <v>2321</v>
-      </c>
       <c r="H3" s="20" t="s">
+        <v>2323</v>
+      </c>
+      <c r="I3" s="20" t="s">
         <v>2322</v>
       </c>
-      <c r="I3" s="20" t="s">
-        <v>2321</v>
-      </c>
       <c r="J3" s="20" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="20" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="D4" s="21"/>
       <c r="E4" s="21" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>779</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="H4" s="21" t="s">
         <v>1085</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="J4" s="21" t="s">
         <v>259</v>
@@ -23138,13 +23142,13 @@
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="20" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="21" t="s">
@@ -23154,13 +23158,13 @@
         <v>1091</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>1079</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="J5" s="21" t="s">
         <v>1073</v>
@@ -23172,7 +23176,7 @@
       <c r="C6" s="21"/>
       <c r="D6" s="21"/>
       <c r="E6" s="21" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>1453</v>
@@ -23180,7 +23184,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="21" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="J6" s="21" t="s">
         <v>1374</v>
@@ -23188,20 +23192,20 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="16" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="B7" s="20" t="s">
         <v>1091</v>
       </c>
       <c r="D7" s="24"/>
       <c r="E7" s="21" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>253</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="J7" s="21" t="s">
         <v>3</v>
@@ -23217,7 +23221,7 @@
       <c r="D8" s="21"/>
       <c r="H8" s="24"/>
       <c r="I8" s="21" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="J8" s="21" t="s">
         <v>1092</v>
@@ -23225,24 +23229,24 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="20" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="B9" s="21" t="s">
         <v>1091</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="16" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="F9" s="20" t="s">
         <v>362</v>
       </c>
       <c r="H9" s="24"/>
       <c r="I9" s="21" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="J9" s="21" t="s">
         <v>362</v>
@@ -23250,7 +23254,7 @@
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="20" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="D10" s="24"/>
       <c r="F10" s="20" t="s">
@@ -23261,7 +23265,7 @@
       </c>
       <c r="H10" s="24"/>
       <c r="I10" s="21" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="J10" s="21" t="s">
         <v>890</v>
@@ -23269,27 +23273,27 @@
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="20" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="20" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>362</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="H11" s="25"/>
       <c r="I11" s="21" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="J11" s="21" t="s">
         <v>1057</v>
@@ -23301,11 +23305,11 @@
       <c r="C12" s="24"/>
       <c r="D12" s="24"/>
       <c r="E12" s="20" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="H12" s="25"/>
       <c r="I12" s="21" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="J12" s="21" t="s">
         <v>712</v>
@@ -23313,24 +23317,24 @@
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="16" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="B13" s="20" t="s">
         <v>225</v>
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="20" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="H13" s="21"/>
       <c r="I13" s="21" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="J13" s="21" t="s">
         <v>1061</v>
@@ -23346,7 +23350,7 @@
       <c r="D14" s="24"/>
       <c r="H14" s="21"/>
       <c r="I14" s="21" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="J14" s="21" t="s">
         <v>249</v>
@@ -23354,23 +23358,23 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="B15" s="21" t="s">
         <v>225</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>2276</v>
       </c>
       <c r="H15" s="21"/>
       <c r="I15" s="21" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="J15" s="21" t="s">
         <v>923</v>
@@ -23378,13 +23382,13 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="20" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>2300</v>
@@ -23394,7 +23398,7 @@
       </c>
       <c r="H16" s="25"/>
       <c r="I16" s="21" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="J16" s="21" t="s">
         <v>2276</v>
@@ -23402,22 +23406,22 @@
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="20" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="F17" s="21" t="s">
         <v>2276</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="H17" s="25"/>
       <c r="I17" s="25"/>
@@ -23425,7 +23429,7 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="E18" s="20" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="H18" s="21"/>
       <c r="I18" s="21"/>
@@ -23437,13 +23441,13 @@
       <c r="C19" s="21"/>
       <c r="D19" s="21"/>
       <c r="E19" s="20" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="H19" s="21"/>
     </row>
@@ -23459,7 +23463,7 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="20" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="B21" s="20" t="s">
         <v>2300</v>
@@ -23467,30 +23471,30 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="B22" s="20" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="20" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="B23" s="21" t="s">
         <v>17</v>
@@ -23505,7 +23509,7 @@
         <v>29</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="G23" s="21" t="s">
         <v>1567</v>
@@ -23516,7 +23520,7 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="20" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="B24" s="21" t="s">
         <v>13</v>
@@ -23533,7 +23537,7 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="20" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="B25" s="21" t="s">
         <v>15</v>
@@ -23548,15 +23552,15 @@
         <v>27</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="20" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="B26" s="20" t="s">
         <v>2301</v>
@@ -23564,45 +23568,45 @@
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="B27" s="20" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="20" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="B28" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>41</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="H28" s="21" t="s">
         <v>450</v>
@@ -23610,13 +23614,13 @@
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="20" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="B29" s="21" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="D29" s="21" t="s">
         <v>37</v>
@@ -23624,22 +23628,22 @@
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="20" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="B30" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="D30" s="21" t="s">
         <v>39</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="G30" s="21" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
     </row>
   </sheetData>
@@ -23695,10 +23699,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="20" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="E1" s="24"/>
       <c r="F1" s="25"/>
@@ -23729,11 +23733,11 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="20" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
       <c r="E4" s="24"/>
       <c r="F4" s="20" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="J4" s="21"/>
     </row>
@@ -23750,30 +23754,30 @@
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="16"/>
       <c r="B6" s="20" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="16"/>
       <c r="G6" s="20" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="J6" s="21"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="20" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="B7" s="21" t="s">
         <v>1288</v>
@@ -23782,11 +23786,11 @@
         <v>1288</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="E7" s="24"/>
       <c r="F7" s="20" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="G7" s="21" t="s">
         <v>1513</v>
@@ -23795,33 +23799,33 @@
         <v>1513</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="J7" s="21"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="20" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="20" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="J8" s="21"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="20" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="E9" s="24"/>
       <c r="F9" s="20" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="J9" s="21"/>
     </row>
@@ -23838,144 +23842,150 @@
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="16"/>
       <c r="B11" s="20" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="16"/>
       <c r="G11" s="20" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="J11" s="21"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="20" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="C12" s="21" t="s">
         <v>1288</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="E12" s="24"/>
       <c r="F12" s="20" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="H12" s="21" t="s">
         <v>1513</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="J12" s="21"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="20" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>2389</v>
+        <v>2390</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>2387</v>
       </c>
       <c r="E13" s="24"/>
       <c r="F13" s="20" t="s">
-        <v>2323</v>
+        <v>2324</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>2386</v>
       </c>
       <c r="J13" s="21"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="20" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="E14" s="24"/>
       <c r="F14" s="20" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="J14" s="21"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="E15" s="24"/>
       <c r="F15" s="20" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="J15" s="21"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="20" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="D16" s="27"/>
       <c r="E16" s="24"/>
       <c r="F16" s="20" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
       <c r="H16" s="27"/>
       <c r="J16" s="21"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="20" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="E17" s="24"/>
       <c r="F17" s="20" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="J17" s="21"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="20" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="E18" s="24"/>
       <c r="F18" s="20" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="G18" s="21" t="s">
         <v>1513</v>
@@ -23987,10 +23997,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="20" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="J20" s="21"/>
     </row>
@@ -24006,35 +24016,35 @@
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="16"/>
       <c r="B22" s="20" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="F22" s="16"/>
       <c r="G22" s="20" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="I22" s="20" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="J22" s="21"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="20" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="B23" s="21" t="s">
         <v>714</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="G23" s="21" t="s">
         <v>150</v>
@@ -24043,19 +24053,19 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="20" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="J24" s="21"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="20" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="J25" s="21"/>
     </row>
@@ -24072,37 +24082,37 @@
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="16"/>
       <c r="B27" s="20" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="E27" s="24"/>
       <c r="F27" s="16"/>
       <c r="G27" s="20" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="I27" s="20" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="J27" s="21"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="20" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="B28" s="21" t="s">
         <v>714</v>
       </c>
       <c r="E28" s="24"/>
       <c r="F28" s="20" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="G28" s="21" t="s">
         <v>150</v>
@@ -24111,81 +24121,81 @@
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="20" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="E29" s="24"/>
       <c r="F29" s="20" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="J29" s="21"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="20" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="E30" s="24"/>
       <c r="F30" s="20" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="J30" s="21"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="20" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="E31" s="24"/>
       <c r="F31" s="20" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="J31" s="21"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="20" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="C32" s="27"/>
       <c r="E32" s="24"/>
       <c r="F32" s="20" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="H32" s="27"/>
       <c r="J32" s="21"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="20" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="E33" s="24"/>
       <c r="F33" s="20" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="G33" s="21" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="J33" s="21"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="20" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="E34" s="24"/>
       <c r="F34" s="20" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="G34" s="21" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="J34" s="21"/>
     </row>
@@ -24203,10 +24213,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="20" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="E36" s="24"/>
       <c r="F36" s="25"/>
@@ -24217,16 +24227,16 @@
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="20" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="B37" s="21" t="s">
+        <v>2414</v>
+      </c>
+      <c r="C37" s="20" t="s">
         <v>2413</v>
       </c>
-      <c r="C37" s="20" t="s">
-        <v>2412</v>
-      </c>
       <c r="D37" s="21" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="E37" s="24"/>
       <c r="F37" s="25"/>
@@ -24237,16 +24247,16 @@
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="20" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="E38" s="24"/>
       <c r="F38" s="25"/>
@@ -24257,16 +24267,16 @@
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="20" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="E39" s="24"/>
       <c r="F39" s="25"/>
@@ -24382,10 +24392,10 @@
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="G7:G9"/>
     <mergeCell ref="G12:G14"/>
-    <mergeCell ref="H12:H14"/>
     <mergeCell ref="I12:I14"/>
     <mergeCell ref="F15:I15"/>
     <mergeCell ref="H16:I18"/>
+    <mergeCell ref="H13:H14"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="B23:D25"/>
     <mergeCell ref="A26:D26"/>
@@ -24395,11 +24405,11 @@
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C12:C14"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="D16:D18"/>
     <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C13:C14"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -24417,154 +24427,154 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="20" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="D1" s="20" t="s">
         <v>1084</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="H1" s="20" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="21" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="21" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="21" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>452</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="21" t="s">
+        <v>2443</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>2444</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>2445</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>2446</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>2440</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>2441</v>
+      </c>
+      <c r="H5" s="21" t="s">
         <v>2442</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>2443</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>2444</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>2445</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>2439</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>2440</v>
-      </c>
-      <c r="H5" s="21" t="s">
-        <v>2441</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="21" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="21" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="F7" s="21"/>
       <c r="G7" s="21"/>
@@ -24572,131 +24582,131 @@
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="21" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="21" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="21" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="21" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="21" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="21" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="F13" s="21"/>
       <c r="G13" s="21"/>
@@ -24704,128 +24714,128 @@
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="21" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="21" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="H15" s="21"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="21" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="21" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="21" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="H17" s="21"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="21" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="21" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="H19" s="21"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="21" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>2091</v>
@@ -24837,16 +24847,16 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="21" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
@@ -24855,16 +24865,16 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="21" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="E22" s="21"/>
       <c r="F22" s="21"/>
@@ -24873,16 +24883,16 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="E23" s="21"/>
       <c r="F23" s="21"/>
@@ -24891,16 +24901,16 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
@@ -24909,16 +24919,16 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="E25" s="21"/>
       <c r="F25" s="21"/>
@@ -24927,16 +24937,16 @@
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="E26" s="21"/>
       <c r="F26" s="21"/>
@@ -24945,16 +24955,16 @@
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
@@ -24963,16 +24973,16 @@
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="21" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
@@ -24991,63 +25001,63 @@
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="16" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="H30" s="21"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>2572</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>2578</v>
+        <v>2579</v>
       </c>
     </row>
   </sheetData>
@@ -25085,175 +25095,175 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="28" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="29" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="29" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>2586</v>
+        <v>2587</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>2587</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="29" t="s">
-        <v>2588</v>
+        <v>2589</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>2589</v>
+        <v>2590</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>2590</v>
+        <v>2591</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>2591</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="29" t="s">
-        <v>2592</v>
+        <v>2593</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>2593</v>
+        <v>2594</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>2594</v>
+        <v>2595</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>2595</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="29" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>2598</v>
+        <v>2599</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>2599</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="29" t="s">
-        <v>2600</v>
+        <v>2601</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>2601</v>
+        <v>2602</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>2603</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="29" t="s">
-        <v>2604</v>
+        <v>2605</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>2605</v>
+        <v>2606</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>2607</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="29" t="s">
-        <v>2608</v>
+        <v>2609</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>2609</v>
+        <v>2610</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>2610</v>
+        <v>2611</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>2611</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="29" t="s">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>2607</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="29" t="s">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>2616</v>
+        <v>2617</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>2617</v>
+        <v>2618</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>2618</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="29" t="s">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>2620</v>
+        <v>2621</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>2621</v>
+        <v>2622</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>2622</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="30" t="s">
-        <v>2623</v>
+        <v>2624</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>2624</v>
+        <v>2625</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>2625</v>
+        <v>2626</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>2626</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
@@ -25270,7 +25280,7 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="30" t="s">
-        <v>2627</v>
+        <v>2628</v>
       </c>
       <c r="D15" s="21"/>
       <c r="E15" s="31"/>
@@ -25282,10 +25292,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="21" t="s">
-        <v>2628</v>
+        <v>2629</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>2629</v>
+        <v>2630</v>
       </c>
       <c r="D16" s="21"/>
       <c r="E16" s="31"/>
@@ -25297,10 +25307,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="21" t="s">
-        <v>2630</v>
+        <v>2631</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>2631</v>
+        <v>2632</v>
       </c>
       <c r="D17" s="21"/>
       <c r="E17" s="21"/>
@@ -25312,10 +25322,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="21" t="s">
-        <v>2632</v>
+        <v>2633</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>2633</v>
+        <v>2634</v>
       </c>
       <c r="D18" s="21"/>
       <c r="E18" s="31"/>
@@ -25327,10 +25337,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="21" t="s">
-        <v>2634</v>
+        <v>2635</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>2635</v>
+        <v>2636</v>
       </c>
       <c r="D19" s="21"/>
       <c r="E19" s="31"/>
@@ -25342,10 +25352,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="21" t="s">
-        <v>2636</v>
+        <v>2637</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>2637</v>
+        <v>2638</v>
       </c>
       <c r="D20" s="21"/>
       <c r="E20" s="31"/>
@@ -25369,18 +25379,18 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="28" t="s">
-        <v>2638</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="32" t="s">
-        <v>2639</v>
+        <v>2640</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>2640</v>
+        <v>2641</v>
       </c>
       <c r="G23" s="32" t="s">
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="J23" s="21"/>
     </row>
@@ -25389,37 +25399,37 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="33" t="s">
-        <v>2642</v>
+        <v>2643</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>2643</v>
+        <v>2644</v>
       </c>
       <c r="G25" s="33" t="s">
-        <v>2644</v>
+        <v>2645</v>
       </c>
       <c r="J25" s="21"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="33" t="s">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>2646</v>
+        <v>2647</v>
       </c>
       <c r="G26" s="33" t="s">
-        <v>2647</v>
+        <v>2648</v>
       </c>
       <c r="J26" s="21"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="33" t="s">
-        <v>2648</v>
+        <v>2649</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>2649</v>
+        <v>2650</v>
       </c>
       <c r="G27" s="33" t="s">
-        <v>2650</v>
+        <v>2651</v>
       </c>
       <c r="J27" s="21"/>
     </row>

--- a/Conlangs/Kagalarian.xlsx
+++ b/Conlangs/Kagalarian.xlsx
@@ -11,14 +11,14 @@
     <sheet state="visible" name="Grammar" sheetId="6" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Kagalarian!$A$1:$C$1231</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Kagalarian!$A$1:$C$1233</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4278" uniqueCount="2844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4284" uniqueCount="2848">
   <si>
     <t>Word</t>
   </si>
@@ -4194,6 +4194,18 @@
   </si>
   <si>
     <t>previous, last (indeclinable)</t>
+  </si>
+  <si>
+    <t>printso</t>
+  </si>
+  <si>
+    <t>prince</t>
+  </si>
+  <si>
+    <t>printsya</t>
+  </si>
+  <si>
+    <t>princess</t>
   </si>
   <si>
     <t>srokor</t>
@@ -9346,13 +9358,13 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
@@ -9514,8 +9526,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C1231" displayName="Table1" name="Table1" id="1">
-  <autoFilter ref="$A$1:$C$1231"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C1233" displayName="Table1" name="Table1" id="1">
+  <autoFilter ref="$A$1:$C$1233"/>
   <tableColumns count="3">
     <tableColumn name="Word" id="1"/>
     <tableColumn name="Part of Speech" id="2"/>
@@ -18029,7 +18041,7 @@
         <v>1394</v>
       </c>
       <c r="B694" s="10" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="C694" s="4" t="s">
         <v>1395</v>
@@ -18043,7 +18055,7 @@
       <c r="B695" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C695" s="9" t="s">
+      <c r="C695" s="4" t="s">
         <v>1397</v>
       </c>
       <c r="D695" s="14"/>
@@ -18052,8 +18064,8 @@
       <c r="A696" s="4" t="s">
         <v>1398</v>
       </c>
-      <c r="B696" s="5" t="s">
-        <v>4</v>
+      <c r="B696" s="10" t="s">
+        <v>61</v>
       </c>
       <c r="C696" s="4" t="s">
         <v>1399</v>
@@ -18064,10 +18076,10 @@
       <c r="A697" s="4" t="s">
         <v>1400</v>
       </c>
-      <c r="B697" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C697" s="4" t="s">
+      <c r="B697" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C697" s="9" t="s">
         <v>1401</v>
       </c>
       <c r="D697" s="14"/>
@@ -18076,7 +18088,7 @@
       <c r="A698" s="4" t="s">
         <v>1402</v>
       </c>
-      <c r="B698" s="10" t="s">
+      <c r="B698" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C698" s="4" t="s">
@@ -18085,25 +18097,25 @@
       <c r="D698" s="14"/>
     </row>
     <row r="699" ht="22.5" customHeight="1">
-      <c r="A699" s="9" t="s">
+      <c r="A699" s="4" t="s">
         <v>1404</v>
       </c>
-      <c r="B699" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C699" s="9" t="s">
+      <c r="B699" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C699" s="4" t="s">
         <v>1405</v>
       </c>
       <c r="D699" s="14"/>
     </row>
     <row r="700" ht="22.5" customHeight="1">
-      <c r="A700" s="9" t="s">
+      <c r="A700" s="4" t="s">
         <v>1406</v>
       </c>
       <c r="B700" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C700" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C700" s="4" t="s">
         <v>1407</v>
       </c>
       <c r="D700" s="14"/>
@@ -18112,7 +18124,7 @@
       <c r="A701" s="9" t="s">
         <v>1408</v>
       </c>
-      <c r="B701" s="5" t="s">
+      <c r="B701" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C701" s="9" t="s">
@@ -18121,25 +18133,25 @@
       <c r="D701" s="14"/>
     </row>
     <row r="702" ht="22.5" customHeight="1">
-      <c r="A702" s="4" t="s">
+      <c r="A702" s="9" t="s">
         <v>1410</v>
       </c>
-      <c r="B702" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C702" s="4" t="s">
+      <c r="B702" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C702" s="9" t="s">
         <v>1411</v>
       </c>
       <c r="D702" s="14"/>
     </row>
     <row r="703" ht="22.5" customHeight="1">
-      <c r="A703" s="4" t="s">
+      <c r="A703" s="9" t="s">
         <v>1412</v>
       </c>
-      <c r="B703" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C703" s="4" t="s">
+      <c r="B703" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C703" s="9" t="s">
         <v>1413</v>
       </c>
       <c r="D703" s="14"/>
@@ -18148,7 +18160,7 @@
       <c r="A704" s="4" t="s">
         <v>1414</v>
       </c>
-      <c r="B704" s="7" t="s">
+      <c r="B704" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C704" s="4" t="s">
@@ -18169,13 +18181,13 @@
       <c r="D705" s="14"/>
     </row>
     <row r="706" ht="22.5" customHeight="1">
-      <c r="A706" s="9" t="s">
+      <c r="A706" s="4" t="s">
         <v>1418</v>
       </c>
-      <c r="B706" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C706" s="9" t="s">
+      <c r="B706" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C706" s="4" t="s">
         <v>1419</v>
       </c>
       <c r="D706" s="14"/>
@@ -18193,13 +18205,13 @@
       <c r="D707" s="14"/>
     </row>
     <row r="708" ht="22.5" customHeight="1">
-      <c r="A708" s="4" t="s">
+      <c r="A708" s="9" t="s">
         <v>1422</v>
       </c>
-      <c r="B708" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C708" s="4" t="s">
+      <c r="B708" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C708" s="9" t="s">
         <v>1423</v>
       </c>
       <c r="D708" s="14"/>
@@ -18208,7 +18220,7 @@
       <c r="A709" s="4" t="s">
         <v>1424</v>
       </c>
-      <c r="B709" s="5" t="s">
+      <c r="B709" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C709" s="4" t="s">
@@ -18217,13 +18229,13 @@
       <c r="D709" s="14"/>
     </row>
     <row r="710" ht="22.5" customHeight="1">
-      <c r="A710" s="9" t="s">
+      <c r="A710" s="4" t="s">
         <v>1426</v>
       </c>
-      <c r="B710" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C710" s="9" t="s">
+      <c r="B710" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C710" s="4" t="s">
         <v>1427</v>
       </c>
       <c r="D710" s="14"/>
@@ -18244,8 +18256,8 @@
       <c r="A712" s="9" t="s">
         <v>1430</v>
       </c>
-      <c r="B712" s="7" t="s">
-        <v>61</v>
+      <c r="B712" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C712" s="9" t="s">
         <v>1431</v>
@@ -18265,13 +18277,13 @@
       <c r="D713" s="14"/>
     </row>
     <row r="714" ht="22.5" customHeight="1">
-      <c r="A714" s="4" t="s">
+      <c r="A714" s="9" t="s">
         <v>1434</v>
       </c>
-      <c r="B714" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C714" s="4" t="s">
+      <c r="B714" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C714" s="9" t="s">
         <v>1435</v>
       </c>
       <c r="D714" s="14"/>
@@ -18280,7 +18292,7 @@
       <c r="A715" s="4" t="s">
         <v>1436</v>
       </c>
-      <c r="B715" s="10" t="s">
+      <c r="B715" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C715" s="4" t="s">
@@ -18289,61 +18301,61 @@
       <c r="D715" s="14"/>
     </row>
     <row r="716" ht="22.5" customHeight="1">
-      <c r="A716" s="9" t="s">
+      <c r="A716" s="4" t="s">
         <v>1438</v>
       </c>
-      <c r="B716" s="7" t="s">
+      <c r="B716" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C716" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D716" s="14"/>
+    </row>
+    <row r="717" ht="22.5" customHeight="1">
+      <c r="A717" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B717" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C717" s="4" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D717" s="14"/>
+    </row>
+    <row r="718" ht="22.5" customHeight="1">
+      <c r="A718" s="9" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B718" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C716" s="9" t="s">
-        <v>1439</v>
-      </c>
-      <c r="D716" s="14"/>
-    </row>
-    <row r="717" ht="22.5" customHeight="1">
-      <c r="A717" s="9" t="s">
-        <v>1440</v>
-      </c>
-      <c r="B717" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C717" s="9" t="s">
-        <v>1441</v>
-      </c>
-      <c r="D717" s="14"/>
-    </row>
-    <row r="718" ht="22.5" customHeight="1">
-      <c r="A718" s="4" t="s">
-        <v>1442</v>
-      </c>
-      <c r="B718" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C718" s="4" t="s">
+      <c r="C718" s="9" t="s">
         <v>1443</v>
       </c>
       <c r="D718" s="14"/>
     </row>
     <row r="719" ht="22.5" customHeight="1">
-      <c r="A719" s="4" t="s">
+      <c r="A719" s="9" t="s">
         <v>1444</v>
       </c>
-      <c r="B719" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C719" s="4" t="s">
+      <c r="B719" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C719" s="9" t="s">
         <v>1445</v>
       </c>
       <c r="D719" s="14"/>
     </row>
     <row r="720" ht="22.5" customHeight="1">
-      <c r="A720" s="9" t="s">
+      <c r="A720" s="4" t="s">
         <v>1446</v>
       </c>
       <c r="B720" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C720" s="9" t="s">
+      <c r="C720" s="4" t="s">
         <v>1447</v>
       </c>
       <c r="D720" s="14"/>
@@ -18352,7 +18364,7 @@
       <c r="A721" s="4" t="s">
         <v>1448</v>
       </c>
-      <c r="B721" s="5" t="s">
+      <c r="B721" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C721" s="4" t="s">
@@ -18361,13 +18373,13 @@
       <c r="D721" s="14"/>
     </row>
     <row r="722" ht="22.5" customHeight="1">
-      <c r="A722" s="4" t="s">
+      <c r="A722" s="9" t="s">
         <v>1450</v>
       </c>
-      <c r="B722" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C722" s="4" t="s">
+      <c r="B722" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C722" s="9" t="s">
         <v>1451</v>
       </c>
       <c r="D722" s="14"/>
@@ -18385,25 +18397,25 @@
       <c r="D723" s="14"/>
     </row>
     <row r="724" ht="22.5" customHeight="1">
-      <c r="A724" s="9" t="s">
+      <c r="A724" s="4" t="s">
         <v>1454</v>
       </c>
-      <c r="B724" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C724" s="9" t="s">
+      <c r="B724" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C724" s="4" t="s">
         <v>1455</v>
       </c>
       <c r="D724" s="14"/>
     </row>
     <row r="725" ht="22.5" customHeight="1">
-      <c r="A725" s="9" t="s">
+      <c r="A725" s="4" t="s">
         <v>1456</v>
       </c>
       <c r="B725" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C725" s="9" t="s">
+      <c r="C725" s="4" t="s">
         <v>1457</v>
       </c>
       <c r="D725" s="14"/>
@@ -18421,25 +18433,25 @@
       <c r="D726" s="14"/>
     </row>
     <row r="727" ht="22.5" customHeight="1">
-      <c r="A727" s="4" t="s">
+      <c r="A727" s="9" t="s">
         <v>1460</v>
       </c>
-      <c r="B727" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C727" s="4" t="s">
+      <c r="B727" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C727" s="9" t="s">
         <v>1461</v>
       </c>
       <c r="D727" s="14"/>
     </row>
     <row r="728" ht="22.5" customHeight="1">
-      <c r="A728" s="4" t="s">
+      <c r="A728" s="9" t="s">
         <v>1462</v>
       </c>
-      <c r="B728" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C728" s="4" t="s">
+      <c r="B728" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C728" s="9" t="s">
         <v>1463</v>
       </c>
       <c r="D728" s="14"/>
@@ -18448,7 +18460,7 @@
       <c r="A729" s="4" t="s">
         <v>1464</v>
       </c>
-      <c r="B729" s="5" t="s">
+      <c r="B729" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C729" s="4" t="s">
@@ -18457,7 +18469,7 @@
       <c r="D729" s="14"/>
     </row>
     <row r="730" ht="22.5" customHeight="1">
-      <c r="A730" s="9" t="s">
+      <c r="A730" s="4" t="s">
         <v>1466</v>
       </c>
       <c r="B730" s="10" t="s">
@@ -18469,19 +18481,19 @@
       <c r="D730" s="14"/>
     </row>
     <row r="731" ht="22.5" customHeight="1">
-      <c r="A731" s="9" t="s">
+      <c r="A731" s="4" t="s">
         <v>1468</v>
       </c>
       <c r="B731" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C731" s="9" t="s">
+      <c r="C731" s="4" t="s">
         <v>1469</v>
       </c>
       <c r="D731" s="14"/>
     </row>
     <row r="732" ht="22.5" customHeight="1">
-      <c r="A732" s="4" t="s">
+      <c r="A732" s="9" t="s">
         <v>1470</v>
       </c>
       <c r="B732" s="10" t="s">
@@ -18493,13 +18505,13 @@
       <c r="D732" s="14"/>
     </row>
     <row r="733" ht="22.5" customHeight="1">
-      <c r="A733" s="4" t="s">
+      <c r="A733" s="9" t="s">
         <v>1472</v>
       </c>
       <c r="B733" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C733" s="4" t="s">
+      <c r="C733" s="9" t="s">
         <v>1473</v>
       </c>
       <c r="D733" s="14"/>
@@ -18520,8 +18532,8 @@
       <c r="A735" s="4" t="s">
         <v>1476</v>
       </c>
-      <c r="B735" s="7" t="s">
-        <v>61</v>
+      <c r="B735" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C735" s="4" t="s">
         <v>1477</v>
@@ -18532,8 +18544,8 @@
       <c r="A736" s="4" t="s">
         <v>1478</v>
       </c>
-      <c r="B736" s="7" t="s">
-        <v>69</v>
+      <c r="B736" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C736" s="4" t="s">
         <v>1479</v>
@@ -18544,8 +18556,8 @@
       <c r="A737" s="4" t="s">
         <v>1480</v>
       </c>
-      <c r="B737" s="10" t="s">
-        <v>4</v>
+      <c r="B737" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C737" s="4" t="s">
         <v>1481</v>
@@ -18557,7 +18569,7 @@
         <v>1482</v>
       </c>
       <c r="B738" s="7" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C738" s="4" t="s">
         <v>1483</v>
@@ -18565,37 +18577,37 @@
       <c r="D738" s="14"/>
     </row>
     <row r="739" ht="22.5" customHeight="1">
-      <c r="A739" s="9" t="s">
+      <c r="A739" s="4" t="s">
         <v>1484</v>
       </c>
-      <c r="B739" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C739" s="9" t="s">
+      <c r="B739" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C739" s="4" t="s">
         <v>1485</v>
       </c>
       <c r="D739" s="14"/>
     </row>
     <row r="740" ht="22.5" customHeight="1">
-      <c r="A740" s="9" t="s">
+      <c r="A740" s="4" t="s">
         <v>1486</v>
       </c>
       <c r="B740" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C740" s="9" t="s">
+      <c r="C740" s="4" t="s">
         <v>1487</v>
       </c>
       <c r="D740" s="14"/>
     </row>
     <row r="741" ht="22.5" customHeight="1">
-      <c r="A741" s="4" t="s">
+      <c r="A741" s="9" t="s">
         <v>1488</v>
       </c>
-      <c r="B741" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C741" s="4" t="s">
+      <c r="B741" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C741" s="9" t="s">
         <v>1489</v>
       </c>
       <c r="D741" s="14"/>
@@ -18625,61 +18637,61 @@
       <c r="D743" s="14"/>
     </row>
     <row r="744" ht="22.5" customHeight="1">
-      <c r="A744" s="4" t="s">
+      <c r="A744" s="9" t="s">
         <v>1494</v>
       </c>
       <c r="B744" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C744" s="4" t="s">
+      <c r="C744" s="9" t="s">
         <v>1495</v>
       </c>
       <c r="D744" s="14"/>
     </row>
     <row r="745" ht="22.5" customHeight="1">
-      <c r="A745" s="9" t="s">
+      <c r="A745" s="4" t="s">
         <v>1496</v>
       </c>
-      <c r="B745" s="7" t="s">
+      <c r="B745" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C745" s="4" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D745" s="14"/>
+    </row>
+    <row r="746" ht="22.5" customHeight="1">
+      <c r="A746" s="4" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B746" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C745" s="9" t="s">
-        <v>1497</v>
-      </c>
-      <c r="D745" s="14"/>
-    </row>
-    <row r="746" ht="22.5" customHeight="1">
-      <c r="A746" s="9" t="s">
-        <v>1498</v>
-      </c>
-      <c r="B746" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C746" s="9" t="s">
+      <c r="C746" s="4" t="s">
         <v>1499</v>
       </c>
       <c r="D746" s="14"/>
     </row>
     <row r="747" ht="22.5" customHeight="1">
-      <c r="A747" s="4" t="s">
+      <c r="A747" s="9" t="s">
         <v>1500</v>
       </c>
-      <c r="B747" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C747" s="4" t="s">
+      <c r="B747" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C747" s="9" t="s">
         <v>1501</v>
       </c>
       <c r="D747" s="14"/>
     </row>
     <row r="748" ht="22.5" customHeight="1">
-      <c r="A748" s="4" t="s">
+      <c r="A748" s="9" t="s">
         <v>1502</v>
       </c>
       <c r="B748" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C748" s="4" t="s">
+      <c r="C748" s="9" t="s">
         <v>1503</v>
       </c>
       <c r="D748" s="14"/>
@@ -18688,7 +18700,7 @@
       <c r="A749" s="4" t="s">
         <v>1504</v>
       </c>
-      <c r="B749" s="10" t="s">
+      <c r="B749" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C749" s="4" t="s">
@@ -18700,7 +18712,7 @@
       <c r="A750" s="4" t="s">
         <v>1506</v>
       </c>
-      <c r="B750" s="5" t="s">
+      <c r="B750" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C750" s="4" t="s">
@@ -18721,13 +18733,13 @@
       <c r="D751" s="14"/>
     </row>
     <row r="752" ht="22.5" customHeight="1">
-      <c r="A752" s="9" t="s">
+      <c r="A752" s="4" t="s">
         <v>1510</v>
       </c>
-      <c r="B752" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C752" s="9" t="s">
+      <c r="B752" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C752" s="4" t="s">
         <v>1511</v>
       </c>
       <c r="D752" s="14"/>
@@ -18736,7 +18748,7 @@
       <c r="A753" s="4" t="s">
         <v>1512</v>
       </c>
-      <c r="B753" s="7" t="s">
+      <c r="B753" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C753" s="4" t="s">
@@ -18745,37 +18757,37 @@
       <c r="D753" s="14"/>
     </row>
     <row r="754" ht="22.5" customHeight="1">
-      <c r="A754" s="4" t="s">
+      <c r="A754" s="9" t="s">
         <v>1514</v>
       </c>
       <c r="B754" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C754" s="4" t="s">
+      <c r="C754" s="9" t="s">
         <v>1515</v>
       </c>
       <c r="D754" s="14"/>
     </row>
     <row r="755" ht="22.5" customHeight="1">
-      <c r="A755" s="9" t="s">
+      <c r="A755" s="4" t="s">
         <v>1516</v>
       </c>
-      <c r="B755" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C755" s="9" t="s">
+      <c r="B755" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C755" s="4" t="s">
         <v>1517</v>
       </c>
       <c r="D755" s="14"/>
     </row>
     <row r="756" ht="22.5" customHeight="1">
-      <c r="A756" s="9" t="s">
+      <c r="A756" s="4" t="s">
         <v>1518</v>
       </c>
       <c r="B756" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C756" s="9" t="s">
+      <c r="C756" s="4" t="s">
         <v>1519</v>
       </c>
       <c r="D756" s="14"/>
@@ -18793,13 +18805,13 @@
       <c r="D757" s="14"/>
     </row>
     <row r="758" ht="22.5" customHeight="1">
-      <c r="A758" s="4" t="s">
+      <c r="A758" s="9" t="s">
         <v>1522</v>
       </c>
       <c r="B758" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C758" s="4" t="s">
+      <c r="C758" s="9" t="s">
         <v>1523</v>
       </c>
       <c r="D758" s="14"/>
@@ -18809,7 +18821,7 @@
         <v>1524</v>
       </c>
       <c r="B759" s="10" t="s">
-        <v>579</v>
+        <v>4</v>
       </c>
       <c r="C759" s="9" t="s">
         <v>1525</v>
@@ -18817,25 +18829,25 @@
       <c r="D759" s="14"/>
     </row>
     <row r="760" ht="22.5" customHeight="1">
-      <c r="A760" s="9" t="s">
+      <c r="A760" s="4" t="s">
         <v>1526</v>
       </c>
       <c r="B760" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C760" s="9" t="s">
+      <c r="C760" s="4" t="s">
         <v>1527</v>
       </c>
       <c r="D760" s="14"/>
     </row>
     <row r="761" ht="22.5" customHeight="1">
-      <c r="A761" s="4" t="s">
+      <c r="A761" s="9" t="s">
         <v>1528</v>
       </c>
       <c r="B761" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C761" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="C761" s="9" t="s">
         <v>1529</v>
       </c>
       <c r="D761" s="14"/>
@@ -18844,8 +18856,8 @@
       <c r="A762" s="9" t="s">
         <v>1530</v>
       </c>
-      <c r="B762" s="7" t="s">
-        <v>61</v>
+      <c r="B762" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C762" s="9" t="s">
         <v>1531</v>
@@ -18853,25 +18865,25 @@
       <c r="D762" s="14"/>
     </row>
     <row r="763" ht="22.5" customHeight="1">
-      <c r="A763" s="9" t="s">
+      <c r="A763" s="4" t="s">
         <v>1532</v>
       </c>
       <c r="B763" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C763" s="9" t="s">
+      <c r="C763" s="4" t="s">
         <v>1533</v>
       </c>
       <c r="D763" s="14"/>
     </row>
     <row r="764" ht="22.5" customHeight="1">
-      <c r="A764" s="4" t="s">
+      <c r="A764" s="9" t="s">
         <v>1534</v>
       </c>
-      <c r="B764" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C764" s="4" t="s">
+      <c r="B764" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C764" s="9" t="s">
         <v>1535</v>
       </c>
       <c r="D764" s="14"/>
@@ -18892,7 +18904,7 @@
       <c r="A766" s="4" t="s">
         <v>1538</v>
       </c>
-      <c r="B766" s="10" t="s">
+      <c r="B766" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C766" s="4" t="s">
@@ -18904,7 +18916,7 @@
       <c r="A767" s="9" t="s">
         <v>1540</v>
       </c>
-      <c r="B767" s="5" t="s">
+      <c r="B767" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C767" s="9" t="s">
@@ -18916,8 +18928,8 @@
       <c r="A768" s="4" t="s">
         <v>1542</v>
       </c>
-      <c r="B768" s="7" t="s">
-        <v>61</v>
+      <c r="B768" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C768" s="4" t="s">
         <v>1543</v>
@@ -18940,8 +18952,8 @@
       <c r="A770" s="4" t="s">
         <v>1546</v>
       </c>
-      <c r="B770" s="10" t="s">
-        <v>4</v>
+      <c r="B770" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C770" s="4" t="s">
         <v>1547</v>
@@ -18949,25 +18961,25 @@
       <c r="D770" s="14"/>
     </row>
     <row r="771" ht="22.5" customHeight="1">
-      <c r="A771" s="4" t="s">
+      <c r="A771" s="9" t="s">
         <v>1548</v>
       </c>
       <c r="B771" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C771" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C771" s="9" t="s">
         <v>1549</v>
       </c>
       <c r="D771" s="14"/>
     </row>
     <row r="772" ht="22.5" customHeight="1">
-      <c r="A772" s="9" t="s">
+      <c r="A772" s="4" t="s">
         <v>1550</v>
       </c>
       <c r="B772" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C772" s="9" t="s">
+      <c r="C772" s="4" t="s">
         <v>1551</v>
       </c>
       <c r="D772" s="14"/>
@@ -18976,8 +18988,8 @@
       <c r="A773" s="4" t="s">
         <v>1552</v>
       </c>
-      <c r="B773" s="10" t="s">
-        <v>4</v>
+      <c r="B773" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="C773" s="4" t="s">
         <v>1553</v>
@@ -18985,25 +18997,25 @@
       <c r="D773" s="14"/>
     </row>
     <row r="774" ht="22.5" customHeight="1">
-      <c r="A774" s="4" t="s">
+      <c r="A774" s="9" t="s">
         <v>1554</v>
       </c>
       <c r="B774" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C774" s="4" t="s">
+      <c r="C774" s="9" t="s">
         <v>1555</v>
       </c>
       <c r="D774" s="14"/>
     </row>
     <row r="775" ht="22.5" customHeight="1">
-      <c r="A775" s="9" t="s">
+      <c r="A775" s="4" t="s">
         <v>1556</v>
       </c>
       <c r="B775" s="10" t="s">
-        <v>579</v>
-      </c>
-      <c r="C775" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C775" s="4" t="s">
         <v>1557</v>
       </c>
       <c r="D775" s="14"/>
@@ -19021,13 +19033,13 @@
       <c r="D776" s="14"/>
     </row>
     <row r="777" ht="22.5" customHeight="1">
-      <c r="A777" s="4" t="s">
+      <c r="A777" s="9" t="s">
         <v>1560</v>
       </c>
       <c r="B777" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C777" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="C777" s="9" t="s">
         <v>1561</v>
       </c>
       <c r="D777" s="14"/>
@@ -19049,7 +19061,7 @@
         <v>1564</v>
       </c>
       <c r="B779" s="10" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="C779" s="4" t="s">
         <v>1565</v>
@@ -19057,25 +19069,25 @@
       <c r="D779" s="14"/>
     </row>
     <row r="780" ht="22.5" customHeight="1">
-      <c r="A780" s="9" t="s">
+      <c r="A780" s="4" t="s">
         <v>1566</v>
       </c>
-      <c r="B780" s="7" t="s">
+      <c r="B780" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C780" s="4" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D780" s="14"/>
+    </row>
+    <row r="781" ht="22.5" customHeight="1">
+      <c r="A781" s="4" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B781" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C780" s="9" t="s">
-        <v>1567</v>
-      </c>
-      <c r="D780" s="14"/>
-    </row>
-    <row r="781" ht="22.5" customHeight="1">
-      <c r="A781" s="9" t="s">
-        <v>1568</v>
-      </c>
-      <c r="B781" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C781" s="9" t="s">
+      <c r="C781" s="4" t="s">
         <v>1569</v>
       </c>
       <c r="D781" s="14"/>
@@ -19084,8 +19096,8 @@
       <c r="A782" s="9" t="s">
         <v>1570</v>
       </c>
-      <c r="B782" s="10" t="s">
-        <v>4</v>
+      <c r="B782" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C782" s="9" t="s">
         <v>1571</v>
@@ -19093,37 +19105,37 @@
       <c r="D782" s="14"/>
     </row>
     <row r="783" ht="22.5" customHeight="1">
-      <c r="A783" s="4" t="s">
+      <c r="A783" s="9" t="s">
         <v>1572</v>
       </c>
-      <c r="B783" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C783" s="4" t="s">
+      <c r="B783" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C783" s="9" t="s">
         <v>1573</v>
       </c>
       <c r="D783" s="14"/>
     </row>
     <row r="784" ht="22.5" customHeight="1">
-      <c r="A784" s="4" t="s">
+      <c r="A784" s="9" t="s">
         <v>1574</v>
       </c>
       <c r="B784" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C784" s="4" t="s">
+      <c r="C784" s="9" t="s">
         <v>1575</v>
       </c>
       <c r="D784" s="14"/>
     </row>
     <row r="785" ht="22.5" customHeight="1">
-      <c r="A785" s="9" t="s">
+      <c r="A785" s="4" t="s">
         <v>1576</v>
       </c>
       <c r="B785" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C785" s="9" t="s">
+      <c r="C785" s="4" t="s">
         <v>1577</v>
       </c>
       <c r="D785" s="14"/>
@@ -19144,7 +19156,7 @@
       <c r="A787" s="9" t="s">
         <v>1580</v>
       </c>
-      <c r="B787" s="5" t="s">
+      <c r="B787" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C787" s="9" t="s">
@@ -19156,8 +19168,8 @@
       <c r="A788" s="4" t="s">
         <v>1582</v>
       </c>
-      <c r="B788" s="7" t="s">
-        <v>69</v>
+      <c r="B788" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C788" s="4" t="s">
         <v>1583</v>
@@ -19165,13 +19177,13 @@
       <c r="D788" s="14"/>
     </row>
     <row r="789" ht="22.5" customHeight="1">
-      <c r="A789" s="4" t="s">
+      <c r="A789" s="9" t="s">
         <v>1584</v>
       </c>
-      <c r="B789" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C789" s="4" t="s">
+      <c r="B789" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C789" s="9" t="s">
         <v>1585</v>
       </c>
       <c r="D789" s="14"/>
@@ -19189,37 +19201,37 @@
       <c r="D790" s="14"/>
     </row>
     <row r="791" ht="22.5" customHeight="1">
-      <c r="A791" s="9" t="s">
+      <c r="A791" s="4" t="s">
         <v>1588</v>
       </c>
-      <c r="B791" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C791" s="9" t="s">
+      <c r="B791" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C791" s="4" t="s">
         <v>1589</v>
       </c>
       <c r="D791" s="14"/>
     </row>
     <row r="792" ht="22.5" customHeight="1">
-      <c r="A792" s="9" t="s">
+      <c r="A792" s="4" t="s">
         <v>1590</v>
       </c>
-      <c r="B792" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C792" s="9" t="s">
+      <c r="B792" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C792" s="4" t="s">
         <v>1591</v>
       </c>
       <c r="D792" s="14"/>
     </row>
     <row r="793" ht="22.5" customHeight="1">
-      <c r="A793" s="4" t="s">
+      <c r="A793" s="9" t="s">
         <v>1592</v>
       </c>
       <c r="B793" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C793" s="4" t="s">
+      <c r="C793" s="9" t="s">
         <v>1593</v>
       </c>
       <c r="D793" s="14"/>
@@ -19229,7 +19241,7 @@
         <v>1594</v>
       </c>
       <c r="B794" s="5" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="C794" s="9" t="s">
         <v>1595</v>
@@ -19252,8 +19264,8 @@
       <c r="A796" s="9" t="s">
         <v>1598</v>
       </c>
-      <c r="B796" s="10" t="s">
-        <v>4</v>
+      <c r="B796" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="C796" s="9" t="s">
         <v>1599</v>
@@ -19261,37 +19273,37 @@
       <c r="D796" s="14"/>
     </row>
     <row r="797" ht="22.5" customHeight="1">
-      <c r="A797" s="9" t="s">
+      <c r="A797" s="4" t="s">
         <v>1600</v>
       </c>
-      <c r="B797" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C797" s="9" t="s">
+      <c r="B797" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C797" s="4" t="s">
         <v>1601</v>
       </c>
       <c r="D797" s="14"/>
     </row>
     <row r="798" ht="22.5" customHeight="1">
-      <c r="A798" s="4" t="s">
+      <c r="A798" s="9" t="s">
         <v>1602</v>
       </c>
       <c r="B798" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C798" s="4" t="s">
+      <c r="C798" s="9" t="s">
         <v>1603</v>
       </c>
       <c r="D798" s="14"/>
     </row>
     <row r="799" ht="22.5" customHeight="1">
-      <c r="A799" s="4" t="s">
+      <c r="A799" s="9" t="s">
         <v>1604</v>
       </c>
       <c r="B799" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C799" s="4" t="s">
+      <c r="C799" s="9" t="s">
         <v>1605</v>
       </c>
       <c r="D799" s="14"/>
@@ -19300,7 +19312,7 @@
       <c r="A800" s="4" t="s">
         <v>1606</v>
       </c>
-      <c r="B800" s="5" t="s">
+      <c r="B800" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C800" s="4" t="s">
@@ -19312,8 +19324,8 @@
       <c r="A801" s="4" t="s">
         <v>1608</v>
       </c>
-      <c r="B801" s="5" t="s">
-        <v>61</v>
+      <c r="B801" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C801" s="4" t="s">
         <v>1609</v>
@@ -19324,7 +19336,7 @@
       <c r="A802" s="4" t="s">
         <v>1610</v>
       </c>
-      <c r="B802" s="10" t="s">
+      <c r="B802" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C802" s="4" t="s">
@@ -19336,8 +19348,8 @@
       <c r="A803" s="4" t="s">
         <v>1612</v>
       </c>
-      <c r="B803" s="10" t="s">
-        <v>4</v>
+      <c r="B803" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="C803" s="4" t="s">
         <v>1613</v>
@@ -19348,8 +19360,8 @@
       <c r="A804" s="4" t="s">
         <v>1614</v>
       </c>
-      <c r="B804" s="7" t="s">
-        <v>61</v>
+      <c r="B804" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C804" s="4" t="s">
         <v>1615</v>
@@ -19360,8 +19372,8 @@
       <c r="A805" s="4" t="s">
         <v>1616</v>
       </c>
-      <c r="B805" s="7" t="s">
-        <v>61</v>
+      <c r="B805" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C805" s="4" t="s">
         <v>1617</v>
@@ -19369,97 +19381,97 @@
       <c r="D805" s="14"/>
     </row>
     <row r="806" ht="22.5" customHeight="1">
-      <c r="A806" s="9" t="s">
+      <c r="A806" s="4" t="s">
         <v>1618</v>
       </c>
-      <c r="B806" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C806" s="9" t="s">
+      <c r="B806" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C806" s="4" t="s">
         <v>1619</v>
       </c>
       <c r="D806" s="14"/>
     </row>
     <row r="807" ht="22.5" customHeight="1">
-      <c r="A807" s="9" t="s">
+      <c r="A807" s="4" t="s">
         <v>1620</v>
       </c>
-      <c r="B807" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C807" s="9" t="s">
+      <c r="B807" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C807" s="4" t="s">
         <v>1621</v>
       </c>
       <c r="D807" s="14"/>
     </row>
     <row r="808" ht="22.5" customHeight="1">
-      <c r="A808" s="4" t="s">
+      <c r="A808" s="9" t="s">
         <v>1622</v>
       </c>
       <c r="B808" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C808" s="4" t="s">
+      <c r="C808" s="9" t="s">
         <v>1623</v>
       </c>
       <c r="D808" s="14"/>
     </row>
     <row r="809" ht="22.5" customHeight="1">
-      <c r="A809" s="4" t="s">
+      <c r="A809" s="9" t="s">
         <v>1624</v>
       </c>
       <c r="B809" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C809" s="4" t="s">
+      <c r="C809" s="9" t="s">
         <v>1625</v>
       </c>
       <c r="D809" s="14"/>
     </row>
     <row r="810" ht="22.5" customHeight="1">
-      <c r="A810" s="9" t="s">
+      <c r="A810" s="4" t="s">
         <v>1626</v>
       </c>
-      <c r="B810" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C810" s="9" t="s">
+      <c r="B810" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C810" s="4" t="s">
         <v>1627</v>
       </c>
       <c r="D810" s="14"/>
     </row>
     <row r="811" ht="22.5" customHeight="1">
-      <c r="A811" s="9" t="s">
+      <c r="A811" s="4" t="s">
         <v>1628</v>
       </c>
-      <c r="B811" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C811" s="9" t="s">
+      <c r="B811" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C811" s="4" t="s">
         <v>1629</v>
       </c>
       <c r="D811" s="14"/>
     </row>
     <row r="812" ht="22.5" customHeight="1">
-      <c r="A812" s="4" t="s">
+      <c r="A812" s="9" t="s">
         <v>1630</v>
       </c>
-      <c r="B812" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C812" s="4" t="s">
+      <c r="B812" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C812" s="9" t="s">
         <v>1631</v>
       </c>
       <c r="D812" s="14"/>
     </row>
     <row r="813" ht="22.5" customHeight="1">
-      <c r="A813" s="4" t="s">
+      <c r="A813" s="9" t="s">
         <v>1632</v>
       </c>
-      <c r="B813" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C813" s="4" t="s">
+      <c r="B813" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C813" s="9" t="s">
         <v>1633</v>
       </c>
       <c r="D813" s="14"/>
@@ -19480,8 +19492,8 @@
       <c r="A815" s="4" t="s">
         <v>1636</v>
       </c>
-      <c r="B815" s="5" t="s">
-        <v>4</v>
+      <c r="B815" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C815" s="4" t="s">
         <v>1637</v>
@@ -19504,8 +19516,8 @@
       <c r="A817" s="4" t="s">
         <v>1640</v>
       </c>
-      <c r="B817" s="10" t="s">
-        <v>61</v>
+      <c r="B817" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C817" s="4" t="s">
         <v>1641</v>
@@ -19513,13 +19525,13 @@
       <c r="D817" s="14"/>
     </row>
     <row r="818" ht="22.5" customHeight="1">
-      <c r="A818" s="9" t="s">
+      <c r="A818" s="4" t="s">
         <v>1642</v>
       </c>
-      <c r="B818" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C818" s="9" t="s">
+      <c r="B818" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C818" s="4" t="s">
         <v>1643</v>
       </c>
       <c r="D818" s="14"/>
@@ -19529,7 +19541,7 @@
         <v>1644</v>
       </c>
       <c r="B819" s="10" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C819" s="4" t="s">
         <v>1645</v>
@@ -19561,13 +19573,13 @@
       <c r="D821" s="14"/>
     </row>
     <row r="822" ht="22.5" customHeight="1">
-      <c r="A822" s="4" t="s">
+      <c r="A822" s="9" t="s">
         <v>1650</v>
       </c>
-      <c r="B822" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C822" s="4" t="s">
+      <c r="B822" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C822" s="9" t="s">
         <v>1651</v>
       </c>
       <c r="D822" s="14"/>
@@ -19576,8 +19588,8 @@
       <c r="A823" s="4" t="s">
         <v>1652</v>
       </c>
-      <c r="B823" s="7" t="s">
-        <v>61</v>
+      <c r="B823" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C823" s="4" t="s">
         <v>1653</v>
@@ -19585,13 +19597,13 @@
       <c r="D823" s="14"/>
     </row>
     <row r="824" ht="22.5" customHeight="1">
-      <c r="A824" s="9" t="s">
+      <c r="A824" s="4" t="s">
         <v>1654</v>
       </c>
-      <c r="B824" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C824" s="9" t="s">
+      <c r="B824" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C824" s="4" t="s">
         <v>1655</v>
       </c>
       <c r="D824" s="14"/>
@@ -19600,8 +19612,8 @@
       <c r="A825" s="4" t="s">
         <v>1656</v>
       </c>
-      <c r="B825" s="10" t="s">
-        <v>4</v>
+      <c r="B825" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C825" s="4" t="s">
         <v>1657</v>
@@ -19633,13 +19645,13 @@
       <c r="D827" s="14"/>
     </row>
     <row r="828" ht="22.5" customHeight="1">
-      <c r="A828" s="4" t="s">
+      <c r="A828" s="9" t="s">
         <v>1662</v>
       </c>
-      <c r="B828" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C828" s="4" t="s">
+      <c r="B828" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C828" s="9" t="s">
         <v>1663</v>
       </c>
       <c r="D828" s="14"/>
@@ -19648,7 +19660,7 @@
       <c r="A829" s="4" t="s">
         <v>1664</v>
       </c>
-      <c r="B829" s="5" t="s">
+      <c r="B829" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C829" s="4" t="s">
@@ -19660,7 +19672,7 @@
       <c r="A830" s="4" t="s">
         <v>1666</v>
       </c>
-      <c r="B830" s="7" t="s">
+      <c r="B830" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C830" s="4" t="s">
@@ -19669,49 +19681,49 @@
       <c r="D830" s="14"/>
     </row>
     <row r="831" ht="22.5" customHeight="1">
-      <c r="A831" s="9" t="s">
+      <c r="A831" s="4" t="s">
         <v>1668</v>
       </c>
       <c r="B831" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C831" s="9" t="s">
+      <c r="C831" s="4" t="s">
         <v>1669</v>
       </c>
       <c r="D831" s="14"/>
     </row>
     <row r="832" ht="22.5" customHeight="1">
-      <c r="A832" s="9" t="s">
+      <c r="A832" s="4" t="s">
         <v>1670</v>
       </c>
       <c r="B832" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C832" s="9" t="s">
+      <c r="C832" s="4" t="s">
         <v>1671</v>
       </c>
       <c r="D832" s="14"/>
     </row>
     <row r="833" ht="22.5" customHeight="1">
-      <c r="A833" s="4" t="s">
+      <c r="A833" s="9" t="s">
         <v>1672</v>
       </c>
-      <c r="B833" s="7" t="s">
+      <c r="B833" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C833" s="9" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D833" s="14"/>
+    </row>
+    <row r="834" ht="22.5" customHeight="1">
+      <c r="A834" s="9" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B834" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C833" s="4" t="s">
-        <v>1673</v>
-      </c>
-      <c r="D833" s="14"/>
-    </row>
-    <row r="834" ht="22.5" customHeight="1">
-      <c r="A834" s="15" t="s">
-        <v>1674</v>
-      </c>
-      <c r="B834" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C834" s="15" t="s">
+      <c r="C834" s="9" t="s">
         <v>1675</v>
       </c>
       <c r="D834" s="14"/>
@@ -19720,8 +19732,8 @@
       <c r="A835" s="4" t="s">
         <v>1676</v>
       </c>
-      <c r="B835" s="10" t="s">
-        <v>4</v>
+      <c r="B835" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C835" s="4" t="s">
         <v>1677</v>
@@ -19729,25 +19741,25 @@
       <c r="D835" s="14"/>
     </row>
     <row r="836" ht="22.5" customHeight="1">
-      <c r="A836" s="4" t="s">
+      <c r="A836" s="15" t="s">
         <v>1678</v>
       </c>
-      <c r="B836" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C836" s="4" t="s">
+      <c r="B836" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C836" s="15" t="s">
         <v>1679</v>
       </c>
       <c r="D836" s="14"/>
     </row>
     <row r="837" ht="22.5" customHeight="1">
-      <c r="A837" s="9" t="s">
+      <c r="A837" s="4" t="s">
         <v>1680</v>
       </c>
       <c r="B837" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C837" s="9" t="s">
+      <c r="C837" s="4" t="s">
         <v>1681</v>
       </c>
       <c r="D837" s="14"/>
@@ -19756,8 +19768,8 @@
       <c r="A838" s="4" t="s">
         <v>1682</v>
       </c>
-      <c r="B838" s="10" t="s">
-        <v>120</v>
+      <c r="B838" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C838" s="4" t="s">
         <v>1683</v>
@@ -19765,25 +19777,25 @@
       <c r="D838" s="14"/>
     </row>
     <row r="839" ht="22.5" customHeight="1">
-      <c r="A839" s="4" t="s">
+      <c r="A839" s="9" t="s">
         <v>1684</v>
       </c>
       <c r="B839" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C839" s="4" t="s">
+      <c r="C839" s="9" t="s">
         <v>1685</v>
       </c>
       <c r="D839" s="14"/>
     </row>
     <row r="840" ht="22.5" customHeight="1">
-      <c r="A840" s="9" t="s">
+      <c r="A840" s="4" t="s">
         <v>1686</v>
       </c>
-      <c r="B840" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C840" s="9" t="s">
+      <c r="B840" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C840" s="4" t="s">
         <v>1687</v>
       </c>
       <c r="D840" s="14"/>
@@ -19792,8 +19804,8 @@
       <c r="A841" s="4" t="s">
         <v>1688</v>
       </c>
-      <c r="B841" s="7" t="s">
-        <v>46</v>
+      <c r="B841" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C841" s="4" t="s">
         <v>1689</v>
@@ -19801,25 +19813,25 @@
       <c r="D841" s="14"/>
     </row>
     <row r="842" ht="22.5" customHeight="1">
-      <c r="A842" s="4" t="s">
+      <c r="A842" s="9" t="s">
         <v>1690</v>
       </c>
-      <c r="B842" s="7" t="s">
+      <c r="B842" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C842" s="9" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D842" s="14"/>
+    </row>
+    <row r="843" ht="22.5" customHeight="1">
+      <c r="A843" s="4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B843" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C842" s="4" t="s">
-        <v>1691</v>
-      </c>
-      <c r="D842" s="14"/>
-    </row>
-    <row r="843" ht="22.5" customHeight="1">
-      <c r="A843" s="9" t="s">
-        <v>1692</v>
-      </c>
-      <c r="B843" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C843" s="9" t="s">
+      <c r="C843" s="4" t="s">
         <v>1693</v>
       </c>
       <c r="D843" s="14"/>
@@ -19828,8 +19840,8 @@
       <c r="A844" s="4" t="s">
         <v>1694</v>
       </c>
-      <c r="B844" s="5" t="s">
-        <v>4</v>
+      <c r="B844" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="C844" s="4" t="s">
         <v>1695</v>
@@ -19837,13 +19849,13 @@
       <c r="D844" s="14"/>
     </row>
     <row r="845" ht="22.5" customHeight="1">
-      <c r="A845" s="4" t="s">
+      <c r="A845" s="9" t="s">
         <v>1696</v>
       </c>
-      <c r="B845" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C845" s="4" t="s">
+      <c r="B845" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C845" s="9" t="s">
         <v>1697</v>
       </c>
       <c r="D845" s="14"/>
@@ -19852,7 +19864,7 @@
       <c r="A846" s="4" t="s">
         <v>1698</v>
       </c>
-      <c r="B846" s="10" t="s">
+      <c r="B846" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C846" s="4" t="s">
@@ -19861,25 +19873,25 @@
       <c r="D846" s="14"/>
     </row>
     <row r="847" ht="22.5" customHeight="1">
-      <c r="A847" s="9" t="s">
+      <c r="A847" s="4" t="s">
         <v>1700</v>
       </c>
-      <c r="B847" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C847" s="9" t="s">
+      <c r="B847" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C847" s="4" t="s">
         <v>1701</v>
       </c>
       <c r="D847" s="14"/>
     </row>
     <row r="848" ht="22.5" customHeight="1">
-      <c r="A848" s="9" t="s">
+      <c r="A848" s="4" t="s">
         <v>1702</v>
       </c>
       <c r="B848" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C848" s="9" t="s">
+      <c r="C848" s="4" t="s">
         <v>1703</v>
       </c>
       <c r="D848" s="14"/>
@@ -19888,7 +19900,7 @@
       <c r="A849" s="9" t="s">
         <v>1704</v>
       </c>
-      <c r="B849" s="5" t="s">
+      <c r="B849" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C849" s="9" t="s">
@@ -19897,37 +19909,37 @@
       <c r="D849" s="14"/>
     </row>
     <row r="850" ht="22.5" customHeight="1">
-      <c r="A850" s="4" t="s">
+      <c r="A850" s="9" t="s">
         <v>1706</v>
       </c>
       <c r="B850" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C850" s="4" t="s">
+      <c r="C850" s="9" t="s">
         <v>1707</v>
       </c>
       <c r="D850" s="14"/>
     </row>
     <row r="851" ht="22.5" customHeight="1">
-      <c r="A851" s="4" t="s">
+      <c r="A851" s="9" t="s">
         <v>1708</v>
       </c>
-      <c r="B851" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C851" s="4" t="s">
+      <c r="B851" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C851" s="9" t="s">
         <v>1709</v>
       </c>
       <c r="D851" s="14"/>
     </row>
     <row r="852" ht="22.5" customHeight="1">
-      <c r="A852" s="9" t="s">
+      <c r="A852" s="4" t="s">
         <v>1710</v>
       </c>
       <c r="B852" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C852" s="9" t="s">
+      <c r="C852" s="4" t="s">
         <v>1711</v>
       </c>
       <c r="D852" s="14"/>
@@ -19937,7 +19949,7 @@
         <v>1712</v>
       </c>
       <c r="B853" s="7" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C853" s="4" t="s">
         <v>1713</v>
@@ -19945,22 +19957,22 @@
       <c r="D853" s="14"/>
     </row>
     <row r="854" ht="22.5" customHeight="1">
-      <c r="A854" s="4" t="s">
+      <c r="A854" s="9" t="s">
         <v>1714</v>
       </c>
       <c r="B854" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C854" s="4" t="s">
+      <c r="C854" s="9" t="s">
         <v>1715</v>
       </c>
       <c r="D854" s="14"/>
     </row>
     <row r="855" ht="22.5" customHeight="1">
-      <c r="A855" s="9" t="s">
+      <c r="A855" s="4" t="s">
         <v>1716</v>
       </c>
-      <c r="B855" s="10" t="s">
+      <c r="B855" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C855" s="4" t="s">
@@ -19969,13 +19981,13 @@
       <c r="D855" s="14"/>
     </row>
     <row r="856" ht="22.5" customHeight="1">
-      <c r="A856" s="9" t="s">
+      <c r="A856" s="4" t="s">
         <v>1718</v>
       </c>
-      <c r="B856" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C856" s="9" t="s">
+      <c r="B856" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C856" s="4" t="s">
         <v>1719</v>
       </c>
       <c r="D856" s="14"/>
@@ -19987,7 +19999,7 @@
       <c r="B857" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C857" s="9" t="s">
+      <c r="C857" s="4" t="s">
         <v>1721</v>
       </c>
       <c r="D857" s="14"/>
@@ -19996,7 +20008,7 @@
       <c r="A858" s="9" t="s">
         <v>1722</v>
       </c>
-      <c r="B858" s="10" t="s">
+      <c r="B858" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C858" s="9" t="s">
@@ -20009,7 +20021,7 @@
         <v>1724</v>
       </c>
       <c r="B859" s="10" t="s">
-        <v>579</v>
+        <v>4</v>
       </c>
       <c r="C859" s="9" t="s">
         <v>1725</v>
@@ -20017,13 +20029,13 @@
       <c r="D859" s="14"/>
     </row>
     <row r="860" ht="22.5" customHeight="1">
-      <c r="A860" s="4" t="s">
+      <c r="A860" s="9" t="s">
         <v>1726</v>
       </c>
       <c r="B860" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C860" s="4" t="s">
+      <c r="C860" s="9" t="s">
         <v>1727</v>
       </c>
       <c r="D860" s="14"/>
@@ -20032,8 +20044,8 @@
       <c r="A861" s="9" t="s">
         <v>1728</v>
       </c>
-      <c r="B861" s="5" t="s">
-        <v>4</v>
+      <c r="B861" s="10" t="s">
+        <v>579</v>
       </c>
       <c r="C861" s="9" t="s">
         <v>1729</v>
@@ -20044,8 +20056,8 @@
       <c r="A862" s="4" t="s">
         <v>1730</v>
       </c>
-      <c r="B862" s="7" t="s">
-        <v>107</v>
+      <c r="B862" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C862" s="4" t="s">
         <v>1731</v>
@@ -20053,13 +20065,13 @@
       <c r="D862" s="14"/>
     </row>
     <row r="863" ht="22.5" customHeight="1">
-      <c r="A863" s="4" t="s">
+      <c r="A863" s="9" t="s">
         <v>1732</v>
       </c>
-      <c r="B863" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C863" s="4" t="s">
+      <c r="B863" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C863" s="9" t="s">
         <v>1733</v>
       </c>
       <c r="D863" s="14"/>
@@ -20068,8 +20080,8 @@
       <c r="A864" s="4" t="s">
         <v>1734</v>
       </c>
-      <c r="B864" s="5" t="s">
-        <v>4</v>
+      <c r="B864" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="C864" s="4" t="s">
         <v>1735</v>
@@ -20077,13 +20089,13 @@
       <c r="D864" s="14"/>
     </row>
     <row r="865" ht="22.5" customHeight="1">
-      <c r="A865" s="9" t="s">
+      <c r="A865" s="4" t="s">
         <v>1736</v>
       </c>
       <c r="B865" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C865" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C865" s="4" t="s">
         <v>1737</v>
       </c>
       <c r="D865" s="14"/>
@@ -20092,8 +20104,8 @@
       <c r="A866" s="4" t="s">
         <v>1738</v>
       </c>
-      <c r="B866" s="7" t="s">
-        <v>107</v>
+      <c r="B866" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C866" s="4" t="s">
         <v>1739</v>
@@ -20101,11 +20113,11 @@
       <c r="D866" s="14"/>
     </row>
     <row r="867" ht="22.5" customHeight="1">
-      <c r="A867" s="4" t="s">
+      <c r="A867" s="9" t="s">
         <v>1740</v>
       </c>
-      <c r="B867" s="7" t="s">
-        <v>210</v>
+      <c r="B867" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C867" s="9" t="s">
         <v>1741</v>
@@ -20117,7 +20129,7 @@
         <v>1742</v>
       </c>
       <c r="B868" s="7" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="C868" s="4" t="s">
         <v>1743</v>
@@ -20128,58 +20140,58 @@
       <c r="A869" s="4" t="s">
         <v>1744</v>
       </c>
-      <c r="B869" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C869" s="4" t="s">
+      <c r="B869" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C869" s="9" t="s">
         <v>1745</v>
       </c>
       <c r="D869" s="14"/>
     </row>
     <row r="870" ht="22.5" customHeight="1">
-      <c r="A870" s="9" t="s">
+      <c r="A870" s="4" t="s">
         <v>1746</v>
       </c>
-      <c r="B870" s="10" t="s">
+      <c r="B870" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C870" s="4" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D870" s="14"/>
+    </row>
+    <row r="871" ht="22.5" customHeight="1">
+      <c r="A871" s="4" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B871" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C871" s="4" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D871" s="14"/>
+    </row>
+    <row r="872" ht="22.5" customHeight="1">
+      <c r="A872" s="9" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B872" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="C870" s="9" t="s">
-        <v>1747</v>
-      </c>
-      <c r="D870" s="14"/>
-    </row>
-    <row r="871" ht="22.5" customHeight="1">
-      <c r="A871" s="9" t="s">
-        <v>1748</v>
-      </c>
-      <c r="B871" s="10" t="s">
+      <c r="C872" s="9" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D872" s="14"/>
+    </row>
+    <row r="873" ht="22.5" customHeight="1">
+      <c r="A873" s="9" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B873" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="C871" s="9" t="s">
-        <v>1749</v>
-      </c>
-      <c r="D871" s="14"/>
-    </row>
-    <row r="872" ht="22.5" customHeight="1">
-      <c r="A872" s="4" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B872" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C872" s="4" t="s">
-        <v>1751</v>
-      </c>
-      <c r="D872" s="14"/>
-    </row>
-    <row r="873" ht="22.5" customHeight="1">
-      <c r="A873" s="4" t="s">
-        <v>1752</v>
-      </c>
-      <c r="B873" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C873" s="4" t="s">
+      <c r="C873" s="9" t="s">
         <v>1753</v>
       </c>
       <c r="D873" s="14"/>
@@ -20189,7 +20201,7 @@
         <v>1754</v>
       </c>
       <c r="B874" s="10" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="C874" s="4" t="s">
         <v>1755</v>
@@ -20197,13 +20209,13 @@
       <c r="D874" s="14"/>
     </row>
     <row r="875" ht="22.5" customHeight="1">
-      <c r="A875" s="9" t="s">
+      <c r="A875" s="4" t="s">
         <v>1756</v>
       </c>
-      <c r="B875" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C875" s="9" t="s">
+      <c r="B875" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C875" s="4" t="s">
         <v>1757</v>
       </c>
       <c r="D875" s="14"/>
@@ -20213,7 +20225,7 @@
         <v>1758</v>
       </c>
       <c r="B876" s="10" t="s">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="C876" s="4" t="s">
         <v>1759</v>
@@ -20221,13 +20233,13 @@
       <c r="D876" s="14"/>
     </row>
     <row r="877" ht="22.5" customHeight="1">
-      <c r="A877" s="4" t="s">
+      <c r="A877" s="9" t="s">
         <v>1760</v>
       </c>
       <c r="B877" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C877" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C877" s="9" t="s">
         <v>1761</v>
       </c>
       <c r="D877" s="14"/>
@@ -20245,49 +20257,49 @@
       <c r="D878" s="14"/>
     </row>
     <row r="879" ht="22.5" customHeight="1">
-      <c r="A879" s="9" t="s">
+      <c r="A879" s="4" t="s">
         <v>1764</v>
       </c>
       <c r="B879" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C879" s="9" t="s">
+      <c r="C879" s="4" t="s">
         <v>1765</v>
       </c>
       <c r="D879" s="14"/>
     </row>
     <row r="880" ht="22.5" customHeight="1">
-      <c r="A880" s="9" t="s">
+      <c r="A880" s="4" t="s">
         <v>1766</v>
       </c>
       <c r="B880" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C880" s="9" t="s">
+      <c r="C880" s="4" t="s">
         <v>1767</v>
       </c>
       <c r="D880" s="14"/>
     </row>
     <row r="881" ht="22.5" customHeight="1">
-      <c r="A881" s="4" t="s">
+      <c r="A881" s="9" t="s">
         <v>1768</v>
       </c>
       <c r="B881" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C881" s="4" t="s">
+      <c r="C881" s="9" t="s">
         <v>1769</v>
       </c>
       <c r="D881" s="14"/>
     </row>
     <row r="882" ht="22.5" customHeight="1">
-      <c r="A882" s="4" t="s">
+      <c r="A882" s="9" t="s">
         <v>1770</v>
       </c>
       <c r="B882" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C882" s="4" t="s">
+      <c r="C882" s="9" t="s">
         <v>1771</v>
       </c>
       <c r="D882" s="14"/>
@@ -20305,13 +20317,13 @@
       <c r="D883" s="14"/>
     </row>
     <row r="884" ht="22.5" customHeight="1">
-      <c r="A884" s="9" t="s">
+      <c r="A884" s="4" t="s">
         <v>1774</v>
       </c>
       <c r="B884" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C884" s="9" t="s">
+      <c r="C884" s="4" t="s">
         <v>1775</v>
       </c>
       <c r="D884" s="14"/>
@@ -20365,37 +20377,37 @@
       <c r="D888" s="14"/>
     </row>
     <row r="889" ht="22.5" customHeight="1">
-      <c r="A889" s="9" t="s">
+      <c r="A889" s="4" t="s">
         <v>1784</v>
       </c>
       <c r="B889" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C889" s="9" t="s">
+      <c r="C889" s="4" t="s">
         <v>1785</v>
       </c>
       <c r="D889" s="14"/>
     </row>
     <row r="890" ht="22.5" customHeight="1">
-      <c r="A890" s="4" t="s">
+      <c r="A890" s="9" t="s">
         <v>1786</v>
       </c>
       <c r="B890" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C890" s="4" t="s">
+      <c r="C890" s="9" t="s">
         <v>1787</v>
       </c>
       <c r="D890" s="14"/>
     </row>
     <row r="891" ht="22.5" customHeight="1">
-      <c r="A891" s="4" t="s">
+      <c r="A891" s="9" t="s">
         <v>1788</v>
       </c>
       <c r="B891" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C891" s="4" t="s">
+      <c r="C891" s="9" t="s">
         <v>1789</v>
       </c>
       <c r="D891" s="14"/>
@@ -20437,13 +20449,13 @@
       <c r="D894" s="14"/>
     </row>
     <row r="895" ht="22.5" customHeight="1">
-      <c r="A895" s="9" t="s">
+      <c r="A895" s="4" t="s">
         <v>1796</v>
       </c>
       <c r="B895" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C895" s="9" t="s">
+      <c r="C895" s="4" t="s">
         <v>1797</v>
       </c>
       <c r="D895" s="14"/>
@@ -20461,13 +20473,13 @@
       <c r="D896" s="14"/>
     </row>
     <row r="897" ht="22.5" customHeight="1">
-      <c r="A897" s="4" t="s">
+      <c r="A897" s="9" t="s">
         <v>1800</v>
       </c>
       <c r="B897" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C897" s="4" t="s">
+      <c r="C897" s="9" t="s">
         <v>1801</v>
       </c>
       <c r="D897" s="14"/>
@@ -20533,13 +20545,13 @@
       <c r="D902" s="14"/>
     </row>
     <row r="903" ht="22.5" customHeight="1">
-      <c r="A903" s="9" t="s">
+      <c r="A903" s="4" t="s">
         <v>1812</v>
       </c>
       <c r="B903" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C903" s="9" t="s">
+      <c r="C903" s="4" t="s">
         <v>1813</v>
       </c>
       <c r="D903" s="14"/>
@@ -20557,37 +20569,37 @@
       <c r="D904" s="14"/>
     </row>
     <row r="905" ht="22.5" customHeight="1">
-      <c r="A905" s="4" t="s">
+      <c r="A905" s="9" t="s">
         <v>1816</v>
       </c>
       <c r="B905" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C905" s="4" t="s">
+      <c r="C905" s="9" t="s">
         <v>1817</v>
       </c>
       <c r="D905" s="14"/>
     </row>
     <row r="906" ht="22.5" customHeight="1">
-      <c r="A906" s="9" t="s">
+      <c r="A906" s="4" t="s">
         <v>1818</v>
       </c>
       <c r="B906" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C906" s="9" t="s">
+      <c r="C906" s="4" t="s">
         <v>1819</v>
       </c>
       <c r="D906" s="14"/>
     </row>
     <row r="907" ht="22.5" customHeight="1">
-      <c r="A907" s="9" t="s">
+      <c r="A907" s="4" t="s">
         <v>1820</v>
       </c>
       <c r="B907" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C907" s="9" t="s">
+      <c r="C907" s="4" t="s">
         <v>1821</v>
       </c>
       <c r="D907" s="14"/>
@@ -20605,13 +20617,13 @@
       <c r="D908" s="14"/>
     </row>
     <row r="909" ht="22.5" customHeight="1">
-      <c r="A909" s="4" t="s">
+      <c r="A909" s="9" t="s">
         <v>1824</v>
       </c>
       <c r="B909" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C909" s="4" t="s">
+      <c r="C909" s="9" t="s">
         <v>1825</v>
       </c>
       <c r="D909" s="14"/>
@@ -20641,13 +20653,13 @@
       <c r="D911" s="14"/>
     </row>
     <row r="912" ht="22.5" customHeight="1">
-      <c r="A912" s="4" t="s">
+      <c r="A912" s="9" t="s">
         <v>1830</v>
       </c>
       <c r="B912" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C912" s="4" t="s">
+      <c r="C912" s="9" t="s">
         <v>1831</v>
       </c>
       <c r="D912" s="14"/>
@@ -20657,7 +20669,7 @@
         <v>1832</v>
       </c>
       <c r="B913" s="10" t="s">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="C913" s="4" t="s">
         <v>1833</v>
@@ -20677,13 +20689,13 @@
       <c r="D914" s="14"/>
     </row>
     <row r="915" ht="22.5" customHeight="1">
-      <c r="A915" s="9" t="s">
+      <c r="A915" s="4" t="s">
         <v>1836</v>
       </c>
       <c r="B915" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C915" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C915" s="4" t="s">
         <v>1837</v>
       </c>
       <c r="D915" s="14"/>
@@ -20725,49 +20737,49 @@
       <c r="D918" s="14"/>
     </row>
     <row r="919" ht="22.5" customHeight="1">
-      <c r="A919" s="4" t="s">
+      <c r="A919" s="9" t="s">
         <v>1844</v>
       </c>
       <c r="B919" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C919" s="4" t="s">
+      <c r="C919" s="9" t="s">
         <v>1845</v>
       </c>
       <c r="D919" s="14"/>
     </row>
     <row r="920" ht="22.5" customHeight="1">
-      <c r="A920" s="9" t="s">
+      <c r="A920" s="4" t="s">
         <v>1846</v>
       </c>
       <c r="B920" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C920" s="9" t="s">
+      <c r="C920" s="4" t="s">
         <v>1847</v>
       </c>
       <c r="D920" s="14"/>
     </row>
     <row r="921" ht="22.5" customHeight="1">
-      <c r="A921" s="9" t="s">
+      <c r="A921" s="4" t="s">
         <v>1848</v>
       </c>
       <c r="B921" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C921" s="9" t="s">
+      <c r="C921" s="4" t="s">
         <v>1849</v>
       </c>
       <c r="D921" s="14"/>
     </row>
     <row r="922" ht="22.5" customHeight="1">
-      <c r="A922" s="4" t="s">
+      <c r="A922" s="9" t="s">
         <v>1850</v>
       </c>
       <c r="B922" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C922" s="4" t="s">
+      <c r="C922" s="9" t="s">
         <v>1851</v>
       </c>
       <c r="D922" s="14"/>
@@ -20821,61 +20833,61 @@
       <c r="D926" s="14"/>
     </row>
     <row r="927" ht="22.5" customHeight="1">
-      <c r="A927" s="4" t="s">
+      <c r="A927" s="9" t="s">
         <v>1860</v>
       </c>
       <c r="B927" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C927" s="4" t="s">
+      <c r="C927" s="9" t="s">
         <v>1861</v>
       </c>
       <c r="D927" s="14"/>
     </row>
     <row r="928" ht="22.5" customHeight="1">
-      <c r="A928" s="9" t="s">
+      <c r="A928" s="4" t="s">
         <v>1862</v>
       </c>
       <c r="B928" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C928" s="9" t="s">
+      <c r="C928" s="4" t="s">
         <v>1863</v>
       </c>
       <c r="D928" s="14"/>
     </row>
     <row r="929" ht="22.5" customHeight="1">
-      <c r="A929" s="9" t="s">
+      <c r="A929" s="4" t="s">
         <v>1864</v>
       </c>
       <c r="B929" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C929" s="9" t="s">
+      <c r="C929" s="4" t="s">
         <v>1865</v>
       </c>
       <c r="D929" s="14"/>
     </row>
     <row r="930" ht="22.5" customHeight="1">
-      <c r="A930" s="4" t="s">
+      <c r="A930" s="9" t="s">
         <v>1866</v>
       </c>
       <c r="B930" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C930" s="4" t="s">
+      <c r="C930" s="9" t="s">
         <v>1867</v>
       </c>
       <c r="D930" s="14"/>
     </row>
     <row r="931" ht="22.5" customHeight="1">
-      <c r="A931" s="4" t="s">
+      <c r="A931" s="9" t="s">
         <v>1868</v>
       </c>
       <c r="B931" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C931" s="4" t="s">
+      <c r="C931" s="9" t="s">
         <v>1869</v>
       </c>
       <c r="D931" s="14"/>
@@ -20893,19 +20905,19 @@
       <c r="D932" s="14"/>
     </row>
     <row r="933" ht="22.5" customHeight="1">
-      <c r="A933" s="9" t="s">
+      <c r="A933" s="4" t="s">
         <v>1872</v>
       </c>
       <c r="B933" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C933" s="9" t="s">
+      <c r="C933" s="4" t="s">
         <v>1873</v>
       </c>
       <c r="D933" s="14"/>
     </row>
     <row r="934" ht="22.5" customHeight="1">
-      <c r="A934" s="9" t="s">
+      <c r="A934" s="4" t="s">
         <v>1874</v>
       </c>
       <c r="B934" s="10" t="s">
@@ -20917,19 +20929,19 @@
       <c r="D934" s="14"/>
     </row>
     <row r="935" ht="22.5" customHeight="1">
-      <c r="A935" s="4" t="s">
+      <c r="A935" s="9" t="s">
         <v>1876</v>
       </c>
       <c r="B935" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C935" s="4" t="s">
+      <c r="C935" s="9" t="s">
         <v>1877</v>
       </c>
       <c r="D935" s="14"/>
     </row>
     <row r="936" ht="22.5" customHeight="1">
-      <c r="A936" s="4" t="s">
+      <c r="A936" s="9" t="s">
         <v>1878</v>
       </c>
       <c r="B936" s="10" t="s">
@@ -20953,13 +20965,13 @@
       <c r="D937" s="14"/>
     </row>
     <row r="938" ht="22.5" customHeight="1">
-      <c r="A938" s="9" t="s">
+      <c r="A938" s="4" t="s">
         <v>1882</v>
       </c>
       <c r="B938" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C938" s="9" t="s">
+      <c r="C938" s="4" t="s">
         <v>1883</v>
       </c>
       <c r="D938" s="14"/>
@@ -20977,13 +20989,13 @@
       <c r="D939" s="14"/>
     </row>
     <row r="940" ht="22.5" customHeight="1">
-      <c r="A940" s="4" t="s">
+      <c r="A940" s="9" t="s">
         <v>1886</v>
       </c>
       <c r="B940" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C940" s="4" t="s">
+      <c r="C940" s="9" t="s">
         <v>1887</v>
       </c>
       <c r="D940" s="14"/>
@@ -21037,49 +21049,49 @@
       <c r="D944" s="14"/>
     </row>
     <row r="945" ht="22.5" customHeight="1">
-      <c r="A945" s="9" t="s">
+      <c r="A945" s="4" t="s">
         <v>1896</v>
       </c>
       <c r="B945" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C945" s="9" t="s">
+      <c r="C945" s="4" t="s">
         <v>1897</v>
       </c>
       <c r="D945" s="14"/>
     </row>
     <row r="946" ht="22.5" customHeight="1">
-      <c r="A946" s="9" t="s">
+      <c r="A946" s="4" t="s">
         <v>1898</v>
       </c>
       <c r="B946" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C946" s="9" t="s">
+      <c r="C946" s="4" t="s">
         <v>1899</v>
       </c>
       <c r="D946" s="14"/>
     </row>
     <row r="947" ht="22.5" customHeight="1">
-      <c r="A947" s="4" t="s">
+      <c r="A947" s="9" t="s">
         <v>1900</v>
       </c>
       <c r="B947" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C947" s="4" t="s">
+      <c r="C947" s="9" t="s">
         <v>1901</v>
       </c>
       <c r="D947" s="14"/>
     </row>
     <row r="948" ht="22.5" customHeight="1">
-      <c r="A948" s="4" t="s">
+      <c r="A948" s="9" t="s">
         <v>1902</v>
       </c>
       <c r="B948" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C948" s="4" t="s">
+      <c r="C948" s="9" t="s">
         <v>1903</v>
       </c>
       <c r="D948" s="14"/>
@@ -21097,25 +21109,25 @@
       <c r="D949" s="14"/>
     </row>
     <row r="950" ht="22.5" customHeight="1">
-      <c r="A950" s="9" t="s">
+      <c r="A950" s="4" t="s">
         <v>1906</v>
       </c>
       <c r="B950" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C950" s="9" t="s">
+      <c r="C950" s="4" t="s">
         <v>1907</v>
       </c>
       <c r="D950" s="14"/>
     </row>
     <row r="951" ht="22.5" customHeight="1">
-      <c r="A951" s="9" t="s">
+      <c r="A951" s="4" t="s">
         <v>1908</v>
       </c>
       <c r="B951" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C951" s="9" t="s">
+      <c r="C951" s="4" t="s">
         <v>1909</v>
       </c>
       <c r="D951" s="14"/>
@@ -21145,37 +21157,37 @@
       <c r="D953" s="14"/>
     </row>
     <row r="954" ht="22.5" customHeight="1">
-      <c r="A954" s="4" t="s">
+      <c r="A954" s="9" t="s">
         <v>1914</v>
       </c>
       <c r="B954" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C954" s="4" t="s">
+      <c r="C954" s="9" t="s">
         <v>1915</v>
       </c>
       <c r="D954" s="14"/>
     </row>
     <row r="955" ht="22.5" customHeight="1">
-      <c r="A955" s="4" t="s">
+      <c r="A955" s="9" t="s">
         <v>1916</v>
       </c>
       <c r="B955" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C955" s="4" t="s">
+      <c r="C955" s="9" t="s">
         <v>1917</v>
       </c>
       <c r="D955" s="14"/>
     </row>
     <row r="956" ht="22.5" customHeight="1">
-      <c r="A956" s="9" t="s">
+      <c r="A956" s="4" t="s">
         <v>1918</v>
       </c>
       <c r="B956" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C956" s="9" t="s">
+      <c r="C956" s="4" t="s">
         <v>1919</v>
       </c>
       <c r="D956" s="14"/>
@@ -21193,13 +21205,13 @@
       <c r="D957" s="14"/>
     </row>
     <row r="958" ht="22.5" customHeight="1">
-      <c r="A958" s="4" t="s">
+      <c r="A958" s="9" t="s">
         <v>1922</v>
       </c>
       <c r="B958" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C958" s="4" t="s">
+      <c r="C958" s="9" t="s">
         <v>1923</v>
       </c>
       <c r="D958" s="14"/>
@@ -21265,13 +21277,13 @@
       <c r="D963" s="14"/>
     </row>
     <row r="964" ht="22.5" customHeight="1">
-      <c r="A964" s="9" t="s">
+      <c r="A964" s="4" t="s">
         <v>1934</v>
       </c>
       <c r="B964" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C964" s="9" t="s">
+      <c r="C964" s="4" t="s">
         <v>1935</v>
       </c>
       <c r="D964" s="14"/>
@@ -21301,13 +21313,13 @@
       <c r="D966" s="14"/>
     </row>
     <row r="967" ht="22.5" customHeight="1">
-      <c r="A967" s="9" t="s">
+      <c r="A967" s="4" t="s">
         <v>1940</v>
       </c>
       <c r="B967" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C967" s="9" t="s">
+      <c r="C967" s="4" t="s">
         <v>1941</v>
       </c>
       <c r="D967" s="14"/>
@@ -21325,37 +21337,37 @@
       <c r="D968" s="14"/>
     </row>
     <row r="969" ht="22.5" customHeight="1">
-      <c r="A969" s="4" t="s">
+      <c r="A969" s="9" t="s">
         <v>1944</v>
       </c>
       <c r="B969" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C969" s="4" t="s">
+      <c r="C969" s="9" t="s">
         <v>1945</v>
       </c>
       <c r="D969" s="14"/>
     </row>
     <row r="970" ht="22.5" customHeight="1">
-      <c r="A970" s="4" t="s">
+      <c r="A970" s="9" t="s">
         <v>1946</v>
       </c>
       <c r="B970" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C970" s="4" t="s">
+      <c r="C970" s="9" t="s">
         <v>1947</v>
       </c>
       <c r="D970" s="14"/>
     </row>
     <row r="971" ht="22.5" customHeight="1">
-      <c r="A971" s="9" t="s">
+      <c r="A971" s="4" t="s">
         <v>1948</v>
       </c>
       <c r="B971" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C971" s="9" t="s">
+      <c r="C971" s="4" t="s">
         <v>1949</v>
       </c>
       <c r="D971" s="14"/>
@@ -21385,13 +21397,13 @@
       <c r="D973" s="14"/>
     </row>
     <row r="974" ht="22.5" customHeight="1">
-      <c r="A974" s="9" t="s">
+      <c r="A974" s="4" t="s">
         <v>1954</v>
       </c>
       <c r="B974" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C974" s="9" t="s">
+      <c r="C974" s="4" t="s">
         <v>1955</v>
       </c>
       <c r="D974" s="14"/>
@@ -21409,37 +21421,37 @@
       <c r="D975" s="14"/>
     </row>
     <row r="976" ht="22.5" customHeight="1">
-      <c r="A976" s="4" t="s">
+      <c r="A976" s="9" t="s">
         <v>1958</v>
       </c>
       <c r="B976" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C976" s="4" t="s">
+      <c r="C976" s="9" t="s">
         <v>1959</v>
       </c>
       <c r="D976" s="14"/>
     </row>
     <row r="977" ht="22.5" customHeight="1">
-      <c r="A977" s="4" t="s">
+      <c r="A977" s="9" t="s">
         <v>1960</v>
       </c>
       <c r="B977" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C977" s="4" t="s">
+      <c r="C977" s="9" t="s">
         <v>1961</v>
       </c>
       <c r="D977" s="14"/>
     </row>
     <row r="978" ht="22.5" customHeight="1">
-      <c r="A978" s="9" t="s">
+      <c r="A978" s="4" t="s">
         <v>1962</v>
       </c>
       <c r="B978" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C978" s="9" t="s">
+      <c r="C978" s="4" t="s">
         <v>1963</v>
       </c>
       <c r="D978" s="14"/>
@@ -21457,13 +21469,13 @@
       <c r="D979" s="14"/>
     </row>
     <row r="980" ht="22.5" customHeight="1">
-      <c r="A980" s="4" t="s">
+      <c r="A980" s="9" t="s">
         <v>1966</v>
       </c>
       <c r="B980" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C980" s="4" t="s">
+      <c r="C980" s="9" t="s">
         <v>1967</v>
       </c>
       <c r="D980" s="14"/>
@@ -21484,7 +21496,7 @@
       <c r="A982" s="4" t="s">
         <v>1970</v>
       </c>
-      <c r="B982" s="7" t="s">
+      <c r="B982" s="10" t="s">
         <v>94</v>
       </c>
       <c r="C982" s="4" t="s">
@@ -21493,49 +21505,49 @@
       <c r="D982" s="14"/>
     </row>
     <row r="983" ht="22.5" customHeight="1">
-      <c r="A983" s="9" t="s">
+      <c r="A983" s="4" t="s">
         <v>1972</v>
       </c>
       <c r="B983" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C983" s="9" t="s">
+      <c r="C983" s="4" t="s">
         <v>1973</v>
       </c>
       <c r="D983" s="14"/>
     </row>
     <row r="984" ht="22.5" customHeight="1">
-      <c r="A984" s="9" t="s">
+      <c r="A984" s="4" t="s">
         <v>1974</v>
       </c>
-      <c r="B984" s="10" t="s">
+      <c r="B984" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C984" s="9" t="s">
+      <c r="C984" s="4" t="s">
         <v>1975</v>
       </c>
       <c r="D984" s="14"/>
     </row>
     <row r="985" ht="22.5" customHeight="1">
-      <c r="A985" s="4" t="s">
+      <c r="A985" s="9" t="s">
         <v>1976</v>
       </c>
       <c r="B985" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C985" s="4" t="s">
+      <c r="C985" s="9" t="s">
         <v>1977</v>
       </c>
       <c r="D985" s="14"/>
     </row>
     <row r="986" ht="22.5" customHeight="1">
-      <c r="A986" s="4" t="s">
+      <c r="A986" s="9" t="s">
         <v>1978</v>
       </c>
       <c r="B986" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C986" s="4" t="s">
+      <c r="C986" s="9" t="s">
         <v>1979</v>
       </c>
       <c r="D986" s="14"/>
@@ -21553,61 +21565,61 @@
       <c r="D987" s="14"/>
     </row>
     <row r="988" ht="22.5" customHeight="1">
-      <c r="A988" s="9" t="s">
+      <c r="A988" s="4" t="s">
         <v>1982</v>
       </c>
       <c r="B988" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C988" s="9" t="s">
+      <c r="C988" s="4" t="s">
         <v>1983</v>
       </c>
       <c r="D988" s="14"/>
     </row>
     <row r="989" ht="22.5" customHeight="1">
-      <c r="A989" s="9" t="s">
+      <c r="A989" s="4" t="s">
         <v>1984</v>
       </c>
       <c r="B989" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C989" s="9" t="s">
+      <c r="C989" s="4" t="s">
         <v>1985</v>
       </c>
       <c r="D989" s="14"/>
     </row>
     <row r="990" ht="22.5" customHeight="1">
-      <c r="A990" s="4" t="s">
+      <c r="A990" s="9" t="s">
         <v>1986</v>
       </c>
       <c r="B990" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C990" s="4" t="s">
+      <c r="C990" s="9" t="s">
         <v>1987</v>
       </c>
       <c r="D990" s="14"/>
     </row>
     <row r="991" ht="22.5" customHeight="1">
-      <c r="A991" s="4" t="s">
+      <c r="A991" s="9" t="s">
         <v>1988</v>
       </c>
       <c r="B991" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C991" s="4" t="s">
+      <c r="C991" s="9" t="s">
         <v>1989</v>
       </c>
       <c r="D991" s="14"/>
     </row>
     <row r="992" ht="22.5" customHeight="1">
-      <c r="A992" s="9" t="s">
+      <c r="A992" s="4" t="s">
         <v>1990</v>
       </c>
       <c r="B992" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C992" s="9" t="s">
+      <c r="C992" s="4" t="s">
         <v>1991</v>
       </c>
       <c r="D992" s="14"/>
@@ -21625,7 +21637,7 @@
       <c r="D993" s="14"/>
     </row>
     <row r="994" ht="22.5" customHeight="1">
-      <c r="A994" s="4" t="s">
+      <c r="A994" s="9" t="s">
         <v>1994</v>
       </c>
       <c r="B994" s="10" t="s">
@@ -21637,13 +21649,13 @@
       <c r="D994" s="14"/>
     </row>
     <row r="995" ht="22.5" customHeight="1">
-      <c r="A995" s="9" t="s">
+      <c r="A995" s="4" t="s">
         <v>1996</v>
       </c>
       <c r="B995" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C995" s="9" t="s">
+      <c r="C995" s="4" t="s">
         <v>1997</v>
       </c>
       <c r="D995" s="14"/>
@@ -21655,31 +21667,31 @@
       <c r="B996" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C996" s="4" t="s">
+      <c r="C996" s="9" t="s">
         <v>1999</v>
       </c>
       <c r="D996" s="14"/>
     </row>
     <row r="997" ht="22.5" customHeight="1">
-      <c r="A997" s="4" t="s">
+      <c r="A997" s="9" t="s">
         <v>2000</v>
       </c>
       <c r="B997" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C997" s="4" t="s">
+      <c r="C997" s="9" t="s">
         <v>2001</v>
       </c>
       <c r="D997" s="14"/>
     </row>
     <row r="998" ht="22.5" customHeight="1">
-      <c r="A998" s="9" t="s">
+      <c r="A998" s="4" t="s">
         <v>2002</v>
       </c>
       <c r="B998" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C998" s="9" t="s">
+      <c r="C998" s="4" t="s">
         <v>2003</v>
       </c>
       <c r="D998" s="14"/>
@@ -21733,37 +21745,37 @@
       <c r="D1002" s="14"/>
     </row>
     <row r="1003" ht="22.5" customHeight="1">
-      <c r="A1003" s="9" t="s">
+      <c r="A1003" s="4" t="s">
         <v>2012</v>
       </c>
       <c r="B1003" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1003" s="9" t="s">
+      <c r="C1003" s="4" t="s">
         <v>2013</v>
       </c>
       <c r="D1003" s="14"/>
     </row>
     <row r="1004" ht="22.5" customHeight="1">
-      <c r="A1004" s="4" t="s">
+      <c r="A1004" s="9" t="s">
         <v>2014</v>
       </c>
       <c r="B1004" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1004" s="4" t="s">
+      <c r="C1004" s="9" t="s">
         <v>2015</v>
       </c>
       <c r="D1004" s="14"/>
     </row>
     <row r="1005" ht="22.5" customHeight="1">
-      <c r="A1005" s="4" t="s">
+      <c r="A1005" s="9" t="s">
         <v>2016</v>
       </c>
       <c r="B1005" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1005" s="4" t="s">
+      <c r="C1005" s="9" t="s">
         <v>2017</v>
       </c>
       <c r="D1005" s="14"/>
@@ -21805,13 +21817,13 @@
       <c r="D1008" s="14"/>
     </row>
     <row r="1009" ht="22.5" customHeight="1">
-      <c r="A1009" s="9" t="s">
+      <c r="A1009" s="4" t="s">
         <v>2024</v>
       </c>
       <c r="B1009" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1009" s="9" t="s">
+      <c r="C1009" s="4" t="s">
         <v>2025</v>
       </c>
       <c r="D1009" s="14"/>
@@ -21829,25 +21841,25 @@
       <c r="D1010" s="14"/>
     </row>
     <row r="1011" ht="22.5" customHeight="1">
-      <c r="A1011" s="4" t="s">
+      <c r="A1011" s="9" t="s">
         <v>2028</v>
       </c>
       <c r="B1011" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1011" s="4" t="s">
+      <c r="C1011" s="9" t="s">
         <v>2029</v>
       </c>
       <c r="D1011" s="14"/>
     </row>
     <row r="1012" ht="22.5" customHeight="1">
-      <c r="A1012" s="9" t="s">
+      <c r="A1012" s="4" t="s">
         <v>2030</v>
       </c>
       <c r="B1012" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1012" s="9" t="s">
+      <c r="C1012" s="4" t="s">
         <v>2031</v>
       </c>
       <c r="D1012" s="14"/>
@@ -21856,7 +21868,7 @@
       <c r="A1013" s="4" t="s">
         <v>2032</v>
       </c>
-      <c r="B1013" s="7" t="s">
+      <c r="B1013" s="10" t="s">
         <v>94</v>
       </c>
       <c r="C1013" s="4" t="s">
@@ -21880,7 +21892,7 @@
       <c r="A1015" s="4" t="s">
         <v>2036</v>
       </c>
-      <c r="B1015" s="10" t="s">
+      <c r="B1015" s="7" t="s">
         <v>94</v>
       </c>
       <c r="C1015" s="4" t="s">
@@ -21889,25 +21901,25 @@
       <c r="D1015" s="14"/>
     </row>
     <row r="1016" ht="22.5" customHeight="1">
-      <c r="A1016" s="4" t="s">
+      <c r="A1016" s="9" t="s">
         <v>2038</v>
       </c>
       <c r="B1016" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1016" s="4" t="s">
+      <c r="C1016" s="9" t="s">
         <v>2039</v>
       </c>
       <c r="D1016" s="14"/>
     </row>
     <row r="1017" ht="22.5" customHeight="1">
-      <c r="A1017" s="9" t="s">
+      <c r="A1017" s="4" t="s">
         <v>2040</v>
       </c>
       <c r="B1017" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1017" s="9" t="s">
+      <c r="C1017" s="4" t="s">
         <v>2041</v>
       </c>
       <c r="D1017" s="14"/>
@@ -21949,13 +21961,13 @@
       <c r="D1020" s="14"/>
     </row>
     <row r="1021" ht="22.5" customHeight="1">
-      <c r="A1021" s="4" t="s">
+      <c r="A1021" s="9" t="s">
         <v>2048</v>
       </c>
       <c r="B1021" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1021" s="4" t="s">
+      <c r="C1021" s="9" t="s">
         <v>2049</v>
       </c>
       <c r="D1021" s="14"/>
@@ -21997,13 +22009,13 @@
       <c r="D1024" s="14"/>
     </row>
     <row r="1025" ht="22.5" customHeight="1">
-      <c r="A1025" s="9" t="s">
+      <c r="A1025" s="4" t="s">
         <v>2056</v>
       </c>
       <c r="B1025" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1025" s="9" t="s">
+      <c r="C1025" s="4" t="s">
         <v>2057</v>
       </c>
       <c r="D1025" s="14"/>
@@ -22033,13 +22045,13 @@
       <c r="D1027" s="14"/>
     </row>
     <row r="1028" ht="22.5" customHeight="1">
-      <c r="A1028" s="9" t="s">
+      <c r="A1028" s="4" t="s">
         <v>2062</v>
       </c>
       <c r="B1028" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1028" s="9" t="s">
+      <c r="C1028" s="4" t="s">
         <v>2063</v>
       </c>
       <c r="D1028" s="14"/>
@@ -22057,25 +22069,25 @@
       <c r="D1029" s="14"/>
     </row>
     <row r="1030" ht="22.5" customHeight="1">
-      <c r="A1030" s="4" t="s">
+      <c r="A1030" s="9" t="s">
         <v>2066</v>
       </c>
       <c r="B1030" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1030" s="4" t="s">
+      <c r="C1030" s="9" t="s">
         <v>2067</v>
       </c>
       <c r="D1030" s="14"/>
     </row>
     <row r="1031" ht="22.5" customHeight="1">
-      <c r="A1031" s="4" t="s">
+      <c r="A1031" s="9" t="s">
         <v>2068</v>
       </c>
       <c r="B1031" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1031" s="4" t="s">
+      <c r="C1031" s="9" t="s">
         <v>2069</v>
       </c>
       <c r="D1031" s="14"/>
@@ -22147,19 +22159,19 @@
       <c r="B1037" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1037" s="9" t="s">
+      <c r="C1037" s="4" t="s">
         <v>2081</v>
       </c>
       <c r="D1037" s="14"/>
     </row>
     <row r="1038" ht="22.5" customHeight="1">
-      <c r="A1038" s="9" t="s">
+      <c r="A1038" s="4" t="s">
         <v>2082</v>
       </c>
       <c r="B1038" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1038" s="9" t="s">
+      <c r="C1038" s="4" t="s">
         <v>2083</v>
       </c>
       <c r="D1038" s="14"/>
@@ -22171,7 +22183,7 @@
       <c r="B1039" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1039" s="4" t="s">
+      <c r="C1039" s="9" t="s">
         <v>2085</v>
       </c>
       <c r="D1039" s="14"/>
@@ -22201,13 +22213,13 @@
       <c r="D1041" s="14"/>
     </row>
     <row r="1042" ht="22.5" customHeight="1">
-      <c r="A1042" s="4" t="s">
+      <c r="A1042" s="9" t="s">
         <v>2090</v>
       </c>
       <c r="B1042" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1042" s="4" t="s">
+      <c r="C1042" s="9" t="s">
         <v>2091</v>
       </c>
       <c r="D1042" s="14"/>
@@ -22225,49 +22237,49 @@
       <c r="D1043" s="14"/>
     </row>
     <row r="1044" ht="22.5" customHeight="1">
-      <c r="A1044" s="9" t="s">
+      <c r="A1044" s="4" t="s">
         <v>2094</v>
       </c>
       <c r="B1044" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1044" s="9" t="s">
+      <c r="C1044" s="4" t="s">
         <v>2095</v>
       </c>
       <c r="D1044" s="14"/>
     </row>
     <row r="1045" ht="22.5" customHeight="1">
-      <c r="A1045" s="9" t="s">
+      <c r="A1045" s="4" t="s">
         <v>2096</v>
       </c>
       <c r="B1045" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1045" s="9" t="s">
+      <c r="C1045" s="4" t="s">
         <v>2097</v>
       </c>
       <c r="D1045" s="14"/>
     </row>
     <row r="1046" ht="22.5" customHeight="1">
-      <c r="A1046" s="4" t="s">
+      <c r="A1046" s="9" t="s">
         <v>2098</v>
       </c>
       <c r="B1046" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1046" s="4" t="s">
+      <c r="C1046" s="9" t="s">
         <v>2099</v>
       </c>
       <c r="D1046" s="14"/>
     </row>
     <row r="1047" ht="22.5" customHeight="1">
-      <c r="A1047" s="4" t="s">
+      <c r="A1047" s="9" t="s">
         <v>2100</v>
       </c>
       <c r="B1047" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1047" s="4" t="s">
+      <c r="C1047" s="9" t="s">
         <v>2101</v>
       </c>
       <c r="D1047" s="14"/>
@@ -22369,13 +22381,13 @@
       <c r="D1055" s="14"/>
     </row>
     <row r="1056" ht="22.5" customHeight="1">
-      <c r="A1056" s="9" t="s">
+      <c r="A1056" s="4" t="s">
         <v>2118</v>
       </c>
       <c r="B1056" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1056" s="9" t="s">
+      <c r="C1056" s="4" t="s">
         <v>2119</v>
       </c>
       <c r="D1056" s="14"/>
@@ -22393,13 +22405,13 @@
       <c r="D1057" s="14"/>
     </row>
     <row r="1058" ht="22.5" customHeight="1">
-      <c r="A1058" s="4" t="s">
+      <c r="A1058" s="9" t="s">
         <v>2122</v>
       </c>
       <c r="B1058" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1058" s="4" t="s">
+      <c r="C1058" s="9" t="s">
         <v>2123</v>
       </c>
       <c r="D1058" s="14"/>
@@ -22453,37 +22465,37 @@
       <c r="D1062" s="14"/>
     </row>
     <row r="1063" ht="22.5" customHeight="1">
-      <c r="A1063" s="9" t="s">
+      <c r="A1063" s="4" t="s">
         <v>2132</v>
       </c>
       <c r="B1063" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1063" s="9" t="s">
+      <c r="C1063" s="4" t="s">
         <v>2133</v>
       </c>
       <c r="D1063" s="14"/>
     </row>
     <row r="1064" ht="22.5" customHeight="1">
-      <c r="A1064" s="9" t="s">
+      <c r="A1064" s="4" t="s">
         <v>2134</v>
       </c>
       <c r="B1064" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1064" s="9" t="s">
+      <c r="C1064" s="4" t="s">
         <v>2135</v>
       </c>
       <c r="D1064" s="14"/>
     </row>
     <row r="1065" ht="22.5" customHeight="1">
-      <c r="A1065" s="4" t="s">
+      <c r="A1065" s="9" t="s">
         <v>2136</v>
       </c>
       <c r="B1065" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1065" s="4" t="s">
+      <c r="C1065" s="9" t="s">
         <v>2137</v>
       </c>
       <c r="D1065" s="14"/>
@@ -22513,13 +22525,13 @@
       <c r="D1067" s="14"/>
     </row>
     <row r="1068" ht="22.5" customHeight="1">
-      <c r="A1068" s="4" t="s">
+      <c r="A1068" s="9" t="s">
         <v>2142</v>
       </c>
       <c r="B1068" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1068" s="4" t="s">
+      <c r="C1068" s="9" t="s">
         <v>2143</v>
       </c>
       <c r="D1068" s="14"/>
@@ -22549,13 +22561,13 @@
       <c r="D1070" s="14"/>
     </row>
     <row r="1071" ht="22.5" customHeight="1">
-      <c r="A1071" s="9" t="s">
+      <c r="A1071" s="4" t="s">
         <v>2148</v>
       </c>
       <c r="B1071" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1071" s="9" t="s">
+      <c r="C1071" s="4" t="s">
         <v>2149</v>
       </c>
       <c r="D1071" s="14"/>
@@ -22573,13 +22585,13 @@
       <c r="D1072" s="14"/>
     </row>
     <row r="1073" ht="22.5" customHeight="1">
-      <c r="A1073" s="4" t="s">
+      <c r="A1073" s="9" t="s">
         <v>2152</v>
       </c>
       <c r="B1073" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1073" s="4" t="s">
+      <c r="C1073" s="9" t="s">
         <v>2153</v>
       </c>
       <c r="D1073" s="14"/>
@@ -22657,25 +22669,25 @@
       <c r="D1079" s="14"/>
     </row>
     <row r="1080" ht="22.5" customHeight="1">
-      <c r="A1080" s="9" t="s">
+      <c r="A1080" s="4" t="s">
         <v>2166</v>
       </c>
       <c r="B1080" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1080" s="9" t="s">
+      <c r="C1080" s="4" t="s">
         <v>2167</v>
       </c>
       <c r="D1080" s="14"/>
     </row>
     <row r="1081" ht="22.5" customHeight="1">
-      <c r="A1081" s="9" t="s">
+      <c r="A1081" s="4" t="s">
         <v>2168</v>
       </c>
       <c r="B1081" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1081" s="9" t="s">
+      <c r="C1081" s="4" t="s">
         <v>2169</v>
       </c>
       <c r="D1081" s="14"/>
@@ -22693,13 +22705,13 @@
       <c r="D1082" s="14"/>
     </row>
     <row r="1083" ht="22.5" customHeight="1">
-      <c r="A1083" s="4" t="s">
+      <c r="A1083" s="9" t="s">
         <v>2172</v>
       </c>
       <c r="B1083" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1083" s="4" t="s">
+      <c r="C1083" s="9" t="s">
         <v>2173</v>
       </c>
       <c r="D1083" s="14"/>
@@ -22765,49 +22777,49 @@
       <c r="D1088" s="14"/>
     </row>
     <row r="1089" ht="22.5" customHeight="1">
-      <c r="A1089" s="9" t="s">
+      <c r="A1089" s="4" t="s">
         <v>2184</v>
       </c>
       <c r="B1089" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1089" s="9" t="s">
+      <c r="C1089" s="4" t="s">
         <v>2185</v>
       </c>
       <c r="D1089" s="14"/>
     </row>
     <row r="1090" ht="22.5" customHeight="1">
-      <c r="A1090" s="4" t="s">
+      <c r="A1090" s="9" t="s">
         <v>2186</v>
       </c>
       <c r="B1090" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1090" s="4" t="s">
+      <c r="C1090" s="9" t="s">
         <v>2187</v>
       </c>
       <c r="D1090" s="14"/>
     </row>
     <row r="1091" ht="22.5" customHeight="1">
-      <c r="A1091" s="4" t="s">
+      <c r="A1091" s="9" t="s">
         <v>2188</v>
       </c>
-      <c r="B1091" s="7" t="s">
+      <c r="B1091" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1091" s="4" t="s">
+      <c r="C1091" s="9" t="s">
         <v>2189</v>
       </c>
       <c r="D1091" s="14"/>
     </row>
     <row r="1092" ht="22.5" customHeight="1">
-      <c r="A1092" s="9" t="s">
+      <c r="A1092" s="4" t="s">
         <v>2190</v>
       </c>
       <c r="B1092" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1092" s="9" t="s">
+      <c r="C1092" s="4" t="s">
         <v>2191</v>
       </c>
       <c r="D1092" s="14"/>
@@ -22816,7 +22828,7 @@
       <c r="A1093" s="4" t="s">
         <v>2192</v>
       </c>
-      <c r="B1093" s="10" t="s">
+      <c r="B1093" s="7" t="s">
         <v>94</v>
       </c>
       <c r="C1093" s="4" t="s">
@@ -22825,13 +22837,13 @@
       <c r="D1093" s="14"/>
     </row>
     <row r="1094" ht="22.5" customHeight="1">
-      <c r="A1094" s="4" t="s">
+      <c r="A1094" s="9" t="s">
         <v>2194</v>
       </c>
       <c r="B1094" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1094" s="4" t="s">
+      <c r="C1094" s="9" t="s">
         <v>2195</v>
       </c>
       <c r="D1094" s="14"/>
@@ -22873,25 +22885,25 @@
       <c r="D1097" s="14"/>
     </row>
     <row r="1098" ht="22.5" customHeight="1">
-      <c r="A1098" s="9" t="s">
+      <c r="A1098" s="4" t="s">
         <v>2202</v>
       </c>
       <c r="B1098" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1098" s="9" t="s">
+      <c r="C1098" s="4" t="s">
         <v>2203</v>
       </c>
       <c r="D1098" s="14"/>
     </row>
     <row r="1099" ht="22.5" customHeight="1">
-      <c r="A1099" s="9" t="s">
+      <c r="A1099" s="4" t="s">
         <v>2204</v>
       </c>
       <c r="B1099" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1099" s="9" t="s">
+      <c r="C1099" s="4" t="s">
         <v>2205</v>
       </c>
       <c r="D1099" s="14"/>
@@ -22909,13 +22921,13 @@
       <c r="D1100" s="14"/>
     </row>
     <row r="1101" ht="22.5" customHeight="1">
-      <c r="A1101" s="4" t="s">
+      <c r="A1101" s="9" t="s">
         <v>2208</v>
       </c>
       <c r="B1101" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1101" s="4" t="s">
+      <c r="C1101" s="9" t="s">
         <v>2209</v>
       </c>
       <c r="D1101" s="14"/>
@@ -22969,25 +22981,25 @@
       <c r="D1105" s="14"/>
     </row>
     <row r="1106" ht="22.5" customHeight="1">
-      <c r="A1106" s="4" t="s">
+      <c r="A1106" s="9" t="s">
         <v>2218</v>
       </c>
       <c r="B1106" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1106" s="4" t="s">
+      <c r="C1106" s="9" t="s">
         <v>2219</v>
       </c>
       <c r="D1106" s="14"/>
     </row>
     <row r="1107" ht="22.5" customHeight="1">
-      <c r="A1107" s="9" t="s">
+      <c r="A1107" s="4" t="s">
         <v>2220</v>
       </c>
       <c r="B1107" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1107" s="9" t="s">
+      <c r="C1107" s="4" t="s">
         <v>2221</v>
       </c>
       <c r="D1107" s="14"/>
@@ -23077,13 +23089,13 @@
       <c r="D1114" s="14"/>
     </row>
     <row r="1115" ht="22.5" customHeight="1">
-      <c r="A1115" s="4" t="s">
+      <c r="A1115" s="9" t="s">
         <v>2236</v>
       </c>
       <c r="B1115" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1115" s="4" t="s">
+      <c r="C1115" s="9" t="s">
         <v>2237</v>
       </c>
       <c r="D1115" s="14"/>
@@ -23101,37 +23113,37 @@
       <c r="D1116" s="14"/>
     </row>
     <row r="1117" ht="22.5" customHeight="1">
-      <c r="A1117" s="9" t="s">
+      <c r="A1117" s="4" t="s">
         <v>2240</v>
       </c>
       <c r="B1117" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1117" s="9" t="s">
+      <c r="C1117" s="4" t="s">
         <v>2241</v>
       </c>
       <c r="D1117" s="14"/>
     </row>
     <row r="1118" ht="22.5" customHeight="1">
-      <c r="A1118" s="9" t="s">
+      <c r="A1118" s="4" t="s">
         <v>2242</v>
       </c>
       <c r="B1118" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1118" s="9" t="s">
+      <c r="C1118" s="4" t="s">
         <v>2243</v>
       </c>
       <c r="D1118" s="14"/>
     </row>
     <row r="1119" ht="22.5" customHeight="1">
-      <c r="A1119" s="4" t="s">
+      <c r="A1119" s="9" t="s">
         <v>2244</v>
       </c>
       <c r="B1119" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1119" s="4" t="s">
+      <c r="C1119" s="9" t="s">
         <v>2245</v>
       </c>
       <c r="D1119" s="14"/>
@@ -23149,13 +23161,13 @@
       <c r="D1120" s="14"/>
     </row>
     <row r="1121" ht="22.5" customHeight="1">
-      <c r="A1121" s="9" t="s">
+      <c r="A1121" s="4" t="s">
         <v>2248</v>
       </c>
       <c r="B1121" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1121" s="9" t="s">
+      <c r="C1121" s="4" t="s">
         <v>2249</v>
       </c>
       <c r="D1121" s="14"/>
@@ -23185,37 +23197,37 @@
       <c r="D1123" s="14"/>
     </row>
     <row r="1124" ht="22.5" customHeight="1">
-      <c r="A1124" s="4" t="s">
+      <c r="A1124" s="9" t="s">
         <v>2254</v>
       </c>
       <c r="B1124" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1124" s="4" t="s">
+      <c r="C1124" s="9" t="s">
         <v>2255</v>
       </c>
       <c r="D1124" s="14"/>
     </row>
     <row r="1125" ht="22.5" customHeight="1">
-      <c r="A1125" s="4" t="s">
+      <c r="A1125" s="9" t="s">
         <v>2256</v>
       </c>
       <c r="B1125" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1125" s="4" t="s">
+      <c r="C1125" s="9" t="s">
         <v>2257</v>
       </c>
       <c r="D1125" s="17"/>
     </row>
     <row r="1126" ht="22.5" customHeight="1">
-      <c r="A1126" s="9" t="s">
+      <c r="A1126" s="4" t="s">
         <v>2258</v>
       </c>
       <c r="B1126" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1126" s="9" t="s">
+      <c r="C1126" s="4" t="s">
         <v>2259</v>
       </c>
       <c r="D1126" s="14"/>
@@ -23245,25 +23257,25 @@
       <c r="D1128" s="14"/>
     </row>
     <row r="1129" ht="22.5" customHeight="1">
-      <c r="A1129" s="9" t="s">
+      <c r="A1129" s="4" t="s">
         <v>2264</v>
       </c>
       <c r="B1129" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1129" s="9" t="s">
+      <c r="C1129" s="4" t="s">
         <v>2265</v>
       </c>
       <c r="D1129" s="14"/>
     </row>
     <row r="1130" ht="22.5" customHeight="1">
-      <c r="A1130" s="4" t="s">
+      <c r="A1130" s="9" t="s">
         <v>2266</v>
       </c>
       <c r="B1130" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1130" s="4" t="s">
+      <c r="C1130" s="9" t="s">
         <v>2267</v>
       </c>
       <c r="D1130" s="14"/>
@@ -23297,7 +23309,7 @@
         <v>2272</v>
       </c>
       <c r="B1133" s="10" t="s">
-        <v>210</v>
+        <v>94</v>
       </c>
       <c r="C1133" s="9" t="s">
         <v>2273</v>
@@ -23308,8 +23320,8 @@
       <c r="A1134" s="4" t="s">
         <v>2274</v>
       </c>
-      <c r="B1134" s="7" t="s">
-        <v>69</v>
+      <c r="B1134" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="C1134" s="4" t="s">
         <v>2275</v>
@@ -23317,13 +23329,13 @@
       <c r="D1134" s="14"/>
     </row>
     <row r="1135" ht="22.5" customHeight="1">
-      <c r="A1135" s="4" t="s">
+      <c r="A1135" s="9" t="s">
         <v>2276</v>
       </c>
-      <c r="B1135" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1135" s="4" t="s">
+      <c r="B1135" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1135" s="9" t="s">
         <v>2277</v>
       </c>
       <c r="D1135" s="14"/>
@@ -23332,7 +23344,7 @@
       <c r="A1136" s="4" t="s">
         <v>2278</v>
       </c>
-      <c r="B1136" s="5" t="s">
+      <c r="B1136" s="7" t="s">
         <v>69</v>
       </c>
       <c r="C1136" s="4" t="s">
@@ -23341,13 +23353,13 @@
       <c r="D1136" s="14"/>
     </row>
     <row r="1137" ht="22.5" customHeight="1">
-      <c r="A1137" s="9" t="s">
+      <c r="A1137" s="4" t="s">
         <v>2280</v>
       </c>
-      <c r="B1137" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1137" s="9" t="s">
+      <c r="B1137" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1137" s="4" t="s">
         <v>2281</v>
       </c>
       <c r="D1137" s="14"/>
@@ -23357,7 +23369,7 @@
         <v>2282</v>
       </c>
       <c r="B1138" s="5" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="C1138" s="4" t="s">
         <v>2283</v>
@@ -23365,25 +23377,25 @@
       <c r="D1138" s="14"/>
     </row>
     <row r="1139" ht="22.5" customHeight="1">
-      <c r="A1139" s="4" t="s">
+      <c r="A1139" s="9" t="s">
         <v>2284</v>
       </c>
       <c r="B1139" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1139" s="4" t="s">
+      <c r="C1139" s="9" t="s">
         <v>2285</v>
       </c>
       <c r="D1139" s="14"/>
     </row>
     <row r="1140" ht="22.5" customHeight="1">
-      <c r="A1140" s="9" t="s">
+      <c r="A1140" s="4" t="s">
         <v>2286</v>
       </c>
-      <c r="B1140" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1140" s="9" t="s">
+      <c r="B1140" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1140" s="4" t="s">
         <v>2287</v>
       </c>
       <c r="D1140" s="14"/>
@@ -23392,7 +23404,7 @@
       <c r="A1141" s="4" t="s">
         <v>2288</v>
       </c>
-      <c r="B1141" s="7" t="s">
+      <c r="B1141" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C1141" s="4" t="s">
@@ -23401,13 +23413,13 @@
       <c r="D1141" s="14"/>
     </row>
     <row r="1142" ht="22.5" customHeight="1">
-      <c r="A1142" s="4" t="s">
+      <c r="A1142" s="9" t="s">
         <v>2290</v>
       </c>
       <c r="B1142" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1142" s="4" t="s">
+      <c r="C1142" s="9" t="s">
         <v>2291</v>
       </c>
       <c r="D1142" s="14"/>
@@ -23416,7 +23428,7 @@
       <c r="A1143" s="4" t="s">
         <v>2292</v>
       </c>
-      <c r="B1143" s="10" t="s">
+      <c r="B1143" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C1143" s="4" t="s">
@@ -23425,37 +23437,37 @@
       <c r="D1143" s="14"/>
     </row>
     <row r="1144" ht="22.5" customHeight="1">
-      <c r="A1144" s="9" t="s">
+      <c r="A1144" s="4" t="s">
         <v>2294</v>
       </c>
       <c r="B1144" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1144" s="9" t="s">
+      <c r="C1144" s="4" t="s">
         <v>2295</v>
       </c>
       <c r="D1144" s="14"/>
     </row>
     <row r="1145" ht="22.5" customHeight="1">
-      <c r="A1145" s="9" t="s">
+      <c r="A1145" s="4" t="s">
         <v>2296</v>
       </c>
       <c r="B1145" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1145" s="9" t="s">
+      <c r="C1145" s="4" t="s">
         <v>2297</v>
       </c>
       <c r="D1145" s="14"/>
     </row>
     <row r="1146" ht="22.5" customHeight="1">
-      <c r="A1146" s="4" t="s">
+      <c r="A1146" s="9" t="s">
         <v>2298</v>
       </c>
       <c r="B1146" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1146" s="4" t="s">
+      <c r="C1146" s="9" t="s">
         <v>2299</v>
       </c>
       <c r="D1146" s="14"/>
@@ -23464,7 +23476,7 @@
       <c r="A1147" s="9" t="s">
         <v>2300</v>
       </c>
-      <c r="B1147" s="5" t="s">
+      <c r="B1147" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C1147" s="9" t="s">
@@ -23473,37 +23485,37 @@
       <c r="D1147" s="14"/>
     </row>
     <row r="1148" ht="22.5" customHeight="1">
-      <c r="A1148" s="9" t="s">
+      <c r="A1148" s="4" t="s">
         <v>2302</v>
       </c>
       <c r="B1148" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1148" s="9" t="s">
+      <c r="C1148" s="4" t="s">
         <v>2303</v>
       </c>
       <c r="D1148" s="14"/>
     </row>
     <row r="1149" ht="22.5" customHeight="1">
-      <c r="A1149" s="4" t="s">
+      <c r="A1149" s="9" t="s">
         <v>2304</v>
       </c>
-      <c r="B1149" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1149" s="4" t="s">
+      <c r="B1149" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1149" s="9" t="s">
         <v>2305</v>
       </c>
       <c r="D1149" s="14"/>
     </row>
     <row r="1150" ht="22.5" customHeight="1">
-      <c r="A1150" s="4" t="s">
+      <c r="A1150" s="9" t="s">
         <v>2306</v>
       </c>
-      <c r="B1150" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1150" s="4" t="s">
+      <c r="B1150" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1150" s="9" t="s">
         <v>2307</v>
       </c>
       <c r="D1150" s="14"/>
@@ -23512,8 +23524,8 @@
       <c r="A1151" s="4" t="s">
         <v>2308</v>
       </c>
-      <c r="B1151" s="10" t="s">
-        <v>4</v>
+      <c r="B1151" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C1151" s="4" t="s">
         <v>2309</v>
@@ -23524,7 +23536,7 @@
       <c r="A1152" s="4" t="s">
         <v>2310</v>
       </c>
-      <c r="B1152" s="10" t="s">
+      <c r="B1152" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C1152" s="4" t="s">
@@ -23533,49 +23545,49 @@
       <c r="D1152" s="14"/>
     </row>
     <row r="1153" ht="22.5" customHeight="1">
-      <c r="A1153" s="9" t="s">
+      <c r="A1153" s="4" t="s">
         <v>2312</v>
       </c>
-      <c r="B1153" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1153" s="9" t="s">
+      <c r="B1153" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1153" s="4" t="s">
         <v>2313</v>
       </c>
       <c r="D1153" s="14"/>
     </row>
     <row r="1154" ht="22.5" customHeight="1">
-      <c r="A1154" s="9" t="s">
+      <c r="A1154" s="4" t="s">
         <v>2314</v>
       </c>
       <c r="B1154" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1154" s="4" t="s">
+        <v>2315</v>
+      </c>
+      <c r="D1154" s="14"/>
+    </row>
+    <row r="1155" ht="22.5" customHeight="1">
+      <c r="A1155" s="9" t="s">
+        <v>2316</v>
+      </c>
+      <c r="B1155" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1155" s="9" t="s">
+        <v>2317</v>
+      </c>
+      <c r="D1155" s="14"/>
+    </row>
+    <row r="1156" ht="22.5" customHeight="1">
+      <c r="A1156" s="9" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B1156" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="C1154" s="9" t="s">
-        <v>2315</v>
-      </c>
-      <c r="D1154" s="14"/>
-    </row>
-    <row r="1155" ht="22.5" customHeight="1">
-      <c r="A1155" s="4" t="s">
-        <v>2316</v>
-      </c>
-      <c r="B1155" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1155" s="4" t="s">
-        <v>2317</v>
-      </c>
-      <c r="D1155" s="14"/>
-    </row>
-    <row r="1156" ht="22.5" customHeight="1">
-      <c r="A1156" s="4" t="s">
-        <v>2318</v>
-      </c>
-      <c r="B1156" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1156" s="4" t="s">
+      <c r="C1156" s="9" t="s">
         <v>2319</v>
       </c>
       <c r="D1156" s="14"/>
@@ -23584,34 +23596,34 @@
       <c r="A1157" s="4" t="s">
         <v>2320</v>
       </c>
-      <c r="B1157" s="10" t="s">
-        <v>4</v>
+      <c r="B1157" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C1157" s="4" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="D1157" s="14"/>
     </row>
     <row r="1158" ht="22.5" customHeight="1">
       <c r="A1158" s="4" t="s">
-        <v>2321</v>
-      </c>
-      <c r="B1158" s="7" t="s">
-        <v>61</v>
+        <v>2322</v>
+      </c>
+      <c r="B1158" s="10" t="s">
+        <v>46</v>
       </c>
       <c r="C1158" s="4" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="D1158" s="14"/>
     </row>
     <row r="1159" ht="22.5" customHeight="1">
-      <c r="A1159" s="9" t="s">
-        <v>2323</v>
+      <c r="A1159" s="4" t="s">
+        <v>2324</v>
       </c>
       <c r="B1159" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="C1159" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1159" s="4" t="s">
         <v>2324</v>
       </c>
       <c r="D1159" s="14"/>
@@ -23620,7 +23632,7 @@
       <c r="A1160" s="4" t="s">
         <v>2325</v>
       </c>
-      <c r="B1160" s="10" t="s">
+      <c r="B1160" s="7" t="s">
         <v>61</v>
       </c>
       <c r="C1160" s="4" t="s">
@@ -23632,7 +23644,7 @@
       <c r="A1161" s="9" t="s">
         <v>2327</v>
       </c>
-      <c r="B1161" s="7" t="s">
+      <c r="B1161" s="10" t="s">
         <v>210</v>
       </c>
       <c r="C1161" s="9" t="s">
@@ -23645,7 +23657,7 @@
         <v>2329</v>
       </c>
       <c r="B1162" s="10" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C1162" s="4" t="s">
         <v>2330</v>
@@ -23653,13 +23665,13 @@
       <c r="D1162" s="14"/>
     </row>
     <row r="1163" ht="22.5" customHeight="1">
-      <c r="A1163" s="4" t="s">
+      <c r="A1163" s="9" t="s">
         <v>2331</v>
       </c>
-      <c r="B1163" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1163" s="4" t="s">
+      <c r="B1163" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1163" s="9" t="s">
         <v>2332</v>
       </c>
       <c r="D1163" s="14"/>
@@ -23677,13 +23689,13 @@
       <c r="D1164" s="14"/>
     </row>
     <row r="1165" ht="22.5" customHeight="1">
-      <c r="A1165" s="9" t="s">
+      <c r="A1165" s="4" t="s">
         <v>2335</v>
       </c>
-      <c r="B1165" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1165" s="9" t="s">
+      <c r="B1165" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1165" s="4" t="s">
         <v>2336</v>
       </c>
       <c r="D1165" s="14"/>
@@ -23704,8 +23716,8 @@
       <c r="A1167" s="9" t="s">
         <v>2339</v>
       </c>
-      <c r="B1167" s="7" t="s">
-        <v>69</v>
+      <c r="B1167" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C1167" s="9" t="s">
         <v>2340</v>
@@ -23713,13 +23725,13 @@
       <c r="D1167" s="14"/>
     </row>
     <row r="1168" ht="22.5" customHeight="1">
-      <c r="A1168" s="9" t="s">
+      <c r="A1168" s="4" t="s">
         <v>2341</v>
       </c>
       <c r="B1168" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1168" s="9" t="s">
+      <c r="C1168" s="4" t="s">
         <v>2342</v>
       </c>
       <c r="D1168" s="14"/>
@@ -23728,8 +23740,8 @@
       <c r="A1169" s="9" t="s">
         <v>2343</v>
       </c>
-      <c r="B1169" s="10" t="s">
-        <v>4</v>
+      <c r="B1169" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="C1169" s="9" t="s">
         <v>2344</v>
@@ -23737,25 +23749,25 @@
       <c r="D1169" s="14"/>
     </row>
     <row r="1170" ht="22.5" customHeight="1">
-      <c r="A1170" s="4" t="s">
+      <c r="A1170" s="9" t="s">
         <v>2345</v>
       </c>
-      <c r="B1170" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1170" s="4" t="s">
+      <c r="B1170" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1170" s="9" t="s">
         <v>2346</v>
       </c>
       <c r="D1170" s="14"/>
     </row>
     <row r="1171" ht="22.5" customHeight="1">
-      <c r="A1171" s="4" t="s">
+      <c r="A1171" s="9" t="s">
         <v>2347</v>
       </c>
       <c r="B1171" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1171" s="4" t="s">
+      <c r="C1171" s="9" t="s">
         <v>2348</v>
       </c>
       <c r="D1171" s="14"/>
@@ -23776,8 +23788,8 @@
       <c r="A1173" s="4" t="s">
         <v>2351</v>
       </c>
-      <c r="B1173" s="7" t="s">
-        <v>61</v>
+      <c r="B1173" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C1173" s="4" t="s">
         <v>2352</v>
@@ -23785,13 +23797,13 @@
       <c r="D1173" s="14"/>
     </row>
     <row r="1174" ht="22.5" customHeight="1">
-      <c r="A1174" s="9" t="s">
+      <c r="A1174" s="4" t="s">
         <v>2353</v>
       </c>
-      <c r="B1174" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1174" s="9" t="s">
+      <c r="B1174" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1174" s="4" t="s">
         <v>2354</v>
       </c>
       <c r="D1174" s="14"/>
@@ -23800,8 +23812,8 @@
       <c r="A1175" s="4" t="s">
         <v>2355</v>
       </c>
-      <c r="B1175" s="10" t="s">
-        <v>4</v>
+      <c r="B1175" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C1175" s="4" t="s">
         <v>2356</v>
@@ -23824,10 +23836,10 @@
       <c r="A1177" s="4" t="s">
         <v>2359</v>
       </c>
-      <c r="B1177" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1177" s="9" t="s">
+      <c r="B1177" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1177" s="4" t="s">
         <v>2360</v>
       </c>
       <c r="D1177" s="14"/>
@@ -23837,7 +23849,7 @@
         <v>2361</v>
       </c>
       <c r="B1178" s="19" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="C1178" s="20" t="s">
         <v>2362</v>
@@ -23848,20 +23860,20 @@
       <c r="A1179" s="4" t="s">
         <v>2363</v>
       </c>
-      <c r="B1179" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1179" s="4" t="s">
+      <c r="B1179" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1179" s="9" t="s">
         <v>2364</v>
       </c>
       <c r="D1179" s="14"/>
     </row>
     <row r="1180" ht="22.5" customHeight="1">
-      <c r="A1180" s="9" t="s">
+      <c r="A1180" s="4" t="s">
         <v>2365</v>
       </c>
-      <c r="B1180" s="5" t="s">
-        <v>4</v>
+      <c r="B1180" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C1180" s="4" t="s">
         <v>2366</v>
@@ -23872,7 +23884,7 @@
       <c r="A1181" s="4" t="s">
         <v>2367</v>
       </c>
-      <c r="B1181" s="10" t="s">
+      <c r="B1181" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C1181" s="4" t="s">
@@ -23881,10 +23893,10 @@
       <c r="D1181" s="14"/>
     </row>
     <row r="1182" ht="22.5" customHeight="1">
-      <c r="A1182" s="4" t="s">
+      <c r="A1182" s="9" t="s">
         <v>2369</v>
       </c>
-      <c r="B1182" s="10" t="s">
+      <c r="B1182" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C1182" s="4" t="s">
@@ -23893,13 +23905,13 @@
       <c r="D1182" s="14"/>
     </row>
     <row r="1183" ht="22.5" customHeight="1">
-      <c r="A1183" s="9" t="s">
+      <c r="A1183" s="4" t="s">
         <v>2371</v>
       </c>
       <c r="B1183" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1183" s="9" t="s">
+      <c r="C1183" s="4" t="s">
         <v>2372</v>
       </c>
       <c r="D1183" s="14"/>
@@ -23908,8 +23920,8 @@
       <c r="A1184" s="4" t="s">
         <v>2373</v>
       </c>
-      <c r="B1184" s="7" t="s">
-        <v>94</v>
+      <c r="B1184" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C1184" s="4" t="s">
         <v>2374</v>
@@ -23932,8 +23944,8 @@
       <c r="A1186" s="4" t="s">
         <v>2377</v>
       </c>
-      <c r="B1186" s="10" t="s">
-        <v>61</v>
+      <c r="B1186" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="C1186" s="4" t="s">
         <v>2378</v>
@@ -23941,109 +23953,109 @@
       <c r="D1186" s="14"/>
     </row>
     <row r="1187" ht="22.5" customHeight="1">
-      <c r="A1187" s="4" t="s">
+      <c r="A1187" s="9" t="s">
         <v>2379</v>
       </c>
       <c r="B1187" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1187" s="9" t="s">
+        <v>2380</v>
+      </c>
+      <c r="D1187" s="14"/>
+    </row>
+    <row r="1188" ht="22.5" customHeight="1">
+      <c r="A1188" s="4" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B1188" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C1187" s="4" t="s">
-        <v>2380</v>
-      </c>
-      <c r="D1187" s="14"/>
-    </row>
-    <row r="1188" ht="22.5" customHeight="1">
-      <c r="A1188" s="9" t="s">
-        <v>2381</v>
-      </c>
-      <c r="B1188" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1188" s="9" t="s">
+      <c r="C1188" s="4" t="s">
         <v>2382</v>
       </c>
       <c r="D1188" s="14"/>
     </row>
     <row r="1189" ht="22.5" customHeight="1">
-      <c r="A1189" s="9" t="s">
+      <c r="A1189" s="4" t="s">
         <v>2383</v>
       </c>
-      <c r="B1189" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1189" s="9" t="s">
+      <c r="B1189" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1189" s="4" t="s">
         <v>2384</v>
       </c>
       <c r="D1189" s="14"/>
     </row>
     <row r="1190" ht="22.5" customHeight="1">
-      <c r="A1190" s="4" t="s">
+      <c r="A1190" s="9" t="s">
         <v>2385</v>
       </c>
-      <c r="B1190" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1190" s="4" t="s">
+      <c r="B1190" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1190" s="9" t="s">
         <v>2386</v>
       </c>
       <c r="D1190" s="14"/>
     </row>
     <row r="1191" ht="22.5" customHeight="1">
-      <c r="A1191" s="4" t="s">
+      <c r="A1191" s="9" t="s">
         <v>2387</v>
       </c>
-      <c r="B1191" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1191" s="4" t="s">
+      <c r="B1191" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1191" s="9" t="s">
         <v>2388</v>
       </c>
       <c r="D1191" s="14"/>
     </row>
     <row r="1192" ht="22.5" customHeight="1">
-      <c r="A1192" s="9" t="s">
+      <c r="A1192" s="4" t="s">
         <v>2389</v>
       </c>
-      <c r="B1192" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1192" s="9" t="s">
+      <c r="B1192" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1192" s="4" t="s">
         <v>2390</v>
       </c>
       <c r="D1192" s="14"/>
     </row>
     <row r="1193" ht="22.5" customHeight="1">
-      <c r="A1193" s="9" t="s">
+      <c r="A1193" s="4" t="s">
         <v>2391</v>
       </c>
-      <c r="B1193" s="7" t="s">
+      <c r="B1193" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1193" s="4" t="s">
+        <v>2392</v>
+      </c>
+      <c r="D1193" s="14"/>
+    </row>
+    <row r="1194" ht="22.5" customHeight="1">
+      <c r="A1194" s="9" t="s">
+        <v>2393</v>
+      </c>
+      <c r="B1194" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1194" s="9" t="s">
+        <v>2394</v>
+      </c>
+      <c r="D1194" s="14"/>
+    </row>
+    <row r="1195" ht="22.5" customHeight="1">
+      <c r="A1195" s="9" t="s">
+        <v>2395</v>
+      </c>
+      <c r="B1195" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C1193" s="9" t="s">
-        <v>2392</v>
-      </c>
-      <c r="D1193" s="14"/>
-    </row>
-    <row r="1194" ht="22.5" customHeight="1">
-      <c r="A1194" s="4" t="s">
-        <v>2393</v>
-      </c>
-      <c r="B1194" s="10" t="s">
-        <v>794</v>
-      </c>
-      <c r="C1194" s="4" t="s">
-        <v>2394</v>
-      </c>
-      <c r="D1194" s="14"/>
-    </row>
-    <row r="1195" ht="22.5" customHeight="1">
-      <c r="A1195" s="4" t="s">
-        <v>2395</v>
-      </c>
-      <c r="B1195" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1195" s="4" t="s">
+      <c r="C1195" s="9" t="s">
         <v>2396</v>
       </c>
       <c r="D1195" s="14"/>
@@ -24052,8 +24064,8 @@
       <c r="A1196" s="4" t="s">
         <v>2397</v>
       </c>
-      <c r="B1196" s="7" t="s">
-        <v>4</v>
+      <c r="B1196" s="10" t="s">
+        <v>794</v>
       </c>
       <c r="C1196" s="4" t="s">
         <v>2398</v>
@@ -24064,8 +24076,8 @@
       <c r="A1197" s="4" t="s">
         <v>2399</v>
       </c>
-      <c r="B1197" s="7" t="s">
-        <v>61</v>
+      <c r="B1197" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C1197" s="4" t="s">
         <v>2400</v>
@@ -24077,7 +24089,7 @@
         <v>2401</v>
       </c>
       <c r="B1198" s="7" t="s">
-        <v>794</v>
+        <v>4</v>
       </c>
       <c r="C1198" s="4" t="s">
         <v>2402</v>
@@ -24089,7 +24101,7 @@
         <v>2403</v>
       </c>
       <c r="B1199" s="7" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="C1199" s="4" t="s">
         <v>2404</v>
@@ -24097,13 +24109,13 @@
       <c r="D1199" s="14"/>
     </row>
     <row r="1200" ht="22.5" customHeight="1">
-      <c r="A1200" s="9" t="s">
+      <c r="A1200" s="4" t="s">
         <v>2405</v>
       </c>
-      <c r="B1200" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1200" s="9" t="s">
+      <c r="B1200" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="C1200" s="4" t="s">
         <v>2406</v>
       </c>
       <c r="D1200" s="14"/>
@@ -24121,13 +24133,13 @@
       <c r="D1201" s="14"/>
     </row>
     <row r="1202" ht="22.5" customHeight="1">
-      <c r="A1202" s="4" t="s">
+      <c r="A1202" s="9" t="s">
         <v>2409</v>
       </c>
-      <c r="B1202" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C1202" s="4" t="s">
+      <c r="B1202" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1202" s="9" t="s">
         <v>2410</v>
       </c>
       <c r="D1202" s="14"/>
@@ -24136,7 +24148,7 @@
       <c r="A1203" s="4" t="s">
         <v>2411</v>
       </c>
-      <c r="B1203" s="10" t="s">
+      <c r="B1203" s="7" t="s">
         <v>107</v>
       </c>
       <c r="C1203" s="4" t="s">
@@ -24157,25 +24169,25 @@
       <c r="D1204" s="14"/>
     </row>
     <row r="1205" ht="22.5" customHeight="1">
-      <c r="A1205" s="9" t="s">
+      <c r="A1205" s="4" t="s">
         <v>2415</v>
       </c>
       <c r="B1205" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1205" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1205" s="4" t="s">
         <v>2416</v>
       </c>
       <c r="D1205" s="14"/>
     </row>
     <row r="1206" ht="22.5" customHeight="1">
-      <c r="A1206" s="9" t="s">
+      <c r="A1206" s="4" t="s">
         <v>2417</v>
       </c>
-      <c r="B1206" s="10" t="s">
+      <c r="B1206" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C1206" s="9" t="s">
+      <c r="C1206" s="4" t="s">
         <v>2418</v>
       </c>
       <c r="D1206" s="14"/>
@@ -24185,7 +24197,7 @@
         <v>2419</v>
       </c>
       <c r="B1207" s="10" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="C1207" s="9" t="s">
         <v>2420</v>
@@ -24193,25 +24205,25 @@
       <c r="D1207" s="14"/>
     </row>
     <row r="1208" ht="22.5" customHeight="1">
-      <c r="A1208" s="4" t="s">
+      <c r="A1208" s="9" t="s">
         <v>2421</v>
       </c>
-      <c r="B1208" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1208" s="4" t="s">
+      <c r="B1208" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1208" s="9" t="s">
         <v>2422</v>
       </c>
       <c r="D1208" s="14"/>
     </row>
     <row r="1209" ht="22.5" customHeight="1">
-      <c r="A1209" s="4" t="s">
+      <c r="A1209" s="9" t="s">
         <v>2423</v>
       </c>
       <c r="B1209" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1209" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1209" s="9" t="s">
         <v>2424</v>
       </c>
       <c r="D1209" s="14"/>
@@ -24220,8 +24232,8 @@
       <c r="A1210" s="4" t="s">
         <v>2425</v>
       </c>
-      <c r="B1210" s="10" t="s">
-        <v>4</v>
+      <c r="B1210" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C1210" s="4" t="s">
         <v>2426</v>
@@ -24229,13 +24241,13 @@
       <c r="D1210" s="14"/>
     </row>
     <row r="1211" ht="22.5" customHeight="1">
-      <c r="A1211" s="9" t="s">
+      <c r="A1211" s="4" t="s">
         <v>2427</v>
       </c>
-      <c r="B1211" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1211" s="9" t="s">
+      <c r="B1211" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1211" s="4" t="s">
         <v>2428</v>
       </c>
       <c r="D1211" s="14"/>
@@ -24253,13 +24265,13 @@
       <c r="D1212" s="14"/>
     </row>
     <row r="1213" ht="22.5" customHeight="1">
-      <c r="A1213" s="4" t="s">
+      <c r="A1213" s="9" t="s">
         <v>2431</v>
       </c>
-      <c r="B1213" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1213" s="4" t="s">
+      <c r="B1213" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1213" s="9" t="s">
         <v>2432</v>
       </c>
       <c r="D1213" s="14"/>
@@ -24277,13 +24289,13 @@
       <c r="D1214" s="14"/>
     </row>
     <row r="1215" ht="22.5" customHeight="1">
-      <c r="A1215" s="9" t="s">
+      <c r="A1215" s="4" t="s">
         <v>2435</v>
       </c>
       <c r="B1215" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1215" s="9" t="s">
+      <c r="C1215" s="4" t="s">
         <v>2436</v>
       </c>
       <c r="D1215" s="14"/>
@@ -24301,73 +24313,73 @@
       <c r="D1216" s="14"/>
     </row>
     <row r="1217" ht="22.5" customHeight="1">
-      <c r="A1217" s="4" t="s">
+      <c r="A1217" s="9" t="s">
         <v>2439</v>
       </c>
       <c r="B1217" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1217" s="4" t="s">
+      <c r="C1217" s="9" t="s">
         <v>2440</v>
       </c>
       <c r="D1217" s="14"/>
     </row>
     <row r="1218" ht="22.5" customHeight="1">
-      <c r="A1218" s="9" t="s">
+      <c r="A1218" s="4" t="s">
         <v>2441</v>
       </c>
       <c r="B1218" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1218" s="9" t="s">
+      <c r="C1218" s="4" t="s">
         <v>2442</v>
       </c>
       <c r="D1218" s="14"/>
     </row>
     <row r="1219" ht="22.5" customHeight="1">
-      <c r="A1219" s="9" t="s">
+      <c r="A1219" s="4" t="s">
         <v>2443</v>
       </c>
       <c r="B1219" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1219" s="9" t="s">
+      <c r="C1219" s="4" t="s">
         <v>2444</v>
       </c>
       <c r="D1219" s="14"/>
     </row>
     <row r="1220" ht="22.5" customHeight="1">
-      <c r="A1220" s="4" t="s">
+      <c r="A1220" s="9" t="s">
         <v>2445</v>
       </c>
-      <c r="B1220" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1220" s="4" t="s">
+      <c r="B1220" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1220" s="9" t="s">
         <v>2446</v>
       </c>
       <c r="D1220" s="14"/>
     </row>
     <row r="1221" ht="22.5" customHeight="1">
-      <c r="A1221" s="4" t="s">
+      <c r="A1221" s="9" t="s">
         <v>2447</v>
       </c>
       <c r="B1221" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1221" s="4" t="s">
+      <c r="C1221" s="9" t="s">
         <v>2448</v>
       </c>
       <c r="D1221" s="14"/>
     </row>
     <row r="1222" ht="22.5" customHeight="1">
-      <c r="A1222" s="9" t="s">
+      <c r="A1222" s="4" t="s">
         <v>2449</v>
       </c>
       <c r="B1222" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1222" s="9" t="s">
+      <c r="C1222" s="4" t="s">
         <v>2450</v>
       </c>
       <c r="D1222" s="14"/>
@@ -24385,37 +24397,37 @@
       <c r="D1223" s="14"/>
     </row>
     <row r="1224" ht="22.5" customHeight="1">
-      <c r="A1224" s="4" t="s">
+      <c r="A1224" s="9" t="s">
         <v>2453</v>
       </c>
-      <c r="B1224" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1224" s="4" t="s">
+      <c r="B1224" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1224" s="9" t="s">
         <v>2454</v>
       </c>
       <c r="D1224" s="14"/>
     </row>
     <row r="1225" ht="22.5" customHeight="1">
-      <c r="A1225" s="9" t="s">
+      <c r="A1225" s="4" t="s">
         <v>2455</v>
       </c>
-      <c r="B1225" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1225" s="9" t="s">
+      <c r="B1225" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1225" s="4" t="s">
         <v>2456</v>
       </c>
       <c r="D1225" s="14"/>
     </row>
     <row r="1226" ht="22.5" customHeight="1">
-      <c r="A1226" s="9" t="s">
+      <c r="A1226" s="4" t="s">
         <v>2457</v>
       </c>
       <c r="B1226" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1226" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1226" s="4" t="s">
         <v>2458</v>
       </c>
       <c r="D1226" s="14"/>
@@ -24424,8 +24436,8 @@
       <c r="A1227" s="9" t="s">
         <v>2459</v>
       </c>
-      <c r="B1227" s="10" t="s">
-        <v>46</v>
+      <c r="B1227" s="7" t="s">
+        <v>4</v>
       </c>
       <c r="C1227" s="9" t="s">
         <v>2460</v>
@@ -24433,25 +24445,25 @@
       <c r="D1227" s="14"/>
     </row>
     <row r="1228" ht="22.5" customHeight="1">
-      <c r="A1228" s="4" t="s">
+      <c r="A1228" s="9" t="s">
         <v>2461</v>
       </c>
-      <c r="B1228" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1228" s="4" t="s">
+      <c r="B1228" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1228" s="9" t="s">
         <v>2462</v>
       </c>
       <c r="D1228" s="14"/>
     </row>
     <row r="1229" ht="22.5" customHeight="1">
-      <c r="A1229" s="4" t="s">
+      <c r="A1229" s="9" t="s">
         <v>2463</v>
       </c>
-      <c r="B1229" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1229" s="4" t="s">
+      <c r="B1229" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1229" s="9" t="s">
         <v>2464</v>
       </c>
       <c r="D1229" s="14"/>
@@ -24460,8 +24472,8 @@
       <c r="A1230" s="4" t="s">
         <v>2465</v>
       </c>
-      <c r="B1230" s="7" t="s">
-        <v>579</v>
+      <c r="B1230" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="C1230" s="4" t="s">
         <v>2466</v>
@@ -24472,17 +24484,41 @@
       <c r="A1231" s="4" t="s">
         <v>2467</v>
       </c>
-      <c r="B1231" s="10" t="s">
-        <v>4</v>
+      <c r="B1231" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C1231" s="4" t="s">
         <v>2468</v>
       </c>
       <c r="D1231" s="14"/>
     </row>
+    <row r="1232" ht="22.5" customHeight="1">
+      <c r="A1232" s="4" t="s">
+        <v>2469</v>
+      </c>
+      <c r="B1232" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="C1232" s="4" t="s">
+        <v>2470</v>
+      </c>
+      <c r="D1232" s="14"/>
+    </row>
+    <row r="1233" ht="22.5" customHeight="1">
+      <c r="A1233" s="4" t="s">
+        <v>2471</v>
+      </c>
+      <c r="B1233" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1233" s="4" t="s">
+        <v>2472</v>
+      </c>
+      <c r="D1233" s="14"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B1231">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B1233">
       <formula1>"adjective,adverb,adverb-preposition,conjunction,noun,numeral,phrase,preposition,pronoun,verb,interjection,prefix,suffix,article"</formula1>
     </dataValidation>
   </dataValidations>
@@ -24505,58 +24541,58 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="21" t="s">
-        <v>2469</v>
+        <v>2473</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="22" t="s">
-        <v>2470</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="23" t="s">
-        <v>2471</v>
+        <v>2475</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>2472</v>
+        <v>2476</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="24" t="s">
-        <v>2473</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="23" t="s">
-        <v>2474</v>
+        <v>2478</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>2475</v>
+        <v>2479</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="24" t="s">
-        <v>2476</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="23" t="s">
-        <v>2477</v>
+        <v>2481</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>2478</v>
+        <v>2482</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="24" t="s">
-        <v>2479</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>2480</v>
+        <v>2484</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>2481</v>
+        <v>2485</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="25"/>
@@ -24565,10 +24601,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="21" t="s">
-        <v>2482</v>
+        <v>2486</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>2483</v>
+        <v>2487</v>
       </c>
       <c r="C6" s="23" t="s">
         <v>1319</v>
@@ -24580,13 +24616,13 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="21" t="s">
-        <v>2484</v>
+        <v>2488</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>2485</v>
+        <v>2489</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="25"/>
@@ -24595,13 +24631,13 @@
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="21" t="s">
-        <v>2487</v>
+        <v>2491</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>2488</v>
+        <v>2492</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>2489</v>
+        <v>2493</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="25"/>
@@ -24610,13 +24646,13 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="21" t="s">
-        <v>2490</v>
+        <v>2494</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="25"/>
@@ -24625,11 +24661,11 @@
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="21" t="s">
-        <v>2493</v>
+        <v>2497</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="24" t="s">
-        <v>2494</v>
+        <v>2498</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="25"/>
@@ -24638,10 +24674,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="21" t="s">
-        <v>2495</v>
+        <v>2499</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>2496</v>
+        <v>2500</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="25"/>
@@ -24659,10 +24695,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="21" t="s">
-        <v>2497</v>
+        <v>2501</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>1796</v>
+        <v>1800</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="25"/>
@@ -24671,10 +24707,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="23" t="s">
-        <v>2471</v>
+        <v>2475</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>1796</v>
+        <v>1800</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="25"/>
@@ -24683,10 +24719,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="23" t="s">
-        <v>2474</v>
+        <v>2478</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>2498</v>
+        <v>2502</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="25"/>
@@ -24695,10 +24731,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="23" t="s">
-        <v>2477</v>
+        <v>2481</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>2499</v>
+        <v>2503</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="25"/>
@@ -24707,10 +24743,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="21" t="s">
-        <v>2480</v>
+        <v>2484</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>2500</v>
+        <v>2504</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="25"/>
@@ -24719,10 +24755,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="21" t="s">
-        <v>2482</v>
+        <v>2486</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>2483</v>
+        <v>2487</v>
       </c>
       <c r="C18" s="23" t="s">
         <v>1319</v>
@@ -24734,13 +24770,13 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="21" t="s">
-        <v>2484</v>
+        <v>2488</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>1796</v>
+        <v>1800</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="25"/>
@@ -24749,13 +24785,13 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="21" t="s">
-        <v>2487</v>
+        <v>2491</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>2503</v>
+        <v>2507</v>
       </c>
       <c r="D20" s="25"/>
       <c r="E20" s="25"/>
@@ -24764,13 +24800,13 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="21" t="s">
-        <v>2490</v>
+        <v>2494</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
       <c r="D21" s="25"/>
       <c r="E21" s="25"/>
@@ -24779,11 +24815,11 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="21" t="s">
-        <v>2493</v>
+        <v>2497</v>
       </c>
       <c r="B22" s="21"/>
       <c r="C22" s="24" t="s">
-        <v>2504</v>
+        <v>2508</v>
       </c>
       <c r="D22" s="25"/>
       <c r="E22" s="25"/>
@@ -24792,10 +24828,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>2495</v>
+        <v>2499</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>1796</v>
+        <v>1800</v>
       </c>
       <c r="D23" s="25"/>
       <c r="E23" s="25"/>
@@ -24837,86 +24873,86 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="22" t="s">
-        <v>2505</v>
+        <v>2509</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>2506</v>
+        <v>2510</v>
       </c>
       <c r="D1" s="27"/>
       <c r="E1" s="26" t="s">
-        <v>2507</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="B2" s="26" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
       <c r="D2" s="27"/>
       <c r="E2" s="26" t="s">
-        <v>2508</v>
+        <v>2512</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>2509</v>
+        <v>2513</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>2510</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="26" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>278</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>2512</v>
+        <v>2516</v>
       </c>
       <c r="D3" s="27"/>
       <c r="E3" s="26" t="s">
-        <v>2513</v>
+        <v>2517</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>2514</v>
+        <v>2518</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>2513</v>
+        <v>2517</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>2514</v>
+        <v>2518</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>2513</v>
+        <v>2517</v>
       </c>
       <c r="J3" s="26" t="s">
-        <v>2514</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="26" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>2516</v>
+        <v>2520</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="27" t="s">
-        <v>2517</v>
+        <v>2521</v>
       </c>
       <c r="F4" s="28" t="s">
         <v>864</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>2518</v>
+        <v>2522</v>
       </c>
       <c r="H4" s="27" t="s">
         <v>1210</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>2519</v>
+        <v>2523</v>
       </c>
       <c r="J4" s="27" t="s">
         <v>284</v>
@@ -24924,13 +24960,13 @@
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>2522</v>
+        <v>2526</v>
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="27" t="s">
@@ -24940,13 +24976,13 @@
         <v>1218</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>2523</v>
+        <v>2527</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>1204</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>2524</v>
+        <v>2528</v>
       </c>
       <c r="J5" s="27" t="s">
         <v>1198</v>
@@ -24958,36 +24994,36 @@
       <c r="C6" s="27"/>
       <c r="D6" s="27"/>
       <c r="E6" s="27" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="30"/>
       <c r="I6" s="27" t="s">
-        <v>2526</v>
+        <v>2530</v>
       </c>
       <c r="J6" s="27" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="22" t="s">
-        <v>2527</v>
+        <v>2531</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>1218</v>
       </c>
       <c r="D7" s="30"/>
       <c r="E7" s="27" t="s">
-        <v>2528</v>
+        <v>2532</v>
       </c>
       <c r="F7" s="28" t="s">
         <v>278</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>2529</v>
+        <v>2533</v>
       </c>
       <c r="J7" s="27" t="s">
         <v>3</v>
@@ -24995,15 +25031,15 @@
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="B8" s="26" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
       <c r="D8" s="27"/>
       <c r="H8" s="30"/>
       <c r="I8" s="27" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="J8" s="27" t="s">
         <v>1220</v>
@@ -25011,43 +25047,43 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="26" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>1218</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>2531</v>
+        <v>2535</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="22" t="s">
-        <v>2510</v>
+        <v>2514</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>2532</v>
+        <v>2536</v>
       </c>
       <c r="H9" s="30"/>
       <c r="I9" s="27" t="s">
-        <v>2533</v>
+        <v>2537</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>2532</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="26" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="D10" s="30"/>
       <c r="F10" s="26" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
       <c r="H10" s="30"/>
       <c r="I10" s="27" t="s">
-        <v>2534</v>
+        <v>2538</v>
       </c>
       <c r="J10" s="27" t="s">
         <v>1001</v>
@@ -25055,27 +25091,27 @@
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>2535</v>
+        <v>2539</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>2536</v>
+        <v>2540</v>
       </c>
       <c r="D11" s="30"/>
       <c r="E11" s="26" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>2532</v>
+        <v>2536</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>2537</v>
+        <v>2541</v>
       </c>
       <c r="H11" s="31"/>
       <c r="I11" s="27" t="s">
-        <v>2538</v>
+        <v>2542</v>
       </c>
       <c r="J11" s="27" t="s">
         <v>1180</v>
@@ -25087,11 +25123,11 @@
       <c r="C12" s="30"/>
       <c r="D12" s="30"/>
       <c r="E12" s="26" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="H12" s="31"/>
       <c r="I12" s="27" t="s">
-        <v>2539</v>
+        <v>2543</v>
       </c>
       <c r="J12" s="27" t="s">
         <v>789</v>
@@ -25099,24 +25135,24 @@
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="22" t="s">
-        <v>2509</v>
+        <v>2513</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>242</v>
       </c>
       <c r="D13" s="30"/>
       <c r="E13" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>2540</v>
+        <v>2544</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>2541</v>
+        <v>2545</v>
       </c>
       <c r="H13" s="27"/>
       <c r="I13" s="27" t="s">
-        <v>2542</v>
+        <v>2546</v>
       </c>
       <c r="J13" s="27" t="s">
         <v>1184</v>
@@ -25124,15 +25160,15 @@
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="B14" s="26" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
       <c r="D14" s="30"/>
       <c r="H14" s="27"/>
       <c r="I14" s="27" t="s">
-        <v>2543</v>
+        <v>2547</v>
       </c>
       <c r="J14" s="27" t="s">
         <v>274</v>
@@ -25140,23 +25176,23 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="26" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="B15" s="27" t="s">
         <v>242</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>2544</v>
+        <v>2548</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>2545</v>
+        <v>2549</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>2467</v>
+        <v>2471</v>
       </c>
       <c r="H15" s="27"/>
       <c r="I15" s="27" t="s">
-        <v>2546</v>
+        <v>2550</v>
       </c>
       <c r="J15" s="27" t="s">
         <v>1034</v>
@@ -25164,46 +25200,46 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="26" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>2547</v>
+        <v>2551</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>2548</v>
+        <v>2552</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
       <c r="H16" s="31"/>
       <c r="I16" s="27" t="s">
-        <v>2549</v>
+        <v>2553</v>
       </c>
       <c r="J16" s="27" t="s">
-        <v>2467</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>2550</v>
+        <v>2554</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>2551</v>
+        <v>2555</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>2467</v>
+        <v>2471</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>2552</v>
+        <v>2556</v>
       </c>
       <c r="H17" s="31"/>
       <c r="I17" s="31"/>
@@ -25211,7 +25247,7 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="E18" s="26" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="H18" s="27"/>
       <c r="I18" s="27"/>
@@ -25223,13 +25259,13 @@
       <c r="C19" s="27"/>
       <c r="D19" s="27"/>
       <c r="E19" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>2553</v>
+        <v>2557</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>2554</v>
+        <v>2558</v>
       </c>
       <c r="H19" s="27"/>
     </row>
@@ -25245,44 +25281,44 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="26" t="s">
-        <v>2555</v>
+        <v>2559</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="B22" s="26" t="s">
-        <v>2556</v>
+        <v>2560</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>2557</v>
+        <v>2561</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>2558</v>
+        <v>2562</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>2559</v>
+        <v>2563</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>2560</v>
+        <v>2564</v>
       </c>
       <c r="G22" s="26" t="s">
-        <v>2561</v>
+        <v>2565</v>
       </c>
       <c r="H22" s="26" t="s">
-        <v>2562</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="26" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="B23" s="27" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>2563</v>
+        <v>2567</v>
       </c>
       <c r="D23" s="27" t="s">
         <v>35</v>
@@ -25291,10 +25327,10 @@
         <v>29</v>
       </c>
       <c r="F23" s="27" t="s">
-        <v>2564</v>
+        <v>2568</v>
       </c>
       <c r="G23" s="27" t="s">
-        <v>1732</v>
+        <v>1736</v>
       </c>
       <c r="H23" s="27" t="s">
         <v>502</v>
@@ -25302,7 +25338,7 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="26" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="B24" s="27" t="s">
         <v>13</v>
@@ -25319,7 +25355,7 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="B25" s="27" t="s">
         <v>15</v>
@@ -25334,61 +25370,61 @@
         <v>27</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>2565</v>
+        <v>2569</v>
       </c>
       <c r="G25" s="27" t="s">
-        <v>2566</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="26" t="s">
-        <v>2555</v>
+        <v>2559</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="B27" s="26" t="s">
-        <v>2556</v>
+        <v>2560</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>2557</v>
+        <v>2561</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>2558</v>
+        <v>2562</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>2559</v>
+        <v>2563</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>2560</v>
+        <v>2564</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>2561</v>
+        <v>2565</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>2562</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="26" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="B28" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>2567</v>
+        <v>2571</v>
       </c>
       <c r="D28" s="27" t="s">
         <v>41</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>2568</v>
+        <v>2572</v>
       </c>
       <c r="G28" s="27" t="s">
-        <v>2569</v>
+        <v>2573</v>
       </c>
       <c r="H28" s="27" t="s">
         <v>500</v>
@@ -25396,13 +25432,13 @@
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="26" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="B29" s="27" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>2570</v>
+        <v>2574</v>
       </c>
       <c r="D29" s="27" t="s">
         <v>37</v>
@@ -25410,22 +25446,22 @@
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="B30" s="27" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>2571</v>
+        <v>2575</v>
       </c>
       <c r="D30" s="27" t="s">
         <v>39</v>
       </c>
       <c r="F30" s="27" t="s">
-        <v>2572</v>
+        <v>2576</v>
       </c>
       <c r="G30" s="27" t="s">
-        <v>2573</v>
+        <v>2577</v>
       </c>
     </row>
   </sheetData>
@@ -25481,10 +25517,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="26" t="s">
-        <v>2574</v>
+        <v>2578</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>2575</v>
+        <v>2579</v>
       </c>
       <c r="E1" s="30"/>
       <c r="F1" s="31"/>
@@ -25515,262 +25551,262 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="26" t="s">
-        <v>2576</v>
+        <v>2580</v>
       </c>
       <c r="E4" s="30"/>
       <c r="F4" s="26" t="s">
-        <v>2577</v>
+        <v>2581</v>
       </c>
       <c r="J4" s="27"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="22" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
       <c r="E5" s="30"/>
       <c r="F5" s="22" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
       <c r="J5" s="27"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="22"/>
       <c r="B6" s="26" t="s">
-        <v>2508</v>
+        <v>2512</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>2509</v>
+        <v>2513</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>2510</v>
+        <v>2514</v>
       </c>
       <c r="E6" s="30"/>
       <c r="F6" s="22"/>
       <c r="G6" s="26" t="s">
-        <v>2508</v>
+        <v>2512</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>2509</v>
+        <v>2513</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>2510</v>
+        <v>2514</v>
       </c>
       <c r="J6" s="27"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="26" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>2578</v>
+        <v>2582</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="26" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1672</v>
+        <v>1676</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>1672</v>
+        <v>1676</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>2579</v>
+        <v>2583</v>
       </c>
       <c r="J7" s="27"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="26" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>2580</v>
+        <v>2584</v>
       </c>
       <c r="E8" s="30"/>
       <c r="F8" s="26" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>2579</v>
+        <v>2583</v>
       </c>
       <c r="J8" s="27"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="J9" s="27"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="26" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
       <c r="E10" s="30"/>
       <c r="F10" s="26" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
       <c r="J10" s="27"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="22"/>
       <c r="B11" s="26" t="s">
-        <v>2508</v>
+        <v>2512</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>2509</v>
+        <v>2513</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>2510</v>
+        <v>2514</v>
       </c>
       <c r="E11" s="30"/>
       <c r="F11" s="22"/>
       <c r="G11" s="26" t="s">
-        <v>2508</v>
+        <v>2512</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>2509</v>
+        <v>2513</v>
       </c>
       <c r="I11" s="26" t="s">
-        <v>2510</v>
+        <v>2514</v>
       </c>
       <c r="J11" s="27"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="26" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>2581</v>
+        <v>2585</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>2580</v>
+        <v>2584</v>
       </c>
       <c r="E12" s="30"/>
       <c r="F12" s="26" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>2582</v>
+        <v>2586</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>1672</v>
+        <v>1676</v>
       </c>
       <c r="I12" s="27" t="s">
-        <v>2579</v>
+        <v>2583</v>
       </c>
       <c r="J12" s="27"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="26" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>2583</v>
+        <v>2587</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>2580</v>
+        <v>2584</v>
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="26" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>2579</v>
+        <v>2583</v>
       </c>
       <c r="J13" s="27"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>2581</v>
+        <v>2585</v>
       </c>
       <c r="E14" s="30"/>
       <c r="F14" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="J14" s="27"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="26" t="s">
-        <v>2584</v>
+        <v>2588</v>
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="26" t="s">
-        <v>2584</v>
+        <v>2588</v>
       </c>
       <c r="J15" s="27"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="26" t="s">
-        <v>2585</v>
+        <v>2589</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>2586</v>
+        <v>2590</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>2587</v>
+        <v>2591</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="30"/>
       <c r="F16" s="26" t="s">
-        <v>2585</v>
+        <v>2589</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>2588</v>
+        <v>2592</v>
       </c>
       <c r="H16" s="33"/>
       <c r="J16" s="27"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="26" t="s">
-        <v>2589</v>
+        <v>2593</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>2590</v>
+        <v>2594</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>2591</v>
+        <v>2595</v>
       </c>
       <c r="E17" s="30"/>
       <c r="F17" s="26" t="s">
-        <v>2589</v>
+        <v>2593</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="J17" s="27"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="26" t="s">
-        <v>2593</v>
+        <v>2597</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>2594</v>
+        <v>2598</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>2595</v>
+        <v>2599</v>
       </c>
       <c r="E18" s="30"/>
       <c r="F18" s="26" t="s">
-        <v>2593</v>
+        <v>2597</v>
       </c>
       <c r="G18" s="27" t="s">
-        <v>1672</v>
+        <v>1676</v>
       </c>
       <c r="J18" s="27"/>
     </row>
@@ -25779,54 +25815,54 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="26" t="s">
-        <v>2596</v>
+        <v>2600</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>2597</v>
+        <v>2601</v>
       </c>
       <c r="J20" s="27"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="22" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
       <c r="J21" s="27"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="22"/>
       <c r="B22" s="26" t="s">
-        <v>2508</v>
+        <v>2512</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>2509</v>
+        <v>2513</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>2510</v>
+        <v>2514</v>
       </c>
       <c r="F22" s="22"/>
       <c r="G22" s="26" t="s">
-        <v>2508</v>
+        <v>2512</v>
       </c>
       <c r="H22" s="26" t="s">
-        <v>2509</v>
+        <v>2513</v>
       </c>
       <c r="I22" s="26" t="s">
-        <v>2510</v>
+        <v>2514</v>
       </c>
       <c r="J22" s="27"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="26" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="B23" s="27" t="s">
         <v>791</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="G23" s="27" t="s">
         <v>163</v>
@@ -25835,66 +25871,66 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="26" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="J24" s="27"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="J25" s="27"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="26" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
       <c r="E26" s="30"/>
       <c r="F26" s="26" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
       <c r="J26" s="27"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="22"/>
       <c r="B27" s="26" t="s">
-        <v>2508</v>
+        <v>2512</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>2509</v>
+        <v>2513</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>2510</v>
+        <v>2514</v>
       </c>
       <c r="E27" s="30"/>
       <c r="F27" s="22"/>
       <c r="G27" s="26" t="s">
-        <v>2508</v>
+        <v>2512</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>2509</v>
+        <v>2513</v>
       </c>
       <c r="I27" s="26" t="s">
-        <v>2510</v>
+        <v>2514</v>
       </c>
       <c r="J27" s="27"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="26" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="B28" s="27" t="s">
         <v>791</v>
       </c>
       <c r="E28" s="30"/>
       <c r="F28" s="26" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="G28" s="27" t="s">
         <v>163</v>
@@ -25903,81 +25939,81 @@
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="26" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="E29" s="30"/>
       <c r="F29" s="26" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="J29" s="27"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="E30" s="30"/>
       <c r="F30" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="J30" s="27"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="26" t="s">
-        <v>2584</v>
+        <v>2588</v>
       </c>
       <c r="E31" s="30"/>
       <c r="F31" s="26" t="s">
-        <v>2584</v>
+        <v>2588</v>
       </c>
       <c r="J31" s="27"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="26" t="s">
-        <v>2585</v>
+        <v>2589</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>2598</v>
+        <v>2602</v>
       </c>
       <c r="C32" s="33"/>
       <c r="E32" s="30"/>
       <c r="F32" s="26" t="s">
-        <v>2585</v>
+        <v>2589</v>
       </c>
       <c r="G32" s="27" t="s">
-        <v>2599</v>
+        <v>2603</v>
       </c>
       <c r="H32" s="33"/>
       <c r="J32" s="27"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="26" t="s">
-        <v>2589</v>
+        <v>2593</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>2600</v>
+        <v>2604</v>
       </c>
       <c r="E33" s="30"/>
       <c r="F33" s="26" t="s">
-        <v>2589</v>
+        <v>2593</v>
       </c>
       <c r="G33" s="27" t="s">
-        <v>2601</v>
+        <v>2605</v>
       </c>
       <c r="J33" s="27"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="26" t="s">
-        <v>2593</v>
+        <v>2597</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>2602</v>
+        <v>2606</v>
       </c>
       <c r="E34" s="30"/>
       <c r="F34" s="26" t="s">
-        <v>2593</v>
+        <v>2597</v>
       </c>
       <c r="G34" s="27" t="s">
-        <v>2603</v>
+        <v>2607</v>
       </c>
       <c r="J34" s="27"/>
     </row>
@@ -25995,10 +26031,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="26" t="s">
-        <v>2604</v>
+        <v>2608</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>2605</v>
+        <v>2609</v>
       </c>
       <c r="E36" s="30"/>
       <c r="F36" s="31"/>
@@ -26009,16 +26045,16 @@
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="26" t="s">
-        <v>2606</v>
+        <v>2610</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>2607</v>
+        <v>2611</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>2606</v>
+        <v>2610</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>2608</v>
+        <v>2612</v>
       </c>
       <c r="E37" s="30"/>
       <c r="F37" s="31"/>
@@ -26029,16 +26065,16 @@
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="26" t="s">
-        <v>2585</v>
+        <v>2589</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>2609</v>
+        <v>2613</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>2585</v>
+        <v>2589</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>2610</v>
+        <v>2614</v>
       </c>
       <c r="E38" s="30"/>
       <c r="F38" s="31"/>
@@ -26049,16 +26085,16 @@
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="26" t="s">
-        <v>2589</v>
+        <v>2593</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>2611</v>
+        <v>2615</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>2589</v>
+        <v>2593</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>2612</v>
+        <v>2616</v>
       </c>
       <c r="E39" s="30"/>
       <c r="F39" s="31"/>
@@ -26209,108 +26245,108 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="26" t="s">
-        <v>2613</v>
+        <v>2617</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>2614</v>
+        <v>2618</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>2615</v>
+        <v>2619</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>1209</v>
       </c>
       <c r="F1" s="26" t="s">
-        <v>2613</v>
+        <v>2617</v>
       </c>
       <c r="G1" s="26" t="s">
-        <v>2614</v>
+        <v>2618</v>
       </c>
       <c r="H1" s="26" t="s">
-        <v>2615</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>2616</v>
+        <v>2620</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>2617</v>
+        <v>2621</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>2618</v>
+        <v>2622</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>2619</v>
+        <v>2623</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>2620</v>
+        <v>2624</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>2621</v>
+        <v>2625</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>2622</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="27" t="s">
-        <v>2623</v>
+        <v>2627</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>2624</v>
+        <v>2628</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>2625</v>
+        <v>2629</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>2626</v>
+        <v>2630</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>2627</v>
+        <v>2631</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>2628</v>
+        <v>2632</v>
       </c>
       <c r="H3" s="27" t="s">
-        <v>2629</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>2630</v>
+        <v>2634</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>2631</v>
+        <v>2635</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>2632</v>
+        <v>2636</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>2633</v>
+        <v>2637</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>2634</v>
+        <v>2638</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>2635</v>
+        <v>2639</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>2636</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>2637</v>
+        <v>2641</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>2638</v>
+        <v>2642</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>2639</v>
+        <v>2643</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>2640</v>
+        <v>2644</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
@@ -26318,131 +26354,131 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>2641</v>
+        <v>2645</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>2642</v>
+        <v>2646</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>2643</v>
+        <v>2647</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>2644</v>
+        <v>2648</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>2645</v>
+        <v>2649</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>2646</v>
+        <v>2650</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>2647</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>2648</v>
+        <v>2652</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>2649</v>
+        <v>2653</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>2650</v>
+        <v>2654</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>2628</v>
+        <v>2632</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>2651</v>
+        <v>2655</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>2652</v>
+        <v>2656</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>2653</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>2654</v>
+        <v>2658</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>2655</v>
+        <v>2659</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>2656</v>
+        <v>2660</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>2657</v>
+        <v>2661</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>2658</v>
+        <v>2662</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>2659</v>
+        <v>2663</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>2660</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>2661</v>
+        <v>2665</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>2662</v>
+        <v>2666</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>2663</v>
+        <v>2667</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>2664</v>
+        <v>2668</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>2665</v>
+        <v>2669</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>2666</v>
+        <v>2670</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>2667</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>2668</v>
+        <v>2672</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>2669</v>
+        <v>2673</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>2670</v>
+        <v>2674</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>2671</v>
+        <v>2675</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>2672</v>
+        <v>2676</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>2673</v>
+        <v>2677</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>2674</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>2675</v>
+        <v>2679</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>2676</v>
+        <v>2680</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>2677</v>
+        <v>2681</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>2678</v>
+        <v>2682</v>
       </c>
       <c r="F11" s="27"/>
       <c r="G11" s="27"/>
@@ -26450,159 +26486,159 @@
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>2679</v>
+        <v>2683</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>2680</v>
+        <v>2684</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>2681</v>
+        <v>2685</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>2682</v>
+        <v>2686</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>2683</v>
+        <v>2687</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>2684</v>
+        <v>2688</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>2685</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>2686</v>
+        <v>2690</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>2687</v>
+        <v>2691</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>2688</v>
+        <v>2692</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>2689</v>
+        <v>2693</v>
       </c>
       <c r="H13" s="27"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>2690</v>
+        <v>2694</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>2691</v>
+        <v>2695</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>2692</v>
+        <v>2696</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>2693</v>
+        <v>2697</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>2694</v>
+        <v>2698</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>2695</v>
+        <v>2699</v>
       </c>
       <c r="H14" s="27" t="s">
-        <v>2696</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>2697</v>
+        <v>2701</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>2698</v>
+        <v>2702</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>2699</v>
+        <v>2703</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>2700</v>
+        <v>2704</v>
       </c>
       <c r="H15" s="27"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>2701</v>
+        <v>2705</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>2702</v>
+        <v>2706</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>2703</v>
+        <v>2707</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>2635</v>
+        <v>2639</v>
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27" t="s">
-        <v>2704</v>
+        <v>2708</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>2705</v>
+        <v>2709</v>
       </c>
       <c r="H16" s="27" t="s">
-        <v>2706</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>2707</v>
+        <v>2711</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>2708</v>
+        <v>2712</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>2709</v>
+        <v>2713</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>2710</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>2711</v>
+        <v>2715</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>2712</v>
+        <v>2716</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>2713</v>
+        <v>2717</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>2714</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>2715</v>
+        <v>2719</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>2716</v>
+        <v>2720</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>2717</v>
+        <v>2721</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>2718</v>
+        <v>2722</v>
       </c>
       <c r="H19" s="27"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>2719</v>
+        <v>2723</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>2720</v>
+        <v>2724</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>2721</v>
+        <v>2725</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>2272</v>
+        <v>2276</v>
       </c>
       <c r="E20" s="27"/>
       <c r="F20" s="27"/>
@@ -26611,16 +26647,16 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>2722</v>
+        <v>2726</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>2723</v>
+        <v>2727</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>2724</v>
+        <v>2728</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>2725</v>
+        <v>2729</v>
       </c>
       <c r="E21" s="27"/>
       <c r="F21" s="27"/>
@@ -26629,16 +26665,16 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>2726</v>
+        <v>2730</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>2727</v>
+        <v>2731</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>2728</v>
+        <v>2732</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>2729</v>
+        <v>2733</v>
       </c>
       <c r="E22" s="27"/>
       <c r="F22" s="27"/>
@@ -26647,16 +26683,16 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="27" t="s">
-        <v>2730</v>
+        <v>2734</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>2731</v>
+        <v>2735</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>2732</v>
+        <v>2736</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>2733</v>
+        <v>2737</v>
       </c>
       <c r="E23" s="27"/>
       <c r="F23" s="27"/>
@@ -26665,16 +26701,16 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>2734</v>
+        <v>2738</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>2735</v>
+        <v>2739</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>2736</v>
+        <v>2740</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>2737</v>
+        <v>2741</v>
       </c>
       <c r="E24" s="27"/>
       <c r="F24" s="27"/>
@@ -26683,16 +26719,16 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>2738</v>
+        <v>2742</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>2739</v>
+        <v>2743</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>2740</v>
+        <v>2744</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>2741</v>
+        <v>2745</v>
       </c>
       <c r="E25" s="27"/>
       <c r="F25" s="27"/>
@@ -26701,16 +26737,16 @@
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>2742</v>
+        <v>2746</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>2743</v>
+        <v>2747</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>2744</v>
+        <v>2748</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>2745</v>
+        <v>2749</v>
       </c>
       <c r="E26" s="27"/>
       <c r="F26" s="27"/>
@@ -26719,16 +26755,16 @@
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="27" t="s">
-        <v>2746</v>
+        <v>2750</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>2747</v>
+        <v>2751</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>2748</v>
+        <v>2752</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>2749</v>
+        <v>2753</v>
       </c>
       <c r="E27" s="27"/>
       <c r="F27" s="27"/>
@@ -26737,16 +26773,16 @@
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="27" t="s">
-        <v>2750</v>
+        <v>2754</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>2751</v>
+        <v>2755</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>2752</v>
+        <v>2756</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>2753</v>
+        <v>2757</v>
       </c>
       <c r="E28" s="27"/>
       <c r="F28" s="27"/>
@@ -26765,63 +26801,63 @@
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="22" t="s">
-        <v>2754</v>
+        <v>2758</v>
       </c>
       <c r="H30" s="27"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="24" t="s">
-        <v>2755</v>
+        <v>2759</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>2756</v>
+        <v>2760</v>
       </c>
       <c r="F31" s="24" t="s">
-        <v>2757</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="24" t="s">
-        <v>2758</v>
+        <v>2762</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>2759</v>
+        <v>2763</v>
       </c>
       <c r="F32" s="24" t="s">
-        <v>2760</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="24" t="s">
-        <v>2761</v>
+        <v>2765</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>2762</v>
+        <v>2766</v>
       </c>
       <c r="F33" s="24" t="s">
-        <v>2763</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="24" t="s">
-        <v>2764</v>
+        <v>2768</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>2765</v>
+        <v>2769</v>
       </c>
       <c r="F34" s="24" t="s">
-        <v>2766</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="24" t="s">
-        <v>2767</v>
+        <v>2771</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>2768</v>
+        <v>2772</v>
       </c>
       <c r="F35" s="24" t="s">
-        <v>2769</v>
+        <v>2773</v>
       </c>
     </row>
   </sheetData>
@@ -26859,175 +26895,175 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="34" t="s">
-        <v>2770</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="35" t="s">
-        <v>2771</v>
+        <v>2775</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>2772</v>
+        <v>2776</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>2773</v>
+        <v>2777</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>2774</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="35" t="s">
-        <v>2775</v>
+        <v>2779</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>2776</v>
+        <v>2780</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>2777</v>
+        <v>2781</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>2778</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="35" t="s">
-        <v>2779</v>
+        <v>2783</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>2780</v>
+        <v>2784</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>2781</v>
+        <v>2785</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>2782</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="35" t="s">
-        <v>2783</v>
+        <v>2787</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>2784</v>
+        <v>2788</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>2785</v>
+        <v>2789</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>2786</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="35" t="s">
-        <v>2787</v>
+        <v>2791</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>2788</v>
+        <v>2792</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>2789</v>
+        <v>2793</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>2790</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="35" t="s">
-        <v>2791</v>
+        <v>2795</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>2792</v>
+        <v>2796</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>2793</v>
+        <v>2797</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>2794</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="35" t="s">
-        <v>2795</v>
+        <v>2799</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>2796</v>
+        <v>2800</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>2797</v>
+        <v>2801</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>2798</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="35" t="s">
-        <v>2799</v>
+        <v>2803</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>2800</v>
+        <v>2804</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>2801</v>
+        <v>2805</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>2802</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="35" t="s">
-        <v>2803</v>
+        <v>2807</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>2804</v>
+        <v>2808</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>2805</v>
+        <v>2809</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>2798</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="35" t="s">
-        <v>2806</v>
+        <v>2810</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>2807</v>
+        <v>2811</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>2808</v>
+        <v>2812</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>2809</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="35" t="s">
-        <v>2810</v>
+        <v>2814</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>2811</v>
+        <v>2815</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>2812</v>
+        <v>2816</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>2813</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="36" t="s">
-        <v>2814</v>
+        <v>2818</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>2815</v>
+        <v>2819</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>2816</v>
+        <v>2820</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>2817</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
@@ -27044,7 +27080,7 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="36" t="s">
-        <v>2818</v>
+        <v>2822</v>
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="37"/>
@@ -27056,10 +27092,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>2819</v>
+        <v>2823</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>2820</v>
+        <v>2824</v>
       </c>
       <c r="D16" s="27"/>
       <c r="E16" s="37"/>
@@ -27071,10 +27107,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>2821</v>
+        <v>2825</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>2822</v>
+        <v>2826</v>
       </c>
       <c r="D17" s="27"/>
       <c r="E17" s="27"/>
@@ -27086,10 +27122,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>2823</v>
+        <v>2827</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>2824</v>
+        <v>2828</v>
       </c>
       <c r="D18" s="27"/>
       <c r="E18" s="37"/>
@@ -27101,10 +27137,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>2825</v>
+        <v>2829</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>2826</v>
+        <v>2830</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="37"/>
@@ -27116,10 +27152,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>2827</v>
+        <v>2831</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>2828</v>
+        <v>2832</v>
       </c>
       <c r="D20" s="27"/>
       <c r="E20" s="37"/>
@@ -27143,18 +27179,18 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="34" t="s">
-        <v>2829</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="38" t="s">
-        <v>2830</v>
+        <v>2834</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>2831</v>
+        <v>2835</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>2832</v>
+        <v>2836</v>
       </c>
       <c r="J23" s="27"/>
     </row>
@@ -27163,46 +27199,46 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="39" t="s">
-        <v>2833</v>
+        <v>2837</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>2834</v>
+        <v>2838</v>
       </c>
       <c r="G25" s="39" t="s">
-        <v>2835</v>
+        <v>2839</v>
       </c>
       <c r="J25" s="27"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="39" t="s">
-        <v>2836</v>
+        <v>2840</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>2837</v>
+        <v>2841</v>
       </c>
       <c r="G26" s="39" t="s">
-        <v>2838</v>
+        <v>2842</v>
       </c>
       <c r="J26" s="27"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="39" t="s">
-        <v>2839</v>
+        <v>2843</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>2840</v>
+        <v>2844</v>
       </c>
       <c r="G27" s="39" t="s">
-        <v>2841</v>
+        <v>2845</v>
       </c>
       <c r="J27" s="27"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="38" t="s">
-        <v>2842</v>
+        <v>2846</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>2843</v>
+        <v>2847</v>
       </c>
       <c r="G28" s="27"/>
       <c r="H28" s="27"/>

--- a/Conlangs/Kagalarian.xlsx
+++ b/Conlangs/Kagalarian.xlsx
@@ -7121,7 +7121,7 @@
     <t>war</t>
   </si>
   <si>
-    <t>nafrav itan</t>
+    <t>nafrav-itan</t>
   </si>
   <si>
     <t>warhead</t>

--- a/Conlangs/Kagalarian.xlsx
+++ b/Conlangs/Kagalarian.xlsx
@@ -11,14 +11,14 @@
     <sheet state="visible" name="Grammar" sheetId="6" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Kagalarian!$A$1:$C$1235</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Kagalarian!$A$1:$C$1236</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4290" uniqueCount="2852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4293" uniqueCount="2854">
   <si>
     <t>Word</t>
   </si>
@@ -6930,6 +6930,12 @@
   </si>
   <si>
     <t>traveler, traveling ship (not a battleship)</t>
+  </si>
+  <si>
+    <t>solerelov</t>
+  </si>
+  <si>
+    <t>travelling, trip, trek</t>
   </si>
   <si>
     <t>aglen</t>
@@ -9538,8 +9544,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C1235" displayName="Table1" name="Table1" id="1">
-  <autoFilter ref="$A$1:$C$1235"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C1236" displayName="Table1" name="Table1" id="1">
+  <autoFilter ref="$A$1:$C$1236"/>
   <tableColumns count="3">
     <tableColumn name="Word" id="1"/>
     <tableColumn name="Part of Speech" id="2"/>
@@ -23521,25 +23527,25 @@
       <c r="D1149" s="14"/>
     </row>
     <row r="1150" ht="22.5" customHeight="1">
-      <c r="A1150" s="4" t="s">
+      <c r="A1150" s="9" t="s">
         <v>2306</v>
       </c>
       <c r="B1150" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1150" s="4" t="s">
+      <c r="C1150" s="9" t="s">
         <v>2307</v>
       </c>
       <c r="D1150" s="14"/>
     </row>
     <row r="1151" ht="22.5" customHeight="1">
-      <c r="A1151" s="9" t="s">
+      <c r="A1151" s="4" t="s">
         <v>2308</v>
       </c>
-      <c r="B1151" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1151" s="9" t="s">
+      <c r="B1151" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1151" s="4" t="s">
         <v>2309</v>
       </c>
       <c r="D1151" s="14"/>
@@ -23548,7 +23554,7 @@
       <c r="A1152" s="9" t="s">
         <v>2310</v>
       </c>
-      <c r="B1152" s="10" t="s">
+      <c r="B1152" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C1152" s="9" t="s">
@@ -23557,13 +23563,13 @@
       <c r="D1152" s="14"/>
     </row>
     <row r="1153" ht="22.5" customHeight="1">
-      <c r="A1153" s="4" t="s">
+      <c r="A1153" s="9" t="s">
         <v>2312</v>
       </c>
-      <c r="B1153" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1153" s="4" t="s">
+      <c r="B1153" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1153" s="9" t="s">
         <v>2313</v>
       </c>
       <c r="D1153" s="14"/>
@@ -23573,7 +23579,7 @@
         <v>2314</v>
       </c>
       <c r="B1154" s="7" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C1154" s="4" t="s">
         <v>2315</v>
@@ -23584,7 +23590,7 @@
       <c r="A1155" s="4" t="s">
         <v>2316</v>
       </c>
-      <c r="B1155" s="10" t="s">
+      <c r="B1155" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C1155" s="4" t="s">
@@ -23605,13 +23611,13 @@
       <c r="D1156" s="14"/>
     </row>
     <row r="1157" ht="22.5" customHeight="1">
-      <c r="A1157" s="9" t="s">
+      <c r="A1157" s="4" t="s">
         <v>2320</v>
       </c>
-      <c r="B1157" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1157" s="9" t="s">
+      <c r="B1157" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1157" s="4" t="s">
         <v>2321</v>
       </c>
       <c r="D1157" s="14"/>
@@ -23620,8 +23626,8 @@
       <c r="A1158" s="9" t="s">
         <v>2322</v>
       </c>
-      <c r="B1158" s="10" t="s">
-        <v>579</v>
+      <c r="B1158" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C1158" s="9" t="s">
         <v>2323</v>
@@ -23629,13 +23635,13 @@
       <c r="D1158" s="14"/>
     </row>
     <row r="1159" ht="22.5" customHeight="1">
-      <c r="A1159" s="4" t="s">
+      <c r="A1159" s="9" t="s">
         <v>2324</v>
       </c>
-      <c r="B1159" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1159" s="4" t="s">
+      <c r="B1159" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="C1159" s="9" t="s">
         <v>2325</v>
       </c>
       <c r="D1159" s="14"/>
@@ -23644,8 +23650,8 @@
       <c r="A1160" s="4" t="s">
         <v>2326</v>
       </c>
-      <c r="B1160" s="10" t="s">
-        <v>46</v>
+      <c r="B1160" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C1160" s="4" t="s">
         <v>2327</v>
@@ -23657,19 +23663,19 @@
         <v>2328</v>
       </c>
       <c r="B1161" s="10" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="C1161" s="4" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="D1161" s="14"/>
     </row>
     <row r="1162" ht="22.5" customHeight="1">
       <c r="A1162" s="4" t="s">
-        <v>2329</v>
-      </c>
-      <c r="B1162" s="7" t="s">
-        <v>61</v>
+        <v>2330</v>
+      </c>
+      <c r="B1162" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C1162" s="4" t="s">
         <v>2330</v>
@@ -23677,49 +23683,49 @@
       <c r="D1162" s="14"/>
     </row>
     <row r="1163" ht="22.5" customHeight="1">
-      <c r="A1163" s="9" t="s">
+      <c r="A1163" s="4" t="s">
         <v>2331</v>
       </c>
-      <c r="B1163" s="10" t="s">
+      <c r="B1163" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1163" s="4" t="s">
+        <v>2332</v>
+      </c>
+      <c r="D1163" s="14"/>
+    </row>
+    <row r="1164" ht="22.5" customHeight="1">
+      <c r="A1164" s="9" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B1164" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="C1163" s="9" t="s">
-        <v>2332</v>
-      </c>
-      <c r="D1163" s="14"/>
-    </row>
-    <row r="1164" ht="22.5" customHeight="1">
-      <c r="A1164" s="4" t="s">
-        <v>2333</v>
-      </c>
-      <c r="B1164" s="10" t="s">
+      <c r="C1164" s="9" t="s">
+        <v>2334</v>
+      </c>
+      <c r="D1164" s="14"/>
+    </row>
+    <row r="1165" ht="22.5" customHeight="1">
+      <c r="A1165" s="4" t="s">
+        <v>2335</v>
+      </c>
+      <c r="B1165" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C1164" s="4" t="s">
-        <v>2334</v>
-      </c>
-      <c r="D1164" s="14"/>
-    </row>
-    <row r="1165" ht="22.5" customHeight="1">
-      <c r="A1165" s="9" t="s">
-        <v>2335</v>
-      </c>
-      <c r="B1165" s="7" t="s">
+      <c r="C1165" s="4" t="s">
+        <v>2336</v>
+      </c>
+      <c r="D1165" s="14"/>
+    </row>
+    <row r="1166" ht="22.5" customHeight="1">
+      <c r="A1166" s="9" t="s">
+        <v>2337</v>
+      </c>
+      <c r="B1166" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="C1165" s="9" t="s">
-        <v>2336</v>
-      </c>
-      <c r="D1165" s="14"/>
-    </row>
-    <row r="1166" ht="22.5" customHeight="1">
-      <c r="A1166" s="4" t="s">
-        <v>2337</v>
-      </c>
-      <c r="B1166" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1166" s="4" t="s">
+      <c r="C1166" s="9" t="s">
         <v>2338</v>
       </c>
       <c r="D1166" s="14"/>
@@ -23749,37 +23755,37 @@
       <c r="D1168" s="14"/>
     </row>
     <row r="1169" ht="22.5" customHeight="1">
-      <c r="A1169" s="9" t="s">
+      <c r="A1169" s="4" t="s">
         <v>2343</v>
       </c>
-      <c r="B1169" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1169" s="9" t="s">
+      <c r="B1169" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1169" s="4" t="s">
         <v>2344</v>
       </c>
       <c r="D1169" s="14"/>
     </row>
     <row r="1170" ht="22.5" customHeight="1">
-      <c r="A1170" s="4" t="s">
+      <c r="A1170" s="9" t="s">
         <v>2345</v>
       </c>
-      <c r="B1170" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1170" s="4" t="s">
+      <c r="B1170" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1170" s="9" t="s">
         <v>2346</v>
       </c>
       <c r="D1170" s="14"/>
     </row>
     <row r="1171" ht="22.5" customHeight="1">
-      <c r="A1171" s="9" t="s">
+      <c r="A1171" s="4" t="s">
         <v>2347</v>
       </c>
-      <c r="B1171" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1171" s="9" t="s">
+      <c r="B1171" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1171" s="4" t="s">
         <v>2348</v>
       </c>
       <c r="D1171" s="14"/>
@@ -23788,8 +23794,8 @@
       <c r="A1172" s="9" t="s">
         <v>2349</v>
       </c>
-      <c r="B1172" s="10" t="s">
-        <v>4</v>
+      <c r="B1172" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="C1172" s="9" t="s">
         <v>2350</v>
@@ -23809,13 +23815,13 @@
       <c r="D1173" s="14"/>
     </row>
     <row r="1174" ht="22.5" customHeight="1">
-      <c r="A1174" s="4" t="s">
+      <c r="A1174" s="9" t="s">
         <v>2353</v>
       </c>
-      <c r="B1174" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1174" s="4" t="s">
+      <c r="B1174" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1174" s="9" t="s">
         <v>2354</v>
       </c>
       <c r="D1174" s="14"/>
@@ -23824,7 +23830,7 @@
       <c r="A1175" s="4" t="s">
         <v>2355</v>
       </c>
-      <c r="B1175" s="10" t="s">
+      <c r="B1175" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C1175" s="4" t="s">
@@ -23836,7 +23842,7 @@
       <c r="A1176" s="4" t="s">
         <v>2357</v>
       </c>
-      <c r="B1176" s="5" t="s">
+      <c r="B1176" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C1176" s="4" t="s">
@@ -23848,8 +23854,8 @@
       <c r="A1177" s="4" t="s">
         <v>2359</v>
       </c>
-      <c r="B1177" s="7" t="s">
-        <v>61</v>
+      <c r="B1177" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C1177" s="4" t="s">
         <v>2360</v>
@@ -23857,46 +23863,46 @@
       <c r="D1177" s="14"/>
     </row>
     <row r="1178" ht="22.5" customHeight="1">
-      <c r="A1178" s="9" t="s">
+      <c r="A1178" s="4" t="s">
         <v>2361</v>
       </c>
-      <c r="B1178" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1178" s="9" t="s">
+      <c r="B1178" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1178" s="4" t="s">
         <v>2362</v>
       </c>
       <c r="D1178" s="14"/>
     </row>
     <row r="1179" ht="22.5" customHeight="1">
-      <c r="A1179" s="18" t="s">
+      <c r="A1179" s="9" t="s">
         <v>2363</v>
       </c>
-      <c r="B1179" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1179" s="20" t="s">
+      <c r="B1179" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1179" s="9" t="s">
         <v>2364</v>
       </c>
       <c r="D1179" s="14"/>
     </row>
     <row r="1180" ht="22.5" customHeight="1">
-      <c r="A1180" s="9" t="s">
+      <c r="A1180" s="18" t="s">
         <v>2365</v>
       </c>
-      <c r="B1180" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1180" s="9" t="s">
+      <c r="B1180" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1180" s="20" t="s">
         <v>2366</v>
       </c>
       <c r="D1180" s="14"/>
     </row>
     <row r="1181" ht="22.5" customHeight="1">
-      <c r="A1181" s="4" t="s">
+      <c r="A1181" s="9" t="s">
         <v>2367</v>
       </c>
-      <c r="B1181" s="5" t="s">
+      <c r="B1181" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C1181" s="9" t="s">
@@ -23908,10 +23914,10 @@
       <c r="A1182" s="4" t="s">
         <v>2369</v>
       </c>
-      <c r="B1182" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1182" s="4" t="s">
+      <c r="B1182" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1182" s="9" t="s">
         <v>2370</v>
       </c>
       <c r="D1182" s="14"/>
@@ -23921,7 +23927,7 @@
         <v>2371</v>
       </c>
       <c r="B1183" s="7" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C1183" s="4" t="s">
         <v>2372</v>
@@ -23929,10 +23935,10 @@
       <c r="D1183" s="14"/>
     </row>
     <row r="1184" ht="22.5" customHeight="1">
-      <c r="A1184" s="9" t="s">
+      <c r="A1184" s="4" t="s">
         <v>2373</v>
       </c>
-      <c r="B1184" s="5" t="s">
+      <c r="B1184" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C1184" s="4" t="s">
@@ -23941,10 +23947,10 @@
       <c r="D1184" s="14"/>
     </row>
     <row r="1185" ht="22.5" customHeight="1">
-      <c r="A1185" s="4" t="s">
+      <c r="A1185" s="9" t="s">
         <v>2375</v>
       </c>
-      <c r="B1185" s="10" t="s">
+      <c r="B1185" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C1185" s="4" t="s">
@@ -23965,13 +23971,13 @@
       <c r="D1186" s="14"/>
     </row>
     <row r="1187" ht="22.5" customHeight="1">
-      <c r="A1187" s="9" t="s">
+      <c r="A1187" s="4" t="s">
         <v>2379</v>
       </c>
       <c r="B1187" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1187" s="9" t="s">
+      <c r="C1187" s="4" t="s">
         <v>2380</v>
       </c>
       <c r="D1187" s="14"/>
@@ -23989,13 +23995,13 @@
       <c r="D1188" s="14"/>
     </row>
     <row r="1189" ht="22.5" customHeight="1">
-      <c r="A1189" s="4" t="s">
+      <c r="A1189" s="9" t="s">
         <v>2383</v>
       </c>
       <c r="B1189" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1189" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1189" s="9" t="s">
         <v>2384</v>
       </c>
       <c r="D1189" s="14"/>
@@ -24017,7 +24023,7 @@
         <v>2387</v>
       </c>
       <c r="B1191" s="10" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C1191" s="4" t="s">
         <v>2388</v>
@@ -24025,13 +24031,13 @@
       <c r="D1191" s="14"/>
     </row>
     <row r="1192" ht="22.5" customHeight="1">
-      <c r="A1192" s="9" t="s">
+      <c r="A1192" s="4" t="s">
         <v>2389</v>
       </c>
-      <c r="B1192" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1192" s="9" t="s">
+      <c r="B1192" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1192" s="4" t="s">
         <v>2390</v>
       </c>
       <c r="D1192" s="14"/>
@@ -24049,13 +24055,13 @@
       <c r="D1193" s="14"/>
     </row>
     <row r="1194" ht="22.5" customHeight="1">
-      <c r="A1194" s="4" t="s">
+      <c r="A1194" s="9" t="s">
         <v>2393</v>
       </c>
-      <c r="B1194" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1194" s="4" t="s">
+      <c r="B1194" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1194" s="9" t="s">
         <v>2394</v>
       </c>
       <c r="D1194" s="14"/>
@@ -24073,13 +24079,13 @@
       <c r="D1195" s="14"/>
     </row>
     <row r="1196" ht="22.5" customHeight="1">
-      <c r="A1196" s="9" t="s">
+      <c r="A1196" s="4" t="s">
         <v>2397</v>
       </c>
-      <c r="B1196" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1196" s="9" t="s">
+      <c r="B1196" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1196" s="4" t="s">
         <v>2398</v>
       </c>
       <c r="D1196" s="14"/>
@@ -24088,8 +24094,8 @@
       <c r="A1197" s="9" t="s">
         <v>2399</v>
       </c>
-      <c r="B1197" s="7" t="s">
-        <v>61</v>
+      <c r="B1197" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C1197" s="9" t="s">
         <v>2400</v>
@@ -24097,13 +24103,13 @@
       <c r="D1197" s="14"/>
     </row>
     <row r="1198" ht="22.5" customHeight="1">
-      <c r="A1198" s="4" t="s">
+      <c r="A1198" s="9" t="s">
         <v>2401</v>
       </c>
-      <c r="B1198" s="10" t="s">
-        <v>796</v>
-      </c>
-      <c r="C1198" s="4" t="s">
+      <c r="B1198" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1198" s="9" t="s">
         <v>2402</v>
       </c>
       <c r="D1198" s="14"/>
@@ -24113,7 +24119,7 @@
         <v>2403</v>
       </c>
       <c r="B1199" s="10" t="s">
-        <v>4</v>
+        <v>796</v>
       </c>
       <c r="C1199" s="4" t="s">
         <v>2404</v>
@@ -24124,7 +24130,7 @@
       <c r="A1200" s="4" t="s">
         <v>2405</v>
       </c>
-      <c r="B1200" s="7" t="s">
+      <c r="B1200" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C1200" s="4" t="s">
@@ -24137,7 +24143,7 @@
         <v>2407</v>
       </c>
       <c r="B1201" s="7" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="C1201" s="4" t="s">
         <v>2408</v>
@@ -24149,7 +24155,7 @@
         <v>2409</v>
       </c>
       <c r="B1202" s="7" t="s">
-        <v>796</v>
+        <v>61</v>
       </c>
       <c r="C1202" s="4" t="s">
         <v>2410</v>
@@ -24161,7 +24167,7 @@
         <v>2411</v>
       </c>
       <c r="B1203" s="7" t="s">
-        <v>107</v>
+        <v>796</v>
       </c>
       <c r="C1203" s="4" t="s">
         <v>2412</v>
@@ -24169,25 +24175,25 @@
       <c r="D1203" s="14"/>
     </row>
     <row r="1204" ht="22.5" customHeight="1">
-      <c r="A1204" s="9" t="s">
+      <c r="A1204" s="4" t="s">
         <v>2413</v>
       </c>
-      <c r="B1204" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1204" s="9" t="s">
+      <c r="B1204" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1204" s="4" t="s">
         <v>2414</v>
       </c>
       <c r="D1204" s="14"/>
     </row>
     <row r="1205" ht="22.5" customHeight="1">
-      <c r="A1205" s="4" t="s">
+      <c r="A1205" s="9" t="s">
         <v>2415</v>
       </c>
-      <c r="B1205" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C1205" s="4" t="s">
+      <c r="B1205" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1205" s="9" t="s">
         <v>2416</v>
       </c>
       <c r="D1205" s="14"/>
@@ -24208,7 +24214,7 @@
       <c r="A1207" s="4" t="s">
         <v>2419</v>
       </c>
-      <c r="B1207" s="10" t="s">
+      <c r="B1207" s="7" t="s">
         <v>107</v>
       </c>
       <c r="C1207" s="4" t="s">
@@ -24220,7 +24226,7 @@
       <c r="A1208" s="4" t="s">
         <v>2421</v>
       </c>
-      <c r="B1208" s="7" t="s">
+      <c r="B1208" s="10" t="s">
         <v>107</v>
       </c>
       <c r="C1208" s="4" t="s">
@@ -24229,13 +24235,13 @@
       <c r="D1208" s="14"/>
     </row>
     <row r="1209" ht="22.5" customHeight="1">
-      <c r="A1209" s="9" t="s">
+      <c r="A1209" s="4" t="s">
         <v>2423</v>
       </c>
-      <c r="B1209" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1209" s="9" t="s">
+      <c r="B1209" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1209" s="4" t="s">
         <v>2424</v>
       </c>
       <c r="D1209" s="14"/>
@@ -24245,7 +24251,7 @@
         <v>2425</v>
       </c>
       <c r="B1210" s="10" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="C1210" s="9" t="s">
         <v>2426</v>
@@ -24265,13 +24271,13 @@
       <c r="D1211" s="14"/>
     </row>
     <row r="1212" ht="22.5" customHeight="1">
-      <c r="A1212" s="4" t="s">
+      <c r="A1212" s="9" t="s">
         <v>2429</v>
       </c>
-      <c r="B1212" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1212" s="4" t="s">
+      <c r="B1212" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1212" s="9" t="s">
         <v>2430</v>
       </c>
       <c r="D1212" s="14"/>
@@ -24280,8 +24286,8 @@
       <c r="A1213" s="4" t="s">
         <v>2431</v>
       </c>
-      <c r="B1213" s="10" t="s">
-        <v>4</v>
+      <c r="B1213" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C1213" s="4" t="s">
         <v>2432</v>
@@ -24301,25 +24307,25 @@
       <c r="D1214" s="14"/>
     </row>
     <row r="1215" ht="22.5" customHeight="1">
-      <c r="A1215" s="9" t="s">
+      <c r="A1215" s="4" t="s">
         <v>2435</v>
       </c>
-      <c r="B1215" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1215" s="9" t="s">
+      <c r="B1215" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1215" s="4" t="s">
         <v>2436</v>
       </c>
       <c r="D1215" s="14"/>
     </row>
     <row r="1216" ht="22.5" customHeight="1">
-      <c r="A1216" s="4" t="s">
+      <c r="A1216" s="9" t="s">
         <v>2437</v>
       </c>
-      <c r="B1216" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1216" s="4" t="s">
+      <c r="B1216" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1216" s="9" t="s">
         <v>2438</v>
       </c>
       <c r="D1216" s="14"/>
@@ -24349,25 +24355,25 @@
       <c r="D1218" s="14"/>
     </row>
     <row r="1219" ht="22.5" customHeight="1">
-      <c r="A1219" s="9" t="s">
+      <c r="A1219" s="4" t="s">
         <v>2443</v>
       </c>
       <c r="B1219" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1219" s="9" t="s">
+      <c r="C1219" s="4" t="s">
         <v>2444</v>
       </c>
       <c r="D1219" s="14"/>
     </row>
     <row r="1220" ht="22.5" customHeight="1">
-      <c r="A1220" s="4" t="s">
+      <c r="A1220" s="9" t="s">
         <v>2445</v>
       </c>
       <c r="B1220" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1220" s="4" t="s">
+      <c r="C1220" s="9" t="s">
         <v>2446</v>
       </c>
       <c r="D1220" s="14"/>
@@ -24385,13 +24391,13 @@
       <c r="D1221" s="14"/>
     </row>
     <row r="1222" ht="22.5" customHeight="1">
-      <c r="A1222" s="9" t="s">
+      <c r="A1222" s="4" t="s">
         <v>2449</v>
       </c>
       <c r="B1222" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1222" s="9" t="s">
+      <c r="C1222" s="4" t="s">
         <v>2450</v>
       </c>
       <c r="D1222" s="14"/>
@@ -24409,13 +24415,13 @@
       <c r="D1223" s="14"/>
     </row>
     <row r="1224" ht="22.5" customHeight="1">
-      <c r="A1224" s="4" t="s">
+      <c r="A1224" s="9" t="s">
         <v>2453</v>
       </c>
-      <c r="B1224" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1224" s="4" t="s">
+      <c r="B1224" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1224" s="9" t="s">
         <v>2454</v>
       </c>
       <c r="D1224" s="14"/>
@@ -24424,7 +24430,7 @@
       <c r="A1225" s="4" t="s">
         <v>2455</v>
       </c>
-      <c r="B1225" s="10" t="s">
+      <c r="B1225" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C1225" s="4" t="s">
@@ -24433,25 +24439,25 @@
       <c r="D1225" s="14"/>
     </row>
     <row r="1226" ht="22.5" customHeight="1">
-      <c r="A1226" s="9" t="s">
+      <c r="A1226" s="4" t="s">
         <v>2457</v>
       </c>
-      <c r="B1226" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1226" s="9" t="s">
+      <c r="B1226" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1226" s="4" t="s">
         <v>2458</v>
       </c>
       <c r="D1226" s="14"/>
     </row>
     <row r="1227" ht="22.5" customHeight="1">
-      <c r="A1227" s="4" t="s">
+      <c r="A1227" s="9" t="s">
         <v>2459</v>
       </c>
-      <c r="B1227" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1227" s="4" t="s">
+      <c r="B1227" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1227" s="9" t="s">
         <v>2460</v>
       </c>
       <c r="D1227" s="14"/>
@@ -24469,13 +24475,13 @@
       <c r="D1228" s="14"/>
     </row>
     <row r="1229" ht="22.5" customHeight="1">
-      <c r="A1229" s="9" t="s">
+      <c r="A1229" s="4" t="s">
         <v>2463</v>
       </c>
-      <c r="B1229" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1229" s="9" t="s">
+      <c r="B1229" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1229" s="4" t="s">
         <v>2464</v>
       </c>
       <c r="D1229" s="14"/>
@@ -24484,8 +24490,8 @@
       <c r="A1230" s="9" t="s">
         <v>2465</v>
       </c>
-      <c r="B1230" s="10" t="s">
-        <v>61</v>
+      <c r="B1230" s="7" t="s">
+        <v>4</v>
       </c>
       <c r="C1230" s="9" t="s">
         <v>2466</v>
@@ -24497,7 +24503,7 @@
         <v>2467</v>
       </c>
       <c r="B1231" s="10" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C1231" s="9" t="s">
         <v>2468</v>
@@ -24505,13 +24511,13 @@
       <c r="D1231" s="14"/>
     </row>
     <row r="1232" ht="22.5" customHeight="1">
-      <c r="A1232" s="4" t="s">
+      <c r="A1232" s="9" t="s">
         <v>2469</v>
       </c>
-      <c r="B1232" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1232" s="4" t="s">
+      <c r="B1232" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1232" s="9" t="s">
         <v>2470</v>
       </c>
       <c r="D1232" s="14"/>
@@ -24520,8 +24526,8 @@
       <c r="A1233" s="4" t="s">
         <v>2471</v>
       </c>
-      <c r="B1233" s="7" t="s">
-        <v>61</v>
+      <c r="B1233" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="C1233" s="4" t="s">
         <v>2472</v>
@@ -24533,7 +24539,7 @@
         <v>2473</v>
       </c>
       <c r="B1234" s="7" t="s">
-        <v>579</v>
+        <v>61</v>
       </c>
       <c r="C1234" s="4" t="s">
         <v>2474</v>
@@ -24544,17 +24550,29 @@
       <c r="A1235" s="4" t="s">
         <v>2475</v>
       </c>
-      <c r="B1235" s="10" t="s">
-        <v>4</v>
+      <c r="B1235" s="7" t="s">
+        <v>579</v>
       </c>
       <c r="C1235" s="4" t="s">
         <v>2476</v>
       </c>
       <c r="D1235" s="14"/>
     </row>
+    <row r="1236" ht="22.5" customHeight="1">
+      <c r="A1236" s="4" t="s">
+        <v>2477</v>
+      </c>
+      <c r="B1236" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1236" s="4" t="s">
+        <v>2478</v>
+      </c>
+      <c r="D1236" s="14"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B1235">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B1236">
       <formula1>"adjective,adverb,adverb-preposition,conjunction,noun,numeral,phrase,preposition,pronoun,verb,interjection,prefix,suffix,article"</formula1>
     </dataValidation>
   </dataValidations>
@@ -24577,58 +24595,58 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="21" t="s">
-        <v>2477</v>
+        <v>2479</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>1790</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="22" t="s">
-        <v>2478</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="23" t="s">
-        <v>2479</v>
+        <v>2481</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>2480</v>
+        <v>2482</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="24" t="s">
-        <v>2481</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="23" t="s">
-        <v>2482</v>
+        <v>2484</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>2483</v>
+        <v>2485</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="24" t="s">
-        <v>2484</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="23" t="s">
-        <v>2485</v>
+        <v>2487</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="24" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>2488</v>
+        <v>2490</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="25"/>
@@ -24637,10 +24655,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="21" t="s">
-        <v>2490</v>
+        <v>2492</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="C6" s="23" t="s">
         <v>1321</v>
@@ -24652,13 +24670,13 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="21" t="s">
-        <v>2492</v>
+        <v>2494</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="25"/>
@@ -24667,13 +24685,13 @@
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="21" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="25"/>
@@ -24682,13 +24700,13 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="21" t="s">
-        <v>2498</v>
+        <v>2500</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="25"/>
@@ -24697,11 +24715,11 @@
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="21" t="s">
-        <v>2501</v>
+        <v>2503</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="24" t="s">
-        <v>2502</v>
+        <v>2504</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="25"/>
@@ -24710,10 +24728,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="21" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="25"/>
@@ -24731,7 +24749,7 @@
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="21" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>1804</v>
@@ -24743,7 +24761,7 @@
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="23" t="s">
-        <v>2479</v>
+        <v>2481</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>1804</v>
@@ -24755,10 +24773,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="23" t="s">
-        <v>2482</v>
+        <v>2484</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="25"/>
@@ -24767,10 +24785,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="23" t="s">
-        <v>2485</v>
+        <v>2487</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="25"/>
@@ -24779,10 +24797,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="21" t="s">
-        <v>2488</v>
+        <v>2490</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="25"/>
@@ -24791,10 +24809,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="21" t="s">
-        <v>2490</v>
+        <v>2492</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="C18" s="23" t="s">
         <v>1321</v>
@@ -24806,13 +24824,13 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="21" t="s">
-        <v>2492</v>
+        <v>2494</v>
       </c>
       <c r="B19" s="24" t="s">
         <v>1804</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="25"/>
@@ -24821,13 +24839,13 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="21" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>2511</v>
+        <v>2513</v>
       </c>
       <c r="D20" s="25"/>
       <c r="E20" s="25"/>
@@ -24836,13 +24854,13 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="21" t="s">
-        <v>2498</v>
+        <v>2500</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="D21" s="25"/>
       <c r="E21" s="25"/>
@@ -24851,11 +24869,11 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="21" t="s">
-        <v>2501</v>
+        <v>2503</v>
       </c>
       <c r="B22" s="21"/>
       <c r="C22" s="24" t="s">
-        <v>2512</v>
+        <v>2514</v>
       </c>
       <c r="D22" s="25"/>
       <c r="E22" s="25"/>
@@ -24864,7 +24882,7 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="B23" s="24" t="s">
         <v>1804</v>
@@ -24909,86 +24927,86 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="22" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="D1" s="27"/>
       <c r="E1" s="26" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="B2" s="26" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="D2" s="27"/>
       <c r="E2" s="26" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="26" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>278</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
       <c r="D3" s="27"/>
       <c r="E3" s="26" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="J3" s="26" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="26" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>2524</v>
+        <v>2526</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="27" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
       <c r="F4" s="28" t="s">
         <v>866</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
       <c r="H4" s="27" t="s">
         <v>1212</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
       <c r="J4" s="27" t="s">
         <v>284</v>
@@ -24996,13 +25014,13 @@
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="27" t="s">
@@ -25012,13 +25030,13 @@
         <v>1220</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>2531</v>
+        <v>2533</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>1206</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>2532</v>
+        <v>2534</v>
       </c>
       <c r="J5" s="27" t="s">
         <v>1200</v>
@@ -25030,7 +25048,7 @@
       <c r="C6" s="27"/>
       <c r="D6" s="27"/>
       <c r="E6" s="27" t="s">
-        <v>2533</v>
+        <v>2535</v>
       </c>
       <c r="F6" s="27" t="s">
         <v>1620</v>
@@ -25038,7 +25056,7 @@
       <c r="G6" s="30"/>
       <c r="H6" s="30"/>
       <c r="I6" s="27" t="s">
-        <v>2534</v>
+        <v>2536</v>
       </c>
       <c r="J6" s="27" t="s">
         <v>1536</v>
@@ -25046,20 +25064,20 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="22" t="s">
-        <v>2535</v>
+        <v>2537</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>1220</v>
       </c>
       <c r="D7" s="30"/>
       <c r="E7" s="27" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
       <c r="F7" s="28" t="s">
         <v>278</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
       <c r="J7" s="27" t="s">
         <v>3</v>
@@ -25067,15 +25085,15 @@
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="B8" s="26" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="D8" s="27"/>
       <c r="H8" s="30"/>
       <c r="I8" s="27" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
       <c r="J8" s="27" t="s">
         <v>1222</v>
@@ -25083,43 +25101,43 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="26" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>1220</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="22" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="H9" s="30"/>
       <c r="I9" s="27" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="26" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="D10" s="30"/>
       <c r="F10" s="26" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="H10" s="30"/>
       <c r="I10" s="27" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
       <c r="J10" s="27" t="s">
         <v>1003</v>
@@ -25127,27 +25145,27 @@
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="26" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>2543</v>
+        <v>2545</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
       <c r="D11" s="30"/>
       <c r="E11" s="26" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>2545</v>
+        <v>2547</v>
       </c>
       <c r="H11" s="31"/>
       <c r="I11" s="27" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
       <c r="J11" s="27" t="s">
         <v>1182</v>
@@ -25159,11 +25177,11 @@
       <c r="C12" s="30"/>
       <c r="D12" s="30"/>
       <c r="E12" s="26" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="H12" s="31"/>
       <c r="I12" s="27" t="s">
-        <v>2547</v>
+        <v>2549</v>
       </c>
       <c r="J12" s="27" t="s">
         <v>791</v>
@@ -25171,24 +25189,24 @@
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="22" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>242</v>
       </c>
       <c r="D13" s="30"/>
       <c r="E13" s="26" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>2548</v>
+        <v>2550</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>2549</v>
+        <v>2551</v>
       </c>
       <c r="H13" s="27"/>
       <c r="I13" s="27" t="s">
-        <v>2550</v>
+        <v>2552</v>
       </c>
       <c r="J13" s="27" t="s">
         <v>1186</v>
@@ -25196,15 +25214,15 @@
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="B14" s="26" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="D14" s="30"/>
       <c r="H14" s="27"/>
       <c r="I14" s="27" t="s">
-        <v>2551</v>
+        <v>2553</v>
       </c>
       <c r="J14" s="27" t="s">
         <v>274</v>
@@ -25212,23 +25230,23 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="26" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="B15" s="27" t="s">
         <v>242</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>2552</v>
+        <v>2554</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>2553</v>
+        <v>2555</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="H15" s="27"/>
       <c r="I15" s="27" t="s">
-        <v>2554</v>
+        <v>2556</v>
       </c>
       <c r="J15" s="27" t="s">
         <v>1036</v>
@@ -25236,46 +25254,46 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="26" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>2555</v>
+        <v>2557</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>2556</v>
+        <v>2558</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="H16" s="31"/>
       <c r="I16" s="27" t="s">
-        <v>2557</v>
+        <v>2559</v>
       </c>
       <c r="J16" s="27" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="26" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>2558</v>
+        <v>2560</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>2559</v>
+        <v>2561</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>2560</v>
+        <v>2562</v>
       </c>
       <c r="H17" s="31"/>
       <c r="I17" s="31"/>
@@ -25283,7 +25301,7 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="E18" s="26" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="H18" s="27"/>
       <c r="I18" s="27"/>
@@ -25295,13 +25313,13 @@
       <c r="C19" s="27"/>
       <c r="D19" s="27"/>
       <c r="E19" s="26" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>2561</v>
+        <v>2563</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>2562</v>
+        <v>2564</v>
       </c>
       <c r="H19" s="27"/>
     </row>
@@ -25317,44 +25335,44 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="26" t="s">
-        <v>2563</v>
+        <v>2565</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="B22" s="26" t="s">
-        <v>2564</v>
+        <v>2566</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>2565</v>
+        <v>2567</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>2566</v>
+        <v>2568</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>2567</v>
+        <v>2569</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="G22" s="26" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="H22" s="26" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="26" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="B23" s="27" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D23" s="27" t="s">
         <v>35</v>
@@ -25363,7 +25381,7 @@
         <v>29</v>
       </c>
       <c r="F23" s="27" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="G23" s="27" t="s">
         <v>1740</v>
@@ -25374,7 +25392,7 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="26" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="B24" s="27" t="s">
         <v>13</v>
@@ -25391,7 +25409,7 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="26" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="B25" s="27" t="s">
         <v>15</v>
@@ -25406,61 +25424,61 @@
         <v>27</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>2573</v>
+        <v>2575</v>
       </c>
       <c r="G25" s="27" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="26" t="s">
-        <v>2563</v>
+        <v>2565</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="B27" s="26" t="s">
-        <v>2564</v>
+        <v>2566</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>2565</v>
+        <v>2567</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>2566</v>
+        <v>2568</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>2567</v>
+        <v>2569</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="26" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="B28" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="D28" s="27" t="s">
         <v>41</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>2576</v>
+        <v>2578</v>
       </c>
       <c r="G28" s="27" t="s">
-        <v>2577</v>
+        <v>2579</v>
       </c>
       <c r="H28" s="27" t="s">
         <v>500</v>
@@ -25468,13 +25486,13 @@
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="26" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="B29" s="27" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>2578</v>
+        <v>2580</v>
       </c>
       <c r="D29" s="27" t="s">
         <v>37</v>
@@ -25482,22 +25500,22 @@
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="26" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="B30" s="27" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>2579</v>
+        <v>2581</v>
       </c>
       <c r="D30" s="27" t="s">
         <v>39</v>
       </c>
       <c r="F30" s="27" t="s">
-        <v>2580</v>
+        <v>2582</v>
       </c>
       <c r="G30" s="27" t="s">
-        <v>2581</v>
+        <v>2583</v>
       </c>
     </row>
   </sheetData>
@@ -25553,10 +25571,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="26" t="s">
-        <v>2582</v>
+        <v>2584</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>2583</v>
+        <v>2585</v>
       </c>
       <c r="E1" s="30"/>
       <c r="F1" s="31"/>
@@ -25587,51 +25605,51 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="26" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
       <c r="E4" s="30"/>
       <c r="F4" s="26" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
       <c r="J4" s="27"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="22" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="E5" s="30"/>
       <c r="F5" s="22" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="J5" s="27"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="22"/>
       <c r="B6" s="26" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="E6" s="30"/>
       <c r="F6" s="22"/>
       <c r="G6" s="26" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="J6" s="27"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="26" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>1446</v>
@@ -25640,11 +25658,11 @@
         <v>1446</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>2586</v>
+        <v>2588</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="26" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="G7" s="27" t="s">
         <v>1680</v>
@@ -25653,193 +25671,193 @@
         <v>1680</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>2587</v>
+        <v>2589</v>
       </c>
       <c r="J7" s="27"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="26" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>2588</v>
+        <v>2590</v>
       </c>
       <c r="E8" s="30"/>
       <c r="F8" s="26" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>2587</v>
+        <v>2589</v>
       </c>
       <c r="J8" s="27"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="26" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="26" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="J9" s="27"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="26" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="E10" s="30"/>
       <c r="F10" s="26" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="J10" s="27"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="22"/>
       <c r="B11" s="26" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="E11" s="30"/>
       <c r="F11" s="22"/>
       <c r="G11" s="26" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="I11" s="26" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="J11" s="27"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="26" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>1446</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>2588</v>
+        <v>2590</v>
       </c>
       <c r="E12" s="30"/>
       <c r="F12" s="26" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>2590</v>
+        <v>2592</v>
       </c>
       <c r="H12" s="27" t="s">
         <v>1680</v>
       </c>
       <c r="I12" s="27" t="s">
-        <v>2587</v>
+        <v>2589</v>
       </c>
       <c r="J12" s="27"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="26" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>2591</v>
+        <v>2593</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>2588</v>
+        <v>2590</v>
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="26" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>2587</v>
+        <v>2589</v>
       </c>
       <c r="J13" s="27"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="26" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
       <c r="E14" s="30"/>
       <c r="F14" s="26" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="J14" s="27"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="26" t="s">
-        <v>2592</v>
+        <v>2594</v>
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="26" t="s">
-        <v>2592</v>
+        <v>2594</v>
       </c>
       <c r="J15" s="27"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="26" t="s">
-        <v>2593</v>
+        <v>2595</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>2594</v>
+        <v>2596</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>2595</v>
+        <v>2597</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="30"/>
       <c r="F16" s="26" t="s">
-        <v>2593</v>
+        <v>2595</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>2596</v>
+        <v>2598</v>
       </c>
       <c r="H16" s="33"/>
       <c r="J16" s="27"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="26" t="s">
-        <v>2597</v>
+        <v>2599</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>2598</v>
+        <v>2600</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>2599</v>
+        <v>2601</v>
       </c>
       <c r="E17" s="30"/>
       <c r="F17" s="26" t="s">
-        <v>2597</v>
+        <v>2599</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>2600</v>
+        <v>2602</v>
       </c>
       <c r="J17" s="27"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="26" t="s">
-        <v>2601</v>
+        <v>2603</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>2602</v>
+        <v>2604</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>2603</v>
+        <v>2605</v>
       </c>
       <c r="E18" s="30"/>
       <c r="F18" s="26" t="s">
-        <v>2601</v>
+        <v>2603</v>
       </c>
       <c r="G18" s="27" t="s">
         <v>1680</v>
@@ -25851,54 +25869,54 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="26" t="s">
-        <v>2604</v>
+        <v>2606</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>2605</v>
+        <v>2607</v>
       </c>
       <c r="J20" s="27"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="22" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="J21" s="27"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="22"/>
       <c r="B22" s="26" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="F22" s="22"/>
       <c r="G22" s="26" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="H22" s="26" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="I22" s="26" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="J22" s="27"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="26" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="B23" s="27" t="s">
         <v>793</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="G23" s="27" t="s">
         <v>163</v>
@@ -25907,66 +25925,66 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="26" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="J24" s="27"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="26" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="J25" s="27"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="26" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="E26" s="30"/>
       <c r="F26" s="26" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="J26" s="27"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="22"/>
       <c r="B27" s="26" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="E27" s="30"/>
       <c r="F27" s="22"/>
       <c r="G27" s="26" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="I27" s="26" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="J27" s="27"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="26" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="B28" s="27" t="s">
         <v>793</v>
       </c>
       <c r="E28" s="30"/>
       <c r="F28" s="26" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="G28" s="27" t="s">
         <v>163</v>
@@ -25975,81 +25993,81 @@
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="26" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="E29" s="30"/>
       <c r="F29" s="26" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="J29" s="27"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="26" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="E30" s="30"/>
       <c r="F30" s="26" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="J30" s="27"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="26" t="s">
-        <v>2592</v>
+        <v>2594</v>
       </c>
       <c r="E31" s="30"/>
       <c r="F31" s="26" t="s">
-        <v>2592</v>
+        <v>2594</v>
       </c>
       <c r="J31" s="27"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="26" t="s">
-        <v>2593</v>
+        <v>2595</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>2606</v>
+        <v>2608</v>
       </c>
       <c r="C32" s="33"/>
       <c r="E32" s="30"/>
       <c r="F32" s="26" t="s">
-        <v>2593</v>
+        <v>2595</v>
       </c>
       <c r="G32" s="27" t="s">
-        <v>2607</v>
+        <v>2609</v>
       </c>
       <c r="H32" s="33"/>
       <c r="J32" s="27"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="26" t="s">
-        <v>2597</v>
+        <v>2599</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>2608</v>
+        <v>2610</v>
       </c>
       <c r="E33" s="30"/>
       <c r="F33" s="26" t="s">
-        <v>2597</v>
+        <v>2599</v>
       </c>
       <c r="G33" s="27" t="s">
-        <v>2609</v>
+        <v>2611</v>
       </c>
       <c r="J33" s="27"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="26" t="s">
-        <v>2601</v>
+        <v>2603</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>2610</v>
+        <v>2612</v>
       </c>
       <c r="E34" s="30"/>
       <c r="F34" s="26" t="s">
-        <v>2601</v>
+        <v>2603</v>
       </c>
       <c r="G34" s="27" t="s">
-        <v>2611</v>
+        <v>2613</v>
       </c>
       <c r="J34" s="27"/>
     </row>
@@ -26067,10 +26085,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="26" t="s">
-        <v>2612</v>
+        <v>2614</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>2613</v>
+        <v>2615</v>
       </c>
       <c r="E36" s="30"/>
       <c r="F36" s="31"/>
@@ -26081,16 +26099,16 @@
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="26" t="s">
-        <v>2614</v>
+        <v>2616</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>2615</v>
+        <v>2617</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>2614</v>
+        <v>2616</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>2616</v>
+        <v>2618</v>
       </c>
       <c r="E37" s="30"/>
       <c r="F37" s="31"/>
@@ -26101,16 +26119,16 @@
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="26" t="s">
-        <v>2593</v>
+        <v>2595</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>2617</v>
+        <v>2619</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>2593</v>
+        <v>2595</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>2618</v>
+        <v>2620</v>
       </c>
       <c r="E38" s="30"/>
       <c r="F38" s="31"/>
@@ -26121,16 +26139,16 @@
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="26" t="s">
-        <v>2597</v>
+        <v>2599</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>2619</v>
+        <v>2621</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>2597</v>
+        <v>2599</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>2620</v>
+        <v>2622</v>
       </c>
       <c r="E39" s="30"/>
       <c r="F39" s="31"/>
@@ -26281,108 +26299,108 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="26" t="s">
-        <v>2621</v>
+        <v>2623</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>2622</v>
+        <v>2624</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>2623</v>
+        <v>2625</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>1211</v>
       </c>
       <c r="F1" s="26" t="s">
-        <v>2621</v>
+        <v>2623</v>
       </c>
       <c r="G1" s="26" t="s">
-        <v>2622</v>
+        <v>2624</v>
       </c>
       <c r="H1" s="26" t="s">
-        <v>2623</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>2624</v>
+        <v>2626</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>2625</v>
+        <v>2627</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>2626</v>
+        <v>2628</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>2627</v>
+        <v>2629</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>2628</v>
+        <v>2630</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>2629</v>
+        <v>2631</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>2630</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="27" t="s">
-        <v>2631</v>
+        <v>2633</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>2632</v>
+        <v>2634</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>2633</v>
+        <v>2635</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>2634</v>
+        <v>2636</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>2635</v>
+        <v>2637</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>2636</v>
+        <v>2638</v>
       </c>
       <c r="H3" s="27" t="s">
-        <v>2637</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>2638</v>
+        <v>2640</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>2639</v>
+        <v>2641</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>2640</v>
+        <v>2642</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>2641</v>
+        <v>2643</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>2642</v>
+        <v>2644</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>2643</v>
+        <v>2645</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>2644</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>2645</v>
+        <v>2647</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>2646</v>
+        <v>2648</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>2647</v>
+        <v>2649</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>2648</v>
+        <v>2650</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
@@ -26390,131 +26408,131 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>2649</v>
+        <v>2651</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>2650</v>
+        <v>2652</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>2651</v>
+        <v>2653</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>2652</v>
+        <v>2654</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>2653</v>
+        <v>2655</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>2654</v>
+        <v>2656</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>2655</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>2656</v>
+        <v>2658</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>2657</v>
+        <v>2659</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>2658</v>
+        <v>2660</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>2636</v>
+        <v>2638</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>2659</v>
+        <v>2661</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>2660</v>
+        <v>2662</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>2661</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>2662</v>
+        <v>2664</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>2663</v>
+        <v>2665</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>2664</v>
+        <v>2666</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>2665</v>
+        <v>2667</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>2666</v>
+        <v>2668</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>2667</v>
+        <v>2669</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>2668</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>2669</v>
+        <v>2671</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>2670</v>
+        <v>2672</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>2671</v>
+        <v>2673</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>2672</v>
+        <v>2674</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>2673</v>
+        <v>2675</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>2674</v>
+        <v>2676</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>2675</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>2676</v>
+        <v>2678</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>2677</v>
+        <v>2679</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>2678</v>
+        <v>2680</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>2679</v>
+        <v>2681</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>2680</v>
+        <v>2682</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>2681</v>
+        <v>2683</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>2682</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>2683</v>
+        <v>2685</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>2684</v>
+        <v>2686</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>2685</v>
+        <v>2687</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>2686</v>
+        <v>2688</v>
       </c>
       <c r="F11" s="27"/>
       <c r="G11" s="27"/>
@@ -26522,156 +26540,156 @@
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>2687</v>
+        <v>2689</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>2688</v>
+        <v>2690</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>2689</v>
+        <v>2691</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>2690</v>
+        <v>2692</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>2691</v>
+        <v>2693</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>2692</v>
+        <v>2694</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>2693</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>2694</v>
+        <v>2696</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>2695</v>
+        <v>2697</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>2696</v>
+        <v>2698</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>2697</v>
+        <v>2699</v>
       </c>
       <c r="H13" s="27"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>2698</v>
+        <v>2700</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>2699</v>
+        <v>2701</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>2700</v>
+        <v>2702</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>2701</v>
+        <v>2703</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>2702</v>
+        <v>2704</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>2703</v>
+        <v>2705</v>
       </c>
       <c r="H14" s="27" t="s">
-        <v>2704</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>2705</v>
+        <v>2707</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>2706</v>
+        <v>2708</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>2707</v>
+        <v>2709</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>2708</v>
+        <v>2710</v>
       </c>
       <c r="H15" s="27"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>2709</v>
+        <v>2711</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>2710</v>
+        <v>2712</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>2711</v>
+        <v>2713</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>2643</v>
+        <v>2645</v>
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27" t="s">
-        <v>2712</v>
+        <v>2714</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>2713</v>
+        <v>2715</v>
       </c>
       <c r="H16" s="27" t="s">
-        <v>2714</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>2715</v>
+        <v>2717</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>2716</v>
+        <v>2718</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>2717</v>
+        <v>2719</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>2718</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>2719</v>
+        <v>2721</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>2720</v>
+        <v>2722</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>2721</v>
+        <v>2723</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>2722</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>2723</v>
+        <v>2725</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>2724</v>
+        <v>2726</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>2725</v>
+        <v>2727</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>2726</v>
+        <v>2728</v>
       </c>
       <c r="H19" s="27"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>2727</v>
+        <v>2729</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>2728</v>
+        <v>2730</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>2729</v>
+        <v>2731</v>
       </c>
       <c r="D20" s="27" t="s">
         <v>2280</v>
@@ -26683,16 +26701,16 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>2730</v>
+        <v>2732</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>2731</v>
+        <v>2733</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>2732</v>
+        <v>2734</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>2733</v>
+        <v>2735</v>
       </c>
       <c r="E21" s="27"/>
       <c r="F21" s="27"/>
@@ -26701,16 +26719,16 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>2734</v>
+        <v>2736</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>2735</v>
+        <v>2737</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>2736</v>
+        <v>2738</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>2737</v>
+        <v>2739</v>
       </c>
       <c r="E22" s="27"/>
       <c r="F22" s="27"/>
@@ -26719,16 +26737,16 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="27" t="s">
-        <v>2738</v>
+        <v>2740</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>2739</v>
+        <v>2741</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>2740</v>
+        <v>2742</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>2741</v>
+        <v>2743</v>
       </c>
       <c r="E23" s="27"/>
       <c r="F23" s="27"/>
@@ -26737,16 +26755,16 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>2742</v>
+        <v>2744</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>2743</v>
+        <v>2745</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>2744</v>
+        <v>2746</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>2745</v>
+        <v>2747</v>
       </c>
       <c r="E24" s="27"/>
       <c r="F24" s="27"/>
@@ -26755,16 +26773,16 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>2746</v>
+        <v>2748</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>2747</v>
+        <v>2749</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>2748</v>
+        <v>2750</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>2749</v>
+        <v>2751</v>
       </c>
       <c r="E25" s="27"/>
       <c r="F25" s="27"/>
@@ -26773,16 +26791,16 @@
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>2750</v>
+        <v>2752</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>2751</v>
+        <v>2753</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>2752</v>
+        <v>2754</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>2753</v>
+        <v>2755</v>
       </c>
       <c r="E26" s="27"/>
       <c r="F26" s="27"/>
@@ -26791,16 +26809,16 @@
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="27" t="s">
-        <v>2754</v>
+        <v>2756</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>2755</v>
+        <v>2757</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>2756</v>
+        <v>2758</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>2757</v>
+        <v>2759</v>
       </c>
       <c r="E27" s="27"/>
       <c r="F27" s="27"/>
@@ -26809,16 +26827,16 @@
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="27" t="s">
-        <v>2758</v>
+        <v>2760</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>2759</v>
+        <v>2761</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>2760</v>
+        <v>2762</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>2761</v>
+        <v>2763</v>
       </c>
       <c r="E28" s="27"/>
       <c r="F28" s="27"/>
@@ -26837,63 +26855,63 @@
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="22" t="s">
-        <v>2762</v>
+        <v>2764</v>
       </c>
       <c r="H30" s="27"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="24" t="s">
-        <v>2763</v>
+        <v>2765</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>2764</v>
+        <v>2766</v>
       </c>
       <c r="F31" s="24" t="s">
-        <v>2765</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="24" t="s">
-        <v>2766</v>
+        <v>2768</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>2767</v>
+        <v>2769</v>
       </c>
       <c r="F32" s="24" t="s">
-        <v>2768</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="24" t="s">
-        <v>2769</v>
+        <v>2771</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>2770</v>
+        <v>2772</v>
       </c>
       <c r="F33" s="24" t="s">
-        <v>2771</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="24" t="s">
-        <v>2772</v>
+        <v>2774</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>2773</v>
+        <v>2775</v>
       </c>
       <c r="F34" s="24" t="s">
-        <v>2774</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="24" t="s">
-        <v>2775</v>
+        <v>2777</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>2776</v>
+        <v>2778</v>
       </c>
       <c r="F35" s="24" t="s">
-        <v>2777</v>
+        <v>2779</v>
       </c>
     </row>
   </sheetData>
@@ -26931,175 +26949,175 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="34" t="s">
-        <v>2778</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="35" t="s">
-        <v>2779</v>
+        <v>2781</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>2780</v>
+        <v>2782</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>2781</v>
+        <v>2783</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>2782</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="35" t="s">
-        <v>2783</v>
+        <v>2785</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>2784</v>
+        <v>2786</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>2785</v>
+        <v>2787</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>2786</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="35" t="s">
-        <v>2787</v>
+        <v>2789</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>2788</v>
+        <v>2790</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>2789</v>
+        <v>2791</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>2790</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="35" t="s">
-        <v>2791</v>
+        <v>2793</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>2792</v>
+        <v>2794</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>2793</v>
+        <v>2795</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>2794</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="35" t="s">
-        <v>2795</v>
+        <v>2797</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>2796</v>
+        <v>2798</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>2797</v>
+        <v>2799</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>2798</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="35" t="s">
-        <v>2799</v>
+        <v>2801</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>2800</v>
+        <v>2802</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>2801</v>
+        <v>2803</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>2802</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="35" t="s">
-        <v>2803</v>
+        <v>2805</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>2804</v>
+        <v>2806</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>2805</v>
+        <v>2807</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>2806</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="35" t="s">
-        <v>2807</v>
+        <v>2809</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>2808</v>
+        <v>2810</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>2809</v>
+        <v>2811</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>2810</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="35" t="s">
-        <v>2811</v>
+        <v>2813</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>2812</v>
+        <v>2814</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>2813</v>
+        <v>2815</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>2806</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="35" t="s">
-        <v>2814</v>
+        <v>2816</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>2815</v>
+        <v>2817</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>2816</v>
+        <v>2818</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>2817</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="35" t="s">
-        <v>2818</v>
+        <v>2820</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>2819</v>
+        <v>2821</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>2820</v>
+        <v>2822</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>2821</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="36" t="s">
-        <v>2822</v>
+        <v>2824</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>2823</v>
+        <v>2825</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>2824</v>
+        <v>2826</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>2825</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
@@ -27116,7 +27134,7 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="36" t="s">
-        <v>2826</v>
+        <v>2828</v>
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="37"/>
@@ -27128,10 +27146,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>2827</v>
+        <v>2829</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>2828</v>
+        <v>2830</v>
       </c>
       <c r="D16" s="27"/>
       <c r="E16" s="37"/>
@@ -27143,10 +27161,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>2829</v>
+        <v>2831</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>2830</v>
+        <v>2832</v>
       </c>
       <c r="D17" s="27"/>
       <c r="E17" s="27"/>
@@ -27158,10 +27176,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>2831</v>
+        <v>2833</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>2832</v>
+        <v>2834</v>
       </c>
       <c r="D18" s="27"/>
       <c r="E18" s="37"/>
@@ -27173,10 +27191,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>2833</v>
+        <v>2835</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>2834</v>
+        <v>2836</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="37"/>
@@ -27188,10 +27206,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>2835</v>
+        <v>2837</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>2836</v>
+        <v>2838</v>
       </c>
       <c r="D20" s="27"/>
       <c r="E20" s="37"/>
@@ -27215,18 +27233,18 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="34" t="s">
-        <v>2837</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="38" t="s">
-        <v>2838</v>
+        <v>2840</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>2839</v>
+        <v>2841</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>2840</v>
+        <v>2842</v>
       </c>
       <c r="J23" s="27"/>
     </row>
@@ -27235,46 +27253,46 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="39" t="s">
-        <v>2841</v>
+        <v>2843</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>2842</v>
+        <v>2844</v>
       </c>
       <c r="G25" s="39" t="s">
-        <v>2843</v>
+        <v>2845</v>
       </c>
       <c r="J25" s="27"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="39" t="s">
-        <v>2844</v>
+        <v>2846</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>2845</v>
+        <v>2847</v>
       </c>
       <c r="G26" s="39" t="s">
-        <v>2846</v>
+        <v>2848</v>
       </c>
       <c r="J26" s="27"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="39" t="s">
-        <v>2847</v>
+        <v>2849</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>2848</v>
+        <v>2850</v>
       </c>
       <c r="G27" s="39" t="s">
-        <v>2849</v>
+        <v>2851</v>
       </c>
       <c r="J27" s="27"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="38" t="s">
-        <v>2850</v>
+        <v>2852</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>2851</v>
+        <v>2853</v>
       </c>
       <c r="G28" s="27"/>
       <c r="H28" s="27"/>

--- a/Conlangs/Kagalarian.xlsx
+++ b/Conlangs/Kagalarian.xlsx
@@ -11,14 +11,14 @@
     <sheet state="visible" name="Grammar" sheetId="6" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Kagalarian!$A$1:$C$1236</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Kagalarian!$A$1:$C$1238</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4293" uniqueCount="2854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4299" uniqueCount="2858">
   <si>
     <t>Word</t>
   </si>
@@ -3522,6 +3522,18 @@
   </si>
   <si>
     <t>module, addon, extension</t>
+  </si>
+  <si>
+    <t>griyza</t>
+  </si>
+  <si>
+    <t>mold, mould, mold fungus</t>
+  </si>
+  <si>
+    <t>griyzniy</t>
+  </si>
+  <si>
+    <t>moldy</t>
   </si>
   <si>
     <t>jenerev</t>
@@ -9379,7 +9391,7 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -9544,8 +9556,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C1236" displayName="Table1" name="Table1" id="1">
-  <autoFilter ref="$A$1:$C$1236"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C1238" displayName="Table1" name="Table1" id="1">
+  <autoFilter ref="$A$1:$C$1238"/>
   <tableColumns count="3">
     <tableColumn name="Word" id="1"/>
     <tableColumn name="Part of Speech" id="2"/>
@@ -16687,25 +16699,25 @@
       <c r="D579" s="13"/>
     </row>
     <row r="580" ht="22.5" customHeight="1">
-      <c r="A580" s="9" t="s">
+      <c r="A580" s="4" t="s">
         <v>1168</v>
       </c>
       <c r="B580" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C580" s="9" t="s">
+      <c r="C580" s="4" t="s">
         <v>1169</v>
       </c>
       <c r="D580" s="13"/>
     </row>
     <row r="581" ht="22.5" customHeight="1">
-      <c r="A581" s="9" t="s">
+      <c r="A581" s="4" t="s">
         <v>1170</v>
       </c>
       <c r="B581" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C581" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C581" s="4" t="s">
         <v>1171</v>
       </c>
       <c r="D581" s="13"/>
@@ -16750,8 +16762,8 @@
       <c r="A585" s="9" t="s">
         <v>1178</v>
       </c>
-      <c r="B585" s="7" t="s">
-        <v>61</v>
+      <c r="B585" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C585" s="9" t="s">
         <v>1179</v>
@@ -16759,73 +16771,73 @@
       <c r="D585" s="13"/>
     </row>
     <row r="586" ht="22.5" customHeight="1">
-      <c r="A586" s="4" t="s">
+      <c r="A586" s="9" t="s">
         <v>1180</v>
       </c>
-      <c r="B586" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C586" s="4" t="s">
+      <c r="B586" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C586" s="9" t="s">
         <v>1181</v>
       </c>
       <c r="D586" s="13"/>
     </row>
     <row r="587" ht="22.5" customHeight="1">
-      <c r="A587" s="4" t="s">
+      <c r="A587" s="9" t="s">
         <v>1182</v>
       </c>
-      <c r="B587" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C587" s="4" t="s">
+      <c r="B587" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C587" s="9" t="s">
         <v>1183</v>
       </c>
       <c r="D587" s="13"/>
     </row>
     <row r="588" ht="22.5" customHeight="1">
-      <c r="A588" s="9" t="s">
+      <c r="A588" s="4" t="s">
         <v>1184</v>
       </c>
       <c r="B588" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C588" s="9" t="s">
+      <c r="C588" s="4" t="s">
         <v>1185</v>
       </c>
       <c r="D588" s="13"/>
     </row>
     <row r="589" ht="22.5" customHeight="1">
-      <c r="A589" s="9" t="s">
+      <c r="A589" s="4" t="s">
         <v>1186</v>
       </c>
       <c r="B589" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C589" s="9" t="s">
+      <c r="C589" s="4" t="s">
         <v>1187</v>
       </c>
       <c r="D589" s="13"/>
     </row>
     <row r="590" ht="22.5" customHeight="1">
-      <c r="A590" s="4" t="s">
+      <c r="A590" s="9" t="s">
         <v>1188</v>
       </c>
-      <c r="B590" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C590" s="4" t="s">
+      <c r="B590" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C590" s="9" t="s">
         <v>1189</v>
       </c>
       <c r="D590" s="13"/>
     </row>
     <row r="591" ht="22.5" customHeight="1">
-      <c r="A591" s="4" t="s">
+      <c r="A591" s="9" t="s">
         <v>1190</v>
       </c>
-      <c r="B591" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C591" s="4" t="s">
+      <c r="B591" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C591" s="9" t="s">
         <v>1191</v>
       </c>
       <c r="D591" s="13"/>
@@ -16834,7 +16846,7 @@
       <c r="A592" s="4" t="s">
         <v>1192</v>
       </c>
-      <c r="B592" s="5" t="s">
+      <c r="B592" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C592" s="4" t="s">
@@ -16843,70 +16855,70 @@
       <c r="D592" s="13"/>
     </row>
     <row r="593" ht="22.5" customHeight="1">
-      <c r="A593" s="9" t="s">
+      <c r="A593" s="4" t="s">
         <v>1194</v>
       </c>
       <c r="B593" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C593" s="9" t="s">
+      <c r="C593" s="4" t="s">
         <v>1195</v>
       </c>
       <c r="D593" s="13"/>
     </row>
     <row r="594" ht="22.5" customHeight="1">
-      <c r="A594" s="9" t="s">
+      <c r="A594" s="4" t="s">
         <v>1196</v>
       </c>
-      <c r="B594" s="10" t="s">
+      <c r="B594" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C594" s="4" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D594" s="13"/>
+    </row>
+    <row r="595" ht="22.5" customHeight="1">
+      <c r="A595" s="9" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B595" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C595" s="9" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D595" s="13"/>
+    </row>
+    <row r="596" ht="22.5" customHeight="1">
+      <c r="A596" s="9" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B596" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C594" s="9" t="s">
-        <v>1197</v>
-      </c>
-      <c r="D594" s="13"/>
-    </row>
-    <row r="595" ht="22.5" customHeight="1">
-      <c r="A595" s="4" t="s">
-        <v>1198</v>
-      </c>
-      <c r="B595" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C595" s="4" t="s">
-        <v>1198</v>
-      </c>
-      <c r="D595" s="13"/>
-    </row>
-    <row r="596" ht="22.5" customHeight="1">
-      <c r="A596" s="4" t="s">
-        <v>1199</v>
-      </c>
-      <c r="B596" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C596" s="4" t="s">
-        <v>1199</v>
+      <c r="C596" s="9" t="s">
+        <v>1201</v>
       </c>
       <c r="D596" s="13"/>
     </row>
     <row r="597" ht="22.5" customHeight="1">
       <c r="A597" s="4" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="B597" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C597" s="4" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="D597" s="13"/>
     </row>
     <row r="598" ht="22.5" customHeight="1">
       <c r="A598" s="4" t="s">
-        <v>1202</v>
-      </c>
-      <c r="B598" s="10" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B598" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C598" s="4" t="s">
@@ -16918,8 +16930,8 @@
       <c r="A599" s="4" t="s">
         <v>1204</v>
       </c>
-      <c r="B599" s="7" t="s">
-        <v>61</v>
+      <c r="B599" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C599" s="4" t="s">
         <v>1205</v>
@@ -16927,13 +16939,13 @@
       <c r="D599" s="13"/>
     </row>
     <row r="600" ht="22.5" customHeight="1">
-      <c r="A600" s="9" t="s">
+      <c r="A600" s="4" t="s">
         <v>1206</v>
       </c>
       <c r="B600" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C600" s="9" t="s">
+      <c r="C600" s="4" t="s">
         <v>1207</v>
       </c>
       <c r="D600" s="13"/>
@@ -16942,8 +16954,8 @@
       <c r="A601" s="4" t="s">
         <v>1208</v>
       </c>
-      <c r="B601" s="5" t="s">
-        <v>4</v>
+      <c r="B601" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C601" s="4" t="s">
         <v>1209</v>
@@ -16954,7 +16966,7 @@
       <c r="A602" s="9" t="s">
         <v>1210</v>
       </c>
-      <c r="B602" s="5" t="s">
+      <c r="B602" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C602" s="9" t="s">
@@ -16963,37 +16975,37 @@
       <c r="D602" s="13"/>
     </row>
     <row r="603" ht="22.5" customHeight="1">
-      <c r="A603" s="9" t="s">
+      <c r="A603" s="4" t="s">
         <v>1212</v>
       </c>
       <c r="B603" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C603" s="9" t="s">
+      <c r="C603" s="4" t="s">
         <v>1213</v>
       </c>
       <c r="D603" s="13"/>
     </row>
     <row r="604" ht="22.5" customHeight="1">
-      <c r="A604" s="4" t="s">
+      <c r="A604" s="9" t="s">
         <v>1214</v>
       </c>
-      <c r="B604" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C604" s="4" t="s">
+      <c r="B604" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C604" s="9" t="s">
         <v>1215</v>
       </c>
       <c r="D604" s="13"/>
     </row>
     <row r="605" ht="22.5" customHeight="1">
-      <c r="A605" s="4" t="s">
+      <c r="A605" s="9" t="s">
         <v>1216</v>
       </c>
-      <c r="B605" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C605" s="4" t="s">
+      <c r="B605" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C605" s="9" t="s">
         <v>1217</v>
       </c>
       <c r="D605" s="13"/>
@@ -17014,8 +17026,8 @@
       <c r="A607" s="4" t="s">
         <v>1220</v>
       </c>
-      <c r="B607" s="5" t="s">
-        <v>4</v>
+      <c r="B607" s="10" t="s">
+        <v>61</v>
       </c>
       <c r="C607" s="4" t="s">
         <v>1221</v>
@@ -17026,8 +17038,8 @@
       <c r="A608" s="4" t="s">
         <v>1222</v>
       </c>
-      <c r="B608" s="10" t="s">
-        <v>4</v>
+      <c r="B608" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C608" s="4" t="s">
         <v>1223</v>
@@ -17038,7 +17050,7 @@
       <c r="A609" s="4" t="s">
         <v>1224</v>
       </c>
-      <c r="B609" s="10" t="s">
+      <c r="B609" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C609" s="4" t="s">
@@ -17047,13 +17059,13 @@
       <c r="D609" s="13"/>
     </row>
     <row r="610" ht="22.5" customHeight="1">
-      <c r="A610" s="9" t="s">
+      <c r="A610" s="4" t="s">
         <v>1226</v>
       </c>
-      <c r="B610" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C610" s="9" t="s">
+      <c r="B610" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C610" s="4" t="s">
         <v>1227</v>
       </c>
       <c r="D610" s="13"/>
@@ -17071,13 +17083,13 @@
       <c r="D611" s="13"/>
     </row>
     <row r="612" ht="22.5" customHeight="1">
-      <c r="A612" s="4" t="s">
+      <c r="A612" s="9" t="s">
         <v>1230</v>
       </c>
-      <c r="B612" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C612" s="4" t="s">
+      <c r="B612" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C612" s="9" t="s">
         <v>1231</v>
       </c>
       <c r="D612" s="13"/>
@@ -17086,8 +17098,8 @@
       <c r="A613" s="4" t="s">
         <v>1232</v>
       </c>
-      <c r="B613" s="7" t="s">
-        <v>120</v>
+      <c r="B613" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C613" s="4" t="s">
         <v>1233</v>
@@ -17095,13 +17107,13 @@
       <c r="D613" s="13"/>
     </row>
     <row r="614" ht="22.5" customHeight="1">
-      <c r="A614" s="9" t="s">
+      <c r="A614" s="4" t="s">
         <v>1234</v>
       </c>
       <c r="B614" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C614" s="9" t="s">
+      <c r="C614" s="4" t="s">
         <v>1235</v>
       </c>
       <c r="D614" s="13"/>
@@ -17110,8 +17122,8 @@
       <c r="A615" s="4" t="s">
         <v>1236</v>
       </c>
-      <c r="B615" s="10" t="s">
-        <v>61</v>
+      <c r="B615" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="C615" s="4" t="s">
         <v>1237</v>
@@ -17119,13 +17131,13 @@
       <c r="D615" s="13"/>
     </row>
     <row r="616" ht="22.5" customHeight="1">
-      <c r="A616" s="4" t="s">
+      <c r="A616" s="9" t="s">
         <v>1238</v>
       </c>
-      <c r="B616" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C616" s="4" t="s">
+      <c r="B616" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C616" s="9" t="s">
         <v>1239</v>
       </c>
       <c r="D616" s="14"/>
@@ -17135,7 +17147,7 @@
         <v>1240</v>
       </c>
       <c r="B617" s="10" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C617" s="4" t="s">
         <v>1241</v>
@@ -17146,8 +17158,8 @@
       <c r="A618" s="4" t="s">
         <v>1242</v>
       </c>
-      <c r="B618" s="7" t="s">
-        <v>61</v>
+      <c r="B618" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C618" s="4" t="s">
         <v>1243</v>
@@ -17158,8 +17170,8 @@
       <c r="A619" s="4" t="s">
         <v>1244</v>
       </c>
-      <c r="B619" s="7" t="s">
-        <v>66</v>
+      <c r="B619" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C619" s="4" t="s">
         <v>1245</v>
@@ -17179,25 +17191,25 @@
       <c r="D620" s="14"/>
     </row>
     <row r="621" ht="22.5" customHeight="1">
-      <c r="A621" s="9" t="s">
+      <c r="A621" s="4" t="s">
         <v>1248</v>
       </c>
-      <c r="B621" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C621" s="9" t="s">
+      <c r="B621" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C621" s="4" t="s">
         <v>1249</v>
       </c>
       <c r="D621" s="14"/>
     </row>
     <row r="622" ht="22.5" customHeight="1">
-      <c r="A622" s="9" t="s">
+      <c r="A622" s="4" t="s">
         <v>1250</v>
       </c>
-      <c r="B622" s="10" t="s">
-        <v>579</v>
-      </c>
-      <c r="C622" s="9" t="s">
+      <c r="B622" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C622" s="4" t="s">
         <v>1251</v>
       </c>
       <c r="D622" s="14"/>
@@ -17207,7 +17219,7 @@
         <v>1252</v>
       </c>
       <c r="B623" s="10" t="s">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="C623" s="9" t="s">
         <v>1253</v>
@@ -17215,25 +17227,25 @@
       <c r="D623" s="14"/>
     </row>
     <row r="624" ht="22.5" customHeight="1">
-      <c r="A624" s="4" t="s">
+      <c r="A624" s="9" t="s">
         <v>1254</v>
       </c>
       <c r="B624" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C624" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="C624" s="9" t="s">
         <v>1255</v>
       </c>
       <c r="D624" s="14"/>
     </row>
     <row r="625" ht="22.5" customHeight="1">
-      <c r="A625" s="4" t="s">
+      <c r="A625" s="9" t="s">
         <v>1256</v>
       </c>
-      <c r="B625" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C625" s="4" t="s">
+      <c r="B625" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C625" s="9" t="s">
         <v>1257</v>
       </c>
       <c r="D625" s="14"/>
@@ -17242,7 +17254,7 @@
       <c r="A626" s="4" t="s">
         <v>1258</v>
       </c>
-      <c r="B626" s="7" t="s">
+      <c r="B626" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C626" s="4" t="s">
@@ -17251,13 +17263,13 @@
       <c r="D626" s="14"/>
     </row>
     <row r="627" ht="22.5" customHeight="1">
-      <c r="A627" s="9" t="s">
+      <c r="A627" s="4" t="s">
         <v>1260</v>
       </c>
       <c r="B627" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C627" s="9" t="s">
+      <c r="C627" s="4" t="s">
         <v>1261</v>
       </c>
       <c r="D627" s="14"/>
@@ -17266,8 +17278,8 @@
       <c r="A628" s="4" t="s">
         <v>1262</v>
       </c>
-      <c r="B628" s="10" t="s">
-        <v>69</v>
+      <c r="B628" s="7" t="s">
+        <v>4</v>
       </c>
       <c r="C628" s="4" t="s">
         <v>1263</v>
@@ -17275,37 +17287,37 @@
       <c r="D628" s="14"/>
     </row>
     <row r="629" ht="22.5" customHeight="1">
-      <c r="A629" s="4" t="s">
+      <c r="A629" s="9" t="s">
         <v>1264</v>
       </c>
-      <c r="B629" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C629" s="4" t="s">
+      <c r="B629" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C629" s="9" t="s">
         <v>1265</v>
       </c>
       <c r="D629" s="14"/>
     </row>
     <row r="630" ht="22.5" customHeight="1">
-      <c r="A630" s="9" t="s">
+      <c r="A630" s="4" t="s">
         <v>1266</v>
       </c>
       <c r="B630" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C630" s="9" t="s">
+      <c r="C630" s="4" t="s">
         <v>1267</v>
       </c>
       <c r="D630" s="14"/>
     </row>
     <row r="631" ht="22.5" customHeight="1">
-      <c r="A631" s="9" t="s">
+      <c r="A631" s="4" t="s">
         <v>1268</v>
       </c>
       <c r="B631" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C631" s="9" t="s">
+      <c r="C631" s="4" t="s">
         <v>1269</v>
       </c>
       <c r="D631" s="14"/>
@@ -17314,8 +17326,8 @@
       <c r="A632" s="9" t="s">
         <v>1270</v>
       </c>
-      <c r="B632" s="5" t="s">
-        <v>4</v>
+      <c r="B632" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="C632" s="9" t="s">
         <v>1271</v>
@@ -17326,8 +17338,8 @@
       <c r="A633" s="9" t="s">
         <v>1272</v>
       </c>
-      <c r="B633" s="5" t="s">
-        <v>66</v>
+      <c r="B633" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="C633" s="9" t="s">
         <v>1273</v>
@@ -17335,25 +17347,25 @@
       <c r="D633" s="14"/>
     </row>
     <row r="634" ht="22.5" customHeight="1">
-      <c r="A634" s="4" t="s">
+      <c r="A634" s="9" t="s">
         <v>1274</v>
       </c>
-      <c r="B634" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="C634" s="4" t="s">
+      <c r="B634" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C634" s="9" t="s">
         <v>1275</v>
       </c>
       <c r="D634" s="14"/>
     </row>
     <row r="635" ht="22.5" customHeight="1">
-      <c r="A635" s="4" t="s">
+      <c r="A635" s="9" t="s">
         <v>1276</v>
       </c>
-      <c r="B635" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C635" s="4" t="s">
+      <c r="B635" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C635" s="9" t="s">
         <v>1277</v>
       </c>
       <c r="D635" s="14"/>
@@ -17362,8 +17374,8 @@
       <c r="A636" s="4" t="s">
         <v>1278</v>
       </c>
-      <c r="B636" s="10" t="s">
-        <v>69</v>
+      <c r="B636" s="7" t="s">
+        <v>210</v>
       </c>
       <c r="C636" s="4" t="s">
         <v>1279</v>
@@ -17374,8 +17386,8 @@
       <c r="A637" s="4" t="s">
         <v>1280</v>
       </c>
-      <c r="B637" s="5" t="s">
-        <v>4</v>
+      <c r="B637" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C637" s="4" t="s">
         <v>1281</v>
@@ -17386,8 +17398,8 @@
       <c r="A638" s="4" t="s">
         <v>1282</v>
       </c>
-      <c r="B638" s="7" t="s">
-        <v>61</v>
+      <c r="B638" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="C638" s="4" t="s">
         <v>1283</v>
@@ -17398,8 +17410,8 @@
       <c r="A639" s="4" t="s">
         <v>1284</v>
       </c>
-      <c r="B639" s="7" t="s">
-        <v>210</v>
+      <c r="B639" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C639" s="4" t="s">
         <v>1285</v>
@@ -17407,25 +17419,25 @@
       <c r="D639" s="14"/>
     </row>
     <row r="640" ht="22.5" customHeight="1">
-      <c r="A640" s="9" t="s">
+      <c r="A640" s="4" t="s">
         <v>1286</v>
       </c>
-      <c r="B640" s="10" t="s">
-        <v>579</v>
-      </c>
-      <c r="C640" s="9" t="s">
+      <c r="B640" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C640" s="4" t="s">
         <v>1287</v>
       </c>
       <c r="D640" s="14"/>
     </row>
     <row r="641" ht="22.5" customHeight="1">
-      <c r="A641" s="9" t="s">
+      <c r="A641" s="4" t="s">
         <v>1288</v>
       </c>
-      <c r="B641" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C641" s="9" t="s">
+      <c r="B641" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C641" s="4" t="s">
         <v>1289</v>
       </c>
       <c r="D641" s="14"/>
@@ -17434,22 +17446,22 @@
       <c r="A642" s="9" t="s">
         <v>1290</v>
       </c>
-      <c r="B642" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C642" s="4" t="s">
+      <c r="B642" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="C642" s="9" t="s">
         <v>1291</v>
       </c>
       <c r="D642" s="14"/>
     </row>
     <row r="643" ht="22.5" customHeight="1">
-      <c r="A643" s="4" t="s">
+      <c r="A643" s="9" t="s">
         <v>1292</v>
       </c>
       <c r="B643" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C643" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C643" s="9" t="s">
         <v>1293</v>
       </c>
       <c r="D643" s="14"/>
@@ -17458,34 +17470,34 @@
       <c r="A644" s="9" t="s">
         <v>1294</v>
       </c>
-      <c r="B644" s="10" t="s">
+      <c r="B644" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C644" s="4" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D644" s="14"/>
+    </row>
+    <row r="645" ht="22.5" customHeight="1">
+      <c r="A645" s="4" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B645" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C645" s="4" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D645" s="14"/>
+    </row>
+    <row r="646" ht="22.5" customHeight="1">
+      <c r="A646" s="9" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B646" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="C644" s="9" t="s">
-        <v>1295</v>
-      </c>
-      <c r="D644" s="14"/>
-    </row>
-    <row r="645" ht="22.5" customHeight="1">
-      <c r="A645" s="9" t="s">
-        <v>1296</v>
-      </c>
-      <c r="B645" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C645" s="9" t="s">
-        <v>1297</v>
-      </c>
-      <c r="D645" s="14"/>
-    </row>
-    <row r="646" ht="22.5" customHeight="1">
-      <c r="A646" s="4" t="s">
-        <v>1298</v>
-      </c>
-      <c r="B646" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C646" s="4" t="s">
+      <c r="C646" s="9" t="s">
         <v>1299</v>
       </c>
       <c r="D646" s="14"/>
@@ -17495,7 +17507,7 @@
         <v>1300</v>
       </c>
       <c r="B647" s="10" t="s">
-        <v>210</v>
+        <v>61</v>
       </c>
       <c r="C647" s="9" t="s">
         <v>1301</v>
@@ -17506,8 +17518,8 @@
       <c r="A648" s="4" t="s">
         <v>1302</v>
       </c>
-      <c r="B648" s="10" t="s">
-        <v>4</v>
+      <c r="B648" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C648" s="4" t="s">
         <v>1303</v>
@@ -17515,25 +17527,25 @@
       <c r="D648" s="14"/>
     </row>
     <row r="649" ht="22.5" customHeight="1">
-      <c r="A649" s="4" t="s">
+      <c r="A649" s="9" t="s">
         <v>1304</v>
       </c>
       <c r="B649" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C649" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C649" s="9" t="s">
         <v>1305</v>
       </c>
       <c r="D649" s="14"/>
     </row>
     <row r="650" ht="22.5" customHeight="1">
-      <c r="A650" s="9" t="s">
+      <c r="A650" s="4" t="s">
         <v>1306</v>
       </c>
       <c r="B650" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="C650" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C650" s="4" t="s">
         <v>1307</v>
       </c>
       <c r="D650" s="14"/>
@@ -17551,13 +17563,13 @@
       <c r="D651" s="14"/>
     </row>
     <row r="652" ht="22.5" customHeight="1">
-      <c r="A652" s="4" t="s">
+      <c r="A652" s="9" t="s">
         <v>1310</v>
       </c>
       <c r="B652" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C652" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C652" s="9" t="s">
         <v>1311</v>
       </c>
       <c r="D652" s="14"/>
@@ -17575,49 +17587,49 @@
       <c r="D653" s="14"/>
     </row>
     <row r="654" ht="22.5" customHeight="1">
-      <c r="A654" s="9" t="s">
+      <c r="A654" s="4" t="s">
         <v>1314</v>
       </c>
-      <c r="B654" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C654" s="9" t="s">
+      <c r="B654" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C654" s="4" t="s">
         <v>1315</v>
       </c>
       <c r="D654" s="14"/>
     </row>
     <row r="655" ht="22.5" customHeight="1">
-      <c r="A655" s="9" t="s">
+      <c r="A655" s="4" t="s">
         <v>1316</v>
       </c>
-      <c r="B655" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C655" s="9" t="s">
+      <c r="B655" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C655" s="4" t="s">
         <v>1317</v>
       </c>
       <c r="D655" s="14"/>
     </row>
     <row r="656" ht="22.5" customHeight="1">
-      <c r="A656" s="4" t="s">
+      <c r="A656" s="9" t="s">
         <v>1318</v>
       </c>
-      <c r="B656" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C656" s="4" t="s">
+      <c r="B656" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C656" s="9" t="s">
         <v>1319</v>
       </c>
       <c r="D656" s="14"/>
     </row>
     <row r="657" ht="22.5" customHeight="1">
-      <c r="A657" s="4" t="s">
+      <c r="A657" s="9" t="s">
         <v>1320</v>
       </c>
-      <c r="B657" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="C657" s="4" t="s">
+      <c r="B657" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C657" s="9" t="s">
         <v>1321</v>
       </c>
       <c r="D657" s="14"/>
@@ -17639,7 +17651,7 @@
         <v>1324</v>
       </c>
       <c r="B659" s="10" t="s">
-        <v>4</v>
+        <v>210</v>
       </c>
       <c r="C659" s="4" t="s">
         <v>1325</v>
@@ -17683,13 +17695,13 @@
       <c r="D662" s="14"/>
     </row>
     <row r="663" ht="22.5" customHeight="1">
-      <c r="A663" s="9" t="s">
+      <c r="A663" s="4" t="s">
         <v>1332</v>
       </c>
-      <c r="B663" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C663" s="9" t="s">
+      <c r="B663" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C663" s="4" t="s">
         <v>1333</v>
       </c>
       <c r="D663" s="14"/>
@@ -17698,7 +17710,7 @@
       <c r="A664" s="4" t="s">
         <v>1334</v>
       </c>
-      <c r="B664" s="5" t="s">
+      <c r="B664" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C664" s="4" t="s">
@@ -17707,13 +17719,13 @@
       <c r="D664" s="14"/>
     </row>
     <row r="665" ht="22.5" customHeight="1">
-      <c r="A665" s="4" t="s">
+      <c r="A665" s="9" t="s">
         <v>1336</v>
       </c>
-      <c r="B665" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C665" s="4" t="s">
+      <c r="B665" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C665" s="9" t="s">
         <v>1337</v>
       </c>
       <c r="D665" s="14"/>
@@ -17722,7 +17734,7 @@
       <c r="A666" s="4" t="s">
         <v>1338</v>
       </c>
-      <c r="B666" s="10" t="s">
+      <c r="B666" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C666" s="4" t="s">
@@ -17734,8 +17746,8 @@
       <c r="A667" s="4" t="s">
         <v>1340</v>
       </c>
-      <c r="B667" s="7" t="s">
-        <v>61</v>
+      <c r="B667" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="C667" s="4" t="s">
         <v>1341</v>
@@ -17746,7 +17758,7 @@
       <c r="A668" s="4" t="s">
         <v>1342</v>
       </c>
-      <c r="B668" s="5" t="s">
+      <c r="B668" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C668" s="4" t="s">
@@ -17758,8 +17770,8 @@
       <c r="A669" s="4" t="s">
         <v>1344</v>
       </c>
-      <c r="B669" s="5" t="s">
-        <v>4</v>
+      <c r="B669" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C669" s="4" t="s">
         <v>1345</v>
@@ -17770,7 +17782,7 @@
       <c r="A670" s="4" t="s">
         <v>1346</v>
       </c>
-      <c r="B670" s="10" t="s">
+      <c r="B670" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C670" s="4" t="s">
@@ -17782,7 +17794,7 @@
       <c r="A671" s="4" t="s">
         <v>1348</v>
       </c>
-      <c r="B671" s="7" t="s">
+      <c r="B671" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C671" s="4" t="s">
@@ -17806,7 +17818,7 @@
       <c r="A673" s="4" t="s">
         <v>1352</v>
       </c>
-      <c r="B673" s="10" t="s">
+      <c r="B673" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C673" s="4" t="s">
@@ -17815,25 +17827,25 @@
       <c r="D673" s="14"/>
     </row>
     <row r="674" ht="22.5" customHeight="1">
-      <c r="A674" s="9" t="s">
+      <c r="A674" s="4" t="s">
         <v>1354</v>
       </c>
       <c r="B674" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C674" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C674" s="4" t="s">
         <v>1355</v>
       </c>
       <c r="D674" s="14"/>
     </row>
     <row r="675" ht="22.5" customHeight="1">
-      <c r="A675" s="9" t="s">
+      <c r="A675" s="4" t="s">
         <v>1356</v>
       </c>
       <c r="B675" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C675" s="9" t="s">
+      <c r="C675" s="4" t="s">
         <v>1357</v>
       </c>
       <c r="D675" s="14"/>
@@ -17842,8 +17854,8 @@
       <c r="A676" s="9" t="s">
         <v>1358</v>
       </c>
-      <c r="B676" s="5" t="s">
-        <v>4</v>
+      <c r="B676" s="10" t="s">
+        <v>61</v>
       </c>
       <c r="C676" s="9" t="s">
         <v>1359</v>
@@ -17854,7 +17866,7 @@
       <c r="A677" s="9" t="s">
         <v>1360</v>
       </c>
-      <c r="B677" s="5" t="s">
+      <c r="B677" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C677" s="9" t="s">
@@ -17863,37 +17875,37 @@
       <c r="D677" s="14"/>
     </row>
     <row r="678" ht="22.5" customHeight="1">
-      <c r="A678" s="4" t="s">
+      <c r="A678" s="9" t="s">
         <v>1362</v>
       </c>
-      <c r="B678" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C678" s="4" t="s">
+      <c r="B678" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C678" s="9" t="s">
         <v>1363</v>
       </c>
       <c r="D678" s="14"/>
     </row>
     <row r="679" ht="22.5" customHeight="1">
-      <c r="A679" s="4" t="s">
+      <c r="A679" s="9" t="s">
         <v>1364</v>
       </c>
-      <c r="B679" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C679" s="4" t="s">
+      <c r="B679" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C679" s="9" t="s">
         <v>1365</v>
       </c>
       <c r="D679" s="14"/>
     </row>
     <row r="680" ht="22.5" customHeight="1">
-      <c r="A680" s="9" t="s">
+      <c r="A680" s="4" t="s">
         <v>1366</v>
       </c>
-      <c r="B680" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C680" s="9" t="s">
+      <c r="B680" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C680" s="4" t="s">
         <v>1367</v>
       </c>
       <c r="D680" s="14"/>
@@ -17911,73 +17923,73 @@
       <c r="D681" s="14"/>
     </row>
     <row r="682" ht="22.5" customHeight="1">
-      <c r="A682" s="4" t="s">
+      <c r="A682" s="9" t="s">
         <v>1370</v>
       </c>
-      <c r="B682" s="7" t="s">
+      <c r="B682" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C682" s="9" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D682" s="14"/>
+    </row>
+    <row r="683" ht="22.5" customHeight="1">
+      <c r="A683" s="4" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B683" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C683" s="4" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D683" s="14"/>
+    </row>
+    <row r="684" ht="22.5" customHeight="1">
+      <c r="A684" s="4" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B684" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C682" s="4" t="s">
-        <v>1371</v>
-      </c>
-      <c r="D682" s="14"/>
-    </row>
-    <row r="683" ht="22.5" customHeight="1">
-      <c r="A683" s="9" t="s">
-        <v>1372</v>
-      </c>
-      <c r="B683" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C683" s="9" t="s">
-        <v>1373</v>
-      </c>
-      <c r="D683" s="14"/>
-    </row>
-    <row r="684" ht="22.5" customHeight="1">
-      <c r="A684" s="9" t="s">
-        <v>1374</v>
-      </c>
-      <c r="B684" s="7" t="s">
+      <c r="C684" s="4" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D684" s="14"/>
+    </row>
+    <row r="685" ht="22.5" customHeight="1">
+      <c r="A685" s="9" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B685" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C685" s="9" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D685" s="14"/>
+    </row>
+    <row r="686" ht="22.5" customHeight="1">
+      <c r="A686" s="9" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B686" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C684" s="9" t="s">
-        <v>1375</v>
-      </c>
-      <c r="D684" s="14"/>
-    </row>
-    <row r="685" ht="22.5" customHeight="1">
-      <c r="A685" s="4" t="s">
-        <v>1376</v>
-      </c>
-      <c r="B685" s="7" t="s">
+      <c r="C686" s="9" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D686" s="14"/>
+    </row>
+    <row r="687" ht="22.5" customHeight="1">
+      <c r="A687" s="4" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B687" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C685" s="4" t="s">
-        <v>1377</v>
-      </c>
-      <c r="D685" s="14"/>
-    </row>
-    <row r="686" ht="22.5" customHeight="1">
-      <c r="A686" s="4" t="s">
-        <v>1378</v>
-      </c>
-      <c r="B686" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C686" s="4" t="s">
-        <v>1379</v>
-      </c>
-      <c r="D686" s="14"/>
-    </row>
-    <row r="687" ht="22.5" customHeight="1">
-      <c r="A687" s="9" t="s">
-        <v>1380</v>
-      </c>
-      <c r="B687" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C687" s="9" t="s">
+      <c r="C687" s="4" t="s">
         <v>1381</v>
       </c>
       <c r="D687" s="14"/>
@@ -17999,7 +18011,7 @@
         <v>1384</v>
       </c>
       <c r="B689" s="10" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C689" s="9" t="s">
         <v>1385</v>
@@ -18022,7 +18034,7 @@
       <c r="A691" s="9" t="s">
         <v>1388</v>
       </c>
-      <c r="B691" s="5" t="s">
+      <c r="B691" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C691" s="9" t="s">
@@ -18034,8 +18046,8 @@
       <c r="A692" s="4" t="s">
         <v>1390</v>
       </c>
-      <c r="B692" s="10" t="s">
-        <v>61</v>
+      <c r="B692" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C692" s="4" t="s">
         <v>1391</v>
@@ -18043,13 +18055,13 @@
       <c r="D692" s="14"/>
     </row>
     <row r="693" ht="22.5" customHeight="1">
-      <c r="A693" s="4" t="s">
+      <c r="A693" s="9" t="s">
         <v>1392</v>
       </c>
-      <c r="B693" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C693" s="4" t="s">
+      <c r="B693" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C693" s="9" t="s">
         <v>1393</v>
       </c>
       <c r="D693" s="14"/>
@@ -18058,7 +18070,7 @@
       <c r="A694" s="4" t="s">
         <v>1394</v>
       </c>
-      <c r="B694" s="5" t="s">
+      <c r="B694" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C694" s="4" t="s">
@@ -18071,7 +18083,7 @@
         <v>1396</v>
       </c>
       <c r="B695" s="10" t="s">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="C695" s="4" t="s">
         <v>1397</v>
@@ -18082,8 +18094,8 @@
       <c r="A696" s="4" t="s">
         <v>1398</v>
       </c>
-      <c r="B696" s="10" t="s">
-        <v>4</v>
+      <c r="B696" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="C696" s="4" t="s">
         <v>1399</v>
@@ -18107,7 +18119,7 @@
         <v>1402</v>
       </c>
       <c r="B698" s="10" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="C698" s="4" t="s">
         <v>1403</v>
@@ -18121,7 +18133,7 @@
       <c r="B699" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C699" s="9" t="s">
+      <c r="C699" s="4" t="s">
         <v>1405</v>
       </c>
       <c r="D699" s="14"/>
@@ -18130,8 +18142,8 @@
       <c r="A700" s="4" t="s">
         <v>1406</v>
       </c>
-      <c r="B700" s="5" t="s">
-        <v>4</v>
+      <c r="B700" s="10" t="s">
+        <v>61</v>
       </c>
       <c r="C700" s="4" t="s">
         <v>1407</v>
@@ -18142,10 +18154,10 @@
       <c r="A701" s="4" t="s">
         <v>1408</v>
       </c>
-      <c r="B701" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C701" s="4" t="s">
+      <c r="B701" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C701" s="9" t="s">
         <v>1409</v>
       </c>
       <c r="D701" s="14"/>
@@ -18154,7 +18166,7 @@
       <c r="A702" s="4" t="s">
         <v>1410</v>
       </c>
-      <c r="B702" s="10" t="s">
+      <c r="B702" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C702" s="4" t="s">
@@ -18163,25 +18175,25 @@
       <c r="D702" s="14"/>
     </row>
     <row r="703" ht="22.5" customHeight="1">
-      <c r="A703" s="9" t="s">
+      <c r="A703" s="4" t="s">
         <v>1412</v>
       </c>
-      <c r="B703" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C703" s="9" t="s">
+      <c r="B703" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C703" s="4" t="s">
         <v>1413</v>
       </c>
       <c r="D703" s="14"/>
     </row>
     <row r="704" ht="22.5" customHeight="1">
-      <c r="A704" s="9" t="s">
+      <c r="A704" s="4" t="s">
         <v>1414</v>
       </c>
       <c r="B704" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C704" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C704" s="4" t="s">
         <v>1415</v>
       </c>
       <c r="D704" s="14"/>
@@ -18190,7 +18202,7 @@
       <c r="A705" s="9" t="s">
         <v>1416</v>
       </c>
-      <c r="B705" s="5" t="s">
+      <c r="B705" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C705" s="9" t="s">
@@ -18199,25 +18211,25 @@
       <c r="D705" s="14"/>
     </row>
     <row r="706" ht="22.5" customHeight="1">
-      <c r="A706" s="4" t="s">
+      <c r="A706" s="9" t="s">
         <v>1418</v>
       </c>
-      <c r="B706" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C706" s="4" t="s">
+      <c r="B706" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C706" s="9" t="s">
         <v>1419</v>
       </c>
       <c r="D706" s="14"/>
     </row>
     <row r="707" ht="22.5" customHeight="1">
-      <c r="A707" s="4" t="s">
+      <c r="A707" s="9" t="s">
         <v>1420</v>
       </c>
-      <c r="B707" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C707" s="4" t="s">
+      <c r="B707" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C707" s="9" t="s">
         <v>1421</v>
       </c>
       <c r="D707" s="14"/>
@@ -18226,7 +18238,7 @@
       <c r="A708" s="4" t="s">
         <v>1422</v>
       </c>
-      <c r="B708" s="7" t="s">
+      <c r="B708" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C708" s="4" t="s">
@@ -18247,13 +18259,13 @@
       <c r="D709" s="14"/>
     </row>
     <row r="710" ht="22.5" customHeight="1">
-      <c r="A710" s="9" t="s">
+      <c r="A710" s="4" t="s">
         <v>1426</v>
       </c>
-      <c r="B710" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C710" s="9" t="s">
+      <c r="B710" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C710" s="4" t="s">
         <v>1427</v>
       </c>
       <c r="D710" s="14"/>
@@ -18271,13 +18283,13 @@
       <c r="D711" s="14"/>
     </row>
     <row r="712" ht="22.5" customHeight="1">
-      <c r="A712" s="4" t="s">
+      <c r="A712" s="9" t="s">
         <v>1430</v>
       </c>
-      <c r="B712" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C712" s="4" t="s">
+      <c r="B712" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C712" s="9" t="s">
         <v>1431</v>
       </c>
       <c r="D712" s="14"/>
@@ -18286,7 +18298,7 @@
       <c r="A713" s="4" t="s">
         <v>1432</v>
       </c>
-      <c r="B713" s="5" t="s">
+      <c r="B713" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C713" s="4" t="s">
@@ -18295,13 +18307,13 @@
       <c r="D713" s="14"/>
     </row>
     <row r="714" ht="22.5" customHeight="1">
-      <c r="A714" s="9" t="s">
+      <c r="A714" s="4" t="s">
         <v>1434</v>
       </c>
-      <c r="B714" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C714" s="9" t="s">
+      <c r="B714" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C714" s="4" t="s">
         <v>1435</v>
       </c>
       <c r="D714" s="14"/>
@@ -18322,8 +18334,8 @@
       <c r="A716" s="9" t="s">
         <v>1438</v>
       </c>
-      <c r="B716" s="7" t="s">
-        <v>61</v>
+      <c r="B716" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C716" s="9" t="s">
         <v>1439</v>
@@ -18343,13 +18355,13 @@
       <c r="D717" s="14"/>
     </row>
     <row r="718" ht="22.5" customHeight="1">
-      <c r="A718" s="4" t="s">
+      <c r="A718" s="9" t="s">
         <v>1442</v>
       </c>
-      <c r="B718" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C718" s="4" t="s">
+      <c r="B718" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C718" s="9" t="s">
         <v>1443</v>
       </c>
       <c r="D718" s="14"/>
@@ -18358,7 +18370,7 @@
       <c r="A719" s="4" t="s">
         <v>1444</v>
       </c>
-      <c r="B719" s="10" t="s">
+      <c r="B719" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C719" s="4" t="s">
@@ -18367,61 +18379,61 @@
       <c r="D719" s="14"/>
     </row>
     <row r="720" ht="22.5" customHeight="1">
-      <c r="A720" s="9" t="s">
+      <c r="A720" s="4" t="s">
         <v>1446</v>
       </c>
-      <c r="B720" s="7" t="s">
+      <c r="B720" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C720" s="4" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D720" s="14"/>
+    </row>
+    <row r="721" ht="22.5" customHeight="1">
+      <c r="A721" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B721" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C721" s="4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D721" s="14"/>
+    </row>
+    <row r="722" ht="22.5" customHeight="1">
+      <c r="A722" s="9" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B722" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C720" s="9" t="s">
-        <v>1447</v>
-      </c>
-      <c r="D720" s="14"/>
-    </row>
-    <row r="721" ht="22.5" customHeight="1">
-      <c r="A721" s="9" t="s">
-        <v>1448</v>
-      </c>
-      <c r="B721" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C721" s="9" t="s">
-        <v>1449</v>
-      </c>
-      <c r="D721" s="14"/>
-    </row>
-    <row r="722" ht="22.5" customHeight="1">
-      <c r="A722" s="4" t="s">
-        <v>1450</v>
-      </c>
-      <c r="B722" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C722" s="4" t="s">
+      <c r="C722" s="9" t="s">
         <v>1451</v>
       </c>
       <c r="D722" s="14"/>
     </row>
     <row r="723" ht="22.5" customHeight="1">
-      <c r="A723" s="4" t="s">
+      <c r="A723" s="9" t="s">
         <v>1452</v>
       </c>
-      <c r="B723" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C723" s="4" t="s">
+      <c r="B723" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C723" s="9" t="s">
         <v>1453</v>
       </c>
       <c r="D723" s="14"/>
     </row>
     <row r="724" ht="22.5" customHeight="1">
-      <c r="A724" s="9" t="s">
+      <c r="A724" s="4" t="s">
         <v>1454</v>
       </c>
       <c r="B724" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C724" s="9" t="s">
+      <c r="C724" s="4" t="s">
         <v>1455</v>
       </c>
       <c r="D724" s="14"/>
@@ -18430,7 +18442,7 @@
       <c r="A725" s="4" t="s">
         <v>1456</v>
       </c>
-      <c r="B725" s="5" t="s">
+      <c r="B725" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C725" s="4" t="s">
@@ -18439,13 +18451,13 @@
       <c r="D725" s="14"/>
     </row>
     <row r="726" ht="22.5" customHeight="1">
-      <c r="A726" s="4" t="s">
+      <c r="A726" s="9" t="s">
         <v>1458</v>
       </c>
-      <c r="B726" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C726" s="4" t="s">
+      <c r="B726" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C726" s="9" t="s">
         <v>1459</v>
       </c>
       <c r="D726" s="14"/>
@@ -18463,25 +18475,25 @@
       <c r="D727" s="14"/>
     </row>
     <row r="728" ht="22.5" customHeight="1">
-      <c r="A728" s="9" t="s">
+      <c r="A728" s="4" t="s">
         <v>1462</v>
       </c>
-      <c r="B728" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C728" s="9" t="s">
+      <c r="B728" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C728" s="4" t="s">
         <v>1463</v>
       </c>
       <c r="D728" s="14"/>
     </row>
     <row r="729" ht="22.5" customHeight="1">
-      <c r="A729" s="9" t="s">
+      <c r="A729" s="4" t="s">
         <v>1464</v>
       </c>
       <c r="B729" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C729" s="9" t="s">
+      <c r="C729" s="4" t="s">
         <v>1465</v>
       </c>
       <c r="D729" s="14"/>
@@ -18499,25 +18511,25 @@
       <c r="D730" s="14"/>
     </row>
     <row r="731" ht="22.5" customHeight="1">
-      <c r="A731" s="4" t="s">
+      <c r="A731" s="9" t="s">
         <v>1468</v>
       </c>
-      <c r="B731" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C731" s="4" t="s">
+      <c r="B731" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C731" s="9" t="s">
         <v>1469</v>
       </c>
       <c r="D731" s="14"/>
     </row>
     <row r="732" ht="22.5" customHeight="1">
-      <c r="A732" s="4" t="s">
+      <c r="A732" s="9" t="s">
         <v>1470</v>
       </c>
-      <c r="B732" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C732" s="4" t="s">
+      <c r="B732" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C732" s="9" t="s">
         <v>1471</v>
       </c>
       <c r="D732" s="14"/>
@@ -18526,7 +18538,7 @@
       <c r="A733" s="4" t="s">
         <v>1472</v>
       </c>
-      <c r="B733" s="5" t="s">
+      <c r="B733" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C733" s="4" t="s">
@@ -18535,7 +18547,7 @@
       <c r="D733" s="14"/>
     </row>
     <row r="734" ht="22.5" customHeight="1">
-      <c r="A734" s="9" t="s">
+      <c r="A734" s="4" t="s">
         <v>1474</v>
       </c>
       <c r="B734" s="10" t="s">
@@ -18547,19 +18559,19 @@
       <c r="D734" s="14"/>
     </row>
     <row r="735" ht="22.5" customHeight="1">
-      <c r="A735" s="9" t="s">
+      <c r="A735" s="4" t="s">
         <v>1476</v>
       </c>
       <c r="B735" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C735" s="9" t="s">
+      <c r="C735" s="4" t="s">
         <v>1477</v>
       </c>
       <c r="D735" s="14"/>
     </row>
     <row r="736" ht="22.5" customHeight="1">
-      <c r="A736" s="4" t="s">
+      <c r="A736" s="9" t="s">
         <v>1478</v>
       </c>
       <c r="B736" s="10" t="s">
@@ -18571,13 +18583,13 @@
       <c r="D736" s="14"/>
     </row>
     <row r="737" ht="22.5" customHeight="1">
-      <c r="A737" s="4" t="s">
+      <c r="A737" s="9" t="s">
         <v>1480</v>
       </c>
       <c r="B737" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C737" s="4" t="s">
+      <c r="C737" s="9" t="s">
         <v>1481</v>
       </c>
       <c r="D737" s="14"/>
@@ -18598,8 +18610,8 @@
       <c r="A739" s="4" t="s">
         <v>1484</v>
       </c>
-      <c r="B739" s="7" t="s">
-        <v>61</v>
+      <c r="B739" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C739" s="4" t="s">
         <v>1485</v>
@@ -18610,8 +18622,8 @@
       <c r="A740" s="4" t="s">
         <v>1486</v>
       </c>
-      <c r="B740" s="7" t="s">
-        <v>69</v>
+      <c r="B740" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C740" s="4" t="s">
         <v>1487</v>
@@ -18622,8 +18634,8 @@
       <c r="A741" s="4" t="s">
         <v>1488</v>
       </c>
-      <c r="B741" s="10" t="s">
-        <v>4</v>
+      <c r="B741" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C741" s="4" t="s">
         <v>1489</v>
@@ -18635,7 +18647,7 @@
         <v>1490</v>
       </c>
       <c r="B742" s="7" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C742" s="4" t="s">
         <v>1491</v>
@@ -18643,37 +18655,37 @@
       <c r="D742" s="14"/>
     </row>
     <row r="743" ht="22.5" customHeight="1">
-      <c r="A743" s="9" t="s">
+      <c r="A743" s="4" t="s">
         <v>1492</v>
       </c>
-      <c r="B743" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C743" s="9" t="s">
+      <c r="B743" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C743" s="4" t="s">
         <v>1493</v>
       </c>
       <c r="D743" s="14"/>
     </row>
     <row r="744" ht="22.5" customHeight="1">
-      <c r="A744" s="9" t="s">
+      <c r="A744" s="4" t="s">
         <v>1494</v>
       </c>
       <c r="B744" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C744" s="9" t="s">
+      <c r="C744" s="4" t="s">
         <v>1495</v>
       </c>
       <c r="D744" s="14"/>
     </row>
     <row r="745" ht="22.5" customHeight="1">
-      <c r="A745" s="4" t="s">
+      <c r="A745" s="9" t="s">
         <v>1496</v>
       </c>
-      <c r="B745" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C745" s="4" t="s">
+      <c r="B745" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C745" s="9" t="s">
         <v>1497</v>
       </c>
       <c r="D745" s="14"/>
@@ -18703,61 +18715,61 @@
       <c r="D747" s="14"/>
     </row>
     <row r="748" ht="22.5" customHeight="1">
-      <c r="A748" s="4" t="s">
+      <c r="A748" s="9" t="s">
         <v>1502</v>
       </c>
       <c r="B748" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C748" s="4" t="s">
+      <c r="C748" s="9" t="s">
         <v>1503</v>
       </c>
       <c r="D748" s="14"/>
     </row>
     <row r="749" ht="22.5" customHeight="1">
-      <c r="A749" s="9" t="s">
+      <c r="A749" s="4" t="s">
         <v>1504</v>
       </c>
-      <c r="B749" s="7" t="s">
+      <c r="B749" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C749" s="4" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D749" s="14"/>
+    </row>
+    <row r="750" ht="22.5" customHeight="1">
+      <c r="A750" s="4" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B750" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C749" s="9" t="s">
-        <v>1505</v>
-      </c>
-      <c r="D749" s="14"/>
-    </row>
-    <row r="750" ht="22.5" customHeight="1">
-      <c r="A750" s="9" t="s">
-        <v>1506</v>
-      </c>
-      <c r="B750" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C750" s="9" t="s">
+      <c r="C750" s="4" t="s">
         <v>1507</v>
       </c>
       <c r="D750" s="14"/>
     </row>
     <row r="751" ht="22.5" customHeight="1">
-      <c r="A751" s="4" t="s">
+      <c r="A751" s="9" t="s">
         <v>1508</v>
       </c>
-      <c r="B751" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C751" s="4" t="s">
+      <c r="B751" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C751" s="9" t="s">
         <v>1509</v>
       </c>
       <c r="D751" s="14"/>
     </row>
     <row r="752" ht="22.5" customHeight="1">
-      <c r="A752" s="4" t="s">
+      <c r="A752" s="9" t="s">
         <v>1510</v>
       </c>
       <c r="B752" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C752" s="4" t="s">
+      <c r="C752" s="9" t="s">
         <v>1511</v>
       </c>
       <c r="D752" s="14"/>
@@ -18766,7 +18778,7 @@
       <c r="A753" s="4" t="s">
         <v>1512</v>
       </c>
-      <c r="B753" s="10" t="s">
+      <c r="B753" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C753" s="4" t="s">
@@ -18778,7 +18790,7 @@
       <c r="A754" s="4" t="s">
         <v>1514</v>
       </c>
-      <c r="B754" s="5" t="s">
+      <c r="B754" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C754" s="4" t="s">
@@ -18799,13 +18811,13 @@
       <c r="D755" s="14"/>
     </row>
     <row r="756" ht="22.5" customHeight="1">
-      <c r="A756" s="9" t="s">
+      <c r="A756" s="4" t="s">
         <v>1518</v>
       </c>
-      <c r="B756" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C756" s="9" t="s">
+      <c r="B756" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C756" s="4" t="s">
         <v>1519</v>
       </c>
       <c r="D756" s="14"/>
@@ -18814,7 +18826,7 @@
       <c r="A757" s="4" t="s">
         <v>1520</v>
       </c>
-      <c r="B757" s="7" t="s">
+      <c r="B757" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C757" s="4" t="s">
@@ -18823,37 +18835,37 @@
       <c r="D757" s="14"/>
     </row>
     <row r="758" ht="22.5" customHeight="1">
-      <c r="A758" s="4" t="s">
+      <c r="A758" s="9" t="s">
         <v>1522</v>
       </c>
       <c r="B758" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C758" s="4" t="s">
+      <c r="C758" s="9" t="s">
         <v>1523</v>
       </c>
       <c r="D758" s="14"/>
     </row>
     <row r="759" ht="22.5" customHeight="1">
-      <c r="A759" s="9" t="s">
+      <c r="A759" s="4" t="s">
         <v>1524</v>
       </c>
-      <c r="B759" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C759" s="9" t="s">
+      <c r="B759" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C759" s="4" t="s">
         <v>1525</v>
       </c>
       <c r="D759" s="14"/>
     </row>
     <row r="760" ht="22.5" customHeight="1">
-      <c r="A760" s="9" t="s">
+      <c r="A760" s="4" t="s">
         <v>1526</v>
       </c>
       <c r="B760" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C760" s="9" t="s">
+      <c r="C760" s="4" t="s">
         <v>1527</v>
       </c>
       <c r="D760" s="14"/>
@@ -18871,13 +18883,13 @@
       <c r="D761" s="14"/>
     </row>
     <row r="762" ht="22.5" customHeight="1">
-      <c r="A762" s="4" t="s">
+      <c r="A762" s="9" t="s">
         <v>1530</v>
       </c>
       <c r="B762" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C762" s="4" t="s">
+      <c r="C762" s="9" t="s">
         <v>1531</v>
       </c>
       <c r="D762" s="14"/>
@@ -18887,7 +18899,7 @@
         <v>1532</v>
       </c>
       <c r="B763" s="10" t="s">
-        <v>579</v>
+        <v>4</v>
       </c>
       <c r="C763" s="9" t="s">
         <v>1533</v>
@@ -18895,25 +18907,25 @@
       <c r="D763" s="14"/>
     </row>
     <row r="764" ht="22.5" customHeight="1">
-      <c r="A764" s="9" t="s">
+      <c r="A764" s="4" t="s">
         <v>1534</v>
       </c>
       <c r="B764" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C764" s="9" t="s">
+      <c r="C764" s="4" t="s">
         <v>1535</v>
       </c>
       <c r="D764" s="14"/>
     </row>
     <row r="765" ht="22.5" customHeight="1">
-      <c r="A765" s="4" t="s">
+      <c r="A765" s="9" t="s">
         <v>1536</v>
       </c>
       <c r="B765" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C765" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="C765" s="9" t="s">
         <v>1537</v>
       </c>
       <c r="D765" s="14"/>
@@ -18922,8 +18934,8 @@
       <c r="A766" s="9" t="s">
         <v>1538</v>
       </c>
-      <c r="B766" s="7" t="s">
-        <v>61</v>
+      <c r="B766" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C766" s="9" t="s">
         <v>1539</v>
@@ -18931,25 +18943,25 @@
       <c r="D766" s="14"/>
     </row>
     <row r="767" ht="22.5" customHeight="1">
-      <c r="A767" s="9" t="s">
+      <c r="A767" s="4" t="s">
         <v>1540</v>
       </c>
       <c r="B767" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C767" s="9" t="s">
+      <c r="C767" s="4" t="s">
         <v>1541</v>
       </c>
       <c r="D767" s="14"/>
     </row>
     <row r="768" ht="22.5" customHeight="1">
-      <c r="A768" s="4" t="s">
+      <c r="A768" s="9" t="s">
         <v>1542</v>
       </c>
-      <c r="B768" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C768" s="4" t="s">
+      <c r="B768" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C768" s="9" t="s">
         <v>1543</v>
       </c>
       <c r="D768" s="14"/>
@@ -18970,7 +18982,7 @@
       <c r="A770" s="4" t="s">
         <v>1546</v>
       </c>
-      <c r="B770" s="10" t="s">
+      <c r="B770" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C770" s="4" t="s">
@@ -18982,7 +18994,7 @@
       <c r="A771" s="9" t="s">
         <v>1548</v>
       </c>
-      <c r="B771" s="5" t="s">
+      <c r="B771" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C771" s="9" t="s">
@@ -18994,8 +19006,8 @@
       <c r="A772" s="4" t="s">
         <v>1550</v>
       </c>
-      <c r="B772" s="7" t="s">
-        <v>61</v>
+      <c r="B772" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C772" s="4" t="s">
         <v>1551</v>
@@ -19018,8 +19030,8 @@
       <c r="A774" s="4" t="s">
         <v>1554</v>
       </c>
-      <c r="B774" s="10" t="s">
-        <v>4</v>
+      <c r="B774" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C774" s="4" t="s">
         <v>1555</v>
@@ -19027,25 +19039,25 @@
       <c r="D774" s="14"/>
     </row>
     <row r="775" ht="22.5" customHeight="1">
-      <c r="A775" s="4" t="s">
+      <c r="A775" s="9" t="s">
         <v>1556</v>
       </c>
       <c r="B775" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C775" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C775" s="9" t="s">
         <v>1557</v>
       </c>
       <c r="D775" s="14"/>
     </row>
     <row r="776" ht="22.5" customHeight="1">
-      <c r="A776" s="9" t="s">
+      <c r="A776" s="4" t="s">
         <v>1558</v>
       </c>
       <c r="B776" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C776" s="9" t="s">
+      <c r="C776" s="4" t="s">
         <v>1559</v>
       </c>
       <c r="D776" s="14"/>
@@ -19054,8 +19066,8 @@
       <c r="A777" s="4" t="s">
         <v>1560</v>
       </c>
-      <c r="B777" s="10" t="s">
-        <v>4</v>
+      <c r="B777" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="C777" s="4" t="s">
         <v>1561</v>
@@ -19063,25 +19075,25 @@
       <c r="D777" s="14"/>
     </row>
     <row r="778" ht="22.5" customHeight="1">
-      <c r="A778" s="4" t="s">
+      <c r="A778" s="9" t="s">
         <v>1562</v>
       </c>
       <c r="B778" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C778" s="4" t="s">
+      <c r="C778" s="9" t="s">
         <v>1563</v>
       </c>
       <c r="D778" s="14"/>
     </row>
     <row r="779" ht="22.5" customHeight="1">
-      <c r="A779" s="9" t="s">
+      <c r="A779" s="4" t="s">
         <v>1564</v>
       </c>
       <c r="B779" s="10" t="s">
-        <v>579</v>
-      </c>
-      <c r="C779" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C779" s="4" t="s">
         <v>1565</v>
       </c>
       <c r="D779" s="14"/>
@@ -19099,13 +19111,13 @@
       <c r="D780" s="14"/>
     </row>
     <row r="781" ht="22.5" customHeight="1">
-      <c r="A781" s="4" t="s">
+      <c r="A781" s="9" t="s">
         <v>1568</v>
       </c>
       <c r="B781" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C781" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="C781" s="9" t="s">
         <v>1569</v>
       </c>
       <c r="D781" s="14"/>
@@ -19127,7 +19139,7 @@
         <v>1572</v>
       </c>
       <c r="B783" s="10" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="C783" s="4" t="s">
         <v>1573</v>
@@ -19135,25 +19147,25 @@
       <c r="D783" s="14"/>
     </row>
     <row r="784" ht="22.5" customHeight="1">
-      <c r="A784" s="9" t="s">
+      <c r="A784" s="4" t="s">
         <v>1574</v>
       </c>
-      <c r="B784" s="7" t="s">
+      <c r="B784" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C784" s="4" t="s">
+        <v>1575</v>
+      </c>
+      <c r="D784" s="14"/>
+    </row>
+    <row r="785" ht="22.5" customHeight="1">
+      <c r="A785" s="4" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B785" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C784" s="9" t="s">
-        <v>1575</v>
-      </c>
-      <c r="D784" s="14"/>
-    </row>
-    <row r="785" ht="22.5" customHeight="1">
-      <c r="A785" s="9" t="s">
-        <v>1576</v>
-      </c>
-      <c r="B785" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C785" s="9" t="s">
+      <c r="C785" s="4" t="s">
         <v>1577</v>
       </c>
       <c r="D785" s="14"/>
@@ -19162,8 +19174,8 @@
       <c r="A786" s="9" t="s">
         <v>1578</v>
       </c>
-      <c r="B786" s="10" t="s">
-        <v>4</v>
+      <c r="B786" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C786" s="9" t="s">
         <v>1579</v>
@@ -19171,37 +19183,37 @@
       <c r="D786" s="14"/>
     </row>
     <row r="787" ht="22.5" customHeight="1">
-      <c r="A787" s="4" t="s">
+      <c r="A787" s="9" t="s">
         <v>1580</v>
       </c>
-      <c r="B787" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C787" s="4" t="s">
+      <c r="B787" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C787" s="9" t="s">
         <v>1581</v>
       </c>
       <c r="D787" s="14"/>
     </row>
     <row r="788" ht="22.5" customHeight="1">
-      <c r="A788" s="4" t="s">
+      <c r="A788" s="9" t="s">
         <v>1582</v>
       </c>
       <c r="B788" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C788" s="4" t="s">
+      <c r="C788" s="9" t="s">
         <v>1583</v>
       </c>
       <c r="D788" s="14"/>
     </row>
     <row r="789" ht="22.5" customHeight="1">
-      <c r="A789" s="9" t="s">
+      <c r="A789" s="4" t="s">
         <v>1584</v>
       </c>
       <c r="B789" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C789" s="9" t="s">
+      <c r="C789" s="4" t="s">
         <v>1585</v>
       </c>
       <c r="D789" s="14"/>
@@ -19222,7 +19234,7 @@
       <c r="A791" s="9" t="s">
         <v>1588</v>
       </c>
-      <c r="B791" s="5" t="s">
+      <c r="B791" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C791" s="9" t="s">
@@ -19234,8 +19246,8 @@
       <c r="A792" s="4" t="s">
         <v>1590</v>
       </c>
-      <c r="B792" s="7" t="s">
-        <v>69</v>
+      <c r="B792" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C792" s="4" t="s">
         <v>1591</v>
@@ -19243,13 +19255,13 @@
       <c r="D792" s="14"/>
     </row>
     <row r="793" ht="22.5" customHeight="1">
-      <c r="A793" s="4" t="s">
+      <c r="A793" s="9" t="s">
         <v>1592</v>
       </c>
-      <c r="B793" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C793" s="4" t="s">
+      <c r="B793" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C793" s="9" t="s">
         <v>1593</v>
       </c>
       <c r="D793" s="14"/>
@@ -19267,37 +19279,37 @@
       <c r="D794" s="14"/>
     </row>
     <row r="795" ht="22.5" customHeight="1">
-      <c r="A795" s="9" t="s">
+      <c r="A795" s="4" t="s">
         <v>1596</v>
       </c>
-      <c r="B795" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C795" s="9" t="s">
+      <c r="B795" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C795" s="4" t="s">
         <v>1597</v>
       </c>
       <c r="D795" s="14"/>
     </row>
     <row r="796" ht="22.5" customHeight="1">
-      <c r="A796" s="9" t="s">
+      <c r="A796" s="4" t="s">
         <v>1598</v>
       </c>
-      <c r="B796" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C796" s="9" t="s">
+      <c r="B796" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C796" s="4" t="s">
         <v>1599</v>
       </c>
       <c r="D796" s="14"/>
     </row>
     <row r="797" ht="22.5" customHeight="1">
-      <c r="A797" s="4" t="s">
+      <c r="A797" s="9" t="s">
         <v>1600</v>
       </c>
       <c r="B797" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C797" s="4" t="s">
+      <c r="C797" s="9" t="s">
         <v>1601</v>
       </c>
       <c r="D797" s="14"/>
@@ -19307,7 +19319,7 @@
         <v>1602</v>
       </c>
       <c r="B798" s="5" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="C798" s="9" t="s">
         <v>1603</v>
@@ -19330,8 +19342,8 @@
       <c r="A800" s="9" t="s">
         <v>1606</v>
       </c>
-      <c r="B800" s="10" t="s">
-        <v>4</v>
+      <c r="B800" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="C800" s="9" t="s">
         <v>1607</v>
@@ -19339,37 +19351,37 @@
       <c r="D800" s="14"/>
     </row>
     <row r="801" ht="22.5" customHeight="1">
-      <c r="A801" s="9" t="s">
+      <c r="A801" s="4" t="s">
         <v>1608</v>
       </c>
-      <c r="B801" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C801" s="9" t="s">
+      <c r="B801" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C801" s="4" t="s">
         <v>1609</v>
       </c>
       <c r="D801" s="14"/>
     </row>
     <row r="802" ht="22.5" customHeight="1">
-      <c r="A802" s="4" t="s">
+      <c r="A802" s="9" t="s">
         <v>1610</v>
       </c>
       <c r="B802" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C802" s="4" t="s">
+      <c r="C802" s="9" t="s">
         <v>1611</v>
       </c>
       <c r="D802" s="14"/>
     </row>
     <row r="803" ht="22.5" customHeight="1">
-      <c r="A803" s="4" t="s">
+      <c r="A803" s="9" t="s">
         <v>1612</v>
       </c>
       <c r="B803" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C803" s="4" t="s">
+      <c r="C803" s="9" t="s">
         <v>1613</v>
       </c>
       <c r="D803" s="14"/>
@@ -19378,7 +19390,7 @@
       <c r="A804" s="4" t="s">
         <v>1614</v>
       </c>
-      <c r="B804" s="5" t="s">
+      <c r="B804" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C804" s="4" t="s">
@@ -19390,8 +19402,8 @@
       <c r="A805" s="4" t="s">
         <v>1616</v>
       </c>
-      <c r="B805" s="5" t="s">
-        <v>61</v>
+      <c r="B805" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C805" s="4" t="s">
         <v>1617</v>
@@ -19402,7 +19414,7 @@
       <c r="A806" s="4" t="s">
         <v>1618</v>
       </c>
-      <c r="B806" s="10" t="s">
+      <c r="B806" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C806" s="4" t="s">
@@ -19414,8 +19426,8 @@
       <c r="A807" s="4" t="s">
         <v>1620</v>
       </c>
-      <c r="B807" s="10" t="s">
-        <v>4</v>
+      <c r="B807" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="C807" s="4" t="s">
         <v>1621</v>
@@ -19426,8 +19438,8 @@
       <c r="A808" s="4" t="s">
         <v>1622</v>
       </c>
-      <c r="B808" s="7" t="s">
-        <v>61</v>
+      <c r="B808" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C808" s="4" t="s">
         <v>1623</v>
@@ -19438,8 +19450,8 @@
       <c r="A809" s="4" t="s">
         <v>1624</v>
       </c>
-      <c r="B809" s="7" t="s">
-        <v>61</v>
+      <c r="B809" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C809" s="4" t="s">
         <v>1625</v>
@@ -19447,97 +19459,97 @@
       <c r="D809" s="14"/>
     </row>
     <row r="810" ht="22.5" customHeight="1">
-      <c r="A810" s="9" t="s">
+      <c r="A810" s="4" t="s">
         <v>1626</v>
       </c>
-      <c r="B810" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C810" s="9" t="s">
+      <c r="B810" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C810" s="4" t="s">
         <v>1627</v>
       </c>
       <c r="D810" s="14"/>
     </row>
     <row r="811" ht="22.5" customHeight="1">
-      <c r="A811" s="9" t="s">
+      <c r="A811" s="4" t="s">
         <v>1628</v>
       </c>
-      <c r="B811" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C811" s="9" t="s">
+      <c r="B811" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C811" s="4" t="s">
         <v>1629</v>
       </c>
       <c r="D811" s="14"/>
     </row>
     <row r="812" ht="22.5" customHeight="1">
-      <c r="A812" s="4" t="s">
+      <c r="A812" s="9" t="s">
         <v>1630</v>
       </c>
       <c r="B812" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C812" s="4" t="s">
+      <c r="C812" s="9" t="s">
         <v>1631</v>
       </c>
       <c r="D812" s="14"/>
     </row>
     <row r="813" ht="22.5" customHeight="1">
-      <c r="A813" s="4" t="s">
+      <c r="A813" s="9" t="s">
         <v>1632</v>
       </c>
       <c r="B813" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C813" s="4" t="s">
+      <c r="C813" s="9" t="s">
         <v>1633</v>
       </c>
       <c r="D813" s="14"/>
     </row>
     <row r="814" ht="22.5" customHeight="1">
-      <c r="A814" s="9" t="s">
+      <c r="A814" s="4" t="s">
         <v>1634</v>
       </c>
-      <c r="B814" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C814" s="9" t="s">
+      <c r="B814" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C814" s="4" t="s">
         <v>1635</v>
       </c>
       <c r="D814" s="14"/>
     </row>
     <row r="815" ht="22.5" customHeight="1">
-      <c r="A815" s="9" t="s">
+      <c r="A815" s="4" t="s">
         <v>1636</v>
       </c>
-      <c r="B815" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C815" s="9" t="s">
+      <c r="B815" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C815" s="4" t="s">
         <v>1637</v>
       </c>
       <c r="D815" s="14"/>
     </row>
     <row r="816" ht="22.5" customHeight="1">
-      <c r="A816" s="4" t="s">
+      <c r="A816" s="9" t="s">
         <v>1638</v>
       </c>
-      <c r="B816" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C816" s="4" t="s">
+      <c r="B816" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C816" s="9" t="s">
         <v>1639</v>
       </c>
       <c r="D816" s="14"/>
     </row>
     <row r="817" ht="22.5" customHeight="1">
-      <c r="A817" s="4" t="s">
+      <c r="A817" s="9" t="s">
         <v>1640</v>
       </c>
-      <c r="B817" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C817" s="4" t="s">
+      <c r="B817" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C817" s="9" t="s">
         <v>1641</v>
       </c>
       <c r="D817" s="14"/>
@@ -19558,8 +19570,8 @@
       <c r="A819" s="4" t="s">
         <v>1644</v>
       </c>
-      <c r="B819" s="5" t="s">
-        <v>4</v>
+      <c r="B819" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C819" s="4" t="s">
         <v>1645</v>
@@ -19582,8 +19594,8 @@
       <c r="A821" s="4" t="s">
         <v>1648</v>
       </c>
-      <c r="B821" s="10" t="s">
-        <v>61</v>
+      <c r="B821" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C821" s="4" t="s">
         <v>1649</v>
@@ -19591,13 +19603,13 @@
       <c r="D821" s="14"/>
     </row>
     <row r="822" ht="22.5" customHeight="1">
-      <c r="A822" s="9" t="s">
+      <c r="A822" s="4" t="s">
         <v>1650</v>
       </c>
-      <c r="B822" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C822" s="9" t="s">
+      <c r="B822" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C822" s="4" t="s">
         <v>1651</v>
       </c>
       <c r="D822" s="14"/>
@@ -19607,7 +19619,7 @@
         <v>1652</v>
       </c>
       <c r="B823" s="10" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C823" s="4" t="s">
         <v>1653</v>
@@ -19639,13 +19651,13 @@
       <c r="D825" s="14"/>
     </row>
     <row r="826" ht="22.5" customHeight="1">
-      <c r="A826" s="4" t="s">
+      <c r="A826" s="9" t="s">
         <v>1658</v>
       </c>
-      <c r="B826" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C826" s="4" t="s">
+      <c r="B826" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C826" s="9" t="s">
         <v>1659</v>
       </c>
       <c r="D826" s="14"/>
@@ -19654,8 +19666,8 @@
       <c r="A827" s="4" t="s">
         <v>1660</v>
       </c>
-      <c r="B827" s="7" t="s">
-        <v>61</v>
+      <c r="B827" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C827" s="4" t="s">
         <v>1661</v>
@@ -19663,13 +19675,13 @@
       <c r="D827" s="14"/>
     </row>
     <row r="828" ht="22.5" customHeight="1">
-      <c r="A828" s="9" t="s">
+      <c r="A828" s="4" t="s">
         <v>1662</v>
       </c>
-      <c r="B828" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C828" s="9" t="s">
+      <c r="B828" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C828" s="4" t="s">
         <v>1663</v>
       </c>
       <c r="D828" s="14"/>
@@ -19678,8 +19690,8 @@
       <c r="A829" s="4" t="s">
         <v>1664</v>
       </c>
-      <c r="B829" s="10" t="s">
-        <v>4</v>
+      <c r="B829" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C829" s="4" t="s">
         <v>1665</v>
@@ -19711,13 +19723,13 @@
       <c r="D831" s="14"/>
     </row>
     <row r="832" ht="22.5" customHeight="1">
-      <c r="A832" s="4" t="s">
+      <c r="A832" s="9" t="s">
         <v>1670</v>
       </c>
-      <c r="B832" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C832" s="4" t="s">
+      <c r="B832" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C832" s="9" t="s">
         <v>1671</v>
       </c>
       <c r="D832" s="14"/>
@@ -19726,7 +19738,7 @@
       <c r="A833" s="4" t="s">
         <v>1672</v>
       </c>
-      <c r="B833" s="5" t="s">
+      <c r="B833" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C833" s="4" t="s">
@@ -19738,7 +19750,7 @@
       <c r="A834" s="4" t="s">
         <v>1674</v>
       </c>
-      <c r="B834" s="7" t="s">
+      <c r="B834" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C834" s="4" t="s">
@@ -19747,49 +19759,49 @@
       <c r="D834" s="14"/>
     </row>
     <row r="835" ht="22.5" customHeight="1">
-      <c r="A835" s="9" t="s">
+      <c r="A835" s="4" t="s">
         <v>1676</v>
       </c>
       <c r="B835" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C835" s="9" t="s">
+      <c r="C835" s="4" t="s">
         <v>1677</v>
       </c>
       <c r="D835" s="14"/>
     </row>
     <row r="836" ht="22.5" customHeight="1">
-      <c r="A836" s="9" t="s">
+      <c r="A836" s="4" t="s">
         <v>1678</v>
       </c>
       <c r="B836" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C836" s="9" t="s">
+      <c r="C836" s="4" t="s">
         <v>1679</v>
       </c>
       <c r="D836" s="14"/>
     </row>
     <row r="837" ht="22.5" customHeight="1">
-      <c r="A837" s="4" t="s">
+      <c r="A837" s="9" t="s">
         <v>1680</v>
       </c>
-      <c r="B837" s="7" t="s">
+      <c r="B837" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C837" s="9" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D837" s="14"/>
+    </row>
+    <row r="838" ht="22.5" customHeight="1">
+      <c r="A838" s="9" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B838" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C837" s="4" t="s">
-        <v>1681</v>
-      </c>
-      <c r="D837" s="14"/>
-    </row>
-    <row r="838" ht="22.5" customHeight="1">
-      <c r="A838" s="15" t="s">
-        <v>1682</v>
-      </c>
-      <c r="B838" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C838" s="15" t="s">
+      <c r="C838" s="9" t="s">
         <v>1683</v>
       </c>
       <c r="D838" s="14"/>
@@ -19798,8 +19810,8 @@
       <c r="A839" s="4" t="s">
         <v>1684</v>
       </c>
-      <c r="B839" s="10" t="s">
-        <v>4</v>
+      <c r="B839" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C839" s="4" t="s">
         <v>1685</v>
@@ -19807,25 +19819,25 @@
       <c r="D839" s="14"/>
     </row>
     <row r="840" ht="22.5" customHeight="1">
-      <c r="A840" s="4" t="s">
+      <c r="A840" s="15" t="s">
         <v>1686</v>
       </c>
-      <c r="B840" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C840" s="4" t="s">
+      <c r="B840" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C840" s="15" t="s">
         <v>1687</v>
       </c>
       <c r="D840" s="14"/>
     </row>
     <row r="841" ht="22.5" customHeight="1">
-      <c r="A841" s="9" t="s">
+      <c r="A841" s="4" t="s">
         <v>1688</v>
       </c>
       <c r="B841" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C841" s="9" t="s">
+      <c r="C841" s="4" t="s">
         <v>1689</v>
       </c>
       <c r="D841" s="14"/>
@@ -19834,8 +19846,8 @@
       <c r="A842" s="4" t="s">
         <v>1690</v>
       </c>
-      <c r="B842" s="10" t="s">
-        <v>120</v>
+      <c r="B842" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C842" s="4" t="s">
         <v>1691</v>
@@ -19843,25 +19855,25 @@
       <c r="D842" s="14"/>
     </row>
     <row r="843" ht="22.5" customHeight="1">
-      <c r="A843" s="4" t="s">
+      <c r="A843" s="9" t="s">
         <v>1692</v>
       </c>
       <c r="B843" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C843" s="4" t="s">
+      <c r="C843" s="9" t="s">
         <v>1693</v>
       </c>
       <c r="D843" s="14"/>
     </row>
     <row r="844" ht="22.5" customHeight="1">
-      <c r="A844" s="9" t="s">
+      <c r="A844" s="4" t="s">
         <v>1694</v>
       </c>
-      <c r="B844" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C844" s="9" t="s">
+      <c r="B844" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C844" s="4" t="s">
         <v>1695</v>
       </c>
       <c r="D844" s="14"/>
@@ -19870,8 +19882,8 @@
       <c r="A845" s="4" t="s">
         <v>1696</v>
       </c>
-      <c r="B845" s="7" t="s">
-        <v>46</v>
+      <c r="B845" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C845" s="4" t="s">
         <v>1697</v>
@@ -19879,25 +19891,25 @@
       <c r="D845" s="14"/>
     </row>
     <row r="846" ht="22.5" customHeight="1">
-      <c r="A846" s="4" t="s">
+      <c r="A846" s="9" t="s">
         <v>1698</v>
       </c>
-      <c r="B846" s="7" t="s">
+      <c r="B846" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C846" s="9" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D846" s="14"/>
+    </row>
+    <row r="847" ht="22.5" customHeight="1">
+      <c r="A847" s="4" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B847" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C846" s="4" t="s">
-        <v>1699</v>
-      </c>
-      <c r="D846" s="14"/>
-    </row>
-    <row r="847" ht="22.5" customHeight="1">
-      <c r="A847" s="9" t="s">
-        <v>1700</v>
-      </c>
-      <c r="B847" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C847" s="9" t="s">
+      <c r="C847" s="4" t="s">
         <v>1701</v>
       </c>
       <c r="D847" s="14"/>
@@ -19906,8 +19918,8 @@
       <c r="A848" s="4" t="s">
         <v>1702</v>
       </c>
-      <c r="B848" s="5" t="s">
-        <v>4</v>
+      <c r="B848" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="C848" s="4" t="s">
         <v>1703</v>
@@ -19915,13 +19927,13 @@
       <c r="D848" s="14"/>
     </row>
     <row r="849" ht="22.5" customHeight="1">
-      <c r="A849" s="4" t="s">
+      <c r="A849" s="9" t="s">
         <v>1704</v>
       </c>
-      <c r="B849" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C849" s="4" t="s">
+      <c r="B849" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C849" s="9" t="s">
         <v>1705</v>
       </c>
       <c r="D849" s="14"/>
@@ -19930,7 +19942,7 @@
       <c r="A850" s="4" t="s">
         <v>1706</v>
       </c>
-      <c r="B850" s="10" t="s">
+      <c r="B850" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C850" s="4" t="s">
@@ -19939,25 +19951,25 @@
       <c r="D850" s="14"/>
     </row>
     <row r="851" ht="22.5" customHeight="1">
-      <c r="A851" s="9" t="s">
+      <c r="A851" s="4" t="s">
         <v>1708</v>
       </c>
-      <c r="B851" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C851" s="9" t="s">
+      <c r="B851" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C851" s="4" t="s">
         <v>1709</v>
       </c>
       <c r="D851" s="14"/>
     </row>
     <row r="852" ht="22.5" customHeight="1">
-      <c r="A852" s="9" t="s">
+      <c r="A852" s="4" t="s">
         <v>1710</v>
       </c>
       <c r="B852" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C852" s="9" t="s">
+      <c r="C852" s="4" t="s">
         <v>1711</v>
       </c>
       <c r="D852" s="14"/>
@@ -19966,7 +19978,7 @@
       <c r="A853" s="9" t="s">
         <v>1712</v>
       </c>
-      <c r="B853" s="5" t="s">
+      <c r="B853" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C853" s="9" t="s">
@@ -19975,37 +19987,37 @@
       <c r="D853" s="14"/>
     </row>
     <row r="854" ht="22.5" customHeight="1">
-      <c r="A854" s="4" t="s">
+      <c r="A854" s="9" t="s">
         <v>1714</v>
       </c>
       <c r="B854" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C854" s="4" t="s">
+      <c r="C854" s="9" t="s">
         <v>1715</v>
       </c>
       <c r="D854" s="14"/>
     </row>
     <row r="855" ht="22.5" customHeight="1">
-      <c r="A855" s="4" t="s">
+      <c r="A855" s="9" t="s">
         <v>1716</v>
       </c>
-      <c r="B855" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C855" s="4" t="s">
+      <c r="B855" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C855" s="9" t="s">
         <v>1717</v>
       </c>
       <c r="D855" s="14"/>
     </row>
     <row r="856" ht="22.5" customHeight="1">
-      <c r="A856" s="9" t="s">
+      <c r="A856" s="4" t="s">
         <v>1718</v>
       </c>
       <c r="B856" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C856" s="9" t="s">
+      <c r="C856" s="4" t="s">
         <v>1719</v>
       </c>
       <c r="D856" s="14"/>
@@ -20015,7 +20027,7 @@
         <v>1720</v>
       </c>
       <c r="B857" s="7" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C857" s="4" t="s">
         <v>1721</v>
@@ -20023,22 +20035,22 @@
       <c r="D857" s="14"/>
     </row>
     <row r="858" ht="22.5" customHeight="1">
-      <c r="A858" s="4" t="s">
+      <c r="A858" s="9" t="s">
         <v>1722</v>
       </c>
       <c r="B858" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C858" s="4" t="s">
+      <c r="C858" s="9" t="s">
         <v>1723</v>
       </c>
       <c r="D858" s="14"/>
     </row>
     <row r="859" ht="22.5" customHeight="1">
-      <c r="A859" s="9" t="s">
+      <c r="A859" s="4" t="s">
         <v>1724</v>
       </c>
-      <c r="B859" s="10" t="s">
+      <c r="B859" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C859" s="4" t="s">
@@ -20047,13 +20059,13 @@
       <c r="D859" s="14"/>
     </row>
     <row r="860" ht="22.5" customHeight="1">
-      <c r="A860" s="9" t="s">
+      <c r="A860" s="4" t="s">
         <v>1726</v>
       </c>
-      <c r="B860" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C860" s="9" t="s">
+      <c r="B860" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C860" s="4" t="s">
         <v>1727</v>
       </c>
       <c r="D860" s="14"/>
@@ -20065,7 +20077,7 @@
       <c r="B861" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C861" s="9" t="s">
+      <c r="C861" s="4" t="s">
         <v>1729</v>
       </c>
       <c r="D861" s="14"/>
@@ -20074,7 +20086,7 @@
       <c r="A862" s="9" t="s">
         <v>1730</v>
       </c>
-      <c r="B862" s="10" t="s">
+      <c r="B862" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C862" s="9" t="s">
@@ -20087,7 +20099,7 @@
         <v>1732</v>
       </c>
       <c r="B863" s="10" t="s">
-        <v>579</v>
+        <v>4</v>
       </c>
       <c r="C863" s="9" t="s">
         <v>1733</v>
@@ -20095,13 +20107,13 @@
       <c r="D863" s="14"/>
     </row>
     <row r="864" ht="22.5" customHeight="1">
-      <c r="A864" s="4" t="s">
+      <c r="A864" s="9" t="s">
         <v>1734</v>
       </c>
       <c r="B864" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C864" s="4" t="s">
+      <c r="C864" s="9" t="s">
         <v>1735</v>
       </c>
       <c r="D864" s="14"/>
@@ -20110,8 +20122,8 @@
       <c r="A865" s="9" t="s">
         <v>1736</v>
       </c>
-      <c r="B865" s="5" t="s">
-        <v>4</v>
+      <c r="B865" s="10" t="s">
+        <v>579</v>
       </c>
       <c r="C865" s="9" t="s">
         <v>1737</v>
@@ -20122,8 +20134,8 @@
       <c r="A866" s="4" t="s">
         <v>1738</v>
       </c>
-      <c r="B866" s="7" t="s">
-        <v>107</v>
+      <c r="B866" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C866" s="4" t="s">
         <v>1739</v>
@@ -20131,13 +20143,13 @@
       <c r="D866" s="14"/>
     </row>
     <row r="867" ht="22.5" customHeight="1">
-      <c r="A867" s="4" t="s">
+      <c r="A867" s="9" t="s">
         <v>1740</v>
       </c>
-      <c r="B867" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C867" s="4" t="s">
+      <c r="B867" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C867" s="9" t="s">
         <v>1741</v>
       </c>
       <c r="D867" s="14"/>
@@ -20146,8 +20158,8 @@
       <c r="A868" s="4" t="s">
         <v>1742</v>
       </c>
-      <c r="B868" s="5" t="s">
-        <v>4</v>
+      <c r="B868" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="C868" s="4" t="s">
         <v>1743</v>
@@ -20155,13 +20167,13 @@
       <c r="D868" s="14"/>
     </row>
     <row r="869" ht="22.5" customHeight="1">
-      <c r="A869" s="9" t="s">
+      <c r="A869" s="4" t="s">
         <v>1744</v>
       </c>
       <c r="B869" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C869" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C869" s="4" t="s">
         <v>1745</v>
       </c>
       <c r="D869" s="14"/>
@@ -20170,8 +20182,8 @@
       <c r="A870" s="4" t="s">
         <v>1746</v>
       </c>
-      <c r="B870" s="7" t="s">
-        <v>107</v>
+      <c r="B870" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C870" s="4" t="s">
         <v>1747</v>
@@ -20179,11 +20191,11 @@
       <c r="D870" s="14"/>
     </row>
     <row r="871" ht="22.5" customHeight="1">
-      <c r="A871" s="4" t="s">
+      <c r="A871" s="9" t="s">
         <v>1748</v>
       </c>
-      <c r="B871" s="7" t="s">
-        <v>210</v>
+      <c r="B871" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C871" s="9" t="s">
         <v>1749</v>
@@ -20195,7 +20207,7 @@
         <v>1750</v>
       </c>
       <c r="B872" s="7" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="C872" s="4" t="s">
         <v>1751</v>
@@ -20206,58 +20218,58 @@
       <c r="A873" s="4" t="s">
         <v>1752</v>
       </c>
-      <c r="B873" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C873" s="4" t="s">
+      <c r="B873" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C873" s="9" t="s">
         <v>1753</v>
       </c>
       <c r="D873" s="14"/>
     </row>
     <row r="874" ht="22.5" customHeight="1">
-      <c r="A874" s="9" t="s">
+      <c r="A874" s="4" t="s">
         <v>1754</v>
       </c>
-      <c r="B874" s="10" t="s">
+      <c r="B874" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C874" s="4" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D874" s="14"/>
+    </row>
+    <row r="875" ht="22.5" customHeight="1">
+      <c r="A875" s="4" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B875" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C875" s="4" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D875" s="14"/>
+    </row>
+    <row r="876" ht="22.5" customHeight="1">
+      <c r="A876" s="9" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B876" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="C874" s="9" t="s">
-        <v>1755</v>
-      </c>
-      <c r="D874" s="14"/>
-    </row>
-    <row r="875" ht="22.5" customHeight="1">
-      <c r="A875" s="9" t="s">
-        <v>1756</v>
-      </c>
-      <c r="B875" s="10" t="s">
+      <c r="C876" s="9" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D876" s="14"/>
+    </row>
+    <row r="877" ht="22.5" customHeight="1">
+      <c r="A877" s="9" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B877" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="C875" s="9" t="s">
-        <v>1757</v>
-      </c>
-      <c r="D875" s="14"/>
-    </row>
-    <row r="876" ht="22.5" customHeight="1">
-      <c r="A876" s="4" t="s">
-        <v>1758</v>
-      </c>
-      <c r="B876" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C876" s="4" t="s">
-        <v>1759</v>
-      </c>
-      <c r="D876" s="14"/>
-    </row>
-    <row r="877" ht="22.5" customHeight="1">
-      <c r="A877" s="4" t="s">
-        <v>1760</v>
-      </c>
-      <c r="B877" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C877" s="4" t="s">
+      <c r="C877" s="9" t="s">
         <v>1761</v>
       </c>
       <c r="D877" s="14"/>
@@ -20267,7 +20279,7 @@
         <v>1762</v>
       </c>
       <c r="B878" s="10" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="C878" s="4" t="s">
         <v>1763</v>
@@ -20275,13 +20287,13 @@
       <c r="D878" s="14"/>
     </row>
     <row r="879" ht="22.5" customHeight="1">
-      <c r="A879" s="9" t="s">
+      <c r="A879" s="4" t="s">
         <v>1764</v>
       </c>
-      <c r="B879" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C879" s="9" t="s">
+      <c r="B879" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C879" s="4" t="s">
         <v>1765</v>
       </c>
       <c r="D879" s="14"/>
@@ -20291,7 +20303,7 @@
         <v>1766</v>
       </c>
       <c r="B880" s="10" t="s">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="C880" s="4" t="s">
         <v>1767</v>
@@ -20299,13 +20311,13 @@
       <c r="D880" s="14"/>
     </row>
     <row r="881" ht="22.5" customHeight="1">
-      <c r="A881" s="4" t="s">
+      <c r="A881" s="9" t="s">
         <v>1768</v>
       </c>
       <c r="B881" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C881" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C881" s="9" t="s">
         <v>1769</v>
       </c>
       <c r="D881" s="14"/>
@@ -20323,49 +20335,49 @@
       <c r="D882" s="14"/>
     </row>
     <row r="883" ht="22.5" customHeight="1">
-      <c r="A883" s="9" t="s">
+      <c r="A883" s="4" t="s">
         <v>1772</v>
       </c>
       <c r="B883" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C883" s="9" t="s">
+      <c r="C883" s="4" t="s">
         <v>1773</v>
       </c>
       <c r="D883" s="14"/>
     </row>
     <row r="884" ht="22.5" customHeight="1">
-      <c r="A884" s="9" t="s">
+      <c r="A884" s="4" t="s">
         <v>1774</v>
       </c>
       <c r="B884" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C884" s="9" t="s">
+      <c r="C884" s="4" t="s">
         <v>1775</v>
       </c>
       <c r="D884" s="14"/>
     </row>
     <row r="885" ht="22.5" customHeight="1">
-      <c r="A885" s="4" t="s">
+      <c r="A885" s="9" t="s">
         <v>1776</v>
       </c>
       <c r="B885" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C885" s="4" t="s">
+      <c r="C885" s="9" t="s">
         <v>1777</v>
       </c>
       <c r="D885" s="14"/>
     </row>
     <row r="886" ht="22.5" customHeight="1">
-      <c r="A886" s="4" t="s">
+      <c r="A886" s="9" t="s">
         <v>1778</v>
       </c>
       <c r="B886" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C886" s="4" t="s">
+      <c r="C886" s="9" t="s">
         <v>1779</v>
       </c>
       <c r="D886" s="14"/>
@@ -20383,13 +20395,13 @@
       <c r="D887" s="14"/>
     </row>
     <row r="888" ht="22.5" customHeight="1">
-      <c r="A888" s="9" t="s">
+      <c r="A888" s="4" t="s">
         <v>1782</v>
       </c>
       <c r="B888" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C888" s="9" t="s">
+      <c r="C888" s="4" t="s">
         <v>1783</v>
       </c>
       <c r="D888" s="14"/>
@@ -20443,37 +20455,37 @@
       <c r="D892" s="14"/>
     </row>
     <row r="893" ht="22.5" customHeight="1">
-      <c r="A893" s="9" t="s">
+      <c r="A893" s="4" t="s">
         <v>1792</v>
       </c>
       <c r="B893" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C893" s="9" t="s">
+      <c r="C893" s="4" t="s">
         <v>1793</v>
       </c>
       <c r="D893" s="14"/>
     </row>
     <row r="894" ht="22.5" customHeight="1">
-      <c r="A894" s="4" t="s">
+      <c r="A894" s="9" t="s">
         <v>1794</v>
       </c>
       <c r="B894" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C894" s="4" t="s">
+      <c r="C894" s="9" t="s">
         <v>1795</v>
       </c>
       <c r="D894" s="14"/>
     </row>
     <row r="895" ht="22.5" customHeight="1">
-      <c r="A895" s="4" t="s">
+      <c r="A895" s="9" t="s">
         <v>1796</v>
       </c>
       <c r="B895" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C895" s="4" t="s">
+      <c r="C895" s="9" t="s">
         <v>1797</v>
       </c>
       <c r="D895" s="14"/>
@@ -20515,13 +20527,13 @@
       <c r="D898" s="14"/>
     </row>
     <row r="899" ht="22.5" customHeight="1">
-      <c r="A899" s="9" t="s">
+      <c r="A899" s="4" t="s">
         <v>1804</v>
       </c>
       <c r="B899" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C899" s="9" t="s">
+      <c r="C899" s="4" t="s">
         <v>1805</v>
       </c>
       <c r="D899" s="14"/>
@@ -20539,13 +20551,13 @@
       <c r="D900" s="14"/>
     </row>
     <row r="901" ht="22.5" customHeight="1">
-      <c r="A901" s="4" t="s">
+      <c r="A901" s="9" t="s">
         <v>1808</v>
       </c>
       <c r="B901" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C901" s="4" t="s">
+      <c r="C901" s="9" t="s">
         <v>1809</v>
       </c>
       <c r="D901" s="14"/>
@@ -20611,13 +20623,13 @@
       <c r="D906" s="14"/>
     </row>
     <row r="907" ht="22.5" customHeight="1">
-      <c r="A907" s="9" t="s">
+      <c r="A907" s="4" t="s">
         <v>1820</v>
       </c>
       <c r="B907" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C907" s="9" t="s">
+      <c r="C907" s="4" t="s">
         <v>1821</v>
       </c>
       <c r="D907" s="14"/>
@@ -20635,37 +20647,37 @@
       <c r="D908" s="14"/>
     </row>
     <row r="909" ht="22.5" customHeight="1">
-      <c r="A909" s="4" t="s">
+      <c r="A909" s="9" t="s">
         <v>1824</v>
       </c>
       <c r="B909" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C909" s="4" t="s">
+      <c r="C909" s="9" t="s">
         <v>1825</v>
       </c>
       <c r="D909" s="14"/>
     </row>
     <row r="910" ht="22.5" customHeight="1">
-      <c r="A910" s="9" t="s">
+      <c r="A910" s="4" t="s">
         <v>1826</v>
       </c>
       <c r="B910" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C910" s="9" t="s">
+      <c r="C910" s="4" t="s">
         <v>1827</v>
       </c>
       <c r="D910" s="14"/>
     </row>
     <row r="911" ht="22.5" customHeight="1">
-      <c r="A911" s="9" t="s">
+      <c r="A911" s="4" t="s">
         <v>1828</v>
       </c>
       <c r="B911" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C911" s="9" t="s">
+      <c r="C911" s="4" t="s">
         <v>1829</v>
       </c>
       <c r="D911" s="14"/>
@@ -20683,13 +20695,13 @@
       <c r="D912" s="14"/>
     </row>
     <row r="913" ht="22.5" customHeight="1">
-      <c r="A913" s="4" t="s">
+      <c r="A913" s="9" t="s">
         <v>1832</v>
       </c>
       <c r="B913" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C913" s="4" t="s">
+      <c r="C913" s="9" t="s">
         <v>1833</v>
       </c>
       <c r="D913" s="14"/>
@@ -20719,13 +20731,13 @@
       <c r="D915" s="14"/>
     </row>
     <row r="916" ht="22.5" customHeight="1">
-      <c r="A916" s="4" t="s">
+      <c r="A916" s="9" t="s">
         <v>1838</v>
       </c>
       <c r="B916" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C916" s="4" t="s">
+      <c r="C916" s="9" t="s">
         <v>1839</v>
       </c>
       <c r="D916" s="14"/>
@@ -20735,7 +20747,7 @@
         <v>1840</v>
       </c>
       <c r="B917" s="10" t="s">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="C917" s="4" t="s">
         <v>1841</v>
@@ -20755,13 +20767,13 @@
       <c r="D918" s="14"/>
     </row>
     <row r="919" ht="22.5" customHeight="1">
-      <c r="A919" s="9" t="s">
+      <c r="A919" s="4" t="s">
         <v>1844</v>
       </c>
       <c r="B919" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C919" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C919" s="4" t="s">
         <v>1845</v>
       </c>
       <c r="D919" s="14"/>
@@ -20803,49 +20815,49 @@
       <c r="D922" s="14"/>
     </row>
     <row r="923" ht="22.5" customHeight="1">
-      <c r="A923" s="4" t="s">
+      <c r="A923" s="9" t="s">
         <v>1852</v>
       </c>
       <c r="B923" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C923" s="4" t="s">
+      <c r="C923" s="9" t="s">
         <v>1853</v>
       </c>
       <c r="D923" s="14"/>
     </row>
     <row r="924" ht="22.5" customHeight="1">
-      <c r="A924" s="9" t="s">
+      <c r="A924" s="4" t="s">
         <v>1854</v>
       </c>
       <c r="B924" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C924" s="9" t="s">
+      <c r="C924" s="4" t="s">
         <v>1855</v>
       </c>
       <c r="D924" s="14"/>
     </row>
     <row r="925" ht="22.5" customHeight="1">
-      <c r="A925" s="9" t="s">
+      <c r="A925" s="4" t="s">
         <v>1856</v>
       </c>
       <c r="B925" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C925" s="9" t="s">
+      <c r="C925" s="4" t="s">
         <v>1857</v>
       </c>
       <c r="D925" s="14"/>
     </row>
     <row r="926" ht="22.5" customHeight="1">
-      <c r="A926" s="4" t="s">
+      <c r="A926" s="9" t="s">
         <v>1858</v>
       </c>
       <c r="B926" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C926" s="4" t="s">
+      <c r="C926" s="9" t="s">
         <v>1859</v>
       </c>
       <c r="D926" s="14"/>
@@ -20899,61 +20911,61 @@
       <c r="D930" s="14"/>
     </row>
     <row r="931" ht="22.5" customHeight="1">
-      <c r="A931" s="4" t="s">
+      <c r="A931" s="9" t="s">
         <v>1868</v>
       </c>
       <c r="B931" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C931" s="4" t="s">
+      <c r="C931" s="9" t="s">
         <v>1869</v>
       </c>
       <c r="D931" s="14"/>
     </row>
     <row r="932" ht="22.5" customHeight="1">
-      <c r="A932" s="9" t="s">
+      <c r="A932" s="4" t="s">
         <v>1870</v>
       </c>
       <c r="B932" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C932" s="9" t="s">
+      <c r="C932" s="4" t="s">
         <v>1871</v>
       </c>
       <c r="D932" s="14"/>
     </row>
     <row r="933" ht="22.5" customHeight="1">
-      <c r="A933" s="9" t="s">
+      <c r="A933" s="4" t="s">
         <v>1872</v>
       </c>
       <c r="B933" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C933" s="9" t="s">
+      <c r="C933" s="4" t="s">
         <v>1873</v>
       </c>
       <c r="D933" s="14"/>
     </row>
     <row r="934" ht="22.5" customHeight="1">
-      <c r="A934" s="4" t="s">
+      <c r="A934" s="9" t="s">
         <v>1874</v>
       </c>
       <c r="B934" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C934" s="4" t="s">
+      <c r="C934" s="9" t="s">
         <v>1875</v>
       </c>
       <c r="D934" s="14"/>
     </row>
     <row r="935" ht="22.5" customHeight="1">
-      <c r="A935" s="4" t="s">
+      <c r="A935" s="9" t="s">
         <v>1876</v>
       </c>
       <c r="B935" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C935" s="4" t="s">
+      <c r="C935" s="9" t="s">
         <v>1877</v>
       </c>
       <c r="D935" s="14"/>
@@ -20971,19 +20983,19 @@
       <c r="D936" s="14"/>
     </row>
     <row r="937" ht="22.5" customHeight="1">
-      <c r="A937" s="9" t="s">
+      <c r="A937" s="4" t="s">
         <v>1880</v>
       </c>
       <c r="B937" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C937" s="9" t="s">
+      <c r="C937" s="4" t="s">
         <v>1881</v>
       </c>
       <c r="D937" s="14"/>
     </row>
     <row r="938" ht="22.5" customHeight="1">
-      <c r="A938" s="9" t="s">
+      <c r="A938" s="4" t="s">
         <v>1882</v>
       </c>
       <c r="B938" s="10" t="s">
@@ -20995,19 +21007,19 @@
       <c r="D938" s="14"/>
     </row>
     <row r="939" ht="22.5" customHeight="1">
-      <c r="A939" s="4" t="s">
+      <c r="A939" s="9" t="s">
         <v>1884</v>
       </c>
       <c r="B939" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C939" s="4" t="s">
+      <c r="C939" s="9" t="s">
         <v>1885</v>
       </c>
       <c r="D939" s="14"/>
     </row>
     <row r="940" ht="22.5" customHeight="1">
-      <c r="A940" s="4" t="s">
+      <c r="A940" s="9" t="s">
         <v>1886</v>
       </c>
       <c r="B940" s="10" t="s">
@@ -21031,13 +21043,13 @@
       <c r="D941" s="14"/>
     </row>
     <row r="942" ht="22.5" customHeight="1">
-      <c r="A942" s="9" t="s">
+      <c r="A942" s="4" t="s">
         <v>1890</v>
       </c>
       <c r="B942" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C942" s="9" t="s">
+      <c r="C942" s="4" t="s">
         <v>1891</v>
       </c>
       <c r="D942" s="14"/>
@@ -21055,13 +21067,13 @@
       <c r="D943" s="14"/>
     </row>
     <row r="944" ht="22.5" customHeight="1">
-      <c r="A944" s="4" t="s">
+      <c r="A944" s="9" t="s">
         <v>1894</v>
       </c>
       <c r="B944" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C944" s="4" t="s">
+      <c r="C944" s="9" t="s">
         <v>1895</v>
       </c>
       <c r="D944" s="14"/>
@@ -21115,49 +21127,49 @@
       <c r="D948" s="14"/>
     </row>
     <row r="949" ht="22.5" customHeight="1">
-      <c r="A949" s="9" t="s">
+      <c r="A949" s="4" t="s">
         <v>1904</v>
       </c>
       <c r="B949" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C949" s="9" t="s">
+      <c r="C949" s="4" t="s">
         <v>1905</v>
       </c>
       <c r="D949" s="14"/>
     </row>
     <row r="950" ht="22.5" customHeight="1">
-      <c r="A950" s="9" t="s">
+      <c r="A950" s="4" t="s">
         <v>1906</v>
       </c>
       <c r="B950" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C950" s="9" t="s">
+      <c r="C950" s="4" t="s">
         <v>1907</v>
       </c>
       <c r="D950" s="14"/>
     </row>
     <row r="951" ht="22.5" customHeight="1">
-      <c r="A951" s="4" t="s">
+      <c r="A951" s="9" t="s">
         <v>1908</v>
       </c>
       <c r="B951" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C951" s="4" t="s">
+      <c r="C951" s="9" t="s">
         <v>1909</v>
       </c>
       <c r="D951" s="14"/>
     </row>
     <row r="952" ht="22.5" customHeight="1">
-      <c r="A952" s="4" t="s">
+      <c r="A952" s="9" t="s">
         <v>1910</v>
       </c>
       <c r="B952" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C952" s="4" t="s">
+      <c r="C952" s="9" t="s">
         <v>1911</v>
       </c>
       <c r="D952" s="14"/>
@@ -21175,25 +21187,25 @@
       <c r="D953" s="14"/>
     </row>
     <row r="954" ht="22.5" customHeight="1">
-      <c r="A954" s="9" t="s">
+      <c r="A954" s="4" t="s">
         <v>1914</v>
       </c>
       <c r="B954" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C954" s="9" t="s">
+      <c r="C954" s="4" t="s">
         <v>1915</v>
       </c>
       <c r="D954" s="14"/>
     </row>
     <row r="955" ht="22.5" customHeight="1">
-      <c r="A955" s="9" t="s">
+      <c r="A955" s="4" t="s">
         <v>1916</v>
       </c>
       <c r="B955" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C955" s="9" t="s">
+      <c r="C955" s="4" t="s">
         <v>1917</v>
       </c>
       <c r="D955" s="14"/>
@@ -21223,37 +21235,37 @@
       <c r="D957" s="14"/>
     </row>
     <row r="958" ht="22.5" customHeight="1">
-      <c r="A958" s="4" t="s">
+      <c r="A958" s="9" t="s">
         <v>1922</v>
       </c>
       <c r="B958" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C958" s="4" t="s">
+      <c r="C958" s="9" t="s">
         <v>1923</v>
       </c>
       <c r="D958" s="14"/>
     </row>
     <row r="959" ht="22.5" customHeight="1">
-      <c r="A959" s="4" t="s">
+      <c r="A959" s="9" t="s">
         <v>1924</v>
       </c>
       <c r="B959" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C959" s="4" t="s">
+      <c r="C959" s="9" t="s">
         <v>1925</v>
       </c>
       <c r="D959" s="14"/>
     </row>
     <row r="960" ht="22.5" customHeight="1">
-      <c r="A960" s="9" t="s">
+      <c r="A960" s="4" t="s">
         <v>1926</v>
       </c>
       <c r="B960" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C960" s="9" t="s">
+      <c r="C960" s="4" t="s">
         <v>1927</v>
       </c>
       <c r="D960" s="14"/>
@@ -21271,13 +21283,13 @@
       <c r="D961" s="14"/>
     </row>
     <row r="962" ht="22.5" customHeight="1">
-      <c r="A962" s="4" t="s">
+      <c r="A962" s="9" t="s">
         <v>1930</v>
       </c>
       <c r="B962" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C962" s="4" t="s">
+      <c r="C962" s="9" t="s">
         <v>1931</v>
       </c>
       <c r="D962" s="14"/>
@@ -21343,13 +21355,13 @@
       <c r="D967" s="14"/>
     </row>
     <row r="968" ht="22.5" customHeight="1">
-      <c r="A968" s="9" t="s">
+      <c r="A968" s="4" t="s">
         <v>1942</v>
       </c>
       <c r="B968" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C968" s="9" t="s">
+      <c r="C968" s="4" t="s">
         <v>1943</v>
       </c>
       <c r="D968" s="14"/>
@@ -21379,13 +21391,13 @@
       <c r="D970" s="14"/>
     </row>
     <row r="971" ht="22.5" customHeight="1">
-      <c r="A971" s="9" t="s">
+      <c r="A971" s="4" t="s">
         <v>1948</v>
       </c>
       <c r="B971" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C971" s="9" t="s">
+      <c r="C971" s="4" t="s">
         <v>1949</v>
       </c>
       <c r="D971" s="14"/>
@@ -21403,37 +21415,37 @@
       <c r="D972" s="14"/>
     </row>
     <row r="973" ht="22.5" customHeight="1">
-      <c r="A973" s="4" t="s">
+      <c r="A973" s="9" t="s">
         <v>1952</v>
       </c>
       <c r="B973" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C973" s="4" t="s">
+      <c r="C973" s="9" t="s">
         <v>1953</v>
       </c>
       <c r="D973" s="14"/>
     </row>
     <row r="974" ht="22.5" customHeight="1">
-      <c r="A974" s="4" t="s">
+      <c r="A974" s="9" t="s">
         <v>1954</v>
       </c>
       <c r="B974" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C974" s="4" t="s">
+      <c r="C974" s="9" t="s">
         <v>1955</v>
       </c>
       <c r="D974" s="14"/>
     </row>
     <row r="975" ht="22.5" customHeight="1">
-      <c r="A975" s="9" t="s">
+      <c r="A975" s="4" t="s">
         <v>1956</v>
       </c>
       <c r="B975" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C975" s="9" t="s">
+      <c r="C975" s="4" t="s">
         <v>1957</v>
       </c>
       <c r="D975" s="14"/>
@@ -21463,13 +21475,13 @@
       <c r="D977" s="14"/>
     </row>
     <row r="978" ht="22.5" customHeight="1">
-      <c r="A978" s="9" t="s">
+      <c r="A978" s="4" t="s">
         <v>1962</v>
       </c>
       <c r="B978" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C978" s="9" t="s">
+      <c r="C978" s="4" t="s">
         <v>1963</v>
       </c>
       <c r="D978" s="14"/>
@@ -21487,37 +21499,37 @@
       <c r="D979" s="14"/>
     </row>
     <row r="980" ht="22.5" customHeight="1">
-      <c r="A980" s="4" t="s">
+      <c r="A980" s="9" t="s">
         <v>1966</v>
       </c>
       <c r="B980" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C980" s="4" t="s">
+      <c r="C980" s="9" t="s">
         <v>1967</v>
       </c>
       <c r="D980" s="14"/>
     </row>
     <row r="981" ht="22.5" customHeight="1">
-      <c r="A981" s="4" t="s">
+      <c r="A981" s="9" t="s">
         <v>1968</v>
       </c>
       <c r="B981" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C981" s="4" t="s">
+      <c r="C981" s="9" t="s">
         <v>1969</v>
       </c>
       <c r="D981" s="14"/>
     </row>
     <row r="982" ht="22.5" customHeight="1">
-      <c r="A982" s="9" t="s">
+      <c r="A982" s="4" t="s">
         <v>1970</v>
       </c>
       <c r="B982" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C982" s="9" t="s">
+      <c r="C982" s="4" t="s">
         <v>1971</v>
       </c>
       <c r="D982" s="14"/>
@@ -21535,13 +21547,13 @@
       <c r="D983" s="14"/>
     </row>
     <row r="984" ht="22.5" customHeight="1">
-      <c r="A984" s="4" t="s">
+      <c r="A984" s="9" t="s">
         <v>1974</v>
       </c>
       <c r="B984" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C984" s="4" t="s">
+      <c r="C984" s="9" t="s">
         <v>1975</v>
       </c>
       <c r="D984" s="14"/>
@@ -21562,7 +21574,7 @@
       <c r="A986" s="4" t="s">
         <v>1978</v>
       </c>
-      <c r="B986" s="7" t="s">
+      <c r="B986" s="10" t="s">
         <v>94</v>
       </c>
       <c r="C986" s="4" t="s">
@@ -21571,49 +21583,49 @@
       <c r="D986" s="14"/>
     </row>
     <row r="987" ht="22.5" customHeight="1">
-      <c r="A987" s="9" t="s">
+      <c r="A987" s="4" t="s">
         <v>1980</v>
       </c>
       <c r="B987" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C987" s="9" t="s">
+      <c r="C987" s="4" t="s">
         <v>1981</v>
       </c>
       <c r="D987" s="14"/>
     </row>
     <row r="988" ht="22.5" customHeight="1">
-      <c r="A988" s="9" t="s">
+      <c r="A988" s="4" t="s">
         <v>1982</v>
       </c>
-      <c r="B988" s="10" t="s">
+      <c r="B988" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C988" s="9" t="s">
+      <c r="C988" s="4" t="s">
         <v>1983</v>
       </c>
       <c r="D988" s="14"/>
     </row>
     <row r="989" ht="22.5" customHeight="1">
-      <c r="A989" s="4" t="s">
+      <c r="A989" s="9" t="s">
         <v>1984</v>
       </c>
       <c r="B989" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C989" s="4" t="s">
+      <c r="C989" s="9" t="s">
         <v>1985</v>
       </c>
       <c r="D989" s="14"/>
     </row>
     <row r="990" ht="22.5" customHeight="1">
-      <c r="A990" s="4" t="s">
+      <c r="A990" s="9" t="s">
         <v>1986</v>
       </c>
       <c r="B990" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C990" s="4" t="s">
+      <c r="C990" s="9" t="s">
         <v>1987</v>
       </c>
       <c r="D990" s="14"/>
@@ -21631,61 +21643,61 @@
       <c r="D991" s="14"/>
     </row>
     <row r="992" ht="22.5" customHeight="1">
-      <c r="A992" s="9" t="s">
+      <c r="A992" s="4" t="s">
         <v>1990</v>
       </c>
       <c r="B992" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C992" s="9" t="s">
+      <c r="C992" s="4" t="s">
         <v>1991</v>
       </c>
       <c r="D992" s="14"/>
     </row>
     <row r="993" ht="22.5" customHeight="1">
-      <c r="A993" s="9" t="s">
+      <c r="A993" s="4" t="s">
         <v>1992</v>
       </c>
       <c r="B993" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C993" s="9" t="s">
+      <c r="C993" s="4" t="s">
         <v>1993</v>
       </c>
       <c r="D993" s="14"/>
     </row>
     <row r="994" ht="22.5" customHeight="1">
-      <c r="A994" s="4" t="s">
+      <c r="A994" s="9" t="s">
         <v>1994</v>
       </c>
       <c r="B994" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C994" s="4" t="s">
+      <c r="C994" s="9" t="s">
         <v>1995</v>
       </c>
       <c r="D994" s="14"/>
     </row>
     <row r="995" ht="22.5" customHeight="1">
-      <c r="A995" s="4" t="s">
+      <c r="A995" s="9" t="s">
         <v>1996</v>
       </c>
       <c r="B995" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C995" s="4" t="s">
+      <c r="C995" s="9" t="s">
         <v>1997</v>
       </c>
       <c r="D995" s="14"/>
     </row>
     <row r="996" ht="22.5" customHeight="1">
-      <c r="A996" s="9" t="s">
+      <c r="A996" s="4" t="s">
         <v>1998</v>
       </c>
       <c r="B996" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C996" s="9" t="s">
+      <c r="C996" s="4" t="s">
         <v>1999</v>
       </c>
       <c r="D996" s="14"/>
@@ -21703,7 +21715,7 @@
       <c r="D997" s="14"/>
     </row>
     <row r="998" ht="22.5" customHeight="1">
-      <c r="A998" s="4" t="s">
+      <c r="A998" s="9" t="s">
         <v>2002</v>
       </c>
       <c r="B998" s="10" t="s">
@@ -21715,13 +21727,13 @@
       <c r="D998" s="14"/>
     </row>
     <row r="999" ht="22.5" customHeight="1">
-      <c r="A999" s="9" t="s">
+      <c r="A999" s="4" t="s">
         <v>2004</v>
       </c>
       <c r="B999" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C999" s="9" t="s">
+      <c r="C999" s="4" t="s">
         <v>2005</v>
       </c>
       <c r="D999" s="14"/>
@@ -21733,31 +21745,31 @@
       <c r="B1000" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1000" s="4" t="s">
+      <c r="C1000" s="9" t="s">
         <v>2007</v>
       </c>
       <c r="D1000" s="14"/>
     </row>
     <row r="1001" ht="22.5" customHeight="1">
-      <c r="A1001" s="4" t="s">
+      <c r="A1001" s="9" t="s">
         <v>2008</v>
       </c>
       <c r="B1001" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1001" s="4" t="s">
+      <c r="C1001" s="9" t="s">
         <v>2009</v>
       </c>
       <c r="D1001" s="14"/>
     </row>
     <row r="1002" ht="22.5" customHeight="1">
-      <c r="A1002" s="9" t="s">
+      <c r="A1002" s="4" t="s">
         <v>2010</v>
       </c>
       <c r="B1002" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1002" s="9" t="s">
+      <c r="C1002" s="4" t="s">
         <v>2011</v>
       </c>
       <c r="D1002" s="14"/>
@@ -21811,37 +21823,37 @@
       <c r="D1006" s="14"/>
     </row>
     <row r="1007" ht="22.5" customHeight="1">
-      <c r="A1007" s="9" t="s">
+      <c r="A1007" s="4" t="s">
         <v>2020</v>
       </c>
       <c r="B1007" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1007" s="9" t="s">
+      <c r="C1007" s="4" t="s">
         <v>2021</v>
       </c>
       <c r="D1007" s="14"/>
     </row>
     <row r="1008" ht="22.5" customHeight="1">
-      <c r="A1008" s="4" t="s">
+      <c r="A1008" s="9" t="s">
         <v>2022</v>
       </c>
       <c r="B1008" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1008" s="4" t="s">
+      <c r="C1008" s="9" t="s">
         <v>2023</v>
       </c>
       <c r="D1008" s="14"/>
     </row>
     <row r="1009" ht="22.5" customHeight="1">
-      <c r="A1009" s="4" t="s">
+      <c r="A1009" s="9" t="s">
         <v>2024</v>
       </c>
       <c r="B1009" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1009" s="4" t="s">
+      <c r="C1009" s="9" t="s">
         <v>2025</v>
       </c>
       <c r="D1009" s="14"/>
@@ -21883,13 +21895,13 @@
       <c r="D1012" s="14"/>
     </row>
     <row r="1013" ht="22.5" customHeight="1">
-      <c r="A1013" s="9" t="s">
+      <c r="A1013" s="4" t="s">
         <v>2032</v>
       </c>
       <c r="B1013" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1013" s="9" t="s">
+      <c r="C1013" s="4" t="s">
         <v>2033</v>
       </c>
       <c r="D1013" s="14"/>
@@ -21907,25 +21919,25 @@
       <c r="D1014" s="14"/>
     </row>
     <row r="1015" ht="22.5" customHeight="1">
-      <c r="A1015" s="4" t="s">
+      <c r="A1015" s="9" t="s">
         <v>2036</v>
       </c>
       <c r="B1015" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1015" s="4" t="s">
+      <c r="C1015" s="9" t="s">
         <v>2037</v>
       </c>
       <c r="D1015" s="14"/>
     </row>
     <row r="1016" ht="22.5" customHeight="1">
-      <c r="A1016" s="9" t="s">
+      <c r="A1016" s="4" t="s">
         <v>2038</v>
       </c>
       <c r="B1016" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1016" s="9" t="s">
+      <c r="C1016" s="4" t="s">
         <v>2039</v>
       </c>
       <c r="D1016" s="14"/>
@@ -21934,7 +21946,7 @@
       <c r="A1017" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="B1017" s="7" t="s">
+      <c r="B1017" s="10" t="s">
         <v>94</v>
       </c>
       <c r="C1017" s="4" t="s">
@@ -21958,7 +21970,7 @@
       <c r="A1019" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="B1019" s="10" t="s">
+      <c r="B1019" s="7" t="s">
         <v>94</v>
       </c>
       <c r="C1019" s="4" t="s">
@@ -21967,25 +21979,25 @@
       <c r="D1019" s="14"/>
     </row>
     <row r="1020" ht="22.5" customHeight="1">
-      <c r="A1020" s="4" t="s">
+      <c r="A1020" s="9" t="s">
         <v>2046</v>
       </c>
       <c r="B1020" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1020" s="4" t="s">
+      <c r="C1020" s="9" t="s">
         <v>2047</v>
       </c>
       <c r="D1020" s="14"/>
     </row>
     <row r="1021" ht="22.5" customHeight="1">
-      <c r="A1021" s="9" t="s">
+      <c r="A1021" s="4" t="s">
         <v>2048</v>
       </c>
       <c r="B1021" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1021" s="9" t="s">
+      <c r="C1021" s="4" t="s">
         <v>2049</v>
       </c>
       <c r="D1021" s="14"/>
@@ -22027,13 +22039,13 @@
       <c r="D1024" s="14"/>
     </row>
     <row r="1025" ht="22.5" customHeight="1">
-      <c r="A1025" s="4" t="s">
+      <c r="A1025" s="9" t="s">
         <v>2056</v>
       </c>
       <c r="B1025" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1025" s="4" t="s">
+      <c r="C1025" s="9" t="s">
         <v>2057</v>
       </c>
       <c r="D1025" s="14"/>
@@ -22075,13 +22087,13 @@
       <c r="D1028" s="14"/>
     </row>
     <row r="1029" ht="22.5" customHeight="1">
-      <c r="A1029" s="9" t="s">
+      <c r="A1029" s="4" t="s">
         <v>2064</v>
       </c>
       <c r="B1029" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1029" s="9" t="s">
+      <c r="C1029" s="4" t="s">
         <v>2065</v>
       </c>
       <c r="D1029" s="14"/>
@@ -22111,13 +22123,13 @@
       <c r="D1031" s="14"/>
     </row>
     <row r="1032" ht="22.5" customHeight="1">
-      <c r="A1032" s="9" t="s">
+      <c r="A1032" s="4" t="s">
         <v>2070</v>
       </c>
       <c r="B1032" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1032" s="9" t="s">
+      <c r="C1032" s="4" t="s">
         <v>2071</v>
       </c>
       <c r="D1032" s="14"/>
@@ -22135,25 +22147,25 @@
       <c r="D1033" s="14"/>
     </row>
     <row r="1034" ht="22.5" customHeight="1">
-      <c r="A1034" s="4" t="s">
+      <c r="A1034" s="9" t="s">
         <v>2074</v>
       </c>
       <c r="B1034" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1034" s="4" t="s">
+      <c r="C1034" s="9" t="s">
         <v>2075</v>
       </c>
       <c r="D1034" s="14"/>
     </row>
     <row r="1035" ht="22.5" customHeight="1">
-      <c r="A1035" s="4" t="s">
+      <c r="A1035" s="9" t="s">
         <v>2076</v>
       </c>
       <c r="B1035" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1035" s="4" t="s">
+      <c r="C1035" s="9" t="s">
         <v>2077</v>
       </c>
       <c r="D1035" s="14"/>
@@ -22225,19 +22237,19 @@
       <c r="B1041" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1041" s="9" t="s">
+      <c r="C1041" s="4" t="s">
         <v>2089</v>
       </c>
       <c r="D1041" s="14"/>
     </row>
     <row r="1042" ht="22.5" customHeight="1">
-      <c r="A1042" s="9" t="s">
+      <c r="A1042" s="4" t="s">
         <v>2090</v>
       </c>
       <c r="B1042" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1042" s="9" t="s">
+      <c r="C1042" s="4" t="s">
         <v>2091</v>
       </c>
       <c r="D1042" s="14"/>
@@ -22249,7 +22261,7 @@
       <c r="B1043" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1043" s="4" t="s">
+      <c r="C1043" s="9" t="s">
         <v>2093</v>
       </c>
       <c r="D1043" s="14"/>
@@ -22279,13 +22291,13 @@
       <c r="D1045" s="14"/>
     </row>
     <row r="1046" ht="22.5" customHeight="1">
-      <c r="A1046" s="4" t="s">
+      <c r="A1046" s="9" t="s">
         <v>2098</v>
       </c>
       <c r="B1046" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1046" s="4" t="s">
+      <c r="C1046" s="9" t="s">
         <v>2099</v>
       </c>
       <c r="D1046" s="14"/>
@@ -22303,49 +22315,49 @@
       <c r="D1047" s="14"/>
     </row>
     <row r="1048" ht="22.5" customHeight="1">
-      <c r="A1048" s="9" t="s">
+      <c r="A1048" s="4" t="s">
         <v>2102</v>
       </c>
       <c r="B1048" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1048" s="9" t="s">
+      <c r="C1048" s="4" t="s">
         <v>2103</v>
       </c>
       <c r="D1048" s="14"/>
     </row>
     <row r="1049" ht="22.5" customHeight="1">
-      <c r="A1049" s="9" t="s">
+      <c r="A1049" s="4" t="s">
         <v>2104</v>
       </c>
       <c r="B1049" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1049" s="9" t="s">
+      <c r="C1049" s="4" t="s">
         <v>2105</v>
       </c>
       <c r="D1049" s="14"/>
     </row>
     <row r="1050" ht="22.5" customHeight="1">
-      <c r="A1050" s="4" t="s">
+      <c r="A1050" s="9" t="s">
         <v>2106</v>
       </c>
       <c r="B1050" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1050" s="4" t="s">
+      <c r="C1050" s="9" t="s">
         <v>2107</v>
       </c>
       <c r="D1050" s="14"/>
     </row>
     <row r="1051" ht="22.5" customHeight="1">
-      <c r="A1051" s="4" t="s">
+      <c r="A1051" s="9" t="s">
         <v>2108</v>
       </c>
       <c r="B1051" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1051" s="4" t="s">
+      <c r="C1051" s="9" t="s">
         <v>2109</v>
       </c>
       <c r="D1051" s="14"/>
@@ -22447,13 +22459,13 @@
       <c r="D1059" s="14"/>
     </row>
     <row r="1060" ht="22.5" customHeight="1">
-      <c r="A1060" s="9" t="s">
+      <c r="A1060" s="4" t="s">
         <v>2126</v>
       </c>
       <c r="B1060" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1060" s="9" t="s">
+      <c r="C1060" s="4" t="s">
         <v>2127</v>
       </c>
       <c r="D1060" s="14"/>
@@ -22471,13 +22483,13 @@
       <c r="D1061" s="14"/>
     </row>
     <row r="1062" ht="22.5" customHeight="1">
-      <c r="A1062" s="4" t="s">
+      <c r="A1062" s="9" t="s">
         <v>2130</v>
       </c>
       <c r="B1062" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1062" s="4" t="s">
+      <c r="C1062" s="9" t="s">
         <v>2131</v>
       </c>
       <c r="D1062" s="14"/>
@@ -22531,37 +22543,37 @@
       <c r="D1066" s="14"/>
     </row>
     <row r="1067" ht="22.5" customHeight="1">
-      <c r="A1067" s="9" t="s">
+      <c r="A1067" s="4" t="s">
         <v>2140</v>
       </c>
       <c r="B1067" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1067" s="9" t="s">
+      <c r="C1067" s="4" t="s">
         <v>2141</v>
       </c>
       <c r="D1067" s="14"/>
     </row>
     <row r="1068" ht="22.5" customHeight="1">
-      <c r="A1068" s="9" t="s">
+      <c r="A1068" s="4" t="s">
         <v>2142</v>
       </c>
       <c r="B1068" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1068" s="9" t="s">
+      <c r="C1068" s="4" t="s">
         <v>2143</v>
       </c>
       <c r="D1068" s="14"/>
     </row>
     <row r="1069" ht="22.5" customHeight="1">
-      <c r="A1069" s="4" t="s">
+      <c r="A1069" s="9" t="s">
         <v>2144</v>
       </c>
       <c r="B1069" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1069" s="4" t="s">
+      <c r="C1069" s="9" t="s">
         <v>2145</v>
       </c>
       <c r="D1069" s="14"/>
@@ -22591,13 +22603,13 @@
       <c r="D1071" s="14"/>
     </row>
     <row r="1072" ht="22.5" customHeight="1">
-      <c r="A1072" s="4" t="s">
+      <c r="A1072" s="9" t="s">
         <v>2150</v>
       </c>
       <c r="B1072" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1072" s="4" t="s">
+      <c r="C1072" s="9" t="s">
         <v>2151</v>
       </c>
       <c r="D1072" s="14"/>
@@ -22627,13 +22639,13 @@
       <c r="D1074" s="14"/>
     </row>
     <row r="1075" ht="22.5" customHeight="1">
-      <c r="A1075" s="9" t="s">
+      <c r="A1075" s="4" t="s">
         <v>2156</v>
       </c>
       <c r="B1075" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1075" s="9" t="s">
+      <c r="C1075" s="4" t="s">
         <v>2157</v>
       </c>
       <c r="D1075" s="14"/>
@@ -22651,13 +22663,13 @@
       <c r="D1076" s="14"/>
     </row>
     <row r="1077" ht="22.5" customHeight="1">
-      <c r="A1077" s="4" t="s">
+      <c r="A1077" s="9" t="s">
         <v>2160</v>
       </c>
       <c r="B1077" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1077" s="4" t="s">
+      <c r="C1077" s="9" t="s">
         <v>2161</v>
       </c>
       <c r="D1077" s="14"/>
@@ -22735,25 +22747,25 @@
       <c r="D1083" s="14"/>
     </row>
     <row r="1084" ht="22.5" customHeight="1">
-      <c r="A1084" s="9" t="s">
+      <c r="A1084" s="4" t="s">
         <v>2174</v>
       </c>
       <c r="B1084" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1084" s="9" t="s">
+      <c r="C1084" s="4" t="s">
         <v>2175</v>
       </c>
       <c r="D1084" s="14"/>
     </row>
     <row r="1085" ht="22.5" customHeight="1">
-      <c r="A1085" s="9" t="s">
+      <c r="A1085" s="4" t="s">
         <v>2176</v>
       </c>
       <c r="B1085" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1085" s="9" t="s">
+      <c r="C1085" s="4" t="s">
         <v>2177</v>
       </c>
       <c r="D1085" s="14"/>
@@ -22771,13 +22783,13 @@
       <c r="D1086" s="14"/>
     </row>
     <row r="1087" ht="22.5" customHeight="1">
-      <c r="A1087" s="4" t="s">
+      <c r="A1087" s="9" t="s">
         <v>2180</v>
       </c>
       <c r="B1087" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1087" s="4" t="s">
+      <c r="C1087" s="9" t="s">
         <v>2181</v>
       </c>
       <c r="D1087" s="14"/>
@@ -22843,49 +22855,49 @@
       <c r="D1092" s="14"/>
     </row>
     <row r="1093" ht="22.5" customHeight="1">
-      <c r="A1093" s="9" t="s">
+      <c r="A1093" s="4" t="s">
         <v>2192</v>
       </c>
       <c r="B1093" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1093" s="9" t="s">
+      <c r="C1093" s="4" t="s">
         <v>2193</v>
       </c>
       <c r="D1093" s="14"/>
     </row>
     <row r="1094" ht="22.5" customHeight="1">
-      <c r="A1094" s="4" t="s">
+      <c r="A1094" s="9" t="s">
         <v>2194</v>
       </c>
       <c r="B1094" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1094" s="4" t="s">
+      <c r="C1094" s="9" t="s">
         <v>2195</v>
       </c>
       <c r="D1094" s="14"/>
     </row>
     <row r="1095" ht="22.5" customHeight="1">
-      <c r="A1095" s="4" t="s">
+      <c r="A1095" s="9" t="s">
         <v>2196</v>
       </c>
-      <c r="B1095" s="7" t="s">
+      <c r="B1095" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1095" s="4" t="s">
+      <c r="C1095" s="9" t="s">
         <v>2197</v>
       </c>
       <c r="D1095" s="14"/>
     </row>
     <row r="1096" ht="22.5" customHeight="1">
-      <c r="A1096" s="9" t="s">
+      <c r="A1096" s="4" t="s">
         <v>2198</v>
       </c>
       <c r="B1096" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1096" s="9" t="s">
+      <c r="C1096" s="4" t="s">
         <v>2199</v>
       </c>
       <c r="D1096" s="14"/>
@@ -22894,7 +22906,7 @@
       <c r="A1097" s="4" t="s">
         <v>2200</v>
       </c>
-      <c r="B1097" s="10" t="s">
+      <c r="B1097" s="7" t="s">
         <v>94</v>
       </c>
       <c r="C1097" s="4" t="s">
@@ -22903,13 +22915,13 @@
       <c r="D1097" s="14"/>
     </row>
     <row r="1098" ht="22.5" customHeight="1">
-      <c r="A1098" s="4" t="s">
+      <c r="A1098" s="9" t="s">
         <v>2202</v>
       </c>
       <c r="B1098" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1098" s="4" t="s">
+      <c r="C1098" s="9" t="s">
         <v>2203</v>
       </c>
       <c r="D1098" s="14"/>
@@ -22951,25 +22963,25 @@
       <c r="D1101" s="14"/>
     </row>
     <row r="1102" ht="22.5" customHeight="1">
-      <c r="A1102" s="9" t="s">
+      <c r="A1102" s="4" t="s">
         <v>2210</v>
       </c>
       <c r="B1102" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1102" s="9" t="s">
+      <c r="C1102" s="4" t="s">
         <v>2211</v>
       </c>
       <c r="D1102" s="14"/>
     </row>
     <row r="1103" ht="22.5" customHeight="1">
-      <c r="A1103" s="9" t="s">
+      <c r="A1103" s="4" t="s">
         <v>2212</v>
       </c>
       <c r="B1103" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1103" s="9" t="s">
+      <c r="C1103" s="4" t="s">
         <v>2213</v>
       </c>
       <c r="D1103" s="14"/>
@@ -22987,13 +22999,13 @@
       <c r="D1104" s="14"/>
     </row>
     <row r="1105" ht="22.5" customHeight="1">
-      <c r="A1105" s="4" t="s">
+      <c r="A1105" s="9" t="s">
         <v>2216</v>
       </c>
       <c r="B1105" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1105" s="4" t="s">
+      <c r="C1105" s="9" t="s">
         <v>2217</v>
       </c>
       <c r="D1105" s="14"/>
@@ -23047,25 +23059,25 @@
       <c r="D1109" s="14"/>
     </row>
     <row r="1110" ht="22.5" customHeight="1">
-      <c r="A1110" s="4" t="s">
+      <c r="A1110" s="9" t="s">
         <v>2226</v>
       </c>
       <c r="B1110" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1110" s="4" t="s">
+      <c r="C1110" s="9" t="s">
         <v>2227</v>
       </c>
       <c r="D1110" s="14"/>
     </row>
     <row r="1111" ht="22.5" customHeight="1">
-      <c r="A1111" s="9" t="s">
+      <c r="A1111" s="4" t="s">
         <v>2228</v>
       </c>
       <c r="B1111" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1111" s="9" t="s">
+      <c r="C1111" s="4" t="s">
         <v>2229</v>
       </c>
       <c r="D1111" s="14"/>
@@ -23155,13 +23167,13 @@
       <c r="D1118" s="14"/>
     </row>
     <row r="1119" ht="22.5" customHeight="1">
-      <c r="A1119" s="4" t="s">
+      <c r="A1119" s="9" t="s">
         <v>2244</v>
       </c>
       <c r="B1119" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1119" s="4" t="s">
+      <c r="C1119" s="9" t="s">
         <v>2245</v>
       </c>
       <c r="D1119" s="14"/>
@@ -23179,37 +23191,37 @@
       <c r="D1120" s="14"/>
     </row>
     <row r="1121" ht="22.5" customHeight="1">
-      <c r="A1121" s="9" t="s">
+      <c r="A1121" s="4" t="s">
         <v>2248</v>
       </c>
       <c r="B1121" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1121" s="9" t="s">
+      <c r="C1121" s="4" t="s">
         <v>2249</v>
       </c>
       <c r="D1121" s="14"/>
     </row>
     <row r="1122" ht="22.5" customHeight="1">
-      <c r="A1122" s="9" t="s">
+      <c r="A1122" s="4" t="s">
         <v>2250</v>
       </c>
       <c r="B1122" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1122" s="9" t="s">
+      <c r="C1122" s="4" t="s">
         <v>2251</v>
       </c>
       <c r="D1122" s="14"/>
     </row>
     <row r="1123" ht="22.5" customHeight="1">
-      <c r="A1123" s="4" t="s">
+      <c r="A1123" s="9" t="s">
         <v>2252</v>
       </c>
       <c r="B1123" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1123" s="4" t="s">
+      <c r="C1123" s="9" t="s">
         <v>2253</v>
       </c>
       <c r="D1123" s="14"/>
@@ -23227,13 +23239,13 @@
       <c r="D1124" s="14"/>
     </row>
     <row r="1125" ht="22.5" customHeight="1">
-      <c r="A1125" s="9" t="s">
+      <c r="A1125" s="4" t="s">
         <v>2256</v>
       </c>
       <c r="B1125" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1125" s="9" t="s">
+      <c r="C1125" s="4" t="s">
         <v>2257</v>
       </c>
       <c r="D1125" s="17"/>
@@ -23263,37 +23275,37 @@
       <c r="D1127" s="14"/>
     </row>
     <row r="1128" ht="22.5" customHeight="1">
-      <c r="A1128" s="4" t="s">
+      <c r="A1128" s="9" t="s">
         <v>2262</v>
       </c>
       <c r="B1128" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1128" s="4" t="s">
+      <c r="C1128" s="9" t="s">
         <v>2263</v>
       </c>
       <c r="D1128" s="14"/>
     </row>
     <row r="1129" ht="22.5" customHeight="1">
-      <c r="A1129" s="4" t="s">
+      <c r="A1129" s="9" t="s">
         <v>2264</v>
       </c>
       <c r="B1129" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1129" s="4" t="s">
+      <c r="C1129" s="9" t="s">
         <v>2265</v>
       </c>
       <c r="D1129" s="14"/>
     </row>
     <row r="1130" ht="22.5" customHeight="1">
-      <c r="A1130" s="9" t="s">
+      <c r="A1130" s="4" t="s">
         <v>2266</v>
       </c>
       <c r="B1130" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1130" s="9" t="s">
+      <c r="C1130" s="4" t="s">
         <v>2267</v>
       </c>
       <c r="D1130" s="14"/>
@@ -23323,25 +23335,25 @@
       <c r="D1132" s="14"/>
     </row>
     <row r="1133" ht="22.5" customHeight="1">
-      <c r="A1133" s="9" t="s">
+      <c r="A1133" s="4" t="s">
         <v>2272</v>
       </c>
       <c r="B1133" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1133" s="9" t="s">
+      <c r="C1133" s="4" t="s">
         <v>2273</v>
       </c>
       <c r="D1133" s="14"/>
     </row>
     <row r="1134" ht="22.5" customHeight="1">
-      <c r="A1134" s="4" t="s">
+      <c r="A1134" s="9" t="s">
         <v>2274</v>
       </c>
       <c r="B1134" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1134" s="4" t="s">
+      <c r="C1134" s="9" t="s">
         <v>2275</v>
       </c>
       <c r="D1134" s="14"/>
@@ -23375,7 +23387,7 @@
         <v>2280</v>
       </c>
       <c r="B1137" s="10" t="s">
-        <v>210</v>
+        <v>94</v>
       </c>
       <c r="C1137" s="9" t="s">
         <v>2281</v>
@@ -23386,8 +23398,8 @@
       <c r="A1138" s="4" t="s">
         <v>2282</v>
       </c>
-      <c r="B1138" s="7" t="s">
-        <v>69</v>
+      <c r="B1138" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="C1138" s="4" t="s">
         <v>2283</v>
@@ -23395,13 +23407,13 @@
       <c r="D1138" s="14"/>
     </row>
     <row r="1139" ht="22.5" customHeight="1">
-      <c r="A1139" s="4" t="s">
+      <c r="A1139" s="9" t="s">
         <v>2284</v>
       </c>
-      <c r="B1139" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1139" s="4" t="s">
+      <c r="B1139" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1139" s="9" t="s">
         <v>2285</v>
       </c>
       <c r="D1139" s="14"/>
@@ -23410,7 +23422,7 @@
       <c r="A1140" s="4" t="s">
         <v>2286</v>
       </c>
-      <c r="B1140" s="5" t="s">
+      <c r="B1140" s="7" t="s">
         <v>69</v>
       </c>
       <c r="C1140" s="4" t="s">
@@ -23419,13 +23431,13 @@
       <c r="D1140" s="14"/>
     </row>
     <row r="1141" ht="22.5" customHeight="1">
-      <c r="A1141" s="9" t="s">
+      <c r="A1141" s="4" t="s">
         <v>2288</v>
       </c>
-      <c r="B1141" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1141" s="9" t="s">
+      <c r="B1141" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1141" s="4" t="s">
         <v>2289</v>
       </c>
       <c r="D1141" s="14"/>
@@ -23435,7 +23447,7 @@
         <v>2290</v>
       </c>
       <c r="B1142" s="5" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="C1142" s="4" t="s">
         <v>2291</v>
@@ -23443,25 +23455,25 @@
       <c r="D1142" s="14"/>
     </row>
     <row r="1143" ht="22.5" customHeight="1">
-      <c r="A1143" s="4" t="s">
+      <c r="A1143" s="9" t="s">
         <v>2292</v>
       </c>
       <c r="B1143" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1143" s="4" t="s">
+      <c r="C1143" s="9" t="s">
         <v>2293</v>
       </c>
       <c r="D1143" s="14"/>
     </row>
     <row r="1144" ht="22.5" customHeight="1">
-      <c r="A1144" s="9" t="s">
+      <c r="A1144" s="4" t="s">
         <v>2294</v>
       </c>
-      <c r="B1144" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1144" s="9" t="s">
+      <c r="B1144" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1144" s="4" t="s">
         <v>2295</v>
       </c>
       <c r="D1144" s="14"/>
@@ -23470,7 +23482,7 @@
       <c r="A1145" s="4" t="s">
         <v>2296</v>
       </c>
-      <c r="B1145" s="7" t="s">
+      <c r="B1145" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C1145" s="4" t="s">
@@ -23479,13 +23491,13 @@
       <c r="D1145" s="14"/>
     </row>
     <row r="1146" ht="22.5" customHeight="1">
-      <c r="A1146" s="4" t="s">
+      <c r="A1146" s="9" t="s">
         <v>2298</v>
       </c>
       <c r="B1146" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1146" s="4" t="s">
+      <c r="C1146" s="9" t="s">
         <v>2299</v>
       </c>
       <c r="D1146" s="14"/>
@@ -23494,7 +23506,7 @@
       <c r="A1147" s="4" t="s">
         <v>2300</v>
       </c>
-      <c r="B1147" s="10" t="s">
+      <c r="B1147" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C1147" s="4" t="s">
@@ -23503,25 +23515,25 @@
       <c r="D1147" s="14"/>
     </row>
     <row r="1148" ht="22.5" customHeight="1">
-      <c r="A1148" s="9" t="s">
+      <c r="A1148" s="4" t="s">
         <v>2302</v>
       </c>
       <c r="B1148" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1148" s="9" t="s">
+      <c r="C1148" s="4" t="s">
         <v>2303</v>
       </c>
       <c r="D1148" s="14"/>
     </row>
     <row r="1149" ht="22.5" customHeight="1">
-      <c r="A1149" s="9" t="s">
+      <c r="A1149" s="4" t="s">
         <v>2304</v>
       </c>
       <c r="B1149" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1149" s="9" t="s">
+      <c r="C1149" s="4" t="s">
         <v>2305</v>
       </c>
       <c r="D1149" s="14"/>
@@ -23539,13 +23551,13 @@
       <c r="D1150" s="14"/>
     </row>
     <row r="1151" ht="22.5" customHeight="1">
-      <c r="A1151" s="4" t="s">
+      <c r="A1151" s="9" t="s">
         <v>2308</v>
       </c>
       <c r="B1151" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1151" s="4" t="s">
+      <c r="C1151" s="9" t="s">
         <v>2309</v>
       </c>
       <c r="D1151" s="14"/>
@@ -23554,7 +23566,7 @@
       <c r="A1152" s="9" t="s">
         <v>2310</v>
       </c>
-      <c r="B1152" s="5" t="s">
+      <c r="B1152" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C1152" s="9" t="s">
@@ -23563,37 +23575,37 @@
       <c r="D1152" s="14"/>
     </row>
     <row r="1153" ht="22.5" customHeight="1">
-      <c r="A1153" s="9" t="s">
+      <c r="A1153" s="4" t="s">
         <v>2312</v>
       </c>
       <c r="B1153" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1153" s="9" t="s">
+      <c r="C1153" s="4" t="s">
         <v>2313</v>
       </c>
       <c r="D1153" s="14"/>
     </row>
     <row r="1154" ht="22.5" customHeight="1">
-      <c r="A1154" s="4" t="s">
+      <c r="A1154" s="9" t="s">
         <v>2314</v>
       </c>
-      <c r="B1154" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1154" s="4" t="s">
+      <c r="B1154" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1154" s="9" t="s">
         <v>2315</v>
       </c>
       <c r="D1154" s="14"/>
     </row>
     <row r="1155" ht="22.5" customHeight="1">
-      <c r="A1155" s="4" t="s">
+      <c r="A1155" s="9" t="s">
         <v>2316</v>
       </c>
-      <c r="B1155" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1155" s="4" t="s">
+      <c r="B1155" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1155" s="9" t="s">
         <v>2317</v>
       </c>
       <c r="D1155" s="14"/>
@@ -23602,8 +23614,8 @@
       <c r="A1156" s="4" t="s">
         <v>2318</v>
       </c>
-      <c r="B1156" s="10" t="s">
-        <v>4</v>
+      <c r="B1156" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C1156" s="4" t="s">
         <v>2319</v>
@@ -23614,7 +23626,7 @@
       <c r="A1157" s="4" t="s">
         <v>2320</v>
       </c>
-      <c r="B1157" s="10" t="s">
+      <c r="B1157" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C1157" s="4" t="s">
@@ -23623,49 +23635,49 @@
       <c r="D1157" s="14"/>
     </row>
     <row r="1158" ht="22.5" customHeight="1">
-      <c r="A1158" s="9" t="s">
+      <c r="A1158" s="4" t="s">
         <v>2322</v>
       </c>
-      <c r="B1158" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1158" s="9" t="s">
+      <c r="B1158" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1158" s="4" t="s">
         <v>2323</v>
       </c>
       <c r="D1158" s="14"/>
     </row>
     <row r="1159" ht="22.5" customHeight="1">
-      <c r="A1159" s="9" t="s">
+      <c r="A1159" s="4" t="s">
         <v>2324</v>
       </c>
       <c r="B1159" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1159" s="4" t="s">
+        <v>2325</v>
+      </c>
+      <c r="D1159" s="14"/>
+    </row>
+    <row r="1160" ht="22.5" customHeight="1">
+      <c r="A1160" s="9" t="s">
+        <v>2326</v>
+      </c>
+      <c r="B1160" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1160" s="9" t="s">
+        <v>2327</v>
+      </c>
+      <c r="D1160" s="14"/>
+    </row>
+    <row r="1161" ht="22.5" customHeight="1">
+      <c r="A1161" s="9" t="s">
+        <v>2328</v>
+      </c>
+      <c r="B1161" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="C1159" s="9" t="s">
-        <v>2325</v>
-      </c>
-      <c r="D1159" s="14"/>
-    </row>
-    <row r="1160" ht="22.5" customHeight="1">
-      <c r="A1160" s="4" t="s">
-        <v>2326</v>
-      </c>
-      <c r="B1160" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1160" s="4" t="s">
-        <v>2327</v>
-      </c>
-      <c r="D1160" s="14"/>
-    </row>
-    <row r="1161" ht="22.5" customHeight="1">
-      <c r="A1161" s="4" t="s">
-        <v>2328</v>
-      </c>
-      <c r="B1161" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1161" s="4" t="s">
+      <c r="C1161" s="9" t="s">
         <v>2329</v>
       </c>
       <c r="D1161" s="14"/>
@@ -23674,34 +23686,34 @@
       <c r="A1162" s="4" t="s">
         <v>2330</v>
       </c>
-      <c r="B1162" s="10" t="s">
-        <v>4</v>
+      <c r="B1162" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C1162" s="4" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="D1162" s="14"/>
     </row>
     <row r="1163" ht="22.5" customHeight="1">
       <c r="A1163" s="4" t="s">
-        <v>2331</v>
-      </c>
-      <c r="B1163" s="7" t="s">
-        <v>61</v>
+        <v>2332</v>
+      </c>
+      <c r="B1163" s="10" t="s">
+        <v>46</v>
       </c>
       <c r="C1163" s="4" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="D1163" s="14"/>
     </row>
     <row r="1164" ht="22.5" customHeight="1">
-      <c r="A1164" s="9" t="s">
-        <v>2333</v>
+      <c r="A1164" s="4" t="s">
+        <v>2334</v>
       </c>
       <c r="B1164" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="C1164" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1164" s="4" t="s">
         <v>2334</v>
       </c>
       <c r="D1164" s="14"/>
@@ -23710,7 +23722,7 @@
       <c r="A1165" s="4" t="s">
         <v>2335</v>
       </c>
-      <c r="B1165" s="10" t="s">
+      <c r="B1165" s="7" t="s">
         <v>61</v>
       </c>
       <c r="C1165" s="4" t="s">
@@ -23722,7 +23734,7 @@
       <c r="A1166" s="9" t="s">
         <v>2337</v>
       </c>
-      <c r="B1166" s="7" t="s">
+      <c r="B1166" s="10" t="s">
         <v>210</v>
       </c>
       <c r="C1166" s="9" t="s">
@@ -23735,7 +23747,7 @@
         <v>2339</v>
       </c>
       <c r="B1167" s="10" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C1167" s="4" t="s">
         <v>2340</v>
@@ -23743,13 +23755,13 @@
       <c r="D1167" s="14"/>
     </row>
     <row r="1168" ht="22.5" customHeight="1">
-      <c r="A1168" s="4" t="s">
+      <c r="A1168" s="9" t="s">
         <v>2341</v>
       </c>
-      <c r="B1168" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1168" s="4" t="s">
+      <c r="B1168" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1168" s="9" t="s">
         <v>2342</v>
       </c>
       <c r="D1168" s="14"/>
@@ -23767,13 +23779,13 @@
       <c r="D1169" s="14"/>
     </row>
     <row r="1170" ht="22.5" customHeight="1">
-      <c r="A1170" s="9" t="s">
+      <c r="A1170" s="4" t="s">
         <v>2345</v>
       </c>
-      <c r="B1170" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1170" s="9" t="s">
+      <c r="B1170" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1170" s="4" t="s">
         <v>2346</v>
       </c>
       <c r="D1170" s="14"/>
@@ -23794,8 +23806,8 @@
       <c r="A1172" s="9" t="s">
         <v>2349</v>
       </c>
-      <c r="B1172" s="7" t="s">
-        <v>69</v>
+      <c r="B1172" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C1172" s="9" t="s">
         <v>2350</v>
@@ -23803,13 +23815,13 @@
       <c r="D1172" s="14"/>
     </row>
     <row r="1173" ht="22.5" customHeight="1">
-      <c r="A1173" s="9" t="s">
+      <c r="A1173" s="4" t="s">
         <v>2351</v>
       </c>
       <c r="B1173" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1173" s="9" t="s">
+      <c r="C1173" s="4" t="s">
         <v>2352</v>
       </c>
       <c r="D1173" s="14"/>
@@ -23818,8 +23830,8 @@
       <c r="A1174" s="9" t="s">
         <v>2353</v>
       </c>
-      <c r="B1174" s="10" t="s">
-        <v>4</v>
+      <c r="B1174" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="C1174" s="9" t="s">
         <v>2354</v>
@@ -23827,25 +23839,25 @@
       <c r="D1174" s="14"/>
     </row>
     <row r="1175" ht="22.5" customHeight="1">
-      <c r="A1175" s="4" t="s">
+      <c r="A1175" s="9" t="s">
         <v>2355</v>
       </c>
-      <c r="B1175" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1175" s="4" t="s">
+      <c r="B1175" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1175" s="9" t="s">
         <v>2356</v>
       </c>
       <c r="D1175" s="14"/>
     </row>
     <row r="1176" ht="22.5" customHeight="1">
-      <c r="A1176" s="4" t="s">
+      <c r="A1176" s="9" t="s">
         <v>2357</v>
       </c>
       <c r="B1176" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1176" s="4" t="s">
+      <c r="C1176" s="9" t="s">
         <v>2358</v>
       </c>
       <c r="D1176" s="14"/>
@@ -23866,8 +23878,8 @@
       <c r="A1178" s="4" t="s">
         <v>2361</v>
       </c>
-      <c r="B1178" s="7" t="s">
-        <v>61</v>
+      <c r="B1178" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C1178" s="4" t="s">
         <v>2362</v>
@@ -23875,13 +23887,13 @@
       <c r="D1178" s="14"/>
     </row>
     <row r="1179" ht="22.5" customHeight="1">
-      <c r="A1179" s="9" t="s">
+      <c r="A1179" s="4" t="s">
         <v>2363</v>
       </c>
-      <c r="B1179" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1179" s="9" t="s">
+      <c r="B1179" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1179" s="4" t="s">
         <v>2364</v>
       </c>
       <c r="D1179" s="14"/>
@@ -23891,7 +23903,7 @@
         <v>2365</v>
       </c>
       <c r="B1180" s="19" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C1180" s="20" t="s">
         <v>2366</v>
@@ -23914,22 +23926,22 @@
       <c r="A1182" s="4" t="s">
         <v>2369</v>
       </c>
-      <c r="B1182" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1182" s="9" t="s">
+      <c r="B1182" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1182" s="4" t="s">
         <v>2370</v>
       </c>
       <c r="D1182" s="14"/>
     </row>
     <row r="1183" ht="22.5" customHeight="1">
-      <c r="A1183" s="4" t="s">
+      <c r="A1183" s="9" t="s">
         <v>2371</v>
       </c>
-      <c r="B1183" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1183" s="4" t="s">
+      <c r="B1183" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1183" s="9" t="s">
         <v>2372</v>
       </c>
       <c r="D1183" s="14"/>
@@ -23938,20 +23950,20 @@
       <c r="A1184" s="4" t="s">
         <v>2373</v>
       </c>
-      <c r="B1184" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1184" s="4" t="s">
+      <c r="B1184" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1184" s="9" t="s">
         <v>2374</v>
       </c>
       <c r="D1184" s="14"/>
     </row>
     <row r="1185" ht="22.5" customHeight="1">
-      <c r="A1185" s="9" t="s">
+      <c r="A1185" s="4" t="s">
         <v>2375</v>
       </c>
-      <c r="B1185" s="5" t="s">
-        <v>4</v>
+      <c r="B1185" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C1185" s="4" t="s">
         <v>2376</v>
@@ -23962,7 +23974,7 @@
       <c r="A1186" s="4" t="s">
         <v>2377</v>
       </c>
-      <c r="B1186" s="10" t="s">
+      <c r="B1186" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C1186" s="4" t="s">
@@ -23971,10 +23983,10 @@
       <c r="D1186" s="14"/>
     </row>
     <row r="1187" ht="22.5" customHeight="1">
-      <c r="A1187" s="4" t="s">
+      <c r="A1187" s="9" t="s">
         <v>2379</v>
       </c>
-      <c r="B1187" s="10" t="s">
+      <c r="B1187" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C1187" s="4" t="s">
@@ -23983,49 +23995,49 @@
       <c r="D1187" s="14"/>
     </row>
     <row r="1188" ht="22.5" customHeight="1">
-      <c r="A1188" s="9" t="s">
+      <c r="A1188" s="4" t="s">
         <v>2381</v>
       </c>
       <c r="B1188" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1188" s="9" t="s">
+      <c r="C1188" s="4" t="s">
         <v>2382</v>
       </c>
       <c r="D1188" s="14"/>
     </row>
     <row r="1189" ht="22.5" customHeight="1">
-      <c r="A1189" s="9" t="s">
+      <c r="A1189" s="4" t="s">
         <v>2383</v>
       </c>
       <c r="B1189" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1189" s="9" t="s">
+      <c r="C1189" s="4" t="s">
         <v>2384</v>
       </c>
       <c r="D1189" s="14"/>
     </row>
     <row r="1190" ht="22.5" customHeight="1">
-      <c r="A1190" s="4" t="s">
+      <c r="A1190" s="9" t="s">
         <v>2385</v>
       </c>
       <c r="B1190" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1190" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1190" s="9" t="s">
         <v>2386</v>
       </c>
       <c r="D1190" s="14"/>
     </row>
     <row r="1191" ht="22.5" customHeight="1">
-      <c r="A1191" s="4" t="s">
+      <c r="A1191" s="9" t="s">
         <v>2387</v>
       </c>
       <c r="B1191" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1191" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1191" s="9" t="s">
         <v>2388</v>
       </c>
       <c r="D1191" s="14"/>
@@ -24035,7 +24047,7 @@
         <v>2389</v>
       </c>
       <c r="B1192" s="10" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C1192" s="4" t="s">
         <v>2390</v>
@@ -24043,97 +24055,97 @@
       <c r="D1192" s="14"/>
     </row>
     <row r="1193" ht="22.5" customHeight="1">
-      <c r="A1193" s="9" t="s">
+      <c r="A1193" s="4" t="s">
         <v>2391</v>
       </c>
-      <c r="B1193" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1193" s="9" t="s">
+      <c r="B1193" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1193" s="4" t="s">
         <v>2392</v>
       </c>
       <c r="D1193" s="14"/>
     </row>
     <row r="1194" ht="22.5" customHeight="1">
-      <c r="A1194" s="9" t="s">
+      <c r="A1194" s="4" t="s">
         <v>2393</v>
       </c>
-      <c r="B1194" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1194" s="9" t="s">
+      <c r="B1194" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1194" s="4" t="s">
         <v>2394</v>
       </c>
       <c r="D1194" s="14"/>
     </row>
     <row r="1195" ht="22.5" customHeight="1">
-      <c r="A1195" s="4" t="s">
+      <c r="A1195" s="9" t="s">
         <v>2395</v>
       </c>
-      <c r="B1195" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1195" s="4" t="s">
+      <c r="B1195" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1195" s="9" t="s">
         <v>2396</v>
       </c>
       <c r="D1195" s="14"/>
     </row>
     <row r="1196" ht="22.5" customHeight="1">
-      <c r="A1196" s="4" t="s">
+      <c r="A1196" s="9" t="s">
         <v>2397</v>
       </c>
-      <c r="B1196" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1196" s="4" t="s">
+      <c r="B1196" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1196" s="9" t="s">
         <v>2398</v>
       </c>
       <c r="D1196" s="14"/>
     </row>
     <row r="1197" ht="22.5" customHeight="1">
-      <c r="A1197" s="9" t="s">
+      <c r="A1197" s="4" t="s">
         <v>2399</v>
       </c>
-      <c r="B1197" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1197" s="9" t="s">
+      <c r="B1197" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1197" s="4" t="s">
         <v>2400</v>
       </c>
       <c r="D1197" s="14"/>
     </row>
     <row r="1198" ht="22.5" customHeight="1">
-      <c r="A1198" s="9" t="s">
+      <c r="A1198" s="4" t="s">
         <v>2401</v>
       </c>
-      <c r="B1198" s="7" t="s">
+      <c r="B1198" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1198" s="4" t="s">
+        <v>2402</v>
+      </c>
+      <c r="D1198" s="14"/>
+    </row>
+    <row r="1199" ht="22.5" customHeight="1">
+      <c r="A1199" s="9" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B1199" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1199" s="9" t="s">
+        <v>2404</v>
+      </c>
+      <c r="D1199" s="14"/>
+    </row>
+    <row r="1200" ht="22.5" customHeight="1">
+      <c r="A1200" s="9" t="s">
+        <v>2405</v>
+      </c>
+      <c r="B1200" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C1198" s="9" t="s">
-        <v>2402</v>
-      </c>
-      <c r="D1198" s="14"/>
-    </row>
-    <row r="1199" ht="22.5" customHeight="1">
-      <c r="A1199" s="4" t="s">
-        <v>2403</v>
-      </c>
-      <c r="B1199" s="10" t="s">
-        <v>796</v>
-      </c>
-      <c r="C1199" s="4" t="s">
-        <v>2404</v>
-      </c>
-      <c r="D1199" s="14"/>
-    </row>
-    <row r="1200" ht="22.5" customHeight="1">
-      <c r="A1200" s="4" t="s">
-        <v>2405</v>
-      </c>
-      <c r="B1200" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1200" s="4" t="s">
+      <c r="C1200" s="9" t="s">
         <v>2406</v>
       </c>
       <c r="D1200" s="14"/>
@@ -24142,8 +24154,8 @@
       <c r="A1201" s="4" t="s">
         <v>2407</v>
       </c>
-      <c r="B1201" s="7" t="s">
-        <v>4</v>
+      <c r="B1201" s="10" t="s">
+        <v>796</v>
       </c>
       <c r="C1201" s="4" t="s">
         <v>2408</v>
@@ -24154,8 +24166,8 @@
       <c r="A1202" s="4" t="s">
         <v>2409</v>
       </c>
-      <c r="B1202" s="7" t="s">
-        <v>61</v>
+      <c r="B1202" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C1202" s="4" t="s">
         <v>2410</v>
@@ -24167,7 +24179,7 @@
         <v>2411</v>
       </c>
       <c r="B1203" s="7" t="s">
-        <v>796</v>
+        <v>4</v>
       </c>
       <c r="C1203" s="4" t="s">
         <v>2412</v>
@@ -24179,7 +24191,7 @@
         <v>2413</v>
       </c>
       <c r="B1204" s="7" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="C1204" s="4" t="s">
         <v>2414</v>
@@ -24187,13 +24199,13 @@
       <c r="D1204" s="14"/>
     </row>
     <row r="1205" ht="22.5" customHeight="1">
-      <c r="A1205" s="9" t="s">
+      <c r="A1205" s="4" t="s">
         <v>2415</v>
       </c>
-      <c r="B1205" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1205" s="9" t="s">
+      <c r="B1205" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="C1205" s="4" t="s">
         <v>2416</v>
       </c>
       <c r="D1205" s="14"/>
@@ -24211,13 +24223,13 @@
       <c r="D1206" s="14"/>
     </row>
     <row r="1207" ht="22.5" customHeight="1">
-      <c r="A1207" s="4" t="s">
+      <c r="A1207" s="9" t="s">
         <v>2419</v>
       </c>
-      <c r="B1207" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C1207" s="4" t="s">
+      <c r="B1207" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1207" s="9" t="s">
         <v>2420</v>
       </c>
       <c r="D1207" s="14"/>
@@ -24226,7 +24238,7 @@
       <c r="A1208" s="4" t="s">
         <v>2421</v>
       </c>
-      <c r="B1208" s="10" t="s">
+      <c r="B1208" s="7" t="s">
         <v>107</v>
       </c>
       <c r="C1208" s="4" t="s">
@@ -24247,25 +24259,25 @@
       <c r="D1209" s="14"/>
     </row>
     <row r="1210" ht="22.5" customHeight="1">
-      <c r="A1210" s="9" t="s">
+      <c r="A1210" s="4" t="s">
         <v>2425</v>
       </c>
       <c r="B1210" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1210" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1210" s="4" t="s">
         <v>2426</v>
       </c>
       <c r="D1210" s="14"/>
     </row>
     <row r="1211" ht="22.5" customHeight="1">
-      <c r="A1211" s="9" t="s">
+      <c r="A1211" s="4" t="s">
         <v>2427</v>
       </c>
-      <c r="B1211" s="10" t="s">
+      <c r="B1211" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C1211" s="9" t="s">
+      <c r="C1211" s="4" t="s">
         <v>2428</v>
       </c>
       <c r="D1211" s="14"/>
@@ -24275,7 +24287,7 @@
         <v>2429</v>
       </c>
       <c r="B1212" s="10" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="C1212" s="9" t="s">
         <v>2430</v>
@@ -24283,25 +24295,25 @@
       <c r="D1212" s="14"/>
     </row>
     <row r="1213" ht="22.5" customHeight="1">
-      <c r="A1213" s="4" t="s">
+      <c r="A1213" s="9" t="s">
         <v>2431</v>
       </c>
-      <c r="B1213" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1213" s="4" t="s">
+      <c r="B1213" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1213" s="9" t="s">
         <v>2432</v>
       </c>
       <c r="D1213" s="14"/>
     </row>
     <row r="1214" ht="22.5" customHeight="1">
-      <c r="A1214" s="4" t="s">
+      <c r="A1214" s="9" t="s">
         <v>2433</v>
       </c>
       <c r="B1214" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1214" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1214" s="9" t="s">
         <v>2434</v>
       </c>
       <c r="D1214" s="14"/>
@@ -24310,8 +24322,8 @@
       <c r="A1215" s="4" t="s">
         <v>2435</v>
       </c>
-      <c r="B1215" s="10" t="s">
-        <v>4</v>
+      <c r="B1215" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C1215" s="4" t="s">
         <v>2436</v>
@@ -24319,13 +24331,13 @@
       <c r="D1215" s="14"/>
     </row>
     <row r="1216" ht="22.5" customHeight="1">
-      <c r="A1216" s="9" t="s">
+      <c r="A1216" s="4" t="s">
         <v>2437</v>
       </c>
-      <c r="B1216" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1216" s="9" t="s">
+      <c r="B1216" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1216" s="4" t="s">
         <v>2438</v>
       </c>
       <c r="D1216" s="14"/>
@@ -24343,13 +24355,13 @@
       <c r="D1217" s="14"/>
     </row>
     <row r="1218" ht="22.5" customHeight="1">
-      <c r="A1218" s="4" t="s">
+      <c r="A1218" s="9" t="s">
         <v>2441</v>
       </c>
-      <c r="B1218" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1218" s="4" t="s">
+      <c r="B1218" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1218" s="9" t="s">
         <v>2442</v>
       </c>
       <c r="D1218" s="14"/>
@@ -24367,13 +24379,13 @@
       <c r="D1219" s="14"/>
     </row>
     <row r="1220" ht="22.5" customHeight="1">
-      <c r="A1220" s="9" t="s">
+      <c r="A1220" s="4" t="s">
         <v>2445</v>
       </c>
       <c r="B1220" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1220" s="9" t="s">
+      <c r="C1220" s="4" t="s">
         <v>2446</v>
       </c>
       <c r="D1220" s="14"/>
@@ -24391,73 +24403,73 @@
       <c r="D1221" s="14"/>
     </row>
     <row r="1222" ht="22.5" customHeight="1">
-      <c r="A1222" s="4" t="s">
+      <c r="A1222" s="9" t="s">
         <v>2449</v>
       </c>
       <c r="B1222" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1222" s="4" t="s">
+      <c r="C1222" s="9" t="s">
         <v>2450</v>
       </c>
       <c r="D1222" s="14"/>
     </row>
     <row r="1223" ht="22.5" customHeight="1">
-      <c r="A1223" s="9" t="s">
+      <c r="A1223" s="4" t="s">
         <v>2451</v>
       </c>
       <c r="B1223" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1223" s="9" t="s">
+      <c r="C1223" s="4" t="s">
         <v>2452</v>
       </c>
       <c r="D1223" s="14"/>
     </row>
     <row r="1224" ht="22.5" customHeight="1">
-      <c r="A1224" s="9" t="s">
+      <c r="A1224" s="4" t="s">
         <v>2453</v>
       </c>
       <c r="B1224" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1224" s="9" t="s">
+      <c r="C1224" s="4" t="s">
         <v>2454</v>
       </c>
       <c r="D1224" s="14"/>
     </row>
     <row r="1225" ht="22.5" customHeight="1">
-      <c r="A1225" s="4" t="s">
+      <c r="A1225" s="9" t="s">
         <v>2455</v>
       </c>
-      <c r="B1225" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1225" s="4" t="s">
+      <c r="B1225" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1225" s="9" t="s">
         <v>2456</v>
       </c>
       <c r="D1225" s="14"/>
     </row>
     <row r="1226" ht="22.5" customHeight="1">
-      <c r="A1226" s="4" t="s">
+      <c r="A1226" s="9" t="s">
         <v>2457</v>
       </c>
       <c r="B1226" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1226" s="4" t="s">
+      <c r="C1226" s="9" t="s">
         <v>2458</v>
       </c>
       <c r="D1226" s="14"/>
     </row>
     <row r="1227" ht="22.5" customHeight="1">
-      <c r="A1227" s="9" t="s">
+      <c r="A1227" s="4" t="s">
         <v>2459</v>
       </c>
       <c r="B1227" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1227" s="9" t="s">
+      <c r="C1227" s="4" t="s">
         <v>2460</v>
       </c>
       <c r="D1227" s="14"/>
@@ -24475,37 +24487,37 @@
       <c r="D1228" s="14"/>
     </row>
     <row r="1229" ht="22.5" customHeight="1">
-      <c r="A1229" s="4" t="s">
+      <c r="A1229" s="9" t="s">
         <v>2463</v>
       </c>
-      <c r="B1229" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1229" s="4" t="s">
+      <c r="B1229" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1229" s="9" t="s">
         <v>2464</v>
       </c>
       <c r="D1229" s="14"/>
     </row>
     <row r="1230" ht="22.5" customHeight="1">
-      <c r="A1230" s="9" t="s">
+      <c r="A1230" s="4" t="s">
         <v>2465</v>
       </c>
-      <c r="B1230" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1230" s="9" t="s">
+      <c r="B1230" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1230" s="4" t="s">
         <v>2466</v>
       </c>
       <c r="D1230" s="14"/>
     </row>
     <row r="1231" ht="22.5" customHeight="1">
-      <c r="A1231" s="9" t="s">
+      <c r="A1231" s="4" t="s">
         <v>2467</v>
       </c>
       <c r="B1231" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1231" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1231" s="4" t="s">
         <v>2468</v>
       </c>
       <c r="D1231" s="14"/>
@@ -24514,8 +24526,8 @@
       <c r="A1232" s="9" t="s">
         <v>2469</v>
       </c>
-      <c r="B1232" s="10" t="s">
-        <v>46</v>
+      <c r="B1232" s="7" t="s">
+        <v>4</v>
       </c>
       <c r="C1232" s="9" t="s">
         <v>2470</v>
@@ -24523,25 +24535,25 @@
       <c r="D1232" s="14"/>
     </row>
     <row r="1233" ht="22.5" customHeight="1">
-      <c r="A1233" s="4" t="s">
+      <c r="A1233" s="9" t="s">
         <v>2471</v>
       </c>
-      <c r="B1233" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1233" s="4" t="s">
+      <c r="B1233" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1233" s="9" t="s">
         <v>2472</v>
       </c>
       <c r="D1233" s="14"/>
     </row>
     <row r="1234" ht="22.5" customHeight="1">
-      <c r="A1234" s="4" t="s">
+      <c r="A1234" s="9" t="s">
         <v>2473</v>
       </c>
-      <c r="B1234" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1234" s="4" t="s">
+      <c r="B1234" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1234" s="9" t="s">
         <v>2474</v>
       </c>
       <c r="D1234" s="14"/>
@@ -24550,8 +24562,8 @@
       <c r="A1235" s="4" t="s">
         <v>2475</v>
       </c>
-      <c r="B1235" s="7" t="s">
-        <v>579</v>
+      <c r="B1235" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="C1235" s="4" t="s">
         <v>2476</v>
@@ -24562,17 +24574,41 @@
       <c r="A1236" s="4" t="s">
         <v>2477</v>
       </c>
-      <c r="B1236" s="10" t="s">
-        <v>4</v>
+      <c r="B1236" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C1236" s="4" t="s">
         <v>2478</v>
       </c>
       <c r="D1236" s="14"/>
     </row>
+    <row r="1237" ht="22.5" customHeight="1">
+      <c r="A1237" s="4" t="s">
+        <v>2479</v>
+      </c>
+      <c r="B1237" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="C1237" s="4" t="s">
+        <v>2480</v>
+      </c>
+      <c r="D1237" s="14"/>
+    </row>
+    <row r="1238" ht="22.5" customHeight="1">
+      <c r="A1238" s="4" t="s">
+        <v>2481</v>
+      </c>
+      <c r="B1238" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1238" s="4" t="s">
+        <v>2482</v>
+      </c>
+      <c r="D1238" s="14"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B1236">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B1238">
       <formula1>"adjective,adverb,adverb-preposition,conjunction,noun,numeral,phrase,preposition,pronoun,verb,interjection,prefix,suffix,article"</formula1>
     </dataValidation>
   </dataValidations>
@@ -24595,58 +24631,58 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="21" t="s">
-        <v>2479</v>
+        <v>2483</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>1790</v>
+        <v>1794</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="22" t="s">
-        <v>2480</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="23" t="s">
-        <v>2481</v>
+        <v>2485</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>2482</v>
+        <v>2486</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="24" t="s">
-        <v>2483</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="23" t="s">
-        <v>2484</v>
+        <v>2488</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>2485</v>
+        <v>2489</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="24" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="23" t="s">
-        <v>2487</v>
+        <v>2491</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>2488</v>
+        <v>2492</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="24" t="s">
-        <v>2489</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>2490</v>
+        <v>2494</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="25"/>
@@ -24655,13 +24691,13 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="21" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>2493</v>
+        <v>2497</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="25"/>
@@ -24670,13 +24706,13 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="21" t="s">
-        <v>2494</v>
+        <v>2498</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>2495</v>
+        <v>2499</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>2496</v>
+        <v>2500</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="25"/>
@@ -24685,13 +24721,13 @@
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="21" t="s">
-        <v>2497</v>
+        <v>2501</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>2498</v>
+        <v>2502</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>2499</v>
+        <v>2503</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="25"/>
@@ -24700,13 +24736,13 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="21" t="s">
-        <v>2500</v>
+        <v>2504</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="25"/>
@@ -24715,11 +24751,11 @@
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="21" t="s">
-        <v>2503</v>
+        <v>2507</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="24" t="s">
-        <v>2504</v>
+        <v>2508</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="25"/>
@@ -24728,10 +24764,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="21" t="s">
-        <v>2505</v>
+        <v>2509</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>2506</v>
+        <v>2510</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="25"/>
@@ -24749,10 +24785,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="21" t="s">
-        <v>2507</v>
+        <v>2511</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>1804</v>
+        <v>1808</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="25"/>
@@ -24761,10 +24797,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="23" t="s">
-        <v>2481</v>
+        <v>2485</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>1804</v>
+        <v>1808</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="25"/>
@@ -24773,10 +24809,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="23" t="s">
-        <v>2484</v>
+        <v>2488</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>2508</v>
+        <v>2512</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="25"/>
@@ -24785,10 +24821,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="23" t="s">
-        <v>2487</v>
+        <v>2491</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>2509</v>
+        <v>2513</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="25"/>
@@ -24797,10 +24833,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="21" t="s">
-        <v>2490</v>
+        <v>2494</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>2510</v>
+        <v>2514</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="25"/>
@@ -24809,13 +24845,13 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="21" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>2493</v>
+        <v>2497</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="D18" s="25"/>
       <c r="E18" s="25"/>
@@ -24824,13 +24860,13 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="21" t="s">
-        <v>2494</v>
+        <v>2498</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>1804</v>
+        <v>1808</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="25"/>
@@ -24839,13 +24875,13 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="21" t="s">
-        <v>2497</v>
+        <v>2501</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>2512</v>
+        <v>2516</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>2513</v>
+        <v>2517</v>
       </c>
       <c r="D20" s="25"/>
       <c r="E20" s="25"/>
@@ -24854,13 +24890,13 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="21" t="s">
-        <v>2500</v>
+        <v>2504</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="D21" s="25"/>
       <c r="E21" s="25"/>
@@ -24869,11 +24905,11 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="21" t="s">
-        <v>2503</v>
+        <v>2507</v>
       </c>
       <c r="B22" s="21"/>
       <c r="C22" s="24" t="s">
-        <v>2514</v>
+        <v>2518</v>
       </c>
       <c r="D22" s="25"/>
       <c r="E22" s="25"/>
@@ -24882,10 +24918,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>2505</v>
+        <v>2509</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>1804</v>
+        <v>1808</v>
       </c>
       <c r="D23" s="25"/>
       <c r="E23" s="25"/>
@@ -24927,86 +24963,86 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="22" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>2516</v>
+        <v>2520</v>
       </c>
       <c r="D1" s="27"/>
       <c r="E1" s="26" t="s">
-        <v>2517</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="B2" s="26" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="D2" s="27"/>
       <c r="E2" s="26" t="s">
-        <v>2518</v>
+        <v>2522</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>2519</v>
+        <v>2523</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="26" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>278</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>2522</v>
+        <v>2526</v>
       </c>
       <c r="D3" s="27"/>
       <c r="E3" s="26" t="s">
-        <v>2523</v>
+        <v>2527</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>2524</v>
+        <v>2528</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>2523</v>
+        <v>2527</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>2524</v>
+        <v>2528</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>2523</v>
+        <v>2527</v>
       </c>
       <c r="J3" s="26" t="s">
-        <v>2524</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="26" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>2526</v>
+        <v>2530</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="27" t="s">
-        <v>2527</v>
+        <v>2531</v>
       </c>
       <c r="F4" s="28" t="s">
         <v>866</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>2528</v>
+        <v>2532</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>2529</v>
+        <v>2533</v>
       </c>
       <c r="J4" s="27" t="s">
         <v>284</v>
@@ -25014,32 +25050,32 @@
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>2531</v>
+        <v>2535</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>2532</v>
+        <v>2536</v>
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="27" t="s">
         <v>76</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>2533</v>
+        <v>2537</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>2534</v>
+        <v>2538</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
@@ -25048,36 +25084,36 @@
       <c r="C6" s="27"/>
       <c r="D6" s="27"/>
       <c r="E6" s="27" t="s">
-        <v>2535</v>
+        <v>2539</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="30"/>
       <c r="I6" s="27" t="s">
-        <v>2536</v>
+        <v>2540</v>
       </c>
       <c r="J6" s="27" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="22" t="s">
-        <v>2537</v>
+        <v>2541</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D7" s="30"/>
       <c r="E7" s="27" t="s">
-        <v>2538</v>
+        <v>2542</v>
       </c>
       <c r="F7" s="28" t="s">
         <v>278</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>2539</v>
+        <v>2543</v>
       </c>
       <c r="J7" s="27" t="s">
         <v>3</v>
@@ -25085,59 +25121,59 @@
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="B8" s="26" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="D8" s="27"/>
       <c r="H8" s="30"/>
       <c r="I8" s="27" t="s">
-        <v>2540</v>
+        <v>2544</v>
       </c>
       <c r="J8" s="27" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="26" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>2541</v>
+        <v>2545</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="22" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>2542</v>
+        <v>2546</v>
       </c>
       <c r="H9" s="30"/>
       <c r="I9" s="27" t="s">
-        <v>2543</v>
+        <v>2547</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>2542</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="26" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="D10" s="30"/>
       <c r="F10" s="26" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="H10" s="30"/>
       <c r="I10" s="27" t="s">
-        <v>2544</v>
+        <v>2548</v>
       </c>
       <c r="J10" s="27" t="s">
         <v>1003</v>
@@ -25145,30 +25181,30 @@
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="26" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>2545</v>
+        <v>2549</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>2546</v>
+        <v>2550</v>
       </c>
       <c r="D11" s="30"/>
       <c r="E11" s="26" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>2542</v>
+        <v>2546</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>2547</v>
+        <v>2551</v>
       </c>
       <c r="H11" s="31"/>
       <c r="I11" s="27" t="s">
-        <v>2548</v>
+        <v>2552</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
@@ -25177,11 +25213,11 @@
       <c r="C12" s="30"/>
       <c r="D12" s="30"/>
       <c r="E12" s="26" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="H12" s="31"/>
       <c r="I12" s="27" t="s">
-        <v>2549</v>
+        <v>2553</v>
       </c>
       <c r="J12" s="27" t="s">
         <v>791</v>
@@ -25189,40 +25225,40 @@
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="22" t="s">
-        <v>2519</v>
+        <v>2523</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>242</v>
       </c>
       <c r="D13" s="30"/>
       <c r="E13" s="26" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>2550</v>
+        <v>2554</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>2551</v>
+        <v>2555</v>
       </c>
       <c r="H13" s="27"/>
       <c r="I13" s="27" t="s">
-        <v>2552</v>
+        <v>2556</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="B14" s="26" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="D14" s="30"/>
       <c r="H14" s="27"/>
       <c r="I14" s="27" t="s">
-        <v>2553</v>
+        <v>2557</v>
       </c>
       <c r="J14" s="27" t="s">
         <v>274</v>
@@ -25230,23 +25266,23 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="26" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="B15" s="27" t="s">
         <v>242</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>2554</v>
+        <v>2558</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>2555</v>
+        <v>2559</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>2477</v>
+        <v>2481</v>
       </c>
       <c r="H15" s="27"/>
       <c r="I15" s="27" t="s">
-        <v>2556</v>
+        <v>2560</v>
       </c>
       <c r="J15" s="27" t="s">
         <v>1036</v>
@@ -25254,46 +25290,46 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="26" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>2557</v>
+        <v>2561</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>2558</v>
+        <v>2562</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="H16" s="31"/>
       <c r="I16" s="27" t="s">
-        <v>2559</v>
+        <v>2563</v>
       </c>
       <c r="J16" s="27" t="s">
-        <v>2477</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="26" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>2560</v>
+        <v>2564</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>2561</v>
+        <v>2565</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>2477</v>
+        <v>2481</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>2562</v>
+        <v>2566</v>
       </c>
       <c r="H17" s="31"/>
       <c r="I17" s="31"/>
@@ -25301,7 +25337,7 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="E18" s="26" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="H18" s="27"/>
       <c r="I18" s="27"/>
@@ -25313,13 +25349,13 @@
       <c r="C19" s="27"/>
       <c r="D19" s="27"/>
       <c r="E19" s="26" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>2563</v>
+        <v>2567</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>2564</v>
+        <v>2568</v>
       </c>
       <c r="H19" s="27"/>
     </row>
@@ -25335,44 +25371,44 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="26" t="s">
-        <v>2565</v>
+        <v>2569</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="B22" s="26" t="s">
-        <v>2566</v>
+        <v>2570</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>2567</v>
+        <v>2571</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>2568</v>
+        <v>2572</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>2569</v>
+        <v>2573</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>2570</v>
+        <v>2574</v>
       </c>
       <c r="G22" s="26" t="s">
-        <v>2571</v>
+        <v>2575</v>
       </c>
       <c r="H22" s="26" t="s">
-        <v>2572</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="26" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="B23" s="27" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>2573</v>
+        <v>2577</v>
       </c>
       <c r="D23" s="27" t="s">
         <v>35</v>
@@ -25381,10 +25417,10 @@
         <v>29</v>
       </c>
       <c r="F23" s="27" t="s">
-        <v>2574</v>
+        <v>2578</v>
       </c>
       <c r="G23" s="27" t="s">
-        <v>1740</v>
+        <v>1744</v>
       </c>
       <c r="H23" s="27" t="s">
         <v>502</v>
@@ -25392,7 +25428,7 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="26" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="B24" s="27" t="s">
         <v>13</v>
@@ -25409,7 +25445,7 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="26" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="B25" s="27" t="s">
         <v>15</v>
@@ -25424,61 +25460,61 @@
         <v>27</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>2575</v>
+        <v>2579</v>
       </c>
       <c r="G25" s="27" t="s">
-        <v>2576</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="26" t="s">
-        <v>2565</v>
+        <v>2569</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="B27" s="26" t="s">
-        <v>2566</v>
+        <v>2570</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>2567</v>
+        <v>2571</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>2568</v>
+        <v>2572</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>2569</v>
+        <v>2573</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>2570</v>
+        <v>2574</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>2571</v>
+        <v>2575</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>2572</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="26" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="B28" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>2577</v>
+        <v>2581</v>
       </c>
       <c r="D28" s="27" t="s">
         <v>41</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>2578</v>
+        <v>2582</v>
       </c>
       <c r="G28" s="27" t="s">
-        <v>2579</v>
+        <v>2583</v>
       </c>
       <c r="H28" s="27" t="s">
         <v>500</v>
@@ -25486,13 +25522,13 @@
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="26" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="B29" s="27" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>2580</v>
+        <v>2584</v>
       </c>
       <c r="D29" s="27" t="s">
         <v>37</v>
@@ -25500,22 +25536,22 @@
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="26" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="B30" s="27" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>2581</v>
+        <v>2585</v>
       </c>
       <c r="D30" s="27" t="s">
         <v>39</v>
       </c>
       <c r="F30" s="27" t="s">
-        <v>2582</v>
+        <v>2586</v>
       </c>
       <c r="G30" s="27" t="s">
-        <v>2583</v>
+        <v>2587</v>
       </c>
     </row>
   </sheetData>
@@ -25571,10 +25607,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="26" t="s">
-        <v>2584</v>
+        <v>2588</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>2585</v>
+        <v>2589</v>
       </c>
       <c r="E1" s="30"/>
       <c r="F1" s="31"/>
@@ -25605,262 +25641,262 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="26" t="s">
-        <v>2586</v>
+        <v>2590</v>
       </c>
       <c r="E4" s="30"/>
       <c r="F4" s="26" t="s">
-        <v>2587</v>
+        <v>2591</v>
       </c>
       <c r="J4" s="27"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="22" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
       <c r="E5" s="30"/>
       <c r="F5" s="22" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
       <c r="J5" s="27"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="22"/>
       <c r="B6" s="26" t="s">
-        <v>2518</v>
+        <v>2522</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>2519</v>
+        <v>2523</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="E6" s="30"/>
       <c r="F6" s="22"/>
       <c r="G6" s="26" t="s">
-        <v>2518</v>
+        <v>2522</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>2519</v>
+        <v>2523</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="J6" s="27"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="26" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>2588</v>
+        <v>2592</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="26" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>2589</v>
+        <v>2593</v>
       </c>
       <c r="J7" s="27"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="26" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>2590</v>
+        <v>2594</v>
       </c>
       <c r="E8" s="30"/>
       <c r="F8" s="26" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>2589</v>
+        <v>2593</v>
       </c>
       <c r="J8" s="27"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="26" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="26" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="J9" s="27"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="26" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="E10" s="30"/>
       <c r="F10" s="26" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="J10" s="27"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="22"/>
       <c r="B11" s="26" t="s">
-        <v>2518</v>
+        <v>2522</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>2519</v>
+        <v>2523</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="E11" s="30"/>
       <c r="F11" s="22"/>
       <c r="G11" s="26" t="s">
-        <v>2518</v>
+        <v>2522</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>2519</v>
+        <v>2523</v>
       </c>
       <c r="I11" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="J11" s="27"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="26" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>2591</v>
+        <v>2595</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>2590</v>
+        <v>2594</v>
       </c>
       <c r="E12" s="30"/>
       <c r="F12" s="26" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="I12" s="27" t="s">
-        <v>2589</v>
+        <v>2593</v>
       </c>
       <c r="J12" s="27"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="26" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>2593</v>
+        <v>2597</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>2590</v>
+        <v>2594</v>
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="26" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>2589</v>
+        <v>2593</v>
       </c>
       <c r="J13" s="27"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="26" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>2591</v>
+        <v>2595</v>
       </c>
       <c r="E14" s="30"/>
       <c r="F14" s="26" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="J14" s="27"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="26" t="s">
-        <v>2594</v>
+        <v>2598</v>
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="26" t="s">
-        <v>2594</v>
+        <v>2598</v>
       </c>
       <c r="J15" s="27"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="26" t="s">
-        <v>2595</v>
+        <v>2599</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>2596</v>
+        <v>2600</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>2597</v>
+        <v>2601</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="30"/>
       <c r="F16" s="26" t="s">
-        <v>2595</v>
+        <v>2599</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>2598</v>
+        <v>2602</v>
       </c>
       <c r="H16" s="33"/>
       <c r="J16" s="27"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="26" t="s">
-        <v>2599</v>
+        <v>2603</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>2600</v>
+        <v>2604</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>2601</v>
+        <v>2605</v>
       </c>
       <c r="E17" s="30"/>
       <c r="F17" s="26" t="s">
-        <v>2599</v>
+        <v>2603</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>2602</v>
+        <v>2606</v>
       </c>
       <c r="J17" s="27"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="26" t="s">
-        <v>2603</v>
+        <v>2607</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>2604</v>
+        <v>2608</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>2605</v>
+        <v>2609</v>
       </c>
       <c r="E18" s="30"/>
       <c r="F18" s="26" t="s">
-        <v>2603</v>
+        <v>2607</v>
       </c>
       <c r="G18" s="27" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="J18" s="27"/>
     </row>
@@ -25869,54 +25905,54 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="26" t="s">
-        <v>2606</v>
+        <v>2610</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>2607</v>
+        <v>2611</v>
       </c>
       <c r="J20" s="27"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="22" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
       <c r="J21" s="27"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="22"/>
       <c r="B22" s="26" t="s">
-        <v>2518</v>
+        <v>2522</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>2519</v>
+        <v>2523</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="F22" s="22"/>
       <c r="G22" s="26" t="s">
-        <v>2518</v>
+        <v>2522</v>
       </c>
       <c r="H22" s="26" t="s">
-        <v>2519</v>
+        <v>2523</v>
       </c>
       <c r="I22" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="J22" s="27"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="26" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="B23" s="27" t="s">
         <v>793</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="G23" s="27" t="s">
         <v>163</v>
@@ -25925,66 +25961,66 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="26" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="J24" s="27"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="26" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="J25" s="27"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="26" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="E26" s="30"/>
       <c r="F26" s="26" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="J26" s="27"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="22"/>
       <c r="B27" s="26" t="s">
-        <v>2518</v>
+        <v>2522</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>2519</v>
+        <v>2523</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="E27" s="30"/>
       <c r="F27" s="22"/>
       <c r="G27" s="26" t="s">
-        <v>2518</v>
+        <v>2522</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>2519</v>
+        <v>2523</v>
       </c>
       <c r="I27" s="26" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="J27" s="27"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="26" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="B28" s="27" t="s">
         <v>793</v>
       </c>
       <c r="E28" s="30"/>
       <c r="F28" s="26" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="G28" s="27" t="s">
         <v>163</v>
@@ -25993,81 +26029,81 @@
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="26" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="E29" s="30"/>
       <c r="F29" s="26" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="J29" s="27"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="26" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="E30" s="30"/>
       <c r="F30" s="26" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="J30" s="27"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="26" t="s">
-        <v>2594</v>
+        <v>2598</v>
       </c>
       <c r="E31" s="30"/>
       <c r="F31" s="26" t="s">
-        <v>2594</v>
+        <v>2598</v>
       </c>
       <c r="J31" s="27"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="26" t="s">
-        <v>2595</v>
+        <v>2599</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>2608</v>
+        <v>2612</v>
       </c>
       <c r="C32" s="33"/>
       <c r="E32" s="30"/>
       <c r="F32" s="26" t="s">
-        <v>2595</v>
+        <v>2599</v>
       </c>
       <c r="G32" s="27" t="s">
-        <v>2609</v>
+        <v>2613</v>
       </c>
       <c r="H32" s="33"/>
       <c r="J32" s="27"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="26" t="s">
-        <v>2599</v>
+        <v>2603</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>2610</v>
+        <v>2614</v>
       </c>
       <c r="E33" s="30"/>
       <c r="F33" s="26" t="s">
-        <v>2599</v>
+        <v>2603</v>
       </c>
       <c r="G33" s="27" t="s">
-        <v>2611</v>
+        <v>2615</v>
       </c>
       <c r="J33" s="27"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="26" t="s">
-        <v>2603</v>
+        <v>2607</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>2612</v>
+        <v>2616</v>
       </c>
       <c r="E34" s="30"/>
       <c r="F34" s="26" t="s">
-        <v>2603</v>
+        <v>2607</v>
       </c>
       <c r="G34" s="27" t="s">
-        <v>2613</v>
+        <v>2617</v>
       </c>
       <c r="J34" s="27"/>
     </row>
@@ -26085,10 +26121,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="26" t="s">
-        <v>2614</v>
+        <v>2618</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>2615</v>
+        <v>2619</v>
       </c>
       <c r="E36" s="30"/>
       <c r="F36" s="31"/>
@@ -26099,16 +26135,16 @@
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="26" t="s">
-        <v>2616</v>
+        <v>2620</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>2617</v>
+        <v>2621</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>2616</v>
+        <v>2620</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>2618</v>
+        <v>2622</v>
       </c>
       <c r="E37" s="30"/>
       <c r="F37" s="31"/>
@@ -26119,16 +26155,16 @@
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="26" t="s">
-        <v>2595</v>
+        <v>2599</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>2619</v>
+        <v>2623</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>2595</v>
+        <v>2599</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>2620</v>
+        <v>2624</v>
       </c>
       <c r="E38" s="30"/>
       <c r="F38" s="31"/>
@@ -26139,16 +26175,16 @@
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="26" t="s">
-        <v>2599</v>
+        <v>2603</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>2621</v>
+        <v>2625</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>2599</v>
+        <v>2603</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>2622</v>
+        <v>2626</v>
       </c>
       <c r="E39" s="30"/>
       <c r="F39" s="31"/>
@@ -26299,108 +26335,108 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="26" t="s">
-        <v>2623</v>
+        <v>2627</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>2624</v>
+        <v>2628</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>2625</v>
+        <v>2629</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="F1" s="26" t="s">
-        <v>2623</v>
+        <v>2627</v>
       </c>
       <c r="G1" s="26" t="s">
-        <v>2624</v>
+        <v>2628</v>
       </c>
       <c r="H1" s="26" t="s">
-        <v>2625</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>2626</v>
+        <v>2630</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>2627</v>
+        <v>2631</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>2628</v>
+        <v>2632</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>2629</v>
+        <v>2633</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>2630</v>
+        <v>2634</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>2631</v>
+        <v>2635</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>2632</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="27" t="s">
-        <v>2633</v>
+        <v>2637</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>2634</v>
+        <v>2638</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>2635</v>
+        <v>2639</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>2636</v>
+        <v>2640</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>2637</v>
+        <v>2641</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>2638</v>
+        <v>2642</v>
       </c>
       <c r="H3" s="27" t="s">
-        <v>2639</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>2640</v>
+        <v>2644</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>2641</v>
+        <v>2645</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>2642</v>
+        <v>2646</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>2643</v>
+        <v>2647</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>2644</v>
+        <v>2648</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>2645</v>
+        <v>2649</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>2646</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>2647</v>
+        <v>2651</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>2648</v>
+        <v>2652</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>2649</v>
+        <v>2653</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>2650</v>
+        <v>2654</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
@@ -26408,131 +26444,131 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>2651</v>
+        <v>2655</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>2652</v>
+        <v>2656</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>2653</v>
+        <v>2657</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>2654</v>
+        <v>2658</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>2655</v>
+        <v>2659</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>2656</v>
+        <v>2660</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>2657</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>2658</v>
+        <v>2662</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>2659</v>
+        <v>2663</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>2660</v>
+        <v>2664</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>2638</v>
+        <v>2642</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>2661</v>
+        <v>2665</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>2662</v>
+        <v>2666</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>2663</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>2664</v>
+        <v>2668</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>2665</v>
+        <v>2669</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>2666</v>
+        <v>2670</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>2668</v>
+        <v>2672</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>2669</v>
+        <v>2673</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>2670</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>2671</v>
+        <v>2675</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>2672</v>
+        <v>2676</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>2673</v>
+        <v>2677</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>2674</v>
+        <v>2678</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>2675</v>
+        <v>2679</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>2676</v>
+        <v>2680</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>2677</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>2678</v>
+        <v>2682</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>2679</v>
+        <v>2683</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>2680</v>
+        <v>2684</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>2681</v>
+        <v>2685</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>2682</v>
+        <v>2686</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>2683</v>
+        <v>2687</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>2684</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>2685</v>
+        <v>2689</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>2686</v>
+        <v>2690</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>2687</v>
+        <v>2691</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>2688</v>
+        <v>2692</v>
       </c>
       <c r="F11" s="27"/>
       <c r="G11" s="27"/>
@@ -26540,159 +26576,159 @@
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>2689</v>
+        <v>2693</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>2690</v>
+        <v>2694</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>2691</v>
+        <v>2695</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>2692</v>
+        <v>2696</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>2693</v>
+        <v>2697</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>2694</v>
+        <v>2698</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>2695</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>2696</v>
+        <v>2700</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>2697</v>
+        <v>2701</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>2698</v>
+        <v>2702</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>2699</v>
+        <v>2703</v>
       </c>
       <c r="H13" s="27"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>2700</v>
+        <v>2704</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>2701</v>
+        <v>2705</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>2702</v>
+        <v>2706</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>2703</v>
+        <v>2707</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>2704</v>
+        <v>2708</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>2705</v>
+        <v>2709</v>
       </c>
       <c r="H14" s="27" t="s">
-        <v>2706</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>2707</v>
+        <v>2711</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>2708</v>
+        <v>2712</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>2709</v>
+        <v>2713</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>2710</v>
+        <v>2714</v>
       </c>
       <c r="H15" s="27"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>2711</v>
+        <v>2715</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>2712</v>
+        <v>2716</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>2713</v>
+        <v>2717</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>2645</v>
+        <v>2649</v>
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27" t="s">
-        <v>2714</v>
+        <v>2718</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>2715</v>
+        <v>2719</v>
       </c>
       <c r="H16" s="27" t="s">
-        <v>2716</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>2717</v>
+        <v>2721</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>2718</v>
+        <v>2722</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>2719</v>
+        <v>2723</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>2720</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>2721</v>
+        <v>2725</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>2722</v>
+        <v>2726</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>2723</v>
+        <v>2727</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>2724</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>2725</v>
+        <v>2729</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>2726</v>
+        <v>2730</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>2727</v>
+        <v>2731</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>2728</v>
+        <v>2732</v>
       </c>
       <c r="H19" s="27"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>2729</v>
+        <v>2733</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>2730</v>
+        <v>2734</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>2731</v>
+        <v>2735</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>2280</v>
+        <v>2284</v>
       </c>
       <c r="E20" s="27"/>
       <c r="F20" s="27"/>
@@ -26701,16 +26737,16 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>2732</v>
+        <v>2736</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>2733</v>
+        <v>2737</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>2734</v>
+        <v>2738</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>2735</v>
+        <v>2739</v>
       </c>
       <c r="E21" s="27"/>
       <c r="F21" s="27"/>
@@ -26719,16 +26755,16 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>2736</v>
+        <v>2740</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>2737</v>
+        <v>2741</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>2738</v>
+        <v>2742</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>2739</v>
+        <v>2743</v>
       </c>
       <c r="E22" s="27"/>
       <c r="F22" s="27"/>
@@ -26737,16 +26773,16 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="27" t="s">
-        <v>2740</v>
+        <v>2744</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>2741</v>
+        <v>2745</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>2742</v>
+        <v>2746</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>2743</v>
+        <v>2747</v>
       </c>
       <c r="E23" s="27"/>
       <c r="F23" s="27"/>
@@ -26755,16 +26791,16 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>2744</v>
+        <v>2748</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>2745</v>
+        <v>2749</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>2746</v>
+        <v>2750</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>2747</v>
+        <v>2751</v>
       </c>
       <c r="E24" s="27"/>
       <c r="F24" s="27"/>
@@ -26773,16 +26809,16 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>2748</v>
+        <v>2752</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>2749</v>
+        <v>2753</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>2750</v>
+        <v>2754</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>2751</v>
+        <v>2755</v>
       </c>
       <c r="E25" s="27"/>
       <c r="F25" s="27"/>
@@ -26791,16 +26827,16 @@
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>2752</v>
+        <v>2756</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>2753</v>
+        <v>2757</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>2754</v>
+        <v>2758</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>2755</v>
+        <v>2759</v>
       </c>
       <c r="E26" s="27"/>
       <c r="F26" s="27"/>
@@ -26809,16 +26845,16 @@
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="27" t="s">
-        <v>2756</v>
+        <v>2760</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>2757</v>
+        <v>2761</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>2758</v>
+        <v>2762</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>2759</v>
+        <v>2763</v>
       </c>
       <c r="E27" s="27"/>
       <c r="F27" s="27"/>
@@ -26827,16 +26863,16 @@
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="27" t="s">
-        <v>2760</v>
+        <v>2764</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>2761</v>
+        <v>2765</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>2762</v>
+        <v>2766</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>2763</v>
+        <v>2767</v>
       </c>
       <c r="E28" s="27"/>
       <c r="F28" s="27"/>
@@ -26855,63 +26891,63 @@
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="22" t="s">
-        <v>2764</v>
+        <v>2768</v>
       </c>
       <c r="H30" s="27"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="24" t="s">
-        <v>2765</v>
+        <v>2769</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>2766</v>
+        <v>2770</v>
       </c>
       <c r="F31" s="24" t="s">
-        <v>2767</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="24" t="s">
-        <v>2768</v>
+        <v>2772</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>2769</v>
+        <v>2773</v>
       </c>
       <c r="F32" s="24" t="s">
-        <v>2770</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="24" t="s">
-        <v>2771</v>
+        <v>2775</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>2772</v>
+        <v>2776</v>
       </c>
       <c r="F33" s="24" t="s">
-        <v>2773</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="24" t="s">
-        <v>2774</v>
+        <v>2778</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>2775</v>
+        <v>2779</v>
       </c>
       <c r="F34" s="24" t="s">
-        <v>2776</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="24" t="s">
-        <v>2777</v>
+        <v>2781</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>2778</v>
+        <v>2782</v>
       </c>
       <c r="F35" s="24" t="s">
-        <v>2779</v>
+        <v>2783</v>
       </c>
     </row>
   </sheetData>
@@ -26949,175 +26985,175 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="34" t="s">
-        <v>2780</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="35" t="s">
-        <v>2781</v>
+        <v>2785</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>2782</v>
+        <v>2786</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>2783</v>
+        <v>2787</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>2784</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="35" t="s">
-        <v>2785</v>
+        <v>2789</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>2786</v>
+        <v>2790</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>2787</v>
+        <v>2791</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>2788</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="35" t="s">
-        <v>2789</v>
+        <v>2793</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>2790</v>
+        <v>2794</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>2791</v>
+        <v>2795</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>2792</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="35" t="s">
-        <v>2793</v>
+        <v>2797</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>2794</v>
+        <v>2798</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>2795</v>
+        <v>2799</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>2796</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="35" t="s">
-        <v>2797</v>
+        <v>2801</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>2798</v>
+        <v>2802</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>2799</v>
+        <v>2803</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>2800</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="35" t="s">
-        <v>2801</v>
+        <v>2805</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>2802</v>
+        <v>2806</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>2803</v>
+        <v>2807</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>2804</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="35" t="s">
-        <v>2805</v>
+        <v>2809</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>2806</v>
+        <v>2810</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>2807</v>
+        <v>2811</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>2808</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="35" t="s">
-        <v>2809</v>
+        <v>2813</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>2810</v>
+        <v>2814</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>2811</v>
+        <v>2815</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>2812</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="35" t="s">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>2814</v>
+        <v>2818</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>2815</v>
+        <v>2819</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>2808</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="35" t="s">
-        <v>2816</v>
+        <v>2820</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>2817</v>
+        <v>2821</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>2818</v>
+        <v>2822</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>2819</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="35" t="s">
-        <v>2820</v>
+        <v>2824</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>2821</v>
+        <v>2825</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>2822</v>
+        <v>2826</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>2823</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="36" t="s">
-        <v>2824</v>
+        <v>2828</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>2825</v>
+        <v>2829</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>2826</v>
+        <v>2830</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>2827</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
@@ -27134,7 +27170,7 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="36" t="s">
-        <v>2828</v>
+        <v>2832</v>
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="37"/>
@@ -27146,10 +27182,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>2829</v>
+        <v>2833</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>2830</v>
+        <v>2834</v>
       </c>
       <c r="D16" s="27"/>
       <c r="E16" s="37"/>
@@ -27161,10 +27197,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>2831</v>
+        <v>2835</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>2832</v>
+        <v>2836</v>
       </c>
       <c r="D17" s="27"/>
       <c r="E17" s="27"/>
@@ -27176,10 +27212,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>2833</v>
+        <v>2837</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>2834</v>
+        <v>2838</v>
       </c>
       <c r="D18" s="27"/>
       <c r="E18" s="37"/>
@@ -27191,10 +27227,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>2835</v>
+        <v>2839</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>2836</v>
+        <v>2840</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="37"/>
@@ -27206,10 +27242,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>2837</v>
+        <v>2841</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>2838</v>
+        <v>2842</v>
       </c>
       <c r="D20" s="27"/>
       <c r="E20" s="37"/>
@@ -27233,18 +27269,18 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="34" t="s">
-        <v>2839</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="38" t="s">
-        <v>2840</v>
+        <v>2844</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>2841</v>
+        <v>2845</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>2842</v>
+        <v>2846</v>
       </c>
       <c r="J23" s="27"/>
     </row>
@@ -27253,46 +27289,46 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="39" t="s">
-        <v>2843</v>
+        <v>2847</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>2844</v>
+        <v>2848</v>
       </c>
       <c r="G25" s="39" t="s">
-        <v>2845</v>
+        <v>2849</v>
       </c>
       <c r="J25" s="27"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="39" t="s">
-        <v>2846</v>
+        <v>2850</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>2847</v>
+        <v>2851</v>
       </c>
       <c r="G26" s="39" t="s">
-        <v>2848</v>
+        <v>2852</v>
       </c>
       <c r="J26" s="27"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="39" t="s">
-        <v>2849</v>
+        <v>2853</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>2850</v>
+        <v>2854</v>
       </c>
       <c r="G27" s="39" t="s">
-        <v>2851</v>
+        <v>2855</v>
       </c>
       <c r="J27" s="27"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="38" t="s">
-        <v>2852</v>
+        <v>2856</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>2853</v>
+        <v>2857</v>
       </c>
       <c r="G28" s="27"/>
       <c r="H28" s="27"/>

--- a/Conlangs/Kagalarian.xlsx
+++ b/Conlangs/Kagalarian.xlsx
@@ -4325,10 +4325,10 @@
     <t>pattern, design</t>
   </si>
   <si>
-    <t>fyeshon</t>
-  </si>
-  <si>
-    <t>peace, quiet, still, calm</t>
+    <t>fyeshelov</t>
+  </si>
+  <si>
+    <t>peacefulness, calmness, tranquility</t>
   </si>
   <si>
     <t>teysol</t>

--- a/Conlangs/Kagalarian.xlsx
+++ b/Conlangs/Kagalarian.xlsx
@@ -11,14 +11,14 @@
     <sheet state="visible" name="Grammar" sheetId="6" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Kagalarian!$A$1:$C$1380</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Kagalarian!$A$1:$C$1382</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4798" uniqueCount="3186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4804" uniqueCount="3190">
   <si>
     <t>Word</t>
   </si>
@@ -1574,7 +1574,7 @@
     <t>deactivation</t>
   </si>
   <si>
-    <t>pochka</t>
+    <t>pachya</t>
   </si>
   <si>
     <t>dear</t>
@@ -5285,6 +5285,12 @@
     <t>snow</t>
   </si>
   <si>
+    <t>tak</t>
+  </si>
+  <si>
+    <t>so, thus, therefore</t>
+  </si>
+  <si>
     <t>to</t>
   </si>
   <si>
@@ -5513,6 +5519,12 @@
     <t>sticky</t>
   </si>
   <si>
+    <t>iytsa</t>
+  </si>
+  <si>
+    <t>still, idle, unmoving</t>
+  </si>
+  <si>
     <t>grenk</t>
   </si>
   <si>
@@ -6833,7 +6845,7 @@
     <t>horoshat</t>
   </si>
   <si>
-    <t>to make safe; to relieve, to sooth</t>
+    <t>to make safe, to relieve, to sooth</t>
   </si>
   <si>
     <t>somyenat</t>
@@ -10296,7 +10308,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -10364,7 +10376,10 @@
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
@@ -10523,8 +10538,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C1380" displayName="Table1" name="Table1" id="1">
-  <autoFilter ref="$A$1:$C$1380"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C1382" displayName="Table1" name="Table1" id="1">
+  <autoFilter ref="$A$1:$C$1382"/>
   <tableColumns count="3">
     <tableColumn name="Word" id="1"/>
     <tableColumn name="Part of Speech" id="2"/>
@@ -21222,8 +21237,8 @@
       <c r="A876" s="4" t="s">
         <v>1755</v>
       </c>
-      <c r="B876" s="9" t="s">
-        <v>72</v>
+      <c r="B876" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="C876" s="4" t="s">
         <v>1756</v>
@@ -21235,7 +21250,7 @@
         <v>1757</v>
       </c>
       <c r="B877" s="9" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C877" s="4" t="s">
         <v>1758</v>
@@ -21247,7 +21262,7 @@
         <v>1759</v>
       </c>
       <c r="B878" s="9" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C878" s="4" t="s">
         <v>1760</v>
@@ -21255,13 +21270,13 @@
       <c r="D878" s="15"/>
     </row>
     <row r="879" ht="22.5" customHeight="1">
-      <c r="A879" s="10" t="s">
+      <c r="A879" s="4" t="s">
         <v>1761</v>
       </c>
-      <c r="B879" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C879" s="10" t="s">
+      <c r="B879" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C879" s="4" t="s">
         <v>1762</v>
       </c>
       <c r="D879" s="15"/>
@@ -21279,49 +21294,49 @@
       <c r="D880" s="15"/>
     </row>
     <row r="881" ht="22.5" customHeight="1">
-      <c r="A881" s="4" t="s">
+      <c r="A881" s="10" t="s">
         <v>1765</v>
       </c>
       <c r="B881" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C881" s="4" t="s">
+      <c r="C881" s="10" t="s">
         <v>1766</v>
       </c>
       <c r="D881" s="15"/>
     </row>
     <row r="882" ht="22.5" customHeight="1">
-      <c r="A882" s="10" t="s">
+      <c r="A882" s="4" t="s">
         <v>1767</v>
       </c>
       <c r="B882" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C882" s="4" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D882" s="15"/>
+    </row>
+    <row r="883" ht="22.5" customHeight="1">
+      <c r="A883" s="10" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B883" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C882" s="10" t="s">
-        <v>1768</v>
-      </c>
-      <c r="D882" s="15"/>
-    </row>
-    <row r="883" ht="22.5" customHeight="1">
-      <c r="A883" s="4" t="s">
-        <v>1769</v>
-      </c>
-      <c r="B883" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C883" s="4" t="s">
+      <c r="C883" s="10" t="s">
         <v>1770</v>
       </c>
       <c r="D883" s="15"/>
     </row>
     <row r="884" ht="22.5" customHeight="1">
-      <c r="A884" s="10" t="s">
+      <c r="A884" s="4" t="s">
         <v>1771</v>
       </c>
-      <c r="B884" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C884" s="10" t="s">
+      <c r="B884" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C884" s="4" t="s">
         <v>1772</v>
       </c>
       <c r="D884" s="15"/>
@@ -21339,13 +21354,13 @@
       <c r="D885" s="15"/>
     </row>
     <row r="886" ht="22.5" customHeight="1">
-      <c r="A886" s="4" t="s">
+      <c r="A886" s="10" t="s">
         <v>1775</v>
       </c>
       <c r="B886" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C886" s="4" t="s">
+      <c r="C886" s="10" t="s">
         <v>1776</v>
       </c>
       <c r="D886" s="15"/>
@@ -21366,7 +21381,7 @@
       <c r="A888" s="4" t="s">
         <v>1779</v>
       </c>
-      <c r="B888" s="7" t="s">
+      <c r="B888" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C888" s="4" t="s">
@@ -21379,7 +21394,7 @@
         <v>1781</v>
       </c>
       <c r="B889" s="7" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="C889" s="4" t="s">
         <v>1782</v>
@@ -21390,8 +21405,8 @@
       <c r="A890" s="4" t="s">
         <v>1783</v>
       </c>
-      <c r="B890" s="5" t="s">
-        <v>7</v>
+      <c r="B890" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="C890" s="4" t="s">
         <v>1784</v>
@@ -21414,8 +21429,8 @@
       <c r="A892" s="4" t="s">
         <v>1787</v>
       </c>
-      <c r="B892" s="9" t="s">
-        <v>64</v>
+      <c r="B892" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C892" s="4" t="s">
         <v>1788</v>
@@ -21435,13 +21450,13 @@
       <c r="D893" s="15"/>
     </row>
     <row r="894" ht="22.5" customHeight="1">
-      <c r="A894" s="10" t="s">
+      <c r="A894" s="4" t="s">
         <v>1791</v>
       </c>
-      <c r="B894" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C894" s="10" t="s">
+      <c r="B894" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C894" s="4" t="s">
         <v>1792</v>
       </c>
       <c r="D894" s="15"/>
@@ -21459,13 +21474,13 @@
       <c r="D895" s="15"/>
     </row>
     <row r="896" ht="22.5" customHeight="1">
-      <c r="A896" s="4" t="s">
+      <c r="A896" s="10" t="s">
         <v>1795</v>
       </c>
       <c r="B896" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C896" s="4" t="s">
+      <c r="C896" s="10" t="s">
         <v>1796</v>
       </c>
       <c r="D896" s="15"/>
@@ -21495,13 +21510,13 @@
       <c r="D898" s="15"/>
     </row>
     <row r="899" ht="22.5" customHeight="1">
-      <c r="A899" s="10" t="s">
+      <c r="A899" s="4" t="s">
         <v>1801</v>
       </c>
-      <c r="B899" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C899" s="10" t="s">
+      <c r="B899" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C899" s="4" t="s">
         <v>1802</v>
       </c>
       <c r="D899" s="15"/>
@@ -21519,13 +21534,13 @@
       <c r="D900" s="15"/>
     </row>
     <row r="901" ht="22.5" customHeight="1">
-      <c r="A901" s="4" t="s">
+      <c r="A901" s="10" t="s">
         <v>1805</v>
       </c>
-      <c r="B901" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C901" s="4" t="s">
+      <c r="B901" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C901" s="10" t="s">
         <v>1806</v>
       </c>
       <c r="D901" s="15"/>
@@ -21534,8 +21549,8 @@
       <c r="A902" s="4" t="s">
         <v>1807</v>
       </c>
-      <c r="B902" s="9" t="s">
-        <v>64</v>
+      <c r="B902" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C902" s="4" t="s">
         <v>1808</v>
@@ -21546,8 +21561,8 @@
       <c r="A903" s="4" t="s">
         <v>1809</v>
       </c>
-      <c r="B903" s="5" t="s">
-        <v>7</v>
+      <c r="B903" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C903" s="4" t="s">
         <v>1810</v>
@@ -21558,7 +21573,7 @@
       <c r="A904" s="4" t="s">
         <v>1811</v>
       </c>
-      <c r="B904" s="7" t="s">
+      <c r="B904" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C904" s="4" t="s">
@@ -21570,7 +21585,7 @@
       <c r="A905" s="4" t="s">
         <v>1813</v>
       </c>
-      <c r="B905" s="5" t="s">
+      <c r="B905" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C905" s="4" t="s">
@@ -21583,7 +21598,7 @@
         <v>1815</v>
       </c>
       <c r="B906" s="5" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="C906" s="4" t="s">
         <v>1816</v>
@@ -21591,49 +21606,49 @@
       <c r="D906" s="15"/>
     </row>
     <row r="907" ht="22.5" customHeight="1">
-      <c r="A907" s="10" t="s">
+      <c r="A907" s="4" t="s">
         <v>1817</v>
       </c>
-      <c r="B907" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C907" s="10" t="s">
+      <c r="B907" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C907" s="4" t="s">
         <v>1818</v>
       </c>
       <c r="D907" s="15"/>
     </row>
     <row r="908" ht="22.5" customHeight="1">
-      <c r="A908" s="4" t="s">
+      <c r="A908" s="10" t="s">
         <v>1819</v>
       </c>
-      <c r="B908" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C908" s="4" t="s">
+      <c r="B908" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C908" s="10" t="s">
         <v>1820</v>
       </c>
       <c r="D908" s="15"/>
     </row>
     <row r="909" ht="22.5" customHeight="1">
-      <c r="A909" s="10" t="s">
+      <c r="A909" s="4" t="s">
         <v>1821</v>
       </c>
-      <c r="B909" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C909" s="10" t="s">
+      <c r="B909" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C909" s="4" t="s">
         <v>1822</v>
       </c>
       <c r="D909" s="15"/>
     </row>
     <row r="910" ht="22.5" customHeight="1">
-      <c r="A910" s="4" t="s">
+      <c r="A910" s="10" t="s">
         <v>1823</v>
       </c>
-      <c r="B910" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C910" s="4" t="s">
+      <c r="B910" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C910" s="10" t="s">
         <v>1824</v>
       </c>
       <c r="D910" s="15"/>
@@ -21666,8 +21681,8 @@
       <c r="A913" s="4" t="s">
         <v>1829</v>
       </c>
-      <c r="B913" s="9" t="s">
-        <v>64</v>
+      <c r="B913" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C913" s="4" t="s">
         <v>1830</v>
@@ -21675,13 +21690,13 @@
       <c r="D913" s="15"/>
     </row>
     <row r="914" ht="22.5" customHeight="1">
-      <c r="A914" s="10" t="s">
+      <c r="A914" s="4" t="s">
         <v>1831</v>
       </c>
-      <c r="B914" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C914" s="10" t="s">
+      <c r="B914" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C914" s="4" t="s">
         <v>1832</v>
       </c>
       <c r="D914" s="15"/>
@@ -21691,7 +21706,7 @@
         <v>1833</v>
       </c>
       <c r="B915" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C915" s="4" t="s">
         <v>1834</v>
@@ -21723,13 +21738,13 @@
       <c r="D917" s="15"/>
     </row>
     <row r="918" ht="22.5" customHeight="1">
-      <c r="A918" s="4" t="s">
+      <c r="A918" s="10" t="s">
         <v>1839</v>
       </c>
-      <c r="B918" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C918" s="4" t="s">
+      <c r="B918" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C918" s="10" t="s">
         <v>1840</v>
       </c>
       <c r="D918" s="15"/>
@@ -21739,7 +21754,7 @@
         <v>1841</v>
       </c>
       <c r="B919" s="5" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="C919" s="4" t="s">
         <v>1842</v>
@@ -21750,7 +21765,7 @@
       <c r="A920" s="4" t="s">
         <v>1843</v>
       </c>
-      <c r="B920" s="7" t="s">
+      <c r="B920" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C920" s="4" t="s">
@@ -21762,7 +21777,7 @@
       <c r="A921" s="4" t="s">
         <v>1845</v>
       </c>
-      <c r="B921" s="9" t="s">
+      <c r="B921" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C921" s="4" t="s">
@@ -21771,61 +21786,61 @@
       <c r="D921" s="15"/>
     </row>
     <row r="922" ht="22.5" customHeight="1">
-      <c r="A922" s="10" t="s">
+      <c r="A922" s="4" t="s">
         <v>1847</v>
       </c>
       <c r="B922" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C922" s="10" t="s">
+      <c r="C922" s="4" t="s">
         <v>1848</v>
       </c>
       <c r="D922" s="15"/>
     </row>
     <row r="923" ht="22.5" customHeight="1">
-      <c r="A923" s="10" t="s">
+      <c r="A923" s="4" t="s">
         <v>1849</v>
       </c>
       <c r="B923" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C923" s="10" t="s">
+      <c r="C923" s="4" t="s">
         <v>1850</v>
       </c>
       <c r="D923" s="15"/>
     </row>
     <row r="924" ht="22.5" customHeight="1">
-      <c r="A924" s="4" t="s">
+      <c r="A924" s="10" t="s">
         <v>1851</v>
       </c>
-      <c r="B924" s="9" t="s">
+      <c r="B924" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C924" s="10" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D924" s="15"/>
+    </row>
+    <row r="925" ht="22.5" customHeight="1">
+      <c r="A925" s="10" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B925" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C924" s="4" t="s">
-        <v>1852</v>
-      </c>
-      <c r="D924" s="15"/>
-    </row>
-    <row r="925" ht="22.5" customHeight="1">
-      <c r="A925" s="4" t="s">
-        <v>1853</v>
-      </c>
-      <c r="B925" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C925" s="4" t="s">
+      <c r="C925" s="10" t="s">
         <v>1854</v>
       </c>
       <c r="D925" s="15"/>
     </row>
     <row r="926" ht="22.5" customHeight="1">
-      <c r="A926" s="16" t="s">
+      <c r="A926" s="4" t="s">
         <v>1855</v>
       </c>
-      <c r="B926" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C926" s="16" t="s">
+      <c r="B926" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C926" s="4" t="s">
         <v>1856</v>
       </c>
       <c r="D926" s="15"/>
@@ -21843,13 +21858,13 @@
       <c r="D927" s="15"/>
     </row>
     <row r="928" ht="22.5" customHeight="1">
-      <c r="A928" s="4" t="s">
+      <c r="A928" s="16" t="s">
         <v>1859</v>
       </c>
-      <c r="B928" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C928" s="4" t="s">
+      <c r="B928" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C928" s="16" t="s">
         <v>1860</v>
       </c>
       <c r="D928" s="15"/>
@@ -21867,13 +21882,13 @@
       <c r="D929" s="15"/>
     </row>
     <row r="930" ht="22.5" customHeight="1">
-      <c r="A930" s="10" t="s">
+      <c r="A930" s="4" t="s">
         <v>1863</v>
       </c>
-      <c r="B930" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C930" s="10" t="s">
+      <c r="B930" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C930" s="4" t="s">
         <v>1864</v>
       </c>
       <c r="D930" s="15"/>
@@ -21883,7 +21898,7 @@
         <v>1865</v>
       </c>
       <c r="B931" s="5" t="s">
-        <v>130</v>
+        <v>7</v>
       </c>
       <c r="C931" s="4" t="s">
         <v>1866</v>
@@ -21891,25 +21906,25 @@
       <c r="D931" s="15"/>
     </row>
     <row r="932" ht="22.5" customHeight="1">
-      <c r="A932" s="4" t="s">
+      <c r="A932" s="10" t="s">
         <v>1867</v>
       </c>
       <c r="B932" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C932" s="4" t="s">
+      <c r="C932" s="10" t="s">
         <v>1868</v>
       </c>
       <c r="D932" s="15"/>
     </row>
     <row r="933" ht="22.5" customHeight="1">
-      <c r="A933" s="10" t="s">
+      <c r="A933" s="4" t="s">
         <v>1869</v>
       </c>
-      <c r="B933" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C933" s="10" t="s">
+      <c r="B933" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C933" s="4" t="s">
         <v>1870</v>
       </c>
       <c r="D933" s="15"/>
@@ -21918,8 +21933,8 @@
       <c r="A934" s="4" t="s">
         <v>1871</v>
       </c>
-      <c r="B934" s="9" t="s">
-        <v>49</v>
+      <c r="B934" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C934" s="4" t="s">
         <v>1872</v>
@@ -21927,25 +21942,25 @@
       <c r="D934" s="15"/>
     </row>
     <row r="935" ht="22.5" customHeight="1">
-      <c r="A935" s="4" t="s">
+      <c r="A935" s="10" t="s">
         <v>1873</v>
       </c>
-      <c r="B935" s="9" t="s">
+      <c r="B935" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C935" s="10" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D935" s="15"/>
+    </row>
+    <row r="936" ht="22.5" customHeight="1">
+      <c r="A936" s="4" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B936" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C935" s="4" t="s">
-        <v>1874</v>
-      </c>
-      <c r="D935" s="15"/>
-    </row>
-    <row r="936" ht="22.5" customHeight="1">
-      <c r="A936" s="10" t="s">
-        <v>1875</v>
-      </c>
-      <c r="B936" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C936" s="10" t="s">
+      <c r="C936" s="4" t="s">
         <v>1876</v>
       </c>
       <c r="D936" s="15"/>
@@ -21954,8 +21969,8 @@
       <c r="A937" s="4" t="s">
         <v>1877</v>
       </c>
-      <c r="B937" s="5" t="s">
-        <v>7</v>
+      <c r="B937" s="9" t="s">
+        <v>49</v>
       </c>
       <c r="C937" s="4" t="s">
         <v>1878</v>
@@ -21963,13 +21978,13 @@
       <c r="D937" s="15"/>
     </row>
     <row r="938" ht="22.5" customHeight="1">
-      <c r="A938" s="4" t="s">
+      <c r="A938" s="10" t="s">
         <v>1879</v>
       </c>
-      <c r="B938" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C938" s="4" t="s">
+      <c r="B938" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C938" s="10" t="s">
         <v>1880</v>
       </c>
       <c r="D938" s="15"/>
@@ -21978,8 +21993,8 @@
       <c r="A939" s="4" t="s">
         <v>1881</v>
       </c>
-      <c r="B939" s="9" t="s">
-        <v>64</v>
+      <c r="B939" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C939" s="4" t="s">
         <v>1882</v>
@@ -21990,7 +22005,7 @@
       <c r="A940" s="4" t="s">
         <v>1883</v>
       </c>
-      <c r="B940" s="5" t="s">
+      <c r="B940" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C940" s="4" t="s">
@@ -21999,25 +22014,25 @@
       <c r="D940" s="15"/>
     </row>
     <row r="941" ht="22.5" customHeight="1">
-      <c r="A941" s="10" t="s">
+      <c r="A941" s="4" t="s">
         <v>1885</v>
       </c>
-      <c r="B941" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C941" s="10" t="s">
+      <c r="B941" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C941" s="4" t="s">
         <v>1886</v>
       </c>
       <c r="D941" s="15"/>
     </row>
     <row r="942" ht="22.5" customHeight="1">
-      <c r="A942" s="10" t="s">
+      <c r="A942" s="4" t="s">
         <v>1887</v>
       </c>
       <c r="B942" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C942" s="10" t="s">
+      <c r="C942" s="4" t="s">
         <v>1888</v>
       </c>
       <c r="D942" s="15"/>
@@ -22026,7 +22041,7 @@
       <c r="A943" s="10" t="s">
         <v>1889</v>
       </c>
-      <c r="B943" s="7" t="s">
+      <c r="B943" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C943" s="10" t="s">
@@ -22035,37 +22050,37 @@
       <c r="D943" s="15"/>
     </row>
     <row r="944" ht="22.5" customHeight="1">
-      <c r="A944" s="4" t="s">
+      <c r="A944" s="10" t="s">
         <v>1891</v>
       </c>
       <c r="B944" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C944" s="4" t="s">
+      <c r="C944" s="10" t="s">
         <v>1892</v>
       </c>
       <c r="D944" s="15"/>
     </row>
     <row r="945" ht="22.5" customHeight="1">
-      <c r="A945" s="4" t="s">
+      <c r="A945" s="10" t="s">
         <v>1893</v>
       </c>
-      <c r="B945" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C945" s="4" t="s">
+      <c r="B945" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C945" s="10" t="s">
         <v>1894</v>
       </c>
       <c r="D945" s="15"/>
     </row>
     <row r="946" ht="22.5" customHeight="1">
-      <c r="A946" s="10" t="s">
+      <c r="A946" s="4" t="s">
         <v>1895</v>
       </c>
       <c r="B946" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C946" s="10" t="s">
+      <c r="C946" s="4" t="s">
         <v>1896</v>
       </c>
       <c r="D946" s="15"/>
@@ -22075,7 +22090,7 @@
         <v>1897</v>
       </c>
       <c r="B947" s="9" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="C947" s="4" t="s">
         <v>1898</v>
@@ -22083,13 +22098,13 @@
       <c r="D947" s="15"/>
     </row>
     <row r="948" ht="22.5" customHeight="1">
-      <c r="A948" s="4" t="s">
+      <c r="A948" s="10" t="s">
         <v>1899</v>
       </c>
       <c r="B948" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C948" s="4" t="s">
+      <c r="C948" s="10" t="s">
         <v>1900</v>
       </c>
       <c r="D948" s="15"/>
@@ -22098,7 +22113,7 @@
       <c r="A949" s="4" t="s">
         <v>1901</v>
       </c>
-      <c r="B949" s="5" t="s">
+      <c r="B949" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C949" s="4" t="s">
@@ -22107,7 +22122,7 @@
       <c r="D949" s="15"/>
     </row>
     <row r="950" ht="22.5" customHeight="1">
-      <c r="A950" s="10" t="s">
+      <c r="A950" s="4" t="s">
         <v>1903</v>
       </c>
       <c r="B950" s="5" t="s">
@@ -22119,13 +22134,13 @@
       <c r="D950" s="15"/>
     </row>
     <row r="951" ht="22.5" customHeight="1">
-      <c r="A951" s="10" t="s">
+      <c r="A951" s="4" t="s">
         <v>1905</v>
       </c>
-      <c r="B951" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C951" s="10" t="s">
+      <c r="B951" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C951" s="4" t="s">
         <v>1906</v>
       </c>
       <c r="D951" s="15"/>
@@ -22137,7 +22152,7 @@
       <c r="B952" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C952" s="10" t="s">
+      <c r="C952" s="4" t="s">
         <v>1908</v>
       </c>
       <c r="D952" s="15"/>
@@ -22146,7 +22161,7 @@
       <c r="A953" s="10" t="s">
         <v>1909</v>
       </c>
-      <c r="B953" s="5" t="s">
+      <c r="B953" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C953" s="10" t="s">
@@ -22159,7 +22174,7 @@
         <v>1911</v>
       </c>
       <c r="B954" s="5" t="s">
-        <v>623</v>
+        <v>7</v>
       </c>
       <c r="C954" s="10" t="s">
         <v>1912</v>
@@ -22167,13 +22182,13 @@
       <c r="D954" s="15"/>
     </row>
     <row r="955" ht="22.5" customHeight="1">
-      <c r="A955" s="4" t="s">
+      <c r="A955" s="10" t="s">
         <v>1913</v>
       </c>
       <c r="B955" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C955" s="4" t="s">
+      <c r="C955" s="10" t="s">
         <v>1914</v>
       </c>
       <c r="D955" s="15"/>
@@ -22182,8 +22197,8 @@
       <c r="A956" s="10" t="s">
         <v>1915</v>
       </c>
-      <c r="B956" s="7" t="s">
-        <v>7</v>
+      <c r="B956" s="5" t="s">
+        <v>623</v>
       </c>
       <c r="C956" s="10" t="s">
         <v>1916</v>
@@ -22203,13 +22218,13 @@
       <c r="D957" s="15"/>
     </row>
     <row r="958" ht="22.5" customHeight="1">
-      <c r="A958" s="4" t="s">
+      <c r="A958" s="10" t="s">
         <v>1919</v>
       </c>
-      <c r="B958" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C958" s="4" t="s">
+      <c r="B958" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C958" s="10" t="s">
         <v>1920</v>
       </c>
       <c r="D958" s="15"/>
@@ -22218,8 +22233,8 @@
       <c r="A959" s="4" t="s">
         <v>1921</v>
       </c>
-      <c r="B959" s="9" t="s">
-        <v>115</v>
+      <c r="B959" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C959" s="4" t="s">
         <v>1922</v>
@@ -22231,7 +22246,7 @@
         <v>1923</v>
       </c>
       <c r="B960" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C960" s="4" t="s">
         <v>1924</v>
@@ -22242,8 +22257,8 @@
       <c r="A961" s="4" t="s">
         <v>1925</v>
       </c>
-      <c r="B961" s="7" t="s">
-        <v>7</v>
+      <c r="B961" s="9" t="s">
+        <v>115</v>
       </c>
       <c r="C961" s="4" t="s">
         <v>1926</v>
@@ -22251,13 +22266,13 @@
       <c r="D961" s="15"/>
     </row>
     <row r="962" ht="22.5" customHeight="1">
-      <c r="A962" s="10" t="s">
+      <c r="A962" s="4" t="s">
         <v>1927</v>
       </c>
       <c r="B962" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C962" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C962" s="4" t="s">
         <v>1928</v>
       </c>
       <c r="D962" s="15"/>
@@ -22266,8 +22281,8 @@
       <c r="A963" s="4" t="s">
         <v>1929</v>
       </c>
-      <c r="B963" s="9" t="s">
-        <v>115</v>
+      <c r="B963" s="7" t="s">
+        <v>7</v>
       </c>
       <c r="C963" s="4" t="s">
         <v>1930</v>
@@ -22275,11 +22290,11 @@
       <c r="D963" s="15"/>
     </row>
     <row r="964" ht="22.5" customHeight="1">
-      <c r="A964" s="4" t="s">
+      <c r="A964" s="10" t="s">
         <v>1931</v>
       </c>
-      <c r="B964" s="9" t="s">
-        <v>224</v>
+      <c r="B964" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C964" s="10" t="s">
         <v>1932</v>
@@ -22291,7 +22306,7 @@
         <v>1933</v>
       </c>
       <c r="B965" s="9" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="C965" s="4" t="s">
         <v>1934</v>
@@ -22302,10 +22317,10 @@
       <c r="A966" s="4" t="s">
         <v>1935</v>
       </c>
-      <c r="B966" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C966" s="4" t="s">
+      <c r="B966" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C966" s="10" t="s">
         <v>1936</v>
       </c>
       <c r="D966" s="15"/>
@@ -22314,7 +22329,7 @@
       <c r="A967" s="4" t="s">
         <v>1937</v>
       </c>
-      <c r="B967" s="5" t="s">
+      <c r="B967" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C967" s="4" t="s">
@@ -22323,59 +22338,59 @@
       <c r="D967" s="15"/>
     </row>
     <row r="968" ht="22.5" customHeight="1">
-      <c r="A968" s="10" t="s">
+      <c r="A968" s="4" t="s">
         <v>1939</v>
       </c>
       <c r="B968" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C968" s="4" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D968" s="15"/>
+    </row>
+    <row r="969" ht="22.5" customHeight="1">
+      <c r="A969" s="4" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B969" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C969" s="4" t="s">
+        <v>1942</v>
+      </c>
+      <c r="D969" s="15"/>
+    </row>
+    <row r="970" ht="22.5" customHeight="1">
+      <c r="A970" s="10" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B970" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="C968" s="10" t="s">
-        <v>1940</v>
-      </c>
-      <c r="D968" s="15"/>
-    </row>
-    <row r="969" ht="22.5" customHeight="1">
-      <c r="A969" s="10" t="s">
-        <v>1941</v>
-      </c>
-      <c r="B969" s="5" t="s">
+      <c r="C970" s="10" t="s">
+        <v>1944</v>
+      </c>
+      <c r="D970" s="15"/>
+    </row>
+    <row r="971" ht="22.5" customHeight="1">
+      <c r="A971" s="10" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B971" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="C969" s="10" t="s">
-        <v>1942</v>
-      </c>
-      <c r="D969" s="15"/>
-    </row>
-    <row r="970" ht="22.5" customHeight="1">
-      <c r="A970" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="B970" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C970" s="4" t="s">
-        <v>1943</v>
-      </c>
-      <c r="D970" s="15"/>
-    </row>
-    <row r="971" ht="22.5" customHeight="1">
-      <c r="A971" s="4" t="s">
-        <v>1944</v>
-      </c>
-      <c r="B971" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C971" s="4" t="s">
-        <v>1945</v>
+      <c r="C971" s="10" t="s">
+        <v>1946</v>
       </c>
       <c r="D971" s="15"/>
     </row>
     <row r="972" ht="22.5" customHeight="1">
       <c r="A972" s="4" t="s">
-        <v>1946</v>
+        <v>688</v>
       </c>
       <c r="B972" s="5" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="C972" s="4" t="s">
         <v>1947</v>
@@ -22383,13 +22398,13 @@
       <c r="D972" s="15"/>
     </row>
     <row r="973" ht="22.5" customHeight="1">
-      <c r="A973" s="10" t="s">
+      <c r="A973" s="4" t="s">
         <v>1948</v>
       </c>
-      <c r="B973" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C973" s="10" t="s">
+      <c r="B973" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C973" s="4" t="s">
         <v>1949</v>
       </c>
       <c r="D973" s="15"/>
@@ -22399,7 +22414,7 @@
         <v>1950</v>
       </c>
       <c r="B974" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C974" s="4" t="s">
         <v>1951</v>
@@ -22407,13 +22422,13 @@
       <c r="D974" s="15"/>
     </row>
     <row r="975" ht="22.5" customHeight="1">
-      <c r="A975" s="4" t="s">
+      <c r="A975" s="10" t="s">
         <v>1952</v>
       </c>
       <c r="B975" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C975" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C975" s="10" t="s">
         <v>1953</v>
       </c>
       <c r="D975" s="15"/>
@@ -22431,49 +22446,49 @@
       <c r="D976" s="15"/>
     </row>
     <row r="977" ht="22.5" customHeight="1">
-      <c r="A977" s="10" t="s">
+      <c r="A977" s="4" t="s">
         <v>1956</v>
       </c>
       <c r="B977" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C977" s="10" t="s">
+      <c r="C977" s="4" t="s">
         <v>1957</v>
       </c>
       <c r="D977" s="15"/>
     </row>
     <row r="978" ht="22.5" customHeight="1">
-      <c r="A978" s="10" t="s">
+      <c r="A978" s="4" t="s">
         <v>1958</v>
       </c>
       <c r="B978" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C978" s="10" t="s">
+      <c r="C978" s="4" t="s">
         <v>1959</v>
       </c>
       <c r="D978" s="15"/>
     </row>
     <row r="979" ht="22.5" customHeight="1">
-      <c r="A979" s="4" t="s">
+      <c r="A979" s="10" t="s">
         <v>1960</v>
       </c>
       <c r="B979" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C979" s="4" t="s">
+      <c r="C979" s="10" t="s">
         <v>1961</v>
       </c>
       <c r="D979" s="15"/>
     </row>
     <row r="980" ht="22.5" customHeight="1">
-      <c r="A980" s="4" t="s">
+      <c r="A980" s="10" t="s">
         <v>1962</v>
       </c>
       <c r="B980" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C980" s="4" t="s">
+      <c r="C980" s="10" t="s">
         <v>1963</v>
       </c>
       <c r="D980" s="15"/>
@@ -22491,13 +22506,13 @@
       <c r="D981" s="15"/>
     </row>
     <row r="982" ht="22.5" customHeight="1">
-      <c r="A982" s="10" t="s">
+      <c r="A982" s="4" t="s">
         <v>1966</v>
       </c>
       <c r="B982" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C982" s="10" t="s">
+      <c r="C982" s="4" t="s">
         <v>1967</v>
       </c>
       <c r="D982" s="15"/>
@@ -22515,25 +22530,25 @@
       <c r="D983" s="15"/>
     </row>
     <row r="984" ht="22.5" customHeight="1">
-      <c r="A984" s="4" t="s">
+      <c r="A984" s="10" t="s">
         <v>1970</v>
       </c>
       <c r="B984" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C984" s="4" t="s">
+      <c r="C984" s="10" t="s">
         <v>1971</v>
       </c>
       <c r="D984" s="15"/>
     </row>
     <row r="985" ht="22.5" customHeight="1">
-      <c r="A985" s="10" t="s">
+      <c r="A985" s="4" t="s">
         <v>1972</v>
       </c>
       <c r="B985" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C985" s="10" t="s">
+      <c r="C985" s="4" t="s">
         <v>1973</v>
       </c>
       <c r="D985" s="15"/>
@@ -22551,13 +22566,13 @@
       <c r="D986" s="15"/>
     </row>
     <row r="987" ht="22.5" customHeight="1">
-      <c r="A987" s="4" t="s">
+      <c r="A987" s="10" t="s">
         <v>1976</v>
       </c>
       <c r="B987" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C987" s="4" t="s">
+      <c r="C987" s="10" t="s">
         <v>1977</v>
       </c>
       <c r="D987" s="15"/>
@@ -22575,49 +22590,49 @@
       <c r="D988" s="15"/>
     </row>
     <row r="989" ht="22.5" customHeight="1">
-      <c r="A989" s="10" t="s">
+      <c r="A989" s="4" t="s">
         <v>1980</v>
       </c>
       <c r="B989" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C989" s="10" t="s">
+      <c r="C989" s="4" t="s">
         <v>1981</v>
       </c>
       <c r="D989" s="15"/>
     </row>
     <row r="990" ht="22.5" customHeight="1">
-      <c r="A990" s="10" t="s">
+      <c r="A990" s="4" t="s">
         <v>1982</v>
       </c>
       <c r="B990" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C990" s="10" t="s">
+      <c r="C990" s="4" t="s">
         <v>1983</v>
       </c>
       <c r="D990" s="15"/>
     </row>
     <row r="991" ht="22.5" customHeight="1">
-      <c r="A991" s="4" t="s">
+      <c r="A991" s="10" t="s">
         <v>1984</v>
       </c>
       <c r="B991" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C991" s="4" t="s">
+      <c r="C991" s="10" t="s">
         <v>1985</v>
       </c>
       <c r="D991" s="15"/>
     </row>
     <row r="992" ht="22.5" customHeight="1">
-      <c r="A992" s="4" t="s">
+      <c r="A992" s="10" t="s">
         <v>1986</v>
       </c>
       <c r="B992" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C992" s="4" t="s">
+      <c r="C992" s="10" t="s">
         <v>1987</v>
       </c>
       <c r="D992" s="15"/>
@@ -22659,49 +22674,49 @@
       <c r="D995" s="15"/>
     </row>
     <row r="996" ht="22.5" customHeight="1">
-      <c r="A996" s="10" t="s">
+      <c r="A996" s="4" t="s">
         <v>1994</v>
       </c>
-      <c r="B996" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C996" s="10" t="s">
+      <c r="B996" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C996" s="4" t="s">
         <v>1995</v>
       </c>
       <c r="D996" s="15"/>
     </row>
     <row r="997" ht="22.5" customHeight="1">
-      <c r="A997" s="10" t="s">
+      <c r="A997" s="4" t="s">
         <v>1996</v>
       </c>
       <c r="B997" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C997" s="10" t="s">
+      <c r="C997" s="4" t="s">
         <v>1997</v>
       </c>
       <c r="D997" s="15"/>
     </row>
     <row r="998" ht="22.5" customHeight="1">
-      <c r="A998" s="4" t="s">
+      <c r="A998" s="10" t="s">
         <v>1998</v>
       </c>
-      <c r="B998" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C998" s="4" t="s">
+      <c r="B998" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C998" s="10" t="s">
         <v>1999</v>
       </c>
       <c r="D998" s="15"/>
     </row>
     <row r="999" ht="22.5" customHeight="1">
-      <c r="A999" s="4" t="s">
+      <c r="A999" s="10" t="s">
         <v>2000</v>
       </c>
       <c r="B999" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C999" s="4" t="s">
+      <c r="C999" s="10" t="s">
         <v>2001</v>
       </c>
       <c r="D999" s="15"/>
@@ -22767,13 +22782,13 @@
       <c r="D1004" s="15"/>
     </row>
     <row r="1005" ht="22.5" customHeight="1">
-      <c r="A1005" s="10" t="s">
+      <c r="A1005" s="4" t="s">
         <v>2012</v>
       </c>
       <c r="B1005" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1005" s="10" t="s">
+      <c r="C1005" s="4" t="s">
         <v>2013</v>
       </c>
       <c r="D1005" s="15"/>
@@ -22791,37 +22806,37 @@
       <c r="D1006" s="15"/>
     </row>
     <row r="1007" ht="22.5" customHeight="1">
-      <c r="A1007" s="4" t="s">
+      <c r="A1007" s="10" t="s">
         <v>2016</v>
       </c>
       <c r="B1007" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1007" s="4" t="s">
+      <c r="C1007" s="10" t="s">
         <v>2017</v>
       </c>
       <c r="D1007" s="15"/>
     </row>
     <row r="1008" ht="22.5" customHeight="1">
-      <c r="A1008" s="10" t="s">
+      <c r="A1008" s="4" t="s">
         <v>2018</v>
       </c>
       <c r="B1008" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1008" s="10" t="s">
+      <c r="C1008" s="4" t="s">
         <v>2019</v>
       </c>
       <c r="D1008" s="15"/>
     </row>
     <row r="1009" ht="22.5" customHeight="1">
-      <c r="A1009" s="10" t="s">
+      <c r="A1009" s="4" t="s">
         <v>2020</v>
       </c>
       <c r="B1009" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1009" s="10" t="s">
+      <c r="C1009" s="4" t="s">
         <v>2021</v>
       </c>
       <c r="D1009" s="15"/>
@@ -22839,13 +22854,13 @@
       <c r="D1010" s="15"/>
     </row>
     <row r="1011" ht="22.5" customHeight="1">
-      <c r="A1011" s="4" t="s">
+      <c r="A1011" s="10" t="s">
         <v>2024</v>
       </c>
       <c r="B1011" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1011" s="4" t="s">
+      <c r="C1011" s="10" t="s">
         <v>2025</v>
       </c>
       <c r="D1011" s="15"/>
@@ -22875,13 +22890,13 @@
       <c r="D1013" s="15"/>
     </row>
     <row r="1014" ht="22.5" customHeight="1">
-      <c r="A1014" s="4" t="s">
+      <c r="A1014" s="10" t="s">
         <v>2030</v>
       </c>
       <c r="B1014" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1014" s="4" t="s">
+      <c r="C1014" s="10" t="s">
         <v>2031</v>
       </c>
       <c r="D1014" s="15"/>
@@ -22923,13 +22938,13 @@
       <c r="D1017" s="15"/>
     </row>
     <row r="1018" ht="22.5" customHeight="1">
-      <c r="A1018" s="10" t="s">
+      <c r="A1018" s="4" t="s">
         <v>2038</v>
       </c>
       <c r="B1018" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1018" s="10" t="s">
+      <c r="C1018" s="4" t="s">
         <v>2039</v>
       </c>
       <c r="D1018" s="15"/>
@@ -22947,25 +22962,25 @@
       <c r="D1019" s="15"/>
     </row>
     <row r="1020" ht="22.5" customHeight="1">
-      <c r="A1020" s="4" t="s">
+      <c r="A1020" s="10" t="s">
         <v>2042</v>
       </c>
       <c r="B1020" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1020" s="4" t="s">
+      <c r="C1020" s="10" t="s">
         <v>2043</v>
       </c>
       <c r="D1020" s="15"/>
     </row>
     <row r="1021" ht="22.5" customHeight="1">
-      <c r="A1021" s="10" t="s">
+      <c r="A1021" s="4" t="s">
         <v>2044</v>
       </c>
       <c r="B1021" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1021" s="10" t="s">
+      <c r="C1021" s="4" t="s">
         <v>2045</v>
       </c>
       <c r="D1021" s="15"/>
@@ -23055,13 +23070,13 @@
       <c r="D1028" s="15"/>
     </row>
     <row r="1029" ht="22.5" customHeight="1">
-      <c r="A1029" s="4" t="s">
+      <c r="A1029" s="10" t="s">
         <v>2060</v>
       </c>
       <c r="B1029" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1029" s="4" t="s">
+      <c r="C1029" s="10" t="s">
         <v>2061</v>
       </c>
       <c r="D1029" s="15"/>
@@ -23079,49 +23094,49 @@
       <c r="D1030" s="15"/>
     </row>
     <row r="1031" ht="22.5" customHeight="1">
-      <c r="A1031" s="10" t="s">
+      <c r="A1031" s="4" t="s">
         <v>2064</v>
       </c>
       <c r="B1031" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1031" s="10" t="s">
+      <c r="C1031" s="4" t="s">
         <v>2065</v>
       </c>
       <c r="D1031" s="15"/>
     </row>
     <row r="1032" ht="22.5" customHeight="1">
-      <c r="A1032" s="10" t="s">
+      <c r="A1032" s="4" t="s">
         <v>2066</v>
       </c>
       <c r="B1032" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1032" s="10" t="s">
+      <c r="C1032" s="4" t="s">
         <v>2067</v>
       </c>
       <c r="D1032" s="15"/>
     </row>
     <row r="1033" ht="22.5" customHeight="1">
-      <c r="A1033" s="4" t="s">
+      <c r="A1033" s="10" t="s">
         <v>2068</v>
       </c>
       <c r="B1033" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1033" s="4" t="s">
+      <c r="C1033" s="10" t="s">
         <v>2069</v>
       </c>
       <c r="D1033" s="15"/>
     </row>
     <row r="1034" ht="22.5" customHeight="1">
-      <c r="A1034" s="4" t="s">
+      <c r="A1034" s="10" t="s">
         <v>2070</v>
       </c>
       <c r="B1034" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1034" s="4" t="s">
+      <c r="C1034" s="10" t="s">
         <v>2071</v>
       </c>
       <c r="D1034" s="15"/>
@@ -23139,19 +23154,19 @@
       <c r="D1035" s="15"/>
     </row>
     <row r="1036" ht="22.5" customHeight="1">
-      <c r="A1036" s="10" t="s">
+      <c r="A1036" s="4" t="s">
         <v>2074</v>
       </c>
       <c r="B1036" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1036" s="10" t="s">
+      <c r="C1036" s="4" t="s">
         <v>2075</v>
       </c>
       <c r="D1036" s="15"/>
     </row>
     <row r="1037" ht="22.5" customHeight="1">
-      <c r="A1037" s="10" t="s">
+      <c r="A1037" s="4" t="s">
         <v>2076</v>
       </c>
       <c r="B1037" s="5" t="s">
@@ -23163,19 +23178,19 @@
       <c r="D1037" s="15"/>
     </row>
     <row r="1038" ht="22.5" customHeight="1">
-      <c r="A1038" s="4" t="s">
+      <c r="A1038" s="10" t="s">
         <v>2078</v>
       </c>
       <c r="B1038" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1038" s="4" t="s">
+      <c r="C1038" s="10" t="s">
         <v>2079</v>
       </c>
       <c r="D1038" s="15"/>
     </row>
     <row r="1039" ht="22.5" customHeight="1">
-      <c r="A1039" s="4" t="s">
+      <c r="A1039" s="10" t="s">
         <v>2080</v>
       </c>
       <c r="B1039" s="5" t="s">
@@ -23199,13 +23214,13 @@
       <c r="D1040" s="15"/>
     </row>
     <row r="1041" ht="22.5" customHeight="1">
-      <c r="A1041" s="10" t="s">
+      <c r="A1041" s="4" t="s">
         <v>2084</v>
       </c>
       <c r="B1041" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1041" s="10" t="s">
+      <c r="C1041" s="4" t="s">
         <v>2085</v>
       </c>
       <c r="D1041" s="15"/>
@@ -23223,13 +23238,13 @@
       <c r="D1042" s="15"/>
     </row>
     <row r="1043" ht="22.5" customHeight="1">
-      <c r="A1043" s="4" t="s">
+      <c r="A1043" s="10" t="s">
         <v>2088</v>
       </c>
       <c r="B1043" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1043" s="4" t="s">
+      <c r="C1043" s="10" t="s">
         <v>2089</v>
       </c>
       <c r="D1043" s="15"/>
@@ -23283,49 +23298,49 @@
       <c r="D1047" s="15"/>
     </row>
     <row r="1048" ht="22.5" customHeight="1">
-      <c r="A1048" s="10" t="s">
+      <c r="A1048" s="4" t="s">
         <v>2098</v>
       </c>
       <c r="B1048" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1048" s="10" t="s">
+      <c r="C1048" s="4" t="s">
         <v>2099</v>
       </c>
       <c r="D1048" s="15"/>
     </row>
     <row r="1049" ht="22.5" customHeight="1">
-      <c r="A1049" s="10" t="s">
+      <c r="A1049" s="4" t="s">
         <v>2100</v>
       </c>
       <c r="B1049" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1049" s="10" t="s">
+      <c r="C1049" s="4" t="s">
         <v>2101</v>
       </c>
       <c r="D1049" s="15"/>
     </row>
     <row r="1050" ht="22.5" customHeight="1">
-      <c r="A1050" s="4" t="s">
+      <c r="A1050" s="10" t="s">
         <v>2102</v>
       </c>
       <c r="B1050" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1050" s="4" t="s">
+      <c r="C1050" s="10" t="s">
         <v>2103</v>
       </c>
       <c r="D1050" s="15"/>
     </row>
     <row r="1051" ht="22.5" customHeight="1">
-      <c r="A1051" s="4" t="s">
+      <c r="A1051" s="10" t="s">
         <v>2104</v>
       </c>
       <c r="B1051" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1051" s="4" t="s">
+      <c r="C1051" s="10" t="s">
         <v>2105</v>
       </c>
       <c r="D1051" s="15"/>
@@ -23367,25 +23382,25 @@
       <c r="D1054" s="15"/>
     </row>
     <row r="1055" ht="22.5" customHeight="1">
-      <c r="A1055" s="10" t="s">
+      <c r="A1055" s="4" t="s">
         <v>2112</v>
       </c>
       <c r="B1055" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1055" s="10" t="s">
+      <c r="C1055" s="4" t="s">
         <v>2113</v>
       </c>
       <c r="D1055" s="15"/>
     </row>
     <row r="1056" ht="22.5" customHeight="1">
-      <c r="A1056" s="10" t="s">
+      <c r="A1056" s="4" t="s">
         <v>2114</v>
       </c>
       <c r="B1056" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1056" s="10" t="s">
+      <c r="C1056" s="4" t="s">
         <v>2115</v>
       </c>
       <c r="D1056" s="15"/>
@@ -23403,13 +23418,13 @@
       <c r="D1057" s="15"/>
     </row>
     <row r="1058" ht="22.5" customHeight="1">
-      <c r="A1058" s="4" t="s">
+      <c r="A1058" s="10" t="s">
         <v>2118</v>
       </c>
       <c r="B1058" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1058" s="4" t="s">
+      <c r="C1058" s="10" t="s">
         <v>2119</v>
       </c>
       <c r="D1058" s="15"/>
@@ -23439,13 +23454,13 @@
       <c r="D1060" s="15"/>
     </row>
     <row r="1061" ht="22.5" customHeight="1">
-      <c r="A1061" s="4" t="s">
+      <c r="A1061" s="10" t="s">
         <v>2124</v>
       </c>
       <c r="B1061" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1061" s="4" t="s">
+      <c r="C1061" s="10" t="s">
         <v>2125</v>
       </c>
       <c r="D1061" s="15"/>
@@ -23463,13 +23478,13 @@
       <c r="D1062" s="15"/>
     </row>
     <row r="1063" ht="22.5" customHeight="1">
-      <c r="A1063" s="10" t="s">
+      <c r="A1063" s="4" t="s">
         <v>2128</v>
       </c>
       <c r="B1063" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1063" s="10" t="s">
+      <c r="C1063" s="4" t="s">
         <v>2129</v>
       </c>
       <c r="D1063" s="15"/>
@@ -23487,13 +23502,13 @@
       <c r="D1064" s="15"/>
     </row>
     <row r="1065" ht="22.5" customHeight="1">
-      <c r="A1065" s="4" t="s">
+      <c r="A1065" s="10" t="s">
         <v>2132</v>
       </c>
       <c r="B1065" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1065" s="4" t="s">
+      <c r="C1065" s="10" t="s">
         <v>2133</v>
       </c>
       <c r="D1065" s="15"/>
@@ -23595,13 +23610,13 @@
       <c r="D1073" s="15"/>
     </row>
     <row r="1074" ht="22.5" customHeight="1">
-      <c r="A1074" s="10" t="s">
+      <c r="A1074" s="4" t="s">
         <v>2150</v>
       </c>
       <c r="B1074" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1074" s="10" t="s">
+      <c r="C1074" s="4" t="s">
         <v>2151</v>
       </c>
       <c r="D1074" s="15"/>
@@ -23631,13 +23646,13 @@
       <c r="D1076" s="15"/>
     </row>
     <row r="1077" ht="22.5" customHeight="1">
-      <c r="A1077" s="10" t="s">
+      <c r="A1077" s="4" t="s">
         <v>2156</v>
       </c>
       <c r="B1077" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1077" s="10" t="s">
+      <c r="C1077" s="4" t="s">
         <v>2157</v>
       </c>
       <c r="D1077" s="15"/>
@@ -23655,37 +23670,37 @@
       <c r="D1078" s="15"/>
     </row>
     <row r="1079" ht="22.5" customHeight="1">
-      <c r="A1079" s="4" t="s">
+      <c r="A1079" s="10" t="s">
         <v>2160</v>
       </c>
       <c r="B1079" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1079" s="4" t="s">
+      <c r="C1079" s="10" t="s">
         <v>2161</v>
       </c>
       <c r="D1079" s="15"/>
     </row>
     <row r="1080" ht="22.5" customHeight="1">
-      <c r="A1080" s="4" t="s">
+      <c r="A1080" s="10" t="s">
         <v>2162</v>
       </c>
       <c r="B1080" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1080" s="4" t="s">
+      <c r="C1080" s="10" t="s">
         <v>2163</v>
       </c>
       <c r="D1080" s="15"/>
     </row>
     <row r="1081" ht="22.5" customHeight="1">
-      <c r="A1081" s="10" t="s">
+      <c r="A1081" s="4" t="s">
         <v>2164</v>
       </c>
       <c r="B1081" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1081" s="10" t="s">
+      <c r="C1081" s="4" t="s">
         <v>2165</v>
       </c>
       <c r="D1081" s="15"/>
@@ -23715,13 +23730,13 @@
       <c r="D1083" s="15"/>
     </row>
     <row r="1084" ht="22.5" customHeight="1">
-      <c r="A1084" s="10" t="s">
+      <c r="A1084" s="4" t="s">
         <v>2170</v>
       </c>
       <c r="B1084" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1084" s="10" t="s">
+      <c r="C1084" s="4" t="s">
         <v>2171</v>
       </c>
       <c r="D1084" s="15"/>
@@ -23739,25 +23754,25 @@
       <c r="D1085" s="15"/>
     </row>
     <row r="1086" ht="22.5" customHeight="1">
-      <c r="A1086" s="4" t="s">
+      <c r="A1086" s="10" t="s">
         <v>2174</v>
       </c>
       <c r="B1086" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1086" s="4" t="s">
+      <c r="C1086" s="10" t="s">
         <v>2175</v>
       </c>
       <c r="D1086" s="15"/>
     </row>
     <row r="1087" ht="22.5" customHeight="1">
-      <c r="A1087" s="4" t="s">
+      <c r="A1087" s="10" t="s">
         <v>2176</v>
       </c>
       <c r="B1087" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1087" s="4" t="s">
+      <c r="C1087" s="10" t="s">
         <v>2177</v>
       </c>
       <c r="D1087" s="15"/>
@@ -23775,13 +23790,13 @@
       <c r="D1088" s="15"/>
     </row>
     <row r="1089" ht="22.5" customHeight="1">
-      <c r="A1089" s="10" t="s">
+      <c r="A1089" s="4" t="s">
         <v>2180</v>
       </c>
       <c r="B1089" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1089" s="10" t="s">
+      <c r="C1089" s="4" t="s">
         <v>2181</v>
       </c>
       <c r="D1089" s="15"/>
@@ -23799,13 +23814,13 @@
       <c r="D1090" s="15"/>
     </row>
     <row r="1091" ht="22.5" customHeight="1">
-      <c r="A1091" s="4" t="s">
+      <c r="A1091" s="10" t="s">
         <v>2184</v>
       </c>
       <c r="B1091" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1091" s="4" t="s">
+      <c r="C1091" s="10" t="s">
         <v>2185</v>
       </c>
       <c r="D1091" s="15"/>
@@ -23838,7 +23853,7 @@
       <c r="A1094" s="4" t="s">
         <v>2190</v>
       </c>
-      <c r="B1094" s="9" t="s">
+      <c r="B1094" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C1094" s="4" t="s">
@@ -23847,13 +23862,13 @@
       <c r="D1094" s="15"/>
     </row>
     <row r="1095" ht="22.5" customHeight="1">
-      <c r="A1095" s="10" t="s">
+      <c r="A1095" s="4" t="s">
         <v>2192</v>
       </c>
       <c r="B1095" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1095" s="10" t="s">
+      <c r="C1095" s="4" t="s">
         <v>2193</v>
       </c>
       <c r="D1095" s="15"/>
@@ -23862,7 +23877,7 @@
       <c r="A1096" s="4" t="s">
         <v>2194</v>
       </c>
-      <c r="B1096" s="5" t="s">
+      <c r="B1096" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C1096" s="4" t="s">
@@ -23895,13 +23910,13 @@
       <c r="D1098" s="15"/>
     </row>
     <row r="1099" ht="22.5" customHeight="1">
-      <c r="A1099" s="4" t="s">
+      <c r="A1099" s="10" t="s">
         <v>2200</v>
       </c>
       <c r="B1099" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1099" s="4" t="s">
+      <c r="C1099" s="10" t="s">
         <v>2201</v>
       </c>
       <c r="D1099" s="15"/>
@@ -23919,13 +23934,13 @@
       <c r="D1100" s="15"/>
     </row>
     <row r="1101" ht="22.5" customHeight="1">
-      <c r="A1101" s="10" t="s">
+      <c r="A1101" s="4" t="s">
         <v>2204</v>
       </c>
       <c r="B1101" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1101" s="10" t="s">
+      <c r="C1101" s="4" t="s">
         <v>2205</v>
       </c>
       <c r="D1101" s="15"/>
@@ -23967,55 +23982,55 @@
       <c r="D1104" s="15"/>
     </row>
     <row r="1105" ht="22.5" customHeight="1">
-      <c r="A1105" s="4" t="s">
+      <c r="A1105" s="10" t="s">
         <v>2212</v>
       </c>
       <c r="B1105" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1105" s="4" t="s">
+      <c r="C1105" s="10" t="s">
         <v>2213</v>
       </c>
       <c r="D1105" s="15"/>
     </row>
     <row r="1106" ht="22.5" customHeight="1">
-      <c r="A1106" s="10" t="s">
+      <c r="A1106" s="4" t="s">
         <v>2214</v>
       </c>
       <c r="B1106" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1106" s="10" t="s">
+      <c r="C1106" s="4" t="s">
         <v>2215</v>
       </c>
       <c r="D1106" s="15"/>
     </row>
     <row r="1107" ht="22.5" customHeight="1">
-      <c r="A1107" s="10" t="s">
+      <c r="A1107" s="4" t="s">
         <v>2216</v>
       </c>
       <c r="B1107" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1107" s="10" t="s">
+      <c r="C1107" s="4" t="s">
         <v>2217</v>
       </c>
       <c r="D1107" s="15"/>
     </row>
     <row r="1108" ht="22.5" customHeight="1">
-      <c r="A1108" s="4" t="s">
+      <c r="A1108" s="10" t="s">
         <v>2218</v>
       </c>
       <c r="B1108" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1108" s="4" t="s">
+      <c r="C1108" s="10" t="s">
         <v>2219</v>
       </c>
       <c r="D1108" s="15"/>
     </row>
     <row r="1109" ht="22.5" customHeight="1">
-      <c r="A1109" s="4" t="s">
+      <c r="A1109" s="10" t="s">
         <v>2220</v>
       </c>
       <c r="B1109" s="5" t="s">
@@ -24027,13 +24042,13 @@
       <c r="D1109" s="15"/>
     </row>
     <row r="1110" ht="22.5" customHeight="1">
-      <c r="A1110" s="10" t="s">
+      <c r="A1110" s="4" t="s">
         <v>2222</v>
       </c>
       <c r="B1110" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1110" s="10" t="s">
+      <c r="C1110" s="4" t="s">
         <v>2223</v>
       </c>
       <c r="D1110" s="15"/>
@@ -24045,31 +24060,31 @@
       <c r="B1111" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1111" s="4" t="s">
+      <c r="C1111" s="10" t="s">
         <v>2225</v>
       </c>
       <c r="D1111" s="15"/>
     </row>
     <row r="1112" ht="22.5" customHeight="1">
-      <c r="A1112" s="4" t="s">
+      <c r="A1112" s="10" t="s">
         <v>2226</v>
       </c>
       <c r="B1112" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1112" s="4" t="s">
+      <c r="C1112" s="10" t="s">
         <v>2227</v>
       </c>
       <c r="D1112" s="15"/>
     </row>
     <row r="1113" ht="22.5" customHeight="1">
-      <c r="A1113" s="10" t="s">
+      <c r="A1113" s="4" t="s">
         <v>2228</v>
       </c>
       <c r="B1113" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1113" s="10" t="s">
+      <c r="C1113" s="4" t="s">
         <v>2229</v>
       </c>
       <c r="D1113" s="15"/>
@@ -24123,37 +24138,37 @@
       <c r="D1117" s="15"/>
     </row>
     <row r="1118" ht="22.5" customHeight="1">
-      <c r="A1118" s="10" t="s">
+      <c r="A1118" s="4" t="s">
         <v>2238</v>
       </c>
       <c r="B1118" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1118" s="10" t="s">
+      <c r="C1118" s="4" t="s">
         <v>2239</v>
       </c>
       <c r="D1118" s="15"/>
     </row>
     <row r="1119" ht="22.5" customHeight="1">
-      <c r="A1119" s="4" t="s">
+      <c r="A1119" s="10" t="s">
         <v>2240</v>
       </c>
       <c r="B1119" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1119" s="4" t="s">
+      <c r="C1119" s="10" t="s">
         <v>2241</v>
       </c>
       <c r="D1119" s="15"/>
     </row>
     <row r="1120" ht="22.5" customHeight="1">
-      <c r="A1120" s="4" t="s">
+      <c r="A1120" s="10" t="s">
         <v>2242</v>
       </c>
       <c r="B1120" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1120" s="4" t="s">
+      <c r="C1120" s="10" t="s">
         <v>2243</v>
       </c>
       <c r="D1120" s="15"/>
@@ -24195,13 +24210,13 @@
       <c r="D1123" s="15"/>
     </row>
     <row r="1124" ht="22.5" customHeight="1">
-      <c r="A1124" s="10" t="s">
+      <c r="A1124" s="4" t="s">
         <v>2250</v>
       </c>
       <c r="B1124" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1124" s="10" t="s">
+      <c r="C1124" s="4" t="s">
         <v>2251</v>
       </c>
       <c r="D1124" s="15"/>
@@ -24219,25 +24234,25 @@
       <c r="D1125" s="18"/>
     </row>
     <row r="1126" ht="22.5" customHeight="1">
-      <c r="A1126" s="4" t="s">
+      <c r="A1126" s="10" t="s">
         <v>2254</v>
       </c>
       <c r="B1126" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1126" s="4" t="s">
+      <c r="C1126" s="10" t="s">
         <v>2255</v>
       </c>
       <c r="D1126" s="15"/>
     </row>
     <row r="1127" ht="22.5" customHeight="1">
-      <c r="A1127" s="10" t="s">
+      <c r="A1127" s="4" t="s">
         <v>2256</v>
       </c>
       <c r="B1127" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1127" s="10" t="s">
+      <c r="C1127" s="4" t="s">
         <v>2257</v>
       </c>
       <c r="D1127" s="15"/>
@@ -24246,7 +24261,7 @@
       <c r="A1128" s="4" t="s">
         <v>2258</v>
       </c>
-      <c r="B1128" s="9" t="s">
+      <c r="B1128" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C1128" s="4" t="s">
@@ -24255,25 +24270,25 @@
       <c r="D1128" s="15"/>
     </row>
     <row r="1129" ht="22.5" customHeight="1">
-      <c r="A1129" s="4" t="s">
+      <c r="A1129" s="10" t="s">
         <v>2260</v>
       </c>
-      <c r="B1129" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1129" s="4" t="s">
+      <c r="B1129" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1129" s="10" t="s">
         <v>2261</v>
       </c>
       <c r="D1129" s="15"/>
     </row>
     <row r="1130" ht="22.5" customHeight="1">
-      <c r="A1130" s="10" t="s">
+      <c r="A1130" s="4" t="s">
         <v>2262</v>
       </c>
-      <c r="B1130" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1130" s="10" t="s">
+      <c r="B1130" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1130" s="4" t="s">
         <v>2263</v>
       </c>
       <c r="D1130" s="15"/>
@@ -24282,7 +24297,7 @@
       <c r="A1131" s="4" t="s">
         <v>2264</v>
       </c>
-      <c r="B1131" s="5" t="s">
+      <c r="B1131" s="19" t="s">
         <v>4</v>
       </c>
       <c r="C1131" s="4" t="s">
@@ -24291,25 +24306,25 @@
       <c r="D1131" s="15"/>
     </row>
     <row r="1132" ht="22.5" customHeight="1">
-      <c r="A1132" s="4" t="s">
+      <c r="A1132" s="10" t="s">
         <v>2266</v>
       </c>
       <c r="B1132" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1132" s="4" t="s">
+      <c r="C1132" s="10" t="s">
         <v>2267</v>
       </c>
       <c r="D1132" s="15"/>
     </row>
     <row r="1133" ht="22.5" customHeight="1">
-      <c r="A1133" s="10" t="s">
+      <c r="A1133" s="4" t="s">
         <v>2268</v>
       </c>
       <c r="B1133" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1133" s="10" t="s">
+      <c r="C1133" s="4" t="s">
         <v>2269</v>
       </c>
       <c r="D1133" s="15"/>
@@ -24351,13 +24366,13 @@
       <c r="D1136" s="15"/>
     </row>
     <row r="1137" ht="22.5" customHeight="1">
-      <c r="A1137" s="4" t="s">
+      <c r="A1137" s="10" t="s">
         <v>2276</v>
       </c>
       <c r="B1137" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1137" s="4" t="s">
+      <c r="C1137" s="10" t="s">
         <v>2277</v>
       </c>
       <c r="D1137" s="15"/>
@@ -24411,13 +24426,13 @@
       <c r="D1141" s="15"/>
     </row>
     <row r="1142" ht="22.5" customHeight="1">
-      <c r="A1142" s="10" t="s">
+      <c r="A1142" s="4" t="s">
         <v>2286</v>
       </c>
       <c r="B1142" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1142" s="10" t="s">
+      <c r="C1142" s="4" t="s">
         <v>2287</v>
       </c>
       <c r="D1142" s="15"/>
@@ -24507,13 +24522,13 @@
       <c r="D1149" s="15"/>
     </row>
     <row r="1150" ht="22.5" customHeight="1">
-      <c r="A1150" s="4" t="s">
+      <c r="A1150" s="10" t="s">
         <v>2302</v>
       </c>
       <c r="B1150" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1150" s="4" t="s">
+      <c r="C1150" s="10" t="s">
         <v>2303</v>
       </c>
       <c r="D1150" s="15"/>
@@ -24633,7 +24648,7 @@
       <c r="B1160" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1160" s="10" t="s">
+      <c r="C1160" s="4" t="s">
         <v>2323</v>
       </c>
       <c r="D1160" s="15"/>
@@ -24651,7 +24666,7 @@
       <c r="D1161" s="15"/>
     </row>
     <row r="1162" ht="22.5" customHeight="1">
-      <c r="A1162" s="10" t="s">
+      <c r="A1162" s="4" t="s">
         <v>2326</v>
       </c>
       <c r="B1162" s="5" t="s">
@@ -24699,13 +24714,13 @@
       <c r="D1165" s="15"/>
     </row>
     <row r="1166" ht="22.5" customHeight="1">
-      <c r="A1166" s="4" t="s">
+      <c r="A1166" s="10" t="s">
         <v>2334</v>
       </c>
       <c r="B1166" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1166" s="4" t="s">
+      <c r="C1166" s="10" t="s">
         <v>2335</v>
       </c>
       <c r="D1166" s="15"/>
@@ -24735,13 +24750,13 @@
       <c r="D1168" s="15"/>
     </row>
     <row r="1169" ht="22.5" customHeight="1">
-      <c r="A1169" s="10" t="s">
+      <c r="A1169" s="4" t="s">
         <v>2340</v>
       </c>
       <c r="B1169" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1169" s="10" t="s">
+      <c r="C1169" s="4" t="s">
         <v>2341</v>
       </c>
       <c r="D1169" s="15"/>
@@ -24783,13 +24798,13 @@
       <c r="D1172" s="15"/>
     </row>
     <row r="1173" ht="22.5" customHeight="1">
-      <c r="A1173" s="4" t="s">
+      <c r="A1173" s="10" t="s">
         <v>2348</v>
       </c>
       <c r="B1173" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1173" s="4" t="s">
+      <c r="C1173" s="10" t="s">
         <v>2349</v>
       </c>
       <c r="D1173" s="15"/>
@@ -24903,13 +24918,13 @@
       <c r="D1182" s="15"/>
     </row>
     <row r="1183" ht="22.5" customHeight="1">
-      <c r="A1183" s="10" t="s">
+      <c r="A1183" s="4" t="s">
         <v>2368</v>
       </c>
       <c r="B1183" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1183" s="10" t="s">
+      <c r="C1183" s="4" t="s">
         <v>2369</v>
       </c>
       <c r="D1183" s="15"/>
@@ -24927,13 +24942,13 @@
       <c r="D1184" s="15"/>
     </row>
     <row r="1185" ht="22.5" customHeight="1">
-      <c r="A1185" s="4" t="s">
+      <c r="A1185" s="10" t="s">
         <v>2372</v>
       </c>
       <c r="B1185" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1185" s="4" t="s">
+      <c r="C1185" s="10" t="s">
         <v>2373</v>
       </c>
       <c r="D1185" s="15"/>
@@ -24987,13 +25002,13 @@
       <c r="D1189" s="15"/>
     </row>
     <row r="1190" ht="22.5" customHeight="1">
-      <c r="A1190" s="10" t="s">
+      <c r="A1190" s="4" t="s">
         <v>2382</v>
       </c>
       <c r="B1190" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1190" s="10" t="s">
+      <c r="C1190" s="4" t="s">
         <v>2383</v>
       </c>
       <c r="D1190" s="15"/>
@@ -25059,13 +25074,13 @@
       <c r="D1195" s="15"/>
     </row>
     <row r="1196" ht="22.5" customHeight="1">
-      <c r="A1196" s="4" t="s">
+      <c r="A1196" s="10" t="s">
         <v>2394</v>
       </c>
       <c r="B1196" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1196" s="4" t="s">
+      <c r="C1196" s="10" t="s">
         <v>2395</v>
       </c>
       <c r="D1196" s="15"/>
@@ -25119,13 +25134,13 @@
       <c r="D1200" s="15"/>
     </row>
     <row r="1201" ht="22.5" customHeight="1">
-      <c r="A1201" s="10" t="s">
+      <c r="A1201" s="4" t="s">
         <v>2404</v>
       </c>
       <c r="B1201" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1201" s="10" t="s">
+      <c r="C1201" s="4" t="s">
         <v>2405</v>
       </c>
       <c r="D1201" s="15"/>
@@ -25143,13 +25158,13 @@
       <c r="D1202" s="15"/>
     </row>
     <row r="1203" ht="22.5" customHeight="1">
-      <c r="A1203" s="4" t="s">
+      <c r="A1203" s="10" t="s">
         <v>2408</v>
       </c>
       <c r="B1203" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1203" s="4" t="s">
+      <c r="C1203" s="10" t="s">
         <v>2409</v>
       </c>
       <c r="D1203" s="15"/>
@@ -25263,25 +25278,25 @@
       <c r="D1212" s="15"/>
     </row>
     <row r="1213" ht="22.5" customHeight="1">
-      <c r="A1213" s="10" t="s">
+      <c r="A1213" s="4" t="s">
         <v>2428</v>
       </c>
       <c r="B1213" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1213" s="10" t="s">
+      <c r="C1213" s="4" t="s">
         <v>2429</v>
       </c>
       <c r="D1213" s="15"/>
     </row>
     <row r="1214" ht="22.5" customHeight="1">
-      <c r="A1214" s="10" t="s">
+      <c r="A1214" s="4" t="s">
         <v>2430</v>
       </c>
       <c r="B1214" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1214" s="10" t="s">
+      <c r="C1214" s="4" t="s">
         <v>2431</v>
       </c>
       <c r="D1214" s="15"/>
@@ -25299,13 +25314,13 @@
       <c r="D1215" s="15"/>
     </row>
     <row r="1216" ht="22.5" customHeight="1">
-      <c r="A1216" s="4" t="s">
+      <c r="A1216" s="10" t="s">
         <v>2434</v>
       </c>
       <c r="B1216" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1216" s="4" t="s">
+      <c r="C1216" s="10" t="s">
         <v>2435</v>
       </c>
       <c r="D1216" s="15"/>
@@ -25371,49 +25386,49 @@
       <c r="D1221" s="15"/>
     </row>
     <row r="1222" ht="22.5" customHeight="1">
-      <c r="A1222" s="10" t="s">
+      <c r="A1222" s="4" t="s">
         <v>2446</v>
       </c>
       <c r="B1222" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1222" s="10" t="s">
+      <c r="C1222" s="4" t="s">
         <v>2447</v>
       </c>
       <c r="D1222" s="15"/>
     </row>
     <row r="1223" ht="22.5" customHeight="1">
-      <c r="A1223" s="4" t="s">
+      <c r="A1223" s="10" t="s">
         <v>2448</v>
       </c>
       <c r="B1223" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1223" s="4" t="s">
+      <c r="C1223" s="10" t="s">
         <v>2449</v>
       </c>
       <c r="D1223" s="15"/>
     </row>
     <row r="1224" ht="22.5" customHeight="1">
-      <c r="A1224" s="4" t="s">
+      <c r="A1224" s="10" t="s">
         <v>2450</v>
       </c>
-      <c r="B1224" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1224" s="4" t="s">
+      <c r="B1224" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1224" s="10" t="s">
         <v>2451</v>
       </c>
       <c r="D1224" s="15"/>
     </row>
     <row r="1225" ht="22.5" customHeight="1">
-      <c r="A1225" s="10" t="s">
+      <c r="A1225" s="4" t="s">
         <v>2452</v>
       </c>
       <c r="B1225" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1225" s="10" t="s">
+      <c r="C1225" s="4" t="s">
         <v>2453</v>
       </c>
       <c r="D1225" s="15"/>
@@ -25422,7 +25437,7 @@
       <c r="A1226" s="4" t="s">
         <v>2454</v>
       </c>
-      <c r="B1226" s="5" t="s">
+      <c r="B1226" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C1226" s="4" t="s">
@@ -25431,13 +25446,13 @@
       <c r="D1226" s="15"/>
     </row>
     <row r="1227" ht="22.5" customHeight="1">
-      <c r="A1227" s="4" t="s">
+      <c r="A1227" s="10" t="s">
         <v>2456</v>
       </c>
       <c r="B1227" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1227" s="4" t="s">
+      <c r="C1227" s="10" t="s">
         <v>2457</v>
       </c>
       <c r="D1227" s="15"/>
@@ -25491,13 +25506,13 @@
       <c r="D1231" s="15"/>
     </row>
     <row r="1232" ht="22.5" customHeight="1">
-      <c r="A1232" s="10" t="s">
+      <c r="A1232" s="4" t="s">
         <v>2466</v>
       </c>
       <c r="B1232" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1232" s="10" t="s">
+      <c r="C1232" s="4" t="s">
         <v>2467</v>
       </c>
       <c r="D1232" s="15"/>
@@ -25527,25 +25542,25 @@
       <c r="D1234" s="15"/>
     </row>
     <row r="1235" ht="22.5" customHeight="1">
-      <c r="A1235" s="10" t="s">
+      <c r="A1235" s="4" t="s">
         <v>2472</v>
       </c>
       <c r="B1235" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1235" s="10" t="s">
+      <c r="C1235" s="4" t="s">
         <v>2473</v>
       </c>
       <c r="D1235" s="15"/>
     </row>
     <row r="1236" ht="22.5" customHeight="1">
-      <c r="A1236" s="4" t="s">
+      <c r="A1236" s="10" t="s">
         <v>2474</v>
       </c>
       <c r="B1236" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1236" s="4" t="s">
+      <c r="C1236" s="10" t="s">
         <v>2475</v>
       </c>
       <c r="D1236" s="15"/>
@@ -25599,13 +25614,13 @@
       <c r="D1240" s="15"/>
     </row>
     <row r="1241" ht="22.5" customHeight="1">
-      <c r="A1241" s="4" t="s">
+      <c r="A1241" s="10" t="s">
         <v>2484</v>
       </c>
       <c r="B1241" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1241" s="4" t="s">
+      <c r="C1241" s="10" t="s">
         <v>2485</v>
       </c>
       <c r="D1241" s="15"/>
@@ -25623,13 +25638,13 @@
       <c r="D1242" s="15"/>
     </row>
     <row r="1243" ht="22.5" customHeight="1">
-      <c r="A1243" s="10" t="s">
+      <c r="A1243" s="4" t="s">
         <v>2488</v>
       </c>
       <c r="B1243" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1243" s="10" t="s">
+      <c r="C1243" s="4" t="s">
         <v>2489</v>
       </c>
       <c r="D1243" s="15"/>
@@ -25671,25 +25686,25 @@
       <c r="D1246" s="15"/>
     </row>
     <row r="1247" ht="22.5" customHeight="1">
-      <c r="A1247" s="4" t="s">
+      <c r="A1247" s="10" t="s">
         <v>2496</v>
       </c>
       <c r="B1247" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1247" s="4" t="s">
+      <c r="C1247" s="10" t="s">
         <v>2497</v>
       </c>
       <c r="D1247" s="15"/>
     </row>
     <row r="1248" ht="22.5" customHeight="1">
-      <c r="A1248" s="10" t="s">
+      <c r="A1248" s="4" t="s">
         <v>2498</v>
       </c>
       <c r="B1248" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1248" s="10" t="s">
+      <c r="C1248" s="4" t="s">
         <v>2499</v>
       </c>
       <c r="D1248" s="15"/>
@@ -25731,13 +25746,13 @@
       <c r="D1251" s="15"/>
     </row>
     <row r="1252" ht="22.5" customHeight="1">
-      <c r="A1252" s="4" t="s">
+      <c r="A1252" s="10" t="s">
         <v>2506</v>
       </c>
       <c r="B1252" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1252" s="4" t="s">
+      <c r="C1252" s="10" t="s">
         <v>2507</v>
       </c>
       <c r="D1252" s="15"/>
@@ -25755,37 +25770,37 @@
       <c r="D1253" s="15"/>
     </row>
     <row r="1254" ht="22.5" customHeight="1">
-      <c r="A1254" s="10" t="s">
+      <c r="A1254" s="4" t="s">
         <v>2510</v>
       </c>
       <c r="B1254" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1254" s="10" t="s">
+      <c r="C1254" s="4" t="s">
         <v>2511</v>
       </c>
       <c r="D1254" s="15"/>
     </row>
     <row r="1255" ht="22.5" customHeight="1">
-      <c r="A1255" s="10" t="s">
+      <c r="A1255" s="4" t="s">
         <v>2512</v>
       </c>
       <c r="B1255" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1255" s="10" t="s">
+      <c r="C1255" s="4" t="s">
         <v>2513</v>
       </c>
       <c r="D1255" s="15"/>
     </row>
     <row r="1256" ht="22.5" customHeight="1">
-      <c r="A1256" s="4" t="s">
+      <c r="A1256" s="10" t="s">
         <v>2514</v>
       </c>
       <c r="B1256" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1256" s="4" t="s">
+      <c r="C1256" s="10" t="s">
         <v>2515</v>
       </c>
       <c r="D1256" s="15"/>
@@ -25827,13 +25842,13 @@
       <c r="D1259" s="15"/>
     </row>
     <row r="1260" ht="22.5" customHeight="1">
-      <c r="A1260" s="10" t="s">
+      <c r="A1260" s="4" t="s">
         <v>2522</v>
       </c>
       <c r="B1260" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1260" s="10" t="s">
+      <c r="C1260" s="4" t="s">
         <v>2523</v>
       </c>
       <c r="D1260" s="15"/>
@@ -25851,37 +25866,37 @@
       <c r="D1261" s="15"/>
     </row>
     <row r="1262" ht="22.5" customHeight="1">
-      <c r="A1262" s="4" t="s">
+      <c r="A1262" s="10" t="s">
         <v>2526</v>
       </c>
       <c r="B1262" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1262" s="4" t="s">
+      <c r="C1262" s="10" t="s">
         <v>2527</v>
       </c>
       <c r="D1262" s="15"/>
     </row>
     <row r="1263" ht="22.5" customHeight="1">
-      <c r="A1263" s="4" t="s">
+      <c r="A1263" s="10" t="s">
         <v>2528</v>
       </c>
       <c r="B1263" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1263" s="4" t="s">
+      <c r="C1263" s="10" t="s">
         <v>2529</v>
       </c>
       <c r="D1263" s="15"/>
     </row>
     <row r="1264" ht="22.5" customHeight="1">
-      <c r="A1264" s="10" t="s">
+      <c r="A1264" s="4" t="s">
         <v>2530</v>
       </c>
       <c r="B1264" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1264" s="10" t="s">
+      <c r="C1264" s="4" t="s">
         <v>2531</v>
       </c>
       <c r="D1264" s="15"/>
@@ -25899,49 +25914,49 @@
       <c r="D1265" s="15"/>
     </row>
     <row r="1266" ht="22.5" customHeight="1">
-      <c r="A1266" s="4" t="s">
+      <c r="A1266" s="10" t="s">
         <v>2534</v>
       </c>
       <c r="B1266" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1266" s="4" t="s">
+      <c r="C1266" s="10" t="s">
         <v>2535</v>
       </c>
       <c r="D1266" s="15"/>
     </row>
     <row r="1267" ht="22.5" customHeight="1">
-      <c r="A1267" s="10" t="s">
+      <c r="A1267" s="4" t="s">
         <v>2536</v>
       </c>
       <c r="B1267" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1267" s="10" t="s">
+      <c r="C1267" s="4" t="s">
         <v>2537</v>
       </c>
       <c r="D1267" s="15"/>
     </row>
     <row r="1268" ht="22.5" customHeight="1">
-      <c r="A1268" s="10" t="s">
+      <c r="A1268" s="4" t="s">
         <v>2538</v>
       </c>
       <c r="B1268" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1268" s="10" t="s">
+      <c r="C1268" s="4" t="s">
         <v>2539</v>
       </c>
       <c r="D1268" s="15"/>
     </row>
     <row r="1269" ht="22.5" customHeight="1">
-      <c r="A1269" s="4" t="s">
+      <c r="A1269" s="10" t="s">
         <v>2540</v>
       </c>
       <c r="B1269" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1269" s="4" t="s">
+      <c r="C1269" s="10" t="s">
         <v>2541</v>
       </c>
       <c r="D1269" s="15"/>
@@ -25975,7 +25990,7 @@
         <v>2546</v>
       </c>
       <c r="B1272" s="5" t="s">
-        <v>224</v>
+        <v>4</v>
       </c>
       <c r="C1272" s="10" t="s">
         <v>2547</v>
@@ -25986,8 +26001,8 @@
       <c r="A1273" s="4" t="s">
         <v>2548</v>
       </c>
-      <c r="B1273" s="9" t="s">
-        <v>72</v>
+      <c r="B1273" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C1273" s="4" t="s">
         <v>2549</v>
@@ -25995,13 +26010,13 @@
       <c r="D1273" s="15"/>
     </row>
     <row r="1274" ht="22.5" customHeight="1">
-      <c r="A1274" s="4" t="s">
+      <c r="A1274" s="10" t="s">
         <v>2550</v>
       </c>
-      <c r="B1274" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1274" s="4" t="s">
+      <c r="B1274" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1274" s="10" t="s">
         <v>2551</v>
       </c>
       <c r="D1274" s="15"/>
@@ -26010,7 +26025,7 @@
       <c r="A1275" s="4" t="s">
         <v>2552</v>
       </c>
-      <c r="B1275" s="7" t="s">
+      <c r="B1275" s="9" t="s">
         <v>72</v>
       </c>
       <c r="C1275" s="4" t="s">
@@ -26019,13 +26034,13 @@
       <c r="D1275" s="15"/>
     </row>
     <row r="1276" ht="22.5" customHeight="1">
-      <c r="A1276" s="10" t="s">
+      <c r="A1276" s="4" t="s">
         <v>2554</v>
       </c>
-      <c r="B1276" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1276" s="10" t="s">
+      <c r="B1276" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1276" s="4" t="s">
         <v>2555</v>
       </c>
       <c r="D1276" s="15"/>
@@ -26035,7 +26050,7 @@
         <v>2556</v>
       </c>
       <c r="B1277" s="7" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="C1277" s="4" t="s">
         <v>2557</v>
@@ -26043,13 +26058,13 @@
       <c r="D1277" s="15"/>
     </row>
     <row r="1278" ht="22.5" customHeight="1">
-      <c r="A1278" s="4" t="s">
+      <c r="A1278" s="10" t="s">
         <v>2558</v>
       </c>
-      <c r="B1278" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1278" s="4" t="s">
+      <c r="B1278" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1278" s="10" t="s">
         <v>2559</v>
       </c>
       <c r="D1278" s="15"/>
@@ -26058,7 +26073,7 @@
       <c r="A1279" s="4" t="s">
         <v>2560</v>
       </c>
-      <c r="B1279" s="5" t="s">
+      <c r="B1279" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C1279" s="4" t="s">
@@ -26070,7 +26085,7 @@
       <c r="A1280" s="4" t="s">
         <v>2562</v>
       </c>
-      <c r="B1280" s="7" t="s">
+      <c r="B1280" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C1280" s="4" t="s">
@@ -26079,13 +26094,13 @@
       <c r="D1280" s="15"/>
     </row>
     <row r="1281" ht="22.5" customHeight="1">
-      <c r="A1281" s="10" t="s">
+      <c r="A1281" s="4" t="s">
         <v>2564</v>
       </c>
       <c r="B1281" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1281" s="10" t="s">
+      <c r="C1281" s="4" t="s">
         <v>2565</v>
       </c>
       <c r="D1281" s="15"/>
@@ -26094,7 +26109,7 @@
       <c r="A1282" s="4" t="s">
         <v>2566</v>
       </c>
-      <c r="B1282" s="5" t="s">
+      <c r="B1282" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C1282" s="4" t="s">
@@ -26103,13 +26118,13 @@
       <c r="D1282" s="15"/>
     </row>
     <row r="1283" ht="22.5" customHeight="1">
-      <c r="A1283" s="4" t="s">
+      <c r="A1283" s="10" t="s">
         <v>2568</v>
       </c>
-      <c r="B1283" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1283" s="4" t="s">
+      <c r="B1283" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1283" s="10" t="s">
         <v>2569</v>
       </c>
       <c r="D1283" s="15"/>
@@ -26130,7 +26145,7 @@
       <c r="A1285" s="4" t="s">
         <v>2572</v>
       </c>
-      <c r="B1285" s="5" t="s">
+      <c r="B1285" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C1285" s="4" t="s">
@@ -26139,13 +26154,13 @@
       <c r="D1285" s="15"/>
     </row>
     <row r="1286" ht="22.5" customHeight="1">
-      <c r="A1286" s="10" t="s">
+      <c r="A1286" s="4" t="s">
         <v>2574</v>
       </c>
       <c r="B1286" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1286" s="10" t="s">
+      <c r="C1286" s="4" t="s">
         <v>2575</v>
       </c>
       <c r="D1286" s="15"/>
@@ -26175,25 +26190,25 @@
       <c r="D1288" s="15"/>
     </row>
     <row r="1289" ht="22.5" customHeight="1">
-      <c r="A1289" s="10" t="s">
+      <c r="A1289" s="4" t="s">
         <v>2580</v>
       </c>
       <c r="B1289" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1289" s="10" t="s">
+      <c r="C1289" s="4" t="s">
         <v>2581</v>
       </c>
       <c r="D1289" s="15"/>
     </row>
     <row r="1290" ht="22.5" customHeight="1">
-      <c r="A1290" s="4" t="s">
+      <c r="A1290" s="10" t="s">
         <v>2582</v>
       </c>
       <c r="B1290" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1290" s="4" t="s">
+      <c r="C1290" s="10" t="s">
         <v>2583</v>
       </c>
       <c r="D1290" s="15"/>
@@ -26202,7 +26217,7 @@
       <c r="A1291" s="10" t="s">
         <v>2584</v>
       </c>
-      <c r="B1291" s="7" t="s">
+      <c r="B1291" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C1291" s="10" t="s">
@@ -26211,37 +26226,37 @@
       <c r="D1291" s="15"/>
     </row>
     <row r="1292" ht="22.5" customHeight="1">
-      <c r="A1292" s="10" t="s">
+      <c r="A1292" s="4" t="s">
         <v>2586</v>
       </c>
       <c r="B1292" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1292" s="10" t="s">
+      <c r="C1292" s="4" t="s">
         <v>2587</v>
       </c>
       <c r="D1292" s="15"/>
     </row>
     <row r="1293" ht="22.5" customHeight="1">
-      <c r="A1293" s="4" t="s">
+      <c r="A1293" s="10" t="s">
         <v>2588</v>
       </c>
-      <c r="B1293" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1293" s="4" t="s">
+      <c r="B1293" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1293" s="10" t="s">
         <v>2589</v>
       </c>
       <c r="D1293" s="15"/>
     </row>
     <row r="1294" ht="22.5" customHeight="1">
-      <c r="A1294" s="4" t="s">
+      <c r="A1294" s="10" t="s">
         <v>2590</v>
       </c>
-      <c r="B1294" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1294" s="4" t="s">
+      <c r="B1294" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1294" s="10" t="s">
         <v>2591</v>
       </c>
       <c r="D1294" s="15"/>
@@ -26250,8 +26265,8 @@
       <c r="A1295" s="4" t="s">
         <v>2592</v>
       </c>
-      <c r="B1295" s="5" t="s">
-        <v>7</v>
+      <c r="B1295" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C1295" s="4" t="s">
         <v>2593</v>
@@ -26262,7 +26277,7 @@
       <c r="A1296" s="4" t="s">
         <v>2594</v>
       </c>
-      <c r="B1296" s="5" t="s">
+      <c r="B1296" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C1296" s="4" t="s">
@@ -26283,49 +26298,49 @@
       <c r="D1297" s="15"/>
     </row>
     <row r="1298" ht="22.5" customHeight="1">
-      <c r="A1298" s="10" t="s">
+      <c r="A1298" s="4" t="s">
         <v>2598</v>
       </c>
-      <c r="B1298" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1298" s="10" t="s">
+      <c r="B1298" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1298" s="4" t="s">
         <v>2599</v>
       </c>
       <c r="D1298" s="15"/>
     </row>
     <row r="1299" ht="22.5" customHeight="1">
-      <c r="A1299" s="10" t="s">
+      <c r="A1299" s="4" t="s">
         <v>2600</v>
       </c>
       <c r="B1299" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1299" s="4" t="s">
+        <v>2601</v>
+      </c>
+      <c r="D1299" s="15"/>
+    </row>
+    <row r="1300" ht="22.5" customHeight="1">
+      <c r="A1300" s="10" t="s">
+        <v>2602</v>
+      </c>
+      <c r="B1300" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1300" s="10" t="s">
+        <v>2603</v>
+      </c>
+      <c r="D1300" s="15"/>
+    </row>
+    <row r="1301" ht="22.5" customHeight="1">
+      <c r="A1301" s="10" t="s">
+        <v>2604</v>
+      </c>
+      <c r="B1301" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="C1299" s="10" t="s">
-        <v>2601</v>
-      </c>
-      <c r="D1299" s="15"/>
-    </row>
-    <row r="1300" ht="22.5" customHeight="1">
-      <c r="A1300" s="4" t="s">
-        <v>2602</v>
-      </c>
-      <c r="B1300" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1300" s="4" t="s">
-        <v>2603</v>
-      </c>
-      <c r="D1300" s="15"/>
-    </row>
-    <row r="1301" ht="22.5" customHeight="1">
-      <c r="A1301" s="4" t="s">
-        <v>2604</v>
-      </c>
-      <c r="B1301" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1301" s="4" t="s">
+      <c r="C1301" s="10" t="s">
         <v>2605</v>
       </c>
       <c r="D1301" s="15"/>
@@ -26334,34 +26349,34 @@
       <c r="A1302" s="4" t="s">
         <v>2606</v>
       </c>
-      <c r="B1302" s="5" t="s">
-        <v>7</v>
+      <c r="B1302" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C1302" s="4" t="s">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="D1302" s="15"/>
     </row>
     <row r="1303" ht="22.5" customHeight="1">
       <c r="A1303" s="4" t="s">
-        <v>2607</v>
-      </c>
-      <c r="B1303" s="9" t="s">
-        <v>64</v>
+        <v>2608</v>
+      </c>
+      <c r="B1303" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="C1303" s="4" t="s">
-        <v>2608</v>
+        <v>2609</v>
       </c>
       <c r="D1303" s="15"/>
     </row>
     <row r="1304" ht="22.5" customHeight="1">
-      <c r="A1304" s="10" t="s">
-        <v>2609</v>
+      <c r="A1304" s="4" t="s">
+        <v>2610</v>
       </c>
       <c r="B1304" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C1304" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1304" s="4" t="s">
         <v>2610</v>
       </c>
       <c r="D1304" s="15"/>
@@ -26370,8 +26385,8 @@
       <c r="A1305" s="4" t="s">
         <v>2611</v>
       </c>
-      <c r="B1305" s="5" t="s">
-        <v>7</v>
+      <c r="B1305" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C1305" s="4" t="s">
         <v>2612</v>
@@ -26379,25 +26394,25 @@
       <c r="D1305" s="15"/>
     </row>
     <row r="1306" ht="22.5" customHeight="1">
-      <c r="A1306" s="4" t="s">
+      <c r="A1306" s="10" t="s">
         <v>2613</v>
       </c>
       <c r="B1306" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1306" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1306" s="10" t="s">
         <v>2614</v>
       </c>
       <c r="D1306" s="15"/>
     </row>
     <row r="1307" ht="22.5" customHeight="1">
-      <c r="A1307" s="10" t="s">
+      <c r="A1307" s="4" t="s">
         <v>2615</v>
       </c>
-      <c r="B1307" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="C1307" s="10" t="s">
+      <c r="B1307" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1307" s="4" t="s">
         <v>2616</v>
       </c>
       <c r="D1307" s="15"/>
@@ -26407,7 +26422,7 @@
         <v>2617</v>
       </c>
       <c r="B1308" s="5" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="C1308" s="4" t="s">
         <v>2618</v>
@@ -26415,13 +26430,13 @@
       <c r="D1308" s="15"/>
     </row>
     <row r="1309" ht="22.5" customHeight="1">
-      <c r="A1309" s="4" t="s">
+      <c r="A1309" s="10" t="s">
         <v>2619</v>
       </c>
-      <c r="B1309" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1309" s="4" t="s">
+      <c r="B1309" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1309" s="10" t="s">
         <v>2620</v>
       </c>
       <c r="D1309" s="15"/>
@@ -26439,13 +26454,13 @@
       <c r="D1310" s="15"/>
     </row>
     <row r="1311" ht="22.5" customHeight="1">
-      <c r="A1311" s="10" t="s">
+      <c r="A1311" s="4" t="s">
         <v>2623</v>
       </c>
-      <c r="B1311" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1311" s="10" t="s">
+      <c r="B1311" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1311" s="4" t="s">
         <v>2624</v>
       </c>
       <c r="D1311" s="15"/>
@@ -26466,8 +26481,8 @@
       <c r="A1313" s="10" t="s">
         <v>2627</v>
       </c>
-      <c r="B1313" s="9" t="s">
-        <v>72</v>
+      <c r="B1313" s="7" t="s">
+        <v>7</v>
       </c>
       <c r="C1313" s="10" t="s">
         <v>2628</v>
@@ -26490,8 +26505,8 @@
       <c r="A1315" s="10" t="s">
         <v>2631</v>
       </c>
-      <c r="B1315" s="5" t="s">
-        <v>7</v>
+      <c r="B1315" s="9" t="s">
+        <v>72</v>
       </c>
       <c r="C1315" s="10" t="s">
         <v>2632</v>
@@ -26526,7 +26541,7 @@
       <c r="A1318" s="4" t="s">
         <v>2637</v>
       </c>
-      <c r="B1318" s="7" t="s">
+      <c r="B1318" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C1318" s="4" t="s">
@@ -26535,13 +26550,13 @@
       <c r="D1318" s="15"/>
     </row>
     <row r="1319" ht="22.5" customHeight="1">
-      <c r="A1319" s="4" t="s">
+      <c r="A1319" s="10" t="s">
         <v>2639</v>
       </c>
       <c r="B1319" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1319" s="4" t="s">
+      <c r="C1319" s="10" t="s">
         <v>2640</v>
       </c>
       <c r="D1319" s="15"/>
@@ -26562,8 +26577,8 @@
       <c r="A1321" s="4" t="s">
         <v>2643</v>
       </c>
-      <c r="B1321" s="9" t="s">
-        <v>64</v>
+      <c r="B1321" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C1321" s="4" t="s">
         <v>2644</v>
@@ -26571,13 +26586,13 @@
       <c r="D1321" s="15"/>
     </row>
     <row r="1322" ht="22.5" customHeight="1">
-      <c r="A1322" s="10" t="s">
+      <c r="A1322" s="4" t="s">
         <v>2645</v>
       </c>
-      <c r="B1322" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1322" s="10" t="s">
+      <c r="B1322" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1322" s="4" t="s">
         <v>2646</v>
       </c>
       <c r="D1322" s="15"/>
@@ -26586,8 +26601,8 @@
       <c r="A1323" s="4" t="s">
         <v>2647</v>
       </c>
-      <c r="B1323" s="5" t="s">
-        <v>7</v>
+      <c r="B1323" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C1323" s="4" t="s">
         <v>2648</v>
@@ -26610,22 +26625,22 @@
       <c r="A1325" s="4" t="s">
         <v>2651</v>
       </c>
-      <c r="B1325" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1325" s="10" t="s">
+      <c r="B1325" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1325" s="4" t="s">
         <v>2652</v>
       </c>
       <c r="D1325" s="15"/>
     </row>
     <row r="1326" ht="22.5" customHeight="1">
-      <c r="A1326" s="4" t="s">
+      <c r="A1326" s="10" t="s">
         <v>2653</v>
       </c>
-      <c r="B1326" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1326" s="4" t="s">
+      <c r="B1326" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1326" s="10" t="s">
         <v>2654</v>
       </c>
       <c r="D1326" s="15"/>
@@ -26634,20 +26649,20 @@
       <c r="A1327" s="4" t="s">
         <v>2655</v>
       </c>
-      <c r="B1327" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1327" s="4" t="s">
+      <c r="B1327" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1327" s="10" t="s">
         <v>2656</v>
       </c>
       <c r="D1327" s="15"/>
     </row>
     <row r="1328" ht="22.5" customHeight="1">
-      <c r="A1328" s="10" t="s">
+      <c r="A1328" s="4" t="s">
         <v>2657</v>
       </c>
-      <c r="B1328" s="7" t="s">
-        <v>7</v>
+      <c r="B1328" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C1328" s="4" t="s">
         <v>2658</v>
@@ -26658,7 +26673,7 @@
       <c r="A1329" s="4" t="s">
         <v>2659</v>
       </c>
-      <c r="B1329" s="5" t="s">
+      <c r="B1329" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C1329" s="4" t="s">
@@ -26667,10 +26682,10 @@
       <c r="D1329" s="15"/>
     </row>
     <row r="1330" ht="22.5" customHeight="1">
-      <c r="A1330" s="4" t="s">
+      <c r="A1330" s="10" t="s">
         <v>2661</v>
       </c>
-      <c r="B1330" s="5" t="s">
+      <c r="B1330" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C1330" s="4" t="s">
@@ -26679,49 +26694,49 @@
       <c r="D1330" s="15"/>
     </row>
     <row r="1331" ht="22.5" customHeight="1">
-      <c r="A1331" s="10" t="s">
+      <c r="A1331" s="4" t="s">
         <v>2663</v>
       </c>
       <c r="B1331" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1331" s="10" t="s">
+      <c r="C1331" s="4" t="s">
         <v>2664</v>
       </c>
       <c r="D1331" s="15"/>
     </row>
     <row r="1332" ht="22.5" customHeight="1">
-      <c r="A1332" s="10" t="s">
+      <c r="A1332" s="4" t="s">
         <v>2665</v>
       </c>
       <c r="B1332" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1332" s="10" t="s">
+      <c r="C1332" s="4" t="s">
         <v>2666</v>
       </c>
       <c r="D1332" s="15"/>
     </row>
     <row r="1333" ht="22.5" customHeight="1">
-      <c r="A1333" s="4" t="s">
+      <c r="A1333" s="10" t="s">
         <v>2667</v>
       </c>
       <c r="B1333" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1333" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1333" s="10" t="s">
         <v>2668</v>
       </c>
       <c r="D1333" s="15"/>
     </row>
     <row r="1334" ht="22.5" customHeight="1">
-      <c r="A1334" s="4" t="s">
+      <c r="A1334" s="10" t="s">
         <v>2669</v>
       </c>
       <c r="B1334" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1334" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1334" s="10" t="s">
         <v>2670</v>
       </c>
       <c r="D1334" s="15"/>
@@ -26731,7 +26746,7 @@
         <v>2671</v>
       </c>
       <c r="B1335" s="5" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="C1335" s="4" t="s">
         <v>2672</v>
@@ -26739,97 +26754,97 @@
       <c r="D1335" s="15"/>
     </row>
     <row r="1336" ht="22.5" customHeight="1">
-      <c r="A1336" s="10" t="s">
+      <c r="A1336" s="4" t="s">
         <v>2673</v>
       </c>
-      <c r="B1336" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1336" s="10" t="s">
+      <c r="B1336" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1336" s="4" t="s">
         <v>2674</v>
       </c>
       <c r="D1336" s="15"/>
     </row>
     <row r="1337" ht="22.5" customHeight="1">
-      <c r="A1337" s="10" t="s">
+      <c r="A1337" s="4" t="s">
         <v>2675</v>
       </c>
-      <c r="B1337" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1337" s="10" t="s">
+      <c r="B1337" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1337" s="4" t="s">
         <v>2676</v>
       </c>
       <c r="D1337" s="15"/>
     </row>
     <row r="1338" ht="22.5" customHeight="1">
-      <c r="A1338" s="4" t="s">
+      <c r="A1338" s="10" t="s">
         <v>2677</v>
       </c>
-      <c r="B1338" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1338" s="4" t="s">
+      <c r="B1338" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1338" s="10" t="s">
         <v>2678</v>
       </c>
       <c r="D1338" s="15"/>
     </row>
     <row r="1339" ht="22.5" customHeight="1">
-      <c r="A1339" s="4" t="s">
+      <c r="A1339" s="10" t="s">
         <v>2679</v>
       </c>
-      <c r="B1339" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1339" s="4" t="s">
+      <c r="B1339" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1339" s="10" t="s">
         <v>2680</v>
       </c>
       <c r="D1339" s="15"/>
     </row>
     <row r="1340" ht="22.5" customHeight="1">
-      <c r="A1340" s="10" t="s">
+      <c r="A1340" s="4" t="s">
         <v>2681</v>
       </c>
-      <c r="B1340" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1340" s="10" t="s">
+      <c r="B1340" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1340" s="4" t="s">
         <v>2682</v>
       </c>
       <c r="D1340" s="15"/>
     </row>
     <row r="1341" ht="22.5" customHeight="1">
-      <c r="A1341" s="10" t="s">
+      <c r="A1341" s="4" t="s">
+        <v>2683</v>
+      </c>
+      <c r="B1341" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1341" s="4" t="s">
+        <v>2684</v>
+      </c>
+      <c r="D1341" s="15"/>
+    </row>
+    <row r="1342" ht="22.5" customHeight="1">
+      <c r="A1342" s="10" t="s">
+        <v>2685</v>
+      </c>
+      <c r="B1342" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1342" s="10" t="s">
+        <v>2686</v>
+      </c>
+      <c r="D1342" s="15"/>
+    </row>
+    <row r="1343" ht="22.5" customHeight="1">
+      <c r="A1343" s="10" t="s">
         <v>1465</v>
       </c>
-      <c r="B1341" s="9" t="s">
+      <c r="B1343" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C1341" s="10" t="s">
-        <v>2683</v>
-      </c>
-      <c r="D1341" s="15"/>
-    </row>
-    <row r="1342" ht="22.5" customHeight="1">
-      <c r="A1342" s="4" t="s">
-        <v>2684</v>
-      </c>
-      <c r="B1342" s="5" t="s">
-        <v>854</v>
-      </c>
-      <c r="C1342" s="4" t="s">
-        <v>2685</v>
-      </c>
-      <c r="D1342" s="15"/>
-    </row>
-    <row r="1343" ht="22.5" customHeight="1">
-      <c r="A1343" s="4" t="s">
-        <v>2686</v>
-      </c>
-      <c r="B1343" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1343" s="4" t="s">
+      <c r="C1343" s="10" t="s">
         <v>2687</v>
       </c>
       <c r="D1343" s="15"/>
@@ -26838,8 +26853,8 @@
       <c r="A1344" s="4" t="s">
         <v>2688</v>
       </c>
-      <c r="B1344" s="9" t="s">
-        <v>7</v>
+      <c r="B1344" s="5" t="s">
+        <v>854</v>
       </c>
       <c r="C1344" s="4" t="s">
         <v>2689</v>
@@ -26850,8 +26865,8 @@
       <c r="A1345" s="4" t="s">
         <v>2690</v>
       </c>
-      <c r="B1345" s="9" t="s">
-        <v>64</v>
+      <c r="B1345" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C1345" s="4" t="s">
         <v>2691</v>
@@ -26863,7 +26878,7 @@
         <v>2692</v>
       </c>
       <c r="B1346" s="9" t="s">
-        <v>854</v>
+        <v>7</v>
       </c>
       <c r="C1346" s="4" t="s">
         <v>2693</v>
@@ -26875,7 +26890,7 @@
         <v>2694</v>
       </c>
       <c r="B1347" s="9" t="s">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="C1347" s="4" t="s">
         <v>2695</v>
@@ -26883,13 +26898,13 @@
       <c r="D1347" s="15"/>
     </row>
     <row r="1348" ht="22.5" customHeight="1">
-      <c r="A1348" s="10" t="s">
+      <c r="A1348" s="4" t="s">
         <v>2696</v>
       </c>
-      <c r="B1348" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1348" s="10" t="s">
+      <c r="B1348" s="9" t="s">
+        <v>854</v>
+      </c>
+      <c r="C1348" s="4" t="s">
         <v>2697</v>
       </c>
       <c r="D1348" s="15"/>
@@ -26907,13 +26922,13 @@
       <c r="D1349" s="15"/>
     </row>
     <row r="1350" ht="22.5" customHeight="1">
-      <c r="A1350" s="4" t="s">
+      <c r="A1350" s="10" t="s">
         <v>2700</v>
       </c>
-      <c r="B1350" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C1350" s="4" t="s">
+      <c r="B1350" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1350" s="10" t="s">
         <v>2701</v>
       </c>
       <c r="D1350" s="15"/>
@@ -26922,7 +26937,7 @@
       <c r="A1351" s="4" t="s">
         <v>2702</v>
       </c>
-      <c r="B1351" s="5" t="s">
+      <c r="B1351" s="9" t="s">
         <v>115</v>
       </c>
       <c r="C1351" s="4" t="s">
@@ -26947,7 +26962,7 @@
         <v>2706</v>
       </c>
       <c r="B1353" s="5" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="C1353" s="4" t="s">
         <v>2707</v>
@@ -26955,25 +26970,25 @@
       <c r="D1353" s="15"/>
     </row>
     <row r="1354" ht="22.5" customHeight="1">
-      <c r="A1354" s="10" t="s">
+      <c r="A1354" s="4" t="s">
         <v>2708</v>
       </c>
-      <c r="B1354" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1354" s="10" t="s">
+      <c r="B1354" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1354" s="4" t="s">
         <v>2709</v>
       </c>
       <c r="D1354" s="15"/>
     </row>
     <row r="1355" ht="22.5" customHeight="1">
-      <c r="A1355" s="10" t="s">
+      <c r="A1355" s="4" t="s">
         <v>2710</v>
       </c>
       <c r="B1355" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C1355" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1355" s="4" t="s">
         <v>2711</v>
       </c>
       <c r="D1355" s="15"/>
@@ -26983,7 +26998,7 @@
         <v>2712</v>
       </c>
       <c r="B1356" s="5" t="s">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="C1356" s="10" t="s">
         <v>2713</v>
@@ -26991,25 +27006,25 @@
       <c r="D1356" s="15"/>
     </row>
     <row r="1357" ht="22.5" customHeight="1">
-      <c r="A1357" s="4" t="s">
+      <c r="A1357" s="10" t="s">
         <v>2714</v>
       </c>
-      <c r="B1357" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1357" s="4" t="s">
+      <c r="B1357" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1357" s="10" t="s">
         <v>2715</v>
       </c>
       <c r="D1357" s="15"/>
     </row>
     <row r="1358" ht="22.5" customHeight="1">
-      <c r="A1358" s="4" t="s">
+      <c r="A1358" s="10" t="s">
         <v>2716</v>
       </c>
       <c r="B1358" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1358" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1358" s="10" t="s">
         <v>2717</v>
       </c>
       <c r="D1358" s="15"/>
@@ -27018,8 +27033,8 @@
       <c r="A1359" s="4" t="s">
         <v>2718</v>
       </c>
-      <c r="B1359" s="5" t="s">
-        <v>7</v>
+      <c r="B1359" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C1359" s="4" t="s">
         <v>2719</v>
@@ -27027,13 +27042,13 @@
       <c r="D1359" s="15"/>
     </row>
     <row r="1360" ht="22.5" customHeight="1">
-      <c r="A1360" s="10" t="s">
+      <c r="A1360" s="4" t="s">
         <v>2720</v>
       </c>
-      <c r="B1360" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1360" s="10" t="s">
+      <c r="B1360" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1360" s="4" t="s">
         <v>2721</v>
       </c>
       <c r="D1360" s="15"/>
@@ -27051,13 +27066,13 @@
       <c r="D1361" s="15"/>
     </row>
     <row r="1362" ht="22.5" customHeight="1">
-      <c r="A1362" s="4" t="s">
+      <c r="A1362" s="10" t="s">
         <v>2724</v>
       </c>
-      <c r="B1362" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1362" s="4" t="s">
+      <c r="B1362" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1362" s="10" t="s">
         <v>2725</v>
       </c>
       <c r="D1362" s="15"/>
@@ -27075,13 +27090,13 @@
       <c r="D1363" s="15"/>
     </row>
     <row r="1364" ht="22.5" customHeight="1">
-      <c r="A1364" s="10" t="s">
+      <c r="A1364" s="4" t="s">
         <v>2728</v>
       </c>
       <c r="B1364" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1364" s="10" t="s">
+      <c r="C1364" s="4" t="s">
         <v>2729</v>
       </c>
       <c r="D1364" s="15"/>
@@ -27099,73 +27114,73 @@
       <c r="D1365" s="15"/>
     </row>
     <row r="1366" ht="22.5" customHeight="1">
-      <c r="A1366" s="4" t="s">
+      <c r="A1366" s="10" t="s">
         <v>2732</v>
       </c>
       <c r="B1366" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1366" s="4" t="s">
+      <c r="C1366" s="10" t="s">
         <v>2733</v>
       </c>
       <c r="D1366" s="15"/>
     </row>
     <row r="1367" ht="22.5" customHeight="1">
-      <c r="A1367" s="10" t="s">
+      <c r="A1367" s="4" t="s">
         <v>2734</v>
       </c>
       <c r="B1367" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1367" s="10" t="s">
+      <c r="C1367" s="4" t="s">
         <v>2735</v>
       </c>
       <c r="D1367" s="15"/>
     </row>
     <row r="1368" ht="22.5" customHeight="1">
-      <c r="A1368" s="10" t="s">
+      <c r="A1368" s="4" t="s">
         <v>2736</v>
       </c>
       <c r="B1368" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1368" s="10" t="s">
+      <c r="C1368" s="4" t="s">
         <v>2737</v>
       </c>
       <c r="D1368" s="15"/>
     </row>
     <row r="1369" ht="22.5" customHeight="1">
-      <c r="A1369" s="4" t="s">
+      <c r="A1369" s="10" t="s">
         <v>2738</v>
       </c>
-      <c r="B1369" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1369" s="4" t="s">
+      <c r="B1369" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1369" s="10" t="s">
         <v>2739</v>
       </c>
       <c r="D1369" s="15"/>
     </row>
     <row r="1370" ht="22.5" customHeight="1">
-      <c r="A1370" s="4" t="s">
+      <c r="A1370" s="10" t="s">
         <v>2740</v>
       </c>
       <c r="B1370" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1370" s="4" t="s">
+      <c r="C1370" s="10" t="s">
         <v>2741</v>
       </c>
       <c r="D1370" s="15"/>
     </row>
     <row r="1371" ht="22.5" customHeight="1">
-      <c r="A1371" s="10" t="s">
+      <c r="A1371" s="4" t="s">
         <v>2742</v>
       </c>
       <c r="B1371" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1371" s="10" t="s">
+      <c r="C1371" s="4" t="s">
         <v>2743</v>
       </c>
       <c r="D1371" s="15"/>
@@ -27183,37 +27198,37 @@
       <c r="D1372" s="15"/>
     </row>
     <row r="1373" ht="22.5" customHeight="1">
-      <c r="A1373" s="4" t="s">
+      <c r="A1373" s="10" t="s">
         <v>2746</v>
       </c>
-      <c r="B1373" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1373" s="4" t="s">
+      <c r="B1373" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1373" s="10" t="s">
         <v>2747</v>
       </c>
       <c r="D1373" s="15"/>
     </row>
     <row r="1374" ht="22.5" customHeight="1">
-      <c r="A1374" s="10" t="s">
+      <c r="A1374" s="4" t="s">
         <v>2748</v>
       </c>
-      <c r="B1374" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1374" s="10" t="s">
+      <c r="B1374" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1374" s="4" t="s">
         <v>2749</v>
       </c>
       <c r="D1374" s="15"/>
     </row>
     <row r="1375" ht="22.5" customHeight="1">
-      <c r="A1375" s="10" t="s">
+      <c r="A1375" s="4" t="s">
         <v>2750</v>
       </c>
       <c r="B1375" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1375" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1375" s="4" t="s">
         <v>2751</v>
       </c>
       <c r="D1375" s="15"/>
@@ -27222,8 +27237,8 @@
       <c r="A1376" s="10" t="s">
         <v>2752</v>
       </c>
-      <c r="B1376" s="5" t="s">
-        <v>49</v>
+      <c r="B1376" s="9" t="s">
+        <v>7</v>
       </c>
       <c r="C1376" s="10" t="s">
         <v>2753</v>
@@ -27231,25 +27246,25 @@
       <c r="D1376" s="15"/>
     </row>
     <row r="1377" ht="22.5" customHeight="1">
-      <c r="A1377" s="4" t="s">
+      <c r="A1377" s="10" t="s">
         <v>2754</v>
       </c>
-      <c r="B1377" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C1377" s="4" t="s">
+      <c r="B1377" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1377" s="10" t="s">
         <v>2755</v>
       </c>
       <c r="D1377" s="15"/>
     </row>
     <row r="1378" ht="22.5" customHeight="1">
-      <c r="A1378" s="4" t="s">
+      <c r="A1378" s="10" t="s">
         <v>2756</v>
       </c>
-      <c r="B1378" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1378" s="4" t="s">
+      <c r="B1378" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1378" s="10" t="s">
         <v>2757</v>
       </c>
       <c r="D1378" s="15"/>
@@ -27259,7 +27274,7 @@
         <v>2758</v>
       </c>
       <c r="B1379" s="23" t="s">
-        <v>623</v>
+        <v>72</v>
       </c>
       <c r="C1379" s="4" t="s">
         <v>2759</v>
@@ -27270,17 +27285,41 @@
       <c r="A1380" s="4" t="s">
         <v>2760</v>
       </c>
-      <c r="B1380" s="21" t="s">
-        <v>7</v>
+      <c r="B1380" s="24" t="s">
+        <v>64</v>
       </c>
       <c r="C1380" s="4" t="s">
         <v>2761</v>
       </c>
       <c r="D1380" s="15"/>
     </row>
+    <row r="1381" ht="22.5" customHeight="1">
+      <c r="A1381" s="4" t="s">
+        <v>2762</v>
+      </c>
+      <c r="B1381" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="C1381" s="4" t="s">
+        <v>2763</v>
+      </c>
+      <c r="D1381" s="15"/>
+    </row>
+    <row r="1382" ht="22.5" customHeight="1">
+      <c r="A1382" s="4" t="s">
+        <v>2764</v>
+      </c>
+      <c r="B1382" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1382" s="4" t="s">
+        <v>2765</v>
+      </c>
+      <c r="D1382" s="15"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B1380">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B1382">
       <formula1>"adjective,adverb,adverb-preposition,conjunction,noun,numeral,phrase,preposition,pronoun,verb,interjection,prefix,suffix,article"</formula1>
     </dataValidation>
   </dataValidations>
@@ -27302,303 +27341,303 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="24" t="s">
-        <v>2762</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>1980</v>
+      <c r="A1" s="25" t="s">
+        <v>2766</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>1984</v>
       </c>
       <c r="D1" s="8"/>
-      <c r="E1" s="25" t="s">
-        <v>2763</v>
+      <c r="E1" s="26" t="s">
+        <v>2767</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="26" t="s">
-        <v>2764</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>2765</v>
+      <c r="A2" s="27" t="s">
+        <v>2768</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>2769</v>
       </c>
       <c r="D2" s="8"/>
-      <c r="E2" s="27" t="s">
-        <v>2766</v>
+      <c r="E2" s="28" t="s">
+        <v>2770</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="26" t="s">
-        <v>2767</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>2768</v>
+      <c r="A3" s="27" t="s">
+        <v>2771</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>2772</v>
       </c>
       <c r="D3" s="8"/>
-      <c r="E3" s="27" t="s">
-        <v>2769</v>
+      <c r="E3" s="28" t="s">
+        <v>2773</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="26" t="s">
-        <v>2770</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>2771</v>
+      <c r="A4" s="27" t="s">
+        <v>2774</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>2775</v>
       </c>
       <c r="D4" s="8"/>
-      <c r="E4" s="27" t="s">
-        <v>2772</v>
+      <c r="E4" s="28" t="s">
+        <v>2776</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="24" t="s">
-        <v>2773</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>2774</v>
+      <c r="A5" s="25" t="s">
+        <v>2777</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>2778</v>
       </c>
       <c r="D5" s="8"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="24" t="s">
-        <v>2775</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>2776</v>
-      </c>
-      <c r="C6" s="26" t="s">
+      <c r="A6" s="25" t="s">
+        <v>2779</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>2780</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>1428</v>
       </c>
       <c r="D6" s="8"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="24" t="s">
-        <v>2777</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>2778</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>2779</v>
+      <c r="A7" s="25" t="s">
+        <v>2781</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>2782</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>2783</v>
       </c>
       <c r="D7" s="15"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="24" t="s">
-        <v>2780</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>2781</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>2782</v>
+      <c r="A8" s="25" t="s">
+        <v>2784</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>2785</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>2786</v>
       </c>
       <c r="D8" s="8"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="24" t="s">
-        <v>2783</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>2784</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>2785</v>
+      <c r="A9" s="25" t="s">
+        <v>2787</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>2788</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>2789</v>
       </c>
       <c r="D9" s="8"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="24" t="s">
-        <v>2786</v>
-      </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="27" t="s">
-        <v>2787</v>
+      <c r="A10" s="25" t="s">
+        <v>2790</v>
+      </c>
+      <c r="B10" s="25"/>
+      <c r="C10" s="28" t="s">
+        <v>2791</v>
       </c>
       <c r="D10" s="8"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="24" t="s">
-        <v>2788</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>2789</v>
+      <c r="A11" s="25" t="s">
+        <v>2792</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>2793</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="25" t="s">
+        <v>2794</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>2000</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+    </row>
+    <row r="14" ht="18.75" customHeight="1">
+      <c r="A14" s="27" t="s">
+        <v>2768</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>2000</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+    </row>
+    <row r="15" ht="18.75" customHeight="1">
+      <c r="A15" s="27" t="s">
+        <v>2771</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>2795</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+    </row>
+    <row r="16" ht="18.75" customHeight="1">
+      <c r="A16" s="27" t="s">
+        <v>2774</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>2796</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+    </row>
+    <row r="17" ht="18.75" customHeight="1">
+      <c r="A17" s="25" t="s">
+        <v>2777</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>2797</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+    </row>
+    <row r="18" ht="18.75" customHeight="1">
+      <c r="A18" s="25" t="s">
+        <v>2779</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>2780</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+    </row>
+    <row r="19" ht="18.75" customHeight="1">
+      <c r="A19" s="25" t="s">
+        <v>2781</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>2798</v>
+      </c>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+    </row>
+    <row r="20" ht="18.75" customHeight="1">
+      <c r="A20" s="25" t="s">
+        <v>2784</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>2799</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>2800</v>
+      </c>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+    </row>
+    <row r="21" ht="18.75" customHeight="1">
+      <c r="A21" s="25" t="s">
+        <v>2787</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>2788</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>2789</v>
+      </c>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+    </row>
+    <row r="22" ht="18.75" customHeight="1">
+      <c r="A22" s="25" t="s">
         <v>2790</v>
       </c>
-      <c r="B13" s="25" t="s">
-        <v>1996</v>
-      </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-    </row>
-    <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="26" t="s">
-        <v>2764</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>1996</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-    </row>
-    <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="26" t="s">
-        <v>2767</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>2791</v>
-      </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-    </row>
-    <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="26" t="s">
-        <v>2770</v>
-      </c>
-      <c r="B16" s="27" t="s">
+      <c r="B22" s="25"/>
+      <c r="C22" s="28" t="s">
+        <v>2801</v>
+      </c>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+    </row>
+    <row r="23" ht="18.75" customHeight="1">
+      <c r="A23" s="25" t="s">
         <v>2792</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-    </row>
-    <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="24" t="s">
-        <v>2773</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>2793</v>
-      </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-    </row>
-    <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" s="24" t="s">
-        <v>2775</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>2776</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>1428</v>
-      </c>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-    </row>
-    <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" s="24" t="s">
-        <v>2777</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>1996</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>2794</v>
-      </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-    </row>
-    <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="24" t="s">
-        <v>2780</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>2795</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>2796</v>
-      </c>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-    </row>
-    <row r="21" ht="18.75" customHeight="1">
-      <c r="A21" s="24" t="s">
-        <v>2783</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>2784</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>2785</v>
-      </c>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-    </row>
-    <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="24" t="s">
-        <v>2786</v>
-      </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="27" t="s">
-        <v>2797</v>
-      </c>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-    </row>
-    <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" s="24" t="s">
-        <v>2788</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>1996</v>
-      </c>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
+      <c r="B23" s="28" t="s">
+        <v>2000</v>
+      </c>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -27634,774 +27673,774 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="25" t="s">
-        <v>2798</v>
-      </c>
-      <c r="B1" s="29" t="s">
+      <c r="A1" s="26" t="s">
+        <v>2802</v>
+      </c>
+      <c r="B1" s="30" t="s">
         <v>422</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="29" t="s">
-        <v>2799</v>
+      <c r="D1" s="31"/>
+      <c r="E1" s="30" t="s">
+        <v>2803</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="B2" s="29" t="s">
-        <v>2784</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>2785</v>
-      </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="29" t="s">
-        <v>2800</v>
-      </c>
-      <c r="G2" s="29" t="s">
-        <v>2801</v>
-      </c>
-      <c r="I2" s="29" t="s">
-        <v>2802</v>
+      <c r="B2" s="30" t="s">
+        <v>2788</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>2789</v>
+      </c>
+      <c r="D2" s="31"/>
+      <c r="E2" s="30" t="s">
+        <v>2804</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>2805</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>2806</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="29" t="s">
-        <v>2803</v>
-      </c>
-      <c r="B3" s="30" t="s">
+      <c r="A3" s="30" t="s">
+        <v>2807</v>
+      </c>
+      <c r="B3" s="31" t="s">
         <v>422</v>
       </c>
-      <c r="C3" s="30" t="s">
-        <v>2804</v>
-      </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="29" t="s">
+      <c r="C3" s="31" t="s">
+        <v>2808</v>
+      </c>
+      <c r="D3" s="31"/>
+      <c r="E3" s="30" t="s">
+        <v>2809</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>2810</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>2809</v>
+      </c>
+      <c r="H3" s="30" t="s">
+        <v>2810</v>
+      </c>
+      <c r="I3" s="30" t="s">
+        <v>2809</v>
+      </c>
+      <c r="J3" s="30" t="s">
+        <v>2810</v>
+      </c>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="30" t="s">
+        <v>2811</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31" t="s">
+        <v>2813</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>932</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>2814</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>2815</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>2816</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="30" t="s">
+        <v>2817</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>2818</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>2819</v>
+      </c>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>2820</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>1307</v>
+      </c>
+      <c r="I5" s="31" t="s">
+        <v>2821</v>
+      </c>
+      <c r="J5" s="31" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customHeight="1">
+      <c r="A6" s="33"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31" t="s">
+        <v>2822</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>422</v>
+      </c>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="31" t="s">
+        <v>2823</v>
+      </c>
+      <c r="J6" s="31" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="7" ht="18.75" customHeight="1">
+      <c r="A7" s="26" t="s">
+        <v>2824</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D7" s="34"/>
+      <c r="I7" s="31" t="s">
+        <v>2825</v>
+      </c>
+      <c r="J7" s="31" t="s">
+        <v>2826</v>
+      </c>
+    </row>
+    <row r="8" ht="18.75" customHeight="1">
+      <c r="B8" s="30" t="s">
+        <v>2788</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>2789</v>
+      </c>
+      <c r="D8" s="31"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="31" t="s">
+        <v>2827</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="9" ht="18.75" customHeight="1">
+      <c r="A9" s="30" t="s">
+        <v>2807</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>2828</v>
+      </c>
+      <c r="D9" s="31"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="31" t="s">
+        <v>2829</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" ht="18.75" customHeight="1">
+      <c r="A10" s="30" t="s">
+        <v>2811</v>
+      </c>
+      <c r="D10" s="34"/>
+      <c r="E10" s="26" t="s">
+        <v>2806</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>416</v>
+      </c>
+      <c r="H10" s="34"/>
+      <c r="I10" s="31" t="s">
+        <v>2830</v>
+      </c>
+      <c r="J10" s="31" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="11" ht="18.75" customHeight="1">
+      <c r="A11" s="30" t="s">
+        <v>2817</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>2831</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>2832</v>
+      </c>
+      <c r="D11" s="34"/>
+      <c r="F11" s="30" t="s">
+        <v>2788</v>
+      </c>
+      <c r="G11" s="30" t="s">
+        <v>2789</v>
+      </c>
+      <c r="H11" s="35"/>
+      <c r="I11" s="31" t="s">
+        <v>2833</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="12" ht="18.75" customHeight="1">
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="30" t="s">
+        <v>2807</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>416</v>
+      </c>
+      <c r="G12" s="31" t="s">
+        <v>2834</v>
+      </c>
+      <c r="H12" s="35"/>
+      <c r="I12" s="31" t="s">
+        <v>2835</v>
+      </c>
+      <c r="J12" s="31" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="13" ht="18.75" customHeight="1">
+      <c r="A13" s="26" t="s">
         <v>2805</v>
       </c>
-      <c r="F3" s="29" t="s">
-        <v>2806</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>2805</v>
-      </c>
-      <c r="H3" s="29" t="s">
-        <v>2806</v>
-      </c>
-      <c r="I3" s="29" t="s">
-        <v>2805</v>
-      </c>
-      <c r="J3" s="29" t="s">
-        <v>2806</v>
-      </c>
-    </row>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="B13" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="D13" s="34"/>
+      <c r="E13" s="30" t="s">
+        <v>2811</v>
+      </c>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31" t="s">
+        <v>2836</v>
+      </c>
+      <c r="J13" s="31" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="14" ht="18.75" customHeight="1">
+      <c r="B14" s="30" t="s">
+        <v>2788</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>2789</v>
+      </c>
+      <c r="D14" s="34"/>
+      <c r="E14" s="30" t="s">
+        <v>2817</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>2837</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>2838</v>
+      </c>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31" t="s">
+        <v>2839</v>
+      </c>
+      <c r="J14" s="31" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="15" ht="18.75" customHeight="1">
+      <c r="A15" s="30" t="s">
         <v>2807</v>
       </c>
-      <c r="C4" s="30" t="s">
-        <v>2808</v>
-      </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30" t="s">
-        <v>2809</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>932</v>
-      </c>
-      <c r="G4" s="30" t="s">
-        <v>2810</v>
-      </c>
-      <c r="H4" s="30" t="s">
+      <c r="B15" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>2840</v>
+      </c>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31" t="s">
+        <v>2841</v>
+      </c>
+      <c r="J15" s="31" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="16" ht="18.75" customHeight="1">
+      <c r="A16" s="30" t="s">
         <v>2811</v>
       </c>
-      <c r="I4" s="30" t="s">
-        <v>2812</v>
-      </c>
-      <c r="J4" s="30" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="29" t="s">
-        <v>2813</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>2814</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>2815</v>
-      </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>1321</v>
-      </c>
-      <c r="G5" s="30" t="s">
-        <v>2816</v>
-      </c>
-      <c r="H5" s="30" t="s">
-        <v>1307</v>
-      </c>
-      <c r="I5" s="30" t="s">
+      <c r="B16" s="31" t="s">
+        <v>2842</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>2843</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>2844</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>2764</v>
+      </c>
+      <c r="H16" s="35"/>
+      <c r="I16" s="31" t="s">
+        <v>2845</v>
+      </c>
+      <c r="J16" s="31" t="s">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="17" ht="18.75" customHeight="1">
+      <c r="A17" s="30" t="s">
         <v>2817</v>
       </c>
-      <c r="J5" s="30" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="32"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30" t="s">
-        <v>2818</v>
-      </c>
-      <c r="F6" s="31" t="s">
-        <v>422</v>
-      </c>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="30" t="s">
-        <v>2819</v>
-      </c>
-      <c r="J6" s="30" t="s">
-        <v>1680</v>
-      </c>
-    </row>
-    <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="25" t="s">
-        <v>2820</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>1321</v>
-      </c>
-      <c r="D7" s="33"/>
-      <c r="I7" s="30" t="s">
-        <v>2821</v>
-      </c>
-      <c r="J7" s="30" t="s">
-        <v>2822</v>
-      </c>
-    </row>
-    <row r="8" ht="18.75" customHeight="1">
-      <c r="B8" s="29" t="s">
-        <v>2784</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>2785</v>
-      </c>
-      <c r="D8" s="30"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="30" t="s">
-        <v>2823</v>
-      </c>
-      <c r="J8" s="30" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="29" t="s">
-        <v>2803</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>1321</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>2824</v>
-      </c>
-      <c r="D9" s="30"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="30" t="s">
-        <v>2825</v>
-      </c>
-      <c r="J9" s="30" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="29" t="s">
+      <c r="B17" s="31" t="s">
+        <v>2846</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>2847</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>2788</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>2789</v>
+      </c>
+      <c r="H17" s="35"/>
+      <c r="I17" s="31" t="s">
+        <v>2848</v>
+      </c>
+      <c r="J17" s="31" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="18" ht="18.75" customHeight="1">
+      <c r="E18" s="30" t="s">
         <v>2807</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="25" t="s">
-        <v>2802</v>
-      </c>
-      <c r="F10" s="29" t="s">
-        <v>416</v>
-      </c>
-      <c r="H10" s="33"/>
-      <c r="I10" s="30" t="s">
-        <v>2826</v>
-      </c>
-      <c r="J10" s="30" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="29" t="s">
-        <v>2813</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>2827</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>2828</v>
-      </c>
-      <c r="D11" s="33"/>
-      <c r="F11" s="29" t="s">
-        <v>2784</v>
-      </c>
-      <c r="G11" s="29" t="s">
-        <v>2785</v>
-      </c>
-      <c r="H11" s="34"/>
-      <c r="I11" s="30" t="s">
-        <v>2829</v>
-      </c>
-      <c r="J11" s="30" t="s">
-        <v>1283</v>
-      </c>
-    </row>
-    <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="33"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="29" t="s">
-        <v>2803</v>
-      </c>
-      <c r="F12" s="30" t="s">
-        <v>416</v>
-      </c>
-      <c r="G12" s="30" t="s">
-        <v>2830</v>
-      </c>
-      <c r="H12" s="34"/>
-      <c r="I12" s="30" t="s">
-        <v>2831</v>
-      </c>
-      <c r="J12" s="30" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="25" t="s">
-        <v>2801</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>256</v>
-      </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="29" t="s">
+      <c r="F18" s="31" t="s">
+        <v>2764</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>2849</v>
+      </c>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+    </row>
+    <row r="19" ht="18.75" customHeight="1">
+      <c r="A19" s="31"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="30" t="s">
+        <v>2811</v>
+      </c>
+      <c r="H19" s="31"/>
+    </row>
+    <row r="20" ht="18.75" customHeight="1">
+      <c r="A20" s="31"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="30" t="s">
+        <v>2817</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>2850</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>2851</v>
+      </c>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+    </row>
+    <row r="21" ht="18.75" customHeight="1">
+      <c r="A21" s="31"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="H21" s="31"/>
+    </row>
+    <row r="22" ht="18.75" customHeight="1">
+      <c r="A22" s="30" t="s">
+        <v>2852</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>2788</v>
+      </c>
+      <c r="H22" s="30" t="s">
+        <v>2853</v>
+      </c>
+    </row>
+    <row r="23" ht="18.75" customHeight="1">
+      <c r="B23" s="30" t="s">
+        <v>2854</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>2855</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>2856</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>2857</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>2858</v>
+      </c>
+      <c r="G23" s="30" t="s">
+        <v>2859</v>
+      </c>
+      <c r="H23" s="30" t="s">
+        <v>2860</v>
+      </c>
+      <c r="I23" s="30" t="s">
+        <v>2861</v>
+      </c>
+      <c r="J23" s="30" t="s">
+        <v>2862</v>
+      </c>
+    </row>
+    <row r="24" ht="18.75" customHeight="1">
+      <c r="A24" s="30" t="s">
         <v>2807</v>
       </c>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30" t="s">
-        <v>2832</v>
-      </c>
-      <c r="J13" s="30" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="14" ht="18.75" customHeight="1">
-      <c r="B14" s="29" t="s">
-        <v>2784</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>2785</v>
-      </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="29" t="s">
-        <v>2813</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>2833</v>
-      </c>
-      <c r="G14" s="30" t="s">
-        <v>2834</v>
-      </c>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30" t="s">
-        <v>2835</v>
-      </c>
-      <c r="J14" s="30" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="29" t="s">
-        <v>2803</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>2836</v>
-      </c>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30" t="s">
-        <v>2837</v>
-      </c>
-      <c r="J15" s="30" t="s">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="29" t="s">
+      <c r="B24" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>2863</v>
+      </c>
+      <c r="D24" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="31" t="s">
+        <v>2864</v>
+      </c>
+      <c r="G24" s="31" t="s">
+        <v>2865</v>
+      </c>
+      <c r="H24" s="31" t="s">
+        <v>544</v>
+      </c>
+      <c r="I24" s="31" t="s">
+        <v>544</v>
+      </c>
+      <c r="J24" s="31" t="s">
+        <v>2866</v>
+      </c>
+    </row>
+    <row r="25" ht="18.75" customHeight="1">
+      <c r="A25" s="30" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>2867</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="I25" s="31" t="s">
+        <v>2866</v>
+      </c>
+    </row>
+    <row r="26" ht="18.75" customHeight="1">
+      <c r="A26" s="30" t="s">
+        <v>2817</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="31" t="s">
+        <v>2868</v>
+      </c>
+      <c r="G26" s="31" t="s">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="27" ht="18.75" customHeight="1">
+      <c r="A27" s="30" t="s">
+        <v>2852</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>2789</v>
+      </c>
+      <c r="H27" s="30" t="s">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="28" ht="18.75" customHeight="1">
+      <c r="B28" s="30" t="s">
+        <v>2854</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>2855</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>2856</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>2857</v>
+      </c>
+      <c r="F28" s="30" t="s">
+        <v>2858</v>
+      </c>
+      <c r="G28" s="30" t="s">
+        <v>2859</v>
+      </c>
+      <c r="H28" s="30" t="s">
+        <v>2860</v>
+      </c>
+      <c r="I28" s="30" t="s">
+        <v>2861</v>
+      </c>
+      <c r="J28" s="30" t="s">
+        <v>2862</v>
+      </c>
+    </row>
+    <row r="29" ht="18.75" customHeight="1">
+      <c r="A29" s="30" t="s">
         <v>2807</v>
       </c>
-      <c r="B16" s="30" t="s">
-        <v>2838</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>2839</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>2840</v>
-      </c>
-      <c r="F16" s="29" t="s">
-        <v>2760</v>
-      </c>
-      <c r="H16" s="34"/>
-      <c r="I16" s="30" t="s">
-        <v>2841</v>
-      </c>
-      <c r="J16" s="30" t="s">
-        <v>2760</v>
-      </c>
-    </row>
-    <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="29" t="s">
-        <v>2813</v>
-      </c>
-      <c r="B17" s="30" t="s">
-        <v>2842</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>2843</v>
-      </c>
-      <c r="F17" s="29" t="s">
-        <v>2784</v>
-      </c>
-      <c r="G17" s="29" t="s">
-        <v>2785</v>
-      </c>
-      <c r="H17" s="34"/>
-      <c r="I17" s="30" t="s">
-        <v>2844</v>
-      </c>
-      <c r="J17" s="30" t="s">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="18" ht="18.75" customHeight="1">
-      <c r="E18" s="29" t="s">
-        <v>2803</v>
-      </c>
-      <c r="F18" s="30" t="s">
-        <v>2760</v>
-      </c>
-      <c r="G18" s="30" t="s">
-        <v>2845</v>
-      </c>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-    </row>
-    <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" s="30"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="29" t="s">
-        <v>2807</v>
-      </c>
-      <c r="H19" s="30"/>
-    </row>
-    <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="30"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="29" t="s">
-        <v>2813</v>
-      </c>
-      <c r="F20" s="30" t="s">
-        <v>2846</v>
-      </c>
-      <c r="G20" s="30" t="s">
-        <v>2847</v>
-      </c>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-    </row>
-    <row r="21" ht="18.75" customHeight="1">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="H21" s="30"/>
-    </row>
-    <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="29" t="s">
-        <v>2848</v>
-      </c>
-      <c r="B22" s="29" t="s">
-        <v>2784</v>
-      </c>
-      <c r="H22" s="29" t="s">
-        <v>2849</v>
-      </c>
-    </row>
-    <row r="23" ht="18.75" customHeight="1">
-      <c r="B23" s="29" t="s">
-        <v>2850</v>
-      </c>
-      <c r="C23" s="29" t="s">
-        <v>2851</v>
-      </c>
-      <c r="D23" s="29" t="s">
-        <v>2852</v>
-      </c>
-      <c r="E23" s="29" t="s">
-        <v>2853</v>
-      </c>
-      <c r="F23" s="29" t="s">
-        <v>2854</v>
-      </c>
-      <c r="G23" s="29" t="s">
-        <v>2855</v>
-      </c>
-      <c r="H23" s="29" t="s">
-        <v>2856</v>
-      </c>
-      <c r="I23" s="29" t="s">
-        <v>2857</v>
-      </c>
-      <c r="J23" s="29" t="s">
-        <v>2858</v>
-      </c>
-    </row>
-    <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" s="29" t="s">
-        <v>2803</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>2859</v>
-      </c>
-      <c r="D24" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="30" t="s">
+      <c r="B29" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>2871</v>
+      </c>
+      <c r="D29" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" s="31" t="s">
+        <v>2872</v>
+      </c>
+      <c r="G29" s="31" t="s">
+        <v>2873</v>
+      </c>
+      <c r="H29" s="31" t="s">
+        <v>542</v>
+      </c>
+      <c r="J29" s="31" t="s">
+        <v>2874</v>
+      </c>
+    </row>
+    <row r="30" ht="18.75" customHeight="1">
+      <c r="A30" s="30" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B30" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="31" t="s">
+        <v>2875</v>
+      </c>
+      <c r="D30" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="H30" s="31" t="s">
+        <v>2874</v>
+      </c>
+    </row>
+    <row r="31" ht="18.75" customHeight="1">
+      <c r="A31" s="30" t="s">
+        <v>2817</v>
+      </c>
+      <c r="B31" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>2876</v>
+      </c>
+      <c r="D31" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="31" t="s">
+        <v>2877</v>
+      </c>
+      <c r="G31" s="31" t="s">
+        <v>2878</v>
+      </c>
+      <c r="H31" s="31" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="32" ht="18.75" customHeight="1">
+      <c r="A32" s="30"/>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="30" t="s">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="33" ht="18.75" customHeight="1">
+      <c r="A33" s="30"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="30" t="s">
         <v>2860</v>
       </c>
-      <c r="G24" s="30" t="s">
+      <c r="I33" s="30" t="s">
         <v>2861</v>
       </c>
-      <c r="H24" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="I24" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="J24" s="30" t="s">
+      <c r="J33" s="30" t="s">
         <v>2862</v>
       </c>
     </row>
-    <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="29" t="s">
-        <v>2807</v>
-      </c>
-      <c r="B25" s="30" t="s">
-        <v>2863</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="I25" s="30" t="s">
+    <row r="34" ht="18.75" customHeight="1">
+      <c r="A34" s="30"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31" t="s">
+        <v>2865</v>
+      </c>
+      <c r="I34" s="31" t="s">
+        <v>2865</v>
+      </c>
+      <c r="J34" s="31" t="s">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="35" ht="18.75" customHeight="1">
+      <c r="A35" s="30"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="I35" s="31" t="s">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="36" ht="18.75" customHeight="1">
+      <c r="A36" s="30"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+    </row>
+    <row r="37" ht="18.75" customHeight="1">
+      <c r="A37" s="30"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="30" t="s">
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="38" ht="18.75" customHeight="1">
+      <c r="A38" s="30"/>
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="30" t="s">
+        <v>2860</v>
+      </c>
+      <c r="I38" s="30" t="s">
+        <v>2861</v>
+      </c>
+      <c r="J38" s="30" t="s">
         <v>2862</v>
       </c>
     </row>
-    <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="29" t="s">
-        <v>2813</v>
-      </c>
-      <c r="B26" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="30" t="s">
-        <v>2864</v>
-      </c>
-      <c r="G26" s="30" t="s">
-        <v>2865</v>
-      </c>
-    </row>
-    <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="29" t="s">
-        <v>2848</v>
-      </c>
-      <c r="B27" s="29" t="s">
-        <v>2785</v>
-      </c>
-      <c r="H27" s="29" t="s">
-        <v>2866</v>
-      </c>
-    </row>
-    <row r="28" ht="18.75" customHeight="1">
-      <c r="B28" s="29" t="s">
-        <v>2850</v>
-      </c>
-      <c r="C28" s="29" t="s">
-        <v>2851</v>
-      </c>
-      <c r="D28" s="29" t="s">
-        <v>2852</v>
-      </c>
-      <c r="E28" s="29" t="s">
-        <v>2853</v>
-      </c>
-      <c r="F28" s="29" t="s">
-        <v>2854</v>
-      </c>
-      <c r="G28" s="29" t="s">
-        <v>2855</v>
-      </c>
-      <c r="H28" s="29" t="s">
-        <v>2856</v>
-      </c>
-      <c r="I28" s="29" t="s">
-        <v>2857</v>
-      </c>
-      <c r="J28" s="29" t="s">
-        <v>2858</v>
-      </c>
-    </row>
-    <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="29" t="s">
-        <v>2803</v>
-      </c>
-      <c r="B29" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="30" t="s">
-        <v>2867</v>
-      </c>
-      <c r="D29" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="F29" s="30" t="s">
-        <v>2868</v>
-      </c>
-      <c r="G29" s="30" t="s">
-        <v>2869</v>
-      </c>
-      <c r="H29" s="30" t="s">
-        <v>542</v>
-      </c>
-      <c r="J29" s="30" t="s">
-        <v>2870</v>
-      </c>
-    </row>
-    <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" s="29" t="s">
-        <v>2807</v>
-      </c>
-      <c r="B30" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>2871</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="H30" s="30" t="s">
-        <v>2870</v>
-      </c>
-    </row>
-    <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" s="29" t="s">
-        <v>2813</v>
-      </c>
-      <c r="B31" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="30" t="s">
-        <v>2872</v>
-      </c>
-      <c r="D31" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="F31" s="30" t="s">
+    <row r="39" ht="18.75" customHeight="1">
+      <c r="A39" s="30"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="31" t="s">
         <v>2873</v>
       </c>
-      <c r="G31" s="30" t="s">
-        <v>2874</v>
-      </c>
-      <c r="H31" s="30" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" s="29"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="29" t="s">
-        <v>2875</v>
-      </c>
-    </row>
-    <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" s="29"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="29" t="s">
-        <v>2856</v>
-      </c>
-      <c r="I33" s="29" t="s">
-        <v>2857</v>
-      </c>
-      <c r="J33" s="29" t="s">
-        <v>2858</v>
-      </c>
-    </row>
-    <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" s="29"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30" t="s">
-        <v>2861</v>
-      </c>
-      <c r="I34" s="30" t="s">
-        <v>2861</v>
-      </c>
-      <c r="J34" s="30" t="s">
-        <v>2876</v>
-      </c>
-    </row>
-    <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" s="29"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="I35" s="30" t="s">
-        <v>2876</v>
-      </c>
-    </row>
-    <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" s="29"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-    </row>
-    <row r="37" ht="18.75" customHeight="1">
-      <c r="A37" s="29"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="29" t="s">
-        <v>2877</v>
-      </c>
-    </row>
-    <row r="38" ht="18.75" customHeight="1">
-      <c r="A38" s="29"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="29" t="s">
-        <v>2856</v>
-      </c>
-      <c r="I38" s="29" t="s">
-        <v>2857</v>
-      </c>
-      <c r="J38" s="29" t="s">
-        <v>2858</v>
-      </c>
-    </row>
-    <row r="39" ht="18.75" customHeight="1">
-      <c r="A39" s="29"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30" t="s">
-        <v>2869</v>
-      </c>
-      <c r="J39" s="30" t="s">
-        <v>2878</v>
+      <c r="J39" s="31" t="s">
+        <v>2882</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
-      <c r="A40" s="29"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30" t="s">
-        <v>2878</v>
+      <c r="A40" s="30"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31" t="s">
+        <v>2882</v>
       </c>
     </row>
     <row r="41" ht="18.75" customHeight="1">
-      <c r="A41" s="29"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30" t="s">
-        <v>2869</v>
+      <c r="A41" s="30"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31" t="s">
+        <v>2873</v>
       </c>
     </row>
   </sheetData>
@@ -28472,682 +28511,682 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="29" t="s">
-        <v>2879</v>
-      </c>
-      <c r="B1" s="35" t="s">
-        <v>2880</v>
-      </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
+      <c r="A1" s="30" t="s">
+        <v>2883</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>2884</v>
+      </c>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="E2" s="33"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="34"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
+      <c r="A3" s="35"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="29" t="s">
-        <v>2881</v>
-      </c>
-      <c r="E4" s="33"/>
-      <c r="F4" s="29" t="s">
-        <v>2882</v>
-      </c>
-      <c r="J4" s="30"/>
+      <c r="A4" s="30" t="s">
+        <v>2885</v>
+      </c>
+      <c r="E4" s="34"/>
+      <c r="F4" s="30" t="s">
+        <v>2886</v>
+      </c>
+      <c r="J4" s="31"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="25" t="s">
-        <v>2784</v>
-      </c>
-      <c r="E5" s="33"/>
-      <c r="F5" s="25" t="s">
-        <v>2784</v>
-      </c>
-      <c r="J5" s="30"/>
+      <c r="A5" s="26" t="s">
+        <v>2788</v>
+      </c>
+      <c r="E5" s="34"/>
+      <c r="F5" s="26" t="s">
+        <v>2788</v>
+      </c>
+      <c r="J5" s="31"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="29" t="s">
-        <v>2800</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>2801</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>2802</v>
-      </c>
-      <c r="E6" s="33"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="29" t="s">
-        <v>2800</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>2801</v>
-      </c>
-      <c r="I6" s="29" t="s">
-        <v>2802</v>
-      </c>
-      <c r="J6" s="30"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="30" t="s">
+        <v>2804</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>2805</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>2806</v>
+      </c>
+      <c r="E6" s="34"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="30" t="s">
+        <v>2804</v>
+      </c>
+      <c r="H6" s="30" t="s">
+        <v>2805</v>
+      </c>
+      <c r="I6" s="30" t="s">
+        <v>2806</v>
+      </c>
+      <c r="J6" s="31"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="29" t="s">
-        <v>2803</v>
-      </c>
-      <c r="B7" s="30" t="s">
+      <c r="A7" s="30" t="s">
+        <v>2807</v>
+      </c>
+      <c r="B7" s="31" t="s">
         <v>1574</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="31" t="s">
         <v>1574</v>
       </c>
-      <c r="D7" s="30" t="s">
-        <v>2883</v>
-      </c>
-      <c r="E7" s="33"/>
-      <c r="F7" s="29" t="s">
-        <v>2803</v>
-      </c>
-      <c r="G7" s="30" t="s">
-        <v>1851</v>
-      </c>
-      <c r="H7" s="30" t="s">
-        <v>1851</v>
-      </c>
-      <c r="I7" s="30" t="s">
-        <v>2884</v>
-      </c>
-      <c r="J7" s="30"/>
+      <c r="D7" s="31" t="s">
+        <v>2887</v>
+      </c>
+      <c r="E7" s="34"/>
+      <c r="F7" s="30" t="s">
+        <v>2807</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>1855</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I7" s="31" t="s">
+        <v>2888</v>
+      </c>
+      <c r="J7" s="31"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="30" t="s">
+        <v>2811</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>2887</v>
+      </c>
+      <c r="E8" s="34"/>
+      <c r="F8" s="30" t="s">
+        <v>2811</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>2888</v>
+      </c>
+      <c r="J8" s="31"/>
+    </row>
+    <row r="9" ht="18.75" customHeight="1">
+      <c r="A9" s="30" t="s">
+        <v>2817</v>
+      </c>
+      <c r="E9" s="34"/>
+      <c r="F9" s="30" t="s">
+        <v>2817</v>
+      </c>
+      <c r="J9" s="31"/>
+    </row>
+    <row r="10" ht="18.75" customHeight="1">
+      <c r="A10" s="30" t="s">
+        <v>2789</v>
+      </c>
+      <c r="E10" s="34"/>
+      <c r="F10" s="30" t="s">
+        <v>2789</v>
+      </c>
+      <c r="J10" s="31"/>
+    </row>
+    <row r="11" ht="18.75" customHeight="1">
+      <c r="A11" s="26"/>
+      <c r="B11" s="30" t="s">
+        <v>2804</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>2805</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>2806</v>
+      </c>
+      <c r="E11" s="34"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="30" t="s">
+        <v>2804</v>
+      </c>
+      <c r="H11" s="30" t="s">
+        <v>2805</v>
+      </c>
+      <c r="I11" s="30" t="s">
+        <v>2806</v>
+      </c>
+      <c r="J11" s="31"/>
+    </row>
+    <row r="12" ht="18.75" customHeight="1">
+      <c r="A12" s="30" t="s">
         <v>2807</v>
       </c>
-      <c r="C8" s="30" t="s">
-        <v>2883</v>
-      </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="29" t="s">
+      <c r="B12" s="31" t="s">
+        <v>2889</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>1574</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>2890</v>
+      </c>
+      <c r="E12" s="34"/>
+      <c r="F12" s="30" t="s">
         <v>2807</v>
       </c>
-      <c r="H8" s="30" t="s">
-        <v>2884</v>
-      </c>
-      <c r="J8" s="30"/>
-    </row>
-    <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="29" t="s">
-        <v>2813</v>
-      </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="29" t="s">
-        <v>2813</v>
-      </c>
-      <c r="J9" s="30"/>
-    </row>
-    <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="29" t="s">
-        <v>2785</v>
-      </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="29" t="s">
-        <v>2785</v>
-      </c>
-      <c r="J10" s="30"/>
-    </row>
-    <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="29" t="s">
-        <v>2800</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>2801</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>2802</v>
-      </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="29" t="s">
-        <v>2800</v>
-      </c>
-      <c r="H11" s="29" t="s">
-        <v>2801</v>
-      </c>
-      <c r="I11" s="29" t="s">
-        <v>2802</v>
-      </c>
-      <c r="J11" s="30"/>
-    </row>
-    <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="29" t="s">
-        <v>2803</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>2885</v>
-      </c>
-      <c r="C12" s="30" t="s">
+      <c r="G12" s="31" t="s">
+        <v>2891</v>
+      </c>
+      <c r="H12" s="31" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I12" s="31" t="s">
+        <v>2888</v>
+      </c>
+      <c r="J12" s="31"/>
+    </row>
+    <row r="13" ht="18.75" customHeight="1">
+      <c r="A13" s="30" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>2892</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>2887</v>
+      </c>
+      <c r="E13" s="34"/>
+      <c r="F13" s="30" t="s">
+        <v>2811</v>
+      </c>
+      <c r="H13" s="31" t="s">
+        <v>2888</v>
+      </c>
+      <c r="J13" s="31"/>
+    </row>
+    <row r="14" ht="18.75" customHeight="1">
+      <c r="A14" s="30" t="s">
+        <v>2817</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>2889</v>
+      </c>
+      <c r="C14" s="31" t="s">
         <v>1574</v>
       </c>
-      <c r="D12" s="30" t="s">
-        <v>2886</v>
-      </c>
-      <c r="E12" s="33"/>
-      <c r="F12" s="29" t="s">
-        <v>2803</v>
-      </c>
-      <c r="G12" s="30" t="s">
-        <v>2887</v>
-      </c>
-      <c r="H12" s="30" t="s">
-        <v>1851</v>
-      </c>
-      <c r="I12" s="30" t="s">
-        <v>2884</v>
-      </c>
-      <c r="J12" s="30"/>
-    </row>
-    <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="29" t="s">
+      <c r="E14" s="34"/>
+      <c r="F14" s="30" t="s">
+        <v>2817</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>1855</v>
+      </c>
+      <c r="J14" s="31"/>
+    </row>
+    <row r="15" ht="18.75" customHeight="1">
+      <c r="A15" s="30" t="s">
+        <v>2893</v>
+      </c>
+      <c r="E15" s="34"/>
+      <c r="F15" s="30" t="s">
+        <v>2893</v>
+      </c>
+      <c r="J15" s="31"/>
+    </row>
+    <row r="16" ht="18.75" customHeight="1">
+      <c r="A16" s="30" t="s">
+        <v>2894</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>2895</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>2896</v>
+      </c>
+      <c r="D16" s="37"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="30" t="s">
+        <v>2894</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>2897</v>
+      </c>
+      <c r="H16" s="37"/>
+      <c r="J16" s="31"/>
+    </row>
+    <row r="17" ht="18.75" customHeight="1">
+      <c r="A17" s="30" t="s">
+        <v>2898</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>2899</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>2900</v>
+      </c>
+      <c r="E17" s="34"/>
+      <c r="F17" s="30" t="s">
+        <v>2898</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>2901</v>
+      </c>
+      <c r="J17" s="31"/>
+    </row>
+    <row r="18" ht="18.75" customHeight="1">
+      <c r="A18" s="30" t="s">
+        <v>2902</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>2903</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>2904</v>
+      </c>
+      <c r="E18" s="34"/>
+      <c r="F18" s="30" t="s">
+        <v>2902</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>1855</v>
+      </c>
+      <c r="J18" s="31"/>
+    </row>
+    <row r="19" ht="18.75" customHeight="1">
+      <c r="J19" s="31"/>
+    </row>
+    <row r="20" ht="18.75" customHeight="1">
+      <c r="A20" s="30" t="s">
+        <v>2905</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>2906</v>
+      </c>
+      <c r="J20" s="31"/>
+    </row>
+    <row r="21" ht="18.75" customHeight="1">
+      <c r="A21" s="26" t="s">
+        <v>2788</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>2788</v>
+      </c>
+      <c r="J21" s="31"/>
+    </row>
+    <row r="22" ht="18.75" customHeight="1">
+      <c r="A22" s="26"/>
+      <c r="B22" s="30" t="s">
+        <v>2804</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>2805</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>2806</v>
+      </c>
+      <c r="F22" s="26"/>
+      <c r="G22" s="30" t="s">
+        <v>2804</v>
+      </c>
+      <c r="H22" s="30" t="s">
+        <v>2805</v>
+      </c>
+      <c r="I22" s="30" t="s">
+        <v>2806</v>
+      </c>
+      <c r="J22" s="31"/>
+    </row>
+    <row r="23" ht="18.75" customHeight="1">
+      <c r="A23" s="30" t="s">
         <v>2807</v>
       </c>
-      <c r="B13" s="30" t="s">
-        <v>2888</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>2883</v>
-      </c>
-      <c r="E13" s="33"/>
-      <c r="F13" s="29" t="s">
+      <c r="B23" s="31" t="s">
+        <v>2907</v>
+      </c>
+      <c r="F23" s="30" t="s">
         <v>2807</v>
       </c>
-      <c r="H13" s="30" t="s">
-        <v>2884</v>
-      </c>
-      <c r="J13" s="30"/>
-    </row>
-    <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="29" t="s">
-        <v>2813</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>2885</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>1574</v>
-      </c>
-      <c r="E14" s="33"/>
-      <c r="F14" s="29" t="s">
-        <v>2813</v>
-      </c>
-      <c r="H14" s="30" t="s">
-        <v>1851</v>
-      </c>
-      <c r="J14" s="30"/>
-    </row>
-    <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="29" t="s">
-        <v>2889</v>
-      </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="29" t="s">
-        <v>2889</v>
-      </c>
-      <c r="J15" s="30"/>
-    </row>
-    <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="29" t="s">
-        <v>2890</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>2891</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>2892</v>
-      </c>
-      <c r="D16" s="36"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="29" t="s">
-        <v>2890</v>
-      </c>
-      <c r="G16" s="30" t="s">
+      <c r="G23" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="J23" s="31"/>
+    </row>
+    <row r="24" ht="18.75" customHeight="1">
+      <c r="A24" s="30" t="s">
+        <v>2811</v>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>2811</v>
+      </c>
+      <c r="J24" s="31"/>
+    </row>
+    <row r="25" ht="18.75" customHeight="1">
+      <c r="A25" s="30" t="s">
+        <v>2817</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>2817</v>
+      </c>
+      <c r="J25" s="31"/>
+    </row>
+    <row r="26" ht="18.75" customHeight="1">
+      <c r="A26" s="30" t="s">
+        <v>2789</v>
+      </c>
+      <c r="E26" s="34"/>
+      <c r="F26" s="30" t="s">
+        <v>2789</v>
+      </c>
+      <c r="J26" s="31"/>
+    </row>
+    <row r="27" ht="18.75" customHeight="1">
+      <c r="A27" s="26"/>
+      <c r="B27" s="30" t="s">
+        <v>2804</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>2805</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>2806</v>
+      </c>
+      <c r="E27" s="34"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="30" t="s">
+        <v>2804</v>
+      </c>
+      <c r="H27" s="30" t="s">
+        <v>2805</v>
+      </c>
+      <c r="I27" s="30" t="s">
+        <v>2806</v>
+      </c>
+      <c r="J27" s="31"/>
+    </row>
+    <row r="28" ht="18.75" customHeight="1">
+      <c r="A28" s="30" t="s">
+        <v>2807</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>2907</v>
+      </c>
+      <c r="E28" s="34"/>
+      <c r="F28" s="30" t="s">
+        <v>2807</v>
+      </c>
+      <c r="G28" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="J28" s="31"/>
+    </row>
+    <row r="29" ht="18.75" customHeight="1">
+      <c r="A29" s="30" t="s">
+        <v>2811</v>
+      </c>
+      <c r="E29" s="34"/>
+      <c r="F29" s="30" t="s">
+        <v>2811</v>
+      </c>
+      <c r="J29" s="31"/>
+    </row>
+    <row r="30" ht="18.75" customHeight="1">
+      <c r="A30" s="30" t="s">
+        <v>2817</v>
+      </c>
+      <c r="E30" s="34"/>
+      <c r="F30" s="30" t="s">
+        <v>2817</v>
+      </c>
+      <c r="J30" s="31"/>
+    </row>
+    <row r="31" ht="18.75" customHeight="1">
+      <c r="A31" s="30" t="s">
         <v>2893</v>
       </c>
-      <c r="H16" s="36"/>
-      <c r="J16" s="30"/>
-    </row>
-    <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="29" t="s">
+      <c r="E31" s="34"/>
+      <c r="F31" s="30" t="s">
+        <v>2893</v>
+      </c>
+      <c r="J31" s="31"/>
+    </row>
+    <row r="32" ht="18.75" customHeight="1">
+      <c r="A32" s="30" t="s">
         <v>2894</v>
       </c>
-      <c r="B17" s="30" t="s">
-        <v>2895</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>2896</v>
-      </c>
-      <c r="E17" s="33"/>
-      <c r="F17" s="29" t="s">
+      <c r="B32" s="31" t="s">
+        <v>2908</v>
+      </c>
+      <c r="C32" s="37"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="30" t="s">
         <v>2894</v>
       </c>
-      <c r="G17" s="30" t="s">
-        <v>2897</v>
-      </c>
-      <c r="J17" s="30"/>
-    </row>
-    <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" s="29" t="s">
+      <c r="G32" s="31" t="s">
+        <v>2909</v>
+      </c>
+      <c r="H32" s="37"/>
+      <c r="J32" s="31"/>
+    </row>
+    <row r="33" ht="18.75" customHeight="1">
+      <c r="A33" s="30" t="s">
         <v>2898</v>
       </c>
-      <c r="B18" s="30" t="s">
-        <v>2899</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>2900</v>
-      </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="29" t="s">
+      <c r="B33" s="31" t="s">
+        <v>2910</v>
+      </c>
+      <c r="E33" s="34"/>
+      <c r="F33" s="30" t="s">
         <v>2898</v>
       </c>
-      <c r="G18" s="30" t="s">
-        <v>1851</v>
-      </c>
-      <c r="J18" s="30"/>
-    </row>
-    <row r="19" ht="18.75" customHeight="1">
-      <c r="J19" s="30"/>
-    </row>
-    <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="29" t="s">
-        <v>2901</v>
-      </c>
-      <c r="F20" s="29" t="s">
+      <c r="G33" s="31" t="s">
+        <v>2911</v>
+      </c>
+      <c r="J33" s="31"/>
+    </row>
+    <row r="34" ht="18.75" customHeight="1">
+      <c r="A34" s="30" t="s">
         <v>2902</v>
       </c>
-      <c r="J20" s="30"/>
-    </row>
-    <row r="21" ht="18.75" customHeight="1">
-      <c r="A21" s="25" t="s">
-        <v>2784</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>2784</v>
-      </c>
-      <c r="J21" s="30"/>
-    </row>
-    <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="25"/>
-      <c r="B22" s="29" t="s">
-        <v>2800</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>2801</v>
-      </c>
-      <c r="D22" s="29" t="s">
-        <v>2802</v>
-      </c>
-      <c r="F22" s="25"/>
-      <c r="G22" s="29" t="s">
-        <v>2800</v>
-      </c>
-      <c r="H22" s="29" t="s">
-        <v>2801</v>
-      </c>
-      <c r="I22" s="29" t="s">
-        <v>2802</v>
-      </c>
-      <c r="J22" s="30"/>
-    </row>
-    <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" s="29" t="s">
-        <v>2803</v>
-      </c>
-      <c r="B23" s="30" t="s">
-        <v>2903</v>
-      </c>
-      <c r="F23" s="29" t="s">
-        <v>2803</v>
-      </c>
-      <c r="G23" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="J23" s="30"/>
-    </row>
-    <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" s="29" t="s">
-        <v>2807</v>
-      </c>
-      <c r="F24" s="29" t="s">
-        <v>2807</v>
-      </c>
-      <c r="J24" s="30"/>
-    </row>
-    <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="29" t="s">
-        <v>2813</v>
-      </c>
-      <c r="F25" s="29" t="s">
-        <v>2813</v>
-      </c>
-      <c r="J25" s="30"/>
-    </row>
-    <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="29" t="s">
-        <v>2785</v>
-      </c>
-      <c r="E26" s="33"/>
-      <c r="F26" s="29" t="s">
-        <v>2785</v>
-      </c>
-      <c r="J26" s="30"/>
-    </row>
-    <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="25"/>
-      <c r="B27" s="29" t="s">
-        <v>2800</v>
-      </c>
-      <c r="C27" s="29" t="s">
-        <v>2801</v>
-      </c>
-      <c r="D27" s="29" t="s">
-        <v>2802</v>
-      </c>
-      <c r="E27" s="33"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="29" t="s">
-        <v>2800</v>
-      </c>
-      <c r="H27" s="29" t="s">
-        <v>2801</v>
-      </c>
-      <c r="I27" s="29" t="s">
-        <v>2802</v>
-      </c>
-      <c r="J27" s="30"/>
-    </row>
-    <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" s="29" t="s">
-        <v>2803</v>
-      </c>
-      <c r="B28" s="30" t="s">
-        <v>2903</v>
-      </c>
-      <c r="E28" s="33"/>
-      <c r="F28" s="29" t="s">
-        <v>2803</v>
-      </c>
-      <c r="G28" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="J28" s="30"/>
-    </row>
-    <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="29" t="s">
-        <v>2807</v>
-      </c>
-      <c r="E29" s="33"/>
-      <c r="F29" s="29" t="s">
-        <v>2807</v>
-      </c>
-      <c r="J29" s="30"/>
-    </row>
-    <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" s="29" t="s">
-        <v>2813</v>
-      </c>
-      <c r="E30" s="33"/>
-      <c r="F30" s="29" t="s">
-        <v>2813</v>
-      </c>
-      <c r="J30" s="30"/>
-    </row>
-    <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" s="29" t="s">
-        <v>2889</v>
-      </c>
-      <c r="E31" s="33"/>
-      <c r="F31" s="29" t="s">
-        <v>2889</v>
-      </c>
-      <c r="J31" s="30"/>
-    </row>
-    <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" s="29" t="s">
-        <v>2890</v>
-      </c>
-      <c r="B32" s="30" t="s">
-        <v>2904</v>
-      </c>
-      <c r="C32" s="36"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="29" t="s">
-        <v>2890</v>
-      </c>
-      <c r="G32" s="30" t="s">
-        <v>2905</v>
-      </c>
-      <c r="H32" s="36"/>
-      <c r="J32" s="30"/>
-    </row>
-    <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" s="29" t="s">
+      <c r="B34" s="31" t="s">
+        <v>2912</v>
+      </c>
+      <c r="E34" s="34"/>
+      <c r="F34" s="30" t="s">
+        <v>2902</v>
+      </c>
+      <c r="G34" s="31" t="s">
+        <v>2913</v>
+      </c>
+      <c r="J34" s="31"/>
+    </row>
+    <row r="35" ht="18.75" customHeight="1">
+      <c r="A35" s="35"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
+      <c r="J35" s="31"/>
+    </row>
+    <row r="36" ht="18.75" customHeight="1">
+      <c r="A36" s="30" t="s">
+        <v>2914</v>
+      </c>
+      <c r="C36" s="30" t="s">
+        <v>2915</v>
+      </c>
+      <c r="E36" s="34"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
+      <c r="J36" s="31"/>
+    </row>
+    <row r="37" ht="18.75" customHeight="1">
+      <c r="A37" s="30" t="s">
+        <v>2916</v>
+      </c>
+      <c r="B37" s="31" t="s">
+        <v>2917</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>2916</v>
+      </c>
+      <c r="D37" s="31" t="s">
+        <v>2918</v>
+      </c>
+      <c r="E37" s="34"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+    </row>
+    <row r="38" ht="18.75" customHeight="1">
+      <c r="A38" s="30" t="s">
         <v>2894</v>
       </c>
-      <c r="B33" s="30" t="s">
-        <v>2906</v>
-      </c>
-      <c r="E33" s="33"/>
-      <c r="F33" s="29" t="s">
+      <c r="B38" s="31" t="s">
+        <v>2919</v>
+      </c>
+      <c r="C38" s="30" t="s">
         <v>2894</v>
       </c>
-      <c r="G33" s="30" t="s">
-        <v>2907</v>
-      </c>
-      <c r="J33" s="30"/>
-    </row>
-    <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" s="29" t="s">
+      <c r="D38" s="31" t="s">
+        <v>2920</v>
+      </c>
+      <c r="E38" s="34"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
+    </row>
+    <row r="39" ht="18.75" customHeight="1">
+      <c r="A39" s="30" t="s">
         <v>2898</v>
       </c>
-      <c r="B34" s="30" t="s">
-        <v>2908</v>
-      </c>
-      <c r="E34" s="33"/>
-      <c r="F34" s="29" t="s">
+      <c r="B39" s="31" t="s">
+        <v>2921</v>
+      </c>
+      <c r="C39" s="30" t="s">
         <v>2898</v>
       </c>
-      <c r="G34" s="30" t="s">
-        <v>2909</v>
-      </c>
-      <c r="J34" s="30"/>
-    </row>
-    <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" s="34"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="30"/>
-    </row>
-    <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" s="29" t="s">
-        <v>2910</v>
-      </c>
-      <c r="C36" s="29" t="s">
-        <v>2911</v>
-      </c>
-      <c r="E36" s="33"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="30"/>
-      <c r="J36" s="30"/>
-    </row>
-    <row r="37" ht="18.75" customHeight="1">
-      <c r="A37" s="29" t="s">
-        <v>2912</v>
-      </c>
-      <c r="B37" s="30" t="s">
-        <v>2913</v>
-      </c>
-      <c r="C37" s="29" t="s">
-        <v>2912</v>
-      </c>
-      <c r="D37" s="30" t="s">
-        <v>2914</v>
-      </c>
-      <c r="E37" s="33"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-    </row>
-    <row r="38" ht="18.75" customHeight="1">
-      <c r="A38" s="29" t="s">
-        <v>2890</v>
-      </c>
-      <c r="B38" s="30" t="s">
-        <v>2915</v>
-      </c>
-      <c r="C38" s="29" t="s">
-        <v>2890</v>
-      </c>
-      <c r="D38" s="30" t="s">
-        <v>2916</v>
-      </c>
-      <c r="E38" s="33"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="30"/>
-    </row>
-    <row r="39" ht="18.75" customHeight="1">
-      <c r="A39" s="29" t="s">
-        <v>2894</v>
-      </c>
-      <c r="B39" s="30" t="s">
-        <v>2917</v>
-      </c>
-      <c r="C39" s="29" t="s">
-        <v>2894</v>
-      </c>
-      <c r="D39" s="30" t="s">
-        <v>2918</v>
-      </c>
-      <c r="E39" s="33"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30"/>
+      <c r="D39" s="31" t="s">
+        <v>2922</v>
+      </c>
+      <c r="E39" s="34"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="31"/>
+      <c r="J39" s="31"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
-      <c r="A40" s="34"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
+      <c r="A40" s="35"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
-      <c r="A41" s="34"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="30"/>
-      <c r="J41" s="30"/>
+      <c r="A41" s="35"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
-      <c r="A42" s="34"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
+      <c r="A42" s="35"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
-      <c r="A43" s="34"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
+      <c r="A43" s="35"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
-      <c r="A44" s="34"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="30"/>
-      <c r="J44" s="30"/>
+      <c r="A44" s="35"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="31"/>
+      <c r="I44" s="31"/>
+      <c r="J44" s="31"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
-      <c r="A45" s="34"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="34"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="30"/>
-      <c r="J45" s="30"/>
+      <c r="A45" s="35"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="35"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="31"/>
+      <c r="I45" s="31"/>
+      <c r="J45" s="31"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
-      <c r="A46" s="34"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="33"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
+      <c r="A46" s="35"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="35"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31"/>
+      <c r="I46" s="31"/>
+      <c r="J46" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="37">
@@ -29204,621 +29243,621 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="29" t="s">
-        <v>2919</v>
-      </c>
-      <c r="B1" s="29" t="s">
-        <v>2920</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>2921</v>
-      </c>
-      <c r="D1" s="29" t="s">
+      <c r="A1" s="30" t="s">
+        <v>2923</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>2924</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>2925</v>
+      </c>
+      <c r="D1" s="30" t="s">
         <v>1312</v>
       </c>
-      <c r="F1" s="29" t="s">
-        <v>2919</v>
-      </c>
-      <c r="G1" s="29" t="s">
-        <v>2920</v>
-      </c>
-      <c r="H1" s="29" t="s">
-        <v>2921</v>
+      <c r="F1" s="30" t="s">
+        <v>2923</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>2924</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>2925</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="30" t="s">
-        <v>2922</v>
-      </c>
-      <c r="B2" s="30" t="s">
-        <v>2923</v>
-      </c>
-      <c r="C2" s="30" t="s">
-        <v>2924</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>2925</v>
-      </c>
-      <c r="F2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>2926</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>2927</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="C2" s="31" t="s">
         <v>2928</v>
       </c>
+      <c r="D2" s="31" t="s">
+        <v>2929</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>2930</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>2931</v>
+      </c>
+      <c r="H2" s="31" t="s">
+        <v>2932</v>
+      </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="30" t="s">
-        <v>2929</v>
-      </c>
-      <c r="B3" s="30" t="s">
-        <v>2930</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>2931</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>2932</v>
-      </c>
-      <c r="F3" s="30" t="s">
+      <c r="A3" s="31" t="s">
         <v>2933</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>2934</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="C3" s="31" t="s">
         <v>2935</v>
       </c>
+      <c r="D3" s="31" t="s">
+        <v>2936</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>2937</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>2938</v>
+      </c>
+      <c r="H3" s="31" t="s">
+        <v>2939</v>
+      </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="30" t="s">
-        <v>2936</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>2937</v>
-      </c>
-      <c r="C4" s="30" t="s">
+      <c r="A4" s="31" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>2941</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>2942</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>2866</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>2943</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>2944</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>2945</v>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="31" t="s">
+        <v>2946</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>2947</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>2948</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>2949</v>
+      </c>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+    </row>
+    <row r="6" ht="18.75" customHeight="1">
+      <c r="A6" s="31" t="s">
+        <v>2950</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>2951</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>2952</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>2953</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>2954</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>2956</v>
+      </c>
+    </row>
+    <row r="7" ht="18.75" customHeight="1">
+      <c r="A7" s="31" t="s">
+        <v>2957</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>2958</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>2959</v>
+      </c>
+      <c r="D7" s="31" t="s">
         <v>2938</v>
       </c>
-      <c r="D4" s="30" t="s">
-        <v>2862</v>
-      </c>
-      <c r="F4" s="30" t="s">
-        <v>2939</v>
-      </c>
-      <c r="G4" s="30" t="s">
-        <v>2940</v>
-      </c>
-      <c r="H4" s="30" t="s">
-        <v>2941</v>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="30" t="s">
-        <v>2942</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>2943</v>
-      </c>
-      <c r="C5" s="30" t="s">
+      <c r="F7" s="31" t="s">
+        <v>2960</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>2961</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>2962</v>
+      </c>
+    </row>
+    <row r="8" ht="18.75" customHeight="1">
+      <c r="A8" s="31" t="s">
+        <v>2963</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>2964</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>2965</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>2966</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>2967</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>2968</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="9" ht="18.75" customHeight="1">
+      <c r="A9" s="31" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>2971</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>2972</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>2973</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>2974</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>2975</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>2976</v>
+      </c>
+    </row>
+    <row r="10" ht="18.75" customHeight="1">
+      <c r="A10" s="31" t="s">
+        <v>2977</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>2978</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>2979</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>2980</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>2981</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>2982</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>2983</v>
+      </c>
+    </row>
+    <row r="11" ht="18.75" customHeight="1">
+      <c r="A11" s="31" t="s">
+        <v>2984</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>2985</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>2986</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>2987</v>
+      </c>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+    </row>
+    <row r="12" ht="18.75" customHeight="1">
+      <c r="A12" s="31" t="s">
+        <v>2988</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>2989</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>2990</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>2991</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G12" s="31" t="s">
+        <v>2993</v>
+      </c>
+      <c r="H12" s="31" t="s">
+        <v>2994</v>
+      </c>
+    </row>
+    <row r="13" ht="18.75" customHeight="1">
+      <c r="A13" s="31" t="s">
+        <v>2995</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>2996</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>2997</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>2998</v>
+      </c>
+      <c r="H13" s="31"/>
+    </row>
+    <row r="14" ht="18.75" customHeight="1">
+      <c r="A14" s="31" t="s">
+        <v>2999</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>3000</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>3001</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>3002</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>3003</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>3004</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>3005</v>
+      </c>
+    </row>
+    <row r="15" ht="18.75" customHeight="1">
+      <c r="A15" s="31" t="s">
+        <v>3006</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>3008</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>3009</v>
+      </c>
+      <c r="H15" s="31"/>
+    </row>
+    <row r="16" ht="18.75" customHeight="1">
+      <c r="A16" s="31" t="s">
+        <v>3010</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>3011</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>3012</v>
+      </c>
+      <c r="D16" s="31" t="s">
         <v>2944</v>
       </c>
-      <c r="D5" s="30" t="s">
-        <v>2945</v>
-      </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-    </row>
-    <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="30" t="s">
-        <v>2946</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>2947</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>2948</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>2949</v>
-      </c>
-      <c r="F6" s="30" t="s">
-        <v>2950</v>
-      </c>
-      <c r="G6" s="30" t="s">
-        <v>2951</v>
-      </c>
-      <c r="H6" s="30" t="s">
-        <v>2952</v>
-      </c>
-    </row>
-    <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="30" t="s">
-        <v>2953</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>2954</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>2955</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>2934</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>2956</v>
-      </c>
-      <c r="G7" s="30" t="s">
-        <v>2957</v>
-      </c>
-      <c r="H7" s="30" t="s">
-        <v>2958</v>
-      </c>
-    </row>
-    <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="30" t="s">
-        <v>2959</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>2960</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>2961</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>2962</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>2963</v>
-      </c>
-      <c r="G8" s="30" t="s">
-        <v>2964</v>
-      </c>
-      <c r="H8" s="30" t="s">
-        <v>2965</v>
-      </c>
-    </row>
-    <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="30" t="s">
-        <v>2966</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>2967</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>2968</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>2969</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>2970</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>2971</v>
-      </c>
-      <c r="H9" s="27" t="s">
-        <v>2972</v>
-      </c>
-    </row>
-    <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="30" t="s">
-        <v>2973</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>2974</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>2975</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>2976</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>2977</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>2978</v>
-      </c>
-      <c r="H10" s="27" t="s">
-        <v>2979</v>
-      </c>
-    </row>
-    <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="30" t="s">
-        <v>2980</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>2981</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>2982</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>2983</v>
-      </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-    </row>
-    <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="30" t="s">
-        <v>2984</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>2985</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>2986</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>2987</v>
-      </c>
-      <c r="F12" s="30" t="s">
-        <v>2988</v>
-      </c>
-      <c r="G12" s="30" t="s">
-        <v>2989</v>
-      </c>
-      <c r="H12" s="30" t="s">
-        <v>2990</v>
-      </c>
-    </row>
-    <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="30" t="s">
-        <v>2991</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>2992</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>2993</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>2994</v>
-      </c>
-      <c r="H13" s="30"/>
-    </row>
-    <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="30" t="s">
-        <v>2995</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>2996</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>2997</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>2998</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>2999</v>
-      </c>
-      <c r="G14" s="30" t="s">
-        <v>3000</v>
-      </c>
-      <c r="H14" s="30" t="s">
-        <v>3001</v>
-      </c>
-    </row>
-    <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="30" t="s">
-        <v>3002</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>3003</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>3004</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>3005</v>
-      </c>
-      <c r="H15" s="30"/>
-    </row>
-    <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="30" t="s">
-        <v>3006</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>3007</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>3008</v>
-      </c>
-      <c r="D16" s="30" t="s">
-        <v>2940</v>
-      </c>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30" t="s">
-        <v>3009</v>
-      </c>
-      <c r="G16" s="30" t="s">
-        <v>3010</v>
-      </c>
-      <c r="H16" s="30" t="s">
-        <v>3011</v>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31" t="s">
+        <v>3013</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>3014</v>
+      </c>
+      <c r="H16" s="31" t="s">
+        <v>3015</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="30" t="s">
-        <v>3012</v>
-      </c>
-      <c r="B17" s="30" t="s">
-        <v>3013</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>3014</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>3015</v>
+      <c r="A17" s="31" t="s">
+        <v>3016</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>3017</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>3018</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>3019</v>
       </c>
     </row>
     <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" s="30" t="s">
-        <v>3016</v>
-      </c>
-      <c r="B18" s="30" t="s">
-        <v>3017</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>3018</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>3019</v>
-      </c>
-      <c r="H18" s="30"/>
+      <c r="A18" s="31" t="s">
+        <v>3020</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>3021</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>3022</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>3023</v>
+      </c>
+      <c r="H18" s="31"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" s="30" t="s">
-        <v>3020</v>
-      </c>
-      <c r="B19" s="30" t="s">
-        <v>3021</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>3022</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>3023</v>
-      </c>
-      <c r="H19" s="30"/>
+      <c r="A19" s="31" t="s">
+        <v>3024</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>3025</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>3026</v>
+      </c>
+      <c r="D19" s="31" t="s">
+        <v>3027</v>
+      </c>
+      <c r="H19" s="31"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="30" t="s">
-        <v>3024</v>
-      </c>
-      <c r="B20" s="30" t="s">
-        <v>3025</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>3026</v>
-      </c>
-      <c r="D20" s="30" t="s">
-        <v>2546</v>
-      </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
+      <c r="A20" s="31" t="s">
+        <v>3028</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>3029</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>3030</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>2550</v>
+      </c>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
-      <c r="A21" s="30" t="s">
-        <v>3027</v>
-      </c>
-      <c r="B21" s="30" t="s">
-        <v>3028</v>
-      </c>
-      <c r="C21" s="30" t="s">
-        <v>3029</v>
-      </c>
-      <c r="D21" s="30" t="s">
-        <v>3030</v>
-      </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
+      <c r="A21" s="31" t="s">
+        <v>3031</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>3032</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>3033</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>3034</v>
+      </c>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="30" t="s">
-        <v>3031</v>
-      </c>
-      <c r="B22" s="30" t="s">
-        <v>3032</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>3033</v>
-      </c>
-      <c r="D22" s="30" t="s">
-        <v>3034</v>
-      </c>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
+      <c r="A22" s="31" t="s">
+        <v>3035</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>3036</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D22" s="31" t="s">
+        <v>3038</v>
+      </c>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" s="30" t="s">
-        <v>3035</v>
-      </c>
-      <c r="B23" s="30" t="s">
-        <v>3036</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>3037</v>
-      </c>
-      <c r="D23" s="30" t="s">
-        <v>3038</v>
-      </c>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
+      <c r="A23" s="31" t="s">
+        <v>3039</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>3040</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>3041</v>
+      </c>
+      <c r="D23" s="31" t="s">
+        <v>3042</v>
+      </c>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" s="30" t="s">
-        <v>3039</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>3040</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>3041</v>
-      </c>
-      <c r="D24" s="30" t="s">
-        <v>3042</v>
-      </c>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
+      <c r="A24" s="31" t="s">
+        <v>3043</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>3044</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>3045</v>
+      </c>
+      <c r="D24" s="31" t="s">
+        <v>3046</v>
+      </c>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="30" t="s">
-        <v>3043</v>
-      </c>
-      <c r="B25" s="30" t="s">
-        <v>3044</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>3045</v>
-      </c>
-      <c r="D25" s="30" t="s">
-        <v>3046</v>
-      </c>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
+      <c r="A25" s="31" t="s">
+        <v>3047</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>3048</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>3049</v>
+      </c>
+      <c r="D25" s="31" t="s">
+        <v>3050</v>
+      </c>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="30" t="s">
-        <v>3047</v>
-      </c>
-      <c r="B26" s="30" t="s">
-        <v>3048</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>3049</v>
-      </c>
-      <c r="D26" s="30" t="s">
-        <v>3050</v>
-      </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
+      <c r="A26" s="31" t="s">
+        <v>3051</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>3052</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D26" s="31" t="s">
+        <v>3054</v>
+      </c>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="30" t="s">
-        <v>3051</v>
-      </c>
-      <c r="B27" s="30" t="s">
-        <v>3052</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>3053</v>
-      </c>
-      <c r="D27" s="30" t="s">
-        <v>3054</v>
-      </c>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
+      <c r="A27" s="31" t="s">
+        <v>3055</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>3056</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>3057</v>
+      </c>
+      <c r="D27" s="31" t="s">
+        <v>3058</v>
+      </c>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" s="30" t="s">
-        <v>3055</v>
-      </c>
-      <c r="B28" s="30" t="s">
-        <v>3056</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>3057</v>
-      </c>
-      <c r="D28" s="30" t="s">
-        <v>3058</v>
-      </c>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
+      <c r="A28" s="31" t="s">
+        <v>3059</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>3060</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>3061</v>
+      </c>
+      <c r="D28" s="31" t="s">
+        <v>3062</v>
+      </c>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
+      <c r="A29" s="28"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" s="25" t="s">
-        <v>3059</v>
-      </c>
-      <c r="H30" s="30"/>
+      <c r="A30" s="26" t="s">
+        <v>3063</v>
+      </c>
+      <c r="H30" s="31"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" s="27" t="s">
-        <v>3060</v>
-      </c>
-      <c r="D31" s="27" t="s">
-        <v>3061</v>
-      </c>
-      <c r="F31" s="27" t="s">
-        <v>3062</v>
+      <c r="A31" s="28" t="s">
+        <v>3064</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>3065</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>3066</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" s="27" t="s">
-        <v>3063</v>
-      </c>
-      <c r="D32" s="27" t="s">
-        <v>3064</v>
-      </c>
-      <c r="F32" s="27" t="s">
-        <v>3065</v>
+      <c r="A32" s="28" t="s">
+        <v>3067</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>3068</v>
+      </c>
+      <c r="F32" s="28" t="s">
+        <v>3069</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" s="27" t="s">
-        <v>3066</v>
-      </c>
-      <c r="D33" s="27" t="s">
-        <v>3067</v>
-      </c>
-      <c r="F33" s="27" t="s">
-        <v>3068</v>
+      <c r="A33" s="28" t="s">
+        <v>3070</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>3071</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>3072</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" s="27" t="s">
-        <v>3069</v>
-      </c>
-      <c r="D34" s="27" t="s">
-        <v>3070</v>
-      </c>
-      <c r="F34" s="27" t="s">
-        <v>3071</v>
+      <c r="A34" s="28" t="s">
+        <v>3073</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>3074</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>3075</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" s="27" t="s">
-        <v>3072</v>
-      </c>
-      <c r="D35" s="27" t="s">
-        <v>3073</v>
-      </c>
-      <c r="F35" s="27" t="s">
-        <v>3074</v>
+      <c r="A35" s="28" t="s">
+        <v>3076</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>3077</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>3078</v>
       </c>
     </row>
   </sheetData>
@@ -29855,502 +29894,502 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="37" t="s">
-        <v>3075</v>
+      <c r="A1" s="38" t="s">
+        <v>3079</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="38" t="s">
-        <v>3076</v>
+      <c r="A2" s="39" t="s">
+        <v>3080</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>3077</v>
+        <v>3081</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>3078</v>
+        <v>3082</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>3079</v>
+        <v>3083</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="38" t="s">
-        <v>3080</v>
+      <c r="A3" s="39" t="s">
+        <v>3084</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>3081</v>
+        <v>3085</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>3082</v>
+        <v>3086</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>3083</v>
+        <v>3087</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="38" t="s">
-        <v>3084</v>
+      <c r="A4" s="39" t="s">
+        <v>3088</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>3085</v>
+        <v>3089</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>3086</v>
+        <v>3090</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>3087</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="39" t="s">
-        <v>3088</v>
+      <c r="A5" s="40" t="s">
+        <v>3092</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>3089</v>
+        <v>3093</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>3090</v>
+        <v>3094</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>3087</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="38" t="s">
-        <v>3091</v>
+      <c r="A6" s="39" t="s">
+        <v>3095</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>3092</v>
+        <v>3096</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>3093</v>
+        <v>3097</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>3094</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="38" t="s">
-        <v>3095</v>
+      <c r="A7" s="39" t="s">
+        <v>3099</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>3096</v>
+        <v>3100</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>3097</v>
+        <v>3101</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>3098</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="38" t="s">
-        <v>3099</v>
+      <c r="A8" s="39" t="s">
+        <v>3103</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>3100</v>
+        <v>3104</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>3101</v>
+        <v>3105</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>3102</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="38" t="s">
-        <v>3103</v>
+      <c r="A9" s="39" t="s">
+        <v>3107</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>3104</v>
+        <v>3108</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>3105</v>
+        <v>3109</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>3106</v>
+        <v>3110</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="38" t="s">
-        <v>3107</v>
+      <c r="A10" s="39" t="s">
+        <v>3111</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>3108</v>
+        <v>3112</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>3109</v>
+        <v>3113</v>
       </c>
       <c r="I10" s="8" t="s">
+        <v>3114</v>
+      </c>
+    </row>
+    <row r="11" ht="18.75" customHeight="1">
+      <c r="A11" s="39" t="s">
+        <v>3115</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>3116</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>3117</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>3110</v>
       </c>
     </row>
-    <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="38" t="s">
-        <v>3111</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>3112</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>3113</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>3106</v>
-      </c>
-    </row>
     <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="38" t="s">
-        <v>3114</v>
+      <c r="A12" s="39" t="s">
+        <v>3118</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>3115</v>
+        <v>3119</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>3116</v>
+        <v>3120</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>3117</v>
+        <v>3121</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="38" t="s">
-        <v>3118</v>
+      <c r="A13" s="39" t="s">
+        <v>3122</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>3119</v>
+        <v>3123</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>3120</v>
+        <v>3124</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>3121</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="39" t="s">
-        <v>3122</v>
+      <c r="A14" s="40" t="s">
+        <v>3126</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>3123</v>
+        <v>3127</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>3124</v>
+        <v>3128</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>3125</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
+      <c r="A15" s="31"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="39" t="s">
-        <v>3126</v>
-      </c>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
+      <c r="A16" s="40" t="s">
+        <v>3130</v>
+      </c>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="39" t="s">
-        <v>3127</v>
-      </c>
-      <c r="E17" s="39" t="s">
-        <v>3128</v>
-      </c>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
+      <c r="A17" s="40" t="s">
+        <v>3131</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>3132</v>
+      </c>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" s="30" t="s">
-        <v>3129</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>3130</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>3131</v>
-      </c>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
+      <c r="A18" s="31" t="s">
+        <v>3133</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>3134</v>
+      </c>
+      <c r="E18" s="31" t="s">
+        <v>3135</v>
+      </c>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" s="30" t="s">
-        <v>3132</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>3133</v>
-      </c>
-      <c r="E19" s="30" t="s">
+      <c r="A19" s="31" t="s">
+        <v>3136</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>3137</v>
+      </c>
+      <c r="E19" s="31" t="s">
+        <v>3138</v>
+      </c>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+    </row>
+    <row r="20" ht="18.75" customHeight="1">
+      <c r="A20" s="36" t="s">
+        <v>3139</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>3140</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>3141</v>
+      </c>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+    </row>
+    <row r="21" ht="18.75" customHeight="1">
+      <c r="J21" s="41"/>
+    </row>
+    <row r="22" ht="18.75" customHeight="1">
+      <c r="A22" s="31" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E22" s="31" t="s">
+        <v>3143</v>
+      </c>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+    </row>
+    <row r="23" ht="18.75" customHeight="1">
+      <c r="A23" s="31" t="s">
+        <v>3144</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>3145</v>
+      </c>
+      <c r="E23" s="31" t="s">
+        <v>3146</v>
+      </c>
+      <c r="J23" s="41"/>
+    </row>
+    <row r="24" ht="18.75" customHeight="1">
+      <c r="A24" s="31" t="s">
+        <v>3147</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>3137</v>
+      </c>
+      <c r="E24" s="31" t="s">
+        <v>3148</v>
+      </c>
+      <c r="J24" s="41"/>
+    </row>
+    <row r="25" ht="18.75" customHeight="1">
+      <c r="A25" s="31" t="s">
+        <v>3149</v>
+      </c>
+      <c r="C25" s="31" t="s">
         <v>3134</v>
       </c>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
-    </row>
-    <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="35" t="s">
-        <v>3135</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>3136</v>
-      </c>
-      <c r="E20" s="35" t="s">
+      <c r="E25" s="31" t="s">
+        <v>3150</v>
+      </c>
+      <c r="J25" s="41"/>
+    </row>
+    <row r="26" ht="18.75" customHeight="1">
+      <c r="A26" s="31" t="s">
+        <v>3151</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>3134</v>
+      </c>
+      <c r="E26" s="31" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J26" s="41"/>
+    </row>
+    <row r="27" ht="18.75" customHeight="1">
+      <c r="A27" s="31" t="s">
+        <v>3153</v>
+      </c>
+      <c r="C27" s="31" t="s">
         <v>3137</v>
       </c>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-    </row>
-    <row r="21" ht="18.75" customHeight="1">
-      <c r="J21" s="40"/>
-    </row>
-    <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="30" t="s">
-        <v>3138</v>
-      </c>
-      <c r="E22" s="30" t="s">
-        <v>3139</v>
-      </c>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-    </row>
-    <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" s="30" t="s">
+      <c r="E27" s="31" t="s">
+        <v>3154</v>
+      </c>
+      <c r="J27" s="41"/>
+    </row>
+    <row r="28" ht="18.75" customHeight="1">
+      <c r="A28" s="31" t="s">
+        <v>3155</v>
+      </c>
+      <c r="C28" s="31" t="s">
         <v>3140</v>
       </c>
-      <c r="C23" s="30" t="s">
-        <v>3141</v>
-      </c>
-      <c r="E23" s="30" t="s">
-        <v>3142</v>
-      </c>
-      <c r="J23" s="40"/>
-    </row>
-    <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" s="30" t="s">
-        <v>3143</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>3133</v>
-      </c>
-      <c r="E24" s="30" t="s">
-        <v>3144</v>
-      </c>
-      <c r="J24" s="40"/>
-    </row>
-    <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="30" t="s">
-        <v>3145</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>3130</v>
-      </c>
-      <c r="E25" s="30" t="s">
-        <v>3146</v>
-      </c>
-      <c r="J25" s="40"/>
-    </row>
-    <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="30" t="s">
-        <v>3147</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>3130</v>
-      </c>
-      <c r="E26" s="30" t="s">
-        <v>3148</v>
-      </c>
-      <c r="J26" s="40"/>
-    </row>
-    <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="30" t="s">
-        <v>3149</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>3133</v>
-      </c>
-      <c r="E27" s="30" t="s">
-        <v>3150</v>
-      </c>
-      <c r="J27" s="40"/>
-    </row>
-    <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" s="30" t="s">
-        <v>3151</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>3136</v>
-      </c>
-      <c r="E28" s="30" t="s">
-        <v>3152</v>
-      </c>
-      <c r="J28" s="40"/>
+      <c r="E28" s="31" t="s">
+        <v>3156</v>
+      </c>
+      <c r="J28" s="41"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="40"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
+      <c r="A29" s="41"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" s="37" t="s">
-        <v>3153</v>
+      <c r="A30" s="38" t="s">
+        <v>3157</v>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" s="41" t="s">
-        <v>3154</v>
-      </c>
-      <c r="D31" s="41" t="s">
-        <v>3155</v>
-      </c>
-      <c r="G31" s="41" t="s">
-        <v>3156</v>
-      </c>
-      <c r="J31" s="30"/>
+      <c r="A31" s="42" t="s">
+        <v>3158</v>
+      </c>
+      <c r="D31" s="42" t="s">
+        <v>3159</v>
+      </c>
+      <c r="G31" s="42" t="s">
+        <v>3160</v>
+      </c>
+      <c r="J31" s="31"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
-      <c r="J32" s="30"/>
+      <c r="J32" s="31"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" s="42" t="s">
-        <v>3157</v>
-      </c>
-      <c r="D33" s="42" t="s">
-        <v>3158</v>
-      </c>
-      <c r="G33" s="42" t="s">
-        <v>3159</v>
-      </c>
-      <c r="J33" s="30"/>
+      <c r="A33" s="43" t="s">
+        <v>3161</v>
+      </c>
+      <c r="D33" s="43" t="s">
+        <v>3162</v>
+      </c>
+      <c r="G33" s="43" t="s">
+        <v>3163</v>
+      </c>
+      <c r="J33" s="31"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" s="42" t="s">
-        <v>3160</v>
-      </c>
-      <c r="D34" s="42" t="s">
-        <v>3161</v>
-      </c>
-      <c r="G34" s="42" t="s">
-        <v>3162</v>
-      </c>
-      <c r="J34" s="30"/>
+      <c r="A34" s="43" t="s">
+        <v>3164</v>
+      </c>
+      <c r="D34" s="43" t="s">
+        <v>3165</v>
+      </c>
+      <c r="G34" s="43" t="s">
+        <v>3166</v>
+      </c>
+      <c r="J34" s="31"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" s="42" t="s">
-        <v>3163</v>
-      </c>
-      <c r="D35" s="42" t="s">
-        <v>3164</v>
-      </c>
-      <c r="G35" s="42" t="s">
-        <v>3165</v>
-      </c>
-      <c r="J35" s="30"/>
+      <c r="A35" s="43" t="s">
+        <v>3167</v>
+      </c>
+      <c r="D35" s="43" t="s">
+        <v>3168</v>
+      </c>
+      <c r="G35" s="43" t="s">
+        <v>3169</v>
+      </c>
+      <c r="J35" s="31"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" s="42" t="s">
-        <v>3166</v>
-      </c>
-      <c r="D36" s="42" t="s">
-        <v>3167</v>
-      </c>
-      <c r="G36" s="42" t="s">
-        <v>3168</v>
-      </c>
-      <c r="J36" s="30"/>
+      <c r="A36" s="43" t="s">
+        <v>3170</v>
+      </c>
+      <c r="D36" s="43" t="s">
+        <v>3171</v>
+      </c>
+      <c r="G36" s="43" t="s">
+        <v>3172</v>
+      </c>
+      <c r="J36" s="31"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
-      <c r="A37" s="41" t="s">
-        <v>3169</v>
-      </c>
-      <c r="D37" s="41" t="s">
-        <v>3170</v>
-      </c>
-      <c r="G37" s="30"/>
-      <c r="J37" s="30"/>
+      <c r="A37" s="42" t="s">
+        <v>3173</v>
+      </c>
+      <c r="D37" s="42" t="s">
+        <v>3174</v>
+      </c>
+      <c r="G37" s="31"/>
+      <c r="J37" s="31"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
-      <c r="J38" s="40"/>
+      <c r="J38" s="41"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="8" t="s">
-        <v>3171</v>
-      </c>
-      <c r="D39" s="42" t="s">
-        <v>3172</v>
-      </c>
-      <c r="G39" s="42" t="s">
-        <v>3173</v>
-      </c>
-      <c r="J39" s="40"/>
+        <v>3175</v>
+      </c>
+      <c r="D39" s="43" t="s">
+        <v>3176</v>
+      </c>
+      <c r="G39" s="43" t="s">
+        <v>3177</v>
+      </c>
+      <c r="J39" s="41"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="8" t="s">
-        <v>3174</v>
-      </c>
-      <c r="D40" s="42" t="s">
-        <v>3175</v>
-      </c>
-      <c r="G40" s="42" t="s">
-        <v>3176</v>
-      </c>
-      <c r="J40" s="40"/>
+        <v>3178</v>
+      </c>
+      <c r="D40" s="43" t="s">
+        <v>3179</v>
+      </c>
+      <c r="G40" s="43" t="s">
+        <v>3180</v>
+      </c>
+      <c r="J40" s="41"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="8" t="s">
-        <v>3177</v>
-      </c>
-      <c r="D41" s="42" t="s">
-        <v>3178</v>
-      </c>
-      <c r="G41" s="42" t="s">
-        <v>3179</v>
-      </c>
-      <c r="J41" s="40"/>
+        <v>3181</v>
+      </c>
+      <c r="D41" s="43" t="s">
+        <v>3182</v>
+      </c>
+      <c r="G41" s="43" t="s">
+        <v>3183</v>
+      </c>
+      <c r="J41" s="41"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="8" t="s">
-        <v>3180</v>
-      </c>
-      <c r="D42" s="42" t="s">
-        <v>3181</v>
-      </c>
-      <c r="G42" s="42" t="s">
-        <v>3182</v>
-      </c>
-      <c r="J42" s="40"/>
+        <v>3184</v>
+      </c>
+      <c r="D42" s="43" t="s">
+        <v>3185</v>
+      </c>
+      <c r="G42" s="43" t="s">
+        <v>3186</v>
+      </c>
+      <c r="J42" s="41"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="8" t="s">
-        <v>3183</v>
-      </c>
-      <c r="D43" s="42" t="s">
-        <v>3184</v>
-      </c>
-      <c r="G43" s="42" t="s">
-        <v>3185</v>
-      </c>
-      <c r="J43" s="40"/>
+        <v>3187</v>
+      </c>
+      <c r="D43" s="43" t="s">
+        <v>3188</v>
+      </c>
+      <c r="G43" s="43" t="s">
+        <v>3189</v>
+      </c>
+      <c r="J43" s="41"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
-      <c r="J44" s="40"/>
+      <c r="J44" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="119">

--- a/Conlangs/Kagalarian.xlsx
+++ b/Conlangs/Kagalarian.xlsx
@@ -3563,13 +3563,13 @@
     <t>loud, rowdy</t>
   </si>
   <si>
-    <t>lūsabon</t>
+    <t>lūbon</t>
   </si>
   <si>
     <t>love</t>
   </si>
   <si>
-    <t>lūsabo</t>
+    <t>lūbo</t>
   </si>
   <si>
     <t>lover, significant other</t>
@@ -6398,7 +6398,7 @@
     <t>to crawl</t>
   </si>
   <si>
-    <t>kezhat</t>
+    <t>krezhat</t>
   </si>
   <si>
     <t>to crouch, to sneak</t>
@@ -6884,7 +6884,7 @@
     <t>to kill, to slay</t>
   </si>
   <si>
-    <t>keravat</t>
+    <t>kyezhat</t>
   </si>
   <si>
     <t>to kiss</t>
@@ -6980,7 +6980,7 @@
     <t>to louden, to make loud</t>
   </si>
   <si>
-    <t>lūsabat</t>
+    <t>lūbat</t>
   </si>
   <si>
     <t>to love</t>

--- a/Conlangs/Kagalarian.xlsx
+++ b/Conlangs/Kagalarian.xlsx
@@ -11,14 +11,14 @@
     <sheet state="visible" name="Grammar" sheetId="6" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Kagalarian!$A$1:$C$1423</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Kagalarian!$A$1:$C$1425</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4927" uniqueCount="3275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4933" uniqueCount="3279">
   <si>
     <t>Word</t>
   </si>
@@ -1994,6 +1994,12 @@
     <t>elinar</t>
   </si>
   <si>
+    <t>ūra</t>
+  </si>
+  <si>
+    <t>ember, spark</t>
+  </si>
+  <si>
     <t>polonye</t>
   </si>
   <si>
@@ -2291,49 +2297,43 @@
     <t>kraza</t>
   </si>
   <si>
-    <t>fire, blaze, flames</t>
-  </si>
-  <si>
-    <t>ūra</t>
-  </si>
-  <si>
-    <t>fire, ember, spark</t>
+    <t>fire, flames, blaze</t>
+  </si>
+  <si>
+    <t>fyerda (1)</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>fyerda (2)</t>
+  </si>
+  <si>
+    <t>first (indeclinable)</t>
+  </si>
+  <si>
+    <t>fyezh</t>
+  </si>
+  <si>
+    <t>fish</t>
+  </si>
+  <si>
+    <t>gim</t>
+  </si>
+  <si>
+    <t>five</t>
+  </si>
+  <si>
+    <t>sayron</t>
+  </si>
+  <si>
+    <t>flag</t>
   </si>
   <si>
     <t>bral</t>
   </si>
   <si>
-    <t>fire, flame, flicker</t>
-  </si>
-  <si>
-    <t>fyerda (1)</t>
-  </si>
-  <si>
-    <t>first</t>
-  </si>
-  <si>
-    <t>fyerda (2)</t>
-  </si>
-  <si>
-    <t>first (indeclinable)</t>
-  </si>
-  <si>
-    <t>fyezh</t>
-  </si>
-  <si>
-    <t>fish</t>
-  </si>
-  <si>
-    <t>gim</t>
-  </si>
-  <si>
-    <t>five</t>
-  </si>
-  <si>
-    <t>sayron</t>
-  </si>
-  <si>
-    <t>flag</t>
+    <t>flame, flicker</t>
   </si>
   <si>
     <t>dan-neygen</t>
@@ -2708,13 +2708,13 @@
     <t>gorgeous, beautiful</t>
   </si>
   <si>
-    <t>gradanelov</t>
+    <t>gradnelov</t>
   </si>
   <si>
     <t>government</t>
   </si>
   <si>
-    <t>gradandar</t>
+    <t>gradnadar</t>
   </si>
   <si>
     <t>governmental, federal, imperial, sovereign (indeclinable)</t>
@@ -3212,7 +3212,7 @@
     <t>inspection</t>
   </si>
   <si>
-    <t>isha-gradano</t>
+    <t>isha-gradno</t>
   </si>
   <si>
     <t>insurgent, rebel</t>
@@ -6086,7 +6086,7 @@
     <t>to annoy, to bother, to irritate</t>
   </si>
   <si>
-    <t>mishanat</t>
+    <t>mishnat</t>
   </si>
   <si>
     <t>to appear</t>
@@ -6230,6 +6230,12 @@
     <t>to birth</t>
   </si>
   <si>
+    <t>glabnat</t>
+  </si>
+  <si>
+    <t>to blend, to combine, to mix</t>
+  </si>
+  <si>
     <t>krisnat</t>
   </si>
   <si>
@@ -6272,7 +6278,7 @@
     <t>to buy, to purchase</t>
   </si>
   <si>
-    <t>klabanat</t>
+    <t>klabnat</t>
   </si>
   <si>
     <t>to call, to summon; to send someone to (with "vta" + infinitive)</t>
@@ -6554,7 +6560,7 @@
     <t>to drink</t>
   </si>
   <si>
-    <t>zhevanat</t>
+    <t>zhevnat</t>
   </si>
   <si>
     <t>to drive</t>
@@ -6728,7 +6734,7 @@
     <t>to glow</t>
   </si>
   <si>
-    <t>gradanat</t>
+    <t>gradnat</t>
   </si>
   <si>
     <t>to govern</t>
@@ -7523,7 +7529,7 @@
     <t>pliznat</t>
   </si>
   <si>
-    <t>to spark, to stir</t>
+    <t>to spark feelings, to evoke emotions; to arouse, to exite</t>
   </si>
   <si>
     <t>lūtsat</t>
@@ -7590,6 +7596,12 @@
   </si>
   <si>
     <t>to stick to</t>
+  </si>
+  <si>
+    <t>svelat</t>
+  </si>
+  <si>
+    <t>to stir, to mix</t>
   </si>
   <si>
     <t>dovat</t>
@@ -10563,7 +10575,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -10632,9 +10644,6 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
@@ -10793,8 +10802,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C1423" displayName="Table1" name="Table1" id="1">
-  <autoFilter ref="$A$1:$C$1423"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C1425" displayName="Table1" name="Table1" id="1">
+  <autoFilter ref="$A$1:$C$1425"/>
   <tableColumns count="3">
     <tableColumn name="Word" id="1"/>
     <tableColumn name="Part of Speech" id="2"/>
@@ -14868,7 +14877,7 @@
       <c r="A324" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="B324" s="7" t="s">
+      <c r="B324" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C324" s="4" t="s">
@@ -14880,7 +14889,7 @@
       <c r="A325" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="B325" s="5" t="s">
+      <c r="B325" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C325" s="4" t="s">
@@ -14892,7 +14901,7 @@
       <c r="A326" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="B326" s="7" t="s">
+      <c r="B326" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C326" s="4" t="s">
@@ -14904,7 +14913,7 @@
       <c r="A327" s="4" t="s">
         <v>664</v>
       </c>
-      <c r="B327" s="5" t="s">
+      <c r="B327" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C327" s="4" t="s">
@@ -14916,8 +14925,8 @@
       <c r="A328" s="4" t="s">
         <v>666</v>
       </c>
-      <c r="B328" s="9" t="s">
-        <v>64</v>
+      <c r="B328" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C328" s="4" t="s">
         <v>667</v>
@@ -14925,13 +14934,13 @@
       <c r="D328" s="13"/>
     </row>
     <row r="329" ht="22.5" customHeight="1">
-      <c r="A329" s="10" t="s">
+      <c r="A329" s="4" t="s">
         <v>668</v>
       </c>
       <c r="B329" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C329" s="10" t="s">
+      <c r="C329" s="4" t="s">
         <v>669</v>
       </c>
       <c r="D329" s="13"/>
@@ -14940,8 +14949,8 @@
       <c r="A330" s="10" t="s">
         <v>670</v>
       </c>
-      <c r="B330" s="5" t="s">
-        <v>7</v>
+      <c r="B330" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C330" s="10" t="s">
         <v>671</v>
@@ -14952,7 +14961,7 @@
       <c r="A331" s="10" t="s">
         <v>672</v>
       </c>
-      <c r="B331" s="7" t="s">
+      <c r="B331" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C331" s="10" t="s">
@@ -14961,61 +14970,61 @@
       <c r="D331" s="13"/>
     </row>
     <row r="332" ht="22.5" customHeight="1">
-      <c r="A332" s="4" t="s">
+      <c r="A332" s="10" t="s">
         <v>674</v>
       </c>
-      <c r="B332" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C332" s="4" t="s">
+      <c r="B332" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C332" s="10" t="s">
         <v>675</v>
       </c>
       <c r="D332" s="13"/>
     </row>
     <row r="333" ht="22.5" customHeight="1">
-      <c r="A333" s="10" t="s">
+      <c r="A333" s="4" t="s">
         <v>676</v>
       </c>
       <c r="B333" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C333" s="10" t="s">
+      <c r="C333" s="4" t="s">
         <v>677</v>
       </c>
       <c r="D333" s="13"/>
     </row>
     <row r="334" ht="22.5" customHeight="1">
-      <c r="A334" s="4" t="s">
+      <c r="A334" s="10" t="s">
         <v>678</v>
       </c>
-      <c r="B334" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C334" s="4" t="s">
+      <c r="B334" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C334" s="10" t="s">
         <v>679</v>
       </c>
       <c r="D334" s="13"/>
     </row>
     <row r="335" ht="22.5" customHeight="1">
-      <c r="A335" s="10" t="s">
+      <c r="A335" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="B335" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C335" s="10" t="s">
+      <c r="B335" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C335" s="4" t="s">
         <v>681</v>
       </c>
       <c r="D335" s="13"/>
     </row>
     <row r="336" ht="22.5" customHeight="1">
-      <c r="A336" s="4" t="s">
+      <c r="A336" s="10" t="s">
         <v>682</v>
       </c>
-      <c r="B336" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C336" s="4" t="s">
+      <c r="B336" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C336" s="10" t="s">
         <v>683</v>
       </c>
       <c r="D336" s="13"/>
@@ -15024,7 +15033,7 @@
       <c r="A337" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="B337" s="7" t="s">
+      <c r="B337" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C337" s="4" t="s">
@@ -15036,8 +15045,8 @@
       <c r="A338" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="B338" s="5" t="s">
-        <v>72</v>
+      <c r="B338" s="7" t="s">
+        <v>7</v>
       </c>
       <c r="C338" s="4" t="s">
         <v>687</v>
@@ -15048,8 +15057,8 @@
       <c r="A339" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="B339" s="9" t="s">
-        <v>64</v>
+      <c r="B339" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="C339" s="4" t="s">
         <v>689</v>
@@ -15060,8 +15069,8 @@
       <c r="A340" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="B340" s="5" t="s">
-        <v>7</v>
+      <c r="B340" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C340" s="4" t="s">
         <v>691</v>
@@ -15069,25 +15078,25 @@
       <c r="D340" s="13"/>
     </row>
     <row r="341" ht="22.5" customHeight="1">
-      <c r="A341" s="10" t="s">
+      <c r="A341" s="4" t="s">
         <v>692</v>
       </c>
-      <c r="B341" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C341" s="10" t="s">
+      <c r="B341" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C341" s="4" t="s">
         <v>693</v>
       </c>
       <c r="D341" s="13"/>
     </row>
     <row r="342" ht="22.5" customHeight="1">
-      <c r="A342" s="4" t="s">
+      <c r="A342" s="10" t="s">
         <v>694</v>
       </c>
-      <c r="B342" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C342" s="4" t="s">
+      <c r="B342" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C342" s="10" t="s">
         <v>695</v>
       </c>
       <c r="D342" s="13"/>
@@ -15108,8 +15117,8 @@
       <c r="A344" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="B344" s="5" t="s">
-        <v>49</v>
+      <c r="B344" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C344" s="4" t="s">
         <v>699</v>
@@ -15120,8 +15129,8 @@
       <c r="A345" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="B345" s="7" t="s">
-        <v>7</v>
+      <c r="B345" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="C345" s="4" t="s">
         <v>701</v>
@@ -15132,7 +15141,7 @@
       <c r="A346" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="B346" s="5" t="s">
+      <c r="B346" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C346" s="4" t="s">
@@ -15144,8 +15153,8 @@
       <c r="A347" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="B347" s="9" t="s">
-        <v>64</v>
+      <c r="B347" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C347" s="4" t="s">
         <v>705</v>
@@ -15156,8 +15165,8 @@
       <c r="A348" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="B348" s="5" t="s">
-        <v>7</v>
+      <c r="B348" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C348" s="4" t="s">
         <v>707</v>
@@ -15193,7 +15202,7 @@
         <v>712</v>
       </c>
       <c r="B351" s="5" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="C351" s="4" t="s">
         <v>713</v>
@@ -15201,25 +15210,25 @@
       <c r="D351" s="13"/>
     </row>
     <row r="352" ht="22.5" customHeight="1">
-      <c r="A352" s="10" t="s">
+      <c r="A352" s="4" t="s">
         <v>714</v>
       </c>
       <c r="B352" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C352" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C352" s="4" t="s">
         <v>715</v>
       </c>
       <c r="D352" s="13"/>
     </row>
     <row r="353" ht="22.5" customHeight="1">
-      <c r="A353" s="4" t="s">
+      <c r="A353" s="10" t="s">
         <v>716</v>
       </c>
       <c r="B353" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C353" s="4" t="s">
+      <c r="C353" s="10" t="s">
         <v>717</v>
       </c>
       <c r="D353" s="13"/>
@@ -15228,7 +15237,7 @@
       <c r="A354" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="B354" s="7" t="s">
+      <c r="B354" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C354" s="4" t="s">
@@ -15237,25 +15246,25 @@
       <c r="D354" s="13"/>
     </row>
     <row r="355" ht="22.5" customHeight="1">
-      <c r="A355" s="10" t="s">
+      <c r="A355" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="B355" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C355" s="10" t="s">
+      <c r="B355" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C355" s="4" t="s">
         <v>721</v>
       </c>
       <c r="D355" s="13"/>
     </row>
     <row r="356" ht="22.5" customHeight="1">
-      <c r="A356" s="4" t="s">
+      <c r="A356" s="10" t="s">
         <v>722</v>
       </c>
       <c r="B356" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C356" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C356" s="10" t="s">
         <v>723</v>
       </c>
       <c r="D356" s="13"/>
@@ -15264,7 +15273,7 @@
       <c r="A357" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="B357" s="9" t="s">
+      <c r="B357" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C357" s="4" t="s">
@@ -15277,7 +15286,7 @@
         <v>726</v>
       </c>
       <c r="B358" s="9" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="C358" s="4" t="s">
         <v>727</v>
@@ -15288,7 +15297,7 @@
       <c r="A359" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="B359" s="7" t="s">
+      <c r="B359" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C359" s="4" t="s">
@@ -15297,13 +15306,13 @@
       <c r="D359" s="13"/>
     </row>
     <row r="360" ht="22.5" customHeight="1">
-      <c r="A360" s="10" t="s">
+      <c r="A360" s="4" t="s">
         <v>730</v>
       </c>
-      <c r="B360" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C360" s="10" t="s">
+      <c r="B360" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C360" s="4" t="s">
         <v>731</v>
       </c>
       <c r="D360" s="13"/>
@@ -15313,7 +15322,7 @@
         <v>732</v>
       </c>
       <c r="B361" s="9" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C361" s="10" t="s">
         <v>733</v>
@@ -15324,8 +15333,8 @@
       <c r="A362" s="10" t="s">
         <v>734</v>
       </c>
-      <c r="B362" s="5" t="s">
-        <v>7</v>
+      <c r="B362" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C362" s="10" t="s">
         <v>735</v>
@@ -15333,13 +15342,13 @@
       <c r="D362" s="13"/>
     </row>
     <row r="363" ht="22.5" customHeight="1">
-      <c r="A363" s="4" t="s">
+      <c r="A363" s="10" t="s">
         <v>736</v>
       </c>
       <c r="B363" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C363" s="4" t="s">
+      <c r="C363" s="10" t="s">
         <v>737</v>
       </c>
       <c r="D363" s="13"/>
@@ -15360,7 +15369,7 @@
       <c r="A365" s="4" t="s">
         <v>740</v>
       </c>
-      <c r="B365" s="7" t="s">
+      <c r="B365" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C365" s="4" t="s">
@@ -15372,8 +15381,8 @@
       <c r="A366" s="4" t="s">
         <v>742</v>
       </c>
-      <c r="B366" s="5" t="s">
-        <v>4</v>
+      <c r="B366" s="7" t="s">
+        <v>7</v>
       </c>
       <c r="C366" s="4" t="s">
         <v>743</v>
@@ -15385,7 +15394,7 @@
         <v>744</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C367" s="4" t="s">
         <v>745</v>
@@ -15420,8 +15429,8 @@
       <c r="A370" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="B370" s="9" t="s">
-        <v>64</v>
+      <c r="B370" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C370" s="4" t="s">
         <v>751</v>
@@ -15429,49 +15438,49 @@
       <c r="D370" s="13"/>
     </row>
     <row r="371" ht="22.5" customHeight="1">
-      <c r="A371" s="10" t="s">
+      <c r="A371" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="B371" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C371" s="10" t="s">
+      <c r="B371" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C371" s="4" t="s">
         <v>753</v>
       </c>
       <c r="D371" s="13"/>
     </row>
     <row r="372" ht="22.5" customHeight="1">
-      <c r="A372" s="4" t="s">
+      <c r="A372" s="10" t="s">
         <v>754</v>
       </c>
       <c r="B372" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C372" s="4" t="s">
+      <c r="C372" s="10" t="s">
         <v>755</v>
       </c>
       <c r="D372" s="13"/>
     </row>
     <row r="373" ht="22.5" customHeight="1">
-      <c r="A373" s="10" t="s">
+      <c r="A373" s="4" t="s">
         <v>756</v>
       </c>
       <c r="B373" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C373" s="10" t="s">
+      <c r="C373" s="4" t="s">
         <v>757</v>
       </c>
       <c r="D373" s="13"/>
     </row>
     <row r="374" ht="22.5" customHeight="1">
-      <c r="A374" s="4" t="s">
+      <c r="A374" s="10" t="s">
         <v>758</v>
       </c>
       <c r="B374" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C374" s="4" t="s">
+      <c r="C374" s="10" t="s">
         <v>759</v>
       </c>
       <c r="D374" s="13"/>
@@ -15480,8 +15489,8 @@
       <c r="A375" s="4" t="s">
         <v>760</v>
       </c>
-      <c r="B375" s="5" t="s">
-        <v>7</v>
+      <c r="B375" s="9" t="s">
+        <v>72</v>
       </c>
       <c r="C375" s="4" t="s">
         <v>761</v>
@@ -15493,7 +15502,7 @@
         <v>762</v>
       </c>
       <c r="B376" s="9" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C376" s="4" t="s">
         <v>763</v>
@@ -15504,8 +15513,8 @@
       <c r="A377" s="4" t="s">
         <v>764</v>
       </c>
-      <c r="B377" s="9" t="s">
-        <v>64</v>
+      <c r="B377" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C377" s="4" t="s">
         <v>765</v>
@@ -15513,13 +15522,13 @@
       <c r="D377" s="13"/>
     </row>
     <row r="378" ht="22.5" customHeight="1">
-      <c r="A378" s="4" t="s">
+      <c r="A378" s="10" t="s">
         <v>766</v>
       </c>
       <c r="B378" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C378" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="C378" s="10" t="s">
         <v>767</v>
       </c>
       <c r="D378" s="13"/>
@@ -15528,8 +15537,8 @@
       <c r="A379" s="10" t="s">
         <v>768</v>
       </c>
-      <c r="B379" s="5" t="s">
-        <v>651</v>
+      <c r="B379" s="7" t="s">
+        <v>7</v>
       </c>
       <c r="C379" s="10" t="s">
         <v>769</v>
@@ -15537,13 +15546,13 @@
       <c r="D379" s="13"/>
     </row>
     <row r="380" ht="22.5" customHeight="1">
-      <c r="A380" s="10" t="s">
+      <c r="A380" s="4" t="s">
         <v>770</v>
       </c>
-      <c r="B380" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C380" s="10" t="s">
+      <c r="B380" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C380" s="4" t="s">
         <v>771</v>
       </c>
       <c r="D380" s="13"/>
@@ -23385,25 +23394,25 @@
       <c r="D1033" s="15"/>
     </row>
     <row r="1034" ht="22.5" customHeight="1">
-      <c r="A1034" s="10" t="s">
+      <c r="A1034" s="4" t="s">
         <v>2072</v>
       </c>
       <c r="B1034" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1034" s="10" t="s">
+      <c r="C1034" s="4" t="s">
         <v>2073</v>
       </c>
       <c r="D1034" s="15"/>
     </row>
     <row r="1035" ht="22.5" customHeight="1">
-      <c r="A1035" s="4" t="s">
+      <c r="A1035" s="10" t="s">
         <v>2074</v>
       </c>
       <c r="B1035" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1035" s="4" t="s">
+      <c r="C1035" s="10" t="s">
         <v>2075</v>
       </c>
       <c r="D1035" s="15"/>
@@ -23421,13 +23430,13 @@
       <c r="D1036" s="15"/>
     </row>
     <row r="1037" ht="22.5" customHeight="1">
-      <c r="A1037" s="10" t="s">
+      <c r="A1037" s="4" t="s">
         <v>2078</v>
       </c>
       <c r="B1037" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1037" s="10" t="s">
+      <c r="C1037" s="4" t="s">
         <v>2079</v>
       </c>
       <c r="D1037" s="15"/>
@@ -23457,37 +23466,37 @@
       <c r="D1039" s="15"/>
     </row>
     <row r="1040" ht="22.5" customHeight="1">
-      <c r="A1040" s="4" t="s">
+      <c r="A1040" s="10" t="s">
         <v>2084</v>
       </c>
       <c r="B1040" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1040" s="4" t="s">
+      <c r="C1040" s="10" t="s">
         <v>2085</v>
       </c>
       <c r="D1040" s="15"/>
     </row>
     <row r="1041" ht="22.5" customHeight="1">
-      <c r="A1041" s="10" t="s">
+      <c r="A1041" s="4" t="s">
         <v>2086</v>
       </c>
       <c r="B1041" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1041" s="10" t="s">
+      <c r="C1041" s="4" t="s">
         <v>2087</v>
       </c>
       <c r="D1041" s="15"/>
     </row>
     <row r="1042" ht="22.5" customHeight="1">
-      <c r="A1042" s="4" t="s">
+      <c r="A1042" s="10" t="s">
         <v>2088</v>
       </c>
       <c r="B1042" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1042" s="4" t="s">
+      <c r="C1042" s="10" t="s">
         <v>2089</v>
       </c>
       <c r="D1042" s="15"/>
@@ -23553,121 +23562,121 @@
       <c r="D1047" s="15"/>
     </row>
     <row r="1048" ht="22.5" customHeight="1">
-      <c r="A1048" s="10" t="s">
+      <c r="A1048" s="4" t="s">
         <v>2100</v>
       </c>
       <c r="B1048" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1048" s="10" t="s">
+      <c r="C1048" s="4" t="s">
         <v>2101</v>
       </c>
       <c r="D1048" s="15"/>
     </row>
     <row r="1049" ht="22.5" customHeight="1">
-      <c r="A1049" s="4" t="s">
+      <c r="A1049" s="10" t="s">
         <v>2102</v>
       </c>
       <c r="B1049" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1049" s="4" t="s">
+      <c r="C1049" s="10" t="s">
         <v>2103</v>
       </c>
       <c r="D1049" s="15"/>
     </row>
     <row r="1050" ht="22.5" customHeight="1">
-      <c r="A1050" s="10" t="s">
+      <c r="A1050" s="4" t="s">
         <v>2104</v>
       </c>
       <c r="B1050" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1050" s="10" t="s">
+      <c r="C1050" s="4" t="s">
         <v>2105</v>
       </c>
       <c r="D1050" s="15"/>
     </row>
     <row r="1051" ht="22.5" customHeight="1">
-      <c r="A1051" s="4" t="s">
+      <c r="A1051" s="10" t="s">
         <v>2106</v>
       </c>
       <c r="B1051" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1051" s="4" t="s">
+      <c r="C1051" s="10" t="s">
         <v>2107</v>
       </c>
       <c r="D1051" s="15"/>
     </row>
     <row r="1052" ht="22.5" customHeight="1">
-      <c r="A1052" s="10" t="s">
+      <c r="A1052" s="4" t="s">
         <v>2108</v>
       </c>
       <c r="B1052" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1052" s="10" t="s">
+      <c r="C1052" s="4" t="s">
         <v>2109</v>
       </c>
       <c r="D1052" s="15"/>
     </row>
     <row r="1053" ht="22.5" customHeight="1">
-      <c r="A1053" s="4" t="s">
+      <c r="A1053" s="10" t="s">
         <v>2110</v>
       </c>
       <c r="B1053" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1053" s="4" t="s">
+      <c r="C1053" s="10" t="s">
         <v>2111</v>
       </c>
       <c r="D1053" s="15"/>
     </row>
     <row r="1054" ht="22.5" customHeight="1">
-      <c r="A1054" s="10" t="s">
+      <c r="A1054" s="4" t="s">
         <v>2112</v>
       </c>
       <c r="B1054" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1054" s="10" t="s">
+      <c r="C1054" s="4" t="s">
         <v>2113</v>
       </c>
       <c r="D1054" s="15"/>
     </row>
     <row r="1055" ht="22.5" customHeight="1">
-      <c r="A1055" s="4" t="s">
+      <c r="A1055" s="10" t="s">
         <v>2114</v>
       </c>
       <c r="B1055" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1055" s="4" t="s">
+      <c r="C1055" s="10" t="s">
         <v>2115</v>
       </c>
       <c r="D1055" s="15"/>
     </row>
     <row r="1056" ht="22.5" customHeight="1">
-      <c r="A1056" s="10" t="s">
+      <c r="A1056" s="4" t="s">
         <v>2116</v>
       </c>
       <c r="B1056" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1056" s="10" t="s">
+      <c r="C1056" s="4" t="s">
         <v>2117</v>
       </c>
       <c r="D1056" s="15"/>
     </row>
     <row r="1057" ht="22.5" customHeight="1">
-      <c r="A1057" s="4" t="s">
+      <c r="A1057" s="10" t="s">
         <v>2118</v>
       </c>
       <c r="B1057" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1057" s="4" t="s">
+      <c r="C1057" s="10" t="s">
         <v>2119</v>
       </c>
       <c r="D1057" s="15"/>
@@ -23697,13 +23706,13 @@
       <c r="D1059" s="15"/>
     </row>
     <row r="1060" ht="22.5" customHeight="1">
-      <c r="A1060" s="10" t="s">
+      <c r="A1060" s="4" t="s">
         <v>2124</v>
       </c>
       <c r="B1060" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1060" s="10" t="s">
+      <c r="C1060" s="4" t="s">
         <v>2125</v>
       </c>
       <c r="D1060" s="15"/>
@@ -23721,13 +23730,13 @@
       <c r="D1061" s="15"/>
     </row>
     <row r="1062" ht="22.5" customHeight="1">
-      <c r="A1062" s="4" t="s">
+      <c r="A1062" s="10" t="s">
         <v>2128</v>
       </c>
       <c r="B1062" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1062" s="4" t="s">
+      <c r="C1062" s="10" t="s">
         <v>2129</v>
       </c>
       <c r="D1062" s="15"/>
@@ -23757,13 +23766,13 @@
       <c r="D1064" s="15"/>
     </row>
     <row r="1065" ht="22.5" customHeight="1">
-      <c r="A1065" s="10" t="s">
+      <c r="A1065" s="4" t="s">
         <v>2134</v>
       </c>
       <c r="B1065" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1065" s="10" t="s">
+      <c r="C1065" s="4" t="s">
         <v>2135</v>
       </c>
       <c r="D1065" s="15"/>
@@ -23775,13 +23784,13 @@
       <c r="B1066" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1066" s="4" t="s">
+      <c r="C1066" s="10" t="s">
         <v>2137</v>
       </c>
       <c r="D1066" s="15"/>
     </row>
     <row r="1067" ht="22.5" customHeight="1">
-      <c r="A1067" s="4" t="s">
+      <c r="A1067" s="10" t="s">
         <v>2138</v>
       </c>
       <c r="B1067" s="5" t="s">
@@ -23817,25 +23826,25 @@
       <c r="D1069" s="15"/>
     </row>
     <row r="1070" ht="22.5" customHeight="1">
-      <c r="A1070" s="10" t="s">
+      <c r="A1070" s="4" t="s">
         <v>2144</v>
       </c>
       <c r="B1070" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1070" s="10" t="s">
+      <c r="C1070" s="4" t="s">
         <v>2145</v>
       </c>
       <c r="D1070" s="15"/>
     </row>
     <row r="1071" ht="22.5" customHeight="1">
-      <c r="A1071" s="4" t="s">
+      <c r="A1071" s="10" t="s">
         <v>2146</v>
       </c>
       <c r="B1071" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1071" s="4" t="s">
+      <c r="C1071" s="10" t="s">
         <v>2147</v>
       </c>
       <c r="D1071" s="15"/>
@@ -23901,13 +23910,13 @@
       <c r="D1076" s="15"/>
     </row>
     <row r="1077" ht="22.5" customHeight="1">
-      <c r="A1077" s="10" t="s">
+      <c r="A1077" s="4" t="s">
         <v>2158</v>
       </c>
       <c r="B1077" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1077" s="10" t="s">
+      <c r="C1077" s="4" t="s">
         <v>2159</v>
       </c>
       <c r="D1077" s="15"/>
@@ -23925,13 +23934,13 @@
       <c r="D1078" s="15"/>
     </row>
     <row r="1079" ht="22.5" customHeight="1">
-      <c r="A1079" s="4" t="s">
+      <c r="A1079" s="10" t="s">
         <v>2162</v>
       </c>
       <c r="B1079" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1079" s="4" t="s">
+      <c r="C1079" s="10" t="s">
         <v>2163</v>
       </c>
       <c r="D1079" s="15"/>
@@ -23985,37 +23994,37 @@
       <c r="D1083" s="15"/>
     </row>
     <row r="1084" ht="22.5" customHeight="1">
-      <c r="A1084" s="10" t="s">
+      <c r="A1084" s="4" t="s">
         <v>2172</v>
       </c>
       <c r="B1084" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1084" s="10" t="s">
+      <c r="C1084" s="4" t="s">
         <v>2173</v>
       </c>
       <c r="D1084" s="15"/>
     </row>
     <row r="1085" ht="22.5" customHeight="1">
-      <c r="A1085" s="4" t="s">
+      <c r="A1085" s="10" t="s">
         <v>2174</v>
       </c>
       <c r="B1085" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1085" s="4" t="s">
+      <c r="C1085" s="10" t="s">
         <v>2175</v>
       </c>
       <c r="D1085" s="15"/>
     </row>
     <row r="1086" ht="22.5" customHeight="1">
-      <c r="A1086" s="10" t="s">
+      <c r="A1086" s="4" t="s">
         <v>2176</v>
       </c>
       <c r="B1086" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1086" s="10" t="s">
+      <c r="C1086" s="4" t="s">
         <v>2177</v>
       </c>
       <c r="D1086" s="15"/>
@@ -24033,37 +24042,37 @@
       <c r="D1087" s="15"/>
     </row>
     <row r="1088" ht="22.5" customHeight="1">
-      <c r="A1088" s="4" t="s">
+      <c r="A1088" s="10" t="s">
         <v>2180</v>
       </c>
       <c r="B1088" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1088" s="4" t="s">
+      <c r="C1088" s="10" t="s">
         <v>2181</v>
       </c>
       <c r="D1088" s="15"/>
     </row>
     <row r="1089" ht="22.5" customHeight="1">
-      <c r="A1089" s="10" t="s">
+      <c r="A1089" s="4" t="s">
         <v>2182</v>
       </c>
       <c r="B1089" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1089" s="10" t="s">
+      <c r="C1089" s="4" t="s">
         <v>2183</v>
       </c>
       <c r="D1089" s="15"/>
     </row>
     <row r="1090" ht="22.5" customHeight="1">
-      <c r="A1090" s="4" t="s">
+      <c r="A1090" s="10" t="s">
         <v>2184</v>
       </c>
       <c r="B1090" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1090" s="4" t="s">
+      <c r="C1090" s="10" t="s">
         <v>2185</v>
       </c>
       <c r="D1090" s="15"/>
@@ -24093,25 +24102,25 @@
       <c r="D1092" s="15"/>
     </row>
     <row r="1093" ht="22.5" customHeight="1">
-      <c r="A1093" s="10" t="s">
+      <c r="A1093" s="4" t="s">
         <v>2190</v>
       </c>
       <c r="B1093" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1093" s="10" t="s">
+      <c r="C1093" s="4" t="s">
         <v>2191</v>
       </c>
       <c r="D1093" s="15"/>
     </row>
     <row r="1094" ht="22.5" customHeight="1">
-      <c r="A1094" s="4" t="s">
+      <c r="A1094" s="10" t="s">
         <v>2192</v>
       </c>
       <c r="B1094" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1094" s="4" t="s">
+      <c r="C1094" s="10" t="s">
         <v>2193</v>
       </c>
       <c r="D1094" s="15"/>
@@ -24225,37 +24234,37 @@
       <c r="D1103" s="15"/>
     </row>
     <row r="1104" ht="22.5" customHeight="1">
-      <c r="A1104" s="10" t="s">
+      <c r="A1104" s="4" t="s">
         <v>2212</v>
       </c>
       <c r="B1104" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1104" s="10" t="s">
+      <c r="C1104" s="4" t="s">
         <v>2213</v>
       </c>
       <c r="D1104" s="15"/>
     </row>
     <row r="1105" ht="22.5" customHeight="1">
-      <c r="A1105" s="4" t="s">
+      <c r="A1105" s="10" t="s">
         <v>2214</v>
       </c>
       <c r="B1105" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1105" s="4" t="s">
+      <c r="C1105" s="10" t="s">
         <v>2215</v>
       </c>
       <c r="D1105" s="15"/>
     </row>
     <row r="1106" ht="22.5" customHeight="1">
-      <c r="A1106" s="10" t="s">
+      <c r="A1106" s="4" t="s">
         <v>2216</v>
       </c>
       <c r="B1106" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1106" s="10" t="s">
+      <c r="C1106" s="4" t="s">
         <v>2217</v>
       </c>
       <c r="D1106" s="15"/>
@@ -24285,13 +24294,13 @@
       <c r="D1108" s="15"/>
     </row>
     <row r="1109" ht="22.5" customHeight="1">
-      <c r="A1109" s="4" t="s">
+      <c r="A1109" s="10" t="s">
         <v>2222</v>
       </c>
       <c r="B1109" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1109" s="4" t="s">
+      <c r="C1109" s="10" t="s">
         <v>2223</v>
       </c>
       <c r="D1109" s="15"/>
@@ -24309,37 +24318,37 @@
       <c r="D1110" s="15"/>
     </row>
     <row r="1111" ht="22.5" customHeight="1">
-      <c r="A1111" s="10" t="s">
+      <c r="A1111" s="4" t="s">
         <v>2226</v>
       </c>
       <c r="B1111" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1111" s="10" t="s">
+      <c r="C1111" s="4" t="s">
         <v>2227</v>
       </c>
       <c r="D1111" s="15"/>
     </row>
     <row r="1112" ht="22.5" customHeight="1">
-      <c r="A1112" s="4" t="s">
+      <c r="A1112" s="10" t="s">
         <v>2228</v>
       </c>
       <c r="B1112" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1112" s="4" t="s">
+      <c r="C1112" s="10" t="s">
         <v>2229</v>
       </c>
       <c r="D1112" s="15"/>
     </row>
     <row r="1113" ht="22.5" customHeight="1">
-      <c r="A1113" s="10" t="s">
+      <c r="A1113" s="4" t="s">
         <v>2230</v>
       </c>
       <c r="B1113" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1113" s="10" t="s">
+      <c r="C1113" s="4" t="s">
         <v>2231</v>
       </c>
       <c r="D1113" s="15"/>
@@ -24369,13 +24378,13 @@
       <c r="D1115" s="15"/>
     </row>
     <row r="1116" ht="22.5" customHeight="1">
-      <c r="A1116" s="4" t="s">
+      <c r="A1116" s="10" t="s">
         <v>2236</v>
       </c>
       <c r="B1116" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1116" s="4" t="s">
+      <c r="C1116" s="10" t="s">
         <v>2237</v>
       </c>
       <c r="D1116" s="15"/>
@@ -24417,25 +24426,25 @@
       <c r="D1119" s="15"/>
     </row>
     <row r="1120" ht="22.5" customHeight="1">
-      <c r="A1120" s="10" t="s">
+      <c r="A1120" s="4" t="s">
         <v>2244</v>
       </c>
       <c r="B1120" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1120" s="10" t="s">
+      <c r="C1120" s="4" t="s">
         <v>2245</v>
       </c>
       <c r="D1120" s="15"/>
     </row>
     <row r="1121" ht="22.5" customHeight="1">
-      <c r="A1121" s="4" t="s">
+      <c r="A1121" s="10" t="s">
         <v>2246</v>
       </c>
       <c r="B1121" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1121" s="4" t="s">
+      <c r="C1121" s="10" t="s">
         <v>2247</v>
       </c>
       <c r="D1121" s="15"/>
@@ -24480,7 +24489,7 @@
       <c r="A1125" s="4" t="s">
         <v>2254</v>
       </c>
-      <c r="B1125" s="9" t="s">
+      <c r="B1125" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C1125" s="4" t="s">
@@ -24489,25 +24498,25 @@
       <c r="D1125" s="15"/>
     </row>
     <row r="1126" ht="22.5" customHeight="1">
-      <c r="A1126" s="10" t="s">
+      <c r="A1126" s="4" t="s">
         <v>2256</v>
       </c>
-      <c r="B1126" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1126" s="10" t="s">
+      <c r="B1126" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1126" s="4" t="s">
         <v>2257</v>
       </c>
       <c r="D1126" s="15"/>
     </row>
     <row r="1127" ht="22.5" customHeight="1">
-      <c r="A1127" s="4" t="s">
+      <c r="A1127" s="10" t="s">
         <v>2258</v>
       </c>
       <c r="B1127" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1127" s="4" t="s">
+      <c r="C1127" s="10" t="s">
         <v>2259</v>
       </c>
       <c r="D1127" s="15"/>
@@ -24525,25 +24534,25 @@
       <c r="D1128" s="15"/>
     </row>
     <row r="1129" ht="22.5" customHeight="1">
-      <c r="A1129" s="10" t="s">
+      <c r="A1129" s="4" t="s">
         <v>2262</v>
       </c>
       <c r="B1129" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1129" s="10" t="s">
+      <c r="C1129" s="4" t="s">
         <v>2263</v>
       </c>
       <c r="D1129" s="15"/>
     </row>
     <row r="1130" ht="22.5" customHeight="1">
-      <c r="A1130" s="4" t="s">
+      <c r="A1130" s="10" t="s">
         <v>2264</v>
       </c>
       <c r="B1130" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1130" s="4" t="s">
+      <c r="C1130" s="10" t="s">
         <v>2265</v>
       </c>
       <c r="D1130" s="15"/>
@@ -24573,49 +24582,49 @@
       <c r="D1132" s="15"/>
     </row>
     <row r="1133" ht="22.5" customHeight="1">
-      <c r="A1133" s="10" t="s">
+      <c r="A1133" s="4" t="s">
         <v>2270</v>
       </c>
       <c r="B1133" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1133" s="10" t="s">
+      <c r="C1133" s="4" t="s">
         <v>2271</v>
       </c>
       <c r="D1133" s="15"/>
     </row>
     <row r="1134" ht="22.5" customHeight="1">
-      <c r="A1134" s="4" t="s">
+      <c r="A1134" s="10" t="s">
         <v>2272</v>
       </c>
       <c r="B1134" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1134" s="4" t="s">
+      <c r="C1134" s="10" t="s">
         <v>2273</v>
       </c>
       <c r="D1134" s="15"/>
     </row>
     <row r="1135" ht="22.5" customHeight="1">
-      <c r="A1135" s="10" t="s">
+      <c r="A1135" s="4" t="s">
         <v>2274</v>
       </c>
       <c r="B1135" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1135" s="10" t="s">
+      <c r="C1135" s="4" t="s">
         <v>2275</v>
       </c>
       <c r="D1135" s="15"/>
     </row>
     <row r="1136" ht="22.5" customHeight="1">
-      <c r="A1136" s="4" t="s">
+      <c r="A1136" s="10" t="s">
         <v>2276</v>
       </c>
       <c r="B1136" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1136" s="4" t="s">
+      <c r="C1136" s="10" t="s">
         <v>2277</v>
       </c>
       <c r="D1136" s="15"/>
@@ -24633,13 +24642,13 @@
       <c r="D1137" s="15"/>
     </row>
     <row r="1138" ht="22.5" customHeight="1">
-      <c r="A1138" s="10" t="s">
+      <c r="A1138" s="4" t="s">
         <v>2280</v>
       </c>
       <c r="B1138" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1138" s="10" t="s">
+      <c r="C1138" s="4" t="s">
         <v>2281</v>
       </c>
       <c r="D1138" s="15"/>
@@ -24657,13 +24666,13 @@
       <c r="D1139" s="15"/>
     </row>
     <row r="1140" ht="22.5" customHeight="1">
-      <c r="A1140" s="4" t="s">
+      <c r="A1140" s="10" t="s">
         <v>2284</v>
       </c>
       <c r="B1140" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1140" s="4" t="s">
+      <c r="C1140" s="10" t="s">
         <v>2285</v>
       </c>
       <c r="D1140" s="15"/>
@@ -24675,13 +24684,13 @@
       <c r="B1141" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1141" s="10" t="s">
+      <c r="C1141" s="4" t="s">
         <v>2287</v>
       </c>
       <c r="D1141" s="15"/>
     </row>
     <row r="1142" ht="22.5" customHeight="1">
-      <c r="A1142" s="10" t="s">
+      <c r="A1142" s="4" t="s">
         <v>2288</v>
       </c>
       <c r="B1142" s="5" t="s">
@@ -24693,13 +24702,13 @@
       <c r="D1142" s="15"/>
     </row>
     <row r="1143" ht="22.5" customHeight="1">
-      <c r="A1143" s="4" t="s">
+      <c r="A1143" s="10" t="s">
         <v>2290</v>
       </c>
       <c r="B1143" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1143" s="4" t="s">
+      <c r="C1143" s="10" t="s">
         <v>2291</v>
       </c>
       <c r="D1143" s="15"/>
@@ -24717,61 +24726,61 @@
       <c r="D1144" s="15"/>
     </row>
     <row r="1145" ht="22.5" customHeight="1">
-      <c r="A1145" s="10" t="s">
+      <c r="A1145" s="4" t="s">
         <v>2294</v>
       </c>
       <c r="B1145" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1145" s="10" t="s">
+      <c r="C1145" s="4" t="s">
         <v>2295</v>
       </c>
       <c r="D1145" s="15"/>
     </row>
     <row r="1146" ht="22.5" customHeight="1">
-      <c r="A1146" s="4" t="s">
+      <c r="A1146" s="10" t="s">
         <v>2296</v>
       </c>
       <c r="B1146" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1146" s="4" t="s">
+      <c r="C1146" s="10" t="s">
         <v>2297</v>
       </c>
       <c r="D1146" s="15"/>
     </row>
     <row r="1147" ht="22.5" customHeight="1">
-      <c r="A1147" s="10" t="s">
+      <c r="A1147" s="4" t="s">
         <v>2298</v>
       </c>
       <c r="B1147" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1147" s="10" t="s">
+      <c r="C1147" s="4" t="s">
         <v>2299</v>
       </c>
       <c r="D1147" s="15"/>
     </row>
     <row r="1148" ht="22.5" customHeight="1">
-      <c r="A1148" s="4" t="s">
+      <c r="A1148" s="10" t="s">
         <v>2300</v>
       </c>
       <c r="B1148" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1148" s="4" t="s">
+      <c r="C1148" s="10" t="s">
         <v>2301</v>
       </c>
       <c r="D1148" s="15"/>
     </row>
     <row r="1149" ht="22.5" customHeight="1">
-      <c r="A1149" s="10" t="s">
+      <c r="A1149" s="4" t="s">
         <v>2302</v>
       </c>
       <c r="B1149" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1149" s="10" t="s">
+      <c r="C1149" s="4" t="s">
         <v>2303</v>
       </c>
       <c r="D1149" s="15"/>
@@ -24789,13 +24798,13 @@
       <c r="D1150" s="15"/>
     </row>
     <row r="1151" ht="22.5" customHeight="1">
-      <c r="A1151" s="4" t="s">
+      <c r="A1151" s="10" t="s">
         <v>2306</v>
       </c>
       <c r="B1151" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1151" s="4" t="s">
+      <c r="C1151" s="10" t="s">
         <v>2307</v>
       </c>
       <c r="D1151" s="15"/>
@@ -24849,25 +24858,25 @@
       <c r="D1155" s="15"/>
     </row>
     <row r="1156" ht="22.5" customHeight="1">
-      <c r="A1156" s="10" t="s">
+      <c r="A1156" s="4" t="s">
         <v>2316</v>
       </c>
       <c r="B1156" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1156" s="10" t="s">
+      <c r="C1156" s="4" t="s">
         <v>2317</v>
       </c>
       <c r="D1156" s="15"/>
     </row>
     <row r="1157" ht="22.5" customHeight="1">
-      <c r="A1157" s="4" t="s">
+      <c r="A1157" s="10" t="s">
         <v>2318</v>
       </c>
       <c r="B1157" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1157" s="4" t="s">
+      <c r="C1157" s="10" t="s">
         <v>2319</v>
       </c>
       <c r="D1157" s="15"/>
@@ -24885,25 +24894,25 @@
       <c r="D1158" s="15"/>
     </row>
     <row r="1159" ht="22.5" customHeight="1">
-      <c r="A1159" s="10" t="s">
+      <c r="A1159" s="4" t="s">
         <v>2322</v>
       </c>
       <c r="B1159" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1159" s="10" t="s">
+      <c r="C1159" s="4" t="s">
         <v>2323</v>
       </c>
       <c r="D1159" s="15"/>
     </row>
     <row r="1160" ht="22.5" customHeight="1">
-      <c r="A1160" s="4" t="s">
+      <c r="A1160" s="10" t="s">
         <v>2324</v>
       </c>
-      <c r="B1160" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1160" s="4" t="s">
+      <c r="B1160" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1160" s="10" t="s">
         <v>2325</v>
       </c>
       <c r="D1160" s="15"/>
@@ -24912,7 +24921,7 @@
       <c r="A1161" s="4" t="s">
         <v>2326</v>
       </c>
-      <c r="B1161" s="19" t="s">
+      <c r="B1161" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C1161" s="4" t="s">
@@ -24921,25 +24930,25 @@
       <c r="D1161" s="15"/>
     </row>
     <row r="1162" ht="22.5" customHeight="1">
-      <c r="A1162" s="10" t="s">
+      <c r="A1162" s="4" t="s">
         <v>2328</v>
       </c>
-      <c r="B1162" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1162" s="10" t="s">
+      <c r="B1162" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1162" s="4" t="s">
         <v>2329</v>
       </c>
       <c r="D1162" s="15"/>
     </row>
     <row r="1163" ht="22.5" customHeight="1">
-      <c r="A1163" s="4" t="s">
+      <c r="A1163" s="10" t="s">
         <v>2330</v>
       </c>
       <c r="B1163" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1163" s="4" t="s">
+      <c r="C1163" s="10" t="s">
         <v>2331</v>
       </c>
       <c r="D1163" s="15"/>
@@ -24957,25 +24966,25 @@
       <c r="D1164" s="15"/>
     </row>
     <row r="1165" ht="22.5" customHeight="1">
-      <c r="A1165" s="10" t="s">
+      <c r="A1165" s="4" t="s">
         <v>2334</v>
       </c>
       <c r="B1165" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1165" s="10" t="s">
+      <c r="C1165" s="4" t="s">
         <v>2335</v>
       </c>
       <c r="D1165" s="15"/>
     </row>
     <row r="1166" ht="22.5" customHeight="1">
-      <c r="A1166" s="4" t="s">
+      <c r="A1166" s="10" t="s">
         <v>2336</v>
       </c>
       <c r="B1166" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1166" s="4" t="s">
+      <c r="C1166" s="10" t="s">
         <v>2337</v>
       </c>
       <c r="D1166" s="15"/>
@@ -24993,25 +25002,25 @@
       <c r="D1167" s="15"/>
     </row>
     <row r="1168" ht="22.5" customHeight="1">
-      <c r="A1168" s="10" t="s">
+      <c r="A1168" s="4" t="s">
         <v>2340</v>
       </c>
       <c r="B1168" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1168" s="10" t="s">
+      <c r="C1168" s="4" t="s">
         <v>2341</v>
       </c>
       <c r="D1168" s="15"/>
     </row>
     <row r="1169" ht="22.5" customHeight="1">
-      <c r="A1169" s="4" t="s">
+      <c r="A1169" s="10" t="s">
         <v>2342</v>
       </c>
       <c r="B1169" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1169" s="4" t="s">
+      <c r="C1169" s="10" t="s">
         <v>2343</v>
       </c>
       <c r="D1169" s="15"/>
@@ -25077,97 +25086,97 @@
       <c r="D1174" s="15"/>
     </row>
     <row r="1175" ht="22.5" customHeight="1">
-      <c r="A1175" s="10" t="s">
+      <c r="A1175" s="4" t="s">
         <v>2354</v>
       </c>
       <c r="B1175" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1175" s="10" t="s">
+      <c r="C1175" s="4" t="s">
         <v>2355</v>
       </c>
       <c r="D1175" s="15"/>
     </row>
     <row r="1176" ht="22.5" customHeight="1">
-      <c r="A1176" s="4" t="s">
+      <c r="A1176" s="10" t="s">
         <v>2356</v>
       </c>
       <c r="B1176" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1176" s="4" t="s">
+      <c r="C1176" s="10" t="s">
         <v>2357</v>
       </c>
       <c r="D1176" s="15"/>
     </row>
     <row r="1177" ht="22.5" customHeight="1">
-      <c r="A1177" s="10" t="s">
+      <c r="A1177" s="4" t="s">
         <v>2358</v>
       </c>
       <c r="B1177" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1177" s="10" t="s">
+      <c r="C1177" s="4" t="s">
         <v>2359</v>
       </c>
       <c r="D1177" s="15"/>
     </row>
     <row r="1178" ht="22.5" customHeight="1">
-      <c r="A1178" s="4" t="s">
+      <c r="A1178" s="10" t="s">
         <v>2360</v>
       </c>
       <c r="B1178" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1178" s="4" t="s">
+      <c r="C1178" s="10" t="s">
         <v>2361</v>
       </c>
       <c r="D1178" s="15"/>
     </row>
     <row r="1179" ht="22.5" customHeight="1">
-      <c r="A1179" s="10" t="s">
+      <c r="A1179" s="4" t="s">
         <v>2362</v>
       </c>
       <c r="B1179" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1179" s="10" t="s">
+      <c r="C1179" s="4" t="s">
         <v>2363</v>
       </c>
       <c r="D1179" s="15"/>
     </row>
     <row r="1180" ht="22.5" customHeight="1">
-      <c r="A1180" s="4" t="s">
+      <c r="A1180" s="10" t="s">
         <v>2364</v>
       </c>
       <c r="B1180" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1180" s="4" t="s">
+      <c r="C1180" s="10" t="s">
         <v>2365</v>
       </c>
       <c r="D1180" s="15"/>
     </row>
     <row r="1181" ht="22.5" customHeight="1">
-      <c r="A1181" s="10" t="s">
+      <c r="A1181" s="4" t="s">
         <v>2366</v>
       </c>
       <c r="B1181" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1181" s="10" t="s">
+      <c r="C1181" s="4" t="s">
         <v>2367</v>
       </c>
       <c r="D1181" s="15"/>
     </row>
     <row r="1182" ht="22.5" customHeight="1">
-      <c r="A1182" s="4" t="s">
+      <c r="A1182" s="10" t="s">
         <v>2368</v>
       </c>
       <c r="B1182" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1182" s="4" t="s">
+      <c r="C1182" s="10" t="s">
         <v>2369</v>
       </c>
       <c r="D1182" s="15"/>
@@ -25299,7 +25308,7 @@
       <c r="B1193" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1193" s="10" t="s">
+      <c r="C1193" s="4" t="s">
         <v>2391</v>
       </c>
       <c r="D1193" s="15"/>
@@ -25311,55 +25320,55 @@
       <c r="B1194" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1194" s="4" t="s">
+      <c r="C1194" s="10" t="s">
         <v>2393</v>
       </c>
       <c r="D1194" s="15"/>
     </row>
     <row r="1195" ht="22.5" customHeight="1">
-      <c r="A1195" s="10" t="s">
+      <c r="A1195" s="4" t="s">
         <v>2394</v>
       </c>
       <c r="B1195" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1195" s="10" t="s">
+      <c r="C1195" s="4" t="s">
         <v>2395</v>
       </c>
       <c r="D1195" s="15"/>
     </row>
     <row r="1196" ht="22.5" customHeight="1">
-      <c r="A1196" s="4" t="s">
+      <c r="A1196" s="10" t="s">
         <v>2396</v>
       </c>
       <c r="B1196" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1196" s="4" t="s">
+      <c r="C1196" s="10" t="s">
         <v>2397</v>
       </c>
       <c r="D1196" s="15"/>
     </row>
     <row r="1197" ht="22.5" customHeight="1">
-      <c r="A1197" s="10" t="s">
+      <c r="A1197" s="4" t="s">
         <v>2398</v>
       </c>
       <c r="B1197" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1197" s="10" t="s">
+      <c r="C1197" s="4" t="s">
         <v>2399</v>
       </c>
       <c r="D1197" s="15"/>
     </row>
     <row r="1198" ht="22.5" customHeight="1">
-      <c r="A1198" s="4" t="s">
+      <c r="A1198" s="10" t="s">
         <v>2400</v>
       </c>
       <c r="B1198" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1198" s="4" t="s">
+      <c r="C1198" s="10" t="s">
         <v>2401</v>
       </c>
       <c r="D1198" s="15"/>
@@ -25401,49 +25410,49 @@
       <c r="D1201" s="15"/>
     </row>
     <row r="1202" ht="22.5" customHeight="1">
-      <c r="A1202" s="10" t="s">
+      <c r="A1202" s="4" t="s">
         <v>2408</v>
       </c>
       <c r="B1202" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1202" s="10" t="s">
+      <c r="C1202" s="4" t="s">
         <v>2409</v>
       </c>
       <c r="D1202" s="15"/>
     </row>
     <row r="1203" ht="22.5" customHeight="1">
-      <c r="A1203" s="4" t="s">
+      <c r="A1203" s="10" t="s">
         <v>2410</v>
       </c>
       <c r="B1203" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1203" s="4" t="s">
+      <c r="C1203" s="10" t="s">
         <v>2411</v>
       </c>
       <c r="D1203" s="15"/>
     </row>
     <row r="1204" ht="22.5" customHeight="1">
-      <c r="A1204" s="10" t="s">
+      <c r="A1204" s="4" t="s">
         <v>2412</v>
       </c>
       <c r="B1204" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1204" s="10" t="s">
+      <c r="C1204" s="4" t="s">
         <v>2413</v>
       </c>
       <c r="D1204" s="15"/>
     </row>
     <row r="1205" ht="22.5" customHeight="1">
-      <c r="A1205" s="4" t="s">
+      <c r="A1205" s="10" t="s">
         <v>2414</v>
       </c>
       <c r="B1205" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1205" s="4" t="s">
+      <c r="C1205" s="10" t="s">
         <v>2415</v>
       </c>
       <c r="D1205" s="15"/>
@@ -25569,25 +25578,25 @@
       <c r="D1215" s="15"/>
     </row>
     <row r="1216" ht="22.5" customHeight="1">
-      <c r="A1216" s="10" t="s">
+      <c r="A1216" s="4" t="s">
         <v>2436</v>
       </c>
       <c r="B1216" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1216" s="10" t="s">
+      <c r="C1216" s="4" t="s">
         <v>2437</v>
       </c>
       <c r="D1216" s="15"/>
     </row>
     <row r="1217" ht="22.5" customHeight="1">
-      <c r="A1217" s="4" t="s">
+      <c r="A1217" s="10" t="s">
         <v>2438</v>
       </c>
       <c r="B1217" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1217" s="4" t="s">
+      <c r="C1217" s="10" t="s">
         <v>2439</v>
       </c>
       <c r="D1217" s="15"/>
@@ -25653,73 +25662,73 @@
       <c r="D1222" s="15"/>
     </row>
     <row r="1223" ht="22.5" customHeight="1">
-      <c r="A1223" s="10" t="s">
+      <c r="A1223" s="4" t="s">
         <v>2450</v>
       </c>
       <c r="B1223" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1223" s="10" t="s">
+      <c r="C1223" s="4" t="s">
         <v>2451</v>
       </c>
       <c r="D1223" s="15"/>
     </row>
     <row r="1224" ht="22.5" customHeight="1">
-      <c r="A1224" s="4" t="s">
+      <c r="A1224" s="10" t="s">
         <v>2452</v>
       </c>
       <c r="B1224" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1224" s="4" t="s">
+      <c r="C1224" s="10" t="s">
         <v>2453</v>
       </c>
       <c r="D1224" s="15"/>
     </row>
     <row r="1225" ht="22.5" customHeight="1">
-      <c r="A1225" s="10" t="s">
+      <c r="A1225" s="4" t="s">
         <v>2454</v>
       </c>
       <c r="B1225" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1225" s="10" t="s">
+      <c r="C1225" s="4" t="s">
         <v>2455</v>
       </c>
       <c r="D1225" s="15"/>
     </row>
     <row r="1226" ht="22.5" customHeight="1">
-      <c r="A1226" s="4" t="s">
+      <c r="A1226" s="10" t="s">
         <v>2456</v>
       </c>
       <c r="B1226" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1226" s="4" t="s">
+      <c r="C1226" s="10" t="s">
         <v>2457</v>
       </c>
       <c r="D1226" s="15"/>
     </row>
     <row r="1227" ht="22.5" customHeight="1">
-      <c r="A1227" s="10" t="s">
+      <c r="A1227" s="4" t="s">
         <v>2458</v>
       </c>
       <c r="B1227" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1227" s="10" t="s">
+      <c r="C1227" s="4" t="s">
         <v>2459</v>
       </c>
       <c r="D1227" s="15"/>
     </row>
     <row r="1228" ht="22.5" customHeight="1">
-      <c r="A1228" s="4" t="s">
+      <c r="A1228" s="10" t="s">
         <v>2460</v>
       </c>
       <c r="B1228" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1228" s="4" t="s">
+      <c r="C1228" s="10" t="s">
         <v>2461</v>
       </c>
       <c r="D1228" s="15"/>
@@ -25785,25 +25794,25 @@
       <c r="D1233" s="15"/>
     </row>
     <row r="1234" ht="22.5" customHeight="1">
-      <c r="A1234" s="10" t="s">
+      <c r="A1234" s="4" t="s">
         <v>2472</v>
       </c>
       <c r="B1234" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1234" s="10" t="s">
+      <c r="C1234" s="4" t="s">
         <v>2473</v>
       </c>
       <c r="D1234" s="15"/>
     </row>
     <row r="1235" ht="22.5" customHeight="1">
-      <c r="A1235" s="4" t="s">
+      <c r="A1235" s="10" t="s">
         <v>2474</v>
       </c>
       <c r="B1235" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1235" s="4" t="s">
+      <c r="C1235" s="10" t="s">
         <v>2475</v>
       </c>
       <c r="D1235" s="15"/>
@@ -25953,13 +25962,13 @@
       <c r="D1247" s="15"/>
     </row>
     <row r="1248" ht="22.5" customHeight="1">
-      <c r="A1248" s="10" t="s">
+      <c r="A1248" s="4" t="s">
         <v>2500</v>
       </c>
       <c r="B1248" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1248" s="10" t="s">
+      <c r="C1248" s="4" t="s">
         <v>2501</v>
       </c>
       <c r="D1248" s="15"/>
@@ -25989,73 +25998,73 @@
       <c r="D1250" s="15"/>
     </row>
     <row r="1251" ht="22.5" customHeight="1">
-      <c r="A1251" s="4" t="s">
+      <c r="A1251" s="10" t="s">
         <v>2506</v>
       </c>
       <c r="B1251" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1251" s="4" t="s">
+      <c r="C1251" s="10" t="s">
         <v>2507</v>
       </c>
       <c r="D1251" s="15"/>
     </row>
     <row r="1252" ht="22.5" customHeight="1">
-      <c r="A1252" s="10" t="s">
+      <c r="A1252" s="4" t="s">
         <v>2508</v>
       </c>
       <c r="B1252" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1252" s="10" t="s">
+      <c r="C1252" s="4" t="s">
         <v>2509</v>
       </c>
       <c r="D1252" s="15"/>
     </row>
     <row r="1253" ht="22.5" customHeight="1">
-      <c r="A1253" s="4" t="s">
+      <c r="A1253" s="10" t="s">
         <v>2510</v>
       </c>
       <c r="B1253" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1253" s="4" t="s">
+      <c r="C1253" s="10" t="s">
         <v>2511</v>
       </c>
       <c r="D1253" s="15"/>
     </row>
     <row r="1254" ht="22.5" customHeight="1">
-      <c r="A1254" s="10" t="s">
+      <c r="A1254" s="4" t="s">
         <v>2512</v>
       </c>
       <c r="B1254" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1254" s="10" t="s">
+      <c r="C1254" s="4" t="s">
         <v>2513</v>
       </c>
       <c r="D1254" s="15"/>
     </row>
     <row r="1255" ht="22.5" customHeight="1">
-      <c r="A1255" s="4" t="s">
+      <c r="A1255" s="10" t="s">
         <v>2514</v>
       </c>
       <c r="B1255" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1255" s="4" t="s">
+      <c r="C1255" s="10" t="s">
         <v>2515</v>
       </c>
       <c r="D1255" s="15"/>
     </row>
     <row r="1256" ht="22.5" customHeight="1">
-      <c r="A1256" s="10" t="s">
+      <c r="A1256" s="4" t="s">
         <v>2516</v>
       </c>
       <c r="B1256" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1256" s="10" t="s">
+      <c r="C1256" s="4" t="s">
         <v>2517</v>
       </c>
       <c r="D1256" s="15"/>
@@ -26073,13 +26082,13 @@
       <c r="D1257" s="15"/>
     </row>
     <row r="1258" ht="22.5" customHeight="1">
-      <c r="A1258" s="4" t="s">
+      <c r="A1258" s="10" t="s">
         <v>2520</v>
       </c>
       <c r="B1258" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1258" s="4" t="s">
+      <c r="C1258" s="10" t="s">
         <v>2521</v>
       </c>
       <c r="D1258" s="15"/>
@@ -26088,7 +26097,7 @@
       <c r="A1259" s="4" t="s">
         <v>2522</v>
       </c>
-      <c r="B1259" s="9" t="s">
+      <c r="B1259" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C1259" s="4" t="s">
@@ -26097,13 +26106,13 @@
       <c r="D1259" s="15"/>
     </row>
     <row r="1260" ht="22.5" customHeight="1">
-      <c r="A1260" s="10" t="s">
+      <c r="A1260" s="4" t="s">
         <v>2524</v>
       </c>
-      <c r="B1260" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1260" s="10" t="s">
+      <c r="B1260" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1260" s="4" t="s">
         <v>2525</v>
       </c>
       <c r="D1260" s="15"/>
@@ -26121,13 +26130,13 @@
       <c r="D1261" s="15"/>
     </row>
     <row r="1262" ht="22.5" customHeight="1">
-      <c r="A1262" s="4" t="s">
+      <c r="A1262" s="10" t="s">
         <v>2528</v>
       </c>
       <c r="B1262" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1262" s="4" t="s">
+      <c r="C1262" s="10" t="s">
         <v>2529</v>
       </c>
       <c r="D1262" s="15"/>
@@ -26181,13 +26190,13 @@
       <c r="D1266" s="15"/>
     </row>
     <row r="1267" ht="22.5" customHeight="1">
-      <c r="A1267" s="10" t="s">
+      <c r="A1267" s="4" t="s">
         <v>2538</v>
       </c>
       <c r="B1267" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1267" s="10" t="s">
+      <c r="C1267" s="4" t="s">
         <v>2539</v>
       </c>
       <c r="D1267" s="15"/>
@@ -26217,25 +26226,25 @@
       <c r="D1269" s="15"/>
     </row>
     <row r="1270" ht="22.5" customHeight="1">
-      <c r="A1270" s="10" t="s">
+      <c r="A1270" s="4" t="s">
         <v>2544</v>
       </c>
       <c r="B1270" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1270" s="10" t="s">
+      <c r="C1270" s="4" t="s">
         <v>2545</v>
       </c>
       <c r="D1270" s="15"/>
     </row>
     <row r="1271" ht="22.5" customHeight="1">
-      <c r="A1271" s="4" t="s">
+      <c r="A1271" s="10" t="s">
         <v>2546</v>
       </c>
       <c r="B1271" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1271" s="4" t="s">
+      <c r="C1271" s="10" t="s">
         <v>2547</v>
       </c>
       <c r="D1271" s="15"/>
@@ -26289,13 +26298,13 @@
       <c r="D1275" s="15"/>
     </row>
     <row r="1276" ht="22.5" customHeight="1">
-      <c r="A1276" s="4" t="s">
+      <c r="A1276" s="10" t="s">
         <v>2556</v>
       </c>
       <c r="B1276" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1276" s="4" t="s">
+      <c r="C1276" s="10" t="s">
         <v>2557</v>
       </c>
       <c r="D1276" s="15"/>
@@ -26313,13 +26322,13 @@
       <c r="D1277" s="15"/>
     </row>
     <row r="1278" ht="22.5" customHeight="1">
-      <c r="A1278" s="10" t="s">
+      <c r="A1278" s="4" t="s">
         <v>2560</v>
       </c>
       <c r="B1278" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1278" s="10" t="s">
+      <c r="C1278" s="4" t="s">
         <v>2561</v>
       </c>
       <c r="D1278" s="15"/>
@@ -26361,25 +26370,25 @@
       <c r="D1281" s="15"/>
     </row>
     <row r="1282" ht="22.5" customHeight="1">
-      <c r="A1282" s="4" t="s">
+      <c r="A1282" s="10" t="s">
         <v>2568</v>
       </c>
       <c r="B1282" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1282" s="4" t="s">
+      <c r="C1282" s="10" t="s">
         <v>2569</v>
       </c>
       <c r="D1282" s="15"/>
     </row>
     <row r="1283" ht="22.5" customHeight="1">
-      <c r="A1283" s="10" t="s">
+      <c r="A1283" s="4" t="s">
         <v>2570</v>
       </c>
       <c r="B1283" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1283" s="10" t="s">
+      <c r="C1283" s="4" t="s">
         <v>2571</v>
       </c>
       <c r="D1283" s="15"/>
@@ -26397,25 +26406,25 @@
       <c r="D1284" s="15"/>
     </row>
     <row r="1285" ht="22.5" customHeight="1">
-      <c r="A1285" s="4" t="s">
+      <c r="A1285" s="10" t="s">
         <v>2574</v>
       </c>
       <c r="B1285" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1285" s="4" t="s">
+      <c r="C1285" s="10" t="s">
         <v>2575</v>
       </c>
       <c r="D1285" s="15"/>
     </row>
     <row r="1286" ht="22.5" customHeight="1">
-      <c r="A1286" s="10" t="s">
+      <c r="A1286" s="4" t="s">
         <v>2576</v>
       </c>
       <c r="B1286" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1286" s="10" t="s">
+      <c r="C1286" s="4" t="s">
         <v>2577</v>
       </c>
       <c r="D1286" s="15"/>
@@ -26433,13 +26442,13 @@
       <c r="D1287" s="15"/>
     </row>
     <row r="1288" ht="22.5" customHeight="1">
-      <c r="A1288" s="4" t="s">
+      <c r="A1288" s="10" t="s">
         <v>2580</v>
       </c>
       <c r="B1288" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1288" s="4" t="s">
+      <c r="C1288" s="10" t="s">
         <v>2581</v>
       </c>
       <c r="D1288" s="15"/>
@@ -26469,37 +26478,37 @@
       <c r="D1290" s="15"/>
     </row>
     <row r="1291" ht="22.5" customHeight="1">
-      <c r="A1291" s="10" t="s">
+      <c r="A1291" s="4" t="s">
         <v>2586</v>
       </c>
       <c r="B1291" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1291" s="10" t="s">
+      <c r="C1291" s="4" t="s">
         <v>2587</v>
       </c>
       <c r="D1291" s="15"/>
     </row>
     <row r="1292" ht="22.5" customHeight="1">
-      <c r="A1292" s="10" t="s">
+      <c r="A1292" s="4" t="s">
         <v>2588</v>
       </c>
       <c r="B1292" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1292" s="10" t="s">
+      <c r="C1292" s="4" t="s">
         <v>2589</v>
       </c>
       <c r="D1292" s="15"/>
     </row>
     <row r="1293" ht="22.5" customHeight="1">
-      <c r="A1293" s="4" t="s">
+      <c r="A1293" s="10" t="s">
         <v>2590</v>
       </c>
       <c r="B1293" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1293" s="4" t="s">
+      <c r="C1293" s="10" t="s">
         <v>2591</v>
       </c>
       <c r="D1293" s="15"/>
@@ -26541,13 +26550,13 @@
       <c r="D1296" s="15"/>
     </row>
     <row r="1297" ht="22.5" customHeight="1">
-      <c r="A1297" s="10" t="s">
+      <c r="A1297" s="4" t="s">
         <v>2598</v>
       </c>
       <c r="B1297" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1297" s="10" t="s">
+      <c r="C1297" s="4" t="s">
         <v>2599</v>
       </c>
       <c r="D1297" s="15"/>
@@ -26565,37 +26574,37 @@
       <c r="D1298" s="15"/>
     </row>
     <row r="1299" ht="22.5" customHeight="1">
-      <c r="A1299" s="4" t="s">
+      <c r="A1299" s="10" t="s">
         <v>2602</v>
       </c>
       <c r="B1299" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1299" s="4" t="s">
+      <c r="C1299" s="10" t="s">
         <v>2603</v>
       </c>
       <c r="D1299" s="15"/>
     </row>
     <row r="1300" ht="22.5" customHeight="1">
-      <c r="A1300" s="4" t="s">
+      <c r="A1300" s="10" t="s">
         <v>2604</v>
       </c>
       <c r="B1300" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1300" s="4" t="s">
+      <c r="C1300" s="10" t="s">
         <v>2605</v>
       </c>
       <c r="D1300" s="15"/>
     </row>
     <row r="1301" ht="22.5" customHeight="1">
-      <c r="A1301" s="10" t="s">
+      <c r="A1301" s="4" t="s">
         <v>2606</v>
       </c>
       <c r="B1301" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1301" s="10" t="s">
+      <c r="C1301" s="4" t="s">
         <v>2607</v>
       </c>
       <c r="D1301" s="15"/>
@@ -26613,49 +26622,49 @@
       <c r="D1302" s="15"/>
     </row>
     <row r="1303" ht="22.5" customHeight="1">
-      <c r="A1303" s="4" t="s">
+      <c r="A1303" s="10" t="s">
         <v>2610</v>
       </c>
       <c r="B1303" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1303" s="4" t="s">
+      <c r="C1303" s="10" t="s">
         <v>2611</v>
       </c>
       <c r="D1303" s="15"/>
     </row>
     <row r="1304" ht="22.5" customHeight="1">
-      <c r="A1304" s="10" t="s">
+      <c r="A1304" s="4" t="s">
         <v>2612</v>
       </c>
       <c r="B1304" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1304" s="10" t="s">
+      <c r="C1304" s="4" t="s">
         <v>2613</v>
       </c>
       <c r="D1304" s="15"/>
     </row>
     <row r="1305" ht="22.5" customHeight="1">
-      <c r="A1305" s="10" t="s">
+      <c r="A1305" s="4" t="s">
         <v>2614</v>
       </c>
       <c r="B1305" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1305" s="10" t="s">
+      <c r="C1305" s="4" t="s">
         <v>2615</v>
       </c>
       <c r="D1305" s="15"/>
     </row>
     <row r="1306" ht="22.5" customHeight="1">
-      <c r="A1306" s="4" t="s">
+      <c r="A1306" s="10" t="s">
         <v>2616</v>
       </c>
       <c r="B1306" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1306" s="4" t="s">
+      <c r="C1306" s="10" t="s">
         <v>2617</v>
       </c>
       <c r="D1306" s="15"/>
@@ -26689,7 +26698,7 @@
         <v>2622</v>
       </c>
       <c r="B1309" s="5" t="s">
-        <v>238</v>
+        <v>4</v>
       </c>
       <c r="C1309" s="10" t="s">
         <v>2623</v>
@@ -26700,8 +26709,8 @@
       <c r="A1310" s="4" t="s">
         <v>2624</v>
       </c>
-      <c r="B1310" s="9" t="s">
-        <v>72</v>
+      <c r="B1310" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C1310" s="4" t="s">
         <v>2625</v>
@@ -26709,13 +26718,13 @@
       <c r="D1310" s="15"/>
     </row>
     <row r="1311" ht="22.5" customHeight="1">
-      <c r="A1311" s="4" t="s">
+      <c r="A1311" s="10" t="s">
         <v>2626</v>
       </c>
-      <c r="B1311" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1311" s="4" t="s">
+      <c r="B1311" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C1311" s="10" t="s">
         <v>2627</v>
       </c>
       <c r="D1311" s="15"/>
@@ -26724,7 +26733,7 @@
       <c r="A1312" s="4" t="s">
         <v>2628</v>
       </c>
-      <c r="B1312" s="7" t="s">
+      <c r="B1312" s="9" t="s">
         <v>72</v>
       </c>
       <c r="C1312" s="4" t="s">
@@ -26733,13 +26742,13 @@
       <c r="D1312" s="15"/>
     </row>
     <row r="1313" ht="22.5" customHeight="1">
-      <c r="A1313" s="10" t="s">
+      <c r="A1313" s="4" t="s">
         <v>2630</v>
       </c>
-      <c r="B1313" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1313" s="10" t="s">
+      <c r="B1313" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1313" s="4" t="s">
         <v>2631</v>
       </c>
       <c r="D1313" s="15"/>
@@ -26749,7 +26758,7 @@
         <v>2632</v>
       </c>
       <c r="B1314" s="7" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="C1314" s="4" t="s">
         <v>2633</v>
@@ -26757,13 +26766,13 @@
       <c r="D1314" s="15"/>
     </row>
     <row r="1315" ht="22.5" customHeight="1">
-      <c r="A1315" s="4" t="s">
+      <c r="A1315" s="10" t="s">
         <v>2634</v>
       </c>
-      <c r="B1315" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1315" s="4" t="s">
+      <c r="B1315" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1315" s="10" t="s">
         <v>2635</v>
       </c>
       <c r="D1315" s="15"/>
@@ -26772,7 +26781,7 @@
       <c r="A1316" s="4" t="s">
         <v>2636</v>
       </c>
-      <c r="B1316" s="5" t="s">
+      <c r="B1316" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C1316" s="4" t="s">
@@ -26784,7 +26793,7 @@
       <c r="A1317" s="4" t="s">
         <v>2638</v>
       </c>
-      <c r="B1317" s="7" t="s">
+      <c r="B1317" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C1317" s="4" t="s">
@@ -26793,13 +26802,13 @@
       <c r="D1317" s="15"/>
     </row>
     <row r="1318" ht="22.5" customHeight="1">
-      <c r="A1318" s="10" t="s">
+      <c r="A1318" s="4" t="s">
         <v>2640</v>
       </c>
       <c r="B1318" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1318" s="10" t="s">
+      <c r="C1318" s="4" t="s">
         <v>2641</v>
       </c>
       <c r="D1318" s="15"/>
@@ -26808,7 +26817,7 @@
       <c r="A1319" s="4" t="s">
         <v>2642</v>
       </c>
-      <c r="B1319" s="5" t="s">
+      <c r="B1319" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C1319" s="4" t="s">
@@ -26817,13 +26826,13 @@
       <c r="D1319" s="15"/>
     </row>
     <row r="1320" ht="22.5" customHeight="1">
-      <c r="A1320" s="4" t="s">
+      <c r="A1320" s="10" t="s">
         <v>2644</v>
       </c>
-      <c r="B1320" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1320" s="4" t="s">
+      <c r="B1320" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1320" s="10" t="s">
         <v>2645</v>
       </c>
       <c r="D1320" s="15"/>
@@ -26844,7 +26853,7 @@
       <c r="A1322" s="4" t="s">
         <v>2648</v>
       </c>
-      <c r="B1322" s="5" t="s">
+      <c r="B1322" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C1322" s="4" t="s">
@@ -26853,13 +26862,13 @@
       <c r="D1322" s="15"/>
     </row>
     <row r="1323" ht="22.5" customHeight="1">
-      <c r="A1323" s="10" t="s">
+      <c r="A1323" s="4" t="s">
         <v>2650</v>
       </c>
       <c r="B1323" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1323" s="10" t="s">
+      <c r="C1323" s="4" t="s">
         <v>2651</v>
       </c>
       <c r="D1323" s="15"/>
@@ -26889,25 +26898,25 @@
       <c r="D1325" s="15"/>
     </row>
     <row r="1326" ht="22.5" customHeight="1">
-      <c r="A1326" s="10" t="s">
+      <c r="A1326" s="4" t="s">
         <v>2656</v>
       </c>
       <c r="B1326" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1326" s="10" t="s">
+      <c r="C1326" s="4" t="s">
         <v>2657</v>
       </c>
       <c r="D1326" s="15"/>
     </row>
     <row r="1327" ht="22.5" customHeight="1">
-      <c r="A1327" s="4" t="s">
+      <c r="A1327" s="10" t="s">
         <v>2658</v>
       </c>
       <c r="B1327" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1327" s="4" t="s">
+      <c r="C1327" s="10" t="s">
         <v>2659</v>
       </c>
       <c r="D1327" s="15"/>
@@ -26916,7 +26925,7 @@
       <c r="A1328" s="10" t="s">
         <v>2660</v>
       </c>
-      <c r="B1328" s="7" t="s">
+      <c r="B1328" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C1328" s="10" t="s">
@@ -26925,37 +26934,37 @@
       <c r="D1328" s="15"/>
     </row>
     <row r="1329" ht="22.5" customHeight="1">
-      <c r="A1329" s="10" t="s">
+      <c r="A1329" s="4" t="s">
         <v>2662</v>
       </c>
       <c r="B1329" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1329" s="10" t="s">
+      <c r="C1329" s="4" t="s">
         <v>2663</v>
       </c>
       <c r="D1329" s="15"/>
     </row>
     <row r="1330" ht="22.5" customHeight="1">
-      <c r="A1330" s="4" t="s">
+      <c r="A1330" s="10" t="s">
         <v>2664</v>
       </c>
-      <c r="B1330" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1330" s="4" t="s">
+      <c r="B1330" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1330" s="10" t="s">
         <v>2665</v>
       </c>
       <c r="D1330" s="15"/>
     </row>
     <row r="1331" ht="22.5" customHeight="1">
-      <c r="A1331" s="4" t="s">
+      <c r="A1331" s="10" t="s">
         <v>2666</v>
       </c>
-      <c r="B1331" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1331" s="4" t="s">
+      <c r="B1331" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1331" s="10" t="s">
         <v>2667</v>
       </c>
       <c r="D1331" s="15"/>
@@ -26964,8 +26973,8 @@
       <c r="A1332" s="4" t="s">
         <v>2668</v>
       </c>
-      <c r="B1332" s="5" t="s">
-        <v>7</v>
+      <c r="B1332" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C1332" s="4" t="s">
         <v>2669</v>
@@ -26976,8 +26985,8 @@
       <c r="A1333" s="4" t="s">
         <v>2670</v>
       </c>
-      <c r="B1333" s="5" t="s">
-        <v>4</v>
+      <c r="B1333" s="9" t="s">
+        <v>7</v>
       </c>
       <c r="C1333" s="4" t="s">
         <v>2671</v>
@@ -27001,7 +27010,7 @@
         <v>2674</v>
       </c>
       <c r="B1335" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C1335" s="4" t="s">
         <v>2675</v>
@@ -27033,49 +27042,49 @@
       <c r="D1337" s="15"/>
     </row>
     <row r="1338" ht="22.5" customHeight="1">
-      <c r="A1338" s="10" t="s">
+      <c r="A1338" s="4" t="s">
         <v>2680</v>
       </c>
-      <c r="B1338" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1338" s="10" t="s">
+      <c r="B1338" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1338" s="4" t="s">
         <v>2681</v>
       </c>
       <c r="D1338" s="15"/>
     </row>
     <row r="1339" ht="22.5" customHeight="1">
-      <c r="A1339" s="10" t="s">
+      <c r="A1339" s="4" t="s">
         <v>2682</v>
       </c>
       <c r="B1339" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1339" s="4" t="s">
+        <v>2683</v>
+      </c>
+      <c r="D1339" s="15"/>
+    </row>
+    <row r="1340" ht="22.5" customHeight="1">
+      <c r="A1340" s="10" t="s">
+        <v>2684</v>
+      </c>
+      <c r="B1340" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1340" s="10" t="s">
+        <v>2685</v>
+      </c>
+      <c r="D1340" s="15"/>
+    </row>
+    <row r="1341" ht="22.5" customHeight="1">
+      <c r="A1341" s="10" t="s">
+        <v>2686</v>
+      </c>
+      <c r="B1341" s="5" t="s">
         <v>651</v>
       </c>
-      <c r="C1339" s="10" t="s">
-        <v>2683</v>
-      </c>
-      <c r="D1339" s="15"/>
-    </row>
-    <row r="1340" ht="22.5" customHeight="1">
-      <c r="A1340" s="4" t="s">
-        <v>2684</v>
-      </c>
-      <c r="B1340" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1340" s="4" t="s">
-        <v>2685</v>
-      </c>
-      <c r="D1340" s="15"/>
-    </row>
-    <row r="1341" ht="22.5" customHeight="1">
-      <c r="A1341" s="4" t="s">
-        <v>2686</v>
-      </c>
-      <c r="B1341" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1341" s="4" t="s">
+      <c r="C1341" s="10" t="s">
         <v>2687</v>
       </c>
       <c r="D1341" s="15"/>
@@ -27085,7 +27094,7 @@
         <v>2688</v>
       </c>
       <c r="B1342" s="5" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="C1342" s="4" t="s">
         <v>2689</v>
@@ -27096,34 +27105,34 @@
       <c r="A1343" s="4" t="s">
         <v>2690</v>
       </c>
-      <c r="B1343" s="5" t="s">
-        <v>7</v>
+      <c r="B1343" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C1343" s="4" t="s">
-        <v>2690</v>
+        <v>2691</v>
       </c>
       <c r="D1343" s="15"/>
     </row>
     <row r="1344" ht="22.5" customHeight="1">
       <c r="A1344" s="4" t="s">
-        <v>2691</v>
-      </c>
-      <c r="B1344" s="9" t="s">
-        <v>64</v>
+        <v>2692</v>
+      </c>
+      <c r="B1344" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="C1344" s="4" t="s">
-        <v>2692</v>
+        <v>2693</v>
       </c>
       <c r="D1344" s="15"/>
     </row>
     <row r="1345" ht="22.5" customHeight="1">
-      <c r="A1345" s="10" t="s">
-        <v>2693</v>
+      <c r="A1345" s="4" t="s">
+        <v>2694</v>
       </c>
       <c r="B1345" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="C1345" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1345" s="4" t="s">
         <v>2694</v>
       </c>
       <c r="D1345" s="15"/>
@@ -27132,8 +27141,8 @@
       <c r="A1346" s="4" t="s">
         <v>2695</v>
       </c>
-      <c r="B1346" s="5" t="s">
-        <v>7</v>
+      <c r="B1346" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C1346" s="4" t="s">
         <v>2696</v>
@@ -27141,25 +27150,25 @@
       <c r="D1346" s="15"/>
     </row>
     <row r="1347" ht="22.5" customHeight="1">
-      <c r="A1347" s="4" t="s">
+      <c r="A1347" s="10" t="s">
         <v>2697</v>
       </c>
       <c r="B1347" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1347" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C1347" s="10" t="s">
         <v>2698</v>
       </c>
       <c r="D1347" s="15"/>
     </row>
     <row r="1348" ht="22.5" customHeight="1">
-      <c r="A1348" s="10" t="s">
+      <c r="A1348" s="4" t="s">
         <v>2699</v>
       </c>
-      <c r="B1348" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="C1348" s="10" t="s">
+      <c r="B1348" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1348" s="4" t="s">
         <v>2700</v>
       </c>
       <c r="D1348" s="15"/>
@@ -27169,7 +27178,7 @@
         <v>2701</v>
       </c>
       <c r="B1349" s="5" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="C1349" s="4" t="s">
         <v>2702</v>
@@ -27177,13 +27186,13 @@
       <c r="D1349" s="15"/>
     </row>
     <row r="1350" ht="22.5" customHeight="1">
-      <c r="A1350" s="4" t="s">
+      <c r="A1350" s="10" t="s">
         <v>2703</v>
       </c>
-      <c r="B1350" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1350" s="4" t="s">
+      <c r="B1350" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C1350" s="10" t="s">
         <v>2704</v>
       </c>
       <c r="D1350" s="15"/>
@@ -27201,13 +27210,13 @@
       <c r="D1351" s="15"/>
     </row>
     <row r="1352" ht="22.5" customHeight="1">
-      <c r="A1352" s="10" t="s">
+      <c r="A1352" s="4" t="s">
         <v>2707</v>
       </c>
-      <c r="B1352" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1352" s="10" t="s">
+      <c r="B1352" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1352" s="4" t="s">
         <v>2708</v>
       </c>
       <c r="D1352" s="15"/>
@@ -27228,8 +27237,8 @@
       <c r="A1354" s="10" t="s">
         <v>2711</v>
       </c>
-      <c r="B1354" s="9" t="s">
-        <v>72</v>
+      <c r="B1354" s="7" t="s">
+        <v>7</v>
       </c>
       <c r="C1354" s="10" t="s">
         <v>2712</v>
@@ -27252,8 +27261,8 @@
       <c r="A1356" s="10" t="s">
         <v>2715</v>
       </c>
-      <c r="B1356" s="5" t="s">
-        <v>7</v>
+      <c r="B1356" s="9" t="s">
+        <v>72</v>
       </c>
       <c r="C1356" s="10" t="s">
         <v>2716</v>
@@ -27288,7 +27297,7 @@
       <c r="A1359" s="4" t="s">
         <v>2721</v>
       </c>
-      <c r="B1359" s="7" t="s">
+      <c r="B1359" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C1359" s="4" t="s">
@@ -27297,13 +27306,13 @@
       <c r="D1359" s="15"/>
     </row>
     <row r="1360" ht="22.5" customHeight="1">
-      <c r="A1360" s="4" t="s">
+      <c r="A1360" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="B1360" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1360" s="4" t="s">
+      <c r="C1360" s="10" t="s">
         <v>2724</v>
       </c>
       <c r="D1360" s="15"/>
@@ -27324,8 +27333,8 @@
       <c r="A1362" s="4" t="s">
         <v>2727</v>
       </c>
-      <c r="B1362" s="9" t="s">
-        <v>64</v>
+      <c r="B1362" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C1362" s="4" t="s">
         <v>2728</v>
@@ -27336,7 +27345,7 @@
       <c r="A1363" s="4" t="s">
         <v>2729</v>
       </c>
-      <c r="B1363" s="5" t="s">
+      <c r="B1363" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C1363" s="4" t="s">
@@ -27348,8 +27357,8 @@
       <c r="A1364" s="4" t="s">
         <v>2731</v>
       </c>
-      <c r="B1364" s="5" t="s">
-        <v>7</v>
+      <c r="B1364" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C1364" s="4" t="s">
         <v>2732</v>
@@ -27357,13 +27366,13 @@
       <c r="D1364" s="15"/>
     </row>
     <row r="1365" ht="22.5" customHeight="1">
-      <c r="A1365" s="10" t="s">
+      <c r="A1365" s="4" t="s">
         <v>2733</v>
       </c>
       <c r="B1365" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1365" s="10" t="s">
+      <c r="C1365" s="4" t="s">
         <v>2734</v>
       </c>
       <c r="D1365" s="15"/>
@@ -27396,22 +27405,22 @@
       <c r="A1368" s="4" t="s">
         <v>2739</v>
       </c>
-      <c r="B1368" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1368" s="10" t="s">
+      <c r="B1368" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1368" s="4" t="s">
         <v>2740</v>
       </c>
       <c r="D1368" s="15"/>
     </row>
     <row r="1369" ht="22.5" customHeight="1">
-      <c r="A1369" s="4" t="s">
+      <c r="A1369" s="10" t="s">
         <v>2741</v>
       </c>
-      <c r="B1369" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1369" s="4" t="s">
+      <c r="B1369" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1369" s="10" t="s">
         <v>2742</v>
       </c>
       <c r="D1369" s="15"/>
@@ -27420,20 +27429,20 @@
       <c r="A1370" s="4" t="s">
         <v>2743</v>
       </c>
-      <c r="B1370" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1370" s="4" t="s">
+      <c r="B1370" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1370" s="10" t="s">
         <v>2744</v>
       </c>
       <c r="D1370" s="15"/>
     </row>
     <row r="1371" ht="22.5" customHeight="1">
-      <c r="A1371" s="10" t="s">
+      <c r="A1371" s="4" t="s">
         <v>2745</v>
       </c>
-      <c r="B1371" s="7" t="s">
-        <v>7</v>
+      <c r="B1371" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C1371" s="4" t="s">
         <v>2746</v>
@@ -27444,7 +27453,7 @@
       <c r="A1372" s="4" t="s">
         <v>2747</v>
       </c>
-      <c r="B1372" s="5" t="s">
+      <c r="B1372" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C1372" s="4" t="s">
@@ -27453,10 +27462,10 @@
       <c r="D1372" s="15"/>
     </row>
     <row r="1373" ht="22.5" customHeight="1">
-      <c r="A1373" s="4" t="s">
+      <c r="A1373" s="10" t="s">
         <v>2749</v>
       </c>
-      <c r="B1373" s="5" t="s">
+      <c r="B1373" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C1373" s="4" t="s">
@@ -27465,49 +27474,49 @@
       <c r="D1373" s="15"/>
     </row>
     <row r="1374" ht="22.5" customHeight="1">
-      <c r="A1374" s="10" t="s">
+      <c r="A1374" s="4" t="s">
         <v>2751</v>
       </c>
       <c r="B1374" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1374" s="10" t="s">
+      <c r="C1374" s="4" t="s">
         <v>2752</v>
       </c>
       <c r="D1374" s="15"/>
     </row>
     <row r="1375" ht="22.5" customHeight="1">
-      <c r="A1375" s="10" t="s">
+      <c r="A1375" s="4" t="s">
         <v>2753</v>
       </c>
       <c r="B1375" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1375" s="10" t="s">
+      <c r="C1375" s="4" t="s">
         <v>2754</v>
       </c>
       <c r="D1375" s="15"/>
     </row>
     <row r="1376" ht="22.5" customHeight="1">
-      <c r="A1376" s="4" t="s">
+      <c r="A1376" s="10" t="s">
         <v>2755</v>
       </c>
       <c r="B1376" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1376" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1376" s="10" t="s">
         <v>2756</v>
       </c>
       <c r="D1376" s="15"/>
     </row>
     <row r="1377" ht="22.5" customHeight="1">
-      <c r="A1377" s="4" t="s">
+      <c r="A1377" s="10" t="s">
         <v>2757</v>
       </c>
       <c r="B1377" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1377" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1377" s="10" t="s">
         <v>2758</v>
       </c>
       <c r="D1377" s="15"/>
@@ -27517,7 +27526,7 @@
         <v>2759</v>
       </c>
       <c r="B1378" s="23" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="C1378" s="4" t="s">
         <v>2760</v>
@@ -27525,97 +27534,97 @@
       <c r="D1378" s="15"/>
     </row>
     <row r="1379" ht="22.5" customHeight="1">
-      <c r="A1379" s="10" t="s">
+      <c r="A1379" s="4" t="s">
         <v>2761</v>
       </c>
-      <c r="B1379" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1379" s="10" t="s">
+      <c r="B1379" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1379" s="4" t="s">
         <v>2762</v>
       </c>
       <c r="D1379" s="15"/>
     </row>
     <row r="1380" ht="22.5" customHeight="1">
-      <c r="A1380" s="10" t="s">
+      <c r="A1380" s="4" t="s">
         <v>2763</v>
       </c>
-      <c r="B1380" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1380" s="10" t="s">
+      <c r="B1380" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1380" s="4" t="s">
         <v>2764</v>
       </c>
       <c r="D1380" s="15"/>
     </row>
     <row r="1381" ht="22.5" customHeight="1">
-      <c r="A1381" s="4" t="s">
+      <c r="A1381" s="10" t="s">
         <v>2765</v>
       </c>
-      <c r="B1381" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1381" s="4" t="s">
+      <c r="B1381" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1381" s="10" t="s">
         <v>2766</v>
       </c>
       <c r="D1381" s="15"/>
     </row>
     <row r="1382" ht="22.5" customHeight="1">
-      <c r="A1382" s="4" t="s">
+      <c r="A1382" s="10" t="s">
         <v>2767</v>
       </c>
-      <c r="B1382" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1382" s="4" t="s">
+      <c r="B1382" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1382" s="10" t="s">
         <v>2768</v>
       </c>
       <c r="D1382" s="15"/>
     </row>
     <row r="1383" ht="22.5" customHeight="1">
-      <c r="A1383" s="10" t="s">
+      <c r="A1383" s="4" t="s">
         <v>2769</v>
       </c>
-      <c r="B1383" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1383" s="10" t="s">
+      <c r="B1383" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1383" s="4" t="s">
         <v>2770</v>
       </c>
       <c r="D1383" s="15"/>
     </row>
     <row r="1384" ht="22.5" customHeight="1">
-      <c r="A1384" s="10" t="s">
+      <c r="A1384" s="4" t="s">
         <v>2771</v>
       </c>
-      <c r="B1384" s="9" t="s">
+      <c r="B1384" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1384" s="4" t="s">
+        <v>2772</v>
+      </c>
+      <c r="D1384" s="15"/>
+    </row>
+    <row r="1385" ht="22.5" customHeight="1">
+      <c r="A1385" s="10" t="s">
+        <v>2773</v>
+      </c>
+      <c r="B1385" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1385" s="10" t="s">
+        <v>2774</v>
+      </c>
+      <c r="D1385" s="15"/>
+    </row>
+    <row r="1386" ht="22.5" customHeight="1">
+      <c r="A1386" s="10" t="s">
+        <v>2775</v>
+      </c>
+      <c r="B1386" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C1384" s="10" t="s">
-        <v>2772</v>
-      </c>
-      <c r="D1384" s="15"/>
-    </row>
-    <row r="1385" ht="22.5" customHeight="1">
-      <c r="A1385" s="4" t="s">
-        <v>2773</v>
-      </c>
-      <c r="B1385" s="5" t="s">
-        <v>890</v>
-      </c>
-      <c r="C1385" s="4" t="s">
-        <v>2774</v>
-      </c>
-      <c r="D1385" s="15"/>
-    </row>
-    <row r="1386" ht="22.5" customHeight="1">
-      <c r="A1386" s="4" t="s">
-        <v>2775</v>
-      </c>
-      <c r="B1386" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1386" s="4" t="s">
+      <c r="C1386" s="10" t="s">
         <v>2776</v>
       </c>
       <c r="D1386" s="15"/>
@@ -27624,8 +27633,8 @@
       <c r="A1387" s="4" t="s">
         <v>2777</v>
       </c>
-      <c r="B1387" s="9" t="s">
-        <v>7</v>
+      <c r="B1387" s="5" t="s">
+        <v>890</v>
       </c>
       <c r="C1387" s="4" t="s">
         <v>2778</v>
@@ -27636,8 +27645,8 @@
       <c r="A1388" s="4" t="s">
         <v>2779</v>
       </c>
-      <c r="B1388" s="9" t="s">
-        <v>64</v>
+      <c r="B1388" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C1388" s="4" t="s">
         <v>2780</v>
@@ -27649,7 +27658,7 @@
         <v>2781</v>
       </c>
       <c r="B1389" s="9" t="s">
-        <v>890</v>
+        <v>7</v>
       </c>
       <c r="C1389" s="4" t="s">
         <v>2782</v>
@@ -27661,7 +27670,7 @@
         <v>2783</v>
       </c>
       <c r="B1390" s="9" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="C1390" s="4" t="s">
         <v>2784</v>
@@ -27669,13 +27678,13 @@
       <c r="D1390" s="15"/>
     </row>
     <row r="1391" ht="22.5" customHeight="1">
-      <c r="A1391" s="10" t="s">
+      <c r="A1391" s="4" t="s">
         <v>2785</v>
       </c>
-      <c r="B1391" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1391" s="10" t="s">
+      <c r="B1391" s="9" t="s">
+        <v>890</v>
+      </c>
+      <c r="C1391" s="4" t="s">
         <v>2786</v>
       </c>
       <c r="D1391" s="15"/>
@@ -27693,13 +27702,13 @@
       <c r="D1392" s="15"/>
     </row>
     <row r="1393" ht="22.5" customHeight="1">
-      <c r="A1393" s="4" t="s">
+      <c r="A1393" s="10" t="s">
         <v>2789</v>
       </c>
-      <c r="B1393" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C1393" s="4" t="s">
+      <c r="B1393" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1393" s="10" t="s">
         <v>2790</v>
       </c>
       <c r="D1393" s="15"/>
@@ -27708,7 +27717,7 @@
       <c r="A1394" s="4" t="s">
         <v>2791</v>
       </c>
-      <c r="B1394" s="5" t="s">
+      <c r="B1394" s="9" t="s">
         <v>117</v>
       </c>
       <c r="C1394" s="4" t="s">
@@ -27733,7 +27742,7 @@
         <v>2795</v>
       </c>
       <c r="B1396" s="5" t="s">
-        <v>7</v>
+        <v>117</v>
       </c>
       <c r="C1396" s="4" t="s">
         <v>2796</v>
@@ -27741,25 +27750,25 @@
       <c r="D1396" s="15"/>
     </row>
     <row r="1397" ht="22.5" customHeight="1">
-      <c r="A1397" s="10" t="s">
+      <c r="A1397" s="4" t="s">
         <v>2797</v>
       </c>
-      <c r="B1397" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1397" s="10" t="s">
+      <c r="B1397" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1397" s="4" t="s">
         <v>2798</v>
       </c>
       <c r="D1397" s="15"/>
     </row>
     <row r="1398" ht="22.5" customHeight="1">
-      <c r="A1398" s="10" t="s">
+      <c r="A1398" s="4" t="s">
         <v>2799</v>
       </c>
       <c r="B1398" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C1398" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1398" s="4" t="s">
         <v>2800</v>
       </c>
       <c r="D1398" s="15"/>
@@ -27769,7 +27778,7 @@
         <v>2801</v>
       </c>
       <c r="B1399" s="5" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="C1399" s="10" t="s">
         <v>2802</v>
@@ -27777,25 +27786,25 @@
       <c r="D1399" s="15"/>
     </row>
     <row r="1400" ht="22.5" customHeight="1">
-      <c r="A1400" s="4" t="s">
+      <c r="A1400" s="10" t="s">
         <v>2803</v>
       </c>
-      <c r="B1400" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1400" s="4" t="s">
+      <c r="B1400" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1400" s="10" t="s">
         <v>2804</v>
       </c>
       <c r="D1400" s="15"/>
     </row>
     <row r="1401" ht="22.5" customHeight="1">
-      <c r="A1401" s="4" t="s">
+      <c r="A1401" s="10" t="s">
         <v>2805</v>
       </c>
       <c r="B1401" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1401" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1401" s="10" t="s">
         <v>2806</v>
       </c>
       <c r="D1401" s="15"/>
@@ -27804,8 +27813,8 @@
       <c r="A1402" s="4" t="s">
         <v>2807</v>
       </c>
-      <c r="B1402" s="5" t="s">
-        <v>7</v>
+      <c r="B1402" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C1402" s="4" t="s">
         <v>2808</v>
@@ -27813,13 +27822,13 @@
       <c r="D1402" s="15"/>
     </row>
     <row r="1403" ht="22.5" customHeight="1">
-      <c r="A1403" s="10" t="s">
+      <c r="A1403" s="4" t="s">
         <v>2809</v>
       </c>
-      <c r="B1403" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1403" s="10" t="s">
+      <c r="B1403" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1403" s="4" t="s">
         <v>2810</v>
       </c>
       <c r="D1403" s="15"/>
@@ -27837,13 +27846,13 @@
       <c r="D1404" s="15"/>
     </row>
     <row r="1405" ht="22.5" customHeight="1">
-      <c r="A1405" s="4" t="s">
+      <c r="A1405" s="10" t="s">
         <v>2813</v>
       </c>
-      <c r="B1405" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1405" s="4" t="s">
+      <c r="B1405" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1405" s="10" t="s">
         <v>2814</v>
       </c>
       <c r="D1405" s="15"/>
@@ -27861,13 +27870,13 @@
       <c r="D1406" s="15"/>
     </row>
     <row r="1407" ht="22.5" customHeight="1">
-      <c r="A1407" s="10" t="s">
+      <c r="A1407" s="4" t="s">
         <v>2817</v>
       </c>
       <c r="B1407" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1407" s="10" t="s">
+      <c r="C1407" s="4" t="s">
         <v>2818</v>
       </c>
       <c r="D1407" s="15"/>
@@ -27885,73 +27894,73 @@
       <c r="D1408" s="15"/>
     </row>
     <row r="1409" ht="22.5" customHeight="1">
-      <c r="A1409" s="4" t="s">
+      <c r="A1409" s="10" t="s">
         <v>2821</v>
       </c>
       <c r="B1409" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1409" s="4" t="s">
+      <c r="C1409" s="10" t="s">
         <v>2822</v>
       </c>
       <c r="D1409" s="15"/>
     </row>
     <row r="1410" ht="22.5" customHeight="1">
-      <c r="A1410" s="10" t="s">
+      <c r="A1410" s="4" t="s">
         <v>2823</v>
       </c>
       <c r="B1410" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1410" s="10" t="s">
+      <c r="C1410" s="4" t="s">
         <v>2824</v>
       </c>
       <c r="D1410" s="15"/>
     </row>
     <row r="1411" ht="22.5" customHeight="1">
-      <c r="A1411" s="10" t="s">
+      <c r="A1411" s="4" t="s">
         <v>2825</v>
       </c>
       <c r="B1411" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1411" s="10" t="s">
+      <c r="C1411" s="4" t="s">
         <v>2826</v>
       </c>
       <c r="D1411" s="15"/>
     </row>
     <row r="1412" ht="22.5" customHeight="1">
-      <c r="A1412" s="4" t="s">
+      <c r="A1412" s="10" t="s">
         <v>2827</v>
       </c>
-      <c r="B1412" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1412" s="4" t="s">
+      <c r="B1412" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1412" s="10" t="s">
         <v>2828</v>
       </c>
       <c r="D1412" s="15"/>
     </row>
     <row r="1413" ht="22.5" customHeight="1">
-      <c r="A1413" s="4" t="s">
+      <c r="A1413" s="10" t="s">
         <v>2829</v>
       </c>
       <c r="B1413" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1413" s="4" t="s">
+      <c r="C1413" s="10" t="s">
         <v>2830</v>
       </c>
       <c r="D1413" s="15"/>
     </row>
     <row r="1414" ht="22.5" customHeight="1">
-      <c r="A1414" s="10" t="s">
+      <c r="A1414" s="4" t="s">
         <v>2831</v>
       </c>
       <c r="B1414" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1414" s="10" t="s">
+      <c r="C1414" s="4" t="s">
         <v>2832</v>
       </c>
       <c r="D1414" s="15"/>
@@ -27969,37 +27978,37 @@
       <c r="D1415" s="15"/>
     </row>
     <row r="1416" ht="22.5" customHeight="1">
-      <c r="A1416" s="4" t="s">
+      <c r="A1416" s="10" t="s">
         <v>2835</v>
       </c>
-      <c r="B1416" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1416" s="4" t="s">
+      <c r="B1416" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1416" s="10" t="s">
         <v>2836</v>
       </c>
       <c r="D1416" s="15"/>
     </row>
     <row r="1417" ht="22.5" customHeight="1">
-      <c r="A1417" s="10" t="s">
+      <c r="A1417" s="4" t="s">
         <v>2837</v>
       </c>
-      <c r="B1417" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1417" s="10" t="s">
+      <c r="B1417" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1417" s="4" t="s">
         <v>2838</v>
       </c>
       <c r="D1417" s="15"/>
     </row>
     <row r="1418" ht="22.5" customHeight="1">
-      <c r="A1418" s="10" t="s">
+      <c r="A1418" s="4" t="s">
         <v>2839</v>
       </c>
       <c r="B1418" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1418" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1418" s="4" t="s">
         <v>2840</v>
       </c>
       <c r="D1418" s="15"/>
@@ -28008,8 +28017,8 @@
       <c r="A1419" s="10" t="s">
         <v>2841</v>
       </c>
-      <c r="B1419" s="5" t="s">
-        <v>49</v>
+      <c r="B1419" s="9" t="s">
+        <v>7</v>
       </c>
       <c r="C1419" s="10" t="s">
         <v>2842</v>
@@ -28017,25 +28026,25 @@
       <c r="D1419" s="15"/>
     </row>
     <row r="1420" ht="22.5" customHeight="1">
-      <c r="A1420" s="4" t="s">
+      <c r="A1420" s="10" t="s">
         <v>2843</v>
       </c>
-      <c r="B1420" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C1420" s="4" t="s">
+      <c r="B1420" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1420" s="10" t="s">
         <v>2844</v>
       </c>
       <c r="D1420" s="15"/>
     </row>
     <row r="1421" ht="22.5" customHeight="1">
-      <c r="A1421" s="4" t="s">
+      <c r="A1421" s="10" t="s">
         <v>2845</v>
       </c>
-      <c r="B1421" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1421" s="4" t="s">
+      <c r="B1421" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1421" s="10" t="s">
         <v>2846</v>
       </c>
       <c r="D1421" s="15"/>
@@ -28044,8 +28053,8 @@
       <c r="A1422" s="4" t="s">
         <v>2847</v>
       </c>
-      <c r="B1422" s="9" t="s">
-        <v>651</v>
+      <c r="B1422" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="C1422" s="4" t="s">
         <v>2848</v>
@@ -28056,17 +28065,41 @@
       <c r="A1423" s="4" t="s">
         <v>2849</v>
       </c>
-      <c r="B1423" s="5" t="s">
-        <v>7</v>
+      <c r="B1423" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C1423" s="4" t="s">
         <v>2850</v>
       </c>
       <c r="D1423" s="15"/>
     </row>
+    <row r="1424" ht="22.5" customHeight="1">
+      <c r="A1424" s="4" t="s">
+        <v>2851</v>
+      </c>
+      <c r="B1424" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="C1424" s="4" t="s">
+        <v>2852</v>
+      </c>
+      <c r="D1424" s="15"/>
+    </row>
+    <row r="1425" ht="22.5" customHeight="1">
+      <c r="A1425" s="4" t="s">
+        <v>2853</v>
+      </c>
+      <c r="B1425" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1425" s="4" t="s">
+        <v>2854</v>
+      </c>
+      <c r="D1425" s="15"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B1423">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B1425">
       <formula1>"adjective,adverb,adverb-preposition,conjunction,noun,numeral,phrase,preposition,pronoun,verb,interjection,prefix,suffix,article"</formula1>
     </dataValidation>
   </dataValidations>
@@ -28088,303 +28121,303 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="25" t="s">
-        <v>2851</v>
-      </c>
-      <c r="B1" s="26" t="s">
+      <c r="A1" s="24" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B1" s="25" t="s">
         <v>2038</v>
       </c>
       <c r="D1" s="8"/>
-      <c r="E1" s="26" t="s">
-        <v>2852</v>
+      <c r="E1" s="25" t="s">
+        <v>2856</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="27" t="s">
-        <v>2853</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>2854</v>
+      <c r="A2" s="26" t="s">
+        <v>2857</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>2858</v>
       </c>
       <c r="D2" s="8"/>
-      <c r="E2" s="28" t="s">
-        <v>2855</v>
+      <c r="E2" s="27" t="s">
+        <v>2859</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="27" t="s">
-        <v>2856</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>2857</v>
+      <c r="A3" s="26" t="s">
+        <v>2860</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>2861</v>
       </c>
       <c r="D3" s="8"/>
-      <c r="E3" s="28" t="s">
-        <v>2858</v>
+      <c r="E3" s="27" t="s">
+        <v>2862</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="27" t="s">
-        <v>2859</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>2860</v>
+      <c r="A4" s="26" t="s">
+        <v>2863</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>2864</v>
       </c>
       <c r="D4" s="8"/>
-      <c r="E4" s="28" t="s">
-        <v>2861</v>
+      <c r="E4" s="27" t="s">
+        <v>2865</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="25" t="s">
-        <v>2862</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>2863</v>
+      <c r="A5" s="24" t="s">
+        <v>2866</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>2867</v>
       </c>
       <c r="D5" s="8"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="25" t="s">
-        <v>2864</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>2865</v>
-      </c>
-      <c r="C6" s="27" t="s">
+      <c r="A6" s="24" t="s">
+        <v>2868</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>2869</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>1472</v>
       </c>
       <c r="D6" s="8"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="25" t="s">
-        <v>2866</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>2867</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>2868</v>
+      <c r="A7" s="24" t="s">
+        <v>2870</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>2871</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>2872</v>
       </c>
       <c r="D7" s="15"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="25" t="s">
-        <v>2869</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>2870</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>2871</v>
+      <c r="A8" s="24" t="s">
+        <v>2873</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>2874</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>2875</v>
       </c>
       <c r="D8" s="8"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="25" t="s">
-        <v>2872</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>2873</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>2874</v>
+      <c r="A9" s="24" t="s">
+        <v>2876</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>2877</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>2878</v>
       </c>
       <c r="D9" s="8"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="25" t="s">
-        <v>2875</v>
-      </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="28" t="s">
-        <v>2876</v>
+      <c r="A10" s="24" t="s">
+        <v>2879</v>
+      </c>
+      <c r="B10" s="24"/>
+      <c r="C10" s="27" t="s">
+        <v>2880</v>
       </c>
       <c r="D10" s="8"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="25" t="s">
-        <v>2877</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>2878</v>
+      <c r="A11" s="24" t="s">
+        <v>2881</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>2882</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="24" t="s">
+        <v>2883</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>2056</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+    </row>
+    <row r="14" ht="18.75" customHeight="1">
+      <c r="A14" s="26" t="s">
+        <v>2857</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>2056</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+    </row>
+    <row r="15" ht="18.75" customHeight="1">
+      <c r="A15" s="26" t="s">
+        <v>2860</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>2884</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+    </row>
+    <row r="16" ht="18.75" customHeight="1">
+      <c r="A16" s="26" t="s">
+        <v>2863</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>2885</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+    </row>
+    <row r="17" ht="18.75" customHeight="1">
+      <c r="A17" s="24" t="s">
+        <v>2866</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>2886</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+    </row>
+    <row r="18" ht="18.75" customHeight="1">
+      <c r="A18" s="24" t="s">
+        <v>2868</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>2869</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+    </row>
+    <row r="19" ht="18.75" customHeight="1">
+      <c r="A19" s="24" t="s">
+        <v>2870</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>2056</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>2887</v>
+      </c>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+    </row>
+    <row r="20" ht="18.75" customHeight="1">
+      <c r="A20" s="24" t="s">
+        <v>2873</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>2888</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>2889</v>
+      </c>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+    </row>
+    <row r="21" ht="18.75" customHeight="1">
+      <c r="A21" s="24" t="s">
+        <v>2876</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>2877</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>2878</v>
+      </c>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+    </row>
+    <row r="22" ht="18.75" customHeight="1">
+      <c r="A22" s="24" t="s">
         <v>2879</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B22" s="24"/>
+      <c r="C22" s="27" t="s">
+        <v>2890</v>
+      </c>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+    </row>
+    <row r="23" ht="18.75" customHeight="1">
+      <c r="A23" s="24" t="s">
+        <v>2881</v>
+      </c>
+      <c r="B23" s="27" t="s">
         <v>2056</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-    </row>
-    <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="27" t="s">
-        <v>2853</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>2056</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-    </row>
-    <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="27" t="s">
-        <v>2856</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>2880</v>
-      </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-    </row>
-    <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="27" t="s">
-        <v>2859</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>2881</v>
-      </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-    </row>
-    <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="25" t="s">
-        <v>2862</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>2882</v>
-      </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-    </row>
-    <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" s="25" t="s">
-        <v>2864</v>
-      </c>
-      <c r="B18" s="27" t="s">
-        <v>2865</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>1472</v>
-      </c>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-    </row>
-    <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" s="25" t="s">
-        <v>2866</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>2056</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>2883</v>
-      </c>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-    </row>
-    <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="25" t="s">
-        <v>2869</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>2884</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>2885</v>
-      </c>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-    </row>
-    <row r="21" ht="18.75" customHeight="1">
-      <c r="A21" s="25" t="s">
-        <v>2872</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>2873</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>2874</v>
-      </c>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-    </row>
-    <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="25" t="s">
-        <v>2875</v>
-      </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="28" t="s">
-        <v>2886</v>
-      </c>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-    </row>
-    <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" s="25" t="s">
-        <v>2877</v>
-      </c>
-      <c r="B23" s="28" t="s">
-        <v>2056</v>
-      </c>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -28420,774 +28453,774 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="26" t="s">
-        <v>2887</v>
-      </c>
-      <c r="B1" s="30" t="s">
+      <c r="A1" s="25" t="s">
+        <v>2891</v>
+      </c>
+      <c r="B1" s="29" t="s">
         <v>448</v>
       </c>
-      <c r="D1" s="31"/>
-      <c r="E1" s="30" t="s">
-        <v>2888</v>
+      <c r="D1" s="30"/>
+      <c r="E1" s="29" t="s">
+        <v>2892</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="B2" s="30" t="s">
-        <v>2873</v>
-      </c>
-      <c r="C2" s="30" t="s">
-        <v>2874</v>
-      </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="30" t="s">
-        <v>2889</v>
-      </c>
-      <c r="G2" s="30" t="s">
-        <v>2890</v>
-      </c>
-      <c r="I2" s="30" t="s">
-        <v>2891</v>
+      <c r="B2" s="29" t="s">
+        <v>2877</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>2878</v>
+      </c>
+      <c r="D2" s="30"/>
+      <c r="E2" s="29" t="s">
+        <v>2893</v>
+      </c>
+      <c r="G2" s="29" t="s">
+        <v>2894</v>
+      </c>
+      <c r="I2" s="29" t="s">
+        <v>2895</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="30" t="s">
-        <v>2892</v>
-      </c>
-      <c r="B3" s="31" t="s">
+      <c r="A3" s="29" t="s">
+        <v>2896</v>
+      </c>
+      <c r="B3" s="30" t="s">
         <v>448</v>
       </c>
-      <c r="C3" s="31" t="s">
-        <v>2893</v>
-      </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="30" t="s">
+      <c r="C3" s="30" t="s">
+        <v>2897</v>
+      </c>
+      <c r="D3" s="30"/>
+      <c r="E3" s="29" t="s">
+        <v>2898</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>2899</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>2898</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>2899</v>
+      </c>
+      <c r="I3" s="29" t="s">
+        <v>2898</v>
+      </c>
+      <c r="J3" s="29" t="s">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="29" t="s">
+        <v>2900</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>2901</v>
+      </c>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30" t="s">
+        <v>2902</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>970</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>2903</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>2904</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>2905</v>
+      </c>
+      <c r="J4" s="30" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="29" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>2907</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>2908</v>
+      </c>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>1363</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>2909</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>1349</v>
+      </c>
+      <c r="I5" s="30" t="s">
+        <v>2910</v>
+      </c>
+      <c r="J5" s="30" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customHeight="1">
+      <c r="A6" s="32"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30" t="s">
+        <v>2911</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>448</v>
+      </c>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="30" t="s">
+        <v>2912</v>
+      </c>
+      <c r="J6" s="30" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="7" ht="18.75" customHeight="1">
+      <c r="A7" s="25" t="s">
+        <v>2913</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D7" s="33"/>
+      <c r="I7" s="30" t="s">
+        <v>2914</v>
+      </c>
+      <c r="J7" s="30" t="s">
+        <v>2915</v>
+      </c>
+    </row>
+    <row r="8" ht="18.75" customHeight="1">
+      <c r="B8" s="29" t="s">
+        <v>2877</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>2878</v>
+      </c>
+      <c r="D8" s="30"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="30" t="s">
+        <v>2916</v>
+      </c>
+      <c r="J8" s="30" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="9" ht="18.75" customHeight="1">
+      <c r="A9" s="29" t="s">
+        <v>2896</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>2917</v>
+      </c>
+      <c r="D9" s="30"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="30" t="s">
+        <v>2918</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="10" ht="18.75" customHeight="1">
+      <c r="A10" s="29" t="s">
+        <v>2900</v>
+      </c>
+      <c r="D10" s="33"/>
+      <c r="E10" s="25" t="s">
+        <v>2895</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>442</v>
+      </c>
+      <c r="H10" s="33"/>
+      <c r="I10" s="30" t="s">
+        <v>2919</v>
+      </c>
+      <c r="J10" s="30" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="11" ht="18.75" customHeight="1">
+      <c r="A11" s="29" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>2920</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>2921</v>
+      </c>
+      <c r="D11" s="33"/>
+      <c r="F11" s="29" t="s">
+        <v>2877</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>2878</v>
+      </c>
+      <c r="H11" s="34"/>
+      <c r="I11" s="30" t="s">
+        <v>2922</v>
+      </c>
+      <c r="J11" s="30" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="12" ht="18.75" customHeight="1">
+      <c r="A12" s="33"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="29" t="s">
+        <v>2896</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>442</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>2923</v>
+      </c>
+      <c r="H12" s="34"/>
+      <c r="I12" s="30" t="s">
+        <v>2924</v>
+      </c>
+      <c r="J12" s="30" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="13" ht="18.75" customHeight="1">
+      <c r="A13" s="25" t="s">
         <v>2894</v>
       </c>
-      <c r="F3" s="30" t="s">
-        <v>2895</v>
-      </c>
-      <c r="G3" s="30" t="s">
-        <v>2894</v>
-      </c>
-      <c r="H3" s="30" t="s">
-        <v>2895</v>
-      </c>
-      <c r="I3" s="30" t="s">
-        <v>2894</v>
-      </c>
-      <c r="J3" s="30" t="s">
-        <v>2895</v>
-      </c>
-    </row>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="30" t="s">
+      <c r="B13" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="D13" s="33"/>
+      <c r="E13" s="29" t="s">
+        <v>2900</v>
+      </c>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30" t="s">
+        <v>2925</v>
+      </c>
+      <c r="J13" s="30" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="14" ht="18.75" customHeight="1">
+      <c r="B14" s="29" t="s">
+        <v>2877</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>2878</v>
+      </c>
+      <c r="D14" s="33"/>
+      <c r="E14" s="29" t="s">
+        <v>2906</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>2926</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>2927</v>
+      </c>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30" t="s">
+        <v>2928</v>
+      </c>
+      <c r="J14" s="30" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="15" ht="18.75" customHeight="1">
+      <c r="A15" s="29" t="s">
         <v>2896</v>
       </c>
-      <c r="C4" s="31" t="s">
-        <v>2897</v>
-      </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31" t="s">
-        <v>2898</v>
-      </c>
-      <c r="F4" s="32" t="s">
-        <v>970</v>
-      </c>
-      <c r="G4" s="31" t="s">
-        <v>2899</v>
-      </c>
-      <c r="H4" s="31" t="s">
+      <c r="B15" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>2929</v>
+      </c>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30" t="s">
+        <v>2930</v>
+      </c>
+      <c r="J15" s="30" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="16" ht="18.75" customHeight="1">
+      <c r="A16" s="29" t="s">
         <v>2900</v>
       </c>
-      <c r="I4" s="31" t="s">
-        <v>2901</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="30" t="s">
-        <v>2902</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>2903</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>2904</v>
-      </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>1363</v>
-      </c>
-      <c r="G5" s="31" t="s">
-        <v>2905</v>
-      </c>
-      <c r="H5" s="31" t="s">
-        <v>1349</v>
-      </c>
-      <c r="I5" s="31" t="s">
+      <c r="B16" s="30" t="s">
+        <v>2931</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>2932</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>2933</v>
+      </c>
+      <c r="F16" s="29" t="s">
+        <v>2853</v>
+      </c>
+      <c r="H16" s="34"/>
+      <c r="I16" s="30" t="s">
+        <v>2934</v>
+      </c>
+      <c r="J16" s="30" t="s">
+        <v>2853</v>
+      </c>
+    </row>
+    <row r="17" ht="18.75" customHeight="1">
+      <c r="A17" s="29" t="s">
         <v>2906</v>
       </c>
-      <c r="J5" s="31" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31" t="s">
-        <v>2907</v>
-      </c>
-      <c r="F6" s="32" t="s">
-        <v>448</v>
-      </c>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="31" t="s">
-        <v>2908</v>
-      </c>
-      <c r="J6" s="31" t="s">
-        <v>1725</v>
-      </c>
-    </row>
-    <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="26" t="s">
-        <v>2909</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>1363</v>
-      </c>
-      <c r="D7" s="34"/>
-      <c r="I7" s="31" t="s">
-        <v>2910</v>
-      </c>
-      <c r="J7" s="31" t="s">
-        <v>2911</v>
-      </c>
-    </row>
-    <row r="8" ht="18.75" customHeight="1">
-      <c r="B8" s="30" t="s">
-        <v>2873</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>2874</v>
-      </c>
-      <c r="D8" s="31"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="31" t="s">
-        <v>2912</v>
-      </c>
-      <c r="J8" s="31" t="s">
-        <v>1365</v>
-      </c>
-    </row>
-    <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="30" t="s">
-        <v>2892</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>1363</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>2913</v>
-      </c>
-      <c r="D9" s="31"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="31" t="s">
-        <v>2914</v>
-      </c>
-      <c r="J9" s="31" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="30" t="s">
+      <c r="B17" s="30" t="s">
+        <v>2935</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>2936</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>2877</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>2878</v>
+      </c>
+      <c r="H17" s="34"/>
+      <c r="I17" s="30" t="s">
+        <v>2937</v>
+      </c>
+      <c r="J17" s="30" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="18" ht="18.75" customHeight="1">
+      <c r="E18" s="29" t="s">
         <v>2896</v>
       </c>
-      <c r="D10" s="34"/>
-      <c r="E10" s="26" t="s">
-        <v>2891</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>442</v>
-      </c>
-      <c r="H10" s="34"/>
-      <c r="I10" s="31" t="s">
-        <v>2915</v>
-      </c>
-      <c r="J10" s="31" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="30" t="s">
-        <v>2902</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>2916</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>2917</v>
-      </c>
-      <c r="D11" s="34"/>
-      <c r="F11" s="30" t="s">
-        <v>2873</v>
-      </c>
-      <c r="G11" s="30" t="s">
-        <v>2874</v>
-      </c>
-      <c r="H11" s="35"/>
-      <c r="I11" s="31" t="s">
-        <v>2918</v>
-      </c>
-      <c r="J11" s="31" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="34"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="30" t="s">
-        <v>2892</v>
-      </c>
-      <c r="F12" s="31" t="s">
-        <v>442</v>
-      </c>
-      <c r="G12" s="31" t="s">
-        <v>2919</v>
-      </c>
-      <c r="H12" s="35"/>
-      <c r="I12" s="31" t="s">
-        <v>2920</v>
-      </c>
-      <c r="J12" s="31" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="26" t="s">
-        <v>2890</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>270</v>
-      </c>
-      <c r="D13" s="34"/>
-      <c r="E13" s="30" t="s">
+      <c r="F18" s="30" t="s">
+        <v>2853</v>
+      </c>
+      <c r="G18" s="30" t="s">
+        <v>2938</v>
+      </c>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+    </row>
+    <row r="19" ht="18.75" customHeight="1">
+      <c r="A19" s="30"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="29" t="s">
+        <v>2900</v>
+      </c>
+      <c r="H19" s="30"/>
+    </row>
+    <row r="20" ht="18.75" customHeight="1">
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="29" t="s">
+        <v>2906</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>2939</v>
+      </c>
+      <c r="G20" s="30" t="s">
+        <v>2940</v>
+      </c>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+    </row>
+    <row r="21" ht="18.75" customHeight="1">
+      <c r="A21" s="30"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="H21" s="30"/>
+    </row>
+    <row r="22" ht="18.75" customHeight="1">
+      <c r="A22" s="29" t="s">
+        <v>2941</v>
+      </c>
+      <c r="B22" s="29" t="s">
+        <v>2877</v>
+      </c>
+      <c r="H22" s="29" t="s">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="23" ht="18.75" customHeight="1">
+      <c r="B23" s="29" t="s">
+        <v>2943</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>2944</v>
+      </c>
+      <c r="D23" s="29" t="s">
+        <v>2945</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>2946</v>
+      </c>
+      <c r="F23" s="29" t="s">
+        <v>2947</v>
+      </c>
+      <c r="G23" s="29" t="s">
+        <v>2948</v>
+      </c>
+      <c r="H23" s="29" t="s">
+        <v>2949</v>
+      </c>
+      <c r="I23" s="29" t="s">
+        <v>2950</v>
+      </c>
+      <c r="J23" s="29" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="24" ht="18.75" customHeight="1">
+      <c r="A24" s="29" t="s">
         <v>2896</v>
       </c>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31" t="s">
-        <v>2921</v>
-      </c>
-      <c r="J13" s="31" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="14" ht="18.75" customHeight="1">
-      <c r="B14" s="30" t="s">
-        <v>2873</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>2874</v>
-      </c>
-      <c r="D14" s="34"/>
-      <c r="E14" s="30" t="s">
-        <v>2902</v>
-      </c>
-      <c r="F14" s="31" t="s">
-        <v>2922</v>
-      </c>
-      <c r="G14" s="31" t="s">
-        <v>2923</v>
-      </c>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31" t="s">
-        <v>2924</v>
-      </c>
-      <c r="J14" s="31" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="30" t="s">
-        <v>2892</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>270</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>2925</v>
-      </c>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31" t="s">
-        <v>2926</v>
-      </c>
-      <c r="J15" s="31" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="30" t="s">
+      <c r="B24" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>2952</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>2953</v>
+      </c>
+      <c r="G24" s="30" t="s">
+        <v>2954</v>
+      </c>
+      <c r="H24" s="30" t="s">
+        <v>570</v>
+      </c>
+      <c r="I24" s="30" t="s">
+        <v>570</v>
+      </c>
+      <c r="J24" s="30" t="s">
+        <v>2955</v>
+      </c>
+    </row>
+    <row r="25" ht="18.75" customHeight="1">
+      <c r="A25" s="29" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>2956</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="I25" s="30" t="s">
+        <v>2955</v>
+      </c>
+    </row>
+    <row r="26" ht="18.75" customHeight="1">
+      <c r="A26" s="29" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B26" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="30" t="s">
+        <v>2957</v>
+      </c>
+      <c r="G26" s="30" t="s">
+        <v>2958</v>
+      </c>
+    </row>
+    <row r="27" ht="18.75" customHeight="1">
+      <c r="A27" s="29" t="s">
+        <v>2941</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>2878</v>
+      </c>
+      <c r="H27" s="29" t="s">
+        <v>2959</v>
+      </c>
+    </row>
+    <row r="28" ht="18.75" customHeight="1">
+      <c r="B28" s="29" t="s">
+        <v>2943</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>2944</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>2945</v>
+      </c>
+      <c r="E28" s="29" t="s">
+        <v>2946</v>
+      </c>
+      <c r="F28" s="29" t="s">
+        <v>2947</v>
+      </c>
+      <c r="G28" s="29" t="s">
+        <v>2948</v>
+      </c>
+      <c r="H28" s="29" t="s">
+        <v>2949</v>
+      </c>
+      <c r="I28" s="29" t="s">
+        <v>2950</v>
+      </c>
+      <c r="J28" s="29" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="29" ht="18.75" customHeight="1">
+      <c r="A29" s="29" t="s">
         <v>2896</v>
       </c>
-      <c r="B16" s="31" t="s">
-        <v>2927</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>2928</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>2929</v>
-      </c>
-      <c r="F16" s="30" t="s">
-        <v>2849</v>
-      </c>
-      <c r="H16" s="35"/>
-      <c r="I16" s="31" t="s">
-        <v>2930</v>
-      </c>
-      <c r="J16" s="31" t="s">
-        <v>2849</v>
-      </c>
-    </row>
-    <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="30" t="s">
-        <v>2902</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>2931</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>2932</v>
-      </c>
-      <c r="F17" s="30" t="s">
-        <v>2873</v>
-      </c>
-      <c r="G17" s="30" t="s">
-        <v>2874</v>
-      </c>
-      <c r="H17" s="35"/>
-      <c r="I17" s="31" t="s">
-        <v>2933</v>
-      </c>
-      <c r="J17" s="31" t="s">
-        <v>1751</v>
-      </c>
-    </row>
-    <row r="18" ht="18.75" customHeight="1">
-      <c r="E18" s="30" t="s">
-        <v>2892</v>
-      </c>
-      <c r="F18" s="31" t="s">
-        <v>2849</v>
-      </c>
-      <c r="G18" s="31" t="s">
-        <v>2934</v>
-      </c>
-      <c r="H18" s="31"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
-    </row>
-    <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="30" t="s">
-        <v>2896</v>
-      </c>
-      <c r="H19" s="31"/>
-    </row>
-    <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="31"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="30" t="s">
-        <v>2902</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>2935</v>
-      </c>
-      <c r="G20" s="31" t="s">
-        <v>2936</v>
-      </c>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-    </row>
-    <row r="21" ht="18.75" customHeight="1">
-      <c r="A21" s="31"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="H21" s="31"/>
-    </row>
-    <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="30" t="s">
-        <v>2937</v>
-      </c>
-      <c r="B22" s="30" t="s">
-        <v>2873</v>
-      </c>
-      <c r="H22" s="30" t="s">
-        <v>2938</v>
-      </c>
-    </row>
-    <row r="23" ht="18.75" customHeight="1">
-      <c r="B23" s="30" t="s">
-        <v>2939</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>2940</v>
-      </c>
-      <c r="D23" s="30" t="s">
-        <v>2941</v>
-      </c>
-      <c r="E23" s="30" t="s">
-        <v>2942</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>2943</v>
-      </c>
-      <c r="G23" s="30" t="s">
-        <v>2944</v>
-      </c>
-      <c r="H23" s="30" t="s">
-        <v>2945</v>
-      </c>
-      <c r="I23" s="30" t="s">
-        <v>2946</v>
-      </c>
-      <c r="J23" s="30" t="s">
-        <v>2947</v>
-      </c>
-    </row>
-    <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" s="30" t="s">
-        <v>2892</v>
-      </c>
-      <c r="B24" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>2948</v>
-      </c>
-      <c r="D24" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="31" t="s">
+      <c r="B29" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>2960</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" s="30" t="s">
+        <v>2961</v>
+      </c>
+      <c r="G29" s="30" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H29" s="30" t="s">
+        <v>568</v>
+      </c>
+      <c r="J29" s="30" t="s">
+        <v>2963</v>
+      </c>
+    </row>
+    <row r="30" ht="18.75" customHeight="1">
+      <c r="A30" s="29" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>2964</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="H30" s="30" t="s">
+        <v>2963</v>
+      </c>
+    </row>
+    <row r="31" ht="18.75" customHeight="1">
+      <c r="A31" s="29" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B31" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>2965</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>2966</v>
+      </c>
+      <c r="G31" s="30" t="s">
+        <v>2967</v>
+      </c>
+      <c r="H31" s="30" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="32" ht="18.75" customHeight="1">
+      <c r="A32" s="29"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="29" t="s">
+        <v>2968</v>
+      </c>
+    </row>
+    <row r="33" ht="18.75" customHeight="1">
+      <c r="A33" s="29"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="29" t="s">
         <v>2949</v>
       </c>
-      <c r="G24" s="31" t="s">
+      <c r="I33" s="29" t="s">
         <v>2950</v>
       </c>
-      <c r="H24" s="31" t="s">
-        <v>570</v>
-      </c>
-      <c r="I24" s="31" t="s">
-        <v>570</v>
-      </c>
-      <c r="J24" s="31" t="s">
+      <c r="J33" s="29" t="s">
         <v>2951</v>
       </c>
     </row>
-    <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="30" t="s">
-        <v>2896</v>
-      </c>
-      <c r="B25" s="31" t="s">
-        <v>2952</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="I25" s="31" t="s">
+    <row r="34" ht="18.75" customHeight="1">
+      <c r="A34" s="29"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30" t="s">
+        <v>2954</v>
+      </c>
+      <c r="I34" s="30" t="s">
+        <v>2954</v>
+      </c>
+      <c r="J34" s="30" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="35" ht="18.75" customHeight="1">
+      <c r="A35" s="29"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="I35" s="30" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="36" ht="18.75" customHeight="1">
+      <c r="A36" s="29"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+    </row>
+    <row r="37" ht="18.75" customHeight="1">
+      <c r="A37" s="29"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="29" t="s">
+        <v>2970</v>
+      </c>
+    </row>
+    <row r="38" ht="18.75" customHeight="1">
+      <c r="A38" s="29"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="29" t="s">
+        <v>2949</v>
+      </c>
+      <c r="I38" s="29" t="s">
+        <v>2950</v>
+      </c>
+      <c r="J38" s="29" t="s">
         <v>2951</v>
       </c>
     </row>
-    <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="30" t="s">
-        <v>2902</v>
-      </c>
-      <c r="B26" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="31" t="s">
-        <v>2953</v>
-      </c>
-      <c r="G26" s="31" t="s">
-        <v>2954</v>
-      </c>
-    </row>
-    <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="30" t="s">
-        <v>2937</v>
-      </c>
-      <c r="B27" s="30" t="s">
-        <v>2874</v>
-      </c>
-      <c r="H27" s="30" t="s">
-        <v>2955</v>
-      </c>
-    </row>
-    <row r="28" ht="18.75" customHeight="1">
-      <c r="B28" s="30" t="s">
-        <v>2939</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>2940</v>
-      </c>
-      <c r="D28" s="30" t="s">
-        <v>2941</v>
-      </c>
-      <c r="E28" s="30" t="s">
-        <v>2942</v>
-      </c>
-      <c r="F28" s="30" t="s">
-        <v>2943</v>
-      </c>
-      <c r="G28" s="30" t="s">
-        <v>2944</v>
-      </c>
-      <c r="H28" s="30" t="s">
-        <v>2945</v>
-      </c>
-      <c r="I28" s="30" t="s">
-        <v>2946</v>
-      </c>
-      <c r="J28" s="30" t="s">
-        <v>2947</v>
-      </c>
-    </row>
-    <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="30" t="s">
-        <v>2892</v>
-      </c>
-      <c r="B29" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="31" t="s">
-        <v>2956</v>
-      </c>
-      <c r="D29" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="F29" s="31" t="s">
-        <v>2957</v>
-      </c>
-      <c r="G29" s="31" t="s">
-        <v>2958</v>
-      </c>
-      <c r="H29" s="31" t="s">
-        <v>568</v>
-      </c>
-      <c r="J29" s="31" t="s">
-        <v>2959</v>
-      </c>
-    </row>
-    <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" s="30" t="s">
-        <v>2896</v>
-      </c>
-      <c r="B30" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="31" t="s">
-        <v>2960</v>
-      </c>
-      <c r="D30" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="H30" s="31" t="s">
-        <v>2959</v>
-      </c>
-    </row>
-    <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" s="30" t="s">
-        <v>2902</v>
-      </c>
-      <c r="B31" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="31" t="s">
-        <v>2961</v>
-      </c>
-      <c r="D31" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="F31" s="31" t="s">
+    <row r="39" ht="18.75" customHeight="1">
+      <c r="A39" s="29"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30" t="s">
         <v>2962</v>
       </c>
-      <c r="G31" s="31" t="s">
-        <v>2963</v>
-      </c>
-      <c r="H31" s="31" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" s="30"/>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="30" t="s">
-        <v>2964</v>
-      </c>
-    </row>
-    <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" s="30"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="30" t="s">
-        <v>2945</v>
-      </c>
-      <c r="I33" s="30" t="s">
-        <v>2946</v>
-      </c>
-      <c r="J33" s="30" t="s">
-        <v>2947</v>
-      </c>
-    </row>
-    <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" s="30"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31" t="s">
-        <v>2950</v>
-      </c>
-      <c r="I34" s="31" t="s">
-        <v>2950</v>
-      </c>
-      <c r="J34" s="31" t="s">
-        <v>2965</v>
-      </c>
-    </row>
-    <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" s="30"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="I35" s="31" t="s">
-        <v>2965</v>
-      </c>
-    </row>
-    <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" s="30"/>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-    </row>
-    <row r="37" ht="18.75" customHeight="1">
-      <c r="A37" s="30"/>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="30" t="s">
-        <v>2966</v>
-      </c>
-    </row>
-    <row r="38" ht="18.75" customHeight="1">
-      <c r="A38" s="30"/>
-      <c r="B38" s="31"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="30" t="s">
-        <v>2945</v>
-      </c>
-      <c r="I38" s="30" t="s">
-        <v>2946</v>
-      </c>
-      <c r="J38" s="30" t="s">
-        <v>2947</v>
-      </c>
-    </row>
-    <row r="39" ht="18.75" customHeight="1">
-      <c r="A39" s="30"/>
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31" t="s">
-        <v>2958</v>
-      </c>
-      <c r="J39" s="31" t="s">
-        <v>2967</v>
+      <c r="J39" s="30" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
-      <c r="A40" s="30"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31" t="s">
-        <v>2967</v>
+      <c r="A40" s="29"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="41" ht="18.75" customHeight="1">
-      <c r="A41" s="30"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31" t="s">
-        <v>2958</v>
+      <c r="A41" s="29"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30" t="s">
+        <v>2962</v>
       </c>
     </row>
   </sheetData>
@@ -29258,682 +29291,682 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="30" t="s">
-        <v>2968</v>
-      </c>
-      <c r="B1" s="36" t="s">
-        <v>2969</v>
-      </c>
-      <c r="E1" s="34"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
+      <c r="A1" s="29" t="s">
+        <v>2972</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>2973</v>
+      </c>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="E2" s="34"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="35"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
+      <c r="A3" s="34"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="30" t="s">
-        <v>2970</v>
-      </c>
-      <c r="E4" s="34"/>
-      <c r="F4" s="30" t="s">
-        <v>2971</v>
-      </c>
-      <c r="J4" s="31"/>
+      <c r="A4" s="29" t="s">
+        <v>2974</v>
+      </c>
+      <c r="E4" s="33"/>
+      <c r="F4" s="29" t="s">
+        <v>2975</v>
+      </c>
+      <c r="J4" s="30"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="26" t="s">
-        <v>2873</v>
-      </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="26" t="s">
-        <v>2873</v>
-      </c>
-      <c r="J5" s="31"/>
+      <c r="A5" s="25" t="s">
+        <v>2877</v>
+      </c>
+      <c r="E5" s="33"/>
+      <c r="F5" s="25" t="s">
+        <v>2877</v>
+      </c>
+      <c r="J5" s="30"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="26"/>
-      <c r="B6" s="30" t="s">
-        <v>2889</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>2890</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>2891</v>
-      </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="30" t="s">
-        <v>2889</v>
-      </c>
-      <c r="H6" s="30" t="s">
-        <v>2890</v>
-      </c>
-      <c r="I6" s="30" t="s">
-        <v>2891</v>
-      </c>
-      <c r="J6" s="31"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="29" t="s">
+        <v>2893</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>2894</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>2895</v>
+      </c>
+      <c r="E6" s="33"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="29" t="s">
+        <v>2893</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>2894</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>2895</v>
+      </c>
+      <c r="J6" s="30"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="30" t="s">
-        <v>2892</v>
-      </c>
-      <c r="B7" s="31" t="s">
+      <c r="A7" s="29" t="s">
+        <v>2896</v>
+      </c>
+      <c r="B7" s="30" t="s">
         <v>1619</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="30" t="s">
         <v>1619</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>2972</v>
-      </c>
-      <c r="E7" s="34"/>
-      <c r="F7" s="30" t="s">
-        <v>2892</v>
-      </c>
-      <c r="G7" s="31" t="s">
+      <c r="D7" s="30" t="s">
+        <v>2976</v>
+      </c>
+      <c r="E7" s="33"/>
+      <c r="F7" s="29" t="s">
+        <v>2896</v>
+      </c>
+      <c r="G7" s="30" t="s">
         <v>1906</v>
       </c>
-      <c r="H7" s="31" t="s">
+      <c r="H7" s="30" t="s">
         <v>1906</v>
       </c>
-      <c r="I7" s="31" t="s">
-        <v>2973</v>
-      </c>
-      <c r="J7" s="31"/>
+      <c r="I7" s="30" t="s">
+        <v>2977</v>
+      </c>
+      <c r="J7" s="30"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="29" t="s">
+        <v>2900</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>2976</v>
+      </c>
+      <c r="E8" s="33"/>
+      <c r="F8" s="29" t="s">
+        <v>2900</v>
+      </c>
+      <c r="H8" s="30" t="s">
+        <v>2977</v>
+      </c>
+      <c r="J8" s="30"/>
+    </row>
+    <row r="9" ht="18.75" customHeight="1">
+      <c r="A9" s="29" t="s">
+        <v>2906</v>
+      </c>
+      <c r="E9" s="33"/>
+      <c r="F9" s="29" t="s">
+        <v>2906</v>
+      </c>
+      <c r="J9" s="30"/>
+    </row>
+    <row r="10" ht="18.75" customHeight="1">
+      <c r="A10" s="29" t="s">
+        <v>2878</v>
+      </c>
+      <c r="E10" s="33"/>
+      <c r="F10" s="29" t="s">
+        <v>2878</v>
+      </c>
+      <c r="J10" s="30"/>
+    </row>
+    <row r="11" ht="18.75" customHeight="1">
+      <c r="A11" s="25"/>
+      <c r="B11" s="29" t="s">
+        <v>2893</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>2894</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>2895</v>
+      </c>
+      <c r="E11" s="33"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="29" t="s">
+        <v>2893</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>2894</v>
+      </c>
+      <c r="I11" s="29" t="s">
+        <v>2895</v>
+      </c>
+      <c r="J11" s="30"/>
+    </row>
+    <row r="12" ht="18.75" customHeight="1">
+      <c r="A12" s="29" t="s">
         <v>2896</v>
       </c>
-      <c r="C8" s="31" t="s">
-        <v>2972</v>
-      </c>
-      <c r="E8" s="34"/>
-      <c r="F8" s="30" t="s">
+      <c r="B12" s="30" t="s">
+        <v>2978</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>2979</v>
+      </c>
+      <c r="E12" s="33"/>
+      <c r="F12" s="29" t="s">
         <v>2896</v>
       </c>
-      <c r="H8" s="31" t="s">
-        <v>2973</v>
-      </c>
-      <c r="J8" s="31"/>
-    </row>
-    <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="30" t="s">
-        <v>2902</v>
-      </c>
-      <c r="E9" s="34"/>
-      <c r="F9" s="30" t="s">
-        <v>2902</v>
-      </c>
-      <c r="J9" s="31"/>
-    </row>
-    <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="30" t="s">
-        <v>2874</v>
-      </c>
-      <c r="E10" s="34"/>
-      <c r="F10" s="30" t="s">
-        <v>2874</v>
-      </c>
-      <c r="J10" s="31"/>
-    </row>
-    <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="26"/>
-      <c r="B11" s="30" t="s">
-        <v>2889</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>2890</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>2891</v>
-      </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="30" t="s">
-        <v>2889</v>
-      </c>
-      <c r="H11" s="30" t="s">
-        <v>2890</v>
-      </c>
-      <c r="I11" s="30" t="s">
-        <v>2891</v>
-      </c>
-      <c r="J11" s="31"/>
-    </row>
-    <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="30" t="s">
-        <v>2892</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>2974</v>
-      </c>
-      <c r="C12" s="31" t="s">
+      <c r="G12" s="30" t="s">
+        <v>2980</v>
+      </c>
+      <c r="H12" s="30" t="s">
+        <v>1906</v>
+      </c>
+      <c r="I12" s="30" t="s">
+        <v>2977</v>
+      </c>
+      <c r="J12" s="30"/>
+    </row>
+    <row r="13" ht="18.75" customHeight="1">
+      <c r="A13" s="29" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>2981</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>2976</v>
+      </c>
+      <c r="E13" s="33"/>
+      <c r="F13" s="29" t="s">
+        <v>2900</v>
+      </c>
+      <c r="H13" s="30" t="s">
+        <v>2977</v>
+      </c>
+      <c r="J13" s="30"/>
+    </row>
+    <row r="14" ht="18.75" customHeight="1">
+      <c r="A14" s="29" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>2978</v>
+      </c>
+      <c r="C14" s="30" t="s">
         <v>1619</v>
       </c>
-      <c r="D12" s="31" t="s">
-        <v>2975</v>
-      </c>
-      <c r="E12" s="34"/>
-      <c r="F12" s="30" t="s">
-        <v>2892</v>
-      </c>
-      <c r="G12" s="31" t="s">
-        <v>2976</v>
-      </c>
-      <c r="H12" s="31" t="s">
+      <c r="E14" s="33"/>
+      <c r="F14" s="29" t="s">
+        <v>2906</v>
+      </c>
+      <c r="H14" s="30" t="s">
         <v>1906</v>
       </c>
-      <c r="I12" s="31" t="s">
-        <v>2973</v>
-      </c>
-      <c r="J12" s="31"/>
-    </row>
-    <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="30" t="s">
+      <c r="J14" s="30"/>
+    </row>
+    <row r="15" ht="18.75" customHeight="1">
+      <c r="A15" s="29" t="s">
+        <v>2982</v>
+      </c>
+      <c r="E15" s="33"/>
+      <c r="F15" s="29" t="s">
+        <v>2982</v>
+      </c>
+      <c r="J15" s="30"/>
+    </row>
+    <row r="16" ht="18.75" customHeight="1">
+      <c r="A16" s="29" t="s">
+        <v>2983</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>2984</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>2985</v>
+      </c>
+      <c r="D16" s="36"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="29" t="s">
+        <v>2983</v>
+      </c>
+      <c r="G16" s="30" t="s">
+        <v>2986</v>
+      </c>
+      <c r="H16" s="36"/>
+      <c r="J16" s="30"/>
+    </row>
+    <row r="17" ht="18.75" customHeight="1">
+      <c r="A17" s="29" t="s">
+        <v>2987</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>2988</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>2989</v>
+      </c>
+      <c r="E17" s="33"/>
+      <c r="F17" s="29" t="s">
+        <v>2987</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>2990</v>
+      </c>
+      <c r="J17" s="30"/>
+    </row>
+    <row r="18" ht="18.75" customHeight="1">
+      <c r="A18" s="29" t="s">
+        <v>2991</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>2992</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>2993</v>
+      </c>
+      <c r="E18" s="33"/>
+      <c r="F18" s="29" t="s">
+        <v>2991</v>
+      </c>
+      <c r="G18" s="30" t="s">
+        <v>1906</v>
+      </c>
+      <c r="J18" s="30"/>
+    </row>
+    <row r="19" ht="18.75" customHeight="1">
+      <c r="J19" s="30"/>
+    </row>
+    <row r="20" ht="18.75" customHeight="1">
+      <c r="A20" s="29" t="s">
+        <v>2994</v>
+      </c>
+      <c r="F20" s="29" t="s">
+        <v>2995</v>
+      </c>
+      <c r="J20" s="30"/>
+    </row>
+    <row r="21" ht="18.75" customHeight="1">
+      <c r="A21" s="25" t="s">
+        <v>2877</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>2877</v>
+      </c>
+      <c r="J21" s="30"/>
+    </row>
+    <row r="22" ht="18.75" customHeight="1">
+      <c r="A22" s="25"/>
+      <c r="B22" s="29" t="s">
+        <v>2893</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>2894</v>
+      </c>
+      <c r="D22" s="29" t="s">
+        <v>2895</v>
+      </c>
+      <c r="F22" s="25"/>
+      <c r="G22" s="29" t="s">
+        <v>2893</v>
+      </c>
+      <c r="H22" s="29" t="s">
+        <v>2894</v>
+      </c>
+      <c r="I22" s="29" t="s">
+        <v>2895</v>
+      </c>
+      <c r="J22" s="30"/>
+    </row>
+    <row r="23" ht="18.75" customHeight="1">
+      <c r="A23" s="29" t="s">
         <v>2896</v>
       </c>
-      <c r="B13" s="31" t="s">
-        <v>2977</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>2972</v>
-      </c>
-      <c r="E13" s="34"/>
-      <c r="F13" s="30" t="s">
+      <c r="B23" s="30" t="s">
+        <v>2996</v>
+      </c>
+      <c r="F23" s="29" t="s">
         <v>2896</v>
       </c>
-      <c r="H13" s="31" t="s">
-        <v>2973</v>
-      </c>
-      <c r="J13" s="31"/>
-    </row>
-    <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="30" t="s">
-        <v>2902</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>2974</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>1619</v>
-      </c>
-      <c r="E14" s="34"/>
-      <c r="F14" s="30" t="s">
-        <v>2902</v>
-      </c>
-      <c r="H14" s="31" t="s">
-        <v>1906</v>
-      </c>
-      <c r="J14" s="31"/>
-    </row>
-    <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="30" t="s">
-        <v>2978</v>
-      </c>
-      <c r="E15" s="34"/>
-      <c r="F15" s="30" t="s">
-        <v>2978</v>
-      </c>
-      <c r="J15" s="31"/>
-    </row>
-    <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="30" t="s">
-        <v>2979</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>2980</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>2981</v>
-      </c>
-      <c r="D16" s="37"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="30" t="s">
-        <v>2979</v>
-      </c>
-      <c r="G16" s="31" t="s">
+      <c r="G23" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="J23" s="30"/>
+    </row>
+    <row r="24" ht="18.75" customHeight="1">
+      <c r="A24" s="29" t="s">
+        <v>2900</v>
+      </c>
+      <c r="F24" s="29" t="s">
+        <v>2900</v>
+      </c>
+      <c r="J24" s="30"/>
+    </row>
+    <row r="25" ht="18.75" customHeight="1">
+      <c r="A25" s="29" t="s">
+        <v>2906</v>
+      </c>
+      <c r="F25" s="29" t="s">
+        <v>2906</v>
+      </c>
+      <c r="J25" s="30"/>
+    </row>
+    <row r="26" ht="18.75" customHeight="1">
+      <c r="A26" s="29" t="s">
+        <v>2878</v>
+      </c>
+      <c r="E26" s="33"/>
+      <c r="F26" s="29" t="s">
+        <v>2878</v>
+      </c>
+      <c r="J26" s="30"/>
+    </row>
+    <row r="27" ht="18.75" customHeight="1">
+      <c r="A27" s="25"/>
+      <c r="B27" s="29" t="s">
+        <v>2893</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>2894</v>
+      </c>
+      <c r="D27" s="29" t="s">
+        <v>2895</v>
+      </c>
+      <c r="E27" s="33"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="29" t="s">
+        <v>2893</v>
+      </c>
+      <c r="H27" s="29" t="s">
+        <v>2894</v>
+      </c>
+      <c r="I27" s="29" t="s">
+        <v>2895</v>
+      </c>
+      <c r="J27" s="30"/>
+    </row>
+    <row r="28" ht="18.75" customHeight="1">
+      <c r="A28" s="29" t="s">
+        <v>2896</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>2996</v>
+      </c>
+      <c r="E28" s="33"/>
+      <c r="F28" s="29" t="s">
+        <v>2896</v>
+      </c>
+      <c r="G28" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="J28" s="30"/>
+    </row>
+    <row r="29" ht="18.75" customHeight="1">
+      <c r="A29" s="29" t="s">
+        <v>2900</v>
+      </c>
+      <c r="E29" s="33"/>
+      <c r="F29" s="29" t="s">
+        <v>2900</v>
+      </c>
+      <c r="J29" s="30"/>
+    </row>
+    <row r="30" ht="18.75" customHeight="1">
+      <c r="A30" s="29" t="s">
+        <v>2906</v>
+      </c>
+      <c r="E30" s="33"/>
+      <c r="F30" s="29" t="s">
+        <v>2906</v>
+      </c>
+      <c r="J30" s="30"/>
+    </row>
+    <row r="31" ht="18.75" customHeight="1">
+      <c r="A31" s="29" t="s">
         <v>2982</v>
       </c>
-      <c r="H16" s="37"/>
-      <c r="J16" s="31"/>
-    </row>
-    <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="30" t="s">
+      <c r="E31" s="33"/>
+      <c r="F31" s="29" t="s">
+        <v>2982</v>
+      </c>
+      <c r="J31" s="30"/>
+    </row>
+    <row r="32" ht="18.75" customHeight="1">
+      <c r="A32" s="29" t="s">
         <v>2983</v>
       </c>
-      <c r="B17" s="31" t="s">
-        <v>2984</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>2985</v>
-      </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="30" t="s">
+      <c r="B32" s="30" t="s">
+        <v>2997</v>
+      </c>
+      <c r="C32" s="36"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="29" t="s">
         <v>2983</v>
       </c>
-      <c r="G17" s="31" t="s">
-        <v>2986</v>
-      </c>
-      <c r="J17" s="31"/>
-    </row>
-    <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" s="30" t="s">
+      <c r="G32" s="30" t="s">
+        <v>2998</v>
+      </c>
+      <c r="H32" s="36"/>
+      <c r="J32" s="30"/>
+    </row>
+    <row r="33" ht="18.75" customHeight="1">
+      <c r="A33" s="29" t="s">
         <v>2987</v>
       </c>
-      <c r="B18" s="31" t="s">
-        <v>2988</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>2989</v>
-      </c>
-      <c r="E18" s="34"/>
-      <c r="F18" s="30" t="s">
+      <c r="B33" s="30" t="s">
+        <v>2999</v>
+      </c>
+      <c r="E33" s="33"/>
+      <c r="F33" s="29" t="s">
         <v>2987</v>
       </c>
-      <c r="G18" s="31" t="s">
-        <v>1906</v>
-      </c>
-      <c r="J18" s="31"/>
-    </row>
-    <row r="19" ht="18.75" customHeight="1">
-      <c r="J19" s="31"/>
-    </row>
-    <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="30" t="s">
-        <v>2990</v>
-      </c>
-      <c r="F20" s="30" t="s">
+      <c r="G33" s="30" t="s">
+        <v>3000</v>
+      </c>
+      <c r="J33" s="30"/>
+    </row>
+    <row r="34" ht="18.75" customHeight="1">
+      <c r="A34" s="29" t="s">
         <v>2991</v>
       </c>
-      <c r="J20" s="31"/>
-    </row>
-    <row r="21" ht="18.75" customHeight="1">
-      <c r="A21" s="26" t="s">
-        <v>2873</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>2873</v>
-      </c>
-      <c r="J21" s="31"/>
-    </row>
-    <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="26"/>
-      <c r="B22" s="30" t="s">
-        <v>2889</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>2890</v>
-      </c>
-      <c r="D22" s="30" t="s">
-        <v>2891</v>
-      </c>
-      <c r="F22" s="26"/>
-      <c r="G22" s="30" t="s">
-        <v>2889</v>
-      </c>
-      <c r="H22" s="30" t="s">
-        <v>2890</v>
-      </c>
-      <c r="I22" s="30" t="s">
-        <v>2891</v>
-      </c>
-      <c r="J22" s="31"/>
-    </row>
-    <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" s="30" t="s">
-        <v>2892</v>
-      </c>
-      <c r="B23" s="31" t="s">
-        <v>2992</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>2892</v>
-      </c>
-      <c r="G23" s="31" t="s">
-        <v>183</v>
-      </c>
-      <c r="J23" s="31"/>
-    </row>
-    <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" s="30" t="s">
-        <v>2896</v>
-      </c>
-      <c r="F24" s="30" t="s">
-        <v>2896</v>
-      </c>
-      <c r="J24" s="31"/>
-    </row>
-    <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="30" t="s">
-        <v>2902</v>
-      </c>
-      <c r="F25" s="30" t="s">
-        <v>2902</v>
-      </c>
-      <c r="J25" s="31"/>
-    </row>
-    <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="30" t="s">
-        <v>2874</v>
-      </c>
-      <c r="E26" s="34"/>
-      <c r="F26" s="30" t="s">
-        <v>2874</v>
-      </c>
-      <c r="J26" s="31"/>
-    </row>
-    <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="26"/>
-      <c r="B27" s="30" t="s">
-        <v>2889</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>2890</v>
-      </c>
-      <c r="D27" s="30" t="s">
-        <v>2891</v>
-      </c>
-      <c r="E27" s="34"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="30" t="s">
-        <v>2889</v>
-      </c>
-      <c r="H27" s="30" t="s">
-        <v>2890</v>
-      </c>
-      <c r="I27" s="30" t="s">
-        <v>2891</v>
-      </c>
-      <c r="J27" s="31"/>
-    </row>
-    <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" s="30" t="s">
-        <v>2892</v>
-      </c>
-      <c r="B28" s="31" t="s">
-        <v>2992</v>
-      </c>
-      <c r="E28" s="34"/>
-      <c r="F28" s="30" t="s">
-        <v>2892</v>
-      </c>
-      <c r="G28" s="31" t="s">
-        <v>183</v>
-      </c>
-      <c r="J28" s="31"/>
-    </row>
-    <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="30" t="s">
-        <v>2896</v>
-      </c>
-      <c r="E29" s="34"/>
-      <c r="F29" s="30" t="s">
-        <v>2896</v>
-      </c>
-      <c r="J29" s="31"/>
-    </row>
-    <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" s="30" t="s">
-        <v>2902</v>
-      </c>
-      <c r="E30" s="34"/>
-      <c r="F30" s="30" t="s">
-        <v>2902</v>
-      </c>
-      <c r="J30" s="31"/>
-    </row>
-    <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" s="30" t="s">
-        <v>2978</v>
-      </c>
-      <c r="E31" s="34"/>
-      <c r="F31" s="30" t="s">
-        <v>2978</v>
-      </c>
-      <c r="J31" s="31"/>
-    </row>
-    <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" s="30" t="s">
-        <v>2979</v>
-      </c>
-      <c r="B32" s="31" t="s">
-        <v>2993</v>
-      </c>
-      <c r="C32" s="37"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="30" t="s">
-        <v>2979</v>
-      </c>
-      <c r="G32" s="31" t="s">
-        <v>2994</v>
-      </c>
-      <c r="H32" s="37"/>
-      <c r="J32" s="31"/>
-    </row>
-    <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" s="30" t="s">
+      <c r="B34" s="30" t="s">
+        <v>3001</v>
+      </c>
+      <c r="E34" s="33"/>
+      <c r="F34" s="29" t="s">
+        <v>2991</v>
+      </c>
+      <c r="G34" s="30" t="s">
+        <v>3002</v>
+      </c>
+      <c r="J34" s="30"/>
+    </row>
+    <row r="35" ht="18.75" customHeight="1">
+      <c r="A35" s="34"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+    </row>
+    <row r="36" ht="18.75" customHeight="1">
+      <c r="A36" s="29" t="s">
+        <v>3003</v>
+      </c>
+      <c r="C36" s="29" t="s">
+        <v>3004</v>
+      </c>
+      <c r="E36" s="33"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+    </row>
+    <row r="37" ht="18.75" customHeight="1">
+      <c r="A37" s="29" t="s">
+        <v>3005</v>
+      </c>
+      <c r="B37" s="30" t="s">
+        <v>3006</v>
+      </c>
+      <c r="C37" s="29" t="s">
+        <v>3005</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>3007</v>
+      </c>
+      <c r="E37" s="33"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+    </row>
+    <row r="38" ht="18.75" customHeight="1">
+      <c r="A38" s="29" t="s">
         <v>2983</v>
       </c>
-      <c r="B33" s="31" t="s">
-        <v>2995</v>
-      </c>
-      <c r="E33" s="34"/>
-      <c r="F33" s="30" t="s">
+      <c r="B38" s="30" t="s">
+        <v>3008</v>
+      </c>
+      <c r="C38" s="29" t="s">
         <v>2983</v>
       </c>
-      <c r="G33" s="31" t="s">
-        <v>2996</v>
-      </c>
-      <c r="J33" s="31"/>
-    </row>
-    <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" s="30" t="s">
+      <c r="D38" s="30" t="s">
+        <v>3009</v>
+      </c>
+      <c r="E38" s="33"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+    </row>
+    <row r="39" ht="18.75" customHeight="1">
+      <c r="A39" s="29" t="s">
         <v>2987</v>
       </c>
-      <c r="B34" s="31" t="s">
-        <v>2997</v>
-      </c>
-      <c r="E34" s="34"/>
-      <c r="F34" s="30" t="s">
+      <c r="B39" s="30" t="s">
+        <v>3010</v>
+      </c>
+      <c r="C39" s="29" t="s">
         <v>2987</v>
       </c>
-      <c r="G34" s="31" t="s">
-        <v>2998</v>
-      </c>
-      <c r="J34" s="31"/>
-    </row>
-    <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" s="35"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-    </row>
-    <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" s="30" t="s">
-        <v>2999</v>
-      </c>
-      <c r="C36" s="30" t="s">
-        <v>3000</v>
-      </c>
-      <c r="E36" s="34"/>
-      <c r="F36" s="35"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="31"/>
-    </row>
-    <row r="37" ht="18.75" customHeight="1">
-      <c r="A37" s="30" t="s">
-        <v>3001</v>
-      </c>
-      <c r="B37" s="31" t="s">
-        <v>3002</v>
-      </c>
-      <c r="C37" s="30" t="s">
-        <v>3001</v>
-      </c>
-      <c r="D37" s="31" t="s">
-        <v>3003</v>
-      </c>
-      <c r="E37" s="34"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-    </row>
-    <row r="38" ht="18.75" customHeight="1">
-      <c r="A38" s="30" t="s">
-        <v>2979</v>
-      </c>
-      <c r="B38" s="31" t="s">
-        <v>3004</v>
-      </c>
-      <c r="C38" s="30" t="s">
-        <v>2979</v>
-      </c>
-      <c r="D38" s="31" t="s">
-        <v>3005</v>
-      </c>
-      <c r="E38" s="34"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="31"/>
-      <c r="J38" s="31"/>
-    </row>
-    <row r="39" ht="18.75" customHeight="1">
-      <c r="A39" s="30" t="s">
-        <v>2983</v>
-      </c>
-      <c r="B39" s="31" t="s">
-        <v>3006</v>
-      </c>
-      <c r="C39" s="30" t="s">
-        <v>2983</v>
-      </c>
-      <c r="D39" s="31" t="s">
-        <v>3007</v>
-      </c>
-      <c r="E39" s="34"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="31"/>
+      <c r="D39" s="30" t="s">
+        <v>3011</v>
+      </c>
+      <c r="E39" s="33"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
-      <c r="A40" s="35"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
+      <c r="A40" s="34"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
-      <c r="A41" s="35"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
+      <c r="A41" s="34"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="30"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
-      <c r="A42" s="35"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
+      <c r="A42" s="34"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
-      <c r="A43" s="35"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="31"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="31"/>
+      <c r="A43" s="34"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
-      <c r="A44" s="35"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="31"/>
-      <c r="I44" s="31"/>
-      <c r="J44" s="31"/>
+      <c r="A44" s="34"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="33"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
-      <c r="A45" s="35"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="35"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="31"/>
-      <c r="I45" s="31"/>
-      <c r="J45" s="31"/>
+      <c r="A45" s="34"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="30"/>
+      <c r="J45" s="30"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
-      <c r="A46" s="35"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="31"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="31"/>
+      <c r="A46" s="34"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="37">
@@ -29990,621 +30023,621 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="30" t="s">
-        <v>3008</v>
-      </c>
-      <c r="B1" s="30" t="s">
-        <v>3009</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>3010</v>
-      </c>
-      <c r="D1" s="30" t="s">
+      <c r="A1" s="29" t="s">
+        <v>3012</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>3013</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>3014</v>
+      </c>
+      <c r="D1" s="29" t="s">
         <v>1354</v>
       </c>
-      <c r="F1" s="30" t="s">
-        <v>3008</v>
-      </c>
-      <c r="G1" s="30" t="s">
-        <v>3009</v>
-      </c>
-      <c r="H1" s="30" t="s">
-        <v>3010</v>
+      <c r="F1" s="29" t="s">
+        <v>3012</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>3013</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>3014</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="31" t="s">
-        <v>3011</v>
-      </c>
-      <c r="B2" s="31" t="s">
-        <v>3012</v>
-      </c>
-      <c r="C2" s="31" t="s">
-        <v>3013</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>3014</v>
-      </c>
-      <c r="F2" s="31" t="s">
+      <c r="A2" s="30" t="s">
         <v>3015</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="B2" s="30" t="s">
         <v>3016</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="C2" s="30" t="s">
         <v>3017</v>
       </c>
+      <c r="D2" s="30" t="s">
+        <v>3018</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>3019</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>3020</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>3021</v>
+      </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="31" t="s">
-        <v>3018</v>
-      </c>
-      <c r="B3" s="31" t="s">
-        <v>3019</v>
-      </c>
-      <c r="C3" s="31" t="s">
-        <v>3020</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>3021</v>
-      </c>
-      <c r="F3" s="31" t="s">
+      <c r="A3" s="30" t="s">
         <v>3022</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="B3" s="30" t="s">
         <v>3023</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="C3" s="30" t="s">
         <v>3024</v>
       </c>
+      <c r="D3" s="30" t="s">
+        <v>3025</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>3026</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>3027</v>
+      </c>
+      <c r="H3" s="30" t="s">
+        <v>3028</v>
+      </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="31" t="s">
-        <v>3025</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>3026</v>
-      </c>
-      <c r="C4" s="31" t="s">
+      <c r="A4" s="30" t="s">
+        <v>3029</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>3030</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>3031</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>2955</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>3032</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>3033</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="30" t="s">
+        <v>3035</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>3036</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>3038</v>
+      </c>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+    </row>
+    <row r="6" ht="18.75" customHeight="1">
+      <c r="A6" s="30" t="s">
+        <v>3039</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>3040</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>3041</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>3042</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>3043</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>3044</v>
+      </c>
+      <c r="H6" s="30" t="s">
+        <v>3045</v>
+      </c>
+    </row>
+    <row r="7" ht="18.75" customHeight="1">
+      <c r="A7" s="30" t="s">
+        <v>3046</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>3047</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>3048</v>
+      </c>
+      <c r="D7" s="30" t="s">
         <v>3027</v>
       </c>
-      <c r="D4" s="31" t="s">
-        <v>2951</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>3028</v>
-      </c>
-      <c r="G4" s="31" t="s">
-        <v>3029</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>3030</v>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="31" t="s">
-        <v>3031</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>3032</v>
-      </c>
-      <c r="C5" s="31" t="s">
+      <c r="F7" s="30" t="s">
+        <v>3049</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>3050</v>
+      </c>
+      <c r="H7" s="30" t="s">
+        <v>3051</v>
+      </c>
+    </row>
+    <row r="8" ht="18.75" customHeight="1">
+      <c r="A8" s="30" t="s">
+        <v>3052</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>3053</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>3054</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>3055</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>3056</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>3057</v>
+      </c>
+      <c r="H8" s="30" t="s">
+        <v>3058</v>
+      </c>
+    </row>
+    <row r="9" ht="18.75" customHeight="1">
+      <c r="A9" s="30" t="s">
+        <v>3059</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>3060</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>3061</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>3062</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>3063</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>3064</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>3065</v>
+      </c>
+    </row>
+    <row r="10" ht="18.75" customHeight="1">
+      <c r="A10" s="30" t="s">
+        <v>3066</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>3067</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>3068</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>3069</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>3070</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>3071</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>3072</v>
+      </c>
+    </row>
+    <row r="11" ht="18.75" customHeight="1">
+      <c r="A11" s="30" t="s">
+        <v>3073</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>3074</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>3075</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>3076</v>
+      </c>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+    </row>
+    <row r="12" ht="18.75" customHeight="1">
+      <c r="A12" s="30" t="s">
+        <v>3077</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>3078</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>3079</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>3080</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>3081</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>3082</v>
+      </c>
+      <c r="H12" s="30" t="s">
+        <v>3083</v>
+      </c>
+    </row>
+    <row r="13" ht="18.75" customHeight="1">
+      <c r="A13" s="30" t="s">
+        <v>3084</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>3085</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>3086</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>3087</v>
+      </c>
+      <c r="H13" s="30"/>
+    </row>
+    <row r="14" ht="18.75" customHeight="1">
+      <c r="A14" s="30" t="s">
+        <v>3088</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>3089</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>3090</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>3091</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>3092</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>3093</v>
+      </c>
+      <c r="H14" s="30" t="s">
+        <v>3094</v>
+      </c>
+    </row>
+    <row r="15" ht="18.75" customHeight="1">
+      <c r="A15" s="30" t="s">
+        <v>3095</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>3096</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>3097</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>3098</v>
+      </c>
+      <c r="H15" s="30"/>
+    </row>
+    <row r="16" ht="18.75" customHeight="1">
+      <c r="A16" s="30" t="s">
+        <v>3099</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>3100</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>3101</v>
+      </c>
+      <c r="D16" s="30" t="s">
         <v>3033</v>
       </c>
-      <c r="D5" s="31" t="s">
-        <v>3034</v>
-      </c>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-    </row>
-    <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="31" t="s">
-        <v>3035</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>3036</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>3037</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>3038</v>
-      </c>
-      <c r="F6" s="31" t="s">
-        <v>3039</v>
-      </c>
-      <c r="G6" s="31" t="s">
-        <v>3040</v>
-      </c>
-      <c r="H6" s="31" t="s">
-        <v>3041</v>
-      </c>
-    </row>
-    <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="31" t="s">
-        <v>3042</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>3043</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>3044</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>3023</v>
-      </c>
-      <c r="F7" s="31" t="s">
-        <v>3045</v>
-      </c>
-      <c r="G7" s="31" t="s">
-        <v>3046</v>
-      </c>
-      <c r="H7" s="31" t="s">
-        <v>3047</v>
-      </c>
-    </row>
-    <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="31" t="s">
-        <v>3048</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>3049</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>3050</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>3051</v>
-      </c>
-      <c r="F8" s="31" t="s">
-        <v>3052</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>3053</v>
-      </c>
-      <c r="H8" s="31" t="s">
-        <v>3054</v>
-      </c>
-    </row>
-    <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="31" t="s">
-        <v>3055</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>3056</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>3057</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>3058</v>
-      </c>
-      <c r="F9" s="31" t="s">
-        <v>3059</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>3060</v>
-      </c>
-      <c r="H9" s="28" t="s">
-        <v>3061</v>
-      </c>
-    </row>
-    <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="31" t="s">
-        <v>3062</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>3063</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>3064</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>3065</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>3066</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>3067</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>3068</v>
-      </c>
-    </row>
-    <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="31" t="s">
-        <v>3069</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>3070</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>3071</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>3072</v>
-      </c>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-    </row>
-    <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="31" t="s">
-        <v>3073</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>3074</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>3075</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>3076</v>
-      </c>
-      <c r="F12" s="31" t="s">
-        <v>3077</v>
-      </c>
-      <c r="G12" s="31" t="s">
-        <v>3078</v>
-      </c>
-      <c r="H12" s="31" t="s">
-        <v>3079</v>
-      </c>
-    </row>
-    <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="31" t="s">
-        <v>3080</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>3081</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>3082</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>3083</v>
-      </c>
-      <c r="H13" s="31"/>
-    </row>
-    <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="31" t="s">
-        <v>3084</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>3085</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>3086</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>3087</v>
-      </c>
-      <c r="F14" s="31" t="s">
-        <v>3088</v>
-      </c>
-      <c r="G14" s="31" t="s">
-        <v>3089</v>
-      </c>
-      <c r="H14" s="31" t="s">
-        <v>3090</v>
-      </c>
-    </row>
-    <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="31" t="s">
-        <v>3091</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>3092</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>3093</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>3094</v>
-      </c>
-      <c r="H15" s="31"/>
-    </row>
-    <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="31" t="s">
-        <v>3095</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>3096</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>3097</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>3029</v>
-      </c>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31" t="s">
-        <v>3098</v>
-      </c>
-      <c r="G16" s="31" t="s">
-        <v>3099</v>
-      </c>
-      <c r="H16" s="31" t="s">
-        <v>3100</v>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30" t="s">
+        <v>3102</v>
+      </c>
+      <c r="G16" s="30" t="s">
+        <v>3103</v>
+      </c>
+      <c r="H16" s="30" t="s">
+        <v>3104</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="31" t="s">
-        <v>3101</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>3102</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>3103</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>3104</v>
+      <c r="A17" s="30" t="s">
+        <v>3105</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>3106</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>3108</v>
       </c>
     </row>
     <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" s="31" t="s">
-        <v>3105</v>
-      </c>
-      <c r="B18" s="31" t="s">
-        <v>3106</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>3107</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>3108</v>
-      </c>
-      <c r="H18" s="31"/>
+      <c r="A18" s="30" t="s">
+        <v>3109</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>3110</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>3111</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>3112</v>
+      </c>
+      <c r="H18" s="30"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" s="31" t="s">
-        <v>3109</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>3110</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>3111</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>3112</v>
-      </c>
-      <c r="H19" s="31"/>
+      <c r="A19" s="30" t="s">
+        <v>3113</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>3114</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>3115</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>3116</v>
+      </c>
+      <c r="H19" s="30"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="31" t="s">
-        <v>3113</v>
-      </c>
-      <c r="B20" s="31" t="s">
-        <v>3114</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>3115</v>
-      </c>
-      <c r="D20" s="31" t="s">
-        <v>2622</v>
-      </c>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
+      <c r="A20" s="30" t="s">
+        <v>3117</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>3118</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>3119</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>2626</v>
+      </c>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
-      <c r="A21" s="31" t="s">
-        <v>3116</v>
-      </c>
-      <c r="B21" s="31" t="s">
-        <v>3117</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>3118</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>3119</v>
-      </c>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
+      <c r="A21" s="30" t="s">
+        <v>3120</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>3121</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>3122</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>3123</v>
+      </c>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="31" t="s">
-        <v>3120</v>
-      </c>
-      <c r="B22" s="31" t="s">
-        <v>3121</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>3122</v>
-      </c>
-      <c r="D22" s="31" t="s">
-        <v>3123</v>
-      </c>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
+      <c r="A22" s="30" t="s">
+        <v>3124</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>3125</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>3126</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>3127</v>
+      </c>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" s="31" t="s">
-        <v>3124</v>
-      </c>
-      <c r="B23" s="31" t="s">
-        <v>3125</v>
-      </c>
-      <c r="C23" s="31" t="s">
-        <v>3126</v>
-      </c>
-      <c r="D23" s="31" t="s">
-        <v>3127</v>
-      </c>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
+      <c r="A23" s="30" t="s">
+        <v>3128</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>3130</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>3131</v>
+      </c>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" s="31" t="s">
-        <v>3128</v>
-      </c>
-      <c r="B24" s="31" t="s">
-        <v>3129</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>3130</v>
-      </c>
-      <c r="D24" s="31" t="s">
-        <v>3131</v>
-      </c>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
+      <c r="A24" s="30" t="s">
+        <v>3132</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>3133</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>3134</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>3135</v>
+      </c>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="31" t="s">
-        <v>3132</v>
-      </c>
-      <c r="B25" s="31" t="s">
-        <v>3133</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>3134</v>
-      </c>
-      <c r="D25" s="31" t="s">
-        <v>3135</v>
-      </c>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
+      <c r="A25" s="30" t="s">
+        <v>3136</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>3137</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>3138</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>3139</v>
+      </c>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="31" t="s">
-        <v>3136</v>
-      </c>
-      <c r="B26" s="31" t="s">
-        <v>3137</v>
-      </c>
-      <c r="C26" s="31" t="s">
-        <v>3138</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>3139</v>
-      </c>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
+      <c r="A26" s="30" t="s">
+        <v>3140</v>
+      </c>
+      <c r="B26" s="30" t="s">
+        <v>3141</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>3142</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>3143</v>
+      </c>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="31" t="s">
-        <v>3140</v>
-      </c>
-      <c r="B27" s="31" t="s">
-        <v>3141</v>
-      </c>
-      <c r="C27" s="31" t="s">
-        <v>3142</v>
-      </c>
-      <c r="D27" s="31" t="s">
-        <v>3143</v>
-      </c>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
+      <c r="A27" s="30" t="s">
+        <v>3144</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>3145</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>3146</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>3147</v>
+      </c>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" s="31" t="s">
-        <v>3144</v>
-      </c>
-      <c r="B28" s="31" t="s">
-        <v>3145</v>
-      </c>
-      <c r="C28" s="31" t="s">
-        <v>3146</v>
-      </c>
-      <c r="D28" s="31" t="s">
-        <v>3147</v>
-      </c>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
+      <c r="A28" s="30" t="s">
+        <v>3148</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>3149</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>3150</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>3151</v>
+      </c>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="28"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
+      <c r="A29" s="27"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" s="26" t="s">
-        <v>3148</v>
-      </c>
-      <c r="H30" s="31"/>
+      <c r="A30" s="25" t="s">
+        <v>3152</v>
+      </c>
+      <c r="H30" s="30"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" s="28" t="s">
-        <v>3149</v>
-      </c>
-      <c r="D31" s="28" t="s">
-        <v>3150</v>
-      </c>
-      <c r="F31" s="28" t="s">
-        <v>3151</v>
+      <c r="A31" s="27" t="s">
+        <v>3153</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>3154</v>
+      </c>
+      <c r="F31" s="27" t="s">
+        <v>3155</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" s="28" t="s">
-        <v>3152</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>3153</v>
-      </c>
-      <c r="F32" s="28" t="s">
-        <v>3154</v>
+      <c r="A32" s="27" t="s">
+        <v>3156</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>3157</v>
+      </c>
+      <c r="F32" s="27" t="s">
+        <v>3158</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" s="28" t="s">
-        <v>3155</v>
-      </c>
-      <c r="D33" s="28" t="s">
-        <v>3156</v>
-      </c>
-      <c r="F33" s="28" t="s">
-        <v>3157</v>
+      <c r="A33" s="27" t="s">
+        <v>3159</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>3160</v>
+      </c>
+      <c r="F33" s="27" t="s">
+        <v>3161</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" s="28" t="s">
-        <v>3158</v>
-      </c>
-      <c r="D34" s="28" t="s">
-        <v>3159</v>
-      </c>
-      <c r="F34" s="28" t="s">
-        <v>3160</v>
+      <c r="A34" s="27" t="s">
+        <v>3162</v>
+      </c>
+      <c r="D34" s="27" t="s">
+        <v>3163</v>
+      </c>
+      <c r="F34" s="27" t="s">
+        <v>3164</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" s="28" t="s">
-        <v>3161</v>
-      </c>
-      <c r="D35" s="28" t="s">
-        <v>3162</v>
-      </c>
-      <c r="F35" s="28" t="s">
-        <v>3163</v>
+      <c r="A35" s="27" t="s">
+        <v>3165</v>
+      </c>
+      <c r="D35" s="27" t="s">
+        <v>3166</v>
+      </c>
+      <c r="F35" s="27" t="s">
+        <v>3167</v>
       </c>
     </row>
   </sheetData>
@@ -30641,502 +30674,502 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="38" t="s">
-        <v>3164</v>
+      <c r="A1" s="37" t="s">
+        <v>3168</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="39" t="s">
-        <v>3165</v>
+      <c r="A2" s="38" t="s">
+        <v>3169</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>3166</v>
+        <v>3170</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>3167</v>
+        <v>3171</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>3168</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="39" t="s">
-        <v>3169</v>
+      <c r="A3" s="38" t="s">
+        <v>3173</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>3170</v>
+        <v>3174</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>3171</v>
+        <v>3175</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>3172</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="39" t="s">
-        <v>3173</v>
+      <c r="A4" s="38" t="s">
+        <v>3177</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>3174</v>
+        <v>3178</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>3175</v>
+        <v>3179</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>3176</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="40" t="s">
-        <v>3177</v>
+      <c r="A5" s="39" t="s">
+        <v>3181</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>3178</v>
+        <v>3182</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>3179</v>
+        <v>3183</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>3176</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="39" t="s">
-        <v>3180</v>
+      <c r="A6" s="38" t="s">
+        <v>3184</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>3181</v>
+        <v>3185</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>3182</v>
+        <v>3186</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>3183</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="39" t="s">
-        <v>3184</v>
+      <c r="A7" s="38" t="s">
+        <v>3188</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>3185</v>
+        <v>3189</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>3186</v>
+        <v>3190</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>3187</v>
+        <v>3191</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="39" t="s">
-        <v>3188</v>
+      <c r="A8" s="38" t="s">
+        <v>3192</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>3189</v>
+        <v>3193</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>3190</v>
+        <v>3194</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>3191</v>
+        <v>3195</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="39" t="s">
-        <v>3192</v>
+      <c r="A9" s="38" t="s">
+        <v>3196</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>3193</v>
+        <v>3197</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>3194</v>
+        <v>3198</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>3195</v>
+        <v>3199</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="39" t="s">
-        <v>3196</v>
+      <c r="A10" s="38" t="s">
+        <v>3200</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>3197</v>
+        <v>3201</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>3198</v>
+        <v>3202</v>
       </c>
       <c r="I10" s="8" t="s">
+        <v>3203</v>
+      </c>
+    </row>
+    <row r="11" ht="18.75" customHeight="1">
+      <c r="A11" s="38" t="s">
+        <v>3204</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>3205</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>3206</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>3199</v>
       </c>
     </row>
-    <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="39" t="s">
-        <v>3200</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>3201</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>3202</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>3195</v>
-      </c>
-    </row>
     <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="39" t="s">
-        <v>3203</v>
+      <c r="A12" s="38" t="s">
+        <v>3207</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>3204</v>
+        <v>3208</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>3205</v>
+        <v>3209</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>3206</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="39" t="s">
-        <v>3207</v>
+      <c r="A13" s="38" t="s">
+        <v>3211</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>3208</v>
+        <v>3212</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>3209</v>
+        <v>3213</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>3210</v>
+        <v>3214</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="40" t="s">
-        <v>3211</v>
+      <c r="A14" s="39" t="s">
+        <v>3215</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>3212</v>
+        <v>3216</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>3213</v>
+        <v>3217</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>3214</v>
+        <v>3218</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="31"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="40" t="s">
-        <v>3215</v>
-      </c>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
+      <c r="A16" s="39" t="s">
+        <v>3219</v>
+      </c>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="40" t="s">
-        <v>3216</v>
-      </c>
-      <c r="E17" s="40" t="s">
-        <v>3217</v>
-      </c>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
+      <c r="A17" s="39" t="s">
+        <v>3220</v>
+      </c>
+      <c r="E17" s="39" t="s">
+        <v>3221</v>
+      </c>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" s="31" t="s">
-        <v>3218</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>3219</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>3220</v>
-      </c>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
+      <c r="A18" s="30" t="s">
+        <v>3222</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>3223</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>3224</v>
+      </c>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" s="31" t="s">
-        <v>3221</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>3222</v>
-      </c>
-      <c r="E19" s="31" t="s">
+      <c r="A19" s="30" t="s">
+        <v>3225</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>3226</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>3227</v>
+      </c>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+    </row>
+    <row r="20" ht="18.75" customHeight="1">
+      <c r="A20" s="35" t="s">
+        <v>3228</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>3229</v>
+      </c>
+      <c r="E20" s="35" t="s">
+        <v>3230</v>
+      </c>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+    </row>
+    <row r="21" ht="18.75" customHeight="1">
+      <c r="J21" s="40"/>
+    </row>
+    <row r="22" ht="18.75" customHeight="1">
+      <c r="A22" s="30" t="s">
+        <v>3231</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>3232</v>
+      </c>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+    </row>
+    <row r="23" ht="18.75" customHeight="1">
+      <c r="A23" s="30" t="s">
+        <v>3233</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>3234</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>3235</v>
+      </c>
+      <c r="J23" s="40"/>
+    </row>
+    <row r="24" ht="18.75" customHeight="1">
+      <c r="A24" s="30" t="s">
+        <v>3236</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>3226</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>3237</v>
+      </c>
+      <c r="J24" s="40"/>
+    </row>
+    <row r="25" ht="18.75" customHeight="1">
+      <c r="A25" s="30" t="s">
+        <v>3238</v>
+      </c>
+      <c r="C25" s="30" t="s">
         <v>3223</v>
       </c>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-    </row>
-    <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="36" t="s">
-        <v>3224</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>3225</v>
-      </c>
-      <c r="E20" s="36" t="s">
+      <c r="E25" s="30" t="s">
+        <v>3239</v>
+      </c>
+      <c r="J25" s="40"/>
+    </row>
+    <row r="26" ht="18.75" customHeight="1">
+      <c r="A26" s="30" t="s">
+        <v>3240</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>3223</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>3241</v>
+      </c>
+      <c r="J26" s="40"/>
+    </row>
+    <row r="27" ht="18.75" customHeight="1">
+      <c r="A27" s="30" t="s">
+        <v>3242</v>
+      </c>
+      <c r="C27" s="30" t="s">
         <v>3226</v>
       </c>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-    </row>
-    <row r="21" ht="18.75" customHeight="1">
-      <c r="J21" s="41"/>
-    </row>
-    <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="31" t="s">
-        <v>3227</v>
-      </c>
-      <c r="E22" s="31" t="s">
-        <v>3228</v>
-      </c>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-    </row>
-    <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" s="31" t="s">
+      <c r="E27" s="30" t="s">
+        <v>3243</v>
+      </c>
+      <c r="J27" s="40"/>
+    </row>
+    <row r="28" ht="18.75" customHeight="1">
+      <c r="A28" s="30" t="s">
+        <v>3244</v>
+      </c>
+      <c r="C28" s="30" t="s">
         <v>3229</v>
       </c>
-      <c r="C23" s="31" t="s">
-        <v>3230</v>
-      </c>
-      <c r="E23" s="31" t="s">
-        <v>3231</v>
-      </c>
-      <c r="J23" s="41"/>
-    </row>
-    <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" s="31" t="s">
-        <v>3232</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>3222</v>
-      </c>
-      <c r="E24" s="31" t="s">
-        <v>3233</v>
-      </c>
-      <c r="J24" s="41"/>
-    </row>
-    <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="31" t="s">
-        <v>3234</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>3219</v>
-      </c>
-      <c r="E25" s="31" t="s">
-        <v>3235</v>
-      </c>
-      <c r="J25" s="41"/>
-    </row>
-    <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="31" t="s">
-        <v>3236</v>
-      </c>
-      <c r="C26" s="31" t="s">
-        <v>3219</v>
-      </c>
-      <c r="E26" s="31" t="s">
-        <v>3237</v>
-      </c>
-      <c r="J26" s="41"/>
-    </row>
-    <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="31" t="s">
-        <v>3238</v>
-      </c>
-      <c r="C27" s="31" t="s">
-        <v>3222</v>
-      </c>
-      <c r="E27" s="31" t="s">
-        <v>3239</v>
-      </c>
-      <c r="J27" s="41"/>
-    </row>
-    <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" s="31" t="s">
-        <v>3240</v>
-      </c>
-      <c r="C28" s="31" t="s">
-        <v>3225</v>
-      </c>
-      <c r="E28" s="31" t="s">
-        <v>3241</v>
-      </c>
-      <c r="J28" s="41"/>
+      <c r="E28" s="30" t="s">
+        <v>3245</v>
+      </c>
+      <c r="J28" s="40"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="41"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
+      <c r="A29" s="40"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" s="38" t="s">
-        <v>3242</v>
+      <c r="A30" s="37" t="s">
+        <v>3246</v>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" s="42" t="s">
-        <v>3243</v>
-      </c>
-      <c r="D31" s="42" t="s">
-        <v>3244</v>
-      </c>
-      <c r="G31" s="42" t="s">
-        <v>3245</v>
-      </c>
-      <c r="J31" s="31"/>
+      <c r="A31" s="41" t="s">
+        <v>3247</v>
+      </c>
+      <c r="D31" s="41" t="s">
+        <v>3248</v>
+      </c>
+      <c r="G31" s="41" t="s">
+        <v>3249</v>
+      </c>
+      <c r="J31" s="30"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
-      <c r="J32" s="31"/>
+      <c r="J32" s="30"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" s="43" t="s">
-        <v>3246</v>
-      </c>
-      <c r="D33" s="43" t="s">
-        <v>3247</v>
-      </c>
-      <c r="G33" s="43" t="s">
-        <v>3248</v>
-      </c>
-      <c r="J33" s="31"/>
+      <c r="A33" s="42" t="s">
+        <v>3250</v>
+      </c>
+      <c r="D33" s="42" t="s">
+        <v>3251</v>
+      </c>
+      <c r="G33" s="42" t="s">
+        <v>3252</v>
+      </c>
+      <c r="J33" s="30"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" s="43" t="s">
-        <v>3249</v>
-      </c>
-      <c r="D34" s="43" t="s">
-        <v>3250</v>
-      </c>
-      <c r="G34" s="43" t="s">
-        <v>3251</v>
-      </c>
-      <c r="J34" s="31"/>
+      <c r="A34" s="42" t="s">
+        <v>3253</v>
+      </c>
+      <c r="D34" s="42" t="s">
+        <v>3254</v>
+      </c>
+      <c r="G34" s="42" t="s">
+        <v>3255</v>
+      </c>
+      <c r="J34" s="30"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" s="43" t="s">
-        <v>3252</v>
-      </c>
-      <c r="D35" s="43" t="s">
-        <v>3253</v>
-      </c>
-      <c r="G35" s="43" t="s">
-        <v>3254</v>
-      </c>
-      <c r="J35" s="31"/>
+      <c r="A35" s="42" t="s">
+        <v>3256</v>
+      </c>
+      <c r="D35" s="42" t="s">
+        <v>3257</v>
+      </c>
+      <c r="G35" s="42" t="s">
+        <v>3258</v>
+      </c>
+      <c r="J35" s="30"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" s="43" t="s">
-        <v>3255</v>
-      </c>
-      <c r="D36" s="43" t="s">
-        <v>3256</v>
-      </c>
-      <c r="G36" s="43" t="s">
-        <v>3257</v>
-      </c>
-      <c r="J36" s="31"/>
+      <c r="A36" s="42" t="s">
+        <v>3259</v>
+      </c>
+      <c r="D36" s="42" t="s">
+        <v>3260</v>
+      </c>
+      <c r="G36" s="42" t="s">
+        <v>3261</v>
+      </c>
+      <c r="J36" s="30"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
-      <c r="A37" s="42" t="s">
-        <v>3258</v>
-      </c>
-      <c r="D37" s="42" t="s">
-        <v>3259</v>
-      </c>
-      <c r="G37" s="31"/>
-      <c r="J37" s="31"/>
+      <c r="A37" s="41" t="s">
+        <v>3262</v>
+      </c>
+      <c r="D37" s="41" t="s">
+        <v>3263</v>
+      </c>
+      <c r="G37" s="30"/>
+      <c r="J37" s="30"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
-      <c r="J38" s="41"/>
+      <c r="J38" s="40"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="8" t="s">
-        <v>3260</v>
-      </c>
-      <c r="D39" s="43" t="s">
-        <v>3261</v>
-      </c>
-      <c r="G39" s="43" t="s">
-        <v>3262</v>
-      </c>
-      <c r="J39" s="41"/>
+        <v>3264</v>
+      </c>
+      <c r="D39" s="42" t="s">
+        <v>3265</v>
+      </c>
+      <c r="G39" s="42" t="s">
+        <v>3266</v>
+      </c>
+      <c r="J39" s="40"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="8" t="s">
-        <v>3263</v>
-      </c>
-      <c r="D40" s="43" t="s">
-        <v>3264</v>
-      </c>
-      <c r="G40" s="43" t="s">
-        <v>3265</v>
-      </c>
-      <c r="J40" s="41"/>
+        <v>3267</v>
+      </c>
+      <c r="D40" s="42" t="s">
+        <v>3268</v>
+      </c>
+      <c r="G40" s="42" t="s">
+        <v>3269</v>
+      </c>
+      <c r="J40" s="40"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="8" t="s">
-        <v>3266</v>
-      </c>
-      <c r="D41" s="43" t="s">
-        <v>3267</v>
-      </c>
-      <c r="G41" s="43" t="s">
-        <v>3268</v>
-      </c>
-      <c r="J41" s="41"/>
+        <v>3270</v>
+      </c>
+      <c r="D41" s="42" t="s">
+        <v>3271</v>
+      </c>
+      <c r="G41" s="42" t="s">
+        <v>3272</v>
+      </c>
+      <c r="J41" s="40"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="8" t="s">
-        <v>3269</v>
-      </c>
-      <c r="D42" s="43" t="s">
-        <v>3270</v>
-      </c>
-      <c r="G42" s="43" t="s">
-        <v>3271</v>
-      </c>
-      <c r="J42" s="41"/>
+        <v>3273</v>
+      </c>
+      <c r="D42" s="42" t="s">
+        <v>3274</v>
+      </c>
+      <c r="G42" s="42" t="s">
+        <v>3275</v>
+      </c>
+      <c r="J42" s="40"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="8" t="s">
-        <v>3272</v>
-      </c>
-      <c r="D43" s="43" t="s">
-        <v>3273</v>
-      </c>
-      <c r="G43" s="43" t="s">
-        <v>3274</v>
-      </c>
-      <c r="J43" s="41"/>
+        <v>3276</v>
+      </c>
+      <c r="D43" s="42" t="s">
+        <v>3277</v>
+      </c>
+      <c r="G43" s="42" t="s">
+        <v>3278</v>
+      </c>
+      <c r="J43" s="40"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
-      <c r="J44" s="41"/>
+      <c r="J44" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="119">
